--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>55957</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.68499994277954</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>40805</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.68499994277954</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.61500000953674</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.68499994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.66499996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>81512</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.66499996185303</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.61500000953674</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.61500000953674</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>31009</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.70499992370605</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.70499992370605</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>72578</v>
+        <v>35831</v>
       </c>
       <c r="C2715" t="n">
-        <v>3.89499998092651</v>
+        <v>3.93499994277954</v>
       </c>
       <c r="D2715" t="n">
-        <v>3.84500002861023</v>
+        <v>3.89000010490417</v>
       </c>
       <c r="E2715" t="n">
-        <v>3.89499998092651</v>
+        <v>3.91499996185303</v>
       </c>
       <c r="F2715" t="n">
-        <v>3.84999990463257</v>
+        <v>3.91499996185303</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>55739</v>
+        <v>72578</v>
       </c>
       <c r="C2716" t="n">
-        <v>3.875</v>
+        <v>3.89499998092651</v>
       </c>
       <c r="D2716" t="n">
-        <v>3.77999997138977</v>
+        <v>3.84500002861023</v>
       </c>
       <c r="E2716" t="n">
-        <v>3.875</v>
+        <v>3.89499998092651</v>
       </c>
       <c r="F2716" t="n">
-        <v>3.77999997138977</v>
+        <v>3.84999990463257</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>63773</v>
+        <v>55739</v>
       </c>
       <c r="C2717" t="n">
-        <v>3.8050000667572</v>
+        <v>3.875</v>
       </c>
       <c r="D2717" t="n">
-        <v>3.70000004768372</v>
+        <v>3.77999997138977</v>
       </c>
       <c r="E2717" t="n">
-        <v>3.8050000667572</v>
+        <v>3.875</v>
       </c>
       <c r="F2717" t="n">
-        <v>3.70000004768372</v>
+        <v>3.77999997138977</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>113583</v>
+        <v>63773</v>
       </c>
       <c r="C2718" t="n">
-        <v>3.73000001907349</v>
+        <v>3.8050000667572</v>
       </c>
       <c r="D2718" t="n">
-        <v>3.61500000953674</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="E2718" t="n">
-        <v>3.65499997138977</v>
+        <v>3.8050000667572</v>
       </c>
       <c r="F2718" t="n">
-        <v>3.64000010490417</v>
+        <v>3.70000004768372</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>55957</v>
+        <v>113583</v>
       </c>
       <c r="C2719" t="n">
-        <v>3.69000005722046</v>
+        <v>3.73000001907349</v>
       </c>
       <c r="D2719" t="n">
-        <v>3.59999990463257</v>
+        <v>3.61500000953674</v>
       </c>
       <c r="E2719" t="n">
-        <v>3.625</v>
+        <v>3.65499997138977</v>
       </c>
       <c r="F2719" t="n">
-        <v>3.68499994277954</v>
+        <v>3.64000010490417</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>40805</v>
+        <v>55957</v>
       </c>
       <c r="C2720" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="F2720" t="n">
         <v>3.68499994277954</v>
-      </c>
-      <c r="D2720" t="n">
-        <v>3.61500000953674</v>
-      </c>
-      <c r="E2720" t="n">
-        <v>3.68499994277954</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>3.66499996185303</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>81512</v>
+        <v>40805</v>
       </c>
       <c r="C2721" t="n">
-        <v>3.66499996185303</v>
+        <v>3.68499994277954</v>
       </c>
       <c r="D2721" t="n">
         <v>3.61500000953674</v>
       </c>
       <c r="E2721" t="n">
-        <v>3.61500000953674</v>
+        <v>3.68499994277954</v>
       </c>
       <c r="F2721" t="n">
-        <v>3.66000008583069</v>
+        <v>3.66499996185303</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>31009</v>
+        <v>81512</v>
       </c>
       <c r="C2722" t="n">
-        <v>3.70499992370605</v>
+        <v>3.66499996185303</v>
       </c>
       <c r="D2722" t="n">
-        <v>3.64000010490417</v>
+        <v>3.61500000953674</v>
       </c>
       <c r="E2722" t="n">
-        <v>3.70499992370605</v>
+        <v>3.61500000953674</v>
       </c>
       <c r="F2722" t="n">
-        <v>3.6800000667572</v>
+        <v>3.66000008583069</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>151932</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>3.63499999046326</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235925674438</v>
+        <v>4.64235877990723</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37858915328979</v>
+        <v>4.37858867645264</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50783681869507</v>
+        <v>4.50783634185791</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176980018616</v>
+        <v>3.48176956176758</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74553918838501</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.81675744056702</v>
+        <v>3.8167576789856</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.89588928222656</v>
+        <v>3.89588904380798</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522176742554</v>
+        <v>3.83522200584412</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884552001953</v>
+        <v>3.80884456634521</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959713935852</v>
+        <v>3.67959761619568</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754149436951</v>
+        <v>3.92754101753235</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74553918838501</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617617607117</v>
+        <v>3.56617641448975</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65321969985962</v>
+        <v>3.6532199382782</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626123428345</v>
+        <v>3.37626147270203</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220399856567</v>
+        <v>3.44220447540283</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078462600708</v>
+        <v>3.5107843875885</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829382896423</v>
+        <v>3.79829406738281</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498916625977</v>
+        <v>3.73498892784119</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699051856995</v>
+        <v>3.91699075698853</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.81411981582642</v>
+        <v>3.81411957740784</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.84577322006226</v>
+        <v>3.84577250480652</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104775428772</v>
+        <v>3.8510479927063</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061379432678</v>
+        <v>3.89061403274536</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.0910792350769</v>
+        <v>4.09107875823975</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.0620641708374</v>
+        <v>4.06206512451172</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603658676147</v>
+        <v>4.18603610992432</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803865432739</v>
+        <v>4.36803817749023</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473327636719</v>
+        <v>4.30473279953003</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G55" t="n">
-        <v>4.41024160385132</v>
+        <v>4.41024208068848</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047372817993</v>
+        <v>4.51047420501709</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44716930389404</v>
+        <v>4.4471697807312</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G58" t="n">
-        <v>4.38914012908936</v>
+        <v>4.3891396522522</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583522796631</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.5161190032959</v>
       </c>
       <c r="G62" t="n">
-        <v>4.26516771316528</v>
+        <v>4.26516723632812</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G67" t="n">
-        <v>4.10426759719849</v>
+        <v>4.10426807403564</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G73" t="n">
-        <v>4.2467041015625</v>
+        <v>4.24670362472534</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G76" t="n">
-        <v>4.15438461303711</v>
+        <v>4.15438413619995</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241331100464</v>
+        <v>4.2124137878418</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G85" t="n">
-        <v>4.17284822463989</v>
+        <v>4.17284774780273</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119482040405</v>
+        <v>4.14119625091553</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009334564209</v>
+        <v>4.12009382247925</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G88" t="n">
-        <v>4.10426759719849</v>
+        <v>4.10426807403564</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383268356323</v>
+        <v>4.14383363723755</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G92" t="n">
-        <v>4.15438461303711</v>
+        <v>4.15438413619995</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G94" t="n">
-        <v>4.23351430892944</v>
+        <v>4.2335147857666</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044296264648</v>
+        <v>4.27044343948364</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G97" t="n">
-        <v>4.23615264892578</v>
+        <v>4.23615312576294</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G98" t="n">
-        <v>4.15174627304077</v>
+        <v>4.15174579620361</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.51147079467773</v>
       </c>
       <c r="G102" t="n">
-        <v>4.48687314987183</v>
+        <v>4.48687362670898</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743726730347</v>
+        <v>4.46743774414062</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768479347229</v>
+        <v>3.91768527030945</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989706039429</v>
+        <v>3.93989729881287</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.89269661903381</v>
+        <v>3.8926956653595</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="n">
-        <v>3.69278573989868</v>
+        <v>3.6927855014801</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="n">
-        <v>4.01208734512329</v>
+        <v>4.01208686828613</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603735923767</v>
+        <v>3.87603712081909</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.7316575050354</v>
+        <v>3.73165726661682</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111536979675</v>
+        <v>3.70111560821533</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328271865845</v>
+        <v>3.82328248023987</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.94822716712952</v>
+        <v>3.94822645187378</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35915327072144</v>
+        <v>4.35915422439575</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.29806852340698</v>
+        <v>4.2980694770813</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583522796631</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025880813599</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637617111206</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="n">
-        <v>4.23420906066895</v>
+        <v>4.2342095375061</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917644500732</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644330978394</v>
+        <v>4.20644378662109</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16201877593994</v>
+        <v>4.1620192527771</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317066192627</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="n">
-        <v>4.11204242706299</v>
+        <v>4.11204195022583</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150100708008</v>
+        <v>4.08150005340576</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00931072235107</v>
+        <v>4.00931024551392</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9704384803772</v>
+        <v>3.97043871879578</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="n">
-        <v>4.05928754806519</v>
+        <v>4.05928802490234</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152227401733</v>
+        <v>4.03152179718018</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502141952515</v>
+        <v>3.66502070426941</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389151573181</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504292488098</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.61781883239746</v>
+        <v>3.6178195476532</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000911712646</v>
+        <v>3.69000959396362</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224384307861</v>
+        <v>3.66224408149719</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="n">
-        <v>3.67612624168396</v>
+        <v>3.67612648010254</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.61781883239746</v>
+        <v>3.6178195476532</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502141952515</v>
+        <v>3.66502070426941</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504292488098</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838366508484</v>
+        <v>3.59838342666626</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58172416687012</v>
+        <v>3.58172464370728</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660147666931</v>
+        <v>3.85660123825073</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046165466309</v>
+        <v>3.92046141624451</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488571166992</v>
+        <v>3.96488547325134</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.94822716712952</v>
+        <v>3.94822645187378</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="n">
-        <v>3.97321486473083</v>
+        <v>3.97321534156799</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.94267296791077</v>
+        <v>3.9426736831665</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547276496887</v>
+        <v>3.89547252655029</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.89269661903381</v>
+        <v>3.8926956653595</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438944816589</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608203887939</v>
+        <v>3.77608180046082</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107116699219</v>
+        <v>3.80107045173645</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.78718733787537</v>
+        <v>3.78718852996826</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="n">
-        <v>3.75942254066467</v>
+        <v>3.75942230224609</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="n">
-        <v>3.67612624168396</v>
+        <v>3.67612648010254</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.71222138404846</v>
+        <v>3.71222162246704</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504292488098</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059617042542</v>
+        <v>3.62059593200684</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51508736610413</v>
+        <v>3.51508760452271</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007697105408</v>
+        <v>3.54007649421692</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897024154663</v>
+        <v>3.52897071838379</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400333404541</v>
+        <v>3.45400357246399</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398182868958</v>
+        <v>3.50398230552673</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842834472656</v>
+        <v>3.49842858314514</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174781799316</v>
+        <v>3.53174734115601</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732280731201</v>
+        <v>3.48732209205627</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057418823242</v>
+        <v>3.67057371139526</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389151573181</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050633430481</v>
+        <v>3.82050609588623</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.78718733787537</v>
+        <v>3.78718852996826</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608203887939</v>
+        <v>3.77608180046082</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.92879104614258</v>
+        <v>3.92879056930542</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102553367615</v>
+        <v>3.90102601051331</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98709750175476</v>
+        <v>3.98709774017334</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599267959595</v>
+        <v>3.97599220275879</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="n">
-        <v>4.21477365493774</v>
+        <v>4.2147741317749</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="n">
-        <v>4.13147783279419</v>
+        <v>4.13147735595703</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533729553223</v>
+        <v>4.19533777236938</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="n">
-        <v>4.15091276168823</v>
+        <v>4.15091323852539</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481809616089</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="n">
-        <v>4.07872343063354</v>
+        <v>4.0787239074707</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484127044678</v>
+        <v>4.06484079360962</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377993583679</v>
+        <v>3.95377945899963</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438944816589</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86493039131165</v>
+        <v>3.86493062973022</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="n">
-        <v>3.92601466178894</v>
+        <v>3.92601370811462</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599267959595</v>
+        <v>3.97599220275879</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="n">
-        <v>4.16201877593994</v>
+        <v>4.1620192527771</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317066192627</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.353600025177</v>
+        <v>4.35360050201416</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025880813599</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637617111206</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="n">
-        <v>4.22310256958008</v>
+        <v>4.22310304641724</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917644500732</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134260177612</v>
+        <v>4.43134307861328</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188449859619</v>
+        <v>4.46188497543335</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="n">
-        <v>4.40913152694702</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351066589355</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.54240369796753</v>
+        <v>4.542405128479</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="n">
-        <v>4.63402938842773</v>
+        <v>4.63402986526489</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351066589355</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685188293457</v>
+        <v>4.53685140609741</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G326" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G327" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132038116455</v>
+        <v>4.48132085800171</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="n">
-        <v>4.40913152694702</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691902160645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691902160645</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="n">
-        <v>4.36748266220093</v>
+        <v>4.36748218536377</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244909286499</v>
+        <v>4.44244956970215</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="n">
-        <v>4.54795694351196</v>
+        <v>4.54795742034912</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075674057007</v>
+        <v>4.50075531005859</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="n">
-        <v>4.57849884033203</v>
+        <v>4.57849836349487</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793567657471</v>
+        <v>4.59793519973755</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127546310425</v>
+        <v>4.58127593994141</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="n">
-        <v>4.75342082977295</v>
+        <v>4.75342035293579</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="n">
-        <v>4.77563285827637</v>
+        <v>4.77563333511353</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895090103149</v>
+        <v>4.80895137786865</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010278701782</v>
+        <v>4.72010231018066</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="n">
-        <v>4.69233655929565</v>
+        <v>4.69233703613281</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="n">
-        <v>4.65901851654053</v>
+        <v>4.65901899337769</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423746109009</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865699768066</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865699768066</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="n">
-        <v>4.72144651412964</v>
+        <v>4.7214469909668</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.71571016311646</v>
+        <v>4.7157096862793</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="n">
-        <v>4.60384130477905</v>
+        <v>4.60384082794189</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655120849609</v>
+        <v>4.56655168533325</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786659240723</v>
+        <v>4.53786706924438</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507755279541</v>
+        <v>4.55507802963257</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="n">
-        <v>4.64686727523804</v>
+        <v>4.64686822891235</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66121006011963</v>
+        <v>4.66120958328247</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="n">
-        <v>4.76447296142578</v>
+        <v>4.7644739151001</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="n">
-        <v>4.7702112197876</v>
+        <v>4.77021026611328</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="n">
-        <v>4.80750036239624</v>
+        <v>4.80749988555908</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="n">
-        <v>4.77881574630737</v>
+        <v>4.77881622314453</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757902145386</v>
+        <v>4.82757949829102</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="n">
-        <v>4.87060594558716</v>
+        <v>4.87060689926147</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="n">
-        <v>4.81036853790283</v>
+        <v>4.81036901473999</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="n">
-        <v>4.94518613815308</v>
+        <v>4.94518566131592</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="n">
-        <v>4.93084335327148</v>
+        <v>4.93084287643433</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215921401978</v>
+        <v>4.90215826034546</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052633285522</v>
+        <v>4.85052680969238</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="n">
-        <v>4.87347412109375</v>
+        <v>4.87347459793091</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.8878173828125</v>
+        <v>4.88781690597534</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99107980728149</v>
+        <v>4.99108028411865</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="n">
-        <v>5.06565856933594</v>
+        <v>5.0656590461731</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713317871094</v>
+        <v>5.0771336555481</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="n">
-        <v>4.98247528076172</v>
+        <v>4.98247480392456</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="n">
-        <v>5.0312385559082</v>
+        <v>5.03123807907104</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="n">
-        <v>5.4500298500061</v>
+        <v>5.45003032684326</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="n">
-        <v>5.4500298500061</v>
+        <v>5.45003032684326</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871494293213</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="n">
-        <v>5.27505445480347</v>
+        <v>5.27505493164062</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397743225098</v>
+        <v>5.36397695541382</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="n">
-        <v>5.39839839935303</v>
+        <v>5.39839744567871</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70819044113159</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="n">
-        <v>5.98356008529663</v>
+        <v>5.98355960845947</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766450881958</v>
+        <v>5.93766498565674</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292604446411</v>
+        <v>5.82292652130127</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555824279785</v>
+        <v>5.76555871963501</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="n">
-        <v>5.79424238204956</v>
+        <v>5.79424285888672</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="n">
-        <v>6.12124443054199</v>
+        <v>6.12124538421631</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061182022095</v>
+        <v>5.96061134338379</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287588119507</v>
+        <v>6.17287635803223</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="n">
-        <v>6.10977029800415</v>
+        <v>6.10977077484131</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="n">
-        <v>6.20729684829712</v>
+        <v>6.20729732513428</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="n">
-        <v>6.17861366271973</v>
+        <v>6.17861270904541</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36793088912964</v>
+        <v>6.36793041229248</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="n">
-        <v>6.48266696929932</v>
+        <v>6.48266649246216</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="n">
-        <v>6.48266696929932</v>
+        <v>6.48266649246216</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.42529916763306</v>
+        <v>6.4252986907959</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319194793701</v>
+        <v>6.25319147109985</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="n">
-        <v>5.62213659286499</v>
+        <v>5.62213611602783</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476736068726</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="n">
-        <v>5.60492515563965</v>
+        <v>5.60492610931396</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.48158359527588</v>
+        <v>5.48158264160156</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="n">
-        <v>5.61353015899658</v>
+        <v>5.61353063583374</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460861206055</v>
+        <v>5.52460908889771</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476736068726</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.6508207321167</v>
+        <v>5.65082120895386</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655708312988</v>
+        <v>5.6565580368042</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70819044113159</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903100967407</v>
+        <v>5.55903148651123</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="n">
-        <v>5.50739860534668</v>
+        <v>5.50739812850952</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345149993896</v>
+        <v>5.59345245361328</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="n">
-        <v>5.50739860534668</v>
+        <v>5.50739812850952</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="n">
-        <v>5.50739860534668</v>
+        <v>5.50739812850952</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.495924949646</v>
+        <v>5.49592447280884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871494293213</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="n">
-        <v>5.50739860534668</v>
+        <v>5.50739812850952</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.46150302886963</v>
+        <v>5.46150398254395</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171194076538</v>
+        <v>5.15171241760254</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="n">
-        <v>5.0312385559082</v>
+        <v>5.03123807907104</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="n">
-        <v>4.97386884689331</v>
+        <v>4.97386932373047</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="n">
-        <v>5.12302875518799</v>
+        <v>5.12302827835083</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913228988647</v>
+        <v>4.85913181304932</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="n">
-        <v>4.72144651412964</v>
+        <v>4.7214469909668</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423746109009</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="n">
-        <v>4.82471084594727</v>
+        <v>4.82471132278442</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849872589111</v>
+        <v>4.69849967956543</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="n">
-        <v>4.68128871917725</v>
+        <v>4.6812891960144</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239519119263</v>
+        <v>4.96239614486694</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71571016311646</v>
+        <v>4.7157096862793</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245662689209</v>
+        <v>4.54245615005493</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="n">
-        <v>4.42657136917114</v>
+        <v>4.4265718460083</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="n">
-        <v>4.31126022338867</v>
+        <v>4.31126070022583</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057744979858</v>
+        <v>4.50057697296143</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401926040649</v>
+        <v>4.50401973724365</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="n">
-        <v>4.39444541931152</v>
+        <v>4.39444494247437</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.3078179359436</v>
+        <v>4.30781841278076</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.41232681274414</v>
+        <v>4.4123272895813</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>4.49069976806641</v>
+        <v>4.49069929122925</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="n">
-        <v>4.9232931137085</v>
+        <v>4.92329263687134</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262052536011</v>
+        <v>4.68262004852295</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="n">
-        <v>4.96278762817383</v>
+        <v>4.96278810501099</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="n">
-        <v>4.9954948425293</v>
+        <v>4.99549436569214</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628034591675</v>
+        <v>4.83628082275391</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.85479402542114</v>
+        <v>4.8547945022583</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>4.83936643600464</v>
+        <v>4.83936595916748</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>4.76161003112793</v>
+        <v>4.76161050796509</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="n">
-        <v>4.75235366821289</v>
+        <v>4.75235462188721</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430265426636</v>
+        <v>4.84430313110352</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="n">
-        <v>4.9368691444397</v>
+        <v>4.93686866760254</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132953643799</v>
+        <v>4.88132905960083</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>4.89120292663574</v>
+        <v>4.89120388031006</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029081344604</v>
+        <v>5.0602912902832</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031999588013</v>
+        <v>4.96031904220581</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="n">
-        <v>4.9368691444397</v>
+        <v>4.93686866760254</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.80357360839844</v>
+        <v>4.8035740852356</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="n">
-        <v>4.59684228897095</v>
+        <v>4.59684181213379</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>4.49872255325317</v>
+        <v>4.49872207641602</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.39072847366333</v>
+        <v>4.39072799682617</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>4.17474031448364</v>
+        <v>4.17473983764648</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="n">
-        <v>4.41294384002686</v>
+        <v>4.41294431686401</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="n">
-        <v>4.46786642074585</v>
+        <v>4.46786689758301</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="n">
-        <v>4.56290197372437</v>
+        <v>4.56290149688721</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.64991331100464</v>
+        <v>4.6499137878418</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.51908731460571</v>
+        <v>4.51908683776855</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="n">
-        <v>4.42528581619263</v>
+        <v>4.42528629302979</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716499328613</v>
+        <v>4.71716547012329</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="n">
-        <v>4.80870962142944</v>
+        <v>4.80870914459229</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.68996715545654</v>
+        <v>4.6899676322937</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="n">
-        <v>4.64353275299072</v>
+        <v>4.64353179931641</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="n">
-        <v>4.56061172485352</v>
+        <v>4.56061267852783</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="n">
-        <v>4.64353275299072</v>
+        <v>4.64353179931641</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60174036026001</v>
+        <v>4.60173988342285</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.74303722381592</v>
+        <v>4.74303674697876</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273818969727</v>
+        <v>4.80273914337158</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="n">
-        <v>4.68930435180664</v>
+        <v>4.68930387496948</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094722747803</v>
+        <v>4.76094770431519</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637186050415</v>
+        <v>4.87637281417847</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="n">
-        <v>4.81666994094849</v>
+        <v>4.81666946411133</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.6873140335083</v>
+        <v>4.68731355667114</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="n">
-        <v>4.8093729019165</v>
+        <v>4.80937242507935</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="n">
-        <v>4.73043298721313</v>
+        <v>4.73043251037598</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="n">
-        <v>4.79676866531372</v>
+        <v>4.79676818847656</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="n">
-        <v>4.76492738723755</v>
+        <v>4.76492786407471</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="n">
-        <v>4.59776020050049</v>
+        <v>4.59776067733765</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="n">
-        <v>4.38283109664917</v>
+        <v>4.38283157348633</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30588150024414</v>
+        <v>4.30588102340698</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="n">
-        <v>4.32445478439331</v>
+        <v>4.32445526123047</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.36027669906616</v>
+        <v>4.360276222229</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44386053085327</v>
+        <v>4.44385957717896</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589973449707</v>
+        <v>4.43589925765991</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145517349243</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="n">
-        <v>4.3476734161377</v>
+        <v>4.34767293930054</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="n">
-        <v>4.3569598197937</v>
+        <v>4.35696029663086</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.57200002670288</v>
       </c>
       <c r="G685" t="n">
-        <v>4.35961294174194</v>
+        <v>4.3596134185791</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="n">
-        <v>4.36558389663696</v>
+        <v>4.3655834197998</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="n">
-        <v>4.32710886001587</v>
+        <v>4.32710838317871</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="n">
-        <v>4.49029541015625</v>
+        <v>4.49029636383057</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739404678345</v>
+        <v>4.53739452362061</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="n">
-        <v>4.54469108581543</v>
+        <v>4.54469060897827</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012813568115</v>
+        <v>4.39012765884399</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010894775391</v>
+        <v>4.26010942459106</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="n">
-        <v>4.0737042427063</v>
+        <v>4.07370471954346</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>4.05645751953125</v>
+        <v>4.05645704269409</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599168777466</v>
+        <v>4.0159912109375</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312097549438</v>
+        <v>3.92312121391296</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>3.94899225234985</v>
+        <v>3.94899296760559</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.84749794006348</v>
+        <v>3.84749817848206</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648697853088</v>
+        <v>3.91648769378662</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="n">
-        <v>3.95297288894653</v>
+        <v>3.95297265052795</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.90720009803772</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026968955994</v>
+        <v>3.96026945114136</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>3.94700193405151</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>3.94700193405151</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="n">
-        <v>3.98614072799683</v>
+        <v>3.98614048957825</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="n">
-        <v>4.13473415374756</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>4.13871383666992</v>
+        <v>4.13871335983276</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="n">
-        <v>4.12544679641724</v>
+        <v>4.12544631958008</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04716968536377</v>
+        <v>4.04717063903809</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>3.98945760726929</v>
+        <v>3.98945713043213</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766616821289</v>
+        <v>3.94766569137573</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="n">
-        <v>3.89061641693115</v>
+        <v>3.89061665534973</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260649681091</v>
+        <v>3.89260673522949</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184449195862</v>
+        <v>3.91184401512146</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="n">
-        <v>3.99940729141235</v>
+        <v>3.99940800666809</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503175735474</v>
+        <v>4.07503080368042</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.96889281272888</v>
+        <v>3.96889305114746</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189337730408</v>
+        <v>3.90189385414124</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.90720009803772</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88729977607727</v>
+        <v>3.88730001449585</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.85214185714722</v>
+        <v>3.8521420955658</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811138153076</v>
+        <v>3.85811185836792</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219121932983</v>
+        <v>3.84219098091125</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.737380027771</v>
+        <v>3.73737978935242</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848899841309</v>
+        <v>3.64848971366882</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.57950043678284</v>
+        <v>3.57950019836426</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490612030029</v>
+        <v>3.56490659713745</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205388069153</v>
+        <v>3.60205435752869</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="n">
-        <v>3.6962513923645</v>
+        <v>3.69625210762024</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="n">
-        <v>3.76258754730225</v>
+        <v>3.76258778572083</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="n">
-        <v>3.83821105957031</v>
+        <v>3.83821082115173</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.91980457305908</v>
+        <v>3.91980385780334</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587377548218</v>
+        <v>3.90587401390076</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444801330566</v>
+        <v>3.92444825172424</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479474067688</v>
+        <v>3.85479521751404</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.89857649803162</v>
+        <v>3.89857697486877</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="n">
-        <v>3.88000249862671</v>
+        <v>3.88000297546387</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.9151611328125</v>
+        <v>3.91516041755676</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="n">
-        <v>3.87204217910767</v>
+        <v>3.87204241752625</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025050163269</v>
+        <v>3.83025097846985</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="n">
-        <v>3.92842817306519</v>
+        <v>3.92842793464661</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287344932556</v>
+        <v>3.97287368774414</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657495498657</v>
+        <v>4.16657543182373</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937711715698</v>
+        <v>4.13937664031982</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090255737305</v>
+        <v>4.10090208053589</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09957551956177</v>
+        <v>4.09957504272461</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947631835938</v>
+        <v>4.11947679519653</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.11284303665161</v>
+        <v>4.11284255981445</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078369140625</v>
+        <v>3.99078392982483</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017024993896</v>
+        <v>3.98017072677612</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567608833313</v>
+        <v>3.94567537307739</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680400848389</v>
+        <v>3.98680424690247</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="n">
-        <v>4.02461576461792</v>
+        <v>4.02461528778076</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="n">
-        <v>4.07038736343384</v>
+        <v>4.070387840271</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>4.06640768051147</v>
+        <v>4.06640720367432</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="n">
-        <v>4.13473415374756</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="n">
-        <v>4.18448543548584</v>
+        <v>4.184485912323</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="n">
-        <v>4.34501886367798</v>
+        <v>4.34501981735229</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531694412231</v>
+        <v>4.28531742095947</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="n">
-        <v>4.29195070266724</v>
+        <v>4.29194974899292</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609861373901</v>
+        <v>4.39609813690186</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="n">
-        <v>4.41666221618652</v>
+        <v>4.41666269302368</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759244918823</v>
+        <v>4.49759292602539</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069269180298</v>
+        <v>4.41069173812866</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="n">
-        <v>4.30057430267334</v>
+        <v>4.30057382583618</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408910751343</v>
+        <v>4.26408958435059</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>4.30521774291992</v>
+        <v>4.30521726608276</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482046127319</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36491966247559</v>
+        <v>4.36492013931274</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145517349243</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>4.42462253570557</v>
+        <v>4.42462301254272</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511854171753</v>
+        <v>4.32511806488037</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>4.40472173690796</v>
+        <v>4.40472221374512</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>4.46442461013794</v>
+        <v>4.4644250869751</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066204071045</v>
+        <v>4.55066156387329</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49095869064331</v>
+        <v>4.49095916748047</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838605880737</v>
+        <v>4.33838558197021</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482046127319</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52835035324097</v>
+        <v>4.52834987640381</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140874862671</v>
+        <v>4.57140970230103</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G863" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G864" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G874" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>4.29152727127075</v>
+        <v>4.29152679443359</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G880" t="n">
-        <v>4.26999711990356</v>
+        <v>4.26999759674072</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>4.34893846511841</v>
+        <v>4.34893894195557</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>4.33458518981934</v>
+        <v>4.33458566665649</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>4.26999711990356</v>
+        <v>4.26999759674072</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>4.24846887588501</v>
+        <v>4.24846792221069</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411512374878</v>
+        <v>4.23411560058594</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129104614258</v>
+        <v>4.24129152297974</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776210784912</v>
+        <v>4.09776258468628</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>4.05470371246338</v>
+        <v>4.05470323562622</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G915" t="n">
-        <v>4.04752683639526</v>
+        <v>4.04752635955811</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87529158592224</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246846199036</v>
+        <v>3.88246870040894</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764512062073</v>
+        <v>3.76764488220215</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764512062073</v>
+        <v>3.76764488220215</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940935134888</v>
+        <v>3.83940887451172</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.83223295211792</v>
+        <v>3.8322331905365</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.87529158592224</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423316955566</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G938" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G944" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293900489807</v>
+        <v>3.98293876647949</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423316955566</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G957" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G958" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>4.09058618545532</v>
+        <v>4.09058570861816</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G965" t="n">
-        <v>4.11929225921631</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>4.14082050323486</v>
+        <v>4.14082145690918</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211538314819</v>
+        <v>4.11211490631104</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646770477295</v>
+        <v>4.12646818161011</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799833297729</v>
+        <v>4.14799737930298</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646770477295</v>
+        <v>4.12646818161011</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>4.33458518981934</v>
+        <v>4.33458566665649</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G990" t="n">
-        <v>4.33458518981934</v>
+        <v>4.33458566665649</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G992" t="n">
-        <v>4.33458518981934</v>
+        <v>4.33458566665649</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870271682739</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G996" t="n">
-        <v>4.57858610153198</v>
+        <v>4.57858562469482</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552675247192</v>
+        <v>4.53552722930908</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.51399755477905</v>
+        <v>4.51399707794189</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870271682739</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.50682067871094</v>
+        <v>4.5068211555481</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270315170288</v>
+        <v>4.54270267486572</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140874862671</v>
+        <v>4.57140970230103</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.11929225921631</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.93987965583801</v>
+        <v>3.93987989425659</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505679130554</v>
+        <v>3.82505631446838</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.78917479515076</v>
+        <v>3.7891743183136</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.25811576843262</v>
+        <v>3.25811553001404</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299847602844</v>
+        <v>2.62299823760986</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605710983276</v>
+        <v>2.66605734825134</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076298713684</v>
+        <v>2.45076322555542</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.55482220649719</v>
+        <v>2.55482196807861</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.6768217086792</v>
+        <v>2.67682218551636</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.61223411560059</v>
+        <v>2.61223387718201</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423361778259</v>
+        <v>2.73423385620117</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705698013306</v>
+        <v>2.72705721855164</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505771636963</v>
+        <v>2.60505723953247</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.64093971252441</v>
+        <v>2.64093947410583</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.59788060188293</v>
+        <v>2.59788084030151</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329300880432</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.55482220649719</v>
+        <v>2.55482196807861</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.59788060188293</v>
+        <v>2.59788084030151</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511578559875</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.3682336807251</v>
+        <v>2.36823391914368</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.31799864768982</v>
+        <v>2.3179988861084</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.38258671760559</v>
+        <v>2.38258695602417</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.25699877738953</v>
+        <v>2.25699853897095</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.25699877738953</v>
+        <v>2.25699853897095</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105751991272</v>
+        <v>2.36105728149414</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005741119385</v>
+        <v>2.30005764961243</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.33235144615173</v>
+        <v>2.33235168457031</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876348495483</v>
+        <v>2.32876324653625</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.42564558982849</v>
+        <v>2.42564582824707</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893997192383</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81317472457886</v>
+        <v>2.81317520141602</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511578559875</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.411292552948</v>
+        <v>2.41129279136658</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.49023389816284</v>
+        <v>2.49023365974426</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329300880432</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893997192383</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.56775832176208</v>
+        <v>2.56775856018066</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.53709864616394</v>
+        <v>2.53709888458252</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344421386719</v>
+        <v>2.48344397544861</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.44511914253235</v>
+        <v>2.44511938095093</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.5064389705658</v>
+        <v>2.50643873214722</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.46044945716858</v>
+        <v>2.46044921875</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.44511914253235</v>
+        <v>2.44511938095093</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679478645325</v>
+        <v>2.40679454803467</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481528282166</v>
+        <v>2.31481504440308</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.39912962913513</v>
+        <v>2.39912986755371</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.4259569644928</v>
+        <v>2.42595720291138</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.125</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.39529705047607</v>
+        <v>2.39529728889465</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.47961139678955</v>
+        <v>2.47961163520813</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715012550354</v>
+        <v>2.30715036392212</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.25349545478821</v>
+        <v>2.25349569320679</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.36080503463745</v>
+        <v>2.36080479621887</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.43362212181091</v>
+        <v>2.43362188339233</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283601760864</v>
+        <v>2.22283554077148</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750570297241</v>
+        <v>2.20750617980957</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.89707541465759</v>
+        <v>1.8970752954483</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.01971435546875</v>
+        <v>2.01971459388733</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138988018036</v>
+        <v>1.98138976097107</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877381324768</v>
+        <v>2.49877405166626</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291049003601</v>
+        <v>2.63291072845459</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.67506790161133</v>
+        <v>2.67506766319275</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087998390198</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.5</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.68273258209229</v>
+        <v>2.68273305892944</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.75938248634338</v>
+        <v>2.7593822479248</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.83603191375732</v>
+        <v>2.83603167533875</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087998390198</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82070207595825</v>
+        <v>2.82070183753967</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87818908691406</v>
+        <v>2.87818932533264</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651391983032</v>
+        <v>2.9165141582489</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849318504333</v>
+        <v>3.00849342346191</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567633628845</v>
+        <v>2.93567609786987</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.99699592590332</v>
+        <v>2.9969961643219</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.92034602165222</v>
+        <v>2.92034649848938</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.67123556137085</v>
+        <v>2.67123532295227</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.65973806381226</v>
+        <v>2.65973782539368</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.62907814979553</v>
+        <v>2.62907838821411</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.71722507476807</v>
+        <v>2.71722531318665</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.18478751182556</v>
+        <v>3.18478727340698</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676701545715</v>
+        <v>3.27676653862</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12346768379211</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.09280776977539</v>
+        <v>3.09280753135681</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.28826403617859</v>
+        <v>3.28826379776001</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.5412073135376</v>
+        <v>3.54120755195618</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.56036996841431</v>
+        <v>3.56036972999573</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.56420230865479</v>
+        <v>3.56420254707336</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737449645996</v>
+        <v>3.53737473487854</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054739952087</v>
+        <v>3.51054716110229</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557337760925</v>
+        <v>3.39557313919067</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33425354957581</v>
+        <v>3.33425378799438</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.33042120933533</v>
+        <v>3.33042097091675</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.31892371177673</v>
+        <v>3.31892395019531</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.18478751182556</v>
+        <v>3.18478727340698</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927928924561</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.07747793197632</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.07747793197632</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.12346768379211</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610662460327</v>
+        <v>3.24610686302185</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166608810425</v>
+        <v>2.98166584968567</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.05831527709961</v>
+        <v>3.05831551551819</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.875</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.97016835212708</v>
+        <v>2.97016859054565</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.86669158935547</v>
+        <v>2.86669182777405</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387474060059</v>
+        <v>2.79387450218201</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268110275269</v>
+        <v>2.91268134117126</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.99699592590332</v>
+        <v>2.9969961643219</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.07747793197632</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214761734009</v>
+        <v>3.06214809417725</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.05831527709961</v>
+        <v>3.05831551551819</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.94334125518799</v>
+        <v>2.94334101676941</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651391983032</v>
+        <v>2.9165141582489</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.82453417778015</v>
+        <v>2.82453441619873</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.09280776977539</v>
+        <v>3.09280753135681</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927928924561</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.12346768379211</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.24227428436279</v>
+        <v>3.24227452278137</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.40707063674927</v>
+        <v>3.40707087516785</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.45306038856506</v>
+        <v>3.45306062698364</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.07747793197632</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844194412231</v>
+        <v>3.23844170570374</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059911727905</v>
+        <v>3.28059935569763</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.27293419837952</v>
+        <v>3.27293395996094</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.3419189453125</v>
+        <v>3.34191870689392</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491346359253</v>
+        <v>3.36491322517395</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.3495831489563</v>
+        <v>3.34958338737488</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.41856837272644</v>
+        <v>3.41856813430786</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.42240071296692</v>
+        <v>3.4224009513855</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.4262330532074</v>
+        <v>3.42623281478882</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.33425354957581</v>
+        <v>3.33425378799438</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.3419189453125</v>
+        <v>3.34191870689392</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.42240071296692</v>
+        <v>3.4224009513855</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.46455812454224</v>
+        <v>3.46455788612366</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372006416321</v>
+        <v>3.48372030258179</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.56420230865479</v>
+        <v>3.56420254707336</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.54887223243713</v>
+        <v>3.54887247085571</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.49138474464417</v>
+        <v>3.49138498306274</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.49138474464417</v>
+        <v>3.49138498306274</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.5067150592804</v>
+        <v>3.50671482086182</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.54887223243713</v>
+        <v>3.54887247085571</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.4607253074646</v>
+        <v>3.46072554588318</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371388435364</v>
+        <v>3.21371364593506</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804184913635</v>
+        <v>3.26804208755493</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251901626587</v>
+        <v>3.37251877784729</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087725639343</v>
+        <v>3.38087701797485</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.0758044719696</v>
+        <v>3.07580399513245</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132706642151</v>
+        <v>2.97132730484009</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78326821327209</v>
+        <v>2.78326845169067</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595489501953</v>
+        <v>2.84595465660095</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.0883412361145</v>
+        <v>3.08834147453308</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893902778625</v>
+        <v>3.00893878936768</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.975506067276</v>
+        <v>2.97550630569458</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.96296882629395</v>
+        <v>2.96296906471252</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729702949524</v>
+        <v>3.01729679107666</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.95461082458496</v>
+        <v>2.95461106300354</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.82923817634583</v>
+        <v>2.8292384147644</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147748947144</v>
+        <v>2.74147772789001</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.83341765403748</v>
+        <v>2.8334174156189</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.74983596801758</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.69968700408936</v>
+        <v>2.69968676567078</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.26924133300781</v>
+        <v>2.26924157142639</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.23998808860779</v>
+        <v>2.23998785018921</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177881240845</v>
+        <v>2.28177857398987</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.22745060920715</v>
+        <v>2.22745037078857</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.5032696723938</v>
+        <v>2.50326991081238</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744915008545</v>
+        <v>2.50744891166687</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849359512329</v>
+        <v>2.57849335670471</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685183525085</v>
+        <v>2.5868513584137</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.55759811401367</v>
+        <v>2.55759787559509</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.62864232063293</v>
+        <v>2.62864255905151</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.70386552810669</v>
+        <v>2.70386576652527</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.72058248519897</v>
+        <v>2.7205822467804</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282155990601</v>
+        <v>2.63282179832458</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297076225281</v>
+        <v>2.68297052383423</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.71222424507141</v>
+        <v>2.71222400665283</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.70386552810669</v>
+        <v>2.70386576652527</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.63700032234192</v>
+        <v>2.6370005607605</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.64953780174255</v>
+        <v>2.64953804016113</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.73729872703552</v>
+        <v>2.73729848861694</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073097229004</v>
+        <v>2.7707314491272</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.81670117378235</v>
+        <v>2.81670093536377</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.81670117378235</v>
+        <v>2.81670093536377</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.8835666179657</v>
+        <v>2.88356637954712</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.62864232063293</v>
+        <v>2.62864255905151</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.4740161895752</v>
+        <v>2.47401642799377</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.36118125915527</v>
+        <v>2.36118102073669</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.32356953620911</v>
+        <v>2.32356929779053</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.4113302230835</v>
+        <v>2.41132998466492</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550946235657</v>
+        <v>2.41550922393799</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>3.71499991416931</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>37051</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>3.73499989509583</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>3.73499989509583</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G2" t="n">
-        <v>4.56322860717773</v>
+        <v>4.56322813034058</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37858867645264</v>
+        <v>4.37858772277832</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0172233581543</v>
+        <v>4.01722383499146</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176956176758</v>
+        <v>3.48177003860474</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8167576789856</v>
+        <v>3.81675744056702</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.89588904380798</v>
+        <v>3.89588952064514</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522200584412</v>
+        <v>3.8352222442627</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884456634521</v>
+        <v>3.80884480476379</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959761619568</v>
+        <v>3.67959690093994</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467079162598</v>
+        <v>3.82467103004456</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754101753235</v>
+        <v>3.92754125595093</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617641448975</v>
+        <v>3.56617617607117</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.6532199382782</v>
+        <v>3.65322017669678</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405780792236</v>
+        <v>3.33405828475952</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626147270203</v>
+        <v>3.37626171112061</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090044975281</v>
+        <v>3.56090068817139</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220447540283</v>
+        <v>3.44220423698425</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5107843875885</v>
+        <v>3.51078414916992</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.60507488250732</v>
       </c>
       <c r="G32" t="n">
-        <v>3.74817776679993</v>
+        <v>3.74817800521851</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69278597831726</v>
+        <v>3.69278621673584</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467079162598</v>
+        <v>3.82467103004456</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829406738281</v>
+        <v>3.79829382896423</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498892784119</v>
+        <v>3.73498916625977</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699075698853</v>
+        <v>3.9169909954071</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.81411957740784</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.84577250480652</v>
+        <v>3.84577322006226</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061403274536</v>
+        <v>3.89061379432678</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171503067017</v>
+        <v>3.91171455383301</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.09107875823975</v>
+        <v>4.0910792350769</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.06206512451172</v>
+        <v>4.0620641708374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603610992432</v>
+        <v>4.18603658676147</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27308130264282</v>
+        <v>4.27308082580566</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803817749023</v>
+        <v>4.36803865432739</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473279953003</v>
+        <v>4.30473375320435</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G55" t="n">
-        <v>4.41024208068848</v>
+        <v>4.41024160385132</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047420501709</v>
+        <v>4.51047468185425</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G57" t="n">
-        <v>4.4471697807312</v>
+        <v>4.44716882705688</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583522796631</v>
+        <v>4.32583427429199</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658756256104</v>
+        <v>4.19658803939819</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G66" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.18144989013672</v>
       </c>
       <c r="G68" t="n">
-        <v>4.07525300979614</v>
+        <v>4.07525253295898</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G75" t="n">
-        <v>4.16757297515869</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G76" t="n">
-        <v>4.15438413619995</v>
+        <v>4.15438461303711</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16757297515869</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G81" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G83" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G85" t="n">
-        <v>4.17284774780273</v>
+        <v>4.17284822463989</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009382247925</v>
+        <v>4.12009429931641</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383363723755</v>
+        <v>4.14383316040039</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.24406576156616</v>
+        <v>4.24406623840332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G92" t="n">
-        <v>4.15438413619995</v>
+        <v>4.15438461303711</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702199935913</v>
+        <v>4.15702247619629</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G94" t="n">
-        <v>4.2335147857666</v>
+        <v>4.23351526260376</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131183624268</v>
+        <v>4.19131231307983</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.33694076538086</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G101" t="n">
-        <v>4.41190719604492</v>
+        <v>4.41190767288208</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.55795288085938</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51463890075684</v>
+        <v>4.51463842391968</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49797964096069</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G108" t="n">
-        <v>4.41468334197998</v>
+        <v>4.41468381881714</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743774414062</v>
+        <v>4.46743822097778</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G111" t="n">
-        <v>4.47021484375</v>
+        <v>4.47021436691284</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G114" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357780456543</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.19811487197876</v>
+        <v>4.1981143951416</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989729881287</v>
+        <v>3.93989682197571</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.86072492599487</v>
       </c>
       <c r="G122" t="n">
-        <v>4.09815883636475</v>
+        <v>4.0981593132019</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G123" t="n">
-        <v>4.12592458724976</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.8926956653595</v>
+        <v>3.89269638061523</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="n">
-        <v>3.6927855014801</v>
+        <v>3.69278573989868</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="n">
-        <v>3.70944547653198</v>
+        <v>3.7094452381134</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603712081909</v>
+        <v>3.87603735923767</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165726661682</v>
+        <v>3.73165702819824</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111560821533</v>
+        <v>3.70111536979675</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328248023987</v>
+        <v>3.82328271865845</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.94822645187378</v>
+        <v>3.94822692871094</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648822784424</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35915422439575</v>
+        <v>4.35915374755859</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.13496780395508</v>
       </c>
       <c r="G141" t="n">
-        <v>4.2619743347168</v>
+        <v>4.26197481155396</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G143" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357780456543</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583522796631</v>
+        <v>4.32583427429199</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="n">
-        <v>4.30084705352783</v>
+        <v>4.30084609985352</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858915328979</v>
+        <v>4.37858819961548</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637617111206</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.19811487197876</v>
+        <v>4.1981143951416</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917644500732</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423175811768</v>
+        <v>4.18423223495483</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="n">
-        <v>4.1425838470459</v>
+        <v>4.14258337020874</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="n">
-        <v>4.0426287651062</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="n">
-        <v>4.05095863342285</v>
+        <v>4.05095767974854</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="n">
-        <v>4.11204195022583</v>
+        <v>4.11204242706299</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150005340576</v>
+        <v>4.08150053024292</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820446968079</v>
+        <v>3.99820375442505</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="n">
-        <v>4.04818201065063</v>
+        <v>4.04818248748779</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00931024551392</v>
+        <v>4.00931072235107</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="n">
-        <v>4.05928802490234</v>
+        <v>4.05928754806519</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="n">
-        <v>4.00098037719727</v>
+        <v>4.00098085403442</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152179718018</v>
+        <v>4.03152227401733</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384683609009</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502070426941</v>
+        <v>3.66502141952515</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280796051025</v>
+        <v>3.64280867576599</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389151573181</v>
+        <v>3.70389175415039</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.6178195476532</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000959396362</v>
+        <v>3.69000887870789</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276328086853</v>
+        <v>3.74276351928711</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.6178195476532</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113806724548</v>
+        <v>3.65113759040833</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502070426941</v>
+        <v>3.66502141952515</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838342666626</v>
+        <v>3.59838366508484</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58172464370728</v>
+        <v>3.5817244052887</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="n">
-        <v>3.59283113479614</v>
+        <v>3.59283065795898</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660123825073</v>
+        <v>3.85660147666931</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488547325134</v>
+        <v>3.96488618850708</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.94822645187378</v>
+        <v>3.94822692871094</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.9426736831665</v>
+        <v>3.94267344474792</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547252655029</v>
+        <v>3.89547276496887</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8926956653595</v>
+        <v>3.89269638061523</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215472221375</v>
+        <v>3.86215448379517</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384683609009</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438944816589</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107045173645</v>
+        <v>3.80107092857361</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.78718852996826</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996443748474</v>
+        <v>3.78996396064758</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059593200684</v>
+        <v>3.62059640884399</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="n">
-        <v>3.59283113479614</v>
+        <v>3.59283065795898</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179249763489</v>
+        <v>3.43179225921631</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897071838379</v>
+        <v>3.52897000312805</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400357246399</v>
+        <v>3.45400381088257</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="n">
-        <v>3.47066330909729</v>
+        <v>3.47066307067871</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.4762167930603</v>
+        <v>3.47621655464172</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398230552673</v>
+        <v>3.50398206710815</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842858314514</v>
+        <v>3.49842882156372</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174686431885</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732209205627</v>
+        <v>3.48732256889343</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057371139526</v>
+        <v>3.67057394981384</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389151573181</v>
+        <v>3.70389175415039</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050609588623</v>
+        <v>3.82050657272339</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.78718852996826</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384683609009</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.92879056930542</v>
+        <v>3.928790807724</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102601051331</v>
+        <v>3.90102577209473</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154544830322</v>
+        <v>3.98154520988464</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820446968079</v>
+        <v>3.99820375442505</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820446968079</v>
+        <v>3.99820375442505</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="n">
-        <v>4.0426287651062</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648822784424</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G260" t="n">
-        <v>4.12592458724976</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533777236938</v>
+        <v>4.19533681869507</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G266" t="n">
-        <v>4.12592458724976</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G270" t="n">
-        <v>4.12592458724976</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648822784424</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377945899963</v>
+        <v>3.95377969741821</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438944816589</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86493062973022</v>
+        <v>3.8649308681488</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="n">
-        <v>3.92601370811462</v>
+        <v>3.9260139465332</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="n">
-        <v>4.07039356231689</v>
+        <v>4.07039451599121</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="n">
-        <v>4.15646648406982</v>
+        <v>4.15646696090698</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.31472873687744</v>
+        <v>4.31472826004028</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.33694076538086</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.35360050201416</v>
+        <v>4.353600025177</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.31472873687744</v>
+        <v>4.31472826004028</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637617111206</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30084705352783</v>
+        <v>4.30084609985352</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917644500732</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134307861328</v>
+        <v>4.43134260177612</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="n">
-        <v>4.40913105010986</v>
+        <v>4.40913057327271</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="n">
-        <v>4.55351066589355</v>
+        <v>4.55351114273071</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.542405128479</v>
+        <v>4.54240465164185</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="n">
-        <v>4.63402986526489</v>
+        <v>4.63402938842773</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="n">
-        <v>4.55351066589355</v>
+        <v>4.55351114273071</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="n">
-        <v>4.53962755203247</v>
+        <v>4.53962802886963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685140609741</v>
+        <v>4.53685188293457</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G326" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49797964096069</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G327" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49797964096069</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G330" t="n">
-        <v>4.47021484375</v>
+        <v>4.47021436691284</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="n">
-        <v>4.40913105010986</v>
+        <v>4.40913057327271</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691902160645</v>
+        <v>4.38691806793213</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691902160645</v>
+        <v>4.38691806793213</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362272262573</v>
+        <v>4.30362224578857</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244956970215</v>
+        <v>4.44244861602783</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="n">
-        <v>4.54795742034912</v>
+        <v>4.54795694351196</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075531005859</v>
+        <v>4.50075674057007</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="n">
-        <v>4.57849836349487</v>
+        <v>4.57849931716919</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="n">
-        <v>4.60348796844482</v>
+        <v>4.60348749160767</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782361984253</v>
+        <v>4.84782266616821</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.87836503982544</v>
+        <v>4.87836456298828</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782361984253</v>
+        <v>4.84782266616821</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423698425293</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="n">
-        <v>4.72718381881714</v>
+        <v>4.72718334197998</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83618450164795</v>
+        <v>4.83618402481079</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315757751465</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655168533325</v>
+        <v>4.56655216217041</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42312908172607</v>
+        <v>4.42312955856323</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507802963257</v>
+        <v>4.55507755279541</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476148605347</v>
+        <v>4.47476196289062</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="n">
-        <v>4.64686822891235</v>
+        <v>4.64686727523804</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66120958328247</v>
+        <v>4.66121053695679</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315757751465</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="n">
-        <v>4.77021026611328</v>
+        <v>4.77021074295044</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="n">
-        <v>4.80749988555908</v>
+        <v>4.80750036239624</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="n">
-        <v>4.77881622314453</v>
+        <v>4.77881574630737</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="n">
-        <v>4.72718381881714</v>
+        <v>4.72718334197998</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857833862305</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857833862305</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.87634229660034</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="n">
-        <v>4.87060689926147</v>
+        <v>4.87060594558716</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="n">
-        <v>4.82184219360352</v>
+        <v>4.82184171676636</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="n">
-        <v>4.81036901473999</v>
+        <v>4.81036853790283</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215826034546</v>
+        <v>4.90215921401978</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="n">
-        <v>4.93371105194092</v>
+        <v>4.93371200561523</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052680969238</v>
+        <v>4.85052633285522</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="n">
-        <v>4.8017635345459</v>
+        <v>4.80176401138306</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="n">
-        <v>4.87347459793091</v>
+        <v>4.87347412109375</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.87634229660034</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="n">
-        <v>4.81897401809692</v>
+        <v>4.81897354125977</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="n">
-        <v>4.81897401809692</v>
+        <v>4.81897354125977</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="n">
-        <v>4.8390531539917</v>
+        <v>4.83905363082886</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.88781690597534</v>
+        <v>4.88781642913818</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="n">
-        <v>4.95665884017944</v>
+        <v>4.9566593170166</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99108028411865</v>
+        <v>4.99107980728149</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="n">
-        <v>5.0627908706665</v>
+        <v>5.06279039382935</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="n">
-        <v>5.0627908706665</v>
+        <v>5.06279039382935</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.0771336555481</v>
+        <v>5.07713270187378</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871494293213</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="n">
-        <v>5.27792358398438</v>
+        <v>5.27792310714722</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="n">
-        <v>5.54755735397339</v>
+        <v>5.54755687713623</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818996429443</v>
+        <v>5.70818948745728</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208595275879</v>
+        <v>5.97208547592163</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="n">
-        <v>5.89750623703003</v>
+        <v>5.89750671386719</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766498565674</v>
+        <v>5.93766450881958</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555871963501</v>
+        <v>5.76555824279785</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="n">
-        <v>5.68237400054932</v>
+        <v>5.68237352371216</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="n">
-        <v>5.79424285888672</v>
+        <v>5.79424238204956</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="n">
-        <v>6.12124538421631</v>
+        <v>6.12124490737915</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061134338379</v>
+        <v>5.96061182022095</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287635803223</v>
+        <v>6.17287540435791</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="n">
-        <v>6.10977077484131</v>
+        <v>6.10977029800415</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="n">
-        <v>6.19008684158325</v>
+        <v>6.19008636474609</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371788024902</v>
+        <v>6.02371740341187</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="n">
-        <v>6.13271808624268</v>
+        <v>6.13271760940552</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645580291748</v>
+        <v>6.35645532608032</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="n">
-        <v>6.48266649246216</v>
+        <v>6.48266744613647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="n">
-        <v>6.48266649246216</v>
+        <v>6.48266744613647</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319147109985</v>
+        <v>6.25319242477417</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734748840332</v>
+        <v>5.85734796524048</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="n">
-        <v>5.62213611602783</v>
+        <v>5.62213659286499</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="n">
-        <v>5.53608322143555</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="n">
-        <v>5.61353063583374</v>
+        <v>5.6135311126709</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034639358521</v>
+        <v>5.53034591674805</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460908889771</v>
+        <v>5.52460956573486</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.65082120895386</v>
+        <v>5.6508207321167</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.6565580368042</v>
+        <v>5.65655851364136</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818996429443</v>
+        <v>5.70818948745728</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="n">
-        <v>5.71966314315796</v>
+        <v>5.7196626663208</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903148651123</v>
+        <v>5.55903100967407</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345245361328</v>
+        <v>5.59345149993896</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="n">
-        <v>5.53608322143555</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49592447280884</v>
+        <v>5.49592542648315</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871494293213</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="n">
-        <v>5.26645040512085</v>
+        <v>5.26644945144653</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="n">
-        <v>4.97386932373047</v>
+        <v>4.97386884689331</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423698425293</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849967956543</v>
+        <v>4.69849920272827</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="n">
-        <v>4.6812891960144</v>
+        <v>4.68128871917725</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239614486694</v>
+        <v>4.96239566802979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245615005493</v>
+        <v>4.54245662689209</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057697296143</v>
+        <v>4.50057744979858</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401973724365</v>
+        <v>4.50401926040649</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="n">
-        <v>4.33937072753906</v>
+        <v>4.33937120437622</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="n">
-        <v>4.35371351242065</v>
+        <v>4.3537130355835</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449653625488</v>
+        <v>4.04449605941772</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>4.49069929122925</v>
+        <v>4.49069976806641</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262004852295</v>
+        <v>4.68262052536011</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="n">
-        <v>4.78259229660034</v>
+        <v>4.78259181976318</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="n">
-        <v>4.96278810501099</v>
+        <v>4.96278762817383</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="n">
-        <v>5.0967001914978</v>
+        <v>5.09670066833496</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="n">
-        <v>4.99549436569214</v>
+        <v>4.9954948425293</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628082275391</v>
+        <v>4.83628034591675</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="n">
-        <v>4.87454128265381</v>
+        <v>4.87454175949097</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.8547945022583</v>
+        <v>4.85479354858398</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>4.83936595916748</v>
+        <v>4.83936548233032</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813238143921</v>
+        <v>4.83813142776489</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="n">
-        <v>4.75235462188721</v>
+        <v>4.75235366821289</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>4.79061412811279</v>
+        <v>4.79061460494995</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="n">
-        <v>4.93686866760254</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132905960083</v>
+        <v>4.88132953643799</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813238143921</v>
+        <v>4.83813142776489</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>4.89120388031006</v>
+        <v>4.8912034034729</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.0602912902832</v>
+        <v>5.06029081344604</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031904220581</v>
+        <v>4.96031951904297</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="n">
-        <v>4.93686866760254</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="n">
-        <v>4.59684181213379</v>
+        <v>4.59684228897095</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>4.66472434997559</v>
+        <v>4.66472482681274</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>4.61288690567017</v>
+        <v>4.61288738250732</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="n">
-        <v>4.46786689758301</v>
+        <v>4.46786642074585</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.6499137878418</v>
+        <v>4.64991331100464</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716547012329</v>
+        <v>4.71716499328613</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="n">
-        <v>4.85448122024536</v>
+        <v>4.8544807434082</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>4.62495851516724</v>
+        <v>4.62495803833008</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.6899676322937</v>
+        <v>4.68996715545654</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353132247925</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="n">
-        <v>4.56061267852783</v>
+        <v>4.56061220169067</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.56525564193726</v>
+        <v>4.5652551651001</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="n">
-        <v>4.67470979690552</v>
+        <v>4.67471027374268</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353132247925</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60173988342285</v>
+        <v>4.60174036026001</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273914337158</v>
+        <v>4.80273866653442</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.7927885055542</v>
+        <v>4.79278802871704</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>4.65679979324341</v>
+        <v>4.65679931640625</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="n">
-        <v>4.81600618362427</v>
+        <v>4.81600666046143</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637281417847</v>
+        <v>4.87637233734131</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="n">
-        <v>4.7868185043335</v>
+        <v>4.78681802749634</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.68731355667114</v>
+        <v>4.6873140335083</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="n">
-        <v>4.79676818847656</v>
+        <v>4.79676866531372</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.66343307495117</v>
+        <v>4.66343355178833</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="n">
-        <v>4.59776067733765</v>
+        <v>4.59776020050049</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="n">
-        <v>4.38283157348633</v>
+        <v>4.38283109664917</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.360276222229</v>
+        <v>4.36027669906616</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44385957717896</v>
+        <v>4.44386053085327</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589925765991</v>
+        <v>4.43589973449707</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41135549545288</v>
+        <v>4.4113564491272</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="n">
-        <v>4.33241558074951</v>
+        <v>4.33241605758667</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>4.3516526222229</v>
+        <v>4.35165214538574</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="n">
-        <v>4.50090932846069</v>
+        <v>4.50090980529785</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="n">
-        <v>4.49029636383057</v>
+        <v>4.49029588699341</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739452362061</v>
+        <v>4.53739404678345</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="n">
-        <v>4.54469060897827</v>
+        <v>4.54469156265259</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="n">
-        <v>4.48299837112427</v>
+        <v>4.48299884796143</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012765884399</v>
+        <v>4.39012861251831</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966278076172</v>
+        <v>4.34966325759888</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010942459106</v>
+        <v>4.26010894775391</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984199523926</v>
+        <v>4.17984247207642</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="n">
-        <v>4.07370471954346</v>
+        <v>4.0737042427063</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.0159912109375</v>
+        <v>4.01599216461182</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312121391296</v>
+        <v>3.92312097549438</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>3.94899296760559</v>
+        <v>3.94899272918701</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648817062378</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="n">
-        <v>3.95297265052795</v>
+        <v>3.95297241210938</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720081329346</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>3.91051745414734</v>
+        <v>3.91051721572876</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>3.94700241088867</v>
+        <v>3.94700217247009</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>3.94700241088867</v>
+        <v>3.94700217247009</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="n">
-        <v>3.98614048957825</v>
+        <v>3.98614025115967</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="n">
-        <v>4.13473320007324</v>
+        <v>4.1347336769104</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00670480728149</v>
+        <v>4.00670528411865</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.21234703063965</v>
+        <v>4.21234750747681</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="n">
-        <v>4.12544631958008</v>
+        <v>4.12544679641724</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04717063903809</v>
+        <v>4.04716968536377</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="n">
-        <v>3.98216032981873</v>
+        <v>3.9821605682373</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766569137573</v>
+        <v>3.94766592979431</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184401512146</v>
+        <v>3.91184449195862</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="n">
-        <v>3.99940800666809</v>
+        <v>3.99940776824951</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05115032196045</v>
+        <v>4.05114984512329</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.96889305114746</v>
+        <v>3.96889281272888</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189385414124</v>
+        <v>3.90189361572266</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720081329346</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.8521420955658</v>
+        <v>3.85214185714722</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811185836792</v>
+        <v>3.85811161994934</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="n">
-        <v>3.7499840259552</v>
+        <v>3.74998378753662</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848971366882</v>
+        <v>3.64848923683167</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.57950019836426</v>
+        <v>3.5794997215271</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490659713745</v>
+        <v>3.56490635871887</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59741044044495</v>
+        <v>3.59741020202637</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="n">
-        <v>3.52046084403992</v>
+        <v>3.52046036720276</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57021284103394</v>
+        <v>3.57021260261536</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="n">
-        <v>3.69625210762024</v>
+        <v>3.69625186920166</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.91980385780334</v>
+        <v>3.91980457305908</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587401390076</v>
+        <v>3.90587425231934</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444825172424</v>
+        <v>3.92444801330566</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>3.90056705474854</v>
+        <v>3.90056729316711</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.89857697486877</v>
+        <v>3.8985767364502</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91516041755676</v>
+        <v>3.91516089439392</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="n">
-        <v>3.87204241752625</v>
+        <v>3.87204194068909</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025097846985</v>
+        <v>3.83025074005127</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="n">
-        <v>3.92842793464661</v>
+        <v>3.92842864990234</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287368774414</v>
+        <v>3.97287344932556</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.07901096343994</v>
+        <v>4.07901191711426</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657543182373</v>
+        <v>4.16657495498657</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="n">
-        <v>4.1380500793457</v>
+        <v>4.13805055618286</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09957504272461</v>
+        <v>4.09957551956177</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>4.09294176101685</v>
+        <v>4.092942237854</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078392982483</v>
+        <v>3.99078440666199</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>3.9111807346344</v>
+        <v>3.91118025779724</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017072677612</v>
+        <v>3.98017048835754</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567537307739</v>
+        <v>3.94567584991455</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680424690247</v>
+        <v>3.98680377006531</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>4.01665496826172</v>
+        <v>4.01665544509888</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13406991958618</v>
+        <v>4.13407039642334</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="n">
-        <v>4.19178247451782</v>
+        <v>4.19178295135498</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="n">
-        <v>4.13473320007324</v>
+        <v>4.1347336769104</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="n">
-        <v>4.22030735015869</v>
+        <v>4.22030687332153</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="n">
-        <v>4.34501981735229</v>
+        <v>4.34501934051514</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="n">
-        <v>4.41334581375122</v>
+        <v>4.41334533691406</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531742095947</v>
+        <v>4.28531694412231</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="n">
-        <v>4.29194974899292</v>
+        <v>4.29195022583008</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609813690186</v>
+        <v>4.39609861373901</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="n">
-        <v>4.41666269302368</v>
+        <v>4.41666221618652</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="n">
-        <v>4.44717693328857</v>
+        <v>4.44717741012573</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069173812866</v>
+        <v>4.41069221496582</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408958435059</v>
+        <v>4.26408910751343</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>4.30521726608276</v>
+        <v>4.30521774291992</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27204990386963</v>
+        <v>4.27204942703247</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="n">
-        <v>4.38482046127319</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36492013931274</v>
+        <v>4.3649206161499</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3980884552002</v>
+        <v>4.39808797836304</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>4.42462301254272</v>
+        <v>4.42462253570557</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.298583984375</v>
+        <v>4.29858446121216</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511806488037</v>
+        <v>4.32511854171753</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="n">
-        <v>4.37155389785767</v>
+        <v>4.37155437469482</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>4.40472221374512</v>
+        <v>4.40472173690796</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>4.43789052963257</v>
+        <v>4.43789005279541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>4.4644250869751</v>
+        <v>4.46442461013794</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>4.41135549545288</v>
+        <v>4.4113564491272</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066156387329</v>
+        <v>4.55066108703613</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49095916748047</v>
+        <v>4.49095869064331</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="n">
-        <v>4.38482046127319</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.44223260879517</v>
+        <v>4.44223308563232</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G858" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140970230103</v>
+        <v>4.57140874862671</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>4.54987955093384</v>
+        <v>4.549880027771</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>4.42787981033325</v>
+        <v>4.42788028717041</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G881" t="n">
-        <v>4.21976232528687</v>
+        <v>4.21976184844971</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>4.21976232528687</v>
+        <v>4.21976184844971</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670345306396</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.16952753067017</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670345306396</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505573272705</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>4.34893894195557</v>
+        <v>4.34893846511841</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>4.3274097442627</v>
+        <v>4.32740926742554</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411560058594</v>
+        <v>4.23411512374878</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129152297974</v>
+        <v>4.24129199981689</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670345306396</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776258468628</v>
+        <v>4.09776210784912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>4.05470323562622</v>
+        <v>4.05470371246338</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G915" t="n">
-        <v>4.04752635955811</v>
+        <v>4.04752683639526</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87529182434082</v>
+        <v>3.8752920627594</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246870040894</v>
+        <v>3.88246822357178</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>3.79635071754456</v>
+        <v>3.79635119438171</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764488220215</v>
+        <v>3.76764440536499</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764488220215</v>
+        <v>3.76764440536499</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81788039207458</v>
+        <v>3.81788015365601</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658575057983</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658575057983</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G927" t="n">
-        <v>3.79635071754456</v>
+        <v>3.79635119438171</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199768066406</v>
+        <v>3.78199815750122</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352735519409</v>
+        <v>3.80352759361267</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81788039207458</v>
+        <v>3.81788015365601</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940887451172</v>
+        <v>3.83940935134888</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.8322331905365</v>
+        <v>3.83223295211792</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.87529182434082</v>
+        <v>3.8752920627594</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658575057983</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G936" t="n">
-        <v>3.92552709579468</v>
+        <v>3.9255268573761</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>4.04035091400146</v>
+        <v>4.04035043716431</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317356109619</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599811553955</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G944" t="n">
-        <v>3.96858596801758</v>
+        <v>3.968585729599</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599811553955</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317356109619</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293876647949</v>
+        <v>3.98293900489807</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>3.96858596801758</v>
+        <v>3.968585729599</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317356109619</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>4.01164484024048</v>
+        <v>4.01164531707764</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682149887085</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G956" t="n">
-        <v>3.92552709579468</v>
+        <v>3.9255268573761</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G957" t="n">
-        <v>3.96858596801758</v>
+        <v>3.968585729599</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317356109619</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>4.09058570861816</v>
+        <v>4.09058618545532</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670345306396</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16952753067017</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>4.16952753067017</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799737930298</v>
+        <v>4.14799785614014</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G976" t="n">
-        <v>4.13364505767822</v>
+        <v>4.13364458084106</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G979" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G980" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G982" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505573272705</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505573272705</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.42787981033325</v>
+        <v>4.42788028717041</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.42787981033325</v>
+        <v>4.42788028717041</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270267486572</v>
+        <v>4.54270315170288</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140970230103</v>
+        <v>4.57140874862671</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.52117395401001</v>
+        <v>4.52117443084717</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.16952753067017</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682149887085</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.93987989425659</v>
+        <v>3.93987965583801</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.91835069656372</v>
+        <v>3.9183509349823</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505631446838</v>
+        <v>3.82505655288696</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.25811553001404</v>
+        <v>3.25811576843262</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299823760986</v>
+        <v>2.62299871444702</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605734825134</v>
+        <v>2.66605710983276</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076322555542</v>
+        <v>2.450763463974</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305726051331</v>
+        <v>2.48305749893188</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864520072937</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682218551636</v>
+        <v>2.67682194709778</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423385620117</v>
+        <v>2.73423361778259</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705721855164</v>
+        <v>2.72705698013306</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.59070420265198</v>
+        <v>2.59070444107056</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70552778244019</v>
+        <v>2.70552802085876</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.65529251098633</v>
+        <v>2.65529274940491</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505723953247</v>
+        <v>2.60505747795105</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864520072937</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.66964554786682</v>
+        <v>2.66964530944824</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.64093947410583</v>
+        <v>2.64093971252441</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.66964554786682</v>
+        <v>2.66964530944824</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329300880432</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.54764580726624</v>
+        <v>2.54764533042908</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.52252793312073</v>
+        <v>2.52252817153931</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535129547119</v>
+        <v>2.51535153388977</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535129547119</v>
+        <v>2.51535153388977</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.3179988861084</v>
+        <v>2.31799864768982</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305726051331</v>
+        <v>2.48305749893188</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105728149414</v>
+        <v>2.36105751991272</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005764961243</v>
+        <v>2.30005741119385</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876324653625</v>
+        <v>2.32876348495483</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893997192383</v>
+        <v>2.51893973350525</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81317520141602</v>
+        <v>2.81317496299744</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.70552778244019</v>
+        <v>2.70552802085876</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864520072937</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.54764580726624</v>
+        <v>2.54764533042908</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588133811951</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.41129279136658</v>
+        <v>2.411292552948</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.375</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.42205739021301</v>
+        <v>2.42205762863159</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535129547119</v>
+        <v>2.51535153388977</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.49023365974426</v>
+        <v>2.49023389816284</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588133811951</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535129547119</v>
+        <v>2.51535153388977</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588133811951</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588133811951</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329300880432</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.54405736923218</v>
+        <v>2.5440571308136</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893997192383</v>
+        <v>2.51893973350525</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.56775856018066</v>
+        <v>2.56775832176208</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344397544861</v>
+        <v>2.48344421386719</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.34164261817932</v>
+        <v>2.34164237976074</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.40296196937561</v>
+        <v>2.40296220779419</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.46044921875</v>
+        <v>2.46044945716858</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679454803467</v>
+        <v>2.40679478645325</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230253219604</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481504440308</v>
+        <v>2.31481528282166</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.32248020172119</v>
+        <v>2.32247996330261</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697221755981</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697221755981</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.42595720291138</v>
+        <v>2.4259569644928</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.35313987731934</v>
+        <v>2.35314011573792</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.47961163520813</v>
+        <v>2.47961139678955</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.41062712669373</v>
+        <v>2.41062688827515</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715036392212</v>
+        <v>2.30715012550354</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.32248020172119</v>
+        <v>2.32247996330261</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.299485206604</v>
+        <v>2.29948544502258</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.31098294258118</v>
+        <v>2.3109827041626</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27265810966492</v>
+        <v>2.27265787124634</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.35313987731934</v>
+        <v>2.35314011573792</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.47577905654907</v>
+        <v>2.47577929496765</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.47577905654907</v>
+        <v>2.47577929496765</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.43362188339233</v>
+        <v>2.43362212181091</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230253219604</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.31098294258118</v>
+        <v>2.3109827041626</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283554077148</v>
+        <v>2.22283577919006</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.875</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.20367336273193</v>
+        <v>2.20367360115051</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750617980957</v>
+        <v>2.20750570297241</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.17301368713379</v>
+        <v>2.17301344871521</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786151885986</v>
+        <v>2.10786128044128</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.98522222042084</v>
+        <v>1.98522210121155</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.8970752954483</v>
+        <v>1.89707541465759</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.90857267379761</v>
+        <v>1.9085727930069</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138976097107</v>
+        <v>1.98138999938965</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.61758065223694</v>
+        <v>2.61758089065552</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.71339273452759</v>
+        <v>2.71339249610901</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.67506766319275</v>
+        <v>2.67506790161133</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405241012573</v>
+        <v>2.74405217170715</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.77087998390198</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.5</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.68273305892944</v>
+        <v>2.68273282051086</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255491256714</v>
+        <v>2.7325553894043</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.7593822479248</v>
+        <v>2.75938248634338</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.83603167533875</v>
+        <v>2.83603191375732</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.85136198997498</v>
+        <v>2.8513617515564</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87052392959595</v>
+        <v>2.87052416801453</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285924911499</v>
+        <v>2.86285901069641</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620958328247</v>
+        <v>2.78620982170105</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.61758065223694</v>
+        <v>2.61758089065552</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.71339273452759</v>
+        <v>2.71339249610901</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.70956039428711</v>
+        <v>2.70956015586853</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.77087998390198</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82070183753967</v>
+        <v>2.82070231437683</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87818932533264</v>
+        <v>2.87818908691406</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.9165141582489</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245195388794</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849342346191</v>
+        <v>3.00849318504333</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699568748474</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.92034649848938</v>
+        <v>2.9203462600708</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255491256714</v>
+        <v>2.7325553894043</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255491256714</v>
+        <v>2.7325553894043</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.70956039428711</v>
+        <v>2.70956015586853</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.67123532295227</v>
+        <v>2.67123556137085</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.61758065223694</v>
+        <v>2.61758089065552</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207290649414</v>
+        <v>2.65207314491272</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.59841847419739</v>
+        <v>2.59841871261597</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.65973782539368</v>
+        <v>2.65973806381226</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.62907838821411</v>
+        <v>2.62907814979553</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.71722531318665</v>
+        <v>2.71722507476807</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255491256714</v>
+        <v>2.7325553894043</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.96633577346802</v>
+        <v>2.9663360118866</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.01999068260193</v>
+        <v>3.01999092102051</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.13879752159119</v>
+        <v>3.13879728317261</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.15412712097168</v>
+        <v>3.15412735939026</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.21161460876465</v>
+        <v>3.21161437034607</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676653862</v>
+        <v>3.27676701545715</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.17712235450745</v>
+        <v>3.17712211608887</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.09280753135681</v>
+        <v>3.09280776977539</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.21161460876465</v>
+        <v>3.21161437034607</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011734962463</v>
+        <v>3.20011711120605</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209661483765</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.28826379776001</v>
+        <v>3.28826427459717</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.54120755195618</v>
+        <v>3.5412073135376</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.56036972999573</v>
+        <v>3.56036996841431</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.56420254707336</v>
+        <v>3.56420230865479</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054716110229</v>
+        <v>3.51054739952087</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557313919067</v>
+        <v>3.39557337760925</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33425378799438</v>
+        <v>3.33425354957581</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.28443121910095</v>
+        <v>3.28443145751953</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.31892395019531</v>
+        <v>3.31892371177673</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311210632324</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927928924561</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.18861961364746</v>
+        <v>3.18861985206604</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562509536743</v>
+        <v>3.16562485694885</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.97783327102661</v>
+        <v>2.97783350944519</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.07747745513916</v>
+        <v>3.07747769355774</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.15412712097168</v>
+        <v>3.15412735939026</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.07747745513916</v>
+        <v>3.07747769355774</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610686302185</v>
+        <v>3.24610662460327</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377154350281</v>
+        <v>3.25377178192139</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245195388794</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915286064148</v>
+        <v>3.03915309906006</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.97783327102661</v>
+        <v>2.97783350944519</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.01999068260193</v>
+        <v>3.01999092102051</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166584968567</v>
+        <v>2.98166608810425</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.05831551551819</v>
+        <v>3.05831527709961</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.88585424423218</v>
+        <v>2.8858540058136</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387450218201</v>
+        <v>2.79387474060059</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268134117126</v>
+        <v>2.91268110275269</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699568748474</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05448269844055</v>
+        <v>3.05448293685913</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.07747745513916</v>
+        <v>3.07747769355774</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.00466084480286</v>
+        <v>3.00466108322144</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.00466084480286</v>
+        <v>3.00466108322144</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214809417725</v>
+        <v>3.06214761734009</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.05831551551819</v>
+        <v>3.05831527709961</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.94334101676941</v>
+        <v>2.94334125518799</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.21161460876465</v>
+        <v>3.21161437034607</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430526733398</v>
+        <v>3.10430550575256</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915286064148</v>
+        <v>3.03915309906006</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.9165141582489</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.82453441619873</v>
+        <v>2.82453417778015</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.85136198997498</v>
+        <v>2.8513617515564</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207290649414</v>
+        <v>2.65207314491272</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255491256714</v>
+        <v>2.7325553894043</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.81303715705872</v>
+        <v>2.81303691864014</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.97783327102661</v>
+        <v>2.97783350944519</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.09280753135681</v>
+        <v>3.09280776977539</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927928924561</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011734962463</v>
+        <v>3.20011711120605</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311210632324</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562509536743</v>
+        <v>3.16562485694885</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.17712235450745</v>
+        <v>3.17712211608887</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.17712235450745</v>
+        <v>3.17712211608887</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.17712235450745</v>
+        <v>3.17712211608887</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.05448269844055</v>
+        <v>3.05448293685913</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.01999068260193</v>
+        <v>3.01999092102051</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.28443121910095</v>
+        <v>3.28443145751953</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.18861961364746</v>
+        <v>3.18861985206604</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.45306062698364</v>
+        <v>3.45306038856506</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.30359387397766</v>
+        <v>3.30359411239624</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.07747745513916</v>
+        <v>3.07747769355774</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.13879752159119</v>
+        <v>3.13879728317261</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.13879752159119</v>
+        <v>3.13879728317261</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.23077702522278</v>
+        <v>3.2307767868042</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844170570374</v>
+        <v>3.23844194412231</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394945144653</v>
+        <v>3.20394968986511</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.28443121910095</v>
+        <v>3.28443145751953</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311210632324</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059935569763</v>
+        <v>3.28059887886047</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.27293395996094</v>
+        <v>3.27293419837952</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245195388794</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.34191870689392</v>
+        <v>3.3419189453125</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491322517395</v>
+        <v>3.36491346359253</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.34958338737488</v>
+        <v>3.3495831489563</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.4224009513855</v>
+        <v>3.42240071296692</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.42623281478882</v>
+        <v>3.4262330532074</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.33425378799438</v>
+        <v>3.33425354957581</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.34191870689392</v>
+        <v>3.3419189453125</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.4224009513855</v>
+        <v>3.42240071296692</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.50288271903992</v>
+        <v>3.50288248062134</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372030258179</v>
+        <v>3.48372006416321</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.56420254707336</v>
+        <v>3.56420230865479</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.50671482086182</v>
+        <v>3.5067150592804</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.46072554588318</v>
+        <v>3.4607253074646</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209661483765</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371364593506</v>
+        <v>3.21371388435364</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.20953464508057</v>
+        <v>3.20953488349915</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804208755493</v>
+        <v>3.26804184913635</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.36834025382996</v>
+        <v>3.36834001541138</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251877784729</v>
+        <v>3.37251901626587</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.36834025382996</v>
+        <v>3.36834001541138</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087701797485</v>
+        <v>3.38087725639343</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.07580399513245</v>
+        <v>3.0758044719696</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132730484009</v>
+        <v>2.97132706642151</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78326845169067</v>
+        <v>2.78326821327209</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595465660095</v>
+        <v>2.84595489501953</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.08834147453308</v>
+        <v>3.0883412361145</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893878936768</v>
+        <v>3.00893902778625</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.97550630569458</v>
+        <v>2.975506067276</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.96296906471252</v>
+        <v>2.96296882629395</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729679107666</v>
+        <v>3.01729702949524</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.14684867858887</v>
+        <v>3.14684844017029</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.14684867858887</v>
+        <v>3.14684844017029</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.20953464508057</v>
+        <v>3.20953488349915</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.95461106300354</v>
+        <v>2.95461082458496</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.8919243812561</v>
+        <v>2.89192461967468</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8292384147644</v>
+        <v>2.82923817634583</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147772789001</v>
+        <v>2.74147748947144</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.8334174156189</v>
+        <v>2.83341765403748</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983596801758</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.69968676567078</v>
+        <v>2.69968700408936</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.29013705253601</v>
+        <v>2.29013681411743</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.29013705253601</v>
+        <v>2.29013681411743</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.26924157142639</v>
+        <v>2.26924133300781</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.23998785018921</v>
+        <v>2.23998808860779</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177857398987</v>
+        <v>2.28177881240845</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.22745037078857</v>
+        <v>2.22745060920715</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.50326991081238</v>
+        <v>2.5032696723938</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744891166687</v>
+        <v>2.50744915008545</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849335670471</v>
+        <v>2.57849359512329</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.59103083610535</v>
+        <v>2.59103059768677</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.5868513584137</v>
+        <v>2.58685183525085</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.55759787559509</v>
+        <v>2.55759811401367</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.62864255905151</v>
+        <v>2.62864232063293</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.70386576652527</v>
+        <v>2.70386552810669</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.7205822467804</v>
+        <v>2.72058248519897</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282179832458</v>
+        <v>2.63282155990601</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297052383423</v>
+        <v>2.68297076225281</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.71222400665283</v>
+        <v>2.71222424507141</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.70386576652527</v>
+        <v>2.70386552810669</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.6370005607605</v>
+        <v>2.63700032234192</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.64953804016113</v>
+        <v>2.64953780174255</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.59103083610535</v>
+        <v>2.59103059768677</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.73729848861694</v>
+        <v>2.73729872703552</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.7707314491272</v>
+        <v>2.77073097229004</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.81670093536377</v>
+        <v>2.81670117378235</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.81670093536377</v>
+        <v>2.81670117378235</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.88356637954712</v>
+        <v>2.8835666179657</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.8919243812561</v>
+        <v>2.89192461967468</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.62864255905151</v>
+        <v>2.62864232063293</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.47401642799377</v>
+        <v>2.4740161895752</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.36118102073669</v>
+        <v>2.36118125915527</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.32356929779053</v>
+        <v>2.32356953620911</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.41132998466492</v>
+        <v>2.4113302230835</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550922393799</v>
+        <v>2.41550946235657</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>3.70000004768372</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>42254</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>3.74499988555908</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>3.65499997138977</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>3.66499996185303</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>3.66499996185303</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235877990723</v>
+        <v>4.64235925674438</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G4" t="n">
-        <v>4.60015630722046</v>
+        <v>4.60015535354614</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.10179138183594</v>
       </c>
       <c r="G5" t="n">
-        <v>4.59751892089844</v>
+        <v>4.59751844406128</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409700393677</v>
+        <v>4.48409748077393</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37858915328979</v>
+        <v>4.37858867645264</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.73923206329346</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39177656173706</v>
+        <v>4.39177703857422</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G11" t="n">
-        <v>4.18076086044312</v>
+        <v>4.18076038360596</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.01722431182861</v>
+        <v>4.01722383499146</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48177003860474</v>
+        <v>3.48176956176758</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74554014205933</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522200584412</v>
+        <v>3.83522152900696</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959713935852</v>
+        <v>3.6795973777771</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754173278809</v>
+        <v>3.92754125595093</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74554014205933</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246784210205</v>
+        <v>3.78246831893921</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617617607117</v>
+        <v>3.56617641448975</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65322065353394</v>
+        <v>3.65322041511536</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405756950378</v>
+        <v>3.33405804634094</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090092658997</v>
+        <v>3.56090021133423</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220399856567</v>
+        <v>3.44220376014709</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5107843875885</v>
+        <v>3.51078414916992</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.60507488250732</v>
       </c>
       <c r="G32" t="n">
-        <v>3.74817728996277</v>
+        <v>3.74817776679993</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829359054565</v>
+        <v>3.79829406738281</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699051856995</v>
+        <v>3.9169909954071</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G38" t="n">
-        <v>3.86687445640564</v>
+        <v>3.86687397956848</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104823112488</v>
+        <v>3.85104846954346</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8906135559082</v>
+        <v>3.89061403274536</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171550750732</v>
+        <v>3.91171503067017</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.09107971191406</v>
+        <v>4.0910792350769</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.06206464767456</v>
+        <v>4.0620641708374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339872360229</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G48" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27308130264282</v>
+        <v>4.27308082580566</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803817749023</v>
+        <v>4.36803770065308</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221147537231</v>
+        <v>4.35221195220947</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473375320435</v>
+        <v>4.30473327636719</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047372817993</v>
+        <v>4.51047420501709</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G58" t="n">
-        <v>4.38913917541504</v>
+        <v>4.3891396522522</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658708572388</v>
+        <v>4.19658756256104</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.5161190032959</v>
       </c>
       <c r="G62" t="n">
-        <v>4.26516723632812</v>
+        <v>4.26516771316528</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.52076816558838</v>
       </c>
       <c r="G64" t="n">
-        <v>4.26780557632446</v>
+        <v>4.26780605316162</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G67" t="n">
-        <v>4.10426759719849</v>
+        <v>4.10426807403564</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.18144989013672</v>
       </c>
       <c r="G68" t="n">
-        <v>4.07525300979614</v>
+        <v>4.0752534866333</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.18609809875488</v>
       </c>
       <c r="G69" t="n">
-        <v>4.07789087295532</v>
+        <v>4.07789039611816</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G70" t="n">
-        <v>4.18076086044312</v>
+        <v>4.18076038360596</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G75" t="n">
-        <v>4.16757249832153</v>
+        <v>4.16757297515869</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G79" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16757249832153</v>
+        <v>4.16757297515869</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339872360229</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G85" t="n">
-        <v>4.17284822463989</v>
+        <v>4.17284774780273</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119577407837</v>
+        <v>4.14119625091553</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G88" t="n">
-        <v>4.10426759719849</v>
+        <v>4.10426807403564</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G89" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.24406623840332</v>
+        <v>4.24406576156616</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702152252197</v>
+        <v>4.15702247619629</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044248580933</v>
+        <v>4.27044343948364</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G98" t="n">
-        <v>4.15174674987793</v>
+        <v>4.15174627304077</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.33694076538086</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G101" t="n">
-        <v>4.41190767288208</v>
+        <v>4.41190719604492</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.52574443817139</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.52852153778076</v>
+        <v>4.52852249145508</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G107" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.48823022842407</v>
       </c>
       <c r="G109" t="n">
-        <v>4.4729905128479</v>
+        <v>4.47299098968506</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.49287796020508</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47576665878296</v>
+        <v>4.47576713562012</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G114" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357780456543</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768479347229</v>
+        <v>3.91768527030945</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G121" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373573303223</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.86072492599487</v>
       </c>
       <c r="G122" t="n">
-        <v>4.09815883636475</v>
+        <v>4.0981593132019</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G123" t="n">
-        <v>4.12592554092407</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.89269638061523</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="n">
-        <v>3.69278502464294</v>
+        <v>3.6927855014801</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055125236511</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="n">
-        <v>4.01208686828613</v>
+        <v>4.01208639144897</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603664398193</v>
+        <v>3.87603712081909</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165702819824</v>
+        <v>3.73165726661682</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111560821533</v>
+        <v>3.70111513137817</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G136" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373573303223</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.11172723770142</v>
       </c>
       <c r="G138" t="n">
-        <v>4.24809169769287</v>
+        <v>4.24809217453003</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="n">
-        <v>4.18145561218262</v>
+        <v>4.18145608901978</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35915327072144</v>
+        <v>4.35915374755859</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.29806900024414</v>
+        <v>4.2980694770813</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G143" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357780456543</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583522796631</v>
+        <v>4.32583475112915</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858963012695</v>
+        <v>4.37858915328979</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138751983643</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="n">
-        <v>4.10926628112793</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="n">
-        <v>4.2342095375061</v>
+        <v>4.23421001434326</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="n">
-        <v>4.25919771194458</v>
+        <v>4.25919818878174</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644426345825</v>
+        <v>4.20644378662109</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="n">
-        <v>4.05095863342285</v>
+        <v>4.05095815658569</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150053024292</v>
+        <v>4.08150005340576</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="n">
-        <v>4.04818248748779</v>
+        <v>4.04818201065063</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00931072235107</v>
+        <v>4.00931024551392</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9704384803772</v>
+        <v>3.97043895721436</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055125236511</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280843734741</v>
+        <v>3.64280772209167</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.61781907081604</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332763671875</v>
+        <v>3.72332811355591</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000959396362</v>
+        <v>3.69000887870789</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224384307861</v>
+        <v>3.66224360466003</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055125236511</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055125236511</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332763671875</v>
+        <v>3.72332811355591</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="n">
-        <v>3.67612624168396</v>
+        <v>3.67612671852112</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.61781907081604</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.6511378288269</v>
+        <v>3.65113830566406</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838366508484</v>
+        <v>3.59838342666626</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="n">
-        <v>3.70666837692261</v>
+        <v>3.70666813850403</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660171508789</v>
+        <v>3.85660147666931</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046165466309</v>
+        <v>3.92046117782593</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488618850708</v>
+        <v>3.96488523483276</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="n">
-        <v>3.97321534156799</v>
+        <v>3.97321581840515</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.94267416000366</v>
+        <v>3.94267320632935</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547324180603</v>
+        <v>3.89547276496887</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.89269638061523</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438849449158</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107045173645</v>
+        <v>3.80107116699219</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996467590332</v>
+        <v>3.78996443748474</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="n">
-        <v>3.67612624168396</v>
+        <v>3.67612671852112</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.71222162246704</v>
+        <v>3.71222138404846</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.61504244804382</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059617042542</v>
+        <v>3.62059569358826</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400428771973</v>
+        <v>3.45400333404541</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398254394531</v>
+        <v>3.50398206710815</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842834472656</v>
+        <v>3.49842858314514</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174757957458</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050609588623</v>
+        <v>3.82050561904907</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.928790807724</v>
+        <v>3.92879033088684</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599267959595</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G260" t="n">
-        <v>4.12592554092407</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="n">
-        <v>4.18145561218262</v>
+        <v>4.18145608901978</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="n">
-        <v>4.13147783279419</v>
+        <v>4.13147830963135</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="n">
-        <v>4.18700885772705</v>
+        <v>4.18700838088989</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G266" t="n">
-        <v>4.12592554092407</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="n">
-        <v>4.15091371536255</v>
+        <v>4.15091323852539</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481904983521</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G270" t="n">
-        <v>4.12592554092407</v>
+        <v>4.12592506408691</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484031677246</v>
+        <v>4.06484127044678</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377922058105</v>
+        <v>3.95377969741821</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438849449158</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="n">
-        <v>3.8871431350708</v>
+        <v>3.88714361190796</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="n">
-        <v>3.92601442337036</v>
+        <v>3.92601490020752</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599267959595</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G287" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373573303223</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="n">
-        <v>4.10926628112793</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="n">
-        <v>4.10926628112793</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.31472873687744</v>
+        <v>4.31472969055176</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138751983643</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.33694076538086</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.35360050201416</v>
+        <v>4.353600025177</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.31472873687744</v>
+        <v>4.31472969055176</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138751983643</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="n">
-        <v>4.22310256958008</v>
+        <v>4.22310304641724</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="n">
-        <v>4.28696346282959</v>
+        <v>4.28696298599243</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188545227051</v>
+        <v>4.46188497543335</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G314" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="n">
-        <v>4.40913009643555</v>
+        <v>4.40913057327271</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.52574443817139</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.54240369796753</v>
+        <v>4.54240417480469</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="n">
-        <v>4.63402986526489</v>
+        <v>4.63402938842773</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.52574443817139</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="n">
-        <v>4.53962850570679</v>
+        <v>4.53962802886963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685140609741</v>
+        <v>4.53685092926025</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.52574443817139</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="n">
-        <v>4.40913009643555</v>
+        <v>4.40913057327271</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691806793213</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691806793213</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="n">
-        <v>4.36748218536377</v>
+        <v>4.36748266220093</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362272262573</v>
+        <v>4.30362224578857</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244861602783</v>
+        <v>4.44244909286499</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="n">
-        <v>4.54795742034912</v>
+        <v>4.54795694351196</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075626373291</v>
+        <v>4.50075578689575</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793519973755</v>
+        <v>4.59793472290039</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="n">
-        <v>4.60348749160767</v>
+        <v>4.60348701477051</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="n">
-        <v>4.75342082977295</v>
+        <v>4.75342035293579</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.8783655166626</v>
+        <v>4.87836503982544</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423603057861</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865699768066</v>
+        <v>4.73865795135498</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865699768066</v>
+        <v>4.73865795135498</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="n">
-        <v>4.72718381881714</v>
+        <v>4.72718334197998</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="n">
-        <v>4.74726295471191</v>
+        <v>4.74726247787476</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602718353271</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="n">
-        <v>4.7214469909668</v>
+        <v>4.72144746780396</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="n">
-        <v>4.74726295471191</v>
+        <v>4.74726247787476</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="n">
-        <v>4.68415689468384</v>
+        <v>4.68415641784668</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655168533325</v>
+        <v>4.56655216217041</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37436580657959</v>
+        <v>4.37436628341675</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42312908172607</v>
+        <v>4.42312955856323</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="n">
-        <v>4.45468235015869</v>
+        <v>4.45468187332153</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507755279541</v>
+        <v>4.55507707595825</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476196289062</v>
+        <v>4.47476148605347</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="n">
-        <v>4.56081485748291</v>
+        <v>4.56081438064575</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="n">
-        <v>4.68415689468384</v>
+        <v>4.68415641784668</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602718353271</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="n">
-        <v>4.77881622314453</v>
+        <v>4.77881574630737</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602718353271</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="n">
-        <v>4.72718381881714</v>
+        <v>4.72718334197998</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="n">
-        <v>4.73292112350464</v>
+        <v>4.73292064666748</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602718353271</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757949829102</v>
+        <v>4.82757997512817</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="n">
-        <v>4.87060642242432</v>
+        <v>4.87060594558716</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="n">
-        <v>4.81036853790283</v>
+        <v>4.81036901473999</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="n">
-        <v>4.89642143249512</v>
+        <v>4.89642190933228</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215826034546</v>
+        <v>4.90215873718262</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="n">
-        <v>4.93371200561523</v>
+        <v>4.93371152877808</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="n">
-        <v>4.80176258087158</v>
+        <v>4.80176305770874</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="n">
-        <v>4.87347412109375</v>
+        <v>4.87347459793091</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="n">
-        <v>5.05418634414673</v>
+        <v>5.05418586730957</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="n">
-        <v>5.01402807235718</v>
+        <v>5.01402759552002</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99108028411865</v>
+        <v>4.99107980728149</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="n">
-        <v>5.06565952301025</v>
+        <v>5.0656590461731</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713317871094</v>
+        <v>5.07713270187378</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="n">
-        <v>4.98247480392456</v>
+        <v>4.98247528076172</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923944473267</v>
+        <v>5.24923849105835</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397743225098</v>
+        <v>5.36397647857666</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="n">
-        <v>5.30947589874268</v>
+        <v>5.30947637557983</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118743896484</v>
+        <v>5.381187915802</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="n">
-        <v>5.54755687713623</v>
+        <v>5.54755783081055</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384765625</v>
+        <v>5.69384717941284</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="n">
-        <v>5.89750623703003</v>
+        <v>5.89750719070435</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90897989273071</v>
+        <v>5.90898036956787</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90897989273071</v>
+        <v>5.90898036956787</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555776596069</v>
+        <v>5.76555824279785</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="n">
-        <v>5.79424285888672</v>
+        <v>5.79424238204956</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.0696120262146</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.0696120262146</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061229705811</v>
+        <v>5.96061134338379</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287635803223</v>
+        <v>6.17287588119507</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="n">
-        <v>6.20729732513428</v>
+        <v>6.20729684829712</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="n">
-        <v>6.24171829223633</v>
+        <v>6.24171924591064</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="n">
-        <v>6.19008588790894</v>
+        <v>6.19008684158325</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371740341187</v>
+        <v>6.02371788024902</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.0696120262146</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319242477417</v>
+        <v>6.25319194793701</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734796524048</v>
+        <v>5.85734748840332</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476640701294</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.48158264160156</v>
+        <v>5.48158311843872</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034687042236</v>
+        <v>5.53034639358521</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476640701294</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.65082120895386</v>
+        <v>5.6508207321167</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655755996704</v>
+        <v>5.65655708312988</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903100967407</v>
+        <v>5.55903053283691</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345197677612</v>
+        <v>5.59345149993896</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="n">
-        <v>5.48445081710815</v>
+        <v>5.48445129394531</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.4615044593811</v>
+        <v>5.46150350570679</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="n">
-        <v>5.31234550476074</v>
+        <v>5.31234502792358</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171194076538</v>
+        <v>5.15171241760254</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="n">
-        <v>5.12302827835083</v>
+        <v>5.12302780151367</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913181304932</v>
+        <v>4.85913228988647</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="n">
-        <v>4.7214469909668</v>
+        <v>4.72144746780396</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423603057861</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439477920532</v>
+        <v>4.74439382553101</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849872589111</v>
+        <v>4.69849920272827</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="n">
-        <v>4.6812891960144</v>
+        <v>4.68128871917725</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239566802979</v>
+        <v>4.96239614486694</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="n">
-        <v>4.62564086914062</v>
+        <v>4.62564134597778</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245662689209</v>
+        <v>4.54245615005493</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="n">
-        <v>4.42657136917114</v>
+        <v>4.42657089233398</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057744979858</v>
+        <v>4.50057697296143</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401926040649</v>
+        <v>4.50401973724365</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="n">
-        <v>4.33937072753906</v>
+        <v>4.33937120437622</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430730819702</v>
+        <v>4.21430683135986</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732391357422</v>
+        <v>4.32732439041138</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.3078179359436</v>
+        <v>4.30781841278076</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="n">
-        <v>4.28544521331787</v>
+        <v>4.28544425964355</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449605941772</v>
+        <v>4.04449653625488</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.4123272895813</v>
+        <v>4.41232681274414</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262004852295</v>
+        <v>4.68262052536011</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="n">
-        <v>4.96278762817383</v>
+        <v>4.96278810501099</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="n">
-        <v>5.09670066833496</v>
+        <v>5.09669971466064</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493427276611</v>
+        <v>4.79493474960327</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="n">
-        <v>4.87454128265381</v>
+        <v>4.87454175949097</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813238143921</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.90601348876953</v>
+        <v>4.90601396560669</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>4.79061460494995</v>
+        <v>4.79061412811279</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430313110352</v>
+        <v>4.84430360794067</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813238143921</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029081344604</v>
+        <v>5.0602912902832</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031904220581</v>
+        <v>4.96031951904297</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.80357360839844</v>
+        <v>4.80357313156128</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="n">
-        <v>4.59684228897095</v>
+        <v>4.59684276580811</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>4.66472387313843</v>
+        <v>4.66472434997559</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.56660461425781</v>
+        <v>4.5666036605835</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>4.49872207641602</v>
+        <v>4.49872255325317</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.64991331100464</v>
+        <v>4.6499137878418</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.51908683776855</v>
+        <v>4.5190863609314</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="n">
-        <v>4.42528629302979</v>
+        <v>4.42528676986694</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="n">
-        <v>4.70257186889648</v>
+        <v>4.70257139205933</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716499328613</v>
+        <v>4.71716547012329</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="n">
-        <v>4.80870914459229</v>
+        <v>4.80870962142944</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="n">
-        <v>4.59311628341675</v>
+        <v>4.59311676025391</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>4.579185962677</v>
+        <v>4.57918643951416</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="n">
-        <v>4.62164115905762</v>
+        <v>4.62164163589478</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353227615356</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353227615356</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60174036026001</v>
+        <v>4.60173988342285</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.74303674697876</v>
+        <v>4.7430362701416</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273866653442</v>
+        <v>4.80273914337158</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>7.05399990081787</v>
       </c>
       <c r="G646" t="n">
-        <v>4.67935371398926</v>
+        <v>4.67935419082642</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="n">
-        <v>4.68930435180664</v>
+        <v>4.68930387496948</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094770431519</v>
+        <v>4.76094722747803</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="n">
-        <v>4.81600618362427</v>
+        <v>4.81600666046143</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="n">
-        <v>4.81666898727417</v>
+        <v>4.81667041778564</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.6873140335083</v>
+        <v>4.68731355667114</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="n">
-        <v>4.68134355545044</v>
+        <v>4.6813440322876</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="n">
-        <v>4.79676914215088</v>
+        <v>4.79676866531372</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.66343307495117</v>
+        <v>4.66343259811401</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="n">
-        <v>4.59112596511841</v>
+        <v>4.59112644195557</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="n">
-        <v>4.41997909545898</v>
+        <v>4.41997957229614</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="n">
-        <v>4.32445478439331</v>
+        <v>4.32445573806763</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.360276222229</v>
+        <v>4.36027669906616</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44385957717896</v>
+        <v>4.44386053085327</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589973449707</v>
+        <v>4.43589925765991</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="n">
-        <v>4.37022733688354</v>
+        <v>4.37022686004639</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818765640259</v>
+        <v>4.37818717956543</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145517349243</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="n">
-        <v>4.39211750030518</v>
+        <v>4.39211797714233</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="n">
-        <v>4.34767293930054</v>
+        <v>4.34767246246338</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818765640259</v>
+        <v>4.37818717956543</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="n">
-        <v>4.31981182098389</v>
+        <v>4.31981134414673</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="n">
-        <v>4.49029588699341</v>
+        <v>4.49029541015625</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739452362061</v>
+        <v>4.53739404678345</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012813568115</v>
+        <v>4.39012765884399</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966325759888</v>
+        <v>4.34966278076172</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984199523926</v>
+        <v>4.17984247207642</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599168777466</v>
+        <v>4.0159912109375</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312169075012</v>
+        <v>3.92312121391296</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648721694946</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="n">
-        <v>3.95297265052795</v>
+        <v>3.9529721736908</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.90720009803772</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>3.91051745414734</v>
+        <v>3.91051697731018</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.9602689743042</v>
+        <v>3.96026945114136</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="n">
-        <v>3.98614001274109</v>
+        <v>3.98614072799683</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>4.13871335983276</v>
+        <v>4.13871383666992</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="n">
-        <v>4.12544631958008</v>
+        <v>4.12544679641724</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.00604200363159</v>
+        <v>4.00604152679443</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766569137573</v>
+        <v>3.94766616821289</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260625839233</v>
+        <v>3.89260673522949</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184449195862</v>
+        <v>3.91184401512146</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="n">
-        <v>3.99940752983093</v>
+        <v>3.99940800666809</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.90720009803772</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.8521420955658</v>
+        <v>3.85214161872864</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361745834351</v>
+        <v>3.82361698150635</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.76789498329163</v>
+        <v>3.76789474487305</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848971366882</v>
+        <v>3.64848923683167</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.5794997215271</v>
+        <v>3.57950043678284</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="n">
-        <v>3.52046036720276</v>
+        <v>3.52046084403992</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57021284103394</v>
+        <v>3.57021307945251</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="n">
-        <v>3.76258730888367</v>
+        <v>3.76258778572083</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="n">
-        <v>3.85280513763428</v>
+        <v>3.85280466079712</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444777488708</v>
+        <v>3.92444753646851</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479474067688</v>
+        <v>3.85479521751404</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="n">
-        <v>3.88000273704529</v>
+        <v>3.88000297546387</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025050163269</v>
+        <v>3.83025097846985</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287321090698</v>
+        <v>3.97287368774414</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.07901191711426</v>
+        <v>4.0790114402771</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657495498657</v>
+        <v>4.16657543182373</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937664031982</v>
+        <v>4.13937711715698</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090208053589</v>
+        <v>4.10090255737305</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09957599639893</v>
+        <v>4.09957551956177</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.11284255981445</v>
+        <v>4.11284208297729</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078392982483</v>
+        <v>3.99078440666199</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567561149597</v>
+        <v>3.94567537307739</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680472373962</v>
+        <v>3.98680424690247</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="n">
-        <v>4.0730414390564</v>
+        <v>4.07304096221924</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="n">
-        <v>4.19178295135498</v>
+        <v>4.19178247451782</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="n">
-        <v>4.22030735015869</v>
+        <v>4.22030687332153</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="n">
-        <v>4.34501934051514</v>
+        <v>4.34501981735229</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609813690186</v>
+        <v>4.39609861373901</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759292602539</v>
+        <v>4.49759340286255</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069173812866</v>
+        <v>4.41069221496582</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="n">
-        <v>4.30057334899902</v>
+        <v>4.30057382583618</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408958435059</v>
+        <v>4.26408910751343</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27204990386963</v>
+        <v>4.27204942703247</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="n">
-        <v>4.38482093811035</v>
+        <v>4.38482141494751</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145517349243</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.39808797836304</v>
+        <v>4.3980884552002</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.29858446121216</v>
+        <v>4.298583984375</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511854171753</v>
+        <v>4.32511806488037</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="n">
-        <v>4.37155342102051</v>
+        <v>4.37155437469482</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>4.43789052963257</v>
+        <v>4.43789005279541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>4.45115756988525</v>
+        <v>4.4511570930481</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>4.45115756988525</v>
+        <v>4.4511570930481</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838558197021</v>
+        <v>4.33838605880737</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="n">
-        <v>4.38482093811035</v>
+        <v>4.38482141494751</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.44223308563232</v>
+        <v>4.44223260879517</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52835035324097</v>
+        <v>4.52834987640381</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G874" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G877" t="n">
-        <v>4.3704686164856</v>
+        <v>4.37046813964844</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G883" t="n">
-        <v>4.26282072067261</v>
+        <v>4.26282119750977</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18387985229492</v>
+        <v>4.18387937545776</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G890" t="n">
-        <v>4.26282072067261</v>
+        <v>4.26282119750977</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>4.3704686164856</v>
+        <v>4.37046813964844</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>4.32740926742554</v>
+        <v>4.3274097442627</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G906" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>4.24846792221069</v>
+        <v>4.24846839904785</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411512374878</v>
+        <v>4.23411560058594</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776258468628</v>
+        <v>4.09776210784912</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>4.05470323562622</v>
+        <v>4.05470371246338</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.96140909194946</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87529182434082</v>
+        <v>3.8752920627594</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246822357178</v>
+        <v>3.8824679851532</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764464378357</v>
+        <v>3.76764512062073</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764464378357</v>
+        <v>3.76764512062073</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81788015365601</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G924" t="n">
-        <v>3.76046872138977</v>
+        <v>3.76046800613403</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199744224548</v>
+        <v>3.78199815750122</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81788015365601</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.87529182434082</v>
+        <v>3.8752920627594</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658598899841</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399789810181</v>
+        <v>3.90399813652039</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G936" t="n">
-        <v>3.92552709579468</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423316955566</v>
+        <v>3.95423293113708</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>4.04035043716431</v>
+        <v>4.04035091400146</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599716186523</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.96140909194946</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599716186523</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293876647949</v>
+        <v>3.98293900489807</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.96140909194946</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423316955566</v>
+        <v>3.95423293113708</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G956" t="n">
-        <v>3.92552709579468</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>4.09058570861816</v>
+        <v>4.09058618545532</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G965" t="n">
-        <v>4.11929130554199</v>
+        <v>4.11929178237915</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>4.15517425537109</v>
+        <v>4.15517377853394</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>4.14082145690918</v>
+        <v>4.14082098007202</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211538314819</v>
+        <v>4.11211490631104</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799737930298</v>
+        <v>4.14799833297729</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G976" t="n">
-        <v>4.13364458084106</v>
+        <v>4.13364505767822</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.26282072067261</v>
+        <v>4.26282119750977</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305694580078</v>
+        <v>4.31305646896362</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G997" t="n">
-        <v>4.62164449691772</v>
+        <v>4.62164402008057</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G999" t="n">
-        <v>4.3704686164856</v>
+        <v>4.37046813964844</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.51399707794189</v>
+        <v>4.51399755477905</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940853118896</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270315170288</v>
+        <v>4.54270267486572</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.11929130554199</v>
+        <v>4.11929178237915</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729180335999</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399789810181</v>
+        <v>3.90399813652039</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.93987989425659</v>
+        <v>3.93987965583801</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.91835069656372</v>
+        <v>3.91835117340088</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505655288696</v>
+        <v>3.82505702972412</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.78917479515076</v>
+        <v>3.7891743183136</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.26529240608215</v>
+        <v>3.26529216766357</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605734825134</v>
+        <v>2.66605710983276</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076322555542</v>
+        <v>2.45076298713684</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.55482196807861</v>
+        <v>2.55482220649719</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.61223363876343</v>
+        <v>2.61223387718201</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446912765503</v>
+        <v>2.78446888923645</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423361778259</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705698013306</v>
+        <v>2.72705721855164</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70552802085876</v>
+        <v>2.70552754402161</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505723953247</v>
+        <v>2.60505747795105</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.59788060188293</v>
+        <v>2.59788084030151</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.55482196807861</v>
+        <v>2.55482220649719</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.59788060188293</v>
+        <v>2.59788084030151</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.52252793312073</v>
+        <v>2.52252769470215</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535177230835</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535177230835</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.36823391914368</v>
+        <v>2.3682336807251</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952808380127</v>
+        <v>2.33952784538269</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.31082224845886</v>
+        <v>2.31082201004028</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.25699853897095</v>
+        <v>2.25699877738953</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652847290039</v>
+        <v>2.15652823448181</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805767059326</v>
+        <v>2.17805743217468</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.25699853897095</v>
+        <v>2.25699877738953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105751991272</v>
+        <v>2.36105728149414</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005741119385</v>
+        <v>2.30005764961243</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.42564582824707</v>
+        <v>2.42564558982849</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.52611637115479</v>
+        <v>2.52611613273621</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.70552802085876</v>
+        <v>2.70552754402161</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.45793986320496</v>
+        <v>2.45793962478638</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.43999886512756</v>
+        <v>2.43999862670898</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.49382209777832</v>
+        <v>2.49382185935974</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535177230835</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535177230835</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.52611637115479</v>
+        <v>2.52611613273621</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.53709888458252</v>
+        <v>2.53709864616394</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344397544861</v>
+        <v>2.48344421386719</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.42978930473328</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.34164261817932</v>
+        <v>2.34164237976074</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.42978930473328</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.42978930473328</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.50643873214722</v>
+        <v>2.5064389705658</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679454803467</v>
+        <v>2.40679478645325</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481504440308</v>
+        <v>2.31481528282166</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.4259569644928</v>
+        <v>2.42595672607422</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715036392212</v>
+        <v>2.30715012550354</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.24966311454773</v>
+        <v>2.24966287612915</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27265810966492</v>
+        <v>2.27265787124634</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.36080479621887</v>
+        <v>2.36080503463745</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.22666835784912</v>
+        <v>2.22666811943054</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786151885986</v>
+        <v>2.10786128044128</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.06953692436218</v>
+        <v>2.0695366859436</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.9085727930069</v>
+        <v>1.90857291221619</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.91240537166595</v>
+        <v>1.91240501403809</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.625</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.01204967498779</v>
+        <v>2.01204943656921</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.01971459388733</v>
+        <v>2.01971435546875</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138999938965</v>
+        <v>1.98138988018036</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877405166626</v>
+        <v>2.49877381324768</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291072845459</v>
+        <v>2.63291049003601</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638725280762</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.67506766319275</v>
+        <v>2.67506790161133</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.64440822601318</v>
+        <v>2.6444079875946</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.6060836315155</v>
+        <v>2.60608339309692</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405217170715</v>
+        <v>2.74405241012573</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.76321506500244</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.75554966926575</v>
+        <v>2.75554990768433</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.6865656375885</v>
+        <v>2.68656516075134</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638725280762</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087950706482</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.83219909667969</v>
+        <v>2.83219933509827</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.81686949729919</v>
+        <v>2.81686925888062</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.874356508255</v>
+        <v>2.87435674667358</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.85519433021545</v>
+        <v>2.85519409179688</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.89351940155029</v>
+        <v>2.89351916313171</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620982170105</v>
+        <v>2.78620958328247</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.72489047050476</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087950706482</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87818932533264</v>
+        <v>2.87818884849548</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651391983032</v>
+        <v>2.91651368141174</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245171546936</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849342346191</v>
+        <v>3.00849318504333</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567609786987</v>
+        <v>2.93567633628845</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699592590332</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.92034649848938</v>
+        <v>2.92034602165222</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.96250367164612</v>
+        <v>2.96250343322754</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.72489047050476</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.6060836315155</v>
+        <v>2.60608339309692</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.59841823577881</v>
+        <v>2.59841847419739</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.6559054851532</v>
+        <v>2.65590524673462</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.71722483634949</v>
+        <v>2.71722507476807</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638725280762</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.76321506500244</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.85519433021545</v>
+        <v>2.85519409179688</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.9663360118866</v>
+        <v>2.96633577346802</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765583992004</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.98933100700378</v>
+        <v>2.98933124542236</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.15412712097168</v>
+        <v>3.1541268825531</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.14262962341309</v>
+        <v>3.14262986183167</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011734962463</v>
+        <v>3.20011711120605</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.54120755195618</v>
+        <v>3.5412073135376</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737473487854</v>
+        <v>3.53737449645996</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054739952087</v>
+        <v>3.51054763793945</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557337760925</v>
+        <v>3.39557313919067</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.39940595626831</v>
+        <v>3.39940571784973</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927952766418</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.14262962341309</v>
+        <v>3.14262986183167</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562509536743</v>
+        <v>3.16562485694885</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.15412712097168</v>
+        <v>3.1541268825531</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.13496494293213</v>
+        <v>3.13496518135071</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.13496494293213</v>
+        <v>3.13496518135071</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.125</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179203987122</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377178192139</v>
+        <v>3.25377154350281</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245171546936</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765583992004</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.875</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.97016859054565</v>
+        <v>2.97016835212708</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387450218201</v>
+        <v>2.79387474060059</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.75554966926575</v>
+        <v>2.75554990768433</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268110275269</v>
+        <v>2.91268134117126</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699592590332</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897519111633</v>
+        <v>3.08897542953491</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.06981301307678</v>
+        <v>3.0698127746582</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214785575867</v>
+        <v>3.06214761734009</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.115802526474</v>
+        <v>3.11580228805542</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430526733398</v>
+        <v>3.10430550575256</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651391983032</v>
+        <v>2.91651368141174</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.84752941131592</v>
+        <v>2.84752917289734</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.75</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.874356508255</v>
+        <v>2.87435674667358</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.82453441619873</v>
+        <v>2.82453417778015</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>2.83986449241638</v>
+        <v>2.8398642539978</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.72489047050476</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.72489047050476</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.76321506500244</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.88202166557312</v>
+        <v>2.88202142715454</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.115802526474</v>
+        <v>3.11580228805542</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.14262962341309</v>
+        <v>3.14262986183167</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927952766418</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011734962463</v>
+        <v>3.20011711120605</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562509536743</v>
+        <v>3.16562485694885</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.125</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179203987122</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.11197018623352</v>
+        <v>3.11196994781494</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.40707087516785</v>
+        <v>3.40707063674927</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.45306062698364</v>
+        <v>3.45306038856506</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065035820007</v>
+        <v>3.05065059661865</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.98933100700378</v>
+        <v>2.98933124542236</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.23077702522278</v>
+        <v>3.2307767868042</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844194412231</v>
+        <v>3.23844170570374</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394968986511</v>
+        <v>3.20394945144653</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.19245219230652</v>
+        <v>3.19245171546936</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.2652690410614</v>
+        <v>3.26526927947998</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491346359253</v>
+        <v>3.36491370201111</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.34958338737488</v>
+        <v>3.3495831489563</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.42240071296692</v>
+        <v>3.42240047454834</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.42240071296692</v>
+        <v>3.42240047454834</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.49521732330322</v>
+        <v>3.4952175617218</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.52204489707947</v>
+        <v>3.52204465866089</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.5067150592804</v>
+        <v>3.50671529769897</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.4607253074646</v>
+        <v>3.46072506904602</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.4147355556488</v>
+        <v>3.41473579406738</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.43006563186646</v>
+        <v>3.43006539344788</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39940595626831</v>
+        <v>3.39940571784973</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371364593506</v>
+        <v>3.21371388435364</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804208755493</v>
+        <v>3.26804184913635</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177273750305</v>
+        <v>3.40177249908447</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251877784729</v>
+        <v>3.37251901626587</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147433280945</v>
+        <v>3.30147457122803</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.26386260986328</v>
+        <v>3.26386284828186</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.33072781562805</v>
+        <v>3.33072805404663</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.36416101455688</v>
+        <v>3.36416077613831</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087701797485</v>
+        <v>3.38087725639343</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968408584595</v>
+        <v>3.25968384742737</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.07580423355103</v>
+        <v>3.0758044719696</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132730484009</v>
+        <v>2.97132706642151</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595465660095</v>
+        <v>2.84595489501953</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893878936768</v>
+        <v>3.00893902778625</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.97550630569458</v>
+        <v>2.975506067276</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729679107666</v>
+        <v>3.01729702949524</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8292384147644</v>
+        <v>2.82923817634583</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147772789001</v>
+        <v>2.74147748947144</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.8334174156189</v>
+        <v>2.83341765403748</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177857398987</v>
+        <v>2.28177881240845</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.51998615264893</v>
+        <v>2.5199863910675</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.50326991081238</v>
+        <v>2.5032696723938</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744891166687</v>
+        <v>2.50744915008545</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013535499573</v>
+        <v>2.57013511657715</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849335670471</v>
+        <v>2.57849359512329</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685159683228</v>
+        <v>2.58685183525085</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282179832458</v>
+        <v>2.63282155990601</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297052383423</v>
+        <v>2.68297076225281</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.6370005607605</v>
+        <v>2.63700032234192</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.58267259597778</v>
+        <v>2.5826723575592</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073121070862</v>
+        <v>2.77073097229004</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.88356637954712</v>
+        <v>2.8835666179657</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.47401642799377</v>
+        <v>2.4740161895752</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.4405837059021</v>
+        <v>2.44058394432068</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.48237442970276</v>
+        <v>2.48237466812134</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.44476270675659</v>
+        <v>2.44476294517517</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550922393799</v>
+        <v>2.41550946235657</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>3.75500011444092</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>3.75500011444092</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>3.71000003814697</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>3.8050000667572</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>3.65000009536743</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>95696</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>3.80999994277954</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -63285,7 +63285,7 @@
         <v>95696</v>
       </c>
       <c r="C2736" t="n">
-        <v>3.80999994277954</v>
+        <v>3.81500005722046</v>
       </c>
       <c r="D2736" t="n">
         <v>3.59999990463257</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>3.59999990463257</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>3.81500005722046</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>82076</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>3.77500009536743</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>3.76500010490417</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>3.76500010490417</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>3.72499990463257</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>50906</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>3.6800000667572</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>3.63499999046326</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>27344</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>3.71499991416931</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>31633</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>3.71499991416931</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.71499991416931</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235877990723</v>
+        <v>4.64235925674438</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G4" t="n">
-        <v>4.60015535354614</v>
+        <v>4.6001558303833</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.10179138183594</v>
       </c>
       <c r="G5" t="n">
-        <v>4.59751844406128</v>
+        <v>4.59751892089844</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409700393677</v>
+        <v>4.48409795761108</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>7.73923206329346</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39177751541138</v>
+        <v>4.39177799224854</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G11" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.01722431182861</v>
+        <v>4.01722383499146</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176956176758</v>
+        <v>3.48176980018616</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8167576789856</v>
+        <v>3.81675744056702</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522248268127</v>
+        <v>3.83522200584412</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884552001953</v>
+        <v>3.80884480476379</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6795973777771</v>
+        <v>3.67959761619568</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467126846313</v>
+        <v>3.82467150688171</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754125595093</v>
+        <v>3.92754101753235</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246831893921</v>
+        <v>3.78246736526489</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65322041511536</v>
+        <v>3.65322017669678</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090068817139</v>
+        <v>3.56090021133423</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220328330994</v>
+        <v>3.44220447540283</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078414916992</v>
+        <v>3.5107843875885</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69278597831726</v>
+        <v>3.69278573989868</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467126846313</v>
+        <v>3.82467150688171</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829430580139</v>
+        <v>3.79829382896423</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498916625977</v>
+        <v>3.73498940467834</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G38" t="n">
-        <v>3.86687350273132</v>
+        <v>3.86687445640564</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.84577250480652</v>
+        <v>3.84577322006226</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104775428772</v>
+        <v>3.8510479927063</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061403274536</v>
+        <v>3.89061379432678</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171503067017</v>
+        <v>3.91171550750732</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.0620641708374</v>
+        <v>4.06206369400024</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339920043945</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27308130264282</v>
+        <v>4.27308082580566</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803770065308</v>
+        <v>4.36803817749023</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221147537231</v>
+        <v>4.35221242904663</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473327636719</v>
+        <v>4.30473279953003</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047372817993</v>
+        <v>4.51047420501709</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44716930389404</v>
+        <v>4.44716882705688</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583427429199</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658803939819</v>
+        <v>4.19658756256104</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.5161190032959</v>
       </c>
       <c r="G62" t="n">
-        <v>4.26516819000244</v>
+        <v>4.26516771316528</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.18609809875488</v>
       </c>
       <c r="G69" t="n">
-        <v>4.07789039611816</v>
+        <v>4.07789134979248</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G70" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812252044678</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G73" t="n">
-        <v>4.24670314788818</v>
+        <v>4.2467041015625</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812252044678</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241331100464</v>
+        <v>4.2124137878418</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.25582122802734</v>
       </c>
       <c r="G78" t="n">
-        <v>4.11745643615723</v>
+        <v>4.11745595932007</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339920043945</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G85" t="n">
-        <v>4.17284822463989</v>
+        <v>4.17284870147705</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.24406576156616</v>
+        <v>4.24406623840332</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702199935913</v>
+        <v>4.15702152252197</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044343948364</v>
+        <v>4.27044248580933</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032594680786</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.52852153778076</v>
+        <v>4.52852201461792</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.48823022842407</v>
       </c>
       <c r="G109" t="n">
-        <v>4.47299146652222</v>
+        <v>4.47299098968506</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743774414062</v>
+        <v>4.46743822097778</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G111" t="n">
-        <v>4.47021389007568</v>
+        <v>4.47021436691284</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.49287796020508</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47576761245728</v>
+        <v>4.47576713562012</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G114" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357732772827</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768527030945</v>
+        <v>3.91768503189087</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989682197571</v>
+        <v>3.93989658355713</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6.38196182250977</v>
       </c>
       <c r="G118" t="n">
-        <v>3.81217646598816</v>
+        <v>3.81217622756958</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G120" t="n">
-        <v>4.01486301422119</v>
+        <v>4.01486349105835</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G121" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055077552795</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603664398193</v>
+        <v>3.87603712081909</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111489295959</v>
+        <v>3.70111513137817</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328295707703</v>
+        <v>3.82328248023987</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.94822692871094</v>
+        <v>3.94822716712952</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G136" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.11172723770142</v>
       </c>
       <c r="G138" t="n">
-        <v>4.24809217453003</v>
+        <v>4.24809169769287</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G143" t="n">
-        <v>4.40357828140259</v>
+        <v>4.40357732772827</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025880813599</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637664794922</v>
+        <v>4.35637617111206</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="n">
-        <v>4.2342095375061</v>
+        <v>4.23420906066895</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917501449585</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="n">
-        <v>4.21199750900269</v>
+        <v>4.21199703216553</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="n">
-        <v>4.2591986656189</v>
+        <v>4.25919771194458</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644474029541</v>
+        <v>4.20644378662109</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423223495483</v>
+        <v>4.18423175811768</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="n">
-        <v>4.1425838470459</v>
+        <v>4.14258337020874</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="n">
-        <v>4.1620192527771</v>
+        <v>4.16201877593994</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="n">
-        <v>4.0426287651062</v>
+        <v>4.04262924194336</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371160507202</v>
+        <v>4.10371208190918</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150005340576</v>
+        <v>4.08150100708008</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820470809937</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00931072235107</v>
+        <v>4.00931024551392</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97043800354004</v>
+        <v>3.9704384803772</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G176" t="n">
-        <v>4.01486301422119</v>
+        <v>4.01486349105835</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152275085449</v>
+        <v>4.03152322769165</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156766891479</v>
+        <v>3.93156719207764</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055077552795</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280867576599</v>
+        <v>3.64280819892883</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389199256897</v>
+        <v>3.70389151573181</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.61504244804382</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224360466003</v>
+        <v>3.66224336624146</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055077552795</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276328086853</v>
+        <v>3.74276375770569</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055101394653</v>
+        <v>3.72055077552795</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170170783997</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.61504244804382</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838390350342</v>
+        <v>3.59838366508484</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.5817244052887</v>
+        <v>3.58172464370728</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="n">
-        <v>3.59283018112183</v>
+        <v>3.59283041954041</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170170783997</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170170783997</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660147666931</v>
+        <v>3.85660171508789</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046165466309</v>
+        <v>3.92046189308167</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156766891479</v>
+        <v>3.93156719207764</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488571166992</v>
+        <v>3.9648859500885</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.94822692871094</v>
+        <v>3.94822716712952</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215424537659</v>
+        <v>3.86215448379517</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608180046082</v>
+        <v>3.77608132362366</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.78718829154968</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996443748474</v>
+        <v>3.78996467590332</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.7122220993042</v>
+        <v>3.71222162246704</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.61504244804382</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059617042542</v>
+        <v>3.62059593200684</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="n">
-        <v>3.62614846229553</v>
+        <v>3.62614893913269</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="n">
-        <v>3.59283018112183</v>
+        <v>3.59283041954041</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179178237915</v>
+        <v>3.43179202079773</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007625579834</v>
+        <v>3.5400767326355</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897047996521</v>
+        <v>3.52897024154663</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400357246399</v>
+        <v>3.45400381088257</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.47621607780457</v>
+        <v>3.47621655464172</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398206710815</v>
+        <v>3.50398230552673</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057371139526</v>
+        <v>3.67057394981384</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389199256897</v>
+        <v>3.70389151573181</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050609588623</v>
+        <v>3.82050633430481</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.78718829154968</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608180046082</v>
+        <v>3.77608132362366</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.92879033088684</v>
+        <v>3.92879056930542</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102601051331</v>
+        <v>3.90102577209473</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154592514038</v>
+        <v>3.98154497146606</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820470809937</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98709774017334</v>
+        <v>3.98709797859192</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599244117737</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820470809937</v>
+        <v>3.99820446968079</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="n">
-        <v>4.0426287651062</v>
+        <v>4.04262924194336</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="n">
-        <v>4.18700885772705</v>
+        <v>4.18700838088989</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533777236938</v>
+        <v>4.19533729553223</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="n">
-        <v>4.12037086486816</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484079360962</v>
+        <v>4.06484127044678</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="n">
-        <v>4.03429889678955</v>
+        <v>4.03429985046387</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377969741821</v>
+        <v>3.95378017425537</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86493062973022</v>
+        <v>3.86493039131165</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933365821838</v>
+        <v>3.9593334197998</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="n">
-        <v>3.88714361190796</v>
+        <v>3.88714337348938</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="n">
-        <v>3.92601442337036</v>
+        <v>3.92601418495178</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599244117737</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G287" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="n">
-        <v>4.07039356231689</v>
+        <v>4.07039451599121</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="n">
-        <v>4.15646696090698</v>
+        <v>4.15646648406982</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="n">
-        <v>4.1786789894104</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="n">
-        <v>4.1620192527771</v>
+        <v>4.16201877593994</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="n">
-        <v>4.12037086486816</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.12037086486816</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.353600025177</v>
+        <v>4.35360050201416</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025880813599</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637664794922</v>
+        <v>4.35637617111206</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917501449585</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134260177612</v>
+        <v>4.43134307861328</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.54240417480469</v>
+        <v>4.54240369796753</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461572647095</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G326" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G327" t="n">
-        <v>4.49798011779785</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132085800171</v>
+        <v>4.48132038116455</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="n">
-        <v>4.45910835266113</v>
+        <v>4.45910882949829</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G330" t="n">
-        <v>4.47021389007568</v>
+        <v>4.47021436691284</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691806793213</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691806793213</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362224578857</v>
+        <v>4.30362319946289</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244861602783</v>
+        <v>4.44244909286499</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="n">
-        <v>4.57849884033203</v>
+        <v>4.57849931716919</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461572647095</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793472290039</v>
+        <v>4.59793519973755</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="n">
-        <v>4.61459445953369</v>
+        <v>4.61459493637085</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="n">
-        <v>4.60348796844482</v>
+        <v>4.60348844528198</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346574783325</v>
+        <v>4.65346622467041</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895137786865</v>
+        <v>4.80895185470581</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010231018066</v>
+        <v>4.72010278701782</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="n">
-        <v>4.69233703613281</v>
+        <v>4.69233751296997</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423603057861</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="n">
-        <v>4.72718334197998</v>
+        <v>4.7271842956543</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="n">
-        <v>4.74726247787476</v>
+        <v>4.74726295471191</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83618450164795</v>
+        <v>4.83618354797363</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="n">
-        <v>4.74726247787476</v>
+        <v>4.74726295471191</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="n">
-        <v>4.76734209060669</v>
+        <v>4.76734256744385</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.71570920944214</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="n">
-        <v>4.58376264572144</v>
+        <v>4.58376216888428</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="n">
-        <v>4.61818265914917</v>
+        <v>4.61818361282349</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="n">
-        <v>4.61818265914917</v>
+        <v>4.61818361282349</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786754608154</v>
+        <v>4.53786659240723</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507707595825</v>
+        <v>4.55507802963257</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="n">
-        <v>4.56081438064575</v>
+        <v>4.56081485748291</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="n">
-        <v>4.6468677520752</v>
+        <v>4.64686822891235</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66120958328247</v>
+        <v>4.66121053695679</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="n">
-        <v>4.77881574630737</v>
+        <v>4.77881622314453</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="n">
-        <v>4.72718334197998</v>
+        <v>4.7271842956543</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757949829102</v>
+        <v>4.82757902145386</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="n">
-        <v>4.82184219360352</v>
+        <v>4.82184171676636</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="n">
-        <v>4.93084287643433</v>
+        <v>4.93084335327148</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215826034546</v>
+        <v>4.90215873718262</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052680969238</v>
+        <v>4.85052585601807</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="n">
-        <v>4.8390531539917</v>
+        <v>4.83905363082886</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="n">
-        <v>4.95665884017944</v>
+        <v>4.95665836334229</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255298614502</v>
+        <v>5.00255346298218</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="n">
-        <v>5.01115894317627</v>
+        <v>5.01115942001343</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="n">
-        <v>5.0656590461731</v>
+        <v>5.06565999984741</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="n">
-        <v>4.98247528076172</v>
+        <v>4.98247480392456</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="n">
-        <v>5.16318655014038</v>
+        <v>5.16318702697754</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="n">
-        <v>5.27792310714722</v>
+        <v>5.27792406082153</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397743225098</v>
+        <v>5.36397695541382</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="n">
-        <v>5.39266061782837</v>
+        <v>5.39266109466553</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="n">
-        <v>5.30947589874268</v>
+        <v>5.30947685241699</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118743896484</v>
+        <v>5.381187915802</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="n">
-        <v>5.54755783081055</v>
+        <v>5.54755735397339</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818996429443</v>
+        <v>5.70819044113159</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="n">
-        <v>5.98356008529663</v>
+        <v>5.98356056213379</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208499908447</v>
+        <v>5.97208595275879</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="n">
-        <v>5.89750671386719</v>
+        <v>5.89750623703003</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766498565674</v>
+        <v>5.9376654624939</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292699813843</v>
+        <v>5.82292604446411</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="n">
-        <v>5.68237400054932</v>
+        <v>5.68237352371216</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287683486938</v>
+        <v>6.17287635803223</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="n">
-        <v>6.24171829223633</v>
+        <v>6.24171781539917</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="n">
-        <v>6.17861223220825</v>
+        <v>6.17861270904541</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371692657471</v>
+        <v>6.02371740341187</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="n">
-        <v>6.21877098083496</v>
+        <v>6.21877145767212</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36792993545532</v>
+        <v>6.36793041229248</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645580291748</v>
+        <v>6.3564567565918</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="n">
-        <v>6.48266696929932</v>
+        <v>6.48266744613647</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="n">
-        <v>6.48266696929932</v>
+        <v>6.48266744613647</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.42529821395874</v>
+        <v>6.4252986907959</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319290161133</v>
+        <v>6.25319194793701</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="n">
-        <v>5.62213659286499</v>
+        <v>5.62213611602783</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="n">
-        <v>5.60492563247681</v>
+        <v>5.60492515563965</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.4815821647644</v>
+        <v>5.48158311843872</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="n">
-        <v>5.53608226776123</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460908889771</v>
+        <v>5.52460861206055</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.65082120895386</v>
+        <v>5.6508207321167</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655708312988</v>
+        <v>5.65655755996704</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818996429443</v>
+        <v>5.70819044113159</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="n">
-        <v>5.74834775924683</v>
+        <v>5.74834728240967</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="n">
-        <v>5.71966314315796</v>
+        <v>5.7196626663208</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345149993896</v>
+        <v>5.59345197677612</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="n">
-        <v>5.48445177078247</v>
+        <v>5.48445081710815</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="n">
-        <v>5.53608226776123</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.495924949646</v>
+        <v>5.49592542648315</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.4615044593811</v>
+        <v>5.46150302886963</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="n">
-        <v>5.3123459815979</v>
+        <v>5.31234550476074</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="n">
-        <v>5.39266061782837</v>
+        <v>5.39266109466553</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="n">
-        <v>5.26645040512085</v>
+        <v>5.26644992828369</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="n">
-        <v>4.97386884689331</v>
+        <v>4.97386837005615</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913228988647</v>
+        <v>4.85913181304932</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423603057861</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439477920532</v>
+        <v>4.74439430236816</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="n">
-        <v>4.82471132278442</v>
+        <v>4.82471084594727</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239519119263</v>
+        <v>4.96239566802979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71570920944214</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="n">
-        <v>4.58949851989746</v>
+        <v>4.58949899673462</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245662689209</v>
+        <v>4.54245615005493</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="n">
-        <v>4.371497631073</v>
+        <v>4.37149715423584</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="n">
-        <v>4.35371398925781</v>
+        <v>4.35371351242065</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430730819702</v>
+        <v>4.21430778503418</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732391357422</v>
+        <v>4.32732439041138</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.30781841278076</v>
+        <v>4.3078179359436</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="n">
-        <v>4.14259719848633</v>
+        <v>4.14259672164917</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449605941772</v>
+        <v>4.04449653625488</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="n">
-        <v>4.78259181976318</v>
+        <v>4.78259229660034</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="n">
-        <v>4.96278810501099</v>
+        <v>4.96278762817383</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="n">
-        <v>5.09670066833496</v>
+        <v>5.0967001914978</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="n">
-        <v>4.99549531936646</v>
+        <v>4.99549436569214</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493474960327</v>
+        <v>4.79493379592896</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>4.81344795227051</v>
+        <v>4.81344747543335</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086687088013</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.81344795227051</v>
+        <v>4.81344747543335</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813238143921</v>
+        <v>4.83813190460205</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.90601396560669</v>
+        <v>4.90601348876953</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>4.81344795227051</v>
+        <v>4.81344747543335</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>4.76161098480225</v>
+        <v>4.76161003112793</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="n">
-        <v>4.84862232208252</v>
+        <v>4.84862279891968</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="n">
-        <v>4.86281585693359</v>
+        <v>4.86281633377075</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430360794067</v>
+        <v>4.84430265426636</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="n">
-        <v>4.93686962127686</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132905960083</v>
+        <v>4.88132953643799</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813238143921</v>
+        <v>4.83813190460205</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031951904297</v>
+        <v>4.96031904220581</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="n">
-        <v>4.93686962127686</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086687088013</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>4.61288690567017</v>
+        <v>4.61288738250732</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="n">
-        <v>4.54870796203613</v>
+        <v>4.54870748519897</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>4.49872255325317</v>
+        <v>4.49872207641602</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.39072751998901</v>
+        <v>4.39072847366333</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>4.17474031448364</v>
+        <v>4.17473983764648</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="n">
-        <v>4.6252293586731</v>
+        <v>4.62522983551025</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="n">
-        <v>4.42528629302979</v>
+        <v>4.42528676986694</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="n">
-        <v>4.70257091522217</v>
+        <v>4.70257139205933</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="n">
-        <v>4.81534290313721</v>
+        <v>4.81534242630005</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="n">
-        <v>4.80870914459229</v>
+        <v>4.80870962142944</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="n">
-        <v>4.6262845993042</v>
+        <v>4.62628507614136</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>4.579185962677</v>
+        <v>4.57918548583984</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="n">
-        <v>4.56061220169067</v>
+        <v>4.56061172485352</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.5652551651001</v>
+        <v>4.56525564193726</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60173988342285</v>
+        <v>4.60174036026001</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.74303674697876</v>
+        <v>4.7430362701416</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273914337158</v>
+        <v>4.80273866653442</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>4.7927885055542</v>
+        <v>4.79278802871704</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>4.65679931640625</v>
+        <v>4.65679979324341</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="n">
-        <v>4.68930387496948</v>
+        <v>4.68930435180664</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711563110352</v>
+        <v>4.72711610794067</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094675064087</v>
+        <v>4.76094722747803</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="n">
-        <v>4.81600666046143</v>
+        <v>4.81600618362427</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.68731355667114</v>
+        <v>4.68731451034546</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="n">
-        <v>4.68134355545044</v>
+        <v>4.6813440322876</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="n">
-        <v>4.73043251037598</v>
+        <v>4.73043298721313</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="n">
-        <v>4.79676914215088</v>
+        <v>4.79676866531372</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="n">
-        <v>4.76492691040039</v>
+        <v>4.76492738723755</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="n">
-        <v>4.59776020050049</v>
+        <v>4.59776067733765</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="n">
-        <v>4.59112691879272</v>
+        <v>4.59112644195557</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30588150024414</v>
+        <v>4.30588054656982</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.360276222229</v>
+        <v>4.36027669906616</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589925765991</v>
+        <v>4.43590021133423</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="n">
-        <v>4.37022686004639</v>
+        <v>4.37022733688354</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="n">
-        <v>4.3569598197937</v>
+        <v>4.35696029663086</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>4.36160326004028</v>
+        <v>4.36160373687744</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="n">
-        <v>4.37089061737061</v>
+        <v>4.37089014053345</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>4.3516526222229</v>
+        <v>4.35165309906006</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="n">
-        <v>4.32710838317871</v>
+        <v>4.32710790634155</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739404678345</v>
+        <v>4.53739452362061</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392908096313</v>
+        <v>4.56392860412598</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392908096313</v>
+        <v>4.56392860412598</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="n">
-        <v>4.48299884796143</v>
+        <v>4.48299837112427</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012813568115</v>
+        <v>4.39012765884399</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010894775391</v>
+        <v>4.26010847091675</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.24551486968994</v>
+        <v>4.2455153465271</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984294891357</v>
+        <v>4.17984199523926</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599168777466</v>
+        <v>4.01599216461182</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312121391296</v>
+        <v>3.92312097549438</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>3.94899249076843</v>
+        <v>3.94899272918701</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.8474977016449</v>
+        <v>3.84749817848206</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648745536804</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="n">
-        <v>3.95297265052795</v>
+        <v>3.95297241210938</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720081329346</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026945114136</v>
+        <v>3.96026921272278</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="n">
-        <v>3.94434905052185</v>
+        <v>3.94434881210327</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="n">
-        <v>4.14601039886475</v>
+        <v>4.14601135253906</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>4.07237815856934</v>
+        <v>4.07237768173218</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.21234703063965</v>
+        <v>4.21234655380249</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="n">
-        <v>4.07237815856934</v>
+        <v>4.07237768173218</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04717016220093</v>
+        <v>4.04716968536377</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>3.98945713043213</v>
+        <v>3.98945760726929</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766616821289</v>
+        <v>3.94766569137573</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260625839233</v>
+        <v>3.89260649681091</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184401512146</v>
+        <v>3.91184449195862</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="n">
-        <v>3.99940800666809</v>
+        <v>3.99940776824951</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.08630847930908</v>
+        <v>4.08630800247192</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05115032196045</v>
+        <v>4.05114984512329</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.96889305114746</v>
+        <v>3.96889352798462</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189337730408</v>
+        <v>3.90189361572266</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720081329346</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88730001449585</v>
+        <v>3.88729977607727</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.8521420955658</v>
+        <v>3.85214161872864</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811138153076</v>
+        <v>3.85811185836792</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361745834351</v>
+        <v>3.82361674308777</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="n">
-        <v>3.7499840259552</v>
+        <v>3.74998378753662</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219145774841</v>
+        <v>3.84219121932983</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.73737931251526</v>
+        <v>3.73738026618958</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848923683167</v>
+        <v>3.64848947525024</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490612030029</v>
+        <v>3.56490564346313</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="n">
-        <v>3.76258778572083</v>
+        <v>3.76258730888367</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="n">
-        <v>3.85280513763428</v>
+        <v>3.8528048992157</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.91980481147766</v>
+        <v>3.91980457305908</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587401390076</v>
+        <v>3.90587377548218</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444753646851</v>
+        <v>3.92444801330566</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479521751404</v>
+        <v>3.85479474067688</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="n">
-        <v>3.8156566619873</v>
+        <v>3.81565713882446</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.89857649803162</v>
+        <v>3.89857721328735</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="n">
-        <v>3.88000273704529</v>
+        <v>3.88000249862671</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025050163269</v>
+        <v>3.83025074005127</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="n">
-        <v>3.92842793464661</v>
+        <v>3.92842817306519</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287321090698</v>
+        <v>3.97287368774414</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.07901096343994</v>
+        <v>4.0790114402771</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657543182373</v>
+        <v>4.16657447814941</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="n">
-        <v>4.13805055618286</v>
+        <v>4.1380500793457</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937664031982</v>
+        <v>4.13937711715698</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090208053589</v>
+        <v>4.10090303421021</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09957551956177</v>
+        <v>4.09957599639893</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078440666199</v>
+        <v>3.99078416824341</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017024993896</v>
+        <v>3.98017048835754</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567561149597</v>
+        <v>3.94567537307739</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="n">
-        <v>4.08896160125732</v>
+        <v>4.08896207809448</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="n">
-        <v>4.07304096221924</v>
+        <v>4.07304048538208</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13407039642334</v>
+        <v>4.13406991958618</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="n">
-        <v>4.22030687332153</v>
+        <v>4.22030782699585</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="n">
-        <v>4.34501981735229</v>
+        <v>4.34501934051514</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848478317261</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531694412231</v>
+        <v>4.28531742095947</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="n">
-        <v>4.29194974899292</v>
+        <v>4.29195117950439</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609861373901</v>
+        <v>4.39609813690186</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="n">
-        <v>4.41666269302368</v>
+        <v>4.41666221618652</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759340286255</v>
+        <v>4.49759292602539</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="n">
-        <v>4.41002893447876</v>
+        <v>4.4100284576416</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069173812866</v>
+        <v>4.41069221496582</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="n">
-        <v>4.34899997711182</v>
+        <v>4.34899950027466</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="n">
-        <v>4.30057334899902</v>
+        <v>4.30057382583618</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408910751343</v>
+        <v>4.26408958435059</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848478317261</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="n">
-        <v>4.38482046127319</v>
+        <v>4.38482141494751</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.39808797836304</v>
+        <v>4.3980884552002</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511806488037</v>
+        <v>4.32511854171753</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="n">
-        <v>4.37155389785767</v>
+        <v>4.37155342102051</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>4.43789052963257</v>
+        <v>4.43789005279541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="n">
-        <v>4.45779037475586</v>
+        <v>4.45779085159302</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>4.46442413330078</v>
+        <v>4.46442461013794</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066156387329</v>
+        <v>4.55066108703613</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="n">
-        <v>4.38482046127319</v>
+        <v>4.38482141494751</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.44223308563232</v>
+        <v>4.44223260879517</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G858" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52834987640381</v>
+        <v>4.52835035324097</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140874862671</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>4.549880027771</v>
+        <v>4.54987955093384</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G863" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G864" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>6.25</v>
       </c>
       <c r="G873" t="n">
-        <v>4.48529100418091</v>
+        <v>4.48529148101807</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G874" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>4.29152727127075</v>
+        <v>4.29152631759644</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.16952657699585</v>
+        <v>4.16952705383301</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G888" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18387937545776</v>
+        <v>4.18388032913208</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G898" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>4.32740879058838</v>
+        <v>4.3274097442627</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411512374878</v>
+        <v>4.23411464691162</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129104614258</v>
+        <v>4.24129152297974</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776210784912</v>
+        <v>4.09776258468628</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140909194946</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.8824679851532</v>
+        <v>3.88246822357178</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764464378357</v>
+        <v>3.76764535903931</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764464378357</v>
+        <v>3.76764535903931</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81787991523743</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G924" t="n">
-        <v>3.76046824455261</v>
+        <v>3.76046848297119</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658622741699</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658622741699</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352687835693</v>
+        <v>3.80352783203125</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81787991523743</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.83223295211792</v>
+        <v>3.8322331905365</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658622741699</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G936" t="n">
-        <v>3.92552709579468</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423364639282</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>4.04035091400146</v>
+        <v>4.04034996032715</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140909194946</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293852806091</v>
+        <v>3.98293876647949</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140909194946</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423364639282</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682054519653</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G956" t="n">
-        <v>3.92552709579468</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G965" t="n">
-        <v>4.11929178237915</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>4.14082098007202</v>
+        <v>4.14082145690918</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211490631104</v>
+        <v>4.11211538314819</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16952657699585</v>
+        <v>4.16952705383301</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>4.16952657699585</v>
+        <v>4.16952705383301</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G977" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>6</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305599212646</v>
+        <v>4.31305646896362</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552722930908</v>
+        <v>4.53552675247192</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.51399707794189</v>
+        <v>4.51399755477905</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.48529100418091</v>
+        <v>4.48529148101807</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.45658540725708</v>
+        <v>4.45658588409424</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.41352653503418</v>
+        <v>4.4135274887085</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.46376180648804</v>
+        <v>4.46376132965088</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>6</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.50682163238525</v>
+        <v>4.50682067871094</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.55705595016479</v>
+        <v>4.55705642700195</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140874862671</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.52117395401001</v>
+        <v>4.52117347717285</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811508178711</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.11929178237915</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.16952657699585</v>
+        <v>4.16952705383301</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682054519653</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.91835069656372</v>
+        <v>3.91835117340088</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505631446838</v>
+        <v>3.82505655288696</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.78917479515076</v>
+        <v>3.78917455673218</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.35858631134033</v>
+        <v>3.35858583450317</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299823760986</v>
+        <v>2.62299847602844</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605710983276</v>
+        <v>2.66605734825134</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076298713684</v>
+        <v>2.450763463974</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682194709778</v>
+        <v>2.67682218551636</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446888923645</v>
+        <v>2.78446912765503</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.70911622047424</v>
+        <v>2.70911598205566</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.69117522239685</v>
+        <v>2.69117498397827</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.65529251098633</v>
+        <v>2.65529274940491</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505747795105</v>
+        <v>2.60505723953247</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.625</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.60146903991699</v>
+        <v>2.60146927833557</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.59788084030151</v>
+        <v>2.59788060188293</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.53688073158264</v>
+        <v>2.5368812084198</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.56199836730957</v>
+        <v>2.56199860572815</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.59788084030151</v>
+        <v>2.59788060188293</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.50099849700928</v>
+        <v>2.5009982585907</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952784538269</v>
+        <v>2.33952808380127</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.25699853897095</v>
+        <v>2.25699877738953</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652799606323</v>
+        <v>2.15652823448181</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.25699853897095</v>
+        <v>2.25699877738953</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105751991272</v>
+        <v>2.36105728149414</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005717277527</v>
+        <v>2.30005764961243</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.33235144615173</v>
+        <v>2.33235168457031</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.35388088226318</v>
+        <v>2.35388112068176</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.52611613273621</v>
+        <v>2.52611637115479</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.45793962478638</v>
+        <v>2.45793986320496</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.56199836730957</v>
+        <v>2.56199860572815</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56199836730957</v>
+        <v>2.56199860572815</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.411292552948</v>
+        <v>2.41129279136658</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.375</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.42205715179443</v>
+        <v>2.42205762863159</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.49023389816284</v>
+        <v>2.49023365974426</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.50817489624023</v>
+        <v>2.50817513465881</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.52611613273621</v>
+        <v>2.52611637115479</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>3.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.50099849700928</v>
+        <v>2.5009982585907</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.54405736923218</v>
+        <v>2.54405760765076</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344421386719</v>
+        <v>2.48344397544861</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.5064389705658</v>
+        <v>2.50643873214722</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679478645325</v>
+        <v>2.40679454803467</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481528282166</v>
+        <v>2.31481504440308</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697269439697</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697269439697</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.39912962913513</v>
+        <v>2.39912986755371</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.42595672607422</v>
+        <v>2.4259569644928</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.125</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.39529705047607</v>
+        <v>2.39529728889465</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.47961139678955</v>
+        <v>2.47961187362671</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715012550354</v>
+        <v>2.30715036392212</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27265787124634</v>
+        <v>2.27265810966492</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.36080503463745</v>
+        <v>2.36080479621887</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750594139099</v>
+        <v>2.20750617980957</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786128044128</v>
+        <v>2.10786151885986</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.89707517623901</v>
+        <v>1.8970752954483</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.91240501403809</v>
+        <v>1.91240537166595</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.625</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.01204943656921</v>
+        <v>2.01204991340637</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.01971435546875</v>
+        <v>2.01971459388733</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138988018036</v>
+        <v>1.98138976097107</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877381324768</v>
+        <v>2.49877405166626</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291049003601</v>
+        <v>2.63291072845459</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.6444079875946</v>
+        <v>2.64440822601318</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405241012573</v>
+        <v>2.74405217170715</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321506500244</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68656516075134</v>
+        <v>2.68656539916992</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.77087950706482</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.81686925888062</v>
+        <v>2.81686949729919</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87435674667358</v>
+        <v>2.874356508255</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285901069641</v>
+        <v>2.86285924911499</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.70572781562805</v>
+        <v>2.70572757720947</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.77087950706482</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.8053719997406</v>
+        <v>2.80537176132202</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87818884849548</v>
+        <v>2.87818932533264</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651368141174</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.19245171546936</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567633628845</v>
+        <v>2.93567609786987</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.92034602165222</v>
+        <v>2.92034649848938</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.66357040405273</v>
+        <v>2.66357016563416</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.70572781562805</v>
+        <v>2.70572757720947</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.70572781562805</v>
+        <v>2.70572757720947</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.65590524673462</v>
+        <v>2.6559054851532</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.73638725280762</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321506500244</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.96633577346802</v>
+        <v>2.9663360118866</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765536308289</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933076858521</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.1541268825531</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676677703857</v>
+        <v>3.27676653862</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.43389821052551</v>
+        <v>3.43389797210693</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.5412073135376</v>
+        <v>3.54120755195618</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737449645996</v>
+        <v>3.53737473487854</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927952766418</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.1541268825531</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.125</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.16179203987122</v>
+        <v>3.16179227828979</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610662460327</v>
+        <v>3.24610686302185</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.19245171546936</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.12730002403259</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765536308289</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166608810425</v>
+        <v>2.98166632652283</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.875</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.97016835212708</v>
+        <v>2.97016859054565</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.86669182777405</v>
+        <v>2.86669158935547</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387474060059</v>
+        <v>2.79387450218201</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.03148818016052</v>
+        <v>3.03148794174194</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214761734009</v>
+        <v>3.06214785575867</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.11580228805542</v>
+        <v>3.115802526474</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681825637817</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430550575256</v>
+        <v>3.10430526733398</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651368141174</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.75</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.87435674667358</v>
+        <v>2.874356508255</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.82453417778015</v>
+        <v>2.82453465461731</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.66357040405273</v>
+        <v>2.66357016563416</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321506500244</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.88202142715454</v>
+        <v>2.88202166557312</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.11580228805542</v>
+        <v>3.115802526474</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.12730002403259</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927952766418</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681825637817</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.125</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.16179203987122</v>
+        <v>3.16179227828979</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.24227452278137</v>
+        <v>3.24227428436279</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.24993896484375</v>
+        <v>3.24993920326233</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.12730002403259</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.40707063674927</v>
+        <v>3.40707111358643</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.30359363555908</v>
+        <v>3.30359387397766</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933076858521</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.2307767868042</v>
+        <v>3.23077702522278</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394945144653</v>
+        <v>3.20394968986511</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059911727905</v>
+        <v>3.28059935569763</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.27293419837952</v>
+        <v>3.27293372154236</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.19245171546936</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491370201111</v>
+        <v>3.36491322517395</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.3495831489563</v>
+        <v>3.34958362579346</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.42240047454834</v>
+        <v>3.42240071296692</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.42240047454834</v>
+        <v>3.42240071296692</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.5028829574585</v>
+        <v>3.50288271903992</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>4.625</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.54503965377808</v>
+        <v>3.54503989219666</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372030258179</v>
+        <v>3.48372006416321</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.52204465866089</v>
+        <v>3.52204513549805</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.50671529769897</v>
+        <v>3.50671482086182</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.41473579406738</v>
+        <v>3.41473531723022</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.43006539344788</v>
+        <v>3.43006563186646</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371388435364</v>
+        <v>3.21371364593506</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804184913635</v>
+        <v>3.26804208755493</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177249908447</v>
+        <v>3.40177273750305</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251901626587</v>
+        <v>3.37251877784729</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147457122803</v>
+        <v>3.30147433280945</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.26386284828186</v>
+        <v>3.26386260986328</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.33072805404663</v>
+        <v>3.33072781562805</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.36416077613831</v>
+        <v>3.36416101455688</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087725639343</v>
+        <v>3.38087701797485</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968384742737</v>
+        <v>3.25968408584595</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.0758044719696</v>
+        <v>3.07580423355103</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043182373047</v>
+        <v>2.95043158531189</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.90446162223816</v>
+        <v>2.90446186065674</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132706642151</v>
+        <v>2.97132730484009</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.90446162223816</v>
+        <v>2.90446186065674</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595489501953</v>
+        <v>2.84595465660095</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893902778625</v>
+        <v>3.00893878936768</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.975506067276</v>
+        <v>2.97550630569458</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729702949524</v>
+        <v>3.01729679107666</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043182373047</v>
+        <v>2.95043158531189</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.82923817634583</v>
+        <v>2.8292384147644</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147748947144</v>
+        <v>2.74147772789001</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.83341765403748</v>
+        <v>2.8334174156189</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177881240845</v>
+        <v>2.28177857398987</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.5199863910675</v>
+        <v>2.51998615264893</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.5032696723938</v>
+        <v>2.50326991081238</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744915008545</v>
+        <v>2.50744891166687</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013511657715</v>
+        <v>2.57013535499573</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849359512329</v>
+        <v>2.57849335670471</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685183525085</v>
+        <v>2.58685159683228</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282155990601</v>
+        <v>2.63282179832458</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297076225281</v>
+        <v>2.68297052383423</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.63700032234192</v>
+        <v>2.6370005607605</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.5826723575592</v>
+        <v>2.58267259597778</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073097229004</v>
+        <v>2.77073121070862</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.8835666179657</v>
+        <v>2.88356637954712</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.4740161895752</v>
+        <v>2.47401642799377</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.44058394432068</v>
+        <v>2.4405837059021</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.48237466812134</v>
+        <v>2.48237442970276</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.44476294517517</v>
+        <v>2.44476270675659</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550946235657</v>
+        <v>2.41550922393799</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>3.75</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>60041</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -543,7 +543,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409748077393</v>
+        <v>4.48409700393677</v>
       </c>
       <c r="H6" t="n">
         <v>164680</v>
@@ -572,7 +572,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37858819961548</v>
+        <v>4.37858867645264</v>
       </c>
       <c r="H7" t="n">
         <v>111248</v>
@@ -601,7 +601,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H8" t="n">
         <v>127969</v>
@@ -630,7 +630,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50783634185791</v>
+        <v>4.50783681869507</v>
       </c>
       <c r="H9" t="n">
         <v>83967</v>
@@ -717,7 +717,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0172233581543</v>
+        <v>4.01722383499146</v>
       </c>
       <c r="H12" t="n">
         <v>222009</v>
@@ -746,7 +746,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90380191802979</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H13" t="n">
         <v>164720</v>
@@ -775,7 +775,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176980018616</v>
+        <v>3.48177003860474</v>
       </c>
       <c r="H14" t="n">
         <v>416053</v>
@@ -804,7 +804,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74553894996643</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H15" t="n">
         <v>313484</v>
@@ -833,7 +833,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.81675720214844</v>
+        <v>3.81675815582275</v>
       </c>
       <c r="H16" t="n">
         <v>176408</v>
@@ -862,7 +862,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.89588952064514</v>
+        <v>3.89588904380798</v>
       </c>
       <c r="H17" t="n">
         <v>120439</v>
@@ -891,7 +891,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8352222442627</v>
+        <v>3.83522176742554</v>
       </c>
       <c r="H18" t="n">
         <v>75537</v>
@@ -920,7 +920,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884504318237</v>
+        <v>3.80884552001953</v>
       </c>
       <c r="H19" t="n">
         <v>163830</v>
@@ -949,7 +949,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959690093994</v>
+        <v>3.67959713935852</v>
       </c>
       <c r="H20" t="n">
         <v>133261</v>
@@ -978,7 +978,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467103004456</v>
+        <v>3.82467126846313</v>
       </c>
       <c r="H21" t="n">
         <v>190130</v>
@@ -1007,7 +1007,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754125595093</v>
+        <v>3.92754149436951</v>
       </c>
       <c r="H22" t="n">
         <v>169554</v>
@@ -1036,7 +1036,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74553894996643</v>
+        <v>3.74553990364075</v>
       </c>
       <c r="H23" t="n">
         <v>350145</v>
@@ -1065,7 +1065,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246808052063</v>
+        <v>3.78246760368347</v>
       </c>
       <c r="H24" t="n">
         <v>251231</v>
@@ -1123,7 +1123,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.6532199382782</v>
+        <v>3.65322041511536</v>
       </c>
       <c r="H26" t="n">
         <v>190657</v>
@@ -1152,7 +1152,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405804634094</v>
+        <v>3.33405780792236</v>
       </c>
       <c r="H27" t="n">
         <v>238163</v>
@@ -1181,7 +1181,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626099586487</v>
+        <v>3.37626123428345</v>
       </c>
       <c r="H28" t="n">
         <v>216081</v>
@@ -1210,7 +1210,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090021133423</v>
+        <v>3.56090068817139</v>
       </c>
       <c r="H29" t="n">
         <v>200231</v>
@@ -1268,7 +1268,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078462600708</v>
+        <v>3.5107843875885</v>
       </c>
       <c r="H31" t="n">
         <v>208699</v>
@@ -1297,7 +1297,7 @@
         <v>6.60507488250732</v>
       </c>
       <c r="G32" t="n">
-        <v>3.74817800521851</v>
+        <v>3.74817776679993</v>
       </c>
       <c r="H32" t="n">
         <v>131098</v>
@@ -1355,7 +1355,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467103004456</v>
+        <v>3.82467126846313</v>
       </c>
       <c r="H34" t="n">
         <v>72733</v>
@@ -1384,7 +1384,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829406738281</v>
+        <v>3.79829359054565</v>
       </c>
       <c r="H35" t="n">
         <v>53341</v>
@@ -1413,7 +1413,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498916625977</v>
+        <v>3.73498940467834</v>
       </c>
       <c r="H36" t="n">
         <v>83765</v>
@@ -1442,7 +1442,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699147224426</v>
+        <v>3.9169909954071</v>
       </c>
       <c r="H37" t="n">
         <v>87617</v>
@@ -1500,7 +1500,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.81412029266357</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H39" t="n">
         <v>93458</v>
@@ -1558,7 +1558,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104894638062</v>
+        <v>3.85104823112488</v>
       </c>
       <c r="H41" t="n">
         <v>113404</v>
@@ -1616,7 +1616,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171455383301</v>
+        <v>3.91171503067017</v>
       </c>
       <c r="H43" t="n">
         <v>374802</v>
@@ -1645,7 +1645,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.0910792350769</v>
+        <v>4.09107971191406</v>
       </c>
       <c r="H44" t="n">
         <v>354322</v>
@@ -1674,7 +1674,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.06206464767456</v>
+        <v>4.0620641708374</v>
       </c>
       <c r="H45" t="n">
         <v>183400</v>
@@ -1703,7 +1703,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H46" t="n">
         <v>380676</v>
@@ -1732,7 +1732,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339872360229</v>
       </c>
       <c r="H47" t="n">
         <v>153285</v>
@@ -1848,7 +1848,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803817749023</v>
+        <v>4.36803865432739</v>
       </c>
       <c r="H51" t="n">
         <v>187212</v>
@@ -1877,7 +1877,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H52" t="n">
         <v>135917</v>
@@ -1906,7 +1906,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221242904663</v>
+        <v>4.35221147537231</v>
       </c>
       <c r="H53" t="n">
         <v>202614</v>
@@ -1935,7 +1935,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473327636719</v>
+        <v>4.30473279953003</v>
       </c>
       <c r="H54" t="n">
         <v>145802</v>
@@ -1964,7 +1964,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G55" t="n">
-        <v>4.41024160385132</v>
+        <v>4.41024112701416</v>
       </c>
       <c r="H55" t="n">
         <v>165321</v>
@@ -1993,7 +1993,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047420501709</v>
+        <v>4.51047372817993</v>
       </c>
       <c r="H56" t="n">
         <v>440847</v>
@@ -2109,7 +2109,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658803939819</v>
+        <v>4.19658756256104</v>
       </c>
       <c r="H60" t="n">
         <v>142725</v>
@@ -2138,7 +2138,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H61" t="n">
         <v>168165</v>
@@ -2167,7 +2167,7 @@
         <v>7.5161190032959</v>
       </c>
       <c r="G62" t="n">
-        <v>4.26516723632812</v>
+        <v>4.26516771316528</v>
       </c>
       <c r="H62" t="n">
         <v>175234</v>
@@ -2196,7 +2196,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H63" t="n">
         <v>152427</v>
@@ -2254,7 +2254,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H65" t="n">
         <v>63157</v>
@@ -2341,7 +2341,7 @@
         <v>7.18144989013672</v>
       </c>
       <c r="G68" t="n">
-        <v>4.0752534866333</v>
+        <v>4.07525253295898</v>
       </c>
       <c r="H68" t="n">
         <v>38160</v>
@@ -2370,7 +2370,7 @@
         <v>7.18609809875488</v>
       </c>
       <c r="G69" t="n">
-        <v>4.07789087295532</v>
+        <v>4.07789039611816</v>
       </c>
       <c r="H69" t="n">
         <v>110418</v>
@@ -2428,7 +2428,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G71" t="n">
-        <v>4.08844184875488</v>
+        <v>4.08844137191772</v>
       </c>
       <c r="H71" t="n">
         <v>110301</v>
@@ -2457,7 +2457,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812395095825</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H72" t="n">
         <v>138383</v>
@@ -2515,7 +2515,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812395095825</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H74" t="n">
         <v>11963</v>
@@ -2602,7 +2602,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241426467896</v>
+        <v>4.2124137878418</v>
       </c>
       <c r="H77" t="n">
         <v>65491</v>
@@ -2805,7 +2805,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339872360229</v>
       </c>
       <c r="H84" t="n">
         <v>135960</v>
@@ -2834,7 +2834,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G85" t="n">
-        <v>4.17284774780273</v>
+        <v>4.17284822463989</v>
       </c>
       <c r="H85" t="n">
         <v>25765</v>
@@ -2863,7 +2863,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119577407837</v>
+        <v>4.14119625091553</v>
       </c>
       <c r="H86" t="n">
         <v>95409</v>
@@ -2892,7 +2892,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009429931641</v>
+        <v>4.12009382247925</v>
       </c>
       <c r="H87" t="n">
         <v>20188</v>
@@ -2979,7 +2979,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383363723755</v>
+        <v>4.14383316040039</v>
       </c>
       <c r="H90" t="n">
         <v>26575</v>
@@ -3008,7 +3008,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.24406576156616</v>
+        <v>4.24406671524048</v>
       </c>
       <c r="H91" t="n">
         <v>211317</v>
@@ -3066,7 +3066,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702199935913</v>
+        <v>4.15702247619629</v>
       </c>
       <c r="H93" t="n">
         <v>72826</v>
@@ -3095,7 +3095,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G94" t="n">
-        <v>4.23351573944092</v>
+        <v>4.23351526260376</v>
       </c>
       <c r="H94" t="n">
         <v>64992</v>
@@ -3124,7 +3124,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044296264648</v>
+        <v>4.27044343948364</v>
       </c>
       <c r="H95" t="n">
         <v>62480</v>
@@ -3153,7 +3153,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131278991699</v>
+        <v>4.19131135940552</v>
       </c>
       <c r="H96" t="n">
         <v>58862</v>
@@ -3240,7 +3240,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032642364502</v>
+        <v>4.22032690048218</v>
       </c>
       <c r="H99" t="n">
         <v>83655</v>
@@ -3298,7 +3298,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G101" t="n">
-        <v>4.41190814971924</v>
+        <v>4.41190719604492</v>
       </c>
       <c r="H101" t="n">
         <v>66996</v>
@@ -3327,7 +3327,7 @@
         <v>7.51147079467773</v>
       </c>
       <c r="G102" t="n">
-        <v>4.48687314987183</v>
+        <v>4.48687362670898</v>
       </c>
       <c r="H102" t="n">
         <v>87735</v>
@@ -3356,7 +3356,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H103" t="n">
         <v>122131</v>
@@ -3385,7 +3385,7 @@
         <v>7.55795288085938</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51463842391968</v>
+        <v>4.51463890075684</v>
       </c>
       <c r="H104" t="n">
         <v>64852</v>
@@ -3414,7 +3414,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.5285210609436</v>
+        <v>4.52852153778076</v>
       </c>
       <c r="H105" t="n">
         <v>60638</v>
@@ -3501,7 +3501,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G108" t="n">
-        <v>4.41468334197998</v>
+        <v>4.41468381881714</v>
       </c>
       <c r="H108" t="n">
         <v>75432</v>
@@ -3588,7 +3588,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G111" t="n">
-        <v>4.47021436691284</v>
+        <v>4.47021389007568</v>
       </c>
       <c r="H111" t="n">
         <v>58171</v>
@@ -3646,7 +3646,7 @@
         <v>7.49287796020508</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47576761245728</v>
+        <v>4.47576713562012</v>
       </c>
       <c r="H113" t="n">
         <v>86039</v>
@@ -3704,7 +3704,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.19811487197876</v>
+        <v>4.19811391830444</v>
       </c>
       <c r="H115" t="n">
         <v>98580</v>
@@ -3733,7 +3733,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768431663513</v>
+        <v>3.91768455505371</v>
       </c>
       <c r="H116" t="n">
         <v>109038</v>
@@ -3762,7 +3762,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989729881287</v>
+        <v>3.93989706039429</v>
       </c>
       <c r="H117" t="n">
         <v>151204</v>
@@ -3791,7 +3791,7 @@
         <v>6.38196182250977</v>
       </c>
       <c r="G118" t="n">
-        <v>3.81217646598816</v>
+        <v>3.8121771812439</v>
       </c>
       <c r="H118" t="n">
         <v>94805</v>
@@ -3820,7 +3820,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.83161234855652</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H119" t="n">
         <v>396991</v>
@@ -3849,7 +3849,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G120" t="n">
-        <v>4.01486349105835</v>
+        <v>4.01486301422119</v>
       </c>
       <c r="H120" t="n">
         <v>179714</v>
@@ -3878,7 +3878,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G121" t="n">
-        <v>4.05373573303223</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H121" t="n">
         <v>147984</v>
@@ -4023,7 +4023,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="n">
-        <v>3.70944571495056</v>
+        <v>3.7094452381134</v>
       </c>
       <c r="H126" t="n">
         <v>201840</v>
@@ -4052,7 +4052,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H127" t="n">
         <v>204444</v>
@@ -4081,7 +4081,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H128" t="n">
         <v>365836</v>
@@ -4139,7 +4139,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603735923767</v>
+        <v>3.87603759765625</v>
       </c>
       <c r="H130" t="n">
         <v>40805</v>
@@ -4168,7 +4168,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165678977966</v>
+        <v>3.73165702819824</v>
       </c>
       <c r="H131" t="n">
         <v>182299</v>
@@ -4197,7 +4197,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111536979675</v>
+        <v>3.70111584663391</v>
       </c>
       <c r="H132" t="n">
         <v>120419</v>
@@ -4226,7 +4226,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328248023987</v>
+        <v>3.82328295707703</v>
       </c>
       <c r="H133" t="n">
         <v>123098</v>
@@ -4255,7 +4255,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490912437439</v>
       </c>
       <c r="H134" t="n">
         <v>96476</v>
@@ -4284,7 +4284,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.94822692871094</v>
+        <v>3.9482274055481</v>
       </c>
       <c r="H135" t="n">
         <v>150820</v>
@@ -4313,7 +4313,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G136" t="n">
-        <v>4.05373573303223</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H136" t="n">
         <v>104402</v>
@@ -4342,7 +4342,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="n">
-        <v>4.10648822784424</v>
+        <v>4.1064887046814</v>
       </c>
       <c r="H137" t="n">
         <v>161569</v>
@@ -4400,7 +4400,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="n">
-        <v>4.18145561218262</v>
+        <v>4.18145608901978</v>
       </c>
       <c r="H139" t="n">
         <v>148533</v>
@@ -4487,7 +4487,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.29806995391846</v>
+        <v>4.2980694770813</v>
       </c>
       <c r="H142" t="n">
         <v>180595</v>
@@ -4574,7 +4574,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583522796631</v>
+        <v>4.32583475112915</v>
       </c>
       <c r="H145" t="n">
         <v>68143</v>
@@ -4632,7 +4632,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858915328979</v>
+        <v>4.37858867645264</v>
       </c>
       <c r="H147" t="n">
         <v>120474</v>
@@ -4661,7 +4661,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025880813599</v>
       </c>
       <c r="H148" t="n">
         <v>86165</v>
@@ -4690,7 +4690,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H149" t="n">
         <v>169324</v>
@@ -4719,7 +4719,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637617111206</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H150" t="n">
         <v>81896</v>
@@ -4748,7 +4748,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.19811487197876</v>
+        <v>4.19811391830444</v>
       </c>
       <c r="H151" t="n">
         <v>100034</v>
@@ -4777,7 +4777,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="n">
-        <v>4.10926532745361</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H152" t="n">
         <v>260528</v>
@@ -4835,7 +4835,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H154" t="n">
         <v>185636</v>
@@ -4893,7 +4893,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="n">
-        <v>4.21199750900269</v>
+        <v>4.21199703216553</v>
       </c>
       <c r="H156" t="n">
         <v>137973</v>
@@ -4980,7 +4980,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644426345825</v>
+        <v>4.20644378662109</v>
       </c>
       <c r="H159" t="n">
         <v>60390</v>
@@ -5009,7 +5009,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423271179199</v>
+        <v>4.18423175811768</v>
       </c>
       <c r="H160" t="n">
         <v>85871</v>
@@ -5067,7 +5067,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="n">
-        <v>4.16201972961426</v>
+        <v>4.1620192527771</v>
       </c>
       <c r="H162" t="n">
         <v>24012</v>
@@ -5096,7 +5096,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="n">
-        <v>4.04262924194336</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H163" t="n">
         <v>129575</v>
@@ -5125,7 +5125,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="n">
-        <v>4.05095863342285</v>
+        <v>4.05095815658569</v>
       </c>
       <c r="H164" t="n">
         <v>61371</v>
@@ -5154,7 +5154,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H165" t="n">
         <v>82306</v>
@@ -5212,7 +5212,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371255874634</v>
+        <v>4.10371208190918</v>
       </c>
       <c r="H167" t="n">
         <v>23476</v>
@@ -5241,7 +5241,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150005340576</v>
+        <v>4.08150100708008</v>
       </c>
       <c r="H168" t="n">
         <v>81619</v>
@@ -5270,7 +5270,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H169" t="n">
         <v>96105</v>
@@ -5328,7 +5328,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H171" t="n">
         <v>41159</v>
@@ -5386,7 +5386,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.9704384803772</v>
+        <v>3.97043871879578</v>
       </c>
       <c r="H173" t="n">
         <v>185702</v>
@@ -5444,7 +5444,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="n">
-        <v>4.00098037719727</v>
+        <v>4.00098085403442</v>
       </c>
       <c r="H175" t="n">
         <v>47175</v>
@@ -5473,7 +5473,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G176" t="n">
-        <v>4.01486349105835</v>
+        <v>4.01486301422119</v>
       </c>
       <c r="H176" t="n">
         <v>82433</v>
@@ -5502,7 +5502,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152227401733</v>
+        <v>4.03152275085449</v>
       </c>
       <c r="H177" t="n">
         <v>101079</v>
@@ -5531,7 +5531,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156766891479</v>
+        <v>3.93156719207764</v>
       </c>
       <c r="H178" t="n">
         <v>219724</v>
@@ -5560,7 +5560,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="n">
-        <v>3.80384683609009</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H179" t="n">
         <v>313330</v>
@@ -5589,7 +5589,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="n">
-        <v>3.7288806438446</v>
+        <v>3.72888112068176</v>
       </c>
       <c r="H180" t="n">
         <v>212138</v>
@@ -5618,7 +5618,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H181" t="n">
         <v>119833</v>
@@ -5647,7 +5647,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502094268799</v>
+        <v>3.66502118110657</v>
       </c>
       <c r="H182" t="n">
         <v>239810</v>
@@ -5676,7 +5676,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280796051025</v>
+        <v>3.64280819892883</v>
       </c>
       <c r="H183" t="n">
         <v>201842</v>
@@ -5705,7 +5705,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389175415039</v>
+        <v>3.70389223098755</v>
       </c>
       <c r="H184" t="n">
         <v>128389</v>
@@ -5734,7 +5734,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H185" t="n">
         <v>173655</v>
@@ -5763,7 +5763,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.61781883239746</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H186" t="n">
         <v>138681</v>
@@ -5792,7 +5792,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332763671875</v>
+        <v>3.72332787513733</v>
       </c>
       <c r="H187" t="n">
         <v>126621</v>
@@ -5821,7 +5821,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000935554504</v>
+        <v>3.69000959396362</v>
       </c>
       <c r="H188" t="n">
         <v>175447</v>
@@ -5879,7 +5879,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H190" t="n">
         <v>329741</v>
@@ -5908,7 +5908,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276351928711</v>
+        <v>3.74276399612427</v>
       </c>
       <c r="H191" t="n">
         <v>217887</v>
@@ -5937,7 +5937,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H192" t="n">
         <v>103333</v>
@@ -5966,7 +5966,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332763671875</v>
+        <v>3.72332787513733</v>
       </c>
       <c r="H193" t="n">
         <v>167998</v>
@@ -6024,7 +6024,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.61781883239746</v>
+        <v>3.61781930923462</v>
       </c>
       <c r="H195" t="n">
         <v>109567</v>
@@ -6053,7 +6053,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113830566406</v>
+        <v>3.65113806724548</v>
       </c>
       <c r="H196" t="n">
         <v>131242</v>
@@ -6082,7 +6082,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502094268799</v>
+        <v>3.66502118110657</v>
       </c>
       <c r="H197" t="n">
         <v>103315</v>
@@ -6111,7 +6111,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H198" t="n">
         <v>86545</v>
@@ -6140,7 +6140,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H199" t="n">
         <v>78308</v>
@@ -6169,7 +6169,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838342666626</v>
+        <v>3.598384141922</v>
       </c>
       <c r="H200" t="n">
         <v>58597</v>
@@ -6198,7 +6198,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58172416687012</v>
+        <v>3.58172464370728</v>
       </c>
       <c r="H201" t="n">
         <v>105671</v>
@@ -6256,7 +6256,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H203" t="n">
         <v>132879</v>
@@ -6285,7 +6285,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.6317024230957</v>
+        <v>3.63170194625854</v>
       </c>
       <c r="H204" t="n">
         <v>133954</v>
@@ -6314,7 +6314,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="n">
-        <v>3.70666837692261</v>
+        <v>3.70666813850403</v>
       </c>
       <c r="H205" t="n">
         <v>112375</v>
@@ -6372,7 +6372,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046117782593</v>
+        <v>3.92046165466309</v>
       </c>
       <c r="H207" t="n">
         <v>198572</v>
@@ -6401,7 +6401,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156766891479</v>
+        <v>3.93156719207764</v>
       </c>
       <c r="H208" t="n">
         <v>48406</v>
@@ -6430,7 +6430,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488571166992</v>
+        <v>3.96488642692566</v>
       </c>
       <c r="H209" t="n">
         <v>111598</v>
@@ -6459,7 +6459,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.94822692871094</v>
+        <v>3.9482274055481</v>
       </c>
       <c r="H210" t="n">
         <v>182662</v>
@@ -6517,7 +6517,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.94267272949219</v>
+        <v>3.94267344474792</v>
       </c>
       <c r="H212" t="n">
         <v>122111</v>
@@ -6546,7 +6546,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547204971313</v>
+        <v>3.89547276496887</v>
       </c>
       <c r="H213" t="n">
         <v>134927</v>
@@ -6604,7 +6604,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215400695801</v>
+        <v>3.86215448379517</v>
       </c>
       <c r="H215" t="n">
         <v>72762</v>
@@ -6633,7 +6633,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="n">
-        <v>3.80384683609009</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H216" t="n">
         <v>114679</v>
@@ -6662,7 +6662,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438849449158</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H217" t="n">
         <v>51844</v>
@@ -6691,7 +6691,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608132362366</v>
+        <v>3.77608156204224</v>
       </c>
       <c r="H218" t="n">
         <v>66379</v>
@@ -6720,7 +6720,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107045173645</v>
+        <v>3.80107092857361</v>
       </c>
       <c r="H219" t="n">
         <v>60701</v>
@@ -6749,7 +6749,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.7871880531311</v>
+        <v>3.78718829154968</v>
       </c>
       <c r="H220" t="n">
         <v>128863</v>
@@ -6778,7 +6778,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996419906616</v>
+        <v>3.78996467590332</v>
       </c>
       <c r="H221" t="n">
         <v>103648</v>
@@ -6807,7 +6807,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="n">
-        <v>3.75942230224609</v>
+        <v>3.75942301750183</v>
       </c>
       <c r="H222" t="n">
         <v>147024</v>
@@ -6865,7 +6865,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.71222138404846</v>
+        <v>3.71222114562988</v>
       </c>
       <c r="H224" t="n">
         <v>81364</v>
@@ -6894,7 +6894,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.61504292488098</v>
+        <v>3.6150426864624</v>
       </c>
       <c r="H225" t="n">
         <v>166084</v>
@@ -6952,7 +6952,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="n">
-        <v>3.62614893913269</v>
+        <v>3.62614870071411</v>
       </c>
       <c r="H227" t="n">
         <v>55700</v>
@@ -7010,7 +7010,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179225921631</v>
+        <v>3.43179202079773</v>
       </c>
       <c r="H229" t="n">
         <v>391920</v>
@@ -7068,7 +7068,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007649421692</v>
+        <v>3.54007601737976</v>
       </c>
       <c r="H231" t="n">
         <v>177686</v>
@@ -7097,7 +7097,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52896976470947</v>
+        <v>3.52897047996521</v>
       </c>
       <c r="H232" t="n">
         <v>53802</v>
@@ -7126,7 +7126,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400381088257</v>
+        <v>3.45400404930115</v>
       </c>
       <c r="H233" t="n">
         <v>47034</v>
@@ -7184,7 +7184,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.47621631622314</v>
+        <v>3.4762167930603</v>
       </c>
       <c r="H235" t="n">
         <v>66245</v>
@@ -7213,7 +7213,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398182868958</v>
+        <v>3.503981590271</v>
       </c>
       <c r="H236" t="n">
         <v>83410</v>
@@ -7242,7 +7242,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842810630798</v>
+        <v>3.4984290599823</v>
       </c>
       <c r="H237" t="n">
         <v>59122</v>
@@ -7271,7 +7271,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174734115601</v>
+        <v>3.53174757957458</v>
       </c>
       <c r="H238" t="n">
         <v>110615</v>
@@ -7300,7 +7300,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732233047485</v>
+        <v>3.48732304573059</v>
       </c>
       <c r="H239" t="n">
         <v>109337</v>
@@ -7329,7 +7329,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057347297668</v>
+        <v>3.67057371139526</v>
       </c>
       <c r="H240" t="n">
         <v>90169</v>
@@ -7358,7 +7358,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389175415039</v>
+        <v>3.70389223098755</v>
       </c>
       <c r="H241" t="n">
         <v>121643</v>
@@ -7387,7 +7387,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050585746765</v>
+        <v>3.82050609588623</v>
       </c>
       <c r="H242" t="n">
         <v>97760</v>
@@ -7416,7 +7416,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.7871880531311</v>
+        <v>3.78718829154968</v>
       </c>
       <c r="H243" t="n">
         <v>135353</v>
@@ -7445,7 +7445,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="n">
-        <v>3.80384683609009</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H244" t="n">
         <v>97891</v>
@@ -7474,7 +7474,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.83161234855652</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H245" t="n">
         <v>194032</v>
@@ -7503,7 +7503,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608132362366</v>
+        <v>3.77608156204224</v>
       </c>
       <c r="H246" t="n">
         <v>85390</v>
@@ -7532,7 +7532,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.83161234855652</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H247" t="n">
         <v>110497</v>
@@ -7561,7 +7561,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.83161234855652</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H248" t="n">
         <v>128189</v>
@@ -7648,7 +7648,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154544830322</v>
+        <v>3.98154497146606</v>
       </c>
       <c r="H251" t="n">
         <v>198595</v>
@@ -7677,7 +7677,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H252" t="n">
         <v>83758</v>
@@ -7706,7 +7706,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98709774017334</v>
+        <v>3.98709750175476</v>
       </c>
       <c r="H253" t="n">
         <v>124841</v>
@@ -7735,7 +7735,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H254" t="n">
         <v>67846</v>
@@ -7764,7 +7764,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599315643311</v>
       </c>
       <c r="H255" t="n">
         <v>60629</v>
@@ -7793,7 +7793,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H256" t="n">
         <v>75406</v>
@@ -7822,7 +7822,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H257" t="n">
         <v>46248</v>
@@ -7851,7 +7851,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="n">
-        <v>4.04262924194336</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H258" t="n">
         <v>68035</v>
@@ -7880,7 +7880,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="n">
-        <v>4.10648822784424</v>
+        <v>4.1064887046814</v>
       </c>
       <c r="H259" t="n">
         <v>250610</v>
@@ -7938,7 +7938,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="n">
-        <v>4.2147741317749</v>
+        <v>4.21477365493774</v>
       </c>
       <c r="H261" t="n">
         <v>186483</v>
@@ -7967,7 +7967,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="n">
-        <v>4.18145561218262</v>
+        <v>4.18145608901978</v>
       </c>
       <c r="H262" t="n">
         <v>80545</v>
@@ -8112,7 +8112,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H267" t="n">
         <v>54101</v>
@@ -8141,7 +8141,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="n">
-        <v>4.15091371536255</v>
+        <v>4.15091323852539</v>
       </c>
       <c r="H268" t="n">
         <v>41601</v>
@@ -8170,7 +8170,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481904983521</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H269" t="n">
         <v>45733</v>
@@ -8257,7 +8257,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="n">
-        <v>4.10648822784424</v>
+        <v>4.1064887046814</v>
       </c>
       <c r="H272" t="n">
         <v>88527</v>
@@ -8286,7 +8286,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="n">
-        <v>4.07872438430786</v>
+        <v>4.0787239074707</v>
       </c>
       <c r="H273" t="n">
         <v>127436</v>
@@ -8315,7 +8315,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484127044678</v>
+        <v>4.06484079360962</v>
       </c>
       <c r="H274" t="n">
         <v>94442</v>
@@ -8344,7 +8344,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="n">
-        <v>4.03429889678955</v>
+        <v>4.03429937362671</v>
       </c>
       <c r="H275" t="n">
         <v>100684</v>
@@ -8373,7 +8373,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490912437439</v>
       </c>
       <c r="H276" t="n">
         <v>229142</v>
@@ -8402,7 +8402,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377969741821</v>
+        <v>3.95377922058105</v>
       </c>
       <c r="H277" t="n">
         <v>45852</v>
@@ -8431,7 +8431,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438849449158</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H278" t="n">
         <v>128544</v>
@@ -8460,7 +8460,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.8649308681488</v>
+        <v>3.86493039131165</v>
       </c>
       <c r="H279" t="n">
         <v>46654</v>
@@ -8489,7 +8489,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933294296265</v>
+        <v>3.95933318138123</v>
       </c>
       <c r="H280" t="n">
         <v>55134</v>
@@ -8634,7 +8634,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599315643311</v>
       </c>
       <c r="H285" t="n">
         <v>110096</v>
@@ -8663,7 +8663,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H286" t="n">
         <v>167527</v>
@@ -8692,7 +8692,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G287" t="n">
-        <v>4.05373573303223</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H287" t="n">
         <v>78301</v>
@@ -8721,7 +8721,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="n">
-        <v>4.07039403915405</v>
+        <v>4.07039356231689</v>
       </c>
       <c r="H288" t="n">
         <v>67876</v>
@@ -8750,7 +8750,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="n">
-        <v>4.10926532745361</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H289" t="n">
         <v>61110</v>
@@ -8779,7 +8779,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H290" t="n">
         <v>349165</v>
@@ -8837,7 +8837,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H292" t="n">
         <v>61984</v>
@@ -8866,7 +8866,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="n">
-        <v>4.16201972961426</v>
+        <v>4.1620192527771</v>
       </c>
       <c r="H293" t="n">
         <v>49804</v>
@@ -8895,7 +8895,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H294" t="n">
         <v>80824</v>
@@ -8982,7 +8982,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H297" t="n">
         <v>154156</v>
@@ -9040,7 +9040,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="n">
-        <v>4.10926532745361</v>
+        <v>4.10926580429077</v>
       </c>
       <c r="H299" t="n">
         <v>223547</v>
@@ -9069,7 +9069,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.3147292137146</v>
+        <v>4.31472873687744</v>
       </c>
       <c r="H300" t="n">
         <v>617047</v>
@@ -9098,7 +9098,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H301" t="n">
         <v>316194</v>
@@ -9156,7 +9156,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.353600025177</v>
+        <v>4.35360050201416</v>
       </c>
       <c r="H303" t="n">
         <v>161681</v>
@@ -9185,7 +9185,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.3147292137146</v>
+        <v>4.31472873687744</v>
       </c>
       <c r="H304" t="n">
         <v>116065</v>
@@ -9214,7 +9214,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="n">
-        <v>4.33138799667358</v>
+        <v>4.33138847351074</v>
       </c>
       <c r="H305" t="n">
         <v>76534</v>
@@ -9243,7 +9243,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025880813599</v>
       </c>
       <c r="H306" t="n">
         <v>134817</v>
@@ -9272,7 +9272,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637617111206</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H307" t="n">
         <v>145037</v>
@@ -9388,7 +9388,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H311" t="n">
         <v>289755</v>
@@ -9533,7 +9533,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H316" t="n">
         <v>367674</v>
@@ -9620,7 +9620,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="n">
-        <v>4.63402986526489</v>
+        <v>4.63402938842773</v>
       </c>
       <c r="H319" t="n">
         <v>498945</v>
@@ -9649,7 +9649,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H320" t="n">
         <v>231935</v>
@@ -9678,7 +9678,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H321" t="n">
         <v>141204</v>
@@ -9736,7 +9736,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="n">
-        <v>4.53962755203247</v>
+        <v>4.53962802886963</v>
       </c>
       <c r="H323" t="n">
         <v>188080</v>
@@ -9765,7 +9765,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685140609741</v>
+        <v>4.53685188293457</v>
       </c>
       <c r="H324" t="n">
         <v>98610</v>
@@ -9794,7 +9794,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H325" t="n">
         <v>265003</v>
@@ -9881,7 +9881,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132085800171</v>
+        <v>4.48132038116455</v>
       </c>
       <c r="H328" t="n">
         <v>165632</v>
@@ -9939,7 +9939,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G330" t="n">
-        <v>4.47021436691284</v>
+        <v>4.47021389007568</v>
       </c>
       <c r="H330" t="n">
         <v>148997</v>
@@ -9997,7 +9997,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691902160645</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H332" t="n">
         <v>206018</v>
@@ -10026,7 +10026,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691902160645</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H333" t="n">
         <v>196119</v>
@@ -10171,7 +10171,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075578689575</v>
+        <v>4.50075626373291</v>
       </c>
       <c r="H338" t="n">
         <v>185305</v>
@@ -10200,7 +10200,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="n">
-        <v>4.57849884033203</v>
+        <v>4.57849931716919</v>
       </c>
       <c r="H339" t="n">
         <v>327114</v>
@@ -10229,7 +10229,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461620330811</v>
+        <v>4.56461668014526</v>
       </c>
       <c r="H340" t="n">
         <v>221386</v>
@@ -10258,7 +10258,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793519973755</v>
+        <v>4.59793472290039</v>
       </c>
       <c r="H341" t="n">
         <v>312555</v>
@@ -10287,7 +10287,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127641677856</v>
+        <v>4.58127593994141</v>
       </c>
       <c r="H342" t="n">
         <v>62152</v>
@@ -10316,7 +10316,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="n">
-        <v>4.61459350585938</v>
+        <v>4.61459445953369</v>
       </c>
       <c r="H343" t="n">
         <v>203327</v>
@@ -10345,7 +10345,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="n">
-        <v>4.60348749160767</v>
+        <v>4.60348796844482</v>
       </c>
       <c r="H344" t="n">
         <v>103263</v>
@@ -10374,7 +10374,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346527099609</v>
+        <v>4.65346622467041</v>
       </c>
       <c r="H345" t="n">
         <v>177286</v>
@@ -10403,7 +10403,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="n">
-        <v>4.75342082977295</v>
+        <v>4.75342035293579</v>
       </c>
       <c r="H346" t="n">
         <v>342741</v>
@@ -10432,7 +10432,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="n">
-        <v>4.77563285827637</v>
+        <v>4.77563333511353</v>
       </c>
       <c r="H347" t="n">
         <v>352359</v>
@@ -10461,7 +10461,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895185470581</v>
+        <v>4.80895090103149</v>
       </c>
       <c r="H348" t="n">
         <v>235964</v>
@@ -10490,7 +10490,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H349" t="n">
         <v>172083</v>
@@ -10519,7 +10519,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.8783655166626</v>
+        <v>4.87836456298828</v>
       </c>
       <c r="H350" t="n">
         <v>140823</v>
@@ -10548,7 +10548,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H351" t="n">
         <v>122329</v>
@@ -10577,7 +10577,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010278701782</v>
+        <v>4.72010231018066</v>
       </c>
       <c r="H352" t="n">
         <v>291161</v>
@@ -10664,7 +10664,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423603057861</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H355" t="n">
         <v>294138</v>
@@ -10693,7 +10693,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865699768066</v>
       </c>
       <c r="H356" t="n">
         <v>265806</v>
@@ -10722,7 +10722,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H357" t="n">
         <v>212034</v>
@@ -10751,7 +10751,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H358" t="n">
         <v>157901</v>
@@ -10780,7 +10780,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H359" t="n">
         <v>148993</v>
@@ -10809,7 +10809,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865699768066</v>
       </c>
       <c r="H360" t="n">
         <v>158526</v>
@@ -10838,7 +10838,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="n">
-        <v>4.72718334197998</v>
+        <v>4.72718381881714</v>
       </c>
       <c r="H361" t="n">
         <v>132673</v>
@@ -10896,7 +10896,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H363" t="n">
         <v>258831</v>
@@ -11012,7 +11012,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="n">
-        <v>4.7214469909668</v>
+        <v>4.72144651412964</v>
       </c>
       <c r="H367" t="n">
         <v>88872</v>
@@ -11041,7 +11041,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H368" t="n">
         <v>114636</v>
@@ -11128,7 +11128,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="n">
-        <v>4.76734161376953</v>
+        <v>4.76734256744385</v>
       </c>
       <c r="H371" t="n">
         <v>59047</v>
@@ -11186,7 +11186,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H373" t="n">
         <v>190474</v>
@@ -11244,7 +11244,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965726852417</v>
+        <v>4.62965774536133</v>
       </c>
       <c r="H375" t="n">
         <v>145512</v>
@@ -11273,7 +11273,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965726852417</v>
+        <v>4.62965774536133</v>
       </c>
       <c r="H376" t="n">
         <v>155173</v>
@@ -11331,7 +11331,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="n">
-        <v>4.58376216888428</v>
+        <v>4.58376169204712</v>
       </c>
       <c r="H378" t="n">
         <v>95959</v>
@@ -11447,7 +11447,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="n">
-        <v>4.49770927429199</v>
+        <v>4.49770879745483</v>
       </c>
       <c r="H382" t="n">
         <v>132223</v>
@@ -11505,7 +11505,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42313003540039</v>
+        <v>4.42312908172607</v>
       </c>
       <c r="H384" t="n">
         <v>90869</v>
@@ -11592,7 +11592,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507802963257</v>
+        <v>4.55507755279541</v>
       </c>
       <c r="H387" t="n">
         <v>112131</v>
@@ -11621,7 +11621,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476148605347</v>
+        <v>4.47476100921631</v>
       </c>
       <c r="H388" t="n">
         <v>139029</v>
@@ -11679,7 +11679,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="n">
-        <v>4.64686727523804</v>
+        <v>4.64686822891235</v>
       </c>
       <c r="H390" t="n">
         <v>163263</v>
@@ -11737,7 +11737,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66121006011963</v>
+        <v>4.66120958328247</v>
       </c>
       <c r="H392" t="n">
         <v>102329</v>
@@ -11795,7 +11795,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="n">
-        <v>4.7644739151001</v>
+        <v>4.76447343826294</v>
       </c>
       <c r="H394" t="n">
         <v>83113</v>
@@ -11824,7 +11824,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H395" t="n">
         <v>98585</v>
@@ -11882,7 +11882,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="n">
-        <v>4.76160430908203</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H397" t="n">
         <v>136912</v>
@@ -11940,7 +11940,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="n">
-        <v>4.77021026611328</v>
+        <v>4.77021074295044</v>
       </c>
       <c r="H399" t="n">
         <v>76241</v>
@@ -12085,7 +12085,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="n">
-        <v>4.72718334197998</v>
+        <v>4.72718381881714</v>
       </c>
       <c r="H404" t="n">
         <v>157625</v>
@@ -12288,7 +12288,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.87634325027466</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H411" t="n">
         <v>129788</v>
@@ -12433,7 +12433,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H416" t="n">
         <v>400107</v>
@@ -12462,7 +12462,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="n">
-        <v>4.94518518447876</v>
+        <v>4.94518566131592</v>
       </c>
       <c r="H417" t="n">
         <v>199295</v>
@@ -12491,7 +12491,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="n">
-        <v>4.93084335327148</v>
+        <v>4.93084287643433</v>
       </c>
       <c r="H418" t="n">
         <v>170401</v>
@@ -12520,7 +12520,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="n">
-        <v>4.89642143249512</v>
+        <v>4.89642190933228</v>
       </c>
       <c r="H419" t="n">
         <v>51293</v>
@@ -12578,7 +12578,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H421" t="n">
         <v>72335</v>
@@ -12636,7 +12636,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H423" t="n">
         <v>34375</v>
@@ -12665,7 +12665,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86199951171875</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H424" t="n">
         <v>42823</v>
@@ -12694,7 +12694,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052680969238</v>
+        <v>4.85052633285522</v>
       </c>
       <c r="H425" t="n">
         <v>172662</v>
@@ -12810,7 +12810,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="n">
-        <v>4.86199951171875</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H429" t="n">
         <v>34336</v>
@@ -12839,7 +12839,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.87634325027466</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H430" t="n">
         <v>81300</v>
@@ -12926,7 +12926,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="n">
-        <v>4.8390531539917</v>
+        <v>4.83905363082886</v>
       </c>
       <c r="H433" t="n">
         <v>35013</v>
@@ -13042,7 +13042,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H437" t="n">
         <v>135001</v>
@@ -13129,7 +13129,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="n">
-        <v>5.05418634414673</v>
+        <v>5.05418586730957</v>
       </c>
       <c r="H440" t="n">
         <v>88520</v>
@@ -13187,7 +13187,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99108028411865</v>
+        <v>4.99107980728149</v>
       </c>
       <c r="H442" t="n">
         <v>93886</v>
@@ -13216,7 +13216,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H443" t="n">
         <v>69536</v>
@@ -13245,7 +13245,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255393981934</v>
+        <v>5.00255298614502</v>
       </c>
       <c r="H444" t="n">
         <v>82992</v>
@@ -13274,7 +13274,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H445" t="n">
         <v>104775</v>
@@ -13303,7 +13303,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="n">
-        <v>5.02550172805786</v>
+        <v>5.0255012512207</v>
       </c>
       <c r="H446" t="n">
         <v>100760</v>
@@ -13361,7 +13361,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="n">
-        <v>5.06279039382935</v>
+        <v>5.06279134750366</v>
       </c>
       <c r="H448" t="n">
         <v>73261</v>
@@ -13390,7 +13390,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="n">
-        <v>5.06565952301025</v>
+        <v>5.0656590461731</v>
       </c>
       <c r="H449" t="n">
         <v>114555</v>
@@ -13419,7 +13419,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="n">
-        <v>5.06279039382935</v>
+        <v>5.06279134750366</v>
       </c>
       <c r="H450" t="n">
         <v>80452</v>
@@ -13448,7 +13448,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713317871094</v>
+        <v>5.07713222503662</v>
       </c>
       <c r="H451" t="n">
         <v>127366</v>
@@ -13506,7 +13506,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="n">
-        <v>4.96813297271729</v>
+        <v>4.96813249588013</v>
       </c>
       <c r="H453" t="n">
         <v>121584</v>
@@ -13535,7 +13535,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="n">
-        <v>4.9824743270874</v>
+        <v>4.98247528076172</v>
       </c>
       <c r="H454" t="n">
         <v>322636</v>
@@ -13593,7 +13593,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H456" t="n">
         <v>168873</v>
@@ -13622,7 +13622,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="n">
-        <v>5.16318655014038</v>
+        <v>5.16318607330322</v>
       </c>
       <c r="H457" t="n">
         <v>184063</v>
@@ -13651,7 +13651,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923896789551</v>
+        <v>5.24923992156982</v>
       </c>
       <c r="H458" t="n">
         <v>199889</v>
@@ -13738,7 +13738,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871494293213</v>
       </c>
       <c r="H461" t="n">
         <v>90087</v>
@@ -13854,7 +13854,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="n">
-        <v>5.39839744567871</v>
+        <v>5.39839792251587</v>
       </c>
       <c r="H465" t="n">
         <v>318851</v>
@@ -13883,7 +13883,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266157150269</v>
       </c>
       <c r="H466" t="n">
         <v>156702</v>
@@ -13941,7 +13941,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118839263916</v>
+        <v>5.38118743896484</v>
       </c>
       <c r="H468" t="n">
         <v>235300</v>
@@ -13999,7 +13999,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384670257568</v>
+        <v>5.69384765625</v>
       </c>
       <c r="H470" t="n">
         <v>1020120</v>
@@ -14028,7 +14028,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818901062012</v>
       </c>
       <c r="H471" t="n">
         <v>456989</v>
@@ -14057,7 +14057,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="n">
-        <v>5.98355960845947</v>
+        <v>5.98356056213379</v>
       </c>
       <c r="H472" t="n">
         <v>839604</v>
@@ -14115,7 +14115,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="n">
-        <v>5.89750671386719</v>
+        <v>5.89750576019287</v>
       </c>
       <c r="H474" t="n">
         <v>301027</v>
@@ -14144,7 +14144,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90897989273071</v>
+        <v>5.90898084640503</v>
       </c>
       <c r="H475" t="n">
         <v>361115</v>
@@ -14173,7 +14173,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766450881958</v>
+        <v>5.93766498565674</v>
       </c>
       <c r="H476" t="n">
         <v>309094</v>
@@ -14202,7 +14202,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292652130127</v>
+        <v>5.82292699813843</v>
       </c>
       <c r="H477" t="n">
         <v>320356</v>
@@ -14231,7 +14231,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90897989273071</v>
+        <v>5.90898084640503</v>
       </c>
       <c r="H478" t="n">
         <v>447808</v>
@@ -14260,7 +14260,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555824279785</v>
+        <v>5.76555776596069</v>
       </c>
       <c r="H479" t="n">
         <v>231042</v>
@@ -14289,7 +14289,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="n">
-        <v>5.682373046875</v>
+        <v>5.68237352371216</v>
       </c>
       <c r="H480" t="n">
         <v>236079</v>
@@ -14318,7 +14318,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="n">
-        <v>5.79424285888672</v>
+        <v>5.79424238204956</v>
       </c>
       <c r="H481" t="n">
         <v>340167</v>
@@ -14434,7 +14434,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061134338379</v>
+        <v>5.96061182022095</v>
       </c>
       <c r="H485" t="n">
         <v>214159</v>
@@ -14463,7 +14463,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287588119507</v>
+        <v>6.17287635803223</v>
       </c>
       <c r="H486" t="n">
         <v>406962</v>
@@ -14492,7 +14492,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="n">
-        <v>6.16140270233154</v>
+        <v>6.16140222549438</v>
       </c>
       <c r="H487" t="n">
         <v>223944</v>
@@ -14608,7 +14608,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="n">
-        <v>6.19008779525757</v>
+        <v>6.19008684158325</v>
       </c>
       <c r="H491" t="n">
         <v>234121</v>
@@ -14637,7 +14637,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="n">
-        <v>6.17861223220825</v>
+        <v>6.17861270904541</v>
       </c>
       <c r="H492" t="n">
         <v>176102</v>
@@ -14666,7 +14666,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371835708618</v>
+        <v>6.02371740341187</v>
       </c>
       <c r="H493" t="n">
         <v>167344</v>
@@ -14724,7 +14724,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="n">
-        <v>6.16140270233154</v>
+        <v>6.16140222549438</v>
       </c>
       <c r="H495" t="n">
         <v>110811</v>
@@ -14753,7 +14753,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="n">
-        <v>6.13271856307983</v>
+        <v>6.13271760940552</v>
       </c>
       <c r="H496" t="n">
         <v>108347</v>
@@ -14811,7 +14811,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36792993545532</v>
+        <v>6.36792945861816</v>
       </c>
       <c r="H498" t="n">
         <v>358977</v>
@@ -14927,7 +14927,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.42529821395874</v>
+        <v>6.42529916763306</v>
       </c>
       <c r="H502" t="n">
         <v>210048</v>
@@ -14956,7 +14956,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319242477417</v>
+        <v>6.25319147109985</v>
       </c>
       <c r="H503" t="n">
         <v>365311</v>
@@ -14985,7 +14985,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734796524048</v>
+        <v>5.85734844207764</v>
       </c>
       <c r="H504" t="n">
         <v>968569</v>
@@ -15043,7 +15043,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476736068726</v>
+        <v>5.56476640701294</v>
       </c>
       <c r="H506" t="n">
         <v>358726</v>
@@ -15130,7 +15130,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="n">
-        <v>5.53608179092407</v>
+        <v>5.53608322143555</v>
       </c>
       <c r="H509" t="n">
         <v>190384</v>
@@ -15159,7 +15159,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="n">
-        <v>5.6135311126709</v>
+        <v>5.61353063583374</v>
       </c>
       <c r="H510" t="n">
         <v>217678</v>
@@ -15188,7 +15188,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034687042236</v>
+        <v>5.53034639358521</v>
       </c>
       <c r="H511" t="n">
         <v>118130</v>
@@ -15246,7 +15246,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476736068726</v>
+        <v>5.56476640701294</v>
       </c>
       <c r="H513" t="n">
         <v>146003</v>
@@ -15275,7 +15275,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.6508207321167</v>
+        <v>5.65082025527954</v>
       </c>
       <c r="H514" t="n">
         <v>122075</v>
@@ -15304,7 +15304,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655755996704</v>
+        <v>5.6565580368042</v>
       </c>
       <c r="H515" t="n">
         <v>86233</v>
@@ -15333,7 +15333,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818901062012</v>
       </c>
       <c r="H516" t="n">
         <v>147363</v>
@@ -15362,7 +15362,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="n">
-        <v>5.74834823608398</v>
+        <v>5.74834728240967</v>
       </c>
       <c r="H517" t="n">
         <v>220803</v>
@@ -15391,7 +15391,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="n">
-        <v>5.7196626663208</v>
+        <v>5.71966314315796</v>
       </c>
       <c r="H518" t="n">
         <v>305356</v>
@@ -15478,7 +15478,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345149993896</v>
+        <v>5.59345197677612</v>
       </c>
       <c r="H521" t="n">
         <v>134956</v>
@@ -15623,7 +15623,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="n">
-        <v>5.53608179092407</v>
+        <v>5.53608322143555</v>
       </c>
       <c r="H526" t="n">
         <v>224626</v>
@@ -15710,7 +15710,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871494293213</v>
       </c>
       <c r="H529" t="n">
         <v>108597</v>
@@ -15768,7 +15768,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.46150350570679</v>
+        <v>5.46150398254395</v>
       </c>
       <c r="H531" t="n">
         <v>150985</v>
@@ -15826,7 +15826,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266157150269</v>
       </c>
       <c r="H533" t="n">
         <v>107752</v>
@@ -15884,7 +15884,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171241760254</v>
+        <v>5.15171194076538</v>
       </c>
       <c r="H535" t="n">
         <v>131851</v>
@@ -16000,7 +16000,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913276672363</v>
+        <v>4.85913181304932</v>
       </c>
       <c r="H539" t="n">
         <v>191289</v>
@@ -16029,7 +16029,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="n">
-        <v>4.7214469909668</v>
+        <v>4.72144651412964</v>
       </c>
       <c r="H540" t="n">
         <v>263307</v>
@@ -16058,7 +16058,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423603057861</v>
+        <v>4.70423650741577</v>
       </c>
       <c r="H541" t="n">
         <v>193365</v>
@@ -16087,7 +16087,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="n">
-        <v>4.49770927429199</v>
+        <v>4.49770879745483</v>
       </c>
       <c r="H542" t="n">
         <v>312675</v>
@@ -16116,7 +16116,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439382553101</v>
+        <v>4.74439430236816</v>
       </c>
       <c r="H543" t="n">
         <v>179153</v>
@@ -16174,7 +16174,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="n">
-        <v>4.82471084594727</v>
+        <v>4.82471132278442</v>
       </c>
       <c r="H545" t="n">
         <v>123266</v>
@@ -16203,7 +16203,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849872589111</v>
+        <v>4.69849967956543</v>
       </c>
       <c r="H546" t="n">
         <v>190634</v>
@@ -16261,7 +16261,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="n">
-        <v>4.68128871917725</v>
+        <v>4.6812891960144</v>
       </c>
       <c r="H548" t="n">
         <v>251480</v>
@@ -16319,7 +16319,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571016311646</v>
       </c>
       <c r="H550" t="n">
         <v>314139</v>
@@ -16377,7 +16377,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="n">
-        <v>4.62564134597778</v>
+        <v>4.62564086914062</v>
       </c>
       <c r="H552" t="n">
         <v>201959</v>
@@ -16406,7 +16406,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245710372925</v>
+        <v>4.54245662689209</v>
       </c>
       <c r="H553" t="n">
         <v>199605</v>
@@ -16464,7 +16464,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="n">
-        <v>4.31986618041992</v>
+        <v>4.31986570358276</v>
       </c>
       <c r="H555" t="n">
         <v>182195</v>
@@ -16522,7 +16522,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="n">
-        <v>4.37149810791016</v>
+        <v>4.371497631073</v>
       </c>
       <c r="H557" t="n">
         <v>224606</v>
@@ -16551,7 +16551,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057697296143</v>
+        <v>4.50057744979858</v>
       </c>
       <c r="H558" t="n">
         <v>119113</v>
@@ -16580,7 +16580,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401926040649</v>
+        <v>4.50401973724365</v>
       </c>
       <c r="H559" t="n">
         <v>186947</v>
@@ -16609,7 +16609,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="n">
-        <v>4.39444541931152</v>
+        <v>4.39444494247437</v>
       </c>
       <c r="H560" t="n">
         <v>218932</v>
@@ -16667,7 +16667,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="n">
-        <v>4.35371351242065</v>
+        <v>4.3537130355835</v>
       </c>
       <c r="H562" t="n">
         <v>116896</v>
@@ -16725,7 +16725,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430683135986</v>
+        <v>4.21430730819702</v>
       </c>
       <c r="H564" t="n">
         <v>433130</v>
@@ -16754,7 +16754,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="n">
-        <v>4.14775943756104</v>
+        <v>4.14775991439819</v>
       </c>
       <c r="H565" t="n">
         <v>280816</v>
@@ -16783,7 +16783,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732391357422</v>
+        <v>4.32732439041138</v>
       </c>
       <c r="H566" t="n">
         <v>299973</v>
@@ -16812,7 +16812,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.30781841278076</v>
+        <v>4.3078179359436</v>
       </c>
       <c r="H567" t="n">
         <v>181767</v>
@@ -16870,7 +16870,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="n">
-        <v>4.14259624481201</v>
+        <v>4.14259672164917</v>
       </c>
       <c r="H569" t="n">
         <v>904299</v>
@@ -16928,7 +16928,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.41232681274414</v>
+        <v>4.4123272895813</v>
       </c>
       <c r="H571" t="n">
         <v>1211216</v>
@@ -16957,7 +16957,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>4.49069976806641</v>
+        <v>4.49069929122925</v>
       </c>
       <c r="H572" t="n">
         <v>681826</v>
@@ -16986,7 +16986,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="n">
-        <v>4.9232931137085</v>
+        <v>4.92329263687134</v>
       </c>
       <c r="H573" t="n">
         <v>1058195</v>
@@ -17015,7 +17015,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262052536011</v>
+        <v>4.68262004852295</v>
       </c>
       <c r="H574" t="n">
         <v>630734</v>
@@ -17044,7 +17044,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="n">
-        <v>4.78259181976318</v>
+        <v>4.78259229660034</v>
       </c>
       <c r="H575" t="n">
         <v>785969</v>
@@ -17073,7 +17073,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="n">
-        <v>4.96278810501099</v>
+        <v>4.96278762817383</v>
       </c>
       <c r="H576" t="n">
         <v>567327</v>
@@ -17131,7 +17131,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="n">
-        <v>5.09669971466064</v>
+        <v>5.0967001914978</v>
       </c>
       <c r="H578" t="n">
         <v>512001</v>
@@ -17160,7 +17160,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="n">
-        <v>4.99549436569214</v>
+        <v>4.9954948425293</v>
       </c>
       <c r="H579" t="n">
         <v>881747</v>
@@ -17189,7 +17189,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628034591675</v>
+        <v>4.83628082275391</v>
       </c>
       <c r="H580" t="n">
         <v>645972</v>
@@ -17218,7 +17218,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493379592896</v>
+        <v>4.79493427276611</v>
       </c>
       <c r="H581" t="n">
         <v>391338</v>
@@ -17247,7 +17247,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="n">
-        <v>4.87454128265381</v>
+        <v>4.87454080581665</v>
       </c>
       <c r="H582" t="n">
         <v>274280</v>
@@ -17305,7 +17305,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H584" t="n">
         <v>346291</v>
@@ -17334,7 +17334,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.85479402542114</v>
+        <v>4.85479307174683</v>
       </c>
       <c r="H585" t="n">
         <v>306793</v>
@@ -17392,7 +17392,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>4.83936643600464</v>
+        <v>4.83936595916748</v>
       </c>
       <c r="H587" t="n">
         <v>261734</v>
@@ -17421,7 +17421,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84923934936523</v>
+        <v>4.84924030303955</v>
       </c>
       <c r="H588" t="n">
         <v>752626</v>
@@ -17450,7 +17450,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813142776489</v>
+        <v>4.83813190460205</v>
       </c>
       <c r="H589" t="n">
         <v>513903</v>
@@ -17566,7 +17566,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="n">
-        <v>4.75235414505005</v>
+        <v>4.75235366821289</v>
       </c>
       <c r="H593" t="n">
         <v>307986</v>
@@ -17653,7 +17653,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="n">
-        <v>4.86281585693359</v>
+        <v>4.86281633377075</v>
       </c>
       <c r="H596" t="n">
         <v>196693</v>
@@ -17682,7 +17682,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430313110352</v>
+        <v>4.84430265426636</v>
       </c>
       <c r="H597" t="n">
         <v>183693</v>
@@ -17740,7 +17740,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132905960083</v>
+        <v>4.88132953643799</v>
       </c>
       <c r="H599" t="n">
         <v>300176</v>
@@ -17769,7 +17769,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813142776489</v>
+        <v>4.83813190460205</v>
       </c>
       <c r="H600" t="n">
         <v>417093</v>
@@ -17798,7 +17798,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>4.89120292663574</v>
+        <v>4.8912034034729</v>
       </c>
       <c r="H601" t="n">
         <v>368002</v>
@@ -17827,7 +17827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029081344604</v>
+        <v>5.0602912902832</v>
       </c>
       <c r="H602" t="n">
         <v>586567</v>
@@ -17914,7 +17914,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.80357360839844</v>
+        <v>4.8035740852356</v>
       </c>
       <c r="H605" t="n">
         <v>567119</v>
@@ -17943,7 +17943,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H606" t="n">
         <v>413652</v>
@@ -18001,7 +18001,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>4.66472434997559</v>
+        <v>4.66472482681274</v>
       </c>
       <c r="H608" t="n">
         <v>204562</v>
@@ -18146,7 +18146,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.39072751998901</v>
+        <v>4.39072847366333</v>
       </c>
       <c r="H613" t="n">
         <v>283150</v>
@@ -18175,7 +18175,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>4.17474031448364</v>
+        <v>4.17473983764648</v>
       </c>
       <c r="H614" t="n">
         <v>685007</v>
@@ -18204,7 +18204,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="n">
-        <v>4.41294384002686</v>
+        <v>4.41294431686401</v>
       </c>
       <c r="H615" t="n">
         <v>451434</v>
@@ -18262,7 +18262,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="n">
-        <v>4.46786689758301</v>
+        <v>4.46786737442017</v>
       </c>
       <c r="H617" t="n">
         <v>480697</v>
@@ -18349,7 +18349,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="n">
-        <v>4.62522888183594</v>
+        <v>4.6252293586731</v>
       </c>
       <c r="H620" t="n">
         <v>324641</v>
@@ -18378,7 +18378,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.5190863609314</v>
+        <v>4.51908683776855</v>
       </c>
       <c r="H621" t="n">
         <v>353015</v>
@@ -18436,7 +18436,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="n">
-        <v>4.70257186889648</v>
+        <v>4.70257139205933</v>
       </c>
       <c r="H623" t="n">
         <v>331589</v>
@@ -18465,7 +18465,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="n">
-        <v>4.81534242630005</v>
+        <v>4.81534337997437</v>
       </c>
       <c r="H624" t="n">
         <v>341465</v>
@@ -18494,7 +18494,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716594696045</v>
+        <v>4.71716499328613</v>
       </c>
       <c r="H625" t="n">
         <v>188411</v>
@@ -18552,7 +18552,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="n">
-        <v>4.85448122024536</v>
+        <v>4.8544807434082</v>
       </c>
       <c r="H627" t="n">
         <v>274204</v>
@@ -18581,7 +18581,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>4.62495851516724</v>
+        <v>4.62495803833008</v>
       </c>
       <c r="H628" t="n">
         <v>345226</v>
@@ -18610,7 +18610,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="n">
-        <v>4.62628507614136</v>
+        <v>4.6262845993042</v>
       </c>
       <c r="H629" t="n">
         <v>314894</v>
@@ -18668,7 +18668,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>4.579185962677</v>
+        <v>4.57918643951416</v>
       </c>
       <c r="H631" t="n">
         <v>301522</v>
@@ -18697,7 +18697,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.68996715545654</v>
+        <v>4.68996810913086</v>
       </c>
       <c r="H632" t="n">
         <v>571701</v>
@@ -18726,7 +18726,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="n">
-        <v>4.62164068222046</v>
+        <v>4.62164115905762</v>
       </c>
       <c r="H633" t="n">
         <v>306266</v>
@@ -18813,7 +18813,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H636" t="n">
         <v>261556</v>
@@ -18842,7 +18842,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.56525611877441</v>
+        <v>4.5652551651001</v>
       </c>
       <c r="H637" t="n">
         <v>293870</v>
@@ -18871,7 +18871,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="n">
-        <v>4.67471027374268</v>
+        <v>4.67471075057983</v>
       </c>
       <c r="H638" t="n">
         <v>310832</v>
@@ -18900,7 +18900,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.61832427978516</v>
+        <v>4.61832475662231</v>
       </c>
       <c r="H639" t="n">
         <v>277774</v>
@@ -18958,7 +18958,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60173988342285</v>
+        <v>4.60174036026001</v>
       </c>
       <c r="H641" t="n">
         <v>160144</v>
@@ -18987,7 +18987,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.74303674697876</v>
+        <v>4.7430362701416</v>
       </c>
       <c r="H642" t="n">
         <v>298183</v>
@@ -19074,7 +19074,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>4.65679931640625</v>
+        <v>4.65679979324341</v>
       </c>
       <c r="H645" t="n">
         <v>247525</v>
@@ -19161,7 +19161,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711563110352</v>
+        <v>4.72711515426636</v>
       </c>
       <c r="H648" t="n">
         <v>124423</v>
@@ -19190,7 +19190,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094770431519</v>
+        <v>4.76094722747803</v>
       </c>
       <c r="H649" t="n">
         <v>201117</v>
@@ -19306,7 +19306,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="n">
-        <v>4.80406618118286</v>
+        <v>4.8040657043457</v>
       </c>
       <c r="H653" t="n">
         <v>82622</v>
@@ -19364,7 +19364,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.68731451034546</v>
+        <v>4.6873140335083</v>
       </c>
       <c r="H655" t="n">
         <v>115106</v>
@@ -19509,7 +19509,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="n">
-        <v>4.76492738723755</v>
+        <v>4.76492786407471</v>
       </c>
       <c r="H660" t="n">
         <v>90031</v>
@@ -19567,7 +19567,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.66343307495117</v>
+        <v>4.66343355178833</v>
       </c>
       <c r="H662" t="n">
         <v>216850</v>
@@ -19625,7 +19625,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.61832427978516</v>
+        <v>4.61832475662231</v>
       </c>
       <c r="H664" t="n">
         <v>65498</v>
@@ -19683,7 +19683,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="n">
-        <v>4.58316659927368</v>
+        <v>4.58316564559937</v>
       </c>
       <c r="H666" t="n">
         <v>106623</v>
@@ -19712,7 +19712,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="n">
-        <v>4.50621652603149</v>
+        <v>4.50621604919434</v>
       </c>
       <c r="H667" t="n">
         <v>158816</v>
@@ -19741,7 +19741,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="n">
-        <v>4.41997957229614</v>
+        <v>4.41997909545898</v>
       </c>
       <c r="H668" t="n">
         <v>131656</v>
@@ -19770,7 +19770,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="n">
-        <v>4.38283061981201</v>
+        <v>4.38283109664917</v>
       </c>
       <c r="H669" t="n">
         <v>155550</v>
@@ -19799,7 +19799,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30588102340698</v>
+        <v>4.30588150024414</v>
       </c>
       <c r="H670" t="n">
         <v>224367</v>
@@ -19857,7 +19857,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.36027669906616</v>
+        <v>4.36027717590332</v>
       </c>
       <c r="H672" t="n">
         <v>84392</v>
@@ -19886,7 +19886,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44386053085327</v>
+        <v>4.44386005401611</v>
       </c>
       <c r="H673" t="n">
         <v>124244</v>
@@ -20031,7 +20031,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145421981812</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H678" t="n">
         <v>67624</v>
@@ -20060,7 +20060,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41135549545288</v>
+        <v>4.41135597229004</v>
       </c>
       <c r="H679" t="n">
         <v>86398</v>
@@ -20089,7 +20089,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="n">
-        <v>4.39211750030518</v>
+        <v>4.39211797714233</v>
       </c>
       <c r="H680" t="n">
         <v>166661</v>
@@ -20147,7 +20147,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="n">
-        <v>4.35695934295654</v>
+        <v>4.3569598197937</v>
       </c>
       <c r="H682" t="n">
         <v>65373</v>
@@ -20176,7 +20176,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="n">
-        <v>4.33241558074951</v>
+        <v>4.33241605758667</v>
       </c>
       <c r="H683" t="n">
         <v>70783</v>
@@ -20205,7 +20205,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>4.36160278320312</v>
+        <v>4.36160326004028</v>
       </c>
       <c r="H684" t="n">
         <v>132078</v>
@@ -20263,7 +20263,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="n">
-        <v>4.37089061737061</v>
+        <v>4.37089109420776</v>
       </c>
       <c r="H686" t="n">
         <v>63252</v>
@@ -20379,7 +20379,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="n">
-        <v>4.32710790634155</v>
+        <v>4.32710886001587</v>
       </c>
       <c r="H690" t="n">
         <v>84784</v>
@@ -20408,7 +20408,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="n">
-        <v>4.31981182098389</v>
+        <v>4.31981134414673</v>
       </c>
       <c r="H691" t="n">
         <v>143038</v>
@@ -20466,7 +20466,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="n">
-        <v>4.50090980529785</v>
+        <v>4.50090932846069</v>
       </c>
       <c r="H693" t="n">
         <v>229013</v>
@@ -20495,7 +20495,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="n">
-        <v>4.49029541015625</v>
+        <v>4.49029588699341</v>
       </c>
       <c r="H694" t="n">
         <v>128251</v>
@@ -20524,7 +20524,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739452362061</v>
+        <v>4.53739500045776</v>
       </c>
       <c r="H695" t="n">
         <v>120232</v>
@@ -20553,7 +20553,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H696" t="n">
         <v>221443</v>
@@ -20582,7 +20582,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H697" t="n">
         <v>91471</v>
@@ -20669,7 +20669,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="n">
-        <v>4.4703950881958</v>
+        <v>4.47039413452148</v>
       </c>
       <c r="H700" t="n">
         <v>88666</v>
@@ -20698,7 +20698,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012765884399</v>
+        <v>4.39012813568115</v>
       </c>
       <c r="H701" t="n">
         <v>153681</v>
@@ -20727,7 +20727,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966278076172</v>
+        <v>4.34966325759888</v>
       </c>
       <c r="H702" t="n">
         <v>84918</v>
@@ -20930,7 +20930,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599216461182</v>
+        <v>4.01599168777466</v>
       </c>
       <c r="H709" t="n">
         <v>198493</v>
@@ -20959,7 +20959,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312121391296</v>
+        <v>3.92312169075012</v>
       </c>
       <c r="H710" t="n">
         <v>281423</v>
@@ -20988,7 +20988,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>3.94899296760559</v>
+        <v>3.94899272918701</v>
       </c>
       <c r="H711" t="n">
         <v>223508</v>
@@ -21046,7 +21046,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648745536804</v>
+        <v>3.91648769378662</v>
       </c>
       <c r="H713" t="n">
         <v>179781</v>
@@ -21104,7 +21104,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.9072003364563</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H715" t="n">
         <v>154260</v>
@@ -21133,7 +21133,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>3.91051745414734</v>
+        <v>3.91051721572876</v>
       </c>
       <c r="H716" t="n">
         <v>111436</v>
@@ -21162,7 +21162,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026968955994</v>
+        <v>3.96026945114136</v>
       </c>
       <c r="H717" t="n">
         <v>50070</v>
@@ -21191,7 +21191,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>3.94700241088867</v>
+        <v>3.94700217247009</v>
       </c>
       <c r="H718" t="n">
         <v>149820</v>
@@ -21220,7 +21220,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="n">
-        <v>3.94434928894043</v>
+        <v>3.94434905052185</v>
       </c>
       <c r="H719" t="n">
         <v>130093</v>
@@ -21249,7 +21249,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>3.94700241088867</v>
+        <v>3.94700217247009</v>
       </c>
       <c r="H720" t="n">
         <v>47658</v>
@@ -21278,7 +21278,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="n">
-        <v>3.98614025115967</v>
+        <v>3.98614072799683</v>
       </c>
       <c r="H721" t="n">
         <v>73891</v>
@@ -21307,7 +21307,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H722" t="n">
         <v>119608</v>
@@ -21336,7 +21336,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H723" t="n">
         <v>51535</v>
@@ -21365,7 +21365,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H724" t="n">
         <v>227117</v>
@@ -21481,7 +21481,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00670433044434</v>
+        <v>4.00670480728149</v>
       </c>
       <c r="H728" t="n">
         <v>138495</v>
@@ -21510,7 +21510,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.21234750747681</v>
+        <v>4.21234703063965</v>
       </c>
       <c r="H729" t="n">
         <v>153600</v>
@@ -21597,7 +21597,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="n">
-        <v>4.0763578414917</v>
+        <v>4.07635736465454</v>
       </c>
       <c r="H732" t="n">
         <v>64043</v>
@@ -21626,7 +21626,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04717016220093</v>
+        <v>4.04716968536377</v>
       </c>
       <c r="H733" t="n">
         <v>135061</v>
@@ -21684,7 +21684,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.00604152679443</v>
+        <v>4.00604200363159</v>
       </c>
       <c r="H735" t="n">
         <v>123762</v>
@@ -21713,7 +21713,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>3.98945784568787</v>
+        <v>3.98945760726929</v>
       </c>
       <c r="H736" t="n">
         <v>29837</v>
@@ -21742,7 +21742,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766616821289</v>
+        <v>3.94766592979431</v>
       </c>
       <c r="H737" t="n">
         <v>105830</v>
@@ -21771,7 +21771,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="n">
-        <v>3.89061665534973</v>
+        <v>3.89061641693115</v>
       </c>
       <c r="H738" t="n">
         <v>78191</v>
@@ -21800,7 +21800,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260625839233</v>
+        <v>3.89260673522949</v>
       </c>
       <c r="H739" t="n">
         <v>160586</v>
@@ -21829,7 +21829,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184425354004</v>
+        <v>3.91184401512146</v>
       </c>
       <c r="H740" t="n">
         <v>58482</v>
@@ -21858,7 +21858,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="n">
-        <v>3.99940800666809</v>
+        <v>3.99940776824951</v>
       </c>
       <c r="H741" t="n">
         <v>59931</v>
@@ -21887,7 +21887,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503128051758</v>
+        <v>4.07503175735474</v>
       </c>
       <c r="H742" t="n">
         <v>132743</v>
@@ -21916,7 +21916,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.08630847930908</v>
+        <v>4.08630800247192</v>
       </c>
       <c r="H743" t="n">
         <v>40025</v>
@@ -22003,7 +22003,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.9688937664032</v>
+        <v>3.96889328956604</v>
       </c>
       <c r="H746" t="n">
         <v>145833</v>
@@ -22032,7 +22032,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189385414124</v>
+        <v>3.90189409255981</v>
       </c>
       <c r="H747" t="n">
         <v>215638</v>
@@ -22061,7 +22061,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.9072003364563</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H748" t="n">
         <v>102007</v>
@@ -22090,7 +22090,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88729977607727</v>
+        <v>3.88729953765869</v>
       </c>
       <c r="H749" t="n">
         <v>111448</v>
@@ -22119,7 +22119,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.85214161872864</v>
+        <v>3.85214185714722</v>
       </c>
       <c r="H750" t="n">
         <v>141352</v>
@@ -22148,7 +22148,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811185836792</v>
+        <v>3.8581120967865</v>
       </c>
       <c r="H751" t="n">
         <v>63514</v>
@@ -22177,7 +22177,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361674308777</v>
+        <v>3.82361698150635</v>
       </c>
       <c r="H752" t="n">
         <v>90932</v>
@@ -22235,7 +22235,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219121932983</v>
+        <v>3.84219145774841</v>
       </c>
       <c r="H754" t="n">
         <v>195412</v>
@@ -22293,7 +22293,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.737380027771</v>
+        <v>3.73738026618958</v>
       </c>
       <c r="H756" t="n">
         <v>138294</v>
@@ -22322,7 +22322,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848971366882</v>
+        <v>3.64848923683167</v>
       </c>
       <c r="H757" t="n">
         <v>182909</v>
@@ -22351,7 +22351,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.57950019836426</v>
+        <v>3.57949995994568</v>
       </c>
       <c r="H758" t="n">
         <v>159867</v>
@@ -22380,7 +22380,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490659713745</v>
+        <v>3.56490612030029</v>
       </c>
       <c r="H759" t="n">
         <v>317061</v>
@@ -22409,7 +22409,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205388069153</v>
+        <v>3.60205411911011</v>
       </c>
       <c r="H760" t="n">
         <v>153511</v>
@@ -22438,7 +22438,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59741067886353</v>
+        <v>3.5974109172821</v>
       </c>
       <c r="H761" t="n">
         <v>232177</v>
@@ -22467,7 +22467,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="n">
-        <v>3.52046060562134</v>
+        <v>3.52046036720276</v>
       </c>
       <c r="H762" t="n">
         <v>171756</v>
@@ -22496,7 +22496,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57021284103394</v>
+        <v>3.57021260261536</v>
       </c>
       <c r="H763" t="n">
         <v>158919</v>
@@ -22554,7 +22554,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="n">
-        <v>3.76258754730225</v>
+        <v>3.76258778572083</v>
       </c>
       <c r="H765" t="n">
         <v>242926</v>
@@ -22670,7 +22670,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587401390076</v>
+        <v>3.90587377548218</v>
       </c>
       <c r="H769" t="n">
         <v>117696</v>
@@ -22728,7 +22728,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>3.90056705474854</v>
+        <v>3.90056729316711</v>
       </c>
       <c r="H771" t="n">
         <v>149636</v>
@@ -22757,7 +22757,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.8547945022583</v>
+        <v>3.85479497909546</v>
       </c>
       <c r="H772" t="n">
         <v>112700</v>
@@ -22815,7 +22815,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.89857721328735</v>
+        <v>3.8985767364502</v>
       </c>
       <c r="H774" t="n">
         <v>192350</v>
@@ -22873,7 +22873,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91516065597534</v>
+        <v>3.91516137123108</v>
       </c>
       <c r="H776" t="n">
         <v>169016</v>
@@ -22902,7 +22902,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="n">
-        <v>3.87204217910767</v>
+        <v>3.87204241752625</v>
       </c>
       <c r="H777" t="n">
         <v>97481</v>
@@ -22960,7 +22960,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="n">
-        <v>3.92842793464661</v>
+        <v>3.92842817306519</v>
       </c>
       <c r="H779" t="n">
         <v>186851</v>
@@ -22989,7 +22989,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287344932556</v>
+        <v>3.9728729724884</v>
       </c>
       <c r="H780" t="n">
         <v>142710</v>
@@ -23047,7 +23047,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657543182373</v>
+        <v>4.16657495498657</v>
       </c>
       <c r="H782" t="n">
         <v>250025</v>
@@ -23105,7 +23105,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937664031982</v>
+        <v>4.13937711715698</v>
       </c>
       <c r="H784" t="n">
         <v>119629</v>
@@ -23192,7 +23192,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947631835938</v>
+        <v>4.11947584152222</v>
       </c>
       <c r="H787" t="n">
         <v>103841</v>
@@ -23250,7 +23250,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>4.092942237854</v>
+        <v>4.09294271469116</v>
       </c>
       <c r="H789" t="n">
         <v>263354</v>
@@ -23279,7 +23279,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078416824341</v>
+        <v>3.99078392982483</v>
       </c>
       <c r="H790" t="n">
         <v>256263</v>
@@ -23308,7 +23308,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>3.91118121147156</v>
+        <v>3.91118025779724</v>
       </c>
       <c r="H791" t="n">
         <v>263702</v>
@@ -23337,7 +23337,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017072677612</v>
+        <v>3.98017001152039</v>
       </c>
       <c r="H792" t="n">
         <v>238621</v>
@@ -23366,7 +23366,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567561149597</v>
+        <v>3.94567584991455</v>
       </c>
       <c r="H793" t="n">
         <v>513739</v>
@@ -23395,7 +23395,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680424690247</v>
+        <v>3.98680448532104</v>
       </c>
       <c r="H794" t="n">
         <v>129600</v>
@@ -23424,7 +23424,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="n">
-        <v>4.02461528778076</v>
+        <v>4.02461576461792</v>
       </c>
       <c r="H795" t="n">
         <v>148746</v>
@@ -23453,7 +23453,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="n">
-        <v>4.08896160125732</v>
+        <v>4.08896207809448</v>
       </c>
       <c r="H796" t="n">
         <v>427477</v>
@@ -23540,7 +23540,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>4.06640815734863</v>
+        <v>4.06640768051147</v>
       </c>
       <c r="H799" t="n">
         <v>186549</v>
@@ -23569,7 +23569,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>4.01665544509888</v>
+        <v>4.01665496826172</v>
       </c>
       <c r="H800" t="n">
         <v>103894</v>
@@ -23598,7 +23598,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H801" t="n">
         <v>96510</v>
@@ -23627,7 +23627,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13406991958618</v>
+        <v>4.13407039642334</v>
       </c>
       <c r="H802" t="n">
         <v>101135</v>
@@ -23656,7 +23656,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="n">
-        <v>4.19178247451782</v>
+        <v>4.19178295135498</v>
       </c>
       <c r="H803" t="n">
         <v>306156</v>
@@ -23685,7 +23685,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="n">
-        <v>4.10421943664551</v>
+        <v>4.10421895980835</v>
       </c>
       <c r="H804" t="n">
         <v>271028</v>
@@ -23714,7 +23714,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H805" t="n">
         <v>290799</v>
@@ -23743,7 +23743,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="n">
-        <v>4.184485912323</v>
+        <v>4.18448543548584</v>
       </c>
       <c r="H806" t="n">
         <v>224566</v>
@@ -23830,7 +23830,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="n">
-        <v>4.41334581375122</v>
+        <v>4.41334533691406</v>
       </c>
       <c r="H809" t="n">
         <v>326833</v>
@@ -23917,7 +23917,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531646728516</v>
+        <v>4.28531742095947</v>
       </c>
       <c r="H812" t="n">
         <v>82775</v>
@@ -24033,7 +24033,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="n">
-        <v>4.44717645645142</v>
+        <v>4.44717741012573</v>
       </c>
       <c r="H816" t="n">
         <v>261217</v>
@@ -24062,7 +24062,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759244918823</v>
+        <v>4.49759292602539</v>
       </c>
       <c r="H817" t="n">
         <v>195962</v>
@@ -24120,7 +24120,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="n">
-        <v>4.41002893447876</v>
+        <v>4.4100284576416</v>
       </c>
       <c r="H819" t="n">
         <v>92629</v>
@@ -24149,7 +24149,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069221496582</v>
+        <v>4.41069269180298</v>
       </c>
       <c r="H820" t="n">
         <v>59197</v>
@@ -24236,7 +24236,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408910751343</v>
+        <v>4.26408958435059</v>
       </c>
       <c r="H823" t="n">
         <v>139907</v>
@@ -24294,7 +24294,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>4.30521821975708</v>
+        <v>4.30521726608276</v>
       </c>
       <c r="H825" t="n">
         <v>258387</v>
@@ -24352,7 +24352,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H827" t="n">
         <v>108618</v>
@@ -24410,7 +24410,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145421981812</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H829" t="n">
         <v>115908</v>
@@ -24439,7 +24439,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3980884552002</v>
+        <v>4.39808797836304</v>
       </c>
       <c r="H830" t="n">
         <v>151188</v>
@@ -24526,7 +24526,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.298583984375</v>
+        <v>4.29858446121216</v>
       </c>
       <c r="H833" t="n">
         <v>159721</v>
@@ -24613,7 +24613,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>4.40472173690796</v>
+        <v>4.40472221374512</v>
       </c>
       <c r="H836" t="n">
         <v>75933</v>
@@ -24787,7 +24787,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>4.46442413330078</v>
+        <v>4.46442461013794</v>
       </c>
       <c r="H842" t="n">
         <v>113823</v>
@@ -24845,7 +24845,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>4.41135549545288</v>
+        <v>4.41135597229004</v>
       </c>
       <c r="H844" t="n">
         <v>71545</v>
@@ -25019,7 +25019,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066204071045</v>
+        <v>4.55066156387329</v>
       </c>
       <c r="H850" t="n">
         <v>559275</v>
@@ -25048,7 +25048,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49095916748047</v>
+        <v>4.49095869064331</v>
       </c>
       <c r="H851" t="n">
         <v>276372</v>
@@ -25077,7 +25077,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838605880737</v>
+        <v>4.33838558197021</v>
       </c>
       <c r="H852" t="n">
         <v>375070</v>
@@ -25106,7 +25106,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="n">
-        <v>4.38482141494751</v>
+        <v>4.38482093811035</v>
       </c>
       <c r="H853" t="n">
         <v>252709</v>
@@ -25164,7 +25164,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940853118896</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H855" t="n">
         <v>231782</v>
@@ -25222,7 +25222,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.44223308563232</v>
+        <v>4.44223260879517</v>
       </c>
       <c r="H857" t="n">
         <v>126120</v>
@@ -25280,7 +25280,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52834987640381</v>
+        <v>4.52835035324097</v>
       </c>
       <c r="H859" t="n">
         <v>185427</v>
@@ -25309,7 +25309,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140827178955</v>
       </c>
       <c r="H860" t="n">
         <v>106622</v>
@@ -25483,7 +25483,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H866" t="n">
         <v>83940</v>
@@ -25512,7 +25512,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H867" t="n">
         <v>45354</v>
@@ -25541,7 +25541,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H868" t="n">
         <v>132081</v>
@@ -25570,7 +25570,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40634965896606</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H869" t="n">
         <v>55460</v>
@@ -25599,7 +25599,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H870" t="n">
         <v>116258</v>
@@ -25657,7 +25657,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H872" t="n">
         <v>120308</v>
@@ -25773,7 +25773,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H876" t="n">
         <v>88374</v>
@@ -26034,7 +26034,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670297622681</v>
       </c>
       <c r="H885" t="n">
         <v>158011</v>
@@ -26092,7 +26092,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670297622681</v>
       </c>
       <c r="H887" t="n">
         <v>184524</v>
@@ -26121,7 +26121,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G888" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H888" t="n">
         <v>214075</v>
@@ -26150,7 +26150,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18388032913208</v>
+        <v>4.18387937545776</v>
       </c>
       <c r="H889" t="n">
         <v>265335</v>
@@ -26295,7 +26295,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40634965896606</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H894" t="n">
         <v>80568</v>
@@ -26324,7 +26324,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H895" t="n">
         <v>65595</v>
@@ -26353,7 +26353,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H896" t="n">
         <v>44767</v>
@@ -26382,7 +26382,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H897" t="n">
         <v>139790</v>
@@ -26411,7 +26411,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G898" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H898" t="n">
         <v>120359</v>
@@ -26440,7 +26440,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>4.34893846511841</v>
+        <v>4.34893894195557</v>
       </c>
       <c r="H899" t="n">
         <v>149764</v>
@@ -26469,7 +26469,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H900" t="n">
         <v>82729</v>
@@ -26556,7 +26556,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717447280884</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H903" t="n">
         <v>213241</v>
@@ -26614,7 +26614,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717447280884</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H905" t="n">
         <v>82085</v>
@@ -26730,7 +26730,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129104614258</v>
+        <v>4.24129199981689</v>
       </c>
       <c r="H909" t="n">
         <v>98629</v>
@@ -26759,7 +26759,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H910" t="n">
         <v>110250</v>
@@ -26788,7 +26788,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670297622681</v>
       </c>
       <c r="H911" t="n">
         <v>121403</v>
@@ -26817,7 +26817,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H912" t="n">
         <v>162300</v>
@@ -26846,7 +26846,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776258468628</v>
+        <v>4.09776210784912</v>
       </c>
       <c r="H913" t="n">
         <v>213477</v>
@@ -26933,7 +26933,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H916" t="n">
         <v>220296</v>
@@ -26962,7 +26962,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H917" t="n">
         <v>142499</v>
@@ -27049,7 +27049,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>3.79635119438171</v>
+        <v>3.79635071754456</v>
       </c>
       <c r="H920" t="n">
         <v>329655</v>
@@ -27136,7 +27136,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81788039207458</v>
+        <v>3.81788015365601</v>
       </c>
       <c r="H923" t="n">
         <v>149116</v>
@@ -27194,7 +27194,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H925" t="n">
         <v>84785</v>
@@ -27223,7 +27223,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H926" t="n">
         <v>73998</v>
@@ -27252,7 +27252,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G927" t="n">
-        <v>3.79635119438171</v>
+        <v>3.79635071754456</v>
       </c>
       <c r="H927" t="n">
         <v>109743</v>
@@ -27281,7 +27281,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199791908264</v>
+        <v>3.78199815750122</v>
       </c>
       <c r="H928" t="n">
         <v>42652</v>
@@ -27310,7 +27310,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352735519409</v>
+        <v>3.80352759361267</v>
       </c>
       <c r="H929" t="n">
         <v>184164</v>
@@ -27339,7 +27339,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81788039207458</v>
+        <v>3.81788015365601</v>
       </c>
       <c r="H930" t="n">
         <v>183973</v>
@@ -27368,7 +27368,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940958976746</v>
+        <v>3.83940982818604</v>
       </c>
       <c r="H931" t="n">
         <v>200773</v>
@@ -27397,7 +27397,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.8322331905365</v>
+        <v>3.83223295211792</v>
       </c>
       <c r="H932" t="n">
         <v>201583</v>
@@ -27455,7 +27455,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658622741699</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H934" t="n">
         <v>135055</v>
@@ -27484,7 +27484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399742126465</v>
       </c>
       <c r="H935" t="n">
         <v>187953</v>
@@ -27542,7 +27542,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423364639282</v>
       </c>
       <c r="H937" t="n">
         <v>203686</v>
@@ -27571,7 +27571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G938" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H938" t="n">
         <v>122493</v>
@@ -27629,7 +27629,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317451477051</v>
       </c>
       <c r="H940" t="n">
         <v>133834</v>
@@ -27658,7 +27658,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H941" t="n">
         <v>174524</v>
@@ -27687,7 +27687,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H942" t="n">
         <v>254675</v>
@@ -27716,7 +27716,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H943" t="n">
         <v>182425</v>
@@ -27745,7 +27745,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G944" t="n">
-        <v>3.96858596801758</v>
+        <v>3.96858620643616</v>
       </c>
       <c r="H944" t="n">
         <v>193559</v>
@@ -27803,7 +27803,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H946" t="n">
         <v>137576</v>
@@ -27832,7 +27832,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317451477051</v>
       </c>
       <c r="H947" t="n">
         <v>147938</v>
@@ -27861,7 +27861,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293852806091</v>
+        <v>3.98293900489807</v>
       </c>
       <c r="H948" t="n">
         <v>118564</v>
@@ -27890,7 +27890,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H949" t="n">
         <v>84704</v>
@@ -27919,7 +27919,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>3.96858596801758</v>
+        <v>3.96858620643616</v>
       </c>
       <c r="H950" t="n">
         <v>104322</v>
@@ -27948,7 +27948,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423293113708</v>
+        <v>3.95423364639282</v>
       </c>
       <c r="H951" t="n">
         <v>122102</v>
@@ -27977,7 +27977,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H952" t="n">
         <v>71762</v>
@@ -28006,7 +28006,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317451477051</v>
       </c>
       <c r="H953" t="n">
         <v>89858</v>
@@ -28064,7 +28064,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682078361511</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H955" t="n">
         <v>198731</v>
@@ -28122,7 +28122,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G957" t="n">
-        <v>3.96858596801758</v>
+        <v>3.96858620643616</v>
       </c>
       <c r="H957" t="n">
         <v>70802</v>
@@ -28151,7 +28151,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G958" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H958" t="n">
         <v>65548</v>
@@ -28209,7 +28209,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011516571045</v>
+        <v>3.99011540412903</v>
       </c>
       <c r="H960" t="n">
         <v>112689</v>
@@ -28238,7 +28238,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317451477051</v>
       </c>
       <c r="H961" t="n">
         <v>76598</v>
@@ -28267,7 +28267,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>4.08340883255005</v>
+        <v>4.08340930938721</v>
       </c>
       <c r="H962" t="n">
         <v>105538</v>
@@ -28296,7 +28296,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>4.09058618545532</v>
+        <v>4.09058570861816</v>
       </c>
       <c r="H963" t="n">
         <v>142594</v>
@@ -28325,7 +28325,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670297622681</v>
       </c>
       <c r="H964" t="n">
         <v>184280</v>
@@ -28383,7 +28383,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>4.15517425537109</v>
+        <v>4.15517377853394</v>
       </c>
       <c r="H966" t="n">
         <v>139348</v>
@@ -28441,7 +28441,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211490631104</v>
+        <v>4.11211538314819</v>
       </c>
       <c r="H968" t="n">
         <v>76571</v>
@@ -28470,7 +28470,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646818161011</v>
+        <v>4.12646865844727</v>
       </c>
       <c r="H969" t="n">
         <v>66738</v>
@@ -28528,7 +28528,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H971" t="n">
         <v>154145</v>
@@ -28615,7 +28615,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H974" t="n">
         <v>38961</v>
@@ -28644,7 +28644,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646818161011</v>
+        <v>4.12646865844727</v>
       </c>
       <c r="H975" t="n">
         <v>83904</v>
@@ -28702,7 +28702,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G977" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H977" t="n">
         <v>27675</v>
@@ -28760,7 +28760,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G979" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H979" t="n">
         <v>138951</v>
@@ -28789,7 +28789,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G980" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H980" t="n">
         <v>126747</v>
@@ -28818,7 +28818,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H981" t="n">
         <v>169971</v>
@@ -28847,7 +28847,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G982" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564479827881</v>
       </c>
       <c r="H982" t="n">
         <v>98272</v>
@@ -28876,7 +28876,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717447280884</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H983" t="n">
         <v>94635</v>
@@ -28934,7 +28934,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H985" t="n">
         <v>162590</v>
@@ -28992,7 +28992,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717447280884</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H987" t="n">
         <v>69784</v>
@@ -29021,7 +29021,7 @@
         <v>6</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30588006973267</v>
+        <v>4.30587959289551</v>
       </c>
       <c r="H988" t="n">
         <v>135917</v>
@@ -29050,7 +29050,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H989" t="n">
         <v>138068</v>
@@ -29108,7 +29108,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305646896362</v>
+        <v>4.31305694580078</v>
       </c>
       <c r="H991" t="n">
         <v>83600</v>
@@ -29166,7 +29166,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H993" t="n">
         <v>45492</v>
@@ -29224,7 +29224,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H995" t="n">
         <v>358111</v>
@@ -29253,7 +29253,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G996" t="n">
-        <v>4.57858562469482</v>
+        <v>4.57858514785767</v>
       </c>
       <c r="H996" t="n">
         <v>495439</v>
@@ -29282,7 +29282,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G997" t="n">
-        <v>4.62164449691772</v>
+        <v>4.62164402008057</v>
       </c>
       <c r="H997" t="n">
         <v>342817</v>
@@ -29311,7 +29311,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552675247192</v>
+        <v>4.53552722930908</v>
       </c>
       <c r="H998" t="n">
         <v>278924</v>
@@ -29427,7 +29427,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1002" t="n">
         <v>62344</v>
@@ -29514,7 +29514,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940853118896</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1005" t="n">
         <v>77356</v>
@@ -29572,7 +29572,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1007" t="n">
         <v>129466</v>
@@ -29601,7 +29601,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1008" t="n">
         <v>90036</v>
@@ -29659,7 +29659,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40634965896606</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H1010" t="n">
         <v>69927</v>
@@ -29688,7 +29688,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1011" t="n">
         <v>143195</v>
@@ -29717,7 +29717,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1012" t="n">
         <v>242811</v>
@@ -29746,7 +29746,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1013" t="n">
         <v>63163</v>
@@ -29775,7 +29775,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.45658588409424</v>
+        <v>4.45658540725708</v>
       </c>
       <c r="H1014" t="n">
         <v>98685</v>
@@ -29804,7 +29804,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940853118896</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1015" t="n">
         <v>125144</v>
@@ -29862,7 +29862,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.45658588409424</v>
+        <v>4.45658540725708</v>
       </c>
       <c r="H1017" t="n">
         <v>96543</v>
@@ -29891,7 +29891,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1018" t="n">
         <v>130838</v>
@@ -29949,7 +29949,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1020" t="n">
         <v>147871</v>
@@ -30007,7 +30007,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1022" t="n">
         <v>89368</v>
@@ -30036,7 +30036,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.45658588409424</v>
+        <v>4.45658540725708</v>
       </c>
       <c r="H1023" t="n">
         <v>76307</v>
@@ -30065,7 +30065,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.45658588409424</v>
+        <v>4.45658540725708</v>
       </c>
       <c r="H1024" t="n">
         <v>66931</v>
@@ -30094,7 +30094,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1025" t="n">
         <v>56890</v>
@@ -30210,7 +30210,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940853118896</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1029" t="n">
         <v>103178</v>
@@ -30268,7 +30268,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940853118896</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1031" t="n">
         <v>101854</v>
@@ -30326,7 +30326,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.41352701187134</v>
+        <v>4.41352653503418</v>
       </c>
       <c r="H1033" t="n">
         <v>135419</v>
@@ -30413,7 +30413,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917373657227</v>
+        <v>4.39917421340942</v>
       </c>
       <c r="H1036" t="n">
         <v>110854</v>
@@ -30442,7 +30442,7 @@
         <v>6</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.30588006973267</v>
+        <v>4.30587959289551</v>
       </c>
       <c r="H1037" t="n">
         <v>183171</v>
@@ -30471,7 +30471,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870319366455</v>
+        <v>4.29870271682739</v>
       </c>
       <c r="H1038" t="n">
         <v>161115</v>
@@ -30674,7 +30674,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.5068211555481</v>
+        <v>4.50682067871094</v>
       </c>
       <c r="H1045" t="n">
         <v>167360</v>
@@ -30732,7 +30732,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964475631714</v>
       </c>
       <c r="H1047" t="n">
         <v>186654</v>
@@ -30761,7 +30761,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270315170288</v>
+        <v>4.54270362854004</v>
       </c>
       <c r="H1048" t="n">
         <v>201438</v>
@@ -30790,7 +30790,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.55705595016479</v>
+        <v>4.55705642700195</v>
       </c>
       <c r="H1049" t="n">
         <v>136339</v>
@@ -30819,7 +30819,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140827178955</v>
       </c>
       <c r="H1050" t="n">
         <v>112242</v>
@@ -30848,7 +30848,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.52117443084717</v>
+        <v>4.52117395401001</v>
       </c>
       <c r="H1051" t="n">
         <v>126242</v>
@@ -30906,7 +30906,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H1053" t="n">
         <v>645418</v>
@@ -31022,7 +31022,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399742126465</v>
       </c>
       <c r="H1057" t="n">
         <v>651281</v>
@@ -31051,7 +31051,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682078361511</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H1058" t="n">
         <v>494611</v>
@@ -31109,7 +31109,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.91835021972656</v>
+        <v>3.9183509349823</v>
       </c>
       <c r="H1060" t="n">
         <v>289543</v>
@@ -31138,7 +31138,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505679130554</v>
+        <v>3.82505655288696</v>
       </c>
       <c r="H1061" t="n">
         <v>188804</v>
@@ -31283,7 +31283,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299871444702</v>
+        <v>2.62299847602844</v>
       </c>
       <c r="H1066" t="n">
         <v>700650</v>
@@ -31312,7 +31312,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605734825134</v>
+        <v>2.66605710983276</v>
       </c>
       <c r="H1067" t="n">
         <v>497765</v>
@@ -31370,7 +31370,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1069" t="n">
         <v>316624</v>
@@ -31399,7 +31399,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1070" t="n">
         <v>294654</v>
@@ -31428,7 +31428,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.55482196807861</v>
+        <v>2.55482220649719</v>
       </c>
       <c r="H1071" t="n">
         <v>262610</v>
@@ -31457,7 +31457,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682194709778</v>
+        <v>2.67682218551636</v>
       </c>
       <c r="H1072" t="n">
         <v>1041965</v>
@@ -31486,7 +31486,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.61223411560059</v>
+        <v>2.61223387718201</v>
       </c>
       <c r="H1073" t="n">
         <v>255816</v>
@@ -31573,7 +31573,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423361778259</v>
+        <v>2.73423385620117</v>
       </c>
       <c r="H1076" t="n">
         <v>156770</v>
@@ -31602,7 +31602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705721855164</v>
+        <v>2.72705698013306</v>
       </c>
       <c r="H1077" t="n">
         <v>193039</v>
@@ -31660,7 +31660,7 @@
         <v>3.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.69117474555969</v>
+        <v>2.69117498397827</v>
       </c>
       <c r="H1079" t="n">
         <v>342391</v>
@@ -31776,7 +31776,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1083" t="n">
         <v>180927</v>
@@ -31834,7 +31834,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.66964554786682</v>
+        <v>2.66964530944824</v>
       </c>
       <c r="H1085" t="n">
         <v>172170</v>
@@ -31863,7 +31863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.64093947410583</v>
+        <v>2.64093971252441</v>
       </c>
       <c r="H1086" t="n">
         <v>261581</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.66964554786682</v>
+        <v>2.66964530944824</v>
       </c>
       <c r="H1087" t="n">
         <v>189444</v>
@@ -31950,7 +31950,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1089" t="n">
         <v>196323</v>
@@ -32037,7 +32037,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.53688073158264</v>
+        <v>2.5368812084198</v>
       </c>
       <c r="H1092" t="n">
         <v>202956</v>
@@ -32066,7 +32066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329300880432</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1093" t="n">
         <v>139451</v>
@@ -32095,7 +32095,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.54764580726624</v>
+        <v>2.54764556884766</v>
       </c>
       <c r="H1094" t="n">
         <v>108032</v>
@@ -32124,7 +32124,7 @@
         <v>3.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1095" t="n">
         <v>71153</v>
@@ -32153,7 +32153,7 @@
         <v>3.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1096" t="n">
         <v>133075</v>
@@ -32211,7 +32211,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.55482196807861</v>
+        <v>2.55482220649719</v>
       </c>
       <c r="H1098" t="n">
         <v>251103</v>
@@ -32414,7 +32414,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1105" t="n">
         <v>149130</v>
@@ -32443,7 +32443,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.36823391914368</v>
+        <v>2.3682336807251</v>
       </c>
       <c r="H1106" t="n">
         <v>326150</v>
@@ -32501,7 +32501,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.31082224845886</v>
+        <v>2.31082201004028</v>
       </c>
       <c r="H1108" t="n">
         <v>196343</v>
@@ -32530,7 +32530,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.31799864768982</v>
+        <v>2.3179988861084</v>
       </c>
       <c r="H1109" t="n">
         <v>123243</v>
@@ -32559,7 +32559,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1110" t="n">
         <v>311033</v>
@@ -32588,7 +32588,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.38258695602417</v>
+        <v>2.38258671760559</v>
       </c>
       <c r="H1111" t="n">
         <v>243942</v>
@@ -32646,7 +32646,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652823448181</v>
+        <v>2.15652847290039</v>
       </c>
       <c r="H1113" t="n">
         <v>565839</v>
@@ -32675,7 +32675,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805767059326</v>
+        <v>2.17805790901184</v>
       </c>
       <c r="H1114" t="n">
         <v>231502</v>
@@ -32733,7 +32733,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105728149414</v>
+        <v>2.36105751991272</v>
       </c>
       <c r="H1116" t="n">
         <v>277343</v>
@@ -32762,7 +32762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005764961243</v>
+        <v>2.30005741119385</v>
       </c>
       <c r="H1117" t="n">
         <v>282326</v>
@@ -32791,7 +32791,7 @@
         <v>3.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.33235168457031</v>
+        <v>2.33235144615173</v>
       </c>
       <c r="H1118" t="n">
         <v>359504</v>
@@ -32849,7 +32849,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.35388088226318</v>
+        <v>2.35388112068176</v>
       </c>
       <c r="H1120" t="n">
         <v>213833</v>
@@ -32878,7 +32878,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.42564582824707</v>
+        <v>2.42564558982849</v>
       </c>
       <c r="H1121" t="n">
         <v>440602</v>
@@ -32907,7 +32907,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1122" t="n">
         <v>477229</v>
@@ -32965,7 +32965,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.68040990829468</v>
+        <v>2.68041014671326</v>
       </c>
       <c r="H1124" t="n">
         <v>901153</v>
@@ -32994,7 +32994,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81317472457886</v>
+        <v>2.81317496299744</v>
       </c>
       <c r="H1125" t="n">
         <v>470004</v>
@@ -33052,7 +33052,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1127" t="n">
         <v>417942</v>
@@ -33081,7 +33081,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.45435190200806</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1128" t="n">
         <v>348708</v>
@@ -33139,7 +33139,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.45435190200806</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1130" t="n">
         <v>287875</v>
@@ -33226,7 +33226,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.54764580726624</v>
+        <v>2.54764556884766</v>
       </c>
       <c r="H1133" t="n">
         <v>139107</v>
@@ -33255,7 +33255,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.45435190200806</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1134" t="n">
         <v>433647</v>
@@ -33284,7 +33284,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1135" t="n">
         <v>163840</v>
@@ -33313,7 +33313,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588109970093</v>
       </c>
       <c r="H1136" t="n">
         <v>150113</v>
@@ -33429,7 +33429,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.49382209777832</v>
+        <v>2.49382185935974</v>
       </c>
       <c r="H1140" t="n">
         <v>92813</v>
@@ -33487,7 +33487,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.49023389816284</v>
+        <v>2.49023365974426</v>
       </c>
       <c r="H1142" t="n">
         <v>106314</v>
@@ -33545,7 +33545,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588109970093</v>
       </c>
       <c r="H1144" t="n">
         <v>135364</v>
@@ -33632,7 +33632,7 @@
         <v>3.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.51176309585571</v>
+        <v>2.51176333427429</v>
       </c>
       <c r="H1147" t="n">
         <v>88292</v>
@@ -33661,7 +33661,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588109970093</v>
       </c>
       <c r="H1148" t="n">
         <v>130888</v>
@@ -33690,7 +33690,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.47588086128235</v>
+        <v>2.47588109970093</v>
       </c>
       <c r="H1149" t="n">
         <v>127063</v>
@@ -33748,7 +33748,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329300880432</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1151" t="n">
         <v>202010</v>
@@ -33806,7 +33806,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1153" t="n">
         <v>399041</v>
@@ -33864,7 +33864,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.59075379371643</v>
+        <v>2.59075331687927</v>
       </c>
       <c r="H1155" t="n">
         <v>491686</v>
@@ -33951,7 +33951,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344397544861</v>
+        <v>2.48344421386719</v>
       </c>
       <c r="H1158" t="n">
         <v>166881</v>
@@ -33980,7 +33980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.42978978157043</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1159" t="n">
         <v>156578</v>
@@ -34009,7 +34009,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1160" t="n">
         <v>154215</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1161" t="n">
         <v>154775</v>
@@ -34067,7 +34067,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1162" t="n">
         <v>148965</v>
@@ -34096,7 +34096,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.34164261817932</v>
+        <v>2.34164237976074</v>
       </c>
       <c r="H1163" t="n">
         <v>191513</v>
@@ -34154,7 +34154,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1165" t="n">
         <v>148256</v>
@@ -34183,7 +34183,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.42978978157043</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1166" t="n">
         <v>110673</v>
@@ -34212,7 +34212,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.42978978157043</v>
+        <v>2.42978954315186</v>
       </c>
       <c r="H1167" t="n">
         <v>125258</v>
@@ -34241,7 +34241,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.40296196937561</v>
+        <v>2.40296220779419</v>
       </c>
       <c r="H1168" t="n">
         <v>113023</v>
@@ -34270,7 +34270,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1169" t="n">
         <v>159196</v>
@@ -34299,7 +34299,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.44511961936951</v>
+        <v>2.44511938095093</v>
       </c>
       <c r="H1170" t="n">
         <v>128151</v>
@@ -34386,7 +34386,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.44511961936951</v>
+        <v>2.44511938095093</v>
       </c>
       <c r="H1173" t="n">
         <v>106590</v>
@@ -34415,7 +34415,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679478645325</v>
+        <v>2.40679454803467</v>
       </c>
       <c r="H1174" t="n">
         <v>149038</v>
@@ -34444,7 +34444,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1175" t="n">
         <v>77116</v>
@@ -34473,7 +34473,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1176" t="n">
         <v>101920</v>
@@ -34560,7 +34560,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.32247996330261</v>
+        <v>2.32248020172119</v>
       </c>
       <c r="H1179" t="n">
         <v>80748</v>
@@ -34589,7 +34589,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1180" t="n">
         <v>124034</v>
@@ -34618,7 +34618,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697221755981</v>
       </c>
       <c r="H1181" t="n">
         <v>73283</v>
@@ -34734,7 +34734,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.35697245597839</v>
+        <v>2.35697221755981</v>
       </c>
       <c r="H1185" t="n">
         <v>134671</v>
@@ -34792,7 +34792,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.36846947669983</v>
+        <v>2.36846971511841</v>
       </c>
       <c r="H1187" t="n">
         <v>74015</v>
@@ -34879,7 +34879,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1190" t="n">
         <v>56050</v>
@@ -34908,7 +34908,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.35313987731934</v>
+        <v>2.35314011573792</v>
       </c>
       <c r="H1191" t="n">
         <v>58041</v>
@@ -34937,7 +34937,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1192" t="n">
         <v>36038</v>
@@ -34966,7 +34966,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1193" t="n">
         <v>38721</v>
@@ -34995,7 +34995,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1194" t="n">
         <v>286707</v>
@@ -35024,7 +35024,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1195" t="n">
         <v>112081</v>
@@ -35053,7 +35053,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1196" t="n">
         <v>154795</v>
@@ -35082,7 +35082,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.38379979133606</v>
+        <v>2.38379955291748</v>
       </c>
       <c r="H1197" t="n">
         <v>56722</v>
@@ -35169,7 +35169,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715036392212</v>
+        <v>2.30715012550354</v>
       </c>
       <c r="H1200" t="n">
         <v>254056</v>
@@ -35198,7 +35198,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.32247996330261</v>
+        <v>2.32248020172119</v>
       </c>
       <c r="H1201" t="n">
         <v>90187</v>
@@ -35227,7 +35227,7 @@
         <v>3</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.29948544502258</v>
+        <v>2.299485206604</v>
       </c>
       <c r="H1202" t="n">
         <v>89554</v>
@@ -35430,7 +35430,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.35313987731934</v>
+        <v>2.35314011573792</v>
       </c>
       <c r="H1209" t="n">
         <v>246233</v>
@@ -35459,7 +35459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613487243652</v>
+        <v>2.37613463401794</v>
       </c>
       <c r="H1210" t="n">
         <v>130645</v>
@@ -35546,7 +35546,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.47577905654907</v>
+        <v>2.47577929496765</v>
       </c>
       <c r="H1213" t="n">
         <v>269685</v>
@@ -35575,7 +35575,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.47577905654907</v>
+        <v>2.47577929496765</v>
       </c>
       <c r="H1214" t="n">
         <v>246638</v>
@@ -35633,7 +35633,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230253219604</v>
+        <v>2.37230229377747</v>
       </c>
       <c r="H1216" t="n">
         <v>160104</v>
@@ -35691,7 +35691,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283554077148</v>
+        <v>2.22283577919006</v>
       </c>
       <c r="H1218" t="n">
         <v>339921</v>
@@ -35720,7 +35720,7 @@
         <v>2.875</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.20367336273193</v>
+        <v>2.20367360115051</v>
       </c>
       <c r="H1219" t="n">
         <v>195479</v>
@@ -35749,7 +35749,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.2266685962677</v>
+        <v>2.22666835784912</v>
       </c>
       <c r="H1220" t="n">
         <v>102898</v>
@@ -35778,7 +35778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750594139099</v>
+        <v>2.20750570297241</v>
       </c>
       <c r="H1221" t="n">
         <v>142174</v>
@@ -35807,7 +35807,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.17301368713379</v>
+        <v>2.17301344871521</v>
       </c>
       <c r="H1222" t="n">
         <v>242902</v>
@@ -35836,7 +35836,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786151885986</v>
+        <v>2.10786128044128</v>
       </c>
       <c r="H1223" t="n">
         <v>329808</v>
@@ -35894,7 +35894,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.03887677192688</v>
+        <v>2.03887701034546</v>
       </c>
       <c r="H1225" t="n">
         <v>168729</v>
@@ -35923,7 +35923,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.98522222042084</v>
+        <v>1.98522210121155</v>
       </c>
       <c r="H1226" t="n">
         <v>131888</v>
@@ -35981,7 +35981,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.90857267379761</v>
+        <v>1.9085727930069</v>
       </c>
       <c r="H1228" t="n">
         <v>240537</v>
@@ -36010,7 +36010,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.91240513324738</v>
+        <v>1.91240501403809</v>
       </c>
       <c r="H1229" t="n">
         <v>705511</v>
@@ -36097,7 +36097,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.00821733474731</v>
+        <v>2.00821709632874</v>
       </c>
       <c r="H1232" t="n">
         <v>231003</v>
@@ -36213,7 +36213,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877405166626</v>
+        <v>2.49877429008484</v>
       </c>
       <c r="H1236" t="n">
         <v>1002989</v>
@@ -36300,7 +36300,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.59075379371643</v>
+        <v>2.59075331687927</v>
       </c>
       <c r="H1239" t="n">
         <v>250791</v>
@@ -36329,7 +36329,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1240" t="n">
         <v>992861</v>
@@ -36358,7 +36358,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1241" t="n">
         <v>318659</v>
@@ -36387,7 +36387,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.71339273452759</v>
+        <v>2.71339249610901</v>
       </c>
       <c r="H1242" t="n">
         <v>459132</v>
@@ -36416,7 +36416,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.67506766319275</v>
+        <v>2.67506790161133</v>
       </c>
       <c r="H1243" t="n">
         <v>494900</v>
@@ -36532,7 +36532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405241012573</v>
+        <v>2.74405217170715</v>
       </c>
       <c r="H1247" t="n">
         <v>450366</v>
@@ -36561,7 +36561,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1248" t="n">
         <v>269119</v>
@@ -36677,7 +36677,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68656516075134</v>
+        <v>2.68656539916992</v>
       </c>
       <c r="H1252" t="n">
         <v>485014</v>
@@ -36706,7 +36706,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1253" t="n">
         <v>729352</v>
@@ -36764,7 +36764,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1255" t="n">
         <v>268956</v>
@@ -36851,7 +36851,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1258" t="n">
         <v>858635</v>
@@ -36996,7 +36996,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1263" t="n">
         <v>164441</v>
@@ -37083,7 +37083,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1266" t="n">
         <v>404158</v>
@@ -37112,7 +37112,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1267" t="n">
         <v>453222</v>
@@ -37170,7 +37170,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.82836699485779</v>
+        <v>2.82836675643921</v>
       </c>
       <c r="H1269" t="n">
         <v>261734</v>
@@ -37199,7 +37199,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.75938248634338</v>
+        <v>2.7593822479248</v>
       </c>
       <c r="H1270" t="n">
         <v>197407</v>
@@ -37257,7 +37257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1272" t="n">
         <v>280324</v>
@@ -37286,7 +37286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.82836699485779</v>
+        <v>2.82836675643921</v>
       </c>
       <c r="H1273" t="n">
         <v>137710</v>
@@ -37315,7 +37315,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.83603167533875</v>
+        <v>2.83603191375732</v>
       </c>
       <c r="H1274" t="n">
         <v>136480</v>
@@ -37373,7 +37373,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.85136198997498</v>
+        <v>2.8513617515564</v>
       </c>
       <c r="H1276" t="n">
         <v>358795</v>
@@ -37402,7 +37402,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87052392959595</v>
+        <v>2.87052416801453</v>
       </c>
       <c r="H1277" t="n">
         <v>85060</v>
@@ -37431,7 +37431,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1278" t="n">
         <v>80215</v>
@@ -37460,7 +37460,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1279" t="n">
         <v>604084</v>
@@ -37489,7 +37489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1280" t="n">
         <v>254659</v>
@@ -37518,7 +37518,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1281" t="n">
         <v>42257</v>
@@ -37576,7 +37576,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285924911499</v>
+        <v>2.86285901069641</v>
       </c>
       <c r="H1283" t="n">
         <v>574210</v>
@@ -37605,7 +37605,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620958328247</v>
+        <v>2.78620982170105</v>
       </c>
       <c r="H1284" t="n">
         <v>230927</v>
@@ -37692,7 +37692,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1287" t="n">
         <v>186106</v>
@@ -37721,7 +37721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.71339273452759</v>
+        <v>2.71339249610901</v>
       </c>
       <c r="H1288" t="n">
         <v>215050</v>
@@ -37750,7 +37750,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1289" t="n">
         <v>357241</v>
@@ -37808,7 +37808,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1291" t="n">
         <v>279807</v>
@@ -37895,7 +37895,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82070183753967</v>
+        <v>2.82070207595825</v>
       </c>
       <c r="H1294" t="n">
         <v>128387</v>
@@ -37982,7 +37982,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.93950867652893</v>
+        <v>2.93950891494751</v>
       </c>
       <c r="H1297" t="n">
         <v>163979</v>
@@ -38098,7 +38098,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849342346191</v>
+        <v>3.00849318504333</v>
       </c>
       <c r="H1301" t="n">
         <v>169875</v>
@@ -38156,7 +38156,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699568748474</v>
       </c>
       <c r="H1303" t="n">
         <v>311894</v>
@@ -38185,7 +38185,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1304" t="n">
         <v>631921</v>
@@ -38214,7 +38214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369683265686</v>
       </c>
       <c r="H1305" t="n">
         <v>141746</v>
@@ -38243,7 +38243,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.9203462600708</v>
+        <v>2.92034649848938</v>
       </c>
       <c r="H1306" t="n">
         <v>122098</v>
@@ -38272,7 +38272,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1307" t="n">
         <v>163152</v>
@@ -38301,7 +38301,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.96250367164612</v>
+        <v>2.96250343322754</v>
       </c>
       <c r="H1308" t="n">
         <v>124483</v>
@@ -38330,7 +38330,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1309" t="n">
         <v>851470</v>
@@ -38417,7 +38417,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1312" t="n">
         <v>318481</v>
@@ -38446,7 +38446,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1313" t="n">
         <v>282164</v>
@@ -38475,7 +38475,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1314" t="n">
         <v>329760</v>
@@ -38562,7 +38562,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1317" t="n">
         <v>259106</v>
@@ -38591,7 +38591,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1318" t="n">
         <v>510876</v>
@@ -38620,7 +38620,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1319" t="n">
         <v>410062</v>
@@ -38707,7 +38707,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1322" t="n">
         <v>275948</v>
@@ -38736,7 +38736,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1323" t="n">
         <v>221706</v>
@@ -38794,7 +38794,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1325" t="n">
         <v>410108</v>
@@ -38881,7 +38881,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207290649414</v>
+        <v>2.65207314491272</v>
       </c>
       <c r="H1328" t="n">
         <v>523941</v>
@@ -38910,7 +38910,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.59841847419739</v>
+        <v>2.59841871261597</v>
       </c>
       <c r="H1329" t="n">
         <v>172336</v>
@@ -38997,7 +38997,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.6559054851532</v>
+        <v>2.65590524673462</v>
       </c>
       <c r="H1332" t="n">
         <v>124651</v>
@@ -39055,7 +39055,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1334" t="n">
         <v>268795</v>
@@ -39084,7 +39084,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1335" t="n">
         <v>669291</v>
@@ -39113,7 +39113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1336" t="n">
         <v>266103</v>
@@ -39142,7 +39142,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.73638772964478</v>
+        <v>2.7363874912262</v>
       </c>
       <c r="H1337" t="n">
         <v>148748</v>
@@ -39171,7 +39171,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1338" t="n">
         <v>283462</v>
@@ -39229,7 +39229,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1340" t="n">
         <v>294026</v>
@@ -39258,7 +39258,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1341" t="n">
         <v>108872</v>
@@ -39287,7 +39287,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1342" t="n">
         <v>124489</v>
@@ -39316,7 +39316,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.88968658447266</v>
+        <v>2.88968634605408</v>
       </c>
       <c r="H1343" t="n">
         <v>293864</v>
@@ -39345,7 +39345,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.0429859161377</v>
+        <v>3.04298567771912</v>
       </c>
       <c r="H1344" t="n">
         <v>748180</v>
@@ -39374,7 +39374,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1345" t="n">
         <v>248627</v>
@@ -39403,7 +39403,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.96633577346802</v>
+        <v>2.9663360118866</v>
       </c>
       <c r="H1346" t="n">
         <v>181306</v>
@@ -39461,7 +39461,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.97400116920471</v>
+        <v>2.97400093078613</v>
       </c>
       <c r="H1348" t="n">
         <v>114414</v>
@@ -39490,7 +39490,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1349" t="n">
         <v>150256</v>
@@ -39577,7 +39577,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1352" t="n">
         <v>204988</v>
@@ -39635,7 +39635,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1354" t="n">
         <v>192611</v>
@@ -39693,7 +39693,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.15412712097168</v>
+        <v>3.15412735939026</v>
       </c>
       <c r="H1356" t="n">
         <v>386167</v>
@@ -39751,7 +39751,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1358" t="n">
         <v>187366</v>
@@ -39780,7 +39780,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676653862</v>
+        <v>3.27676677703857</v>
       </c>
       <c r="H1359" t="n">
         <v>363222</v>
@@ -39809,7 +39809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1360" t="n">
         <v>294112</v>
@@ -39867,7 +39867,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1362" t="n">
         <v>296147</v>
@@ -39983,7 +39983,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.09280753135681</v>
+        <v>3.09280776977539</v>
       </c>
       <c r="H1366" t="n">
         <v>236757</v>
@@ -40012,7 +40012,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1367" t="n">
         <v>167546</v>
@@ -40041,7 +40041,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.0429859161377</v>
+        <v>3.04298567771912</v>
       </c>
       <c r="H1368" t="n">
         <v>243646</v>
@@ -40157,7 +40157,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897566795349</v>
       </c>
       <c r="H1372" t="n">
         <v>215125</v>
@@ -40215,7 +40215,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.1502947807312</v>
+        <v>3.15029501914978</v>
       </c>
       <c r="H1374" t="n">
         <v>318940</v>
@@ -40244,7 +40244,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1375" t="n">
         <v>216825</v>
@@ -40302,7 +40302,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.2346088886261</v>
+        <v>3.23460912704468</v>
       </c>
       <c r="H1377" t="n">
         <v>538436</v>
@@ -40331,7 +40331,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1378" t="n">
         <v>159804</v>
@@ -40360,7 +40360,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209661483765</v>
       </c>
       <c r="H1379" t="n">
         <v>919643</v>
@@ -40389,7 +40389,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.28826379776001</v>
+        <v>3.28826427459717</v>
       </c>
       <c r="H1380" t="n">
         <v>310169</v>
@@ -40476,7 +40476,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.56036972999573</v>
+        <v>3.56036996841431</v>
       </c>
       <c r="H1383" t="n">
         <v>247312</v>
@@ -40563,7 +40563,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054739952087</v>
+        <v>3.51054787635803</v>
       </c>
       <c r="H1386" t="n">
         <v>316680</v>
@@ -40592,7 +40592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557313919067</v>
+        <v>3.39557290077209</v>
       </c>
       <c r="H1387" t="n">
         <v>935373</v>
@@ -40766,7 +40766,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.31892395019531</v>
+        <v>3.31892371177673</v>
       </c>
       <c r="H1393" t="n">
         <v>211919</v>
@@ -40795,7 +40795,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1394" t="n">
         <v>384891</v>
@@ -40882,7 +40882,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1397" t="n">
         <v>183307</v>
@@ -40911,7 +40911,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1398" t="n">
         <v>112518</v>
@@ -40940,7 +40940,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927928924561</v>
       </c>
       <c r="H1399" t="n">
         <v>295169</v>
@@ -40969,7 +40969,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1400" t="n">
         <v>213421</v>
@@ -41027,7 +41027,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1402" t="n">
         <v>186824</v>
@@ -41056,7 +41056,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1403" t="n">
         <v>236837</v>
@@ -41085,7 +41085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1404" t="n">
         <v>114681</v>
@@ -41172,7 +41172,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.1502947807312</v>
+        <v>3.15029501914978</v>
       </c>
       <c r="H1407" t="n">
         <v>146797</v>
@@ -41201,7 +41201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1408" t="n">
         <v>69983</v>
@@ -41230,7 +41230,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1409" t="n">
         <v>221820</v>
@@ -41259,7 +41259,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1410" t="n">
         <v>178327</v>
@@ -41288,7 +41288,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1411" t="n">
         <v>170666</v>
@@ -41375,7 +41375,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.15412712097168</v>
+        <v>3.15412735939026</v>
       </c>
       <c r="H1414" t="n">
         <v>365235</v>
@@ -41404,7 +41404,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1415" t="n">
         <v>92805</v>
@@ -41433,7 +41433,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1502947807312</v>
+        <v>3.15029501914978</v>
       </c>
       <c r="H1416" t="n">
         <v>121956</v>
@@ -41462,7 +41462,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.1502947807312</v>
+        <v>3.15029501914978</v>
       </c>
       <c r="H1417" t="n">
         <v>112954</v>
@@ -41636,7 +41636,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1423" t="n">
         <v>123011</v>
@@ -41723,7 +41723,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377154350281</v>
+        <v>3.25377178192139</v>
       </c>
       <c r="H1426" t="n">
         <v>193950</v>
@@ -41781,7 +41781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1428" t="n">
         <v>275646</v>
@@ -41810,7 +41810,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1429" t="n">
         <v>95971</v>
@@ -42013,7 +42013,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1436" t="n">
         <v>177399</v>
@@ -42100,7 +42100,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166584968567</v>
+        <v>2.98166608810425</v>
       </c>
       <c r="H1439" t="n">
         <v>590692</v>
@@ -42129,7 +42129,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1440" t="n">
         <v>279680</v>
@@ -42187,7 +42187,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.05831551551819</v>
+        <v>3.05831527709961</v>
       </c>
       <c r="H1442" t="n">
         <v>237497</v>
@@ -42332,7 +42332,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.88585424423218</v>
+        <v>2.8858540058136</v>
       </c>
       <c r="H1447" t="n">
         <v>350177</v>
@@ -42361,7 +42361,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1448" t="n">
         <v>367975</v>
@@ -42390,7 +42390,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153942108154</v>
+        <v>2.80153965950012</v>
       </c>
       <c r="H1449" t="n">
         <v>397419</v>
@@ -42535,7 +42535,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1454" t="n">
         <v>357222</v>
@@ -42593,7 +42593,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268134117126</v>
+        <v>2.91268110275269</v>
       </c>
       <c r="H1456" t="n">
         <v>226254</v>
@@ -42622,7 +42622,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.9969961643219</v>
+        <v>2.99699568748474</v>
       </c>
       <c r="H1457" t="n">
         <v>610266</v>
@@ -42767,7 +42767,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.00466084480286</v>
+        <v>3.00466108322144</v>
       </c>
       <c r="H1462" t="n">
         <v>381784</v>
@@ -42825,7 +42825,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1464" t="n">
         <v>341626</v>
@@ -42854,7 +42854,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1465" t="n">
         <v>296217</v>
@@ -42883,7 +42883,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.00466084480286</v>
+        <v>3.00466108322144</v>
       </c>
       <c r="H1466" t="n">
         <v>181785</v>
@@ -42912,7 +42912,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.03148818016052</v>
+        <v>3.03148794174194</v>
       </c>
       <c r="H1467" t="n">
         <v>119381</v>
@@ -42941,7 +42941,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1468" t="n">
         <v>102163</v>
@@ -42999,7 +42999,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897566795349</v>
       </c>
       <c r="H1470" t="n">
         <v>167749</v>
@@ -43028,7 +43028,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897566795349</v>
       </c>
       <c r="H1471" t="n">
         <v>311050</v>
@@ -43086,7 +43086,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214785575867</v>
+        <v>3.06214761734009</v>
       </c>
       <c r="H1473" t="n">
         <v>159481</v>
@@ -43144,7 +43144,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.05831551551819</v>
+        <v>3.05831527709961</v>
       </c>
       <c r="H1475" t="n">
         <v>118061</v>
@@ -43202,7 +43202,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1477" t="n">
         <v>1174979</v>
@@ -43231,7 +43231,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.11580276489258</v>
+        <v>3.115802526474</v>
       </c>
       <c r="H1478" t="n">
         <v>845247</v>
@@ -43289,7 +43289,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735174179077</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1480" t="n">
         <v>585959</v>
@@ -43434,7 +43434,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.94334101676941</v>
+        <v>2.94334125518799</v>
       </c>
       <c r="H1485" t="n">
         <v>218046</v>
@@ -43463,7 +43463,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1486" t="n">
         <v>385290</v>
@@ -43492,7 +43492,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1487" t="n">
         <v>1594525</v>
@@ -43550,7 +43550,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1489" t="n">
         <v>399032</v>
@@ -43579,7 +43579,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1490" t="n">
         <v>301508</v>
@@ -43608,7 +43608,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047292709351</v>
+        <v>3.10047268867493</v>
       </c>
       <c r="H1491" t="n">
         <v>141241</v>
@@ -43753,7 +43753,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1496" t="n">
         <v>427392</v>
@@ -43869,7 +43869,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.82453441619873</v>
+        <v>2.82453417778015</v>
       </c>
       <c r="H1500" t="n">
         <v>192975</v>
@@ -43898,7 +43898,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.85136198997498</v>
+        <v>2.8513617515564</v>
       </c>
       <c r="H1501" t="n">
         <v>263324</v>
@@ -43985,7 +43985,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1504" t="n">
         <v>285523</v>
@@ -44014,7 +44014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207290649414</v>
+        <v>2.65207314491272</v>
       </c>
       <c r="H1505" t="n">
         <v>615078</v>
@@ -44043,7 +44043,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1506" t="n">
         <v>191990</v>
@@ -44072,7 +44072,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1507" t="n">
         <v>201693</v>
@@ -44101,7 +44101,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1508" t="n">
         <v>218675</v>
@@ -44130,7 +44130,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1509" t="n">
         <v>131010</v>
@@ -44159,7 +44159,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.78237724304199</v>
+        <v>2.78237748146057</v>
       </c>
       <c r="H1510" t="n">
         <v>424497</v>
@@ -44217,7 +44217,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1512" t="n">
         <v>148986</v>
@@ -44304,7 +44304,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.76321482658386</v>
+        <v>2.76321458816528</v>
       </c>
       <c r="H1515" t="n">
         <v>527190</v>
@@ -44362,7 +44362,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735174179077</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1517" t="n">
         <v>354141</v>
@@ -44565,7 +44565,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1524" t="n">
         <v>362207</v>
@@ -44594,7 +44594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1525" t="n">
         <v>179741</v>
@@ -44623,7 +44623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1526" t="n">
         <v>156246</v>
@@ -44681,7 +44681,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.09280753135681</v>
+        <v>3.09280776977539</v>
       </c>
       <c r="H1528" t="n">
         <v>532620</v>
@@ -44710,7 +44710,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.11580276489258</v>
+        <v>3.115802526474</v>
       </c>
       <c r="H1529" t="n">
         <v>212110</v>
@@ -44739,7 +44739,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1530" t="n">
         <v>467217</v>
@@ -44884,7 +44884,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927905082703</v>
+        <v>3.21927928924561</v>
       </c>
       <c r="H1535" t="n">
         <v>639377</v>
@@ -44942,7 +44942,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1537" t="n">
         <v>601285</v>
@@ -44971,7 +44971,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1538" t="n">
         <v>318781</v>
@@ -45087,7 +45087,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.0429859161377</v>
+        <v>3.04298567771912</v>
       </c>
       <c r="H1542" t="n">
         <v>583493</v>
@@ -45116,7 +45116,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681801795959</v>
+        <v>3.04681777954102</v>
       </c>
       <c r="H1543" t="n">
         <v>292809</v>
@@ -45145,7 +45145,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1544" t="n">
         <v>157684</v>
@@ -45174,7 +45174,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1545" t="n">
         <v>194223</v>
@@ -45232,7 +45232,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.1502947807312</v>
+        <v>3.15029501914978</v>
       </c>
       <c r="H1547" t="n">
         <v>415287</v>
@@ -45464,7 +45464,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1555" t="n">
         <v>415471</v>
@@ -45551,7 +45551,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760388374329</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1558" t="n">
         <v>301113</v>
@@ -45609,7 +45609,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760388374329</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1560" t="n">
         <v>279714</v>
@@ -45754,7 +45754,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778203010559</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1565" t="n">
         <v>975722</v>
@@ -45783,7 +45783,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.40707111358643</v>
+        <v>3.40707087516785</v>
       </c>
       <c r="H1566" t="n">
         <v>643548</v>
@@ -45812,7 +45812,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.45306062698364</v>
+        <v>3.45306038856506</v>
       </c>
       <c r="H1567" t="n">
         <v>647492</v>
@@ -45841,7 +45841,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760388374329</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1568" t="n">
         <v>500504</v>
@@ -45870,7 +45870,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.30359387397766</v>
+        <v>3.30359411239624</v>
       </c>
       <c r="H1569" t="n">
         <v>301184</v>
@@ -45899,7 +45899,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.2346088886261</v>
+        <v>3.23460912704468</v>
       </c>
       <c r="H1570" t="n">
         <v>219173</v>
@@ -46073,7 +46073,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.23077702522278</v>
+        <v>3.2307767868042</v>
       </c>
       <c r="H1576" t="n">
         <v>421250</v>
@@ -46102,7 +46102,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694444656372</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1577" t="n">
         <v>314566</v>
@@ -46160,7 +46160,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844170570374</v>
+        <v>3.23844194412231</v>
       </c>
       <c r="H1579" t="n">
         <v>280568</v>
@@ -46189,7 +46189,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394945144653</v>
+        <v>3.20394968986511</v>
       </c>
       <c r="H1580" t="n">
         <v>262215</v>
@@ -46247,7 +46247,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.22311162948608</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1582" t="n">
         <v>154452</v>
@@ -46363,7 +46363,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760388374329</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1586" t="n">
         <v>154125</v>
@@ -46450,7 +46450,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491322517395</v>
+        <v>3.36491346359253</v>
       </c>
       <c r="H1589" t="n">
         <v>186298</v>
@@ -46566,7 +46566,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.42623281478882</v>
+        <v>3.4262330532074</v>
       </c>
       <c r="H1593" t="n">
         <v>476538</v>
@@ -46682,7 +46682,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.50288271903992</v>
+        <v>3.5028829574585</v>
       </c>
       <c r="H1597" t="n">
         <v>291846</v>
@@ -46740,7 +46740,7 @@
         <v>4.625</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.54503989219666</v>
+        <v>3.54504013061523</v>
       </c>
       <c r="H1599" t="n">
         <v>184940</v>
@@ -46769,7 +46769,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372030258179</v>
+        <v>3.48372006416321</v>
       </c>
       <c r="H1600" t="n">
         <v>129996</v>
@@ -46972,7 +46972,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.50671482086182</v>
+        <v>3.5067150592804</v>
       </c>
       <c r="H1607" t="n">
         <v>142915</v>
@@ -47059,7 +47059,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.4147355556488</v>
+        <v>3.41473579406738</v>
       </c>
       <c r="H1610" t="n">
         <v>352993</v>
@@ -47088,7 +47088,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.43006587028503</v>
+        <v>3.43006563186646</v>
       </c>
       <c r="H1611" t="n">
         <v>150531</v>
@@ -47146,7 +47146,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209661483765</v>
       </c>
       <c r="H1613" t="n">
         <v>656275</v>
@@ -47175,7 +47175,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.2346088886261</v>
+        <v>3.23460912704468</v>
       </c>
       <c r="H1614" t="n">
         <v>666814</v>
@@ -47233,7 +47233,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.20953464508057</v>
+        <v>3.20953488349915</v>
       </c>
       <c r="H1616" t="n">
         <v>826619</v>
@@ -47262,7 +47262,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1617" t="n">
         <v>369551</v>
@@ -47291,7 +47291,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804208755493</v>
+        <v>3.26804184913635</v>
       </c>
       <c r="H1618" t="n">
         <v>297177</v>
@@ -47349,7 +47349,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177273750305</v>
+        <v>3.40177249908447</v>
       </c>
       <c r="H1620" t="n">
         <v>184041</v>
@@ -47378,7 +47378,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1621" t="n">
         <v>194836</v>
@@ -47407,7 +47407,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251877784729</v>
+        <v>3.37251901626587</v>
       </c>
       <c r="H1622" t="n">
         <v>196489</v>
@@ -47610,7 +47610,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.38923501968384</v>
+        <v>3.38923525810242</v>
       </c>
       <c r="H1629" t="n">
         <v>109111</v>
@@ -47639,7 +47639,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1630" t="n">
         <v>441762</v>
@@ -47668,7 +47668,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087701797485</v>
+        <v>3.38087725639343</v>
       </c>
       <c r="H1631" t="n">
         <v>335342</v>
@@ -47697,7 +47697,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1632" t="n">
         <v>295881</v>
@@ -47755,7 +47755,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1634" t="n">
         <v>105059</v>
@@ -47813,7 +47813,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968360900879</v>
+        <v>3.25968384742737</v>
       </c>
       <c r="H1636" t="n">
         <v>115170</v>
@@ -47842,7 +47842,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1637" t="n">
         <v>144155</v>
@@ -47929,7 +47929,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1640" t="n">
         <v>210448</v>
@@ -47958,7 +47958,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.93789482116699</v>
+        <v>2.93789458274841</v>
       </c>
       <c r="H1641" t="n">
         <v>158561</v>
@@ -47987,7 +47987,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1642" t="n">
         <v>151991</v>
@@ -48016,7 +48016,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.87520813941956</v>
+        <v>2.87520837783813</v>
       </c>
       <c r="H1643" t="n">
         <v>275360</v>
@@ -48103,7 +48103,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132730484009</v>
+        <v>2.97132706642151</v>
       </c>
       <c r="H1646" t="n">
         <v>131405</v>
@@ -48132,7 +48132,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1647" t="n">
         <v>134428</v>
@@ -48219,7 +48219,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1650" t="n">
         <v>131117</v>
@@ -48248,7 +48248,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1651" t="n">
-        <v>3.05908799171448</v>
+        <v>3.0590877532959</v>
       </c>
       <c r="H1651" t="n">
         <v>134242</v>
@@ -48393,7 +48393,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78326845169067</v>
+        <v>2.78326821327209</v>
       </c>
       <c r="H1656" t="n">
         <v>290500</v>
@@ -48422,7 +48422,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595441818237</v>
+        <v>2.84595465660095</v>
       </c>
       <c r="H1657" t="n">
         <v>159265</v>
@@ -48451,7 +48451,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1658" t="n">
         <v>166380</v>
@@ -48567,7 +48567,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.975506067276</v>
+        <v>2.97550630569458</v>
       </c>
       <c r="H1662" t="n">
         <v>113262</v>
@@ -48596,7 +48596,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.91699886322021</v>
+        <v>2.91699910163879</v>
       </c>
       <c r="H1663" t="n">
         <v>120330</v>
@@ -48799,7 +48799,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1670" t="n">
         <v>140069</v>
@@ -48886,7 +48886,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.99640154838562</v>
+        <v>2.9964017868042</v>
       </c>
       <c r="H1673" t="n">
         <v>58916</v>
@@ -48944,7 +48944,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1675" t="n">
         <v>64858</v>
@@ -49002,7 +49002,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.14684891700745</v>
+        <v>3.14684844017029</v>
       </c>
       <c r="H1677" t="n">
         <v>141377</v>
@@ -49118,7 +49118,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.14684891700745</v>
+        <v>3.14684844017029</v>
       </c>
       <c r="H1681" t="n">
         <v>121914</v>
@@ -49176,7 +49176,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.16356515884399</v>
+        <v>3.16356492042542</v>
       </c>
       <c r="H1683" t="n">
         <v>102151</v>
@@ -49205,7 +49205,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.20953464508057</v>
+        <v>3.20953488349915</v>
       </c>
       <c r="H1684" t="n">
         <v>173010</v>
@@ -49408,7 +49408,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1691" t="n">
         <v>76345</v>
@@ -49524,7 +49524,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.87520813941956</v>
+        <v>2.87520837783813</v>
       </c>
       <c r="H1695" t="n">
         <v>84113</v>
@@ -49669,7 +49669,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.75819420814514</v>
+        <v>2.75819373130798</v>
       </c>
       <c r="H1700" t="n">
         <v>79771</v>
@@ -49727,7 +49727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147748947144</v>
+        <v>2.74147772789001</v>
       </c>
       <c r="H1702" t="n">
         <v>135653</v>
@@ -49785,7 +49785,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.91699886322021</v>
+        <v>2.91699910163879</v>
       </c>
       <c r="H1704" t="n">
         <v>135448</v>
@@ -49901,7 +49901,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.69968676567078</v>
+        <v>2.69968700408936</v>
       </c>
       <c r="H1708" t="n">
         <v>1264562</v>
@@ -49930,7 +49930,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.73311948776245</v>
+        <v>2.73311924934387</v>
       </c>
       <c r="H1709" t="n">
         <v>72871</v>
@@ -50017,7 +50017,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.51162815093994</v>
+        <v>2.51162838935852</v>
       </c>
       <c r="H1712" t="n">
         <v>178826</v>
@@ -50046,7 +50046,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1713" t="n">
         <v>327552</v>
@@ -50075,7 +50075,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.36953949928284</v>
+        <v>2.36953926086426</v>
       </c>
       <c r="H1714" t="n">
         <v>223167</v>
@@ -50220,7 +50220,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.30685305595398</v>
+        <v>2.30685329437256</v>
       </c>
       <c r="H1719" t="n">
         <v>210971</v>
@@ -50249,7 +50249,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1720" t="n">
         <v>157033</v>
@@ -50307,7 +50307,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.23998785018921</v>
+        <v>2.23998808860779</v>
       </c>
       <c r="H1722" t="n">
         <v>166709</v>
@@ -50336,7 +50336,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1723" t="n">
         <v>163103</v>
@@ -50394,7 +50394,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1725" t="n">
         <v>189735</v>
@@ -50423,7 +50423,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.20237588882446</v>
+        <v>2.20237612724304</v>
       </c>
       <c r="H1726" t="n">
         <v>145959</v>
@@ -50452,7 +50452,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.21073412895203</v>
+        <v>2.21073436737061</v>
       </c>
       <c r="H1727" t="n">
         <v>192663</v>
@@ -50481,7 +50481,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.16058540344238</v>
+        <v>2.1605851650238</v>
       </c>
       <c r="H1728" t="n">
         <v>328209</v>
@@ -50510,7 +50510,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.21073412895203</v>
+        <v>2.21073436737061</v>
       </c>
       <c r="H1729" t="n">
         <v>308750</v>
@@ -50539,7 +50539,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1730" t="n">
         <v>525600</v>
@@ -50568,7 +50568,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.22745037078857</v>
+        <v>2.22745060920715</v>
       </c>
       <c r="H1731" t="n">
         <v>234021</v>
@@ -50597,7 +50597,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1732" t="n">
         <v>115131</v>
@@ -50626,7 +50626,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1733" t="n">
         <v>131798</v>
@@ -50655,7 +50655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1734" t="n">
         <v>187787</v>
@@ -50684,7 +50684,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1735" t="n">
         <v>172469</v>
@@ -50800,7 +50800,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1739" t="n">
         <v>123630</v>
@@ -50887,7 +50887,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.50326991081238</v>
+        <v>2.5032696723938</v>
       </c>
       <c r="H1742" t="n">
         <v>250081</v>
@@ -50916,7 +50916,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744915008545</v>
+        <v>2.50744891166687</v>
       </c>
       <c r="H1743" t="n">
         <v>179184</v>
@@ -50945,7 +50945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013535499573</v>
+        <v>2.57013511657715</v>
       </c>
       <c r="H1744" t="n">
         <v>319932</v>
@@ -50974,7 +50974,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1745" t="n">
         <v>149411</v>
@@ -51032,7 +51032,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1747" t="n">
         <v>321826</v>
@@ -51090,7 +51090,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1749" t="n">
         <v>280050</v>
@@ -51148,7 +51148,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.54506063461304</v>
+        <v>2.54506087303162</v>
       </c>
       <c r="H1751" t="n">
         <v>334625</v>
@@ -51177,7 +51177,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.55759787559509</v>
+        <v>2.55759811401367</v>
       </c>
       <c r="H1752" t="n">
         <v>185533</v>
@@ -51206,7 +51206,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.59521007537842</v>
+        <v>2.59520959854126</v>
       </c>
       <c r="H1753" t="n">
         <v>162826</v>
@@ -51293,7 +51293,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1756" t="n">
         <v>119541</v>
@@ -51409,7 +51409,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.7205822467804</v>
+        <v>2.72058248519897</v>
       </c>
       <c r="H1760" t="n">
         <v>266940</v>
@@ -51554,7 +51554,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.73311948776245</v>
+        <v>2.73311924934387</v>
       </c>
       <c r="H1765" t="n">
         <v>229339</v>
@@ -51583,7 +51583,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72476124763489</v>
+        <v>2.72476148605347</v>
       </c>
       <c r="H1766" t="n">
         <v>142984</v>
@@ -51786,7 +51786,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.59938883781433</v>
+        <v>2.59938859939575</v>
       </c>
       <c r="H1773" t="n">
         <v>393315</v>
@@ -51960,7 +51960,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.59521007537842</v>
+        <v>2.59520959854126</v>
       </c>
       <c r="H1779" t="n">
         <v>50328</v>
@@ -52076,7 +52076,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1783" t="n">
         <v>59395</v>
@@ -52134,7 +52134,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.72476124763489</v>
+        <v>2.72476148605347</v>
       </c>
       <c r="H1785" t="n">
         <v>159569</v>
@@ -52192,7 +52192,7 @@
         <v>3.25</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.7164032459259</v>
+        <v>2.71640300750732</v>
       </c>
       <c r="H1787" t="n">
         <v>110388</v>
@@ -52221,7 +52221,7 @@
         <v>3.25</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.7164032459259</v>
+        <v>2.71640300750732</v>
       </c>
       <c r="H1788" t="n">
         <v>169068</v>
@@ -52453,7 +52453,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.81252193450928</v>
+        <v>2.81252217292786</v>
       </c>
       <c r="H1796" t="n">
         <v>189050</v>
@@ -52511,7 +52511,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.88356637954712</v>
+        <v>2.8835666179657</v>
       </c>
       <c r="H1798" t="n">
         <v>177420</v>
@@ -52627,7 +52627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.47401666641235</v>
+        <v>2.47401642799377</v>
       </c>
       <c r="H1802" t="n">
         <v>1663657</v>
@@ -52743,7 +52743,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.39461374282837</v>
+        <v>2.39461398124695</v>
       </c>
       <c r="H1806" t="n">
         <v>489458</v>
@@ -52801,7 +52801,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1808" t="n">
         <v>588277</v>
@@ -52830,7 +52830,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.34864377975464</v>
+        <v>2.34864401817322</v>
       </c>
       <c r="H1809" t="n">
         <v>341799</v>
@@ -52859,7 +52859,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.36953949928284</v>
+        <v>2.36953926086426</v>
       </c>
       <c r="H1810" t="n">
         <v>311648</v>
@@ -52888,7 +52888,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1811" t="n">
         <v>336694</v>
@@ -52946,7 +52946,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.36953949928284</v>
+        <v>2.36953926086426</v>
       </c>
       <c r="H1813" t="n">
         <v>351767</v>
@@ -52975,7 +52975,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.34446501731873</v>
+        <v>2.34446477890015</v>
       </c>
       <c r="H1814" t="n">
         <v>250677</v>
@@ -53062,7 +53062,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.34446501731873</v>
+        <v>2.34446477890015</v>
       </c>
       <c r="H1817" t="n">
         <v>323266</v>
@@ -53120,7 +53120,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.32356929779053</v>
+        <v>2.32356953620911</v>
       </c>
       <c r="H1819" t="n">
         <v>237689</v>
@@ -53149,7 +53149,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.30685305595398</v>
+        <v>2.30685329437256</v>
       </c>
       <c r="H1820" t="n">
         <v>309991</v>
@@ -53178,7 +53178,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1821" t="n">
         <v>691856</v>
@@ -53207,7 +53207,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.39461374282837</v>
+        <v>2.39461398124695</v>
       </c>
       <c r="H1822" t="n">
         <v>890767</v>
@@ -53236,7 +53236,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.39879274368286</v>
+        <v>2.39879298210144</v>
       </c>
       <c r="H1823" t="n">
         <v>526870</v>
@@ -53323,7 +53323,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.36953949928284</v>
+        <v>2.36953926086426</v>
       </c>
       <c r="H1826" t="n">
         <v>118369</v>
@@ -53352,7 +53352,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.39461374282837</v>
+        <v>2.39461398124695</v>
       </c>
       <c r="H1827" t="n">
         <v>165539</v>
@@ -53381,7 +53381,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.42386722564697</v>
+        <v>2.42386746406555</v>
       </c>
       <c r="H1828" t="n">
         <v>291959</v>
@@ -53410,7 +53410,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.39879274368286</v>
+        <v>2.39879298210144</v>
       </c>
       <c r="H1829" t="n">
         <v>280086</v>
@@ -53439,7 +53439,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.38207626342773</v>
+        <v>2.38207650184631</v>
       </c>
       <c r="H1830" t="n">
         <v>365354</v>
@@ -53497,7 +53497,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.37371826171875</v>
+        <v>2.37371850013733</v>
       </c>
       <c r="H1832" t="n">
         <v>440369</v>
@@ -53555,7 +53555,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.34864377975464</v>
+        <v>2.34864401817322</v>
       </c>
       <c r="H1834" t="n">
         <v>455832</v>
@@ -53613,7 +53613,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1836" t="n">
         <v>505563</v>
@@ -53642,7 +53642,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.27342057228088</v>
+        <v>2.2734203338623</v>
       </c>
       <c r="H1837" t="n">
         <v>394668</v>
@@ -53671,7 +53671,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.34446501731873</v>
+        <v>2.34446477890015</v>
       </c>
       <c r="H1838" t="n">
         <v>298411</v>
@@ -53700,7 +53700,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.34446501731873</v>
+        <v>2.34446477890015</v>
       </c>
       <c r="H1839" t="n">
         <v>121336</v>
@@ -53729,7 +53729,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.2943160533905</v>
+        <v>2.29431581497192</v>
       </c>
       <c r="H1840" t="n">
         <v>387840</v>
@@ -53787,7 +53787,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1842" t="n">
         <v>375724</v>
@@ -53816,7 +53816,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.2775993347168</v>
+        <v>2.27759957313538</v>
       </c>
       <c r="H1843" t="n">
         <v>97253</v>
@@ -53845,7 +53845,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.28595781326294</v>
+        <v>2.28595757484436</v>
       </c>
       <c r="H1844" t="n">
         <v>131363</v>
@@ -53874,7 +53874,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1845" t="n">
         <v>224918</v>
@@ -53961,7 +53961,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.34864377975464</v>
+        <v>2.34864401817322</v>
       </c>
       <c r="H1848" t="n">
         <v>276306</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1851" t="n">
         <v>294292</v>
@@ -54077,7 +54077,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1852" t="n">
         <v>247994</v>
@@ -54106,7 +54106,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1853" t="n">
         <v>352350</v>
@@ -54222,7 +54222,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.46147918701172</v>
+        <v>2.46147894859314</v>
       </c>
       <c r="H1857" t="n">
         <v>276583</v>
@@ -54367,7 +54367,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.39879274368286</v>
+        <v>2.39879298210144</v>
       </c>
       <c r="H1862" t="n">
         <v>204962</v>
@@ -54396,7 +54396,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.42386722564697</v>
+        <v>2.42386746406555</v>
       </c>
       <c r="H1863" t="n">
         <v>347556</v>
@@ -54425,7 +54425,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.42386722564697</v>
+        <v>2.42386746406555</v>
       </c>
       <c r="H1864" t="n">
         <v>597686</v>
@@ -54541,7 +54541,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.34864377975464</v>
+        <v>2.34864401817322</v>
       </c>
       <c r="H1868" t="n">
         <v>645135</v>
@@ -79951,6 +79951,64 @@
         <v>26073</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>59045</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>3.65499997138977</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>3.65499997138977</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>147714</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G2" t="n">
-        <v>4.56322860717773</v>
+        <v>4.56322813034058</v>
       </c>
       <c r="H2" t="n">
         <v>105854</v>
@@ -543,7 +543,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409700393677</v>
+        <v>4.48409652709961</v>
       </c>
       <c r="H6" t="n">
         <v>164680</v>
@@ -601,7 +601,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.40496587753296</v>
+        <v>4.40496635437012</v>
       </c>
       <c r="H8" t="n">
         <v>127969</v>
@@ -630,7 +630,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50783681869507</v>
+        <v>4.50783586502075</v>
       </c>
       <c r="H9" t="n">
         <v>83967</v>
@@ -717,7 +717,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.01722383499146</v>
+        <v>4.0172233581543</v>
       </c>
       <c r="H12" t="n">
         <v>222009</v>
@@ -775,7 +775,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48177003860474</v>
+        <v>3.481769323349</v>
       </c>
       <c r="H14" t="n">
         <v>416053</v>
@@ -804,7 +804,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74553990364075</v>
+        <v>3.74553942680359</v>
       </c>
       <c r="H15" t="n">
         <v>313484</v>
@@ -833,7 +833,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.81675815582275</v>
+        <v>3.8167576789856</v>
       </c>
       <c r="H16" t="n">
         <v>176408</v>
@@ -862,7 +862,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.89588904380798</v>
+        <v>3.89588832855225</v>
       </c>
       <c r="H17" t="n">
         <v>120439</v>
@@ -891,7 +891,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522176742554</v>
+        <v>3.83522129058838</v>
       </c>
       <c r="H18" t="n">
         <v>75537</v>
@@ -920,7 +920,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884552001953</v>
+        <v>3.80884456634521</v>
       </c>
       <c r="H19" t="n">
         <v>163830</v>
@@ -949,7 +949,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959713935852</v>
+        <v>3.67959761619568</v>
       </c>
       <c r="H20" t="n">
         <v>133261</v>
@@ -978,7 +978,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467126846313</v>
+        <v>3.82467103004456</v>
       </c>
       <c r="H21" t="n">
         <v>190130</v>
@@ -1036,7 +1036,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74553990364075</v>
+        <v>3.74553942680359</v>
       </c>
       <c r="H23" t="n">
         <v>350145</v>
@@ -1094,7 +1094,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617617607117</v>
+        <v>3.56617665290833</v>
       </c>
       <c r="H25" t="n">
         <v>406980</v>
@@ -1123,7 +1123,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65322041511536</v>
+        <v>3.65322017669678</v>
       </c>
       <c r="H26" t="n">
         <v>190657</v>
@@ -1152,7 +1152,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405780792236</v>
+        <v>3.33405804634094</v>
       </c>
       <c r="H27" t="n">
         <v>238163</v>
@@ -1181,7 +1181,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626123428345</v>
+        <v>3.37626099586487</v>
       </c>
       <c r="H28" t="n">
         <v>216081</v>
@@ -1239,7 +1239,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220399856567</v>
+        <v>3.44220423698425</v>
       </c>
       <c r="H30" t="n">
         <v>158033</v>
@@ -1326,7 +1326,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69278573989868</v>
+        <v>3.692786693573</v>
       </c>
       <c r="H33" t="n">
         <v>218931</v>
@@ -1355,7 +1355,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467126846313</v>
+        <v>3.82467103004456</v>
       </c>
       <c r="H34" t="n">
         <v>72733</v>
@@ -1384,7 +1384,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829359054565</v>
+        <v>3.79829406738281</v>
       </c>
       <c r="H35" t="n">
         <v>53341</v>
@@ -1413,7 +1413,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498940467834</v>
+        <v>3.73498916625977</v>
       </c>
       <c r="H36" t="n">
         <v>83765</v>
@@ -1442,7 +1442,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.9169909954071</v>
+        <v>3.91699051856995</v>
       </c>
       <c r="H37" t="n">
         <v>87617</v>
@@ -1529,7 +1529,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.8457727432251</v>
+        <v>3.84577322006226</v>
       </c>
       <c r="H40" t="n">
         <v>43899</v>
@@ -1558,7 +1558,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104823112488</v>
+        <v>3.85104775428772</v>
       </c>
       <c r="H41" t="n">
         <v>113404</v>
@@ -1587,7 +1587,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061403274536</v>
+        <v>3.89061331748962</v>
       </c>
       <c r="H42" t="n">
         <v>132642</v>
@@ -1674,7 +1674,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.0620641708374</v>
+        <v>4.06206464767456</v>
       </c>
       <c r="H45" t="n">
         <v>183400</v>
@@ -1703,7 +1703,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G46" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H46" t="n">
         <v>380676</v>
@@ -1732,7 +1732,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339920043945</v>
       </c>
       <c r="H47" t="n">
         <v>153285</v>
@@ -1790,7 +1790,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603706359863</v>
+        <v>4.18603658676147</v>
       </c>
       <c r="H49" t="n">
         <v>97201</v>
@@ -1819,7 +1819,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G50" t="n">
-        <v>4.27308082580566</v>
+        <v>4.27308130264282</v>
       </c>
       <c r="H50" t="n">
         <v>189331</v>
@@ -1877,7 +1877,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40496587753296</v>
+        <v>4.40496635437012</v>
       </c>
       <c r="H52" t="n">
         <v>135917</v>
@@ -1906,7 +1906,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221147537231</v>
+        <v>4.35221242904663</v>
       </c>
       <c r="H53" t="n">
         <v>202614</v>
@@ -1935,7 +1935,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473279953003</v>
+        <v>4.30473327636719</v>
       </c>
       <c r="H54" t="n">
         <v>145802</v>
@@ -1964,7 +1964,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G55" t="n">
-        <v>4.41024112701416</v>
+        <v>4.41024160385132</v>
       </c>
       <c r="H55" t="n">
         <v>165321</v>
@@ -1993,7 +1993,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047372817993</v>
+        <v>4.51047420501709</v>
       </c>
       <c r="H56" t="n">
         <v>440847</v>
@@ -2080,7 +2080,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583522796631</v>
       </c>
       <c r="H59" t="n">
         <v>99265</v>
@@ -2109,7 +2109,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658756256104</v>
+        <v>4.19658803939819</v>
       </c>
       <c r="H60" t="n">
         <v>142725</v>
@@ -2138,7 +2138,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H61" t="n">
         <v>168165</v>
@@ -2196,7 +2196,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G63" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H63" t="n">
         <v>152427</v>
@@ -2225,7 +2225,7 @@
         <v>7.52076816558838</v>
       </c>
       <c r="G64" t="n">
-        <v>4.26780557632446</v>
+        <v>4.26780605316162</v>
       </c>
       <c r="H64" t="n">
         <v>132175</v>
@@ -2254,7 +2254,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G65" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H65" t="n">
         <v>63157</v>
@@ -2341,7 +2341,7 @@
         <v>7.18144989013672</v>
       </c>
       <c r="G68" t="n">
-        <v>4.07525253295898</v>
+        <v>4.07525300979614</v>
       </c>
       <c r="H68" t="n">
         <v>38160</v>
@@ -2457,7 +2457,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H72" t="n">
         <v>138383</v>
@@ -2515,7 +2515,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812347412109</v>
       </c>
       <c r="H74" t="n">
         <v>11963</v>
@@ -2573,7 +2573,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G76" t="n">
-        <v>4.15438508987427</v>
+        <v>4.15438365936279</v>
       </c>
       <c r="H76" t="n">
         <v>69912</v>
@@ -2602,7 +2602,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.2124137878418</v>
+        <v>4.21241426467896</v>
       </c>
       <c r="H77" t="n">
         <v>65491</v>
@@ -2805,7 +2805,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339920043945</v>
       </c>
       <c r="H84" t="n">
         <v>135960</v>
@@ -3037,7 +3037,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G92" t="n">
-        <v>4.15438508987427</v>
+        <v>4.15438365936279</v>
       </c>
       <c r="H92" t="n">
         <v>118401</v>
@@ -3066,7 +3066,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702247619629</v>
+        <v>4.15702199935913</v>
       </c>
       <c r="H93" t="n">
         <v>72826</v>
@@ -3095,7 +3095,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G94" t="n">
-        <v>4.23351526260376</v>
+        <v>4.2335147857666</v>
       </c>
       <c r="H94" t="n">
         <v>64992</v>
@@ -3124,7 +3124,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044343948364</v>
+        <v>4.2704439163208</v>
       </c>
       <c r="H95" t="n">
         <v>62480</v>
@@ -3153,7 +3153,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131135940552</v>
+        <v>4.19131183624268</v>
       </c>
       <c r="H96" t="n">
         <v>58862</v>
@@ -3240,7 +3240,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G99" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H99" t="n">
         <v>83655</v>
@@ -3327,7 +3327,7 @@
         <v>7.51147079467773</v>
       </c>
       <c r="G102" t="n">
-        <v>4.48687362670898</v>
+        <v>4.48687314987183</v>
       </c>
       <c r="H102" t="n">
         <v>87735</v>
@@ -3356,7 +3356,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H103" t="n">
         <v>122131</v>
@@ -3414,7 +3414,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.52852153778076</v>
+        <v>4.52852201461792</v>
       </c>
       <c r="H105" t="n">
         <v>60638</v>
@@ -3443,7 +3443,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H106" t="n">
         <v>102357</v>
@@ -3559,7 +3559,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743774414062</v>
+        <v>4.46743869781494</v>
       </c>
       <c r="H110" t="n">
         <v>35336</v>
@@ -3733,7 +3733,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768455505371</v>
+        <v>3.91768503189087</v>
       </c>
       <c r="H116" t="n">
         <v>109038</v>
@@ -3762,7 +3762,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989706039429</v>
+        <v>3.93989658355713</v>
       </c>
       <c r="H117" t="n">
         <v>151204</v>
@@ -3791,7 +3791,7 @@
         <v>6.38196182250977</v>
       </c>
       <c r="G118" t="n">
-        <v>3.8121771812439</v>
+        <v>3.81217670440674</v>
       </c>
       <c r="H118" t="n">
         <v>94805</v>
@@ -3820,7 +3820,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.83161211013794</v>
+        <v>3.83161282539368</v>
       </c>
       <c r="H119" t="n">
         <v>396991</v>
@@ -3936,7 +3936,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G123" t="n">
-        <v>4.12592506408691</v>
+        <v>4.12592458724976</v>
       </c>
       <c r="H123" t="n">
         <v>138672</v>
@@ -4052,7 +4052,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H127" t="n">
         <v>204444</v>
@@ -4081,7 +4081,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594633102417</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H128" t="n">
         <v>365836</v>
@@ -4139,7 +4139,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603759765625</v>
+        <v>3.87603712081909</v>
       </c>
       <c r="H130" t="n">
         <v>40805</v>
@@ -4168,7 +4168,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165702819824</v>
+        <v>3.73165726661682</v>
       </c>
       <c r="H131" t="n">
         <v>182299</v>
@@ -4197,7 +4197,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111584663391</v>
+        <v>3.70111536979675</v>
       </c>
       <c r="H132" t="n">
         <v>120419</v>
@@ -4255,7 +4255,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490912437439</v>
+        <v>3.91490864753723</v>
       </c>
       <c r="H134" t="n">
         <v>96476</v>
@@ -4284,7 +4284,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9482274055481</v>
+        <v>3.94822645187378</v>
       </c>
       <c r="H135" t="n">
         <v>150820</v>
@@ -4400,7 +4400,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H139" t="n">
         <v>148533</v>
@@ -4458,7 +4458,7 @@
         <v>7.13496780395508</v>
       </c>
       <c r="G141" t="n">
-        <v>4.26197481155396</v>
+        <v>4.26197385787964</v>
       </c>
       <c r="H141" t="n">
         <v>144879</v>
@@ -4487,7 +4487,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.2980694770813</v>
+        <v>4.29806900024414</v>
       </c>
       <c r="H142" t="n">
         <v>180595</v>
@@ -4545,7 +4545,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H144" t="n">
         <v>200057</v>
@@ -4574,7 +4574,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583427429199</v>
       </c>
       <c r="H145" t="n">
         <v>68143</v>
@@ -4632,7 +4632,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858867645264</v>
+        <v>4.37858915328979</v>
       </c>
       <c r="H147" t="n">
         <v>120474</v>
@@ -4690,7 +4690,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="n">
-        <v>4.33138847351074</v>
+        <v>4.33138799667358</v>
       </c>
       <c r="H149" t="n">
         <v>169324</v>
@@ -4806,7 +4806,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="n">
-        <v>4.2342095375061</v>
+        <v>4.23420906066895</v>
       </c>
       <c r="H153" t="n">
         <v>141811</v>
@@ -4835,7 +4835,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917501449585</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H154" t="n">
         <v>185636</v>
@@ -4864,7 +4864,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="n">
-        <v>4.22865629196167</v>
+        <v>4.22865581512451</v>
       </c>
       <c r="H155" t="n">
         <v>73708</v>
@@ -4922,7 +4922,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H157" t="n">
         <v>67846</v>
@@ -4951,7 +4951,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="n">
-        <v>4.25919818878174</v>
+        <v>4.2591986656189</v>
       </c>
       <c r="H158" t="n">
         <v>110609</v>
@@ -5009,7 +5009,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423175811768</v>
+        <v>4.18423128128052</v>
       </c>
       <c r="H160" t="n">
         <v>85871</v>
@@ -5154,7 +5154,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317066192627</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H165" t="n">
         <v>82306</v>
@@ -5183,7 +5183,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="n">
-        <v>4.11204242706299</v>
+        <v>4.11204195022583</v>
       </c>
       <c r="H166" t="n">
         <v>46261</v>
@@ -5212,7 +5212,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371208190918</v>
+        <v>4.10371255874634</v>
       </c>
       <c r="H167" t="n">
         <v>23476</v>
@@ -5241,7 +5241,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150100708008</v>
+        <v>4.08150053024292</v>
       </c>
       <c r="H168" t="n">
         <v>81619</v>
@@ -5270,7 +5270,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820423126221</v>
       </c>
       <c r="H169" t="n">
         <v>96105</v>
@@ -5299,7 +5299,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="n">
-        <v>4.04818201065063</v>
+        <v>4.04818248748779</v>
       </c>
       <c r="H170" t="n">
         <v>82611</v>
@@ -5328,7 +5328,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041625976562</v>
       </c>
       <c r="H171" t="n">
         <v>41159</v>
@@ -5357,7 +5357,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00931072235107</v>
+        <v>4.00931024551392</v>
       </c>
       <c r="H172" t="n">
         <v>285790</v>
@@ -5386,7 +5386,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97043871879578</v>
+        <v>3.97043895721436</v>
       </c>
       <c r="H173" t="n">
         <v>185702</v>
@@ -5502,7 +5502,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152275085449</v>
+        <v>4.03152227401733</v>
       </c>
       <c r="H177" t="n">
         <v>101079</v>
@@ -5531,7 +5531,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156719207764</v>
+        <v>3.93156743049622</v>
       </c>
       <c r="H178" t="n">
         <v>219724</v>
@@ -5560,7 +5560,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="n">
-        <v>3.80384731292725</v>
+        <v>3.80384755134583</v>
       </c>
       <c r="H179" t="n">
         <v>313330</v>
@@ -5589,7 +5589,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="n">
-        <v>3.72888112068176</v>
+        <v>3.7288806438446</v>
       </c>
       <c r="H180" t="n">
         <v>212138</v>
@@ -5618,7 +5618,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H181" t="n">
         <v>119833</v>
@@ -5647,7 +5647,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502118110657</v>
+        <v>3.66502046585083</v>
       </c>
       <c r="H182" t="n">
         <v>239810</v>
@@ -5676,7 +5676,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280819892883</v>
+        <v>3.64280843734741</v>
       </c>
       <c r="H183" t="n">
         <v>201842</v>
@@ -5734,7 +5734,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H185" t="n">
         <v>173655</v>
@@ -5792,7 +5792,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332835197449</v>
       </c>
       <c r="H187" t="n">
         <v>126621</v>
@@ -5821,7 +5821,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000959396362</v>
+        <v>3.6900098323822</v>
       </c>
       <c r="H188" t="n">
         <v>175447</v>
@@ -5850,7 +5850,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224384307861</v>
+        <v>3.66224408149719</v>
       </c>
       <c r="H189" t="n">
         <v>128416</v>
@@ -5879,7 +5879,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H190" t="n">
         <v>329741</v>
@@ -5908,7 +5908,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276399612427</v>
+        <v>3.74276351928711</v>
       </c>
       <c r="H191" t="n">
         <v>217887</v>
@@ -5937,7 +5937,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055101394653</v>
       </c>
       <c r="H192" t="n">
         <v>103333</v>
@@ -5966,7 +5966,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332835197449</v>
       </c>
       <c r="H193" t="n">
         <v>167998</v>
@@ -5995,7 +5995,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="n">
-        <v>3.67612648010254</v>
+        <v>3.67612743377686</v>
       </c>
       <c r="H194" t="n">
         <v>104706</v>
@@ -6053,7 +6053,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113806724548</v>
+        <v>3.65113830566406</v>
       </c>
       <c r="H196" t="n">
         <v>131242</v>
@@ -6082,7 +6082,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502118110657</v>
+        <v>3.66502046585083</v>
       </c>
       <c r="H197" t="n">
         <v>103315</v>
@@ -6140,7 +6140,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H199" t="n">
         <v>78308</v>
@@ -6169,7 +6169,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.598384141922</v>
+        <v>3.59838366508484</v>
       </c>
       <c r="H200" t="n">
         <v>58597</v>
@@ -6343,7 +6343,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660123825073</v>
+        <v>3.85660171508789</v>
       </c>
       <c r="H206" t="n">
         <v>205793</v>
@@ -6401,7 +6401,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156719207764</v>
+        <v>3.93156743049622</v>
       </c>
       <c r="H208" t="n">
         <v>48406</v>
@@ -6430,7 +6430,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488642692566</v>
+        <v>3.96488547325134</v>
       </c>
       <c r="H209" t="n">
         <v>111598</v>
@@ -6459,7 +6459,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.9482274055481</v>
+        <v>3.94822645187378</v>
       </c>
       <c r="H210" t="n">
         <v>182662</v>
@@ -6488,7 +6488,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="n">
-        <v>3.97321534156799</v>
+        <v>3.97321486473083</v>
       </c>
       <c r="H211" t="n">
         <v>118720</v>
@@ -6604,7 +6604,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215448379517</v>
+        <v>3.86215496063232</v>
       </c>
       <c r="H215" t="n">
         <v>72762</v>
@@ -6633,7 +6633,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="n">
-        <v>3.80384731292725</v>
+        <v>3.80384755134583</v>
       </c>
       <c r="H216" t="n">
         <v>114679</v>
@@ -6662,7 +6662,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438873291016</v>
+        <v>3.83438920974731</v>
       </c>
       <c r="H217" t="n">
         <v>51844</v>
@@ -6691,7 +6691,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608156204224</v>
+        <v>3.77608251571655</v>
       </c>
       <c r="H218" t="n">
         <v>66379</v>
@@ -6720,7 +6720,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107092857361</v>
+        <v>3.80107045173645</v>
       </c>
       <c r="H219" t="n">
         <v>60701</v>
@@ -6778,7 +6778,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996467590332</v>
+        <v>3.78996515274048</v>
       </c>
       <c r="H221" t="n">
         <v>103648</v>
@@ -6807,7 +6807,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="n">
-        <v>3.75942301750183</v>
+        <v>3.75942254066467</v>
       </c>
       <c r="H222" t="n">
         <v>147024</v>
@@ -6836,7 +6836,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="n">
-        <v>3.67612648010254</v>
+        <v>3.67612743377686</v>
       </c>
       <c r="H223" t="n">
         <v>123488</v>
@@ -6865,7 +6865,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.71222114562988</v>
+        <v>3.7122220993042</v>
       </c>
       <c r="H224" t="n">
         <v>81364</v>
@@ -6894,7 +6894,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504316329956</v>
       </c>
       <c r="H225" t="n">
         <v>166084</v>
@@ -6923,7 +6923,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059640884399</v>
+        <v>3.62059593200684</v>
       </c>
       <c r="H226" t="n">
         <v>137226</v>
@@ -7039,7 +7039,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51508760452271</v>
+        <v>3.51508784294128</v>
       </c>
       <c r="H230" t="n">
         <v>158535</v>
@@ -7068,7 +7068,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007601737976</v>
+        <v>3.54007625579834</v>
       </c>
       <c r="H231" t="n">
         <v>177686</v>
@@ -7097,7 +7097,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897047996521</v>
+        <v>3.52897071838379</v>
       </c>
       <c r="H232" t="n">
         <v>53802</v>
@@ -7126,7 +7126,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400404930115</v>
+        <v>3.45400357246399</v>
       </c>
       <c r="H233" t="n">
         <v>47034</v>
@@ -7184,7 +7184,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.4762167930603</v>
+        <v>3.47621655464172</v>
       </c>
       <c r="H235" t="n">
         <v>66245</v>
@@ -7213,7 +7213,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.503981590271</v>
+        <v>3.50398230552673</v>
       </c>
       <c r="H236" t="n">
         <v>83410</v>
@@ -7242,7 +7242,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.4984290599823</v>
+        <v>3.49842882156372</v>
       </c>
       <c r="H237" t="n">
         <v>59122</v>
@@ -7271,7 +7271,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174757957458</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H238" t="n">
         <v>110615</v>
@@ -7300,7 +7300,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732304573059</v>
+        <v>3.48732256889343</v>
       </c>
       <c r="H239" t="n">
         <v>109337</v>
@@ -7387,7 +7387,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050609588623</v>
+        <v>3.82050657272339</v>
       </c>
       <c r="H242" t="n">
         <v>97760</v>
@@ -7445,7 +7445,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="n">
-        <v>3.80384731292725</v>
+        <v>3.80384755134583</v>
       </c>
       <c r="H244" t="n">
         <v>97891</v>
@@ -7474,7 +7474,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.83161211013794</v>
+        <v>3.83161282539368</v>
       </c>
       <c r="H245" t="n">
         <v>194032</v>
@@ -7503,7 +7503,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608156204224</v>
+        <v>3.77608251571655</v>
       </c>
       <c r="H246" t="n">
         <v>85390</v>
@@ -7532,7 +7532,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.83161211013794</v>
+        <v>3.83161282539368</v>
       </c>
       <c r="H247" t="n">
         <v>110497</v>
@@ -7561,7 +7561,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.83161211013794</v>
+        <v>3.83161282539368</v>
       </c>
       <c r="H248" t="n">
         <v>128189</v>
@@ -7590,7 +7590,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.92879033088684</v>
+        <v>3.92879128456116</v>
       </c>
       <c r="H249" t="n">
         <v>130892</v>
@@ -7619,7 +7619,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102601051331</v>
+        <v>3.90102648735046</v>
       </c>
       <c r="H250" t="n">
         <v>108027</v>
@@ -7677,7 +7677,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820423126221</v>
       </c>
       <c r="H252" t="n">
         <v>83758</v>
@@ -7735,7 +7735,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041625976562</v>
       </c>
       <c r="H254" t="n">
         <v>67846</v>
@@ -7764,7 +7764,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599315643311</v>
+        <v>3.97599220275879</v>
       </c>
       <c r="H255" t="n">
         <v>60629</v>
@@ -7793,7 +7793,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820423126221</v>
       </c>
       <c r="H256" t="n">
         <v>75406</v>
@@ -7822,7 +7822,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041625976562</v>
       </c>
       <c r="H257" t="n">
         <v>46248</v>
@@ -7909,7 +7909,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G260" t="n">
-        <v>4.12592506408691</v>
+        <v>4.12592458724976</v>
       </c>
       <c r="H260" t="n">
         <v>139723</v>
@@ -7967,7 +7967,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="n">
-        <v>4.18145608901978</v>
+        <v>4.18145561218262</v>
       </c>
       <c r="H262" t="n">
         <v>80545</v>
@@ -7996,7 +7996,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="n">
-        <v>4.13147735595703</v>
+        <v>4.13147783279419</v>
       </c>
       <c r="H263" t="n">
         <v>266804</v>
@@ -8025,7 +8025,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="n">
-        <v>4.18700838088989</v>
+        <v>4.18700885772705</v>
       </c>
       <c r="H264" t="n">
         <v>111880</v>
@@ -8054,7 +8054,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533729553223</v>
+        <v>4.19533777236938</v>
       </c>
       <c r="H265" t="n">
         <v>229274</v>
@@ -8083,7 +8083,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G266" t="n">
-        <v>4.12592506408691</v>
+        <v>4.12592458724976</v>
       </c>
       <c r="H266" t="n">
         <v>117768</v>
@@ -8199,7 +8199,7 @@
         <v>6.90720701217651</v>
       </c>
       <c r="G270" t="n">
-        <v>4.12592506408691</v>
+        <v>4.12592458724976</v>
       </c>
       <c r="H270" t="n">
         <v>113318</v>
@@ -8228,7 +8228,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="n">
-        <v>4.12037134170532</v>
+        <v>4.12037086486816</v>
       </c>
       <c r="H271" t="n">
         <v>96672</v>
@@ -8315,7 +8315,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484079360962</v>
+        <v>4.06484127044678</v>
       </c>
       <c r="H274" t="n">
         <v>94442</v>
@@ -8373,7 +8373,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490912437439</v>
+        <v>3.91490864753723</v>
       </c>
       <c r="H276" t="n">
         <v>229142</v>
@@ -8402,7 +8402,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377922058105</v>
+        <v>3.95377969741821</v>
       </c>
       <c r="H277" t="n">
         <v>45852</v>
@@ -8431,7 +8431,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438873291016</v>
+        <v>3.83438920974731</v>
       </c>
       <c r="H278" t="n">
         <v>128544</v>
@@ -8460,7 +8460,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86493039131165</v>
+        <v>3.8649308681488</v>
       </c>
       <c r="H279" t="n">
         <v>46654</v>
@@ -8489,7 +8489,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933318138123</v>
+        <v>3.95933270454407</v>
       </c>
       <c r="H280" t="n">
         <v>55134</v>
@@ -8518,7 +8518,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="n">
-        <v>3.88714289665222</v>
+        <v>3.88714385032654</v>
       </c>
       <c r="H281" t="n">
         <v>68408</v>
@@ -8576,7 +8576,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H283" t="n">
         <v>61425</v>
@@ -8605,7 +8605,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H284" t="n">
         <v>71158</v>
@@ -8634,7 +8634,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599315643311</v>
+        <v>3.97599220275879</v>
       </c>
       <c r="H285" t="n">
         <v>110096</v>
@@ -8663,7 +8663,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594633102417</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H286" t="n">
         <v>167527</v>
@@ -8808,7 +8808,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="n">
-        <v>4.15646648406982</v>
+        <v>4.15646600723267</v>
       </c>
       <c r="H291" t="n">
         <v>112554</v>
@@ -8895,7 +8895,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317066192627</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H294" t="n">
         <v>80824</v>
@@ -8924,7 +8924,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="n">
-        <v>4.12037134170532</v>
+        <v>4.12037086486816</v>
       </c>
       <c r="H295" t="n">
         <v>85676</v>
@@ -8953,7 +8953,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.12037134170532</v>
+        <v>4.12037086486816</v>
       </c>
       <c r="H296" t="n">
         <v>91728</v>
@@ -8982,7 +8982,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594633102417</v>
+        <v>4.07594680786133</v>
       </c>
       <c r="H297" t="n">
         <v>154156</v>
@@ -9098,7 +9098,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="n">
-        <v>4.33138847351074</v>
+        <v>4.33138799667358</v>
       </c>
       <c r="H301" t="n">
         <v>316194</v>
@@ -9214,7 +9214,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="n">
-        <v>4.33138847351074</v>
+        <v>4.33138799667358</v>
       </c>
       <c r="H305" t="n">
         <v>76534</v>
@@ -9330,7 +9330,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="n">
-        <v>4.22310304641724</v>
+        <v>4.22310352325439</v>
       </c>
       <c r="H309" t="n">
         <v>193013</v>
@@ -9388,7 +9388,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917501449585</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H311" t="n">
         <v>289755</v>
@@ -9417,7 +9417,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134307861328</v>
+        <v>4.43134355545044</v>
       </c>
       <c r="H312" t="n">
         <v>618378</v>
@@ -9446,7 +9446,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188497543335</v>
+        <v>4.46188545227051</v>
       </c>
       <c r="H313" t="n">
         <v>304602</v>
@@ -9533,7 +9533,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H316" t="n">
         <v>367674</v>
@@ -9562,7 +9562,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351066589355</v>
       </c>
       <c r="H317" t="n">
         <v>460310</v>
@@ -9649,7 +9649,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461668014526</v>
+        <v>4.56461715698242</v>
       </c>
       <c r="H320" t="n">
         <v>231935</v>
@@ -9678,7 +9678,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H321" t="n">
         <v>141204</v>
@@ -9707,7 +9707,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351066589355</v>
       </c>
       <c r="H322" t="n">
         <v>95409</v>
@@ -9794,7 +9794,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H325" t="n">
         <v>265003</v>
@@ -9823,7 +9823,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G326" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H326" t="n">
         <v>200779</v>
@@ -9852,7 +9852,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G327" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798011779785</v>
       </c>
       <c r="H327" t="n">
         <v>109257</v>
@@ -9881,7 +9881,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132038116455</v>
+        <v>4.48132085800171</v>
       </c>
       <c r="H328" t="n">
         <v>165632</v>
@@ -9910,7 +9910,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="n">
-        <v>4.45910882949829</v>
+        <v>4.45910835266113</v>
       </c>
       <c r="H329" t="n">
         <v>312941</v>
@@ -9997,7 +9997,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691902160645</v>
       </c>
       <c r="H332" t="n">
         <v>206018</v>
@@ -10026,7 +10026,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691854476929</v>
+        <v>4.38691902160645</v>
       </c>
       <c r="H333" t="n">
         <v>196119</v>
@@ -10084,7 +10084,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362319946289</v>
+        <v>4.30362272262573</v>
       </c>
       <c r="H335" t="n">
         <v>151724</v>
@@ -10229,7 +10229,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461668014526</v>
+        <v>4.56461715698242</v>
       </c>
       <c r="H340" t="n">
         <v>221386</v>
@@ -10258,7 +10258,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793472290039</v>
+        <v>4.59793519973755</v>
       </c>
       <c r="H341" t="n">
         <v>312555</v>
@@ -10287,7 +10287,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127593994141</v>
+        <v>4.58127641677856</v>
       </c>
       <c r="H342" t="n">
         <v>62152</v>
@@ -10374,7 +10374,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346622467041</v>
+        <v>4.65346527099609</v>
       </c>
       <c r="H345" t="n">
         <v>177286</v>
@@ -10432,7 +10432,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="n">
-        <v>4.77563333511353</v>
+        <v>4.77563285827637</v>
       </c>
       <c r="H347" t="n">
         <v>352359</v>
@@ -10461,7 +10461,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895090103149</v>
+        <v>4.80895137786865</v>
       </c>
       <c r="H348" t="n">
         <v>235964</v>
@@ -10519,7 +10519,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.87836456298828</v>
+        <v>4.87836503982544</v>
       </c>
       <c r="H350" t="n">
         <v>140823</v>
@@ -10577,7 +10577,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010231018066</v>
+        <v>4.72010183334351</v>
       </c>
       <c r="H352" t="n">
         <v>291161</v>
@@ -10664,7 +10664,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423698425293</v>
       </c>
       <c r="H355" t="n">
         <v>294138</v>
@@ -10693,7 +10693,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865699768066</v>
+        <v>4.73865747451782</v>
       </c>
       <c r="H356" t="n">
         <v>265806</v>
@@ -10809,7 +10809,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865699768066</v>
+        <v>4.73865747451782</v>
       </c>
       <c r="H360" t="n">
         <v>158526</v>
@@ -10867,7 +10867,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="n">
-        <v>4.74726295471191</v>
+        <v>4.74726343154907</v>
       </c>
       <c r="H362" t="n">
         <v>171165</v>
@@ -10925,7 +10925,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83618402481079</v>
+        <v>4.83618450164795</v>
       </c>
       <c r="H364" t="n">
         <v>244646</v>
@@ -10983,7 +10983,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H366" t="n">
         <v>77359</v>
@@ -11070,7 +11070,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H369" t="n">
         <v>54213</v>
@@ -11099,7 +11099,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="n">
-        <v>4.74726295471191</v>
+        <v>4.74726343154907</v>
       </c>
       <c r="H370" t="n">
         <v>118123</v>
@@ -11128,7 +11128,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="n">
-        <v>4.76734256744385</v>
+        <v>4.76734209060669</v>
       </c>
       <c r="H371" t="n">
         <v>59047</v>
@@ -11157,7 +11157,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586843490601</v>
       </c>
       <c r="H372" t="n">
         <v>148350</v>
@@ -11244,7 +11244,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965774536133</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H375" t="n">
         <v>145512</v>
@@ -11273,7 +11273,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965774536133</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H376" t="n">
         <v>155173</v>
@@ -11302,7 +11302,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="n">
-        <v>4.60384130477905</v>
+        <v>4.60384082794189</v>
       </c>
       <c r="H377" t="n">
         <v>76641</v>
@@ -11331,7 +11331,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="n">
-        <v>4.58376169204712</v>
+        <v>4.58376216888428</v>
       </c>
       <c r="H378" t="n">
         <v>95959</v>
@@ -11418,7 +11418,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655168533325</v>
+        <v>4.56655216217041</v>
       </c>
       <c r="H381" t="n">
         <v>80390</v>
@@ -11447,7 +11447,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="n">
-        <v>4.49770879745483</v>
+        <v>4.49770927429199</v>
       </c>
       <c r="H382" t="n">
         <v>132223</v>
@@ -11476,7 +11476,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37436628341675</v>
+        <v>4.37436580657959</v>
       </c>
       <c r="H383" t="n">
         <v>168248</v>
@@ -11505,7 +11505,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42312908172607</v>
+        <v>4.42312955856323</v>
       </c>
       <c r="H384" t="n">
         <v>90869</v>
@@ -11534,7 +11534,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="n">
-        <v>4.45468235015869</v>
+        <v>4.45468187332153</v>
       </c>
       <c r="H385" t="n">
         <v>104028</v>
@@ -11563,7 +11563,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786706924438</v>
+        <v>4.53786754608154</v>
       </c>
       <c r="H386" t="n">
         <v>105901</v>
@@ -11592,7 +11592,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507755279541</v>
+        <v>4.55507802963257</v>
       </c>
       <c r="H387" t="n">
         <v>112131</v>
@@ -11621,7 +11621,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476100921631</v>
+        <v>4.47476148605347</v>
       </c>
       <c r="H388" t="n">
         <v>139029</v>
@@ -11679,7 +11679,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="n">
-        <v>4.64686822891235</v>
+        <v>4.6468677520752</v>
       </c>
       <c r="H390" t="n">
         <v>163263</v>
@@ -11766,7 +11766,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586843490601</v>
       </c>
       <c r="H393" t="n">
         <v>165524</v>
@@ -11795,7 +11795,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="n">
-        <v>4.76447343826294</v>
+        <v>4.7644739151001</v>
       </c>
       <c r="H394" t="n">
         <v>83113</v>
@@ -11853,7 +11853,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H396" t="n">
         <v>93726</v>
@@ -11969,7 +11969,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="n">
-        <v>4.80750036239624</v>
+        <v>4.80749988555908</v>
       </c>
       <c r="H400" t="n">
         <v>175291</v>
@@ -11998,7 +11998,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H401" t="n">
         <v>142867</v>
@@ -12056,7 +12056,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H403" t="n">
         <v>128308</v>
@@ -12172,7 +12172,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="n">
-        <v>4.71857833862305</v>
+        <v>4.71857881546021</v>
       </c>
       <c r="H407" t="n">
         <v>123210</v>
@@ -12201,7 +12201,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="n">
-        <v>4.71857833862305</v>
+        <v>4.71857881546021</v>
       </c>
       <c r="H408" t="n">
         <v>135862</v>
@@ -12230,7 +12230,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H409" t="n">
         <v>386315</v>
@@ -12288,7 +12288,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H411" t="n">
         <v>129788</v>
@@ -12346,7 +12346,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="n">
-        <v>4.82184219360352</v>
+        <v>4.82184171676636</v>
       </c>
       <c r="H413" t="n">
         <v>171784</v>
@@ -12375,7 +12375,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586843490601</v>
       </c>
       <c r="H414" t="n">
         <v>223989</v>
@@ -12433,7 +12433,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H416" t="n">
         <v>400107</v>
@@ -12462,7 +12462,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="n">
-        <v>4.94518566131592</v>
+        <v>4.94518518447876</v>
       </c>
       <c r="H417" t="n">
         <v>199295</v>
@@ -12549,7 +12549,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215873718262</v>
+        <v>4.90215826034546</v>
       </c>
       <c r="H420" t="n">
         <v>122570</v>
@@ -12578,7 +12578,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="n">
-        <v>4.91650104522705</v>
+        <v>4.91650056838989</v>
       </c>
       <c r="H421" t="n">
         <v>72335</v>
@@ -12636,7 +12636,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="n">
-        <v>4.91650104522705</v>
+        <v>4.91650056838989</v>
       </c>
       <c r="H423" t="n">
         <v>34375</v>
@@ -12665,7 +12665,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86199998855591</v>
+        <v>4.86200046539307</v>
       </c>
       <c r="H424" t="n">
         <v>42823</v>
@@ -12723,7 +12723,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H426" t="n">
         <v>53465</v>
@@ -12752,7 +12752,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="n">
-        <v>4.8017635345459</v>
+        <v>4.80176305770874</v>
       </c>
       <c r="H427" t="n">
         <v>143513</v>
@@ -12810,7 +12810,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="n">
-        <v>4.86199998855591</v>
+        <v>4.86200046539307</v>
       </c>
       <c r="H429" t="n">
         <v>34336</v>
@@ -12839,7 +12839,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634229660034</v>
       </c>
       <c r="H430" t="n">
         <v>81300</v>
@@ -12955,7 +12955,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.88781642913818</v>
+        <v>4.88781595230103</v>
       </c>
       <c r="H434" t="n">
         <v>180331</v>
@@ -13013,7 +13013,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G436" t="n">
-        <v>5.04844903945923</v>
+        <v>5.04844856262207</v>
       </c>
       <c r="H436" t="n">
         <v>195985</v>
@@ -13071,7 +13071,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G438" t="n">
-        <v>5.04844903945923</v>
+        <v>5.04844856262207</v>
       </c>
       <c r="H438" t="n">
         <v>182541</v>
@@ -13100,7 +13100,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G439" t="n">
-        <v>5.04844903945923</v>
+        <v>5.04844856262207</v>
       </c>
       <c r="H439" t="n">
         <v>83800</v>
@@ -13158,7 +13158,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="n">
-        <v>5.01402759552002</v>
+        <v>5.01402807235718</v>
       </c>
       <c r="H441" t="n">
         <v>64746</v>
@@ -13216,7 +13216,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H443" t="n">
         <v>69536</v>
@@ -13245,7 +13245,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255298614502</v>
+        <v>5.00255346298218</v>
       </c>
       <c r="H444" t="n">
         <v>82992</v>
@@ -13274,7 +13274,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673845291138</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H445" t="n">
         <v>104775</v>
@@ -13361,7 +13361,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="n">
-        <v>5.06279134750366</v>
+        <v>5.0627908706665</v>
       </c>
       <c r="H448" t="n">
         <v>73261</v>
@@ -13419,7 +13419,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="n">
-        <v>5.06279134750366</v>
+        <v>5.0627908706665</v>
       </c>
       <c r="H450" t="n">
         <v>80452</v>
@@ -13448,7 +13448,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713222503662</v>
+        <v>5.07713317871094</v>
       </c>
       <c r="H451" t="n">
         <v>127366</v>
@@ -13477,7 +13477,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G452" t="n">
-        <v>5.04844903945923</v>
+        <v>5.04844856262207</v>
       </c>
       <c r="H452" t="n">
         <v>67707</v>
@@ -13506,7 +13506,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="n">
-        <v>4.96813249588013</v>
+        <v>4.96813297271729</v>
       </c>
       <c r="H453" t="n">
         <v>121584</v>
@@ -13622,7 +13622,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="n">
-        <v>5.16318607330322</v>
+        <v>5.16318655014038</v>
       </c>
       <c r="H457" t="n">
         <v>184063</v>
@@ -13651,7 +13651,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923992156982</v>
+        <v>5.24923896789551</v>
       </c>
       <c r="H458" t="n">
         <v>199889</v>
@@ -13680,7 +13680,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H459" t="n">
         <v>352083</v>
@@ -13709,7 +13709,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H460" t="n">
         <v>197490</v>
@@ -13738,7 +13738,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871494293213</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="n">
         <v>90087</v>
@@ -13767,7 +13767,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="n">
-        <v>5.27792358398438</v>
+        <v>5.27792310714722</v>
       </c>
       <c r="H462" t="n">
         <v>293930</v>
@@ -13796,7 +13796,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="n">
-        <v>5.27505540847778</v>
+        <v>5.27505493164062</v>
       </c>
       <c r="H463" t="n">
         <v>137784</v>
@@ -13825,7 +13825,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397695541382</v>
+        <v>5.36397647857666</v>
       </c>
       <c r="H464" t="n">
         <v>416344</v>
@@ -13912,7 +13912,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="n">
-        <v>5.30947637557983</v>
+        <v>5.30947685241699</v>
       </c>
       <c r="H467" t="n">
         <v>337168</v>
@@ -13941,7 +13941,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118743896484</v>
+        <v>5.38118839263916</v>
       </c>
       <c r="H468" t="n">
         <v>235300</v>
@@ -13970,7 +13970,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="n">
-        <v>5.54755687713623</v>
+        <v>5.54755735397339</v>
       </c>
       <c r="H469" t="n">
         <v>346414</v>
@@ -13999,7 +13999,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384765625</v>
+        <v>5.69384717941284</v>
       </c>
       <c r="H470" t="n">
         <v>1020120</v>
@@ -14028,7 +14028,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818901062012</v>
+        <v>5.70819044113159</v>
       </c>
       <c r="H471" t="n">
         <v>456989</v>
@@ -14057,7 +14057,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="n">
-        <v>5.98356056213379</v>
+        <v>5.98355960845947</v>
       </c>
       <c r="H472" t="n">
         <v>839604</v>
@@ -14086,7 +14086,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208642959595</v>
+        <v>5.97208595275879</v>
       </c>
       <c r="H473" t="n">
         <v>582524</v>
@@ -14144,7 +14144,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90898084640503</v>
+        <v>5.90898036956787</v>
       </c>
       <c r="H475" t="n">
         <v>361115</v>
@@ -14202,7 +14202,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292699813843</v>
+        <v>5.82292652130127</v>
       </c>
       <c r="H477" t="n">
         <v>320356</v>
@@ -14231,7 +14231,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90898084640503</v>
+        <v>5.90898036956787</v>
       </c>
       <c r="H478" t="n">
         <v>447808</v>
@@ -14260,7 +14260,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555776596069</v>
+        <v>5.76555824279785</v>
       </c>
       <c r="H479" t="n">
         <v>231042</v>
@@ -14289,7 +14289,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="n">
-        <v>5.68237352371216</v>
+        <v>5.682373046875</v>
       </c>
       <c r="H480" t="n">
         <v>236079</v>
@@ -14434,7 +14434,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061182022095</v>
+        <v>5.96061134338379</v>
       </c>
       <c r="H485" t="n">
         <v>214159</v>
@@ -14463,7 +14463,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287635803223</v>
+        <v>6.17287588119507</v>
       </c>
       <c r="H486" t="n">
         <v>406962</v>
@@ -14492,7 +14492,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H487" t="n">
         <v>223944</v>
@@ -14521,7 +14521,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="n">
-        <v>6.10977029800415</v>
+        <v>6.10977077484131</v>
       </c>
       <c r="H488" t="n">
         <v>152139</v>
@@ -14550,7 +14550,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="n">
-        <v>6.20729684829712</v>
+        <v>6.20729732513428</v>
       </c>
       <c r="H489" t="n">
         <v>210356</v>
@@ -14608,7 +14608,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="n">
-        <v>6.19008684158325</v>
+        <v>6.19008731842041</v>
       </c>
       <c r="H491" t="n">
         <v>234121</v>
@@ -14724,7 +14724,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H495" t="n">
         <v>110811</v>
@@ -14753,7 +14753,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="n">
-        <v>6.13271760940552</v>
+        <v>6.13271808624268</v>
       </c>
       <c r="H496" t="n">
         <v>108347</v>
@@ -14811,7 +14811,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36792945861816</v>
+        <v>6.36793041229248</v>
       </c>
       <c r="H498" t="n">
         <v>358977</v>
@@ -14840,7 +14840,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645580291748</v>
+        <v>6.35645627975464</v>
       </c>
       <c r="H499" t="n">
         <v>283557</v>
@@ -14869,7 +14869,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="n">
-        <v>6.48266744613647</v>
+        <v>6.48266696929932</v>
       </c>
       <c r="H500" t="n">
         <v>169190</v>
@@ -14898,7 +14898,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="n">
-        <v>6.48266744613647</v>
+        <v>6.48266696929932</v>
       </c>
       <c r="H501" t="n">
         <v>258499</v>
@@ -14956,7 +14956,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="n">
-        <v>6.25319147109985</v>
+        <v>6.25319194793701</v>
       </c>
       <c r="H503" t="n">
         <v>365311</v>
@@ -14985,7 +14985,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734844207764</v>
+        <v>5.85734796524048</v>
       </c>
       <c r="H504" t="n">
         <v>968569</v>
@@ -15014,7 +15014,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="n">
-        <v>5.62213659286499</v>
+        <v>5.62213563919067</v>
       </c>
       <c r="H505" t="n">
         <v>589679</v>
@@ -15043,7 +15043,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476640701294</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H506" t="n">
         <v>358726</v>
@@ -15101,7 +15101,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.48158264160156</v>
+        <v>5.48158311843872</v>
       </c>
       <c r="H508" t="n">
         <v>285423</v>
@@ -15159,7 +15159,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="n">
-        <v>5.61353063583374</v>
+        <v>5.61353015899658</v>
       </c>
       <c r="H510" t="n">
         <v>217678</v>
@@ -15188,7 +15188,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034639358521</v>
+        <v>5.53034591674805</v>
       </c>
       <c r="H511" t="n">
         <v>118130</v>
@@ -15217,7 +15217,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460861206055</v>
+        <v>5.52460908889771</v>
       </c>
       <c r="H512" t="n">
         <v>137903</v>
@@ -15246,7 +15246,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476640701294</v>
+        <v>5.5647668838501</v>
       </c>
       <c r="H513" t="n">
         <v>146003</v>
@@ -15275,7 +15275,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.65082025527954</v>
+        <v>5.65082120895386</v>
       </c>
       <c r="H514" t="n">
         <v>122075</v>
@@ -15304,7 +15304,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.6565580368042</v>
+        <v>5.65655755996704</v>
       </c>
       <c r="H515" t="n">
         <v>86233</v>
@@ -15333,7 +15333,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818901062012</v>
+        <v>5.70819044113159</v>
       </c>
       <c r="H516" t="n">
         <v>147363</v>
@@ -15420,7 +15420,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903053283691</v>
+        <v>5.55903100967407</v>
       </c>
       <c r="H519" t="n">
         <v>232788</v>
@@ -15478,7 +15478,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345197677612</v>
+        <v>5.59345245361328</v>
       </c>
       <c r="H521" t="n">
         <v>134956</v>
@@ -15507,7 +15507,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H522" t="n">
         <v>131888</v>
@@ -15652,7 +15652,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H527" t="n">
         <v>178839</v>
@@ -15710,7 +15710,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871494293213</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="n">
         <v>108597</v>
@@ -15768,7 +15768,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.46150398254395</v>
+        <v>5.4615044593811</v>
       </c>
       <c r="H531" t="n">
         <v>150985</v>
@@ -15797,7 +15797,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="n">
-        <v>5.31234550476074</v>
+        <v>5.3123459815979</v>
       </c>
       <c r="H532" t="n">
         <v>243466</v>
@@ -15855,7 +15855,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="n">
-        <v>5.26645040512085</v>
+        <v>5.26645088195801</v>
       </c>
       <c r="H534" t="n">
         <v>82474</v>
@@ -15884,7 +15884,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171194076538</v>
+        <v>5.15171241760254</v>
       </c>
       <c r="H535" t="n">
         <v>131851</v>
@@ -16058,7 +16058,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="n">
-        <v>4.70423650741577</v>
+        <v>4.70423698425293</v>
       </c>
       <c r="H541" t="n">
         <v>193365</v>
@@ -16087,7 +16087,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="n">
-        <v>4.49770879745483</v>
+        <v>4.49770927429199</v>
       </c>
       <c r="H542" t="n">
         <v>312675</v>
@@ -16116,7 +16116,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439430236816</v>
+        <v>4.74439477920532</v>
       </c>
       <c r="H543" t="n">
         <v>179153</v>
@@ -16174,7 +16174,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="n">
-        <v>4.82471132278442</v>
+        <v>4.82471084594727</v>
       </c>
       <c r="H545" t="n">
         <v>123266</v>
@@ -16203,7 +16203,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849967956543</v>
+        <v>4.69849920272827</v>
       </c>
       <c r="H546" t="n">
         <v>190634</v>
@@ -16232,7 +16232,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H547" t="n">
         <v>100189</v>
@@ -16348,7 +16348,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="n">
-        <v>4.58949899673462</v>
+        <v>4.58949851989746</v>
       </c>
       <c r="H551" t="n">
         <v>187834</v>
@@ -16464,7 +16464,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="n">
-        <v>4.31986570358276</v>
+        <v>4.31986618041992</v>
       </c>
       <c r="H555" t="n">
         <v>182195</v>
@@ -16609,7 +16609,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="n">
-        <v>4.39444494247437</v>
+        <v>4.39444446563721</v>
       </c>
       <c r="H560" t="n">
         <v>218932</v>
@@ -16638,7 +16638,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="n">
-        <v>4.33937168121338</v>
+        <v>4.33937120437622</v>
       </c>
       <c r="H561" t="n">
         <v>283553</v>
@@ -16696,7 +16696,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="n">
-        <v>4.25676012039185</v>
+        <v>4.25675964355469</v>
       </c>
       <c r="H563" t="n">
         <v>136013</v>
@@ -16725,7 +16725,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430730819702</v>
+        <v>4.21430683135986</v>
       </c>
       <c r="H564" t="n">
         <v>433130</v>
@@ -16754,7 +16754,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="n">
-        <v>4.14775991439819</v>
+        <v>4.14775943756104</v>
       </c>
       <c r="H565" t="n">
         <v>280816</v>
@@ -16783,7 +16783,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732439041138</v>
+        <v>4.32732343673706</v>
       </c>
       <c r="H566" t="n">
         <v>299973</v>
@@ -16870,7 +16870,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="n">
-        <v>4.14259672164917</v>
+        <v>4.14259719848633</v>
       </c>
       <c r="H569" t="n">
         <v>904299</v>
@@ -16899,7 +16899,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449653625488</v>
+        <v>4.04449605941772</v>
       </c>
       <c r="H570" t="n">
         <v>630273</v>
@@ -17189,7 +17189,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628082275391</v>
+        <v>4.83628034591675</v>
       </c>
       <c r="H580" t="n">
         <v>645972</v>
@@ -17218,7 +17218,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493427276611</v>
+        <v>4.79493379592896</v>
       </c>
       <c r="H581" t="n">
         <v>391338</v>
@@ -17247,7 +17247,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="n">
-        <v>4.87454080581665</v>
+        <v>4.87454128265381</v>
       </c>
       <c r="H582" t="n">
         <v>274280</v>
@@ -17276,7 +17276,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H583" t="n">
         <v>201360</v>
@@ -17305,7 +17305,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086639404297</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H584" t="n">
         <v>346291</v>
@@ -17334,7 +17334,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.85479307174683</v>
+        <v>4.85479402542114</v>
       </c>
       <c r="H585" t="n">
         <v>306793</v>
@@ -17363,7 +17363,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H586" t="n">
         <v>659396</v>
@@ -17421,7 +17421,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84924030303955</v>
+        <v>4.84923982620239</v>
       </c>
       <c r="H588" t="n">
         <v>752626</v>
@@ -17450,7 +17450,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813238143921</v>
       </c>
       <c r="H589" t="n">
         <v>513903</v>
@@ -17508,7 +17508,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344795227051</v>
       </c>
       <c r="H591" t="n">
         <v>329652</v>
@@ -17595,7 +17595,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>4.79061460494995</v>
+        <v>4.79061412811279</v>
       </c>
       <c r="H594" t="n">
         <v>309631</v>
@@ -17624,7 +17624,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="n">
-        <v>4.84862279891968</v>
+        <v>4.84862327575684</v>
       </c>
       <c r="H595" t="n">
         <v>284775</v>
@@ -17682,7 +17682,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430265426636</v>
+        <v>4.84430313110352</v>
       </c>
       <c r="H597" t="n">
         <v>183693</v>
@@ -17769,7 +17769,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813238143921</v>
       </c>
       <c r="H600" t="n">
         <v>417093</v>
@@ -17914,7 +17914,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.8035740852356</v>
+        <v>4.80357360839844</v>
       </c>
       <c r="H605" t="n">
         <v>567119</v>
@@ -17943,7 +17943,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086639404297</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H606" t="n">
         <v>413652</v>
@@ -17972,7 +17972,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="n">
-        <v>4.59684228897095</v>
+        <v>4.59684181213379</v>
       </c>
       <c r="H607" t="n">
         <v>613084</v>
@@ -18030,7 +18030,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>4.61288690567017</v>
+        <v>4.61288642883301</v>
       </c>
       <c r="H609" t="n">
         <v>290843</v>
@@ -18059,7 +18059,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.56660413742065</v>
+        <v>4.56660461425781</v>
       </c>
       <c r="H610" t="n">
         <v>544954</v>
@@ -18088,7 +18088,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="n">
-        <v>4.54870748519897</v>
+        <v>4.54870796203613</v>
       </c>
       <c r="H611" t="n">
         <v>252215</v>
@@ -18146,7 +18146,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.39072847366333</v>
+        <v>4.39072799682617</v>
       </c>
       <c r="H613" t="n">
         <v>283150</v>
@@ -18233,7 +18233,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H616" t="n">
         <v>397528</v>
@@ -18262,7 +18262,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="n">
-        <v>4.46786737442017</v>
+        <v>4.46786689758301</v>
       </c>
       <c r="H617" t="n">
         <v>480697</v>
@@ -18378,7 +18378,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.51908683776855</v>
+        <v>4.5190863609314</v>
       </c>
       <c r="H621" t="n">
         <v>353015</v>
@@ -18407,7 +18407,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="n">
-        <v>4.42528629302979</v>
+        <v>4.42528581619263</v>
       </c>
       <c r="H622" t="n">
         <v>399766</v>
@@ -18436,7 +18436,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="n">
-        <v>4.70257139205933</v>
+        <v>4.70257091522217</v>
       </c>
       <c r="H623" t="n">
         <v>331589</v>
@@ -18465,7 +18465,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="n">
-        <v>4.81534337997437</v>
+        <v>4.81534290313721</v>
       </c>
       <c r="H624" t="n">
         <v>341465</v>
@@ -18581,7 +18581,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>4.62495803833008</v>
+        <v>4.62495851516724</v>
       </c>
       <c r="H628" t="n">
         <v>345226</v>
@@ -18639,7 +18639,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="n">
-        <v>4.59311628341675</v>
+        <v>4.59311676025391</v>
       </c>
       <c r="H630" t="n">
         <v>231415</v>
@@ -18668,7 +18668,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>4.57918643951416</v>
+        <v>4.579185962677</v>
       </c>
       <c r="H631" t="n">
         <v>301522</v>
@@ -18697,7 +18697,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.68996810913086</v>
+        <v>4.6899676322937</v>
       </c>
       <c r="H632" t="n">
         <v>571701</v>
@@ -18726,7 +18726,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="n">
-        <v>4.62164115905762</v>
+        <v>4.62164163589478</v>
       </c>
       <c r="H633" t="n">
         <v>306266</v>
@@ -18900,7 +18900,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.61832475662231</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H639" t="n">
         <v>277774</v>
@@ -18958,7 +18958,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60174036026001</v>
+        <v>4.60173988342285</v>
       </c>
       <c r="H641" t="n">
         <v>160144</v>
@@ -18987,7 +18987,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.7430362701416</v>
+        <v>4.74303722381592</v>
       </c>
       <c r="H642" t="n">
         <v>298183</v>
@@ -19074,7 +19074,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>4.65679979324341</v>
+        <v>4.65679931640625</v>
       </c>
       <c r="H645" t="n">
         <v>247525</v>
@@ -19132,7 +19132,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="n">
-        <v>4.68930435180664</v>
+        <v>4.68930387496948</v>
       </c>
       <c r="H647" t="n">
         <v>52795</v>
@@ -19161,7 +19161,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711515426636</v>
+        <v>4.72711563110352</v>
       </c>
       <c r="H648" t="n">
         <v>124423</v>
@@ -19190,7 +19190,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094722747803</v>
+        <v>4.76094770431519</v>
       </c>
       <c r="H649" t="n">
         <v>201117</v>
@@ -19219,7 +19219,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="n">
-        <v>4.81600666046143</v>
+        <v>4.81600618362427</v>
       </c>
       <c r="H650" t="n">
         <v>89728</v>
@@ -19248,7 +19248,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637186050415</v>
+        <v>4.87637233734131</v>
       </c>
       <c r="H651" t="n">
         <v>272806</v>
@@ -19335,7 +19335,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="n">
-        <v>4.81666994094849</v>
+        <v>4.81666946411133</v>
       </c>
       <c r="H654" t="n">
         <v>190438</v>
@@ -19364,7 +19364,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="n">
-        <v>4.6873140335083</v>
+        <v>4.68731355667114</v>
       </c>
       <c r="H655" t="n">
         <v>115106</v>
@@ -19393,7 +19393,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="n">
-        <v>4.80937242507935</v>
+        <v>4.8093729019165</v>
       </c>
       <c r="H656" t="n">
         <v>107726</v>
@@ -19538,7 +19538,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="n">
-        <v>4.74369955062866</v>
+        <v>4.74370002746582</v>
       </c>
       <c r="H661" t="n">
         <v>212597</v>
@@ -19625,7 +19625,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.61832475662231</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H664" t="n">
         <v>65498</v>
@@ -19683,7 +19683,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="n">
-        <v>4.58316564559937</v>
+        <v>4.58316612243652</v>
       </c>
       <c r="H666" t="n">
         <v>106623</v>
@@ -19712,7 +19712,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="n">
-        <v>4.50621604919434</v>
+        <v>4.50621652603149</v>
       </c>
       <c r="H667" t="n">
         <v>158816</v>
@@ -19828,7 +19828,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="n">
-        <v>4.32445526123047</v>
+        <v>4.32445573806763</v>
       </c>
       <c r="H671" t="n">
         <v>112382</v>
@@ -19857,7 +19857,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.36027717590332</v>
+        <v>4.36027669906616</v>
       </c>
       <c r="H672" t="n">
         <v>84392</v>
@@ -19973,7 +19973,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H676" t="n">
         <v>76513</v>
@@ -20002,7 +20002,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H677" t="n">
         <v>51262</v>
@@ -20205,7 +20205,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>4.36160326004028</v>
+        <v>4.36160278320312</v>
       </c>
       <c r="H684" t="n">
         <v>132078</v>
@@ -20292,7 +20292,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H687" t="n">
         <v>314279</v>
@@ -20321,7 +20321,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>4.35165309906006</v>
+        <v>4.3516526222229</v>
       </c>
       <c r="H688" t="n">
         <v>96748</v>
@@ -20379,7 +20379,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="n">
-        <v>4.32710886001587</v>
+        <v>4.32710838317871</v>
       </c>
       <c r="H690" t="n">
         <v>84784</v>
@@ -20437,7 +20437,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="n">
-        <v>4.61567115783691</v>
+        <v>4.61567068099976</v>
       </c>
       <c r="H692" t="n">
         <v>604065</v>
@@ -20466,7 +20466,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="n">
-        <v>4.50090932846069</v>
+        <v>4.50090885162354</v>
       </c>
       <c r="H693" t="n">
         <v>229013</v>
@@ -20495,7 +20495,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="n">
-        <v>4.49029588699341</v>
+        <v>4.49029636383057</v>
       </c>
       <c r="H694" t="n">
         <v>128251</v>
@@ -20524,7 +20524,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739500045776</v>
+        <v>4.53739452362061</v>
       </c>
       <c r="H695" t="n">
         <v>120232</v>
@@ -20553,7 +20553,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392908096313</v>
+        <v>4.56392860412598</v>
       </c>
       <c r="H696" t="n">
         <v>221443</v>
@@ -20582,7 +20582,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392908096313</v>
+        <v>4.56392860412598</v>
       </c>
       <c r="H697" t="n">
         <v>91471</v>
@@ -20669,7 +20669,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="n">
-        <v>4.47039413452148</v>
+        <v>4.47039461135864</v>
       </c>
       <c r="H700" t="n">
         <v>88666</v>
@@ -20727,7 +20727,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966325759888</v>
+        <v>4.34966278076172</v>
       </c>
       <c r="H702" t="n">
         <v>84918</v>
@@ -20756,7 +20756,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010894775391</v>
+        <v>4.26010942459106</v>
       </c>
       <c r="H703" t="n">
         <v>227597</v>
@@ -20785,7 +20785,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H704" t="n">
         <v>120717</v>
@@ -20872,7 +20872,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="n">
-        <v>4.0737042427063</v>
+        <v>4.07370471954346</v>
       </c>
       <c r="H707" t="n">
         <v>234307</v>
@@ -20901,7 +20901,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>4.05645704269409</v>
+        <v>4.05645751953125</v>
       </c>
       <c r="H708" t="n">
         <v>219320</v>
@@ -20959,7 +20959,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312169075012</v>
+        <v>3.92312121391296</v>
       </c>
       <c r="H710" t="n">
         <v>281423</v>
@@ -21017,7 +21017,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.84749817848206</v>
+        <v>3.84749794006348</v>
       </c>
       <c r="H712" t="n">
         <v>189134</v>
@@ -21046,7 +21046,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648721694946</v>
       </c>
       <c r="H713" t="n">
         <v>179781</v>
@@ -21075,7 +21075,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="n">
-        <v>3.95297241210938</v>
+        <v>3.95297288894653</v>
       </c>
       <c r="H714" t="n">
         <v>119203</v>
@@ -21162,7 +21162,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026945114136</v>
+        <v>3.96026992797852</v>
       </c>
       <c r="H717" t="n">
         <v>50070</v>
@@ -21597,7 +21597,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="n">
-        <v>4.07635736465454</v>
+        <v>4.0763578414917</v>
       </c>
       <c r="H732" t="n">
         <v>64043</v>
@@ -21626,7 +21626,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04716968536377</v>
+        <v>4.04717016220093</v>
       </c>
       <c r="H733" t="n">
         <v>135061</v>
@@ -21655,7 +21655,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="n">
-        <v>3.9821605682373</v>
+        <v>3.98216009140015</v>
       </c>
       <c r="H734" t="n">
         <v>67397</v>
@@ -21713,7 +21713,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>3.98945760726929</v>
+        <v>3.98945713043213</v>
       </c>
       <c r="H736" t="n">
         <v>29837</v>
@@ -21829,7 +21829,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184401512146</v>
+        <v>3.9118435382843</v>
       </c>
       <c r="H740" t="n">
         <v>58482</v>
@@ -21887,7 +21887,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503175735474</v>
+        <v>4.07503128051758</v>
       </c>
       <c r="H742" t="n">
         <v>132743</v>
@@ -21916,7 +21916,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="n">
-        <v>4.08630800247192</v>
+        <v>4.08630847930908</v>
       </c>
       <c r="H743" t="n">
         <v>40025</v>
@@ -21945,7 +21945,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05115032196045</v>
+        <v>4.05114936828613</v>
       </c>
       <c r="H744" t="n">
         <v>56164</v>
@@ -22090,7 +22090,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88729953765869</v>
+        <v>3.88730025291443</v>
       </c>
       <c r="H749" t="n">
         <v>111448</v>
@@ -22148,7 +22148,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.8581120967865</v>
+        <v>3.85811138153076</v>
       </c>
       <c r="H751" t="n">
         <v>63514</v>
@@ -22177,7 +22177,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361698150635</v>
+        <v>3.82361745834351</v>
       </c>
       <c r="H752" t="n">
         <v>90932</v>
@@ -22322,7 +22322,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.64848923683167</v>
+        <v>3.64848947525024</v>
       </c>
       <c r="H757" t="n">
         <v>182909</v>
@@ -22351,7 +22351,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.57949995994568</v>
+        <v>3.5794997215271</v>
       </c>
       <c r="H758" t="n">
         <v>159867</v>
@@ -22409,7 +22409,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205411911011</v>
+        <v>3.60205459594727</v>
       </c>
       <c r="H760" t="n">
         <v>153511</v>
@@ -22438,7 +22438,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="n">
-        <v>3.5974109172821</v>
+        <v>3.59741044044495</v>
       </c>
       <c r="H761" t="n">
         <v>232177</v>
@@ -22467,7 +22467,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="n">
-        <v>3.52046036720276</v>
+        <v>3.52046084403992</v>
       </c>
       <c r="H762" t="n">
         <v>171756</v>
@@ -22496,7 +22496,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57021260261536</v>
+        <v>3.57021284103394</v>
       </c>
       <c r="H763" t="n">
         <v>158919</v>
@@ -22641,7 +22641,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.91980481147766</v>
+        <v>3.91980457305908</v>
       </c>
       <c r="H768" t="n">
         <v>165370</v>
@@ -22757,7 +22757,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479497909546</v>
+        <v>3.85479521751404</v>
       </c>
       <c r="H772" t="n">
         <v>112700</v>
@@ -22786,7 +22786,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="n">
-        <v>3.8156566619873</v>
+        <v>3.81565618515015</v>
       </c>
       <c r="H773" t="n">
         <v>122612</v>
@@ -22815,7 +22815,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.8985767364502</v>
+        <v>3.89857721328735</v>
       </c>
       <c r="H774" t="n">
         <v>192350</v>
@@ -22873,7 +22873,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91516137123108</v>
+        <v>3.91516041755676</v>
       </c>
       <c r="H776" t="n">
         <v>169016</v>
@@ -22902,7 +22902,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="n">
-        <v>3.87204241752625</v>
+        <v>3.8720428943634</v>
       </c>
       <c r="H777" t="n">
         <v>97481</v>
@@ -22931,7 +22931,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025121688843</v>
+        <v>3.83025074005127</v>
       </c>
       <c r="H778" t="n">
         <v>123544</v>
@@ -22989,7 +22989,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.9728729724884</v>
+        <v>3.97287392616272</v>
       </c>
       <c r="H780" t="n">
         <v>142710</v>
@@ -23018,7 +23018,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.0790114402771</v>
+        <v>4.07901096343994</v>
       </c>
       <c r="H781" t="n">
         <v>71053</v>
@@ -23105,7 +23105,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937711715698</v>
+        <v>4.13937759399414</v>
       </c>
       <c r="H784" t="n">
         <v>119629</v>
@@ -23192,7 +23192,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947584152222</v>
+        <v>4.11947631835938</v>
       </c>
       <c r="H787" t="n">
         <v>103841</v>
@@ -23250,7 +23250,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>4.09294271469116</v>
+        <v>4.092942237854</v>
       </c>
       <c r="H789" t="n">
         <v>263354</v>
@@ -23308,7 +23308,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>3.91118025779724</v>
+        <v>3.91118121147156</v>
       </c>
       <c r="H791" t="n">
         <v>263702</v>
@@ -23395,7 +23395,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680448532104</v>
+        <v>3.98680424690247</v>
       </c>
       <c r="H794" t="n">
         <v>129600</v>
@@ -23482,7 +23482,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="n">
-        <v>4.07304096221924</v>
+        <v>4.07304048538208</v>
       </c>
       <c r="H797" t="n">
         <v>221439</v>
@@ -23511,7 +23511,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="n">
-        <v>4.07038736343384</v>
+        <v>4.070387840271</v>
       </c>
       <c r="H798" t="n">
         <v>126559</v>
@@ -23540,7 +23540,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>4.06640768051147</v>
+        <v>4.06640720367432</v>
       </c>
       <c r="H799" t="n">
         <v>186549</v>
@@ -23627,7 +23627,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13407039642334</v>
+        <v>4.13406991958618</v>
       </c>
       <c r="H802" t="n">
         <v>101135</v>
@@ -23743,7 +23743,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="n">
-        <v>4.18448543548584</v>
+        <v>4.184485912323</v>
       </c>
       <c r="H806" t="n">
         <v>224566</v>
@@ -23830,7 +23830,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="n">
-        <v>4.41334533691406</v>
+        <v>4.41334581375122</v>
       </c>
       <c r="H809" t="n">
         <v>326833</v>
@@ -23859,7 +23859,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848478317261</v>
       </c>
       <c r="H810" t="n">
         <v>124688</v>
@@ -23888,7 +23888,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H811" t="n">
         <v>155654</v>
@@ -23917,7 +23917,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531742095947</v>
+        <v>4.28531694412231</v>
       </c>
       <c r="H812" t="n">
         <v>82775</v>
@@ -23946,7 +23946,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="n">
-        <v>4.29195022583008</v>
+        <v>4.29195070266724</v>
       </c>
       <c r="H813" t="n">
         <v>178878</v>
@@ -23975,7 +23975,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609813690186</v>
+        <v>4.39609861373901</v>
       </c>
       <c r="H814" t="n">
         <v>210612</v>
@@ -24033,7 +24033,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="n">
-        <v>4.44717741012573</v>
+        <v>4.44717693328857</v>
       </c>
       <c r="H816" t="n">
         <v>261217</v>
@@ -24120,7 +24120,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="n">
-        <v>4.4100284576416</v>
+        <v>4.41002893447876</v>
       </c>
       <c r="H819" t="n">
         <v>92629</v>
@@ -24149,7 +24149,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069269180298</v>
+        <v>4.41069221496582</v>
       </c>
       <c r="H820" t="n">
         <v>59197</v>
@@ -24178,7 +24178,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="n">
-        <v>4.34899997711182</v>
+        <v>4.34899950027466</v>
       </c>
       <c r="H821" t="n">
         <v>196343</v>
@@ -24236,7 +24236,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408958435059</v>
+        <v>4.26408910751343</v>
       </c>
       <c r="H823" t="n">
         <v>139907</v>
@@ -24265,7 +24265,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848478317261</v>
       </c>
       <c r="H824" t="n">
         <v>64218</v>
@@ -24294,7 +24294,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>4.30521726608276</v>
+        <v>4.30521774291992</v>
       </c>
       <c r="H825" t="n">
         <v>258387</v>
@@ -24439,7 +24439,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.39808797836304</v>
+        <v>4.3980884552002</v>
       </c>
       <c r="H830" t="n">
         <v>151188</v>
@@ -24468,7 +24468,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H831" t="n">
         <v>94151</v>
@@ -24526,7 +24526,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.29858446121216</v>
+        <v>4.298583984375</v>
       </c>
       <c r="H833" t="n">
         <v>159721</v>
@@ -24613,7 +24613,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>4.40472221374512</v>
+        <v>4.40472173690796</v>
       </c>
       <c r="H836" t="n">
         <v>75933</v>
@@ -25048,7 +25048,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49095869064331</v>
+        <v>4.49095916748047</v>
       </c>
       <c r="H851" t="n">
         <v>276372</v>
@@ -25077,7 +25077,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838558197021</v>
+        <v>4.33838605880737</v>
       </c>
       <c r="H852" t="n">
         <v>375070</v>
@@ -25135,7 +25135,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H854" t="n">
         <v>242614</v>
@@ -25280,7 +25280,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52835035324097</v>
+        <v>4.52834987640381</v>
       </c>
       <c r="H859" t="n">
         <v>185427</v>
@@ -25309,7 +25309,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140827178955</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H860" t="n">
         <v>106622</v>
@@ -25367,7 +25367,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>4.47093868255615</v>
+        <v>4.47093820571899</v>
       </c>
       <c r="H862" t="n">
         <v>89495</v>
@@ -25454,7 +25454,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>4.42788028717041</v>
+        <v>4.42787981033325</v>
       </c>
       <c r="H865" t="n">
         <v>162526</v>
@@ -25483,7 +25483,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611581802368</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H866" t="n">
         <v>83940</v>
@@ -25512,7 +25512,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611581802368</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H867" t="n">
         <v>45354</v>
@@ -25541,7 +25541,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G868" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H868" t="n">
         <v>132081</v>
@@ -25570,7 +25570,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H869" t="n">
         <v>55460</v>
@@ -25599,7 +25599,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H870" t="n">
         <v>116258</v>
@@ -25657,7 +25657,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H872" t="n">
         <v>120308</v>
@@ -25686,7 +25686,7 @@
         <v>6.25</v>
       </c>
       <c r="G873" t="n">
-        <v>4.48529148101807</v>
+        <v>4.48529195785522</v>
       </c>
       <c r="H873" t="n">
         <v>112876</v>
@@ -25715,7 +25715,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G874" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H874" t="n">
         <v>63208</v>
@@ -25773,7 +25773,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H876" t="n">
         <v>88374</v>
@@ -25860,7 +25860,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H879" t="n">
         <v>122037</v>
@@ -25918,7 +25918,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G881" t="n">
-        <v>4.21976232528687</v>
+        <v>4.21976184844971</v>
       </c>
       <c r="H881" t="n">
         <v>283379</v>
@@ -25947,7 +25947,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>4.21976232528687</v>
+        <v>4.21976184844971</v>
       </c>
       <c r="H882" t="n">
         <v>170721</v>
@@ -26005,7 +26005,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20540952682495</v>
+        <v>4.20541000366211</v>
       </c>
       <c r="H884" t="n">
         <v>123323</v>
@@ -26034,7 +26034,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670297622681</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H885" t="n">
         <v>158011</v>
@@ -26092,7 +26092,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670297622681</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H887" t="n">
         <v>184524</v>
@@ -26121,7 +26121,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G888" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H888" t="n">
         <v>214075</v>
@@ -26150,7 +26150,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G889" t="n">
-        <v>4.18387937545776</v>
+        <v>4.18387985229492</v>
       </c>
       <c r="H889" t="n">
         <v>265335</v>
@@ -26237,7 +26237,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H892" t="n">
         <v>101125</v>
@@ -26266,7 +26266,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H893" t="n">
         <v>56380</v>
@@ -26295,7 +26295,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H894" t="n">
         <v>80568</v>
@@ -26324,7 +26324,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H895" t="n">
         <v>65595</v>
@@ -26353,7 +26353,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H896" t="n">
         <v>44767</v>
@@ -26382,7 +26382,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H897" t="n">
         <v>139790</v>
@@ -26411,7 +26411,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G898" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H898" t="n">
         <v>120359</v>
@@ -26469,7 +26469,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611581802368</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H900" t="n">
         <v>82729</v>
@@ -26556,7 +26556,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H903" t="n">
         <v>213241</v>
@@ -26614,7 +26614,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H905" t="n">
         <v>82085</v>
@@ -26643,7 +26643,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G906" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H906" t="n">
         <v>211543</v>
@@ -26701,7 +26701,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411560058594</v>
+        <v>4.23411512374878</v>
       </c>
       <c r="H908" t="n">
         <v>58990</v>
@@ -26730,7 +26730,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129199981689</v>
+        <v>4.24129152297974</v>
       </c>
       <c r="H909" t="n">
         <v>98629</v>
@@ -26788,7 +26788,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670297622681</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H911" t="n">
         <v>121403</v>
@@ -26817,7 +26817,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H912" t="n">
         <v>162300</v>
@@ -26846,7 +26846,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776210784912</v>
+        <v>4.09776258468628</v>
       </c>
       <c r="H913" t="n">
         <v>213477</v>
@@ -26875,7 +26875,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>4.05470371246338</v>
+        <v>4.05470323562622</v>
       </c>
       <c r="H914" t="n">
         <v>180985</v>
@@ -26933,7 +26933,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H916" t="n">
         <v>220296</v>
@@ -26991,7 +26991,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529158592224</v>
       </c>
       <c r="H918" t="n">
         <v>243157</v>
@@ -27020,7 +27020,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246822357178</v>
+        <v>3.88246870040894</v>
       </c>
       <c r="H919" t="n">
         <v>159908</v>
@@ -27194,7 +27194,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H925" t="n">
         <v>84785</v>
@@ -27223,7 +27223,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H926" t="n">
         <v>73998</v>
@@ -27281,7 +27281,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199815750122</v>
+        <v>3.7819972038269</v>
       </c>
       <c r="H928" t="n">
         <v>42652</v>
@@ -27310,7 +27310,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352759361267</v>
+        <v>3.80352711677551</v>
       </c>
       <c r="H929" t="n">
         <v>184164</v>
@@ -27368,7 +27368,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940982818604</v>
+        <v>3.83940935134888</v>
       </c>
       <c r="H931" t="n">
         <v>200773</v>
@@ -27426,7 +27426,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529158592224</v>
       </c>
       <c r="H933" t="n">
         <v>162454</v>
@@ -27455,7 +27455,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H934" t="n">
         <v>135055</v>
@@ -27484,7 +27484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399742126465</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H935" t="n">
         <v>187953</v>
@@ -27571,7 +27571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G938" t="n">
-        <v>4.01882076263428</v>
+        <v>4.01882123947144</v>
       </c>
       <c r="H938" t="n">
         <v>122493</v>
@@ -27600,7 +27600,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>4.04035043716431</v>
+        <v>4.04035091400146</v>
       </c>
       <c r="H939" t="n">
         <v>113996</v>
@@ -27629,7 +27629,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H940" t="n">
         <v>133834</v>
@@ -27658,7 +27658,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599811553955</v>
       </c>
       <c r="H941" t="n">
         <v>174524</v>
@@ -27687,7 +27687,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>4.01882076263428</v>
+        <v>4.01882123947144</v>
       </c>
       <c r="H942" t="n">
         <v>254675</v>
@@ -27716,7 +27716,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H943" t="n">
         <v>182425</v>
@@ -27803,7 +27803,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599763870239</v>
+        <v>4.02599811553955</v>
       </c>
       <c r="H946" t="n">
         <v>137576</v>
@@ -27832,7 +27832,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H947" t="n">
         <v>147938</v>
@@ -27890,7 +27890,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H949" t="n">
         <v>84704</v>
@@ -28006,7 +28006,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H953" t="n">
         <v>89858</v>
@@ -28064,7 +28064,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H955" t="n">
         <v>198731</v>
@@ -28151,7 +28151,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G958" t="n">
-        <v>4.01882076263428</v>
+        <v>4.01882123947144</v>
       </c>
       <c r="H958" t="n">
         <v>65548</v>
@@ -28238,7 +28238,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H961" t="n">
         <v>76598</v>
@@ -28325,7 +28325,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670297622681</v>
+        <v>4.17670392990112</v>
       </c>
       <c r="H964" t="n">
         <v>184280</v>
@@ -28354,7 +28354,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G965" t="n">
-        <v>4.11929178237915</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H965" t="n">
         <v>251112</v>
@@ -28470,7 +28470,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H969" t="n">
         <v>66738</v>
@@ -28586,7 +28586,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799785614014</v>
+        <v>4.14799737930298</v>
       </c>
       <c r="H973" t="n">
         <v>63185</v>
@@ -28615,7 +28615,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H974" t="n">
         <v>38961</v>
@@ -28644,7 +28644,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H975" t="n">
         <v>83904</v>
@@ -28673,7 +28673,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G976" t="n">
-        <v>4.13364458084106</v>
+        <v>4.13364505767822</v>
       </c>
       <c r="H976" t="n">
         <v>91697</v>
@@ -28702,7 +28702,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G977" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H977" t="n">
         <v>27675</v>
@@ -28731,7 +28731,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H978" t="n">
         <v>130439</v>
@@ -28818,7 +28818,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H981" t="n">
         <v>169971</v>
@@ -28876,7 +28876,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H983" t="n">
         <v>94635</v>
@@ -28934,7 +28934,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H985" t="n">
         <v>162590</v>
@@ -28992,7 +28992,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H987" t="n">
         <v>69784</v>
@@ -29050,7 +29050,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611581802368</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H989" t="n">
         <v>138068</v>
@@ -29108,7 +29108,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305694580078</v>
+        <v>4.31305646896362</v>
       </c>
       <c r="H991" t="n">
         <v>83600</v>
@@ -29166,7 +29166,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870271682739</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H993" t="n">
         <v>45492</v>
@@ -29195,7 +29195,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H994" t="n">
         <v>199251</v>
@@ -29253,7 +29253,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G996" t="n">
-        <v>4.57858514785767</v>
+        <v>4.57858562469482</v>
       </c>
       <c r="H996" t="n">
         <v>495439</v>
@@ -29456,7 +29456,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1003" t="n">
         <v>114564</v>
@@ -29543,7 +29543,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H1006" t="n">
         <v>100264</v>
@@ -29572,7 +29572,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1007" t="n">
         <v>129466</v>
@@ -29601,7 +29601,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1008" t="n">
         <v>90036</v>
@@ -29659,7 +29659,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H1010" t="n">
         <v>69927</v>
@@ -29688,7 +29688,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1011" t="n">
         <v>143195</v>
@@ -29717,7 +29717,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1012" t="n">
         <v>242811</v>
@@ -29746,7 +29746,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1013" t="n">
         <v>63163</v>
@@ -29833,7 +29833,7 @@
         <v>6.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.48529148101807</v>
+        <v>4.48529195785522</v>
       </c>
       <c r="H1016" t="n">
         <v>85906</v>
@@ -29891,7 +29891,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1018" t="n">
         <v>130838</v>
@@ -29949,7 +29949,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1020" t="n">
         <v>147871</v>
@@ -29978,7 +29978,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H1021" t="n">
         <v>186708</v>
@@ -30007,7 +30007,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1022" t="n">
         <v>89368</v>
@@ -30094,7 +30094,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1025" t="n">
         <v>56890</v>
@@ -30152,7 +30152,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1027" t="n">
         <v>46343</v>
@@ -30239,7 +30239,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.42788028717041</v>
+        <v>4.42787981033325</v>
       </c>
       <c r="H1030" t="n">
         <v>139658</v>
@@ -30326,7 +30326,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.41352653503418</v>
+        <v>4.41352701187134</v>
       </c>
       <c r="H1033" t="n">
         <v>135419</v>
@@ -30355,7 +30355,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.47093868255615</v>
+        <v>4.47093820571899</v>
       </c>
       <c r="H1034" t="n">
         <v>100848</v>
@@ -30413,7 +30413,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H1036" t="n">
         <v>110854</v>
@@ -30471,7 +30471,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870271682739</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H1038" t="n">
         <v>161115</v>
@@ -30500,7 +30500,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.39199733734131</v>
+        <v>4.39199686050415</v>
       </c>
       <c r="H1039" t="n">
         <v>164564</v>
@@ -30529,7 +30529,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.42788028717041</v>
+        <v>4.42787981033325</v>
       </c>
       <c r="H1040" t="n">
         <v>165842</v>
@@ -30587,7 +30587,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1042" t="n">
         <v>180031</v>
@@ -30616,7 +30616,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1043" t="n">
         <v>133272</v>
@@ -30674,7 +30674,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.50682067871094</v>
+        <v>4.5068211555481</v>
       </c>
       <c r="H1045" t="n">
         <v>167360</v>
@@ -30703,7 +30703,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1046" t="n">
         <v>128636</v>
@@ -30761,7 +30761,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270362854004</v>
+        <v>4.54270315170288</v>
       </c>
       <c r="H1048" t="n">
         <v>201438</v>
@@ -30819,7 +30819,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140827178955</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H1050" t="n">
         <v>112242</v>
@@ -30877,7 +30877,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.47811460494995</v>
+        <v>4.47811555862427</v>
       </c>
       <c r="H1052" t="n">
         <v>122474</v>
@@ -30935,7 +30935,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.11929178237915</v>
+        <v>4.11929130554199</v>
       </c>
       <c r="H1054" t="n">
         <v>386195</v>
@@ -31022,7 +31022,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399742126465</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H1057" t="n">
         <v>651281</v>
@@ -31051,7 +31051,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H1058" t="n">
         <v>494611</v>
@@ -31167,7 +31167,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.7891743183136</v>
+        <v>3.78917479515076</v>
       </c>
       <c r="H1062" t="n">
         <v>297718</v>
@@ -31254,7 +31254,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.25811576843262</v>
+        <v>3.25811553001404</v>
       </c>
       <c r="H1065" t="n">
         <v>364873</v>
@@ -31312,7 +31312,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605710983276</v>
+        <v>2.66605734825134</v>
       </c>
       <c r="H1067" t="n">
         <v>497765</v>
@@ -31399,7 +31399,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1070" t="n">
         <v>294654</v>
@@ -31428,7 +31428,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.55482220649719</v>
+        <v>2.55482196807861</v>
       </c>
       <c r="H1071" t="n">
         <v>262610</v>
@@ -31515,7 +31515,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446888923645</v>
+        <v>2.78446912765503</v>
       </c>
       <c r="H1074" t="n">
         <v>219271</v>
@@ -31631,7 +31631,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.59070444107056</v>
+        <v>2.59070420265198</v>
       </c>
       <c r="H1078" t="n">
         <v>244939</v>
@@ -31660,7 +31660,7 @@
         <v>3.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.69117498397827</v>
+        <v>2.69117474555969</v>
       </c>
       <c r="H1079" t="n">
         <v>342391</v>
@@ -31689,7 +31689,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70552778244019</v>
+        <v>2.70552802085876</v>
       </c>
       <c r="H1080" t="n">
         <v>292596</v>
@@ -31718,7 +31718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.65529274940491</v>
+        <v>2.65529251098633</v>
       </c>
       <c r="H1081" t="n">
         <v>184630</v>
@@ -31747,7 +31747,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505747795105</v>
+        <v>2.60505723953247</v>
       </c>
       <c r="H1082" t="n">
         <v>90176</v>
@@ -31776,7 +31776,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1083" t="n">
         <v>180927</v>
@@ -31834,7 +31834,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.66964530944824</v>
+        <v>2.66964554786682</v>
       </c>
       <c r="H1085" t="n">
         <v>172170</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.66964530944824</v>
+        <v>2.66964554786682</v>
       </c>
       <c r="H1087" t="n">
         <v>189444</v>
@@ -31979,7 +31979,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.56917476654053</v>
+        <v>2.56917500495911</v>
       </c>
       <c r="H1090" t="n">
         <v>129379</v>
@@ -32037,7 +32037,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.5368812084198</v>
+        <v>2.53688097000122</v>
       </c>
       <c r="H1092" t="n">
         <v>202956</v>
@@ -32095,7 +32095,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1094" t="n">
         <v>108032</v>
@@ -32182,7 +32182,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1097" t="n">
         <v>180573</v>
@@ -32211,7 +32211,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.55482220649719</v>
+        <v>2.55482196807861</v>
       </c>
       <c r="H1098" t="n">
         <v>251103</v>
@@ -32269,7 +32269,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.52252793312073</v>
+        <v>2.52252817153931</v>
       </c>
       <c r="H1100" t="n">
         <v>128839</v>
@@ -32298,7 +32298,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1101" t="n">
         <v>130098</v>
@@ -32356,7 +32356,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1103" t="n">
         <v>141432</v>
@@ -32414,7 +32414,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1105" t="n">
         <v>149130</v>
@@ -32443,7 +32443,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.3682336807251</v>
+        <v>2.36823391914368</v>
       </c>
       <c r="H1106" t="n">
         <v>326150</v>
@@ -32472,7 +32472,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952808380127</v>
+        <v>2.33952784538269</v>
       </c>
       <c r="H1107" t="n">
         <v>248569</v>
@@ -32530,7 +32530,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.3179988861084</v>
+        <v>2.31799864768982</v>
       </c>
       <c r="H1109" t="n">
         <v>123243</v>
@@ -32646,7 +32646,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652847290039</v>
+        <v>2.15652823448181</v>
       </c>
       <c r="H1113" t="n">
         <v>565839</v>
@@ -32675,7 +32675,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805790901184</v>
+        <v>2.17805767059326</v>
       </c>
       <c r="H1114" t="n">
         <v>231502</v>
@@ -32791,7 +32791,7 @@
         <v>3.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.33235144615173</v>
+        <v>2.33235168457031</v>
       </c>
       <c r="H1118" t="n">
         <v>359504</v>
@@ -32820,7 +32820,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876324653625</v>
+        <v>2.32876348495483</v>
       </c>
       <c r="H1119" t="n">
         <v>437387</v>
@@ -32849,7 +32849,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.35388112068176</v>
+        <v>2.35388088226318</v>
       </c>
       <c r="H1120" t="n">
         <v>213833</v>
@@ -32907,7 +32907,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893949508667</v>
+        <v>2.51893973350525</v>
       </c>
       <c r="H1122" t="n">
         <v>477229</v>
@@ -32994,7 +32994,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81317496299744</v>
+        <v>2.81317520141602</v>
       </c>
       <c r="H1125" t="n">
         <v>470004</v>
@@ -33023,7 +33023,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.70552778244019</v>
+        <v>2.70552802085876</v>
       </c>
       <c r="H1126" t="n">
         <v>328129</v>
@@ -33052,7 +33052,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1127" t="n">
         <v>417942</v>
@@ -33081,7 +33081,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1128" t="n">
         <v>348708</v>
@@ -33110,7 +33110,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.45793986320496</v>
+        <v>2.45793962478638</v>
       </c>
       <c r="H1129" t="n">
         <v>299279</v>
@@ -33139,7 +33139,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1130" t="n">
         <v>287875</v>
@@ -33168,7 +33168,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1131" t="n">
         <v>310297</v>
@@ -33197,7 +33197,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1132" t="n">
         <v>158723</v>
@@ -33226,7 +33226,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1133" t="n">
         <v>139107</v>
@@ -33255,7 +33255,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1134" t="n">
         <v>433647</v>
@@ -33284,7 +33284,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1135" t="n">
         <v>163840</v>
@@ -33371,7 +33371,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.43999862670898</v>
+        <v>2.43999886512756</v>
       </c>
       <c r="H1138" t="n">
         <v>136490</v>
@@ -33458,7 +33458,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1141" t="n">
         <v>205219</v>
@@ -33516,7 +33516,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.50817489624023</v>
+        <v>2.50817513465881</v>
       </c>
       <c r="H1143" t="n">
         <v>142239</v>
@@ -33574,7 +33574,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1145" t="n">
         <v>166481</v>
@@ -33806,7 +33806,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893949508667</v>
+        <v>2.51893973350525</v>
       </c>
       <c r="H1153" t="n">
         <v>399041</v>
@@ -33835,7 +33835,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.56917476654053</v>
+        <v>2.56917500495911</v>
       </c>
       <c r="H1154" t="n">
         <v>549822</v>
@@ -33864,7 +33864,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.59075331687927</v>
+        <v>2.59075355529785</v>
       </c>
       <c r="H1155" t="n">
         <v>491686</v>
@@ -33893,7 +33893,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.56775856018066</v>
+        <v>2.56775879859924</v>
       </c>
       <c r="H1156" t="n">
         <v>258924</v>
@@ -33980,7 +33980,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.42978954315186</v>
+        <v>2.42978978157043</v>
       </c>
       <c r="H1159" t="n">
         <v>156578</v>
@@ -34009,7 +34009,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1160" t="n">
         <v>154215</v>
@@ -34096,7 +34096,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.34164237976074</v>
+        <v>2.34164261817932</v>
       </c>
       <c r="H1163" t="n">
         <v>191513</v>
@@ -34154,7 +34154,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1165" t="n">
         <v>148256</v>
@@ -34183,7 +34183,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.42978954315186</v>
+        <v>2.42978978157043</v>
       </c>
       <c r="H1166" t="n">
         <v>110673</v>
@@ -34212,7 +34212,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.42978954315186</v>
+        <v>2.42978978157043</v>
       </c>
       <c r="H1167" t="n">
         <v>125258</v>
@@ -34270,7 +34270,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1169" t="n">
         <v>159196</v>
@@ -34473,7 +34473,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230205535889</v>
       </c>
       <c r="H1176" t="n">
         <v>101920</v>
@@ -34531,7 +34531,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1178" t="n">
         <v>133721</v>
@@ -34589,7 +34589,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1180" t="n">
         <v>124034</v>
@@ -34647,7 +34647,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.33781003952026</v>
+        <v>2.33780980110168</v>
       </c>
       <c r="H1182" t="n">
         <v>87462</v>
@@ -34676,7 +34676,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631278038025</v>
+        <v>2.32631254196167</v>
       </c>
       <c r="H1183" t="n">
         <v>40688</v>
@@ -34705,7 +34705,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.33781003952026</v>
+        <v>2.33780980110168</v>
       </c>
       <c r="H1184" t="n">
         <v>68132</v>
@@ -34821,7 +34821,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.4259569644928</v>
+        <v>2.42595672607422</v>
       </c>
       <c r="H1188" t="n">
         <v>131356</v>
@@ -34879,7 +34879,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1190" t="n">
         <v>56050</v>
@@ -34908,7 +34908,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.35314011573792</v>
+        <v>2.35313963890076</v>
       </c>
       <c r="H1191" t="n">
         <v>58041</v>
@@ -34937,7 +34937,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1192" t="n">
         <v>36038</v>
@@ -34966,7 +34966,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1193" t="n">
         <v>38721</v>
@@ -34995,7 +34995,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1194" t="n">
         <v>286707</v>
@@ -35024,7 +35024,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1195" t="n">
         <v>112081</v>
@@ -35082,7 +35082,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1197" t="n">
         <v>56722</v>
@@ -35169,7 +35169,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715012550354</v>
+        <v>2.30715036392212</v>
       </c>
       <c r="H1200" t="n">
         <v>254056</v>
@@ -35314,7 +35314,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.28798770904541</v>
+        <v>2.28798794746399</v>
       </c>
       <c r="H1205" t="n">
         <v>82329</v>
@@ -35430,7 +35430,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.35314011573792</v>
+        <v>2.35313963890076</v>
       </c>
       <c r="H1209" t="n">
         <v>246233</v>
@@ -35459,7 +35459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1210" t="n">
         <v>130645</v>
@@ -35488,7 +35488,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.41445970535278</v>
+        <v>2.41445994377136</v>
       </c>
       <c r="H1211" t="n">
         <v>151446</v>
@@ -35517,7 +35517,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.41445970535278</v>
+        <v>2.41445994377136</v>
       </c>
       <c r="H1212" t="n">
         <v>181793</v>
@@ -35546,7 +35546,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1213" t="n">
         <v>269685</v>
@@ -35575,7 +35575,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1214" t="n">
         <v>246638</v>
@@ -35633,7 +35633,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230205535889</v>
       </c>
       <c r="H1216" t="n">
         <v>160104</v>
@@ -35720,7 +35720,7 @@
         <v>2.875</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.20367360115051</v>
+        <v>2.20367336273193</v>
       </c>
       <c r="H1219" t="n">
         <v>195479</v>
@@ -35778,7 +35778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750570297241</v>
+        <v>2.20750594139099</v>
       </c>
       <c r="H1221" t="n">
         <v>142174</v>
@@ -35836,7 +35836,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786128044128</v>
+        <v>2.10786151885986</v>
       </c>
       <c r="H1223" t="n">
         <v>329808</v>
@@ -35894,7 +35894,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.03887701034546</v>
+        <v>2.03887677192688</v>
       </c>
       <c r="H1225" t="n">
         <v>168729</v>
@@ -35952,7 +35952,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.89707541465759</v>
+        <v>1.89707517623901</v>
       </c>
       <c r="H1227" t="n">
         <v>334235</v>
@@ -36010,7 +36010,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.91240501403809</v>
+        <v>1.91240525245667</v>
       </c>
       <c r="H1229" t="n">
         <v>705511</v>
@@ -36155,7 +36155,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138976097107</v>
+        <v>1.98138999938965</v>
       </c>
       <c r="H1234" t="n">
         <v>203810</v>
@@ -36213,7 +36213,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877429008484</v>
+        <v>2.49877405166626</v>
       </c>
       <c r="H1236" t="n">
         <v>1002989</v>
@@ -36242,7 +36242,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291072845459</v>
+        <v>2.63291049003601</v>
       </c>
       <c r="H1237" t="n">
         <v>805282</v>
@@ -36300,7 +36300,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.59075331687927</v>
+        <v>2.59075355529785</v>
       </c>
       <c r="H1239" t="n">
         <v>250791</v>
@@ -36445,7 +36445,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.64440822601318</v>
+        <v>2.6444079875946</v>
       </c>
       <c r="H1244" t="n">
         <v>355424</v>
@@ -36532,7 +36532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405217170715</v>
+        <v>2.74405241012573</v>
       </c>
       <c r="H1247" t="n">
         <v>450366</v>
@@ -36561,7 +36561,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321482658386</v>
       </c>
       <c r="H1248" t="n">
         <v>269119</v>
@@ -36677,7 +36677,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68656539916992</v>
+        <v>2.68656516075134</v>
       </c>
       <c r="H1252" t="n">
         <v>485014</v>
@@ -36735,7 +36735,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.77087998390198</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1254" t="n">
         <v>119317</v>
@@ -36851,7 +36851,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1258" t="n">
         <v>858635</v>
@@ -36880,7 +36880,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1259" t="n">
         <v>561880</v>
@@ -37025,7 +37025,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1264" t="n">
         <v>1034179</v>
@@ -37141,7 +37141,7 @@
         <v>3.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.87435674667358</v>
+        <v>2.874356508255</v>
       </c>
       <c r="H1268" t="n">
         <v>163276</v>
@@ -37170,7 +37170,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.82836675643921</v>
+        <v>2.82836699485779</v>
       </c>
       <c r="H1269" t="n">
         <v>261734</v>
@@ -37286,7 +37286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.82836675643921</v>
+        <v>2.82836699485779</v>
       </c>
       <c r="H1273" t="n">
         <v>137710</v>
@@ -37373,7 +37373,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1276" t="n">
         <v>358795</v>
@@ -37576,7 +37576,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285901069641</v>
+        <v>2.86285924911499</v>
       </c>
       <c r="H1283" t="n">
         <v>574210</v>
@@ -37605,7 +37605,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620982170105</v>
+        <v>2.78620958328247</v>
       </c>
       <c r="H1284" t="n">
         <v>230927</v>
@@ -37692,7 +37692,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1287" t="n">
         <v>186106</v>
@@ -37779,7 +37779,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1290" t="n">
         <v>637732</v>
@@ -37808,7 +37808,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1291" t="n">
         <v>279807</v>
@@ -37837,7 +37837,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.77087998390198</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1292" t="n">
         <v>127030</v>
@@ -37895,7 +37895,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82070207595825</v>
+        <v>2.82070183753967</v>
       </c>
       <c r="H1294" t="n">
         <v>128387</v>
@@ -37982,7 +37982,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.93950891494751</v>
+        <v>2.93950867652893</v>
       </c>
       <c r="H1297" t="n">
         <v>163979</v>
@@ -38040,7 +38040,7 @@
         <v>4</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.06598043441772</v>
+        <v>3.06598019599915</v>
       </c>
       <c r="H1299" t="n">
         <v>272536</v>
@@ -38069,7 +38069,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1300" t="n">
         <v>831090</v>
@@ -38098,7 +38098,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849318504333</v>
+        <v>3.00849342346191</v>
       </c>
       <c r="H1301" t="n">
         <v>169875</v>
@@ -38127,7 +38127,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567609786987</v>
+        <v>2.93567633628845</v>
       </c>
       <c r="H1302" t="n">
         <v>184353</v>
@@ -38156,7 +38156,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.99699568748474</v>
+        <v>2.99699592590332</v>
       </c>
       <c r="H1303" t="n">
         <v>311894</v>
@@ -38185,7 +38185,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1304" t="n">
         <v>631921</v>
@@ -38243,7 +38243,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.92034649848938</v>
+        <v>2.9203462600708</v>
       </c>
       <c r="H1306" t="n">
         <v>122098</v>
@@ -38272,7 +38272,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1307" t="n">
         <v>163152</v>
@@ -38417,7 +38417,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.6903977394104</v>
+        <v>2.69039797782898</v>
       </c>
       <c r="H1312" t="n">
         <v>318481</v>
@@ -38533,7 +38533,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1316" t="n">
         <v>315319</v>
@@ -38591,7 +38591,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1318" t="n">
         <v>510876</v>
@@ -38736,7 +38736,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1323" t="n">
         <v>221706</v>
@@ -38794,7 +38794,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.6903977394104</v>
+        <v>2.69039797782898</v>
       </c>
       <c r="H1325" t="n">
         <v>410108</v>
@@ -38881,7 +38881,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1328" t="n">
         <v>523941</v>
@@ -38910,7 +38910,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1329" t="n">
-        <v>2.59841871261597</v>
+        <v>2.59841847419739</v>
       </c>
       <c r="H1329" t="n">
         <v>172336</v>
@@ -38997,7 +38997,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.65590524673462</v>
+        <v>2.6559054851532</v>
       </c>
       <c r="H1332" t="n">
         <v>124651</v>
@@ -39113,7 +39113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1336" t="n">
         <v>266103</v>
@@ -39171,7 +39171,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321482658386</v>
       </c>
       <c r="H1338" t="n">
         <v>283462</v>
@@ -39229,7 +39229,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1340" t="n">
         <v>294026</v>
@@ -39258,7 +39258,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1341" t="n">
         <v>108872</v>
@@ -39316,7 +39316,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.88968634605408</v>
+        <v>2.88968658447266</v>
       </c>
       <c r="H1343" t="n">
         <v>293864</v>
@@ -39374,7 +39374,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1345" t="n">
         <v>248627</v>
@@ -39432,7 +39432,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1347" t="n">
         <v>196520</v>
@@ -39490,7 +39490,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1349" t="n">
         <v>150256</v>
@@ -39548,7 +39548,7 @@
         <v>4</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.06598043441772</v>
+        <v>3.06598019599915</v>
       </c>
       <c r="H1351" t="n">
         <v>440591</v>
@@ -39693,7 +39693,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.15412735939026</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1356" t="n">
         <v>386167</v>
@@ -39780,7 +39780,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676677703857</v>
+        <v>3.27676653862</v>
       </c>
       <c r="H1359" t="n">
         <v>363222</v>
@@ -39809,7 +39809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.15795969963074</v>
+        <v>3.15795993804932</v>
       </c>
       <c r="H1360" t="n">
         <v>294112</v>
@@ -39838,7 +39838,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1361" t="n">
         <v>174283</v>
@@ -39867,7 +39867,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1362" t="n">
         <v>296147</v>
@@ -39954,7 +39954,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.14262986183167</v>
+        <v>3.14263010025024</v>
       </c>
       <c r="H1365" t="n">
         <v>207219</v>
@@ -39983,7 +39983,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.09280776977539</v>
+        <v>3.09280753135681</v>
       </c>
       <c r="H1366" t="n">
         <v>236757</v>
@@ -40215,7 +40215,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1374" t="n">
         <v>318940</v>
@@ -40360,7 +40360,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1379" t="n">
         <v>919643</v>
@@ -40389,7 +40389,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.28826427459717</v>
+        <v>3.28826403617859</v>
       </c>
       <c r="H1380" t="n">
         <v>310169</v>
@@ -40418,7 +40418,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.43389797210693</v>
+        <v>3.43389773368835</v>
       </c>
       <c r="H1381" t="n">
         <v>491076</v>
@@ -40447,7 +40447,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.5412073135376</v>
+        <v>3.54120755195618</v>
       </c>
       <c r="H1382" t="n">
         <v>720088</v>
@@ -40476,7 +40476,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.56036996841431</v>
+        <v>3.56036949157715</v>
       </c>
       <c r="H1383" t="n">
         <v>247312</v>
@@ -40563,7 +40563,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054787635803</v>
+        <v>3.51054739952087</v>
       </c>
       <c r="H1386" t="n">
         <v>316680</v>
@@ -40592,7 +40592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557290077209</v>
+        <v>3.39557313919067</v>
       </c>
       <c r="H1387" t="n">
         <v>935373</v>
@@ -40621,7 +40621,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33425378799438</v>
+        <v>3.33425354957581</v>
       </c>
       <c r="H1388" t="n">
         <v>400605</v>
@@ -40650,7 +40650,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.39940571784973</v>
+        <v>3.39940547943115</v>
       </c>
       <c r="H1389" t="n">
         <v>173631</v>
@@ -40679,7 +40679,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.36874580383301</v>
+        <v>3.36874604225159</v>
       </c>
       <c r="H1390" t="n">
         <v>277398</v>
@@ -40882,7 +40882,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1397" t="n">
         <v>183307</v>
@@ -40911,7 +40911,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1398" t="n">
         <v>112518</v>
@@ -40998,7 +40998,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.14262986183167</v>
+        <v>3.14263010025024</v>
       </c>
       <c r="H1401" t="n">
         <v>131742</v>
@@ -41172,7 +41172,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1407" t="n">
         <v>146797</v>
@@ -41201,7 +41201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1408" t="n">
         <v>69983</v>
@@ -41230,7 +41230,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1409" t="n">
         <v>221820</v>
@@ -41375,7 +41375,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.15412735939026</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1414" t="n">
         <v>365235</v>
@@ -41404,7 +41404,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1415" t="n">
         <v>92805</v>
@@ -41433,7 +41433,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1416" t="n">
         <v>121956</v>
@@ -41462,7 +41462,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1417" t="n">
         <v>112954</v>
@@ -41549,7 +41549,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.0813102722168</v>
+        <v>3.08131003379822</v>
       </c>
       <c r="H1420" t="n">
         <v>108491</v>
@@ -41636,7 +41636,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1423" t="n">
         <v>123011</v>
@@ -41665,7 +41665,7 @@
         <v>4.125</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179251670837</v>
       </c>
       <c r="H1424" t="n">
         <v>65763</v>
@@ -41723,7 +41723,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377178192139</v>
+        <v>3.25377154350281</v>
       </c>
       <c r="H1426" t="n">
         <v>193950</v>
@@ -41781,7 +41781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.15795969963074</v>
+        <v>3.15795993804932</v>
       </c>
       <c r="H1428" t="n">
         <v>275646</v>
@@ -41810,7 +41810,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.15795969963074</v>
+        <v>3.15795993804932</v>
       </c>
       <c r="H1429" t="n">
         <v>95971</v>
@@ -41897,7 +41897,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915286064148</v>
+        <v>3.03915309906006</v>
       </c>
       <c r="H1432" t="n">
         <v>161220</v>
@@ -42071,7 +42071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765583992004</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1438" t="n">
         <v>232582</v>
@@ -42100,7 +42100,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166608810425</v>
+        <v>2.98166584968567</v>
       </c>
       <c r="H1439" t="n">
         <v>590692</v>
@@ -42129,7 +42129,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1440" t="n">
         <v>279680</v>
@@ -42187,7 +42187,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.05831527709961</v>
+        <v>3.05831551551819</v>
       </c>
       <c r="H1442" t="n">
         <v>237497</v>
@@ -42332,7 +42332,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.8858540058136</v>
+        <v>2.88585424423218</v>
       </c>
       <c r="H1447" t="n">
         <v>350177</v>
@@ -42419,7 +42419,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387474060059</v>
+        <v>2.79387450218201</v>
       </c>
       <c r="H1450" t="n">
         <v>304455</v>
@@ -42448,7 +42448,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.77471208572388</v>
+        <v>2.77471232414246</v>
       </c>
       <c r="H1451" t="n">
         <v>246594</v>
@@ -42622,7 +42622,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.99699568748474</v>
+        <v>2.99699592590332</v>
       </c>
       <c r="H1457" t="n">
         <v>610266</v>
@@ -42941,7 +42941,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1468" t="n">
         <v>102163</v>
@@ -43086,7 +43086,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214761734009</v>
+        <v>3.06214785575867</v>
       </c>
       <c r="H1473" t="n">
         <v>159481</v>
@@ -43144,7 +43144,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.05831527709961</v>
+        <v>3.05831551551819</v>
       </c>
       <c r="H1475" t="n">
         <v>118061</v>
@@ -43289,7 +43289,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1480" t="n">
         <v>585959</v>
@@ -43347,7 +43347,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1482" t="n">
         <v>244885</v>
@@ -43434,7 +43434,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.94334125518799</v>
+        <v>2.94334101676941</v>
       </c>
       <c r="H1485" t="n">
         <v>218046</v>
@@ -43492,7 +43492,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.035320520401</v>
+        <v>3.03532075881958</v>
       </c>
       <c r="H1487" t="n">
         <v>1594525</v>
@@ -43666,7 +43666,7 @@
         <v>4</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.06598043441772</v>
+        <v>3.06598019599915</v>
       </c>
       <c r="H1493" t="n">
         <v>170712</v>
@@ -43724,7 +43724,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915286064148</v>
+        <v>3.03915309906006</v>
       </c>
       <c r="H1495" t="n">
         <v>302736</v>
@@ -43753,7 +43753,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1496" t="n">
         <v>427392</v>
@@ -43840,7 +43840,7 @@
         <v>3.75</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.87435674667358</v>
+        <v>2.874356508255</v>
       </c>
       <c r="H1499" t="n">
         <v>488141</v>
@@ -43898,7 +43898,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1501" t="n">
         <v>263324</v>
@@ -43985,7 +43985,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189523696899</v>
+        <v>2.70189547538757</v>
       </c>
       <c r="H1504" t="n">
         <v>285523</v>
@@ -44014,7 +44014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1505" t="n">
         <v>615078</v>
@@ -44072,7 +44072,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1507" t="n">
         <v>201693</v>
@@ -44130,7 +44130,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004240036011</v>
+        <v>2.79004216194153</v>
       </c>
       <c r="H1509" t="n">
         <v>131010</v>
@@ -44217,7 +44217,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1512" t="n">
         <v>148986</v>
@@ -44304,7 +44304,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.76321458816528</v>
+        <v>2.76321482658386</v>
       </c>
       <c r="H1515" t="n">
         <v>527190</v>
@@ -44362,7 +44362,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1517" t="n">
         <v>354141</v>
@@ -44478,7 +44478,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94717359542847</v>
+        <v>2.94717335700989</v>
       </c>
       <c r="H1521" t="n">
         <v>226415</v>
@@ -44594,7 +44594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1525" t="n">
         <v>179741</v>
@@ -44623,7 +44623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867109298706</v>
+        <v>2.95867085456848</v>
       </c>
       <c r="H1526" t="n">
         <v>156246</v>
@@ -44681,7 +44681,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.09280776977539</v>
+        <v>3.09280753135681</v>
       </c>
       <c r="H1528" t="n">
         <v>532620</v>
@@ -44739,7 +44739,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1530" t="n">
         <v>467217</v>
@@ -44826,7 +44826,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.14262986183167</v>
+        <v>3.14263010025024</v>
       </c>
       <c r="H1533" t="n">
         <v>217362</v>
@@ -45029,7 +45029,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1540" t="n">
         <v>383529</v>
@@ -45058,7 +45058,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1541" t="n">
         <v>164325</v>
@@ -45145,7 +45145,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.12346720695496</v>
+        <v>3.12346744537354</v>
       </c>
       <c r="H1544" t="n">
         <v>157684</v>
@@ -45174,7 +45174,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1545" t="n">
         <v>194223</v>
@@ -45232,7 +45232,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.15029501914978</v>
+        <v>3.1502947807312</v>
       </c>
       <c r="H1547" t="n">
         <v>415287</v>
@@ -45261,7 +45261,7 @@
         <v>4.125</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179251670837</v>
       </c>
       <c r="H1548" t="n">
         <v>207618</v>
@@ -45290,7 +45290,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1549" t="n">
         <v>251214</v>
@@ -45348,7 +45348,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.0813102722168</v>
+        <v>3.08131003379822</v>
       </c>
       <c r="H1551" t="n">
         <v>208252</v>
@@ -46073,7 +46073,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.2307767868042</v>
+        <v>3.23077702522278</v>
       </c>
       <c r="H1576" t="n">
         <v>421250</v>
@@ -46160,7 +46160,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844194412231</v>
+        <v>3.23844170570374</v>
       </c>
       <c r="H1579" t="n">
         <v>280568</v>
@@ -46189,7 +46189,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394968986511</v>
+        <v>3.20394945144653</v>
       </c>
       <c r="H1580" t="n">
         <v>262215</v>
@@ -46421,7 +46421,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.3419189453125</v>
+        <v>3.34191870689392</v>
       </c>
       <c r="H1588" t="n">
         <v>333119</v>
@@ -46450,7 +46450,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491346359253</v>
+        <v>3.36491322517395</v>
       </c>
       <c r="H1589" t="n">
         <v>186298</v>
@@ -46566,7 +46566,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.4262330532074</v>
+        <v>3.42623281478882</v>
       </c>
       <c r="H1593" t="n">
         <v>476538</v>
@@ -46595,7 +46595,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.33425378799438</v>
+        <v>3.33425354957581</v>
       </c>
       <c r="H1594" t="n">
         <v>214421</v>
@@ -46624,7 +46624,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.3419189453125</v>
+        <v>3.34191870689392</v>
       </c>
       <c r="H1595" t="n">
         <v>191733</v>
@@ -46682,7 +46682,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.5028829574585</v>
+        <v>3.50288248062134</v>
       </c>
       <c r="H1597" t="n">
         <v>291846</v>
@@ -46711,7 +46711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.46455788612366</v>
+        <v>3.46455764770508</v>
       </c>
       <c r="H1598" t="n">
         <v>146124</v>
@@ -46740,7 +46740,7 @@
         <v>4.625</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.54504013061523</v>
+        <v>3.54503989219666</v>
       </c>
       <c r="H1599" t="n">
         <v>184940</v>
@@ -46769,7 +46769,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372006416321</v>
+        <v>3.48372030258179</v>
       </c>
       <c r="H1600" t="n">
         <v>129996</v>
@@ -46914,7 +46914,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.49138498306274</v>
+        <v>3.49138522148132</v>
       </c>
       <c r="H1605" t="n">
         <v>247326</v>
@@ -46943,7 +46943,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.49138498306274</v>
+        <v>3.49138522148132</v>
       </c>
       <c r="H1606" t="n">
         <v>273277</v>
@@ -47059,7 +47059,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.41473579406738</v>
+        <v>3.41473531723022</v>
       </c>
       <c r="H1610" t="n">
         <v>352993</v>
@@ -47117,7 +47117,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39940571784973</v>
+        <v>3.39940547943115</v>
       </c>
       <c r="H1612" t="n">
         <v>160647</v>
@@ -47146,7 +47146,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1613" t="n">
         <v>656275</v>
@@ -47204,7 +47204,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371388435364</v>
+        <v>3.21371364593506</v>
       </c>
       <c r="H1615" t="n">
         <v>700758</v>
@@ -47233,7 +47233,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1616" t="n">
         <v>826619</v>
@@ -47262,7 +47262,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1617" t="n">
         <v>369551</v>
@@ -47291,7 +47291,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804184913635</v>
+        <v>3.26804208755493</v>
       </c>
       <c r="H1618" t="n">
         <v>297177</v>
@@ -47407,7 +47407,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251901626587</v>
+        <v>3.37251877784729</v>
       </c>
       <c r="H1622" t="n">
         <v>196489</v>
@@ -47436,7 +47436,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147480964661</v>
+        <v>3.30147457122803</v>
       </c>
       <c r="H1623" t="n">
         <v>155525</v>
@@ -47494,7 +47494,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1625" t="n">
         <v>92419</v>
@@ -47552,7 +47552,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1627" t="n">
         <v>103168</v>
@@ -47668,7 +47668,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087725639343</v>
+        <v>3.38087701797485</v>
       </c>
       <c r="H1631" t="n">
         <v>335342</v>
@@ -47697,7 +47697,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1632" t="n">
         <v>295881</v>
@@ -47755,7 +47755,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1634" t="n">
         <v>105059</v>
@@ -47842,7 +47842,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1637" t="n">
         <v>144155</v>
@@ -47900,7 +47900,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.07580423355103</v>
+        <v>3.07580399513245</v>
       </c>
       <c r="H1639" t="n">
         <v>209765</v>
@@ -47987,7 +47987,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1642" t="n">
         <v>151991</v>
@@ -48103,7 +48103,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132706642151</v>
+        <v>2.97132730484009</v>
       </c>
       <c r="H1646" t="n">
         <v>131405</v>
@@ -48132,7 +48132,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1647" t="n">
         <v>134428</v>
@@ -48161,7 +48161,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1648" t="n">
         <v>163785</v>
@@ -48190,7 +48190,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.04237174987793</v>
+        <v>3.04237151145935</v>
       </c>
       <c r="H1649" t="n">
         <v>127541</v>
@@ -48219,7 +48219,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1650" t="n">
         <v>131117</v>
@@ -48364,7 +48364,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.87938737869263</v>
+        <v>2.87938714027405</v>
       </c>
       <c r="H1655" t="n">
         <v>312846</v>
@@ -48393,7 +48393,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78326821327209</v>
+        <v>2.78326845169067</v>
       </c>
       <c r="H1656" t="n">
         <v>290500</v>
@@ -48683,7 +48683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729702949524</v>
+        <v>3.01729679107666</v>
       </c>
       <c r="H1666" t="n">
         <v>33283</v>
@@ -48712,7 +48712,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1667" t="n">
         <v>141470</v>
@@ -48944,7 +48944,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1675" t="n">
         <v>64858</v>
@@ -48973,7 +48973,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.04237174987793</v>
+        <v>3.04237151145935</v>
       </c>
       <c r="H1676" t="n">
         <v>31276</v>
@@ -49002,7 +49002,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1677" t="n">
         <v>141377</v>
@@ -49060,7 +49060,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.08416223526001</v>
+        <v>3.08416247367859</v>
       </c>
       <c r="H1679" t="n">
         <v>129317</v>
@@ -49118,7 +49118,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1681" t="n">
         <v>121914</v>
@@ -49205,7 +49205,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1684" t="n">
         <v>173010</v>
@@ -49234,7 +49234,7 @@
         <v>3.75</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.13431143760681</v>
+        <v>3.13431119918823</v>
       </c>
       <c r="H1685" t="n">
         <v>119056</v>
@@ -49292,7 +49292,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.08416223526001</v>
+        <v>3.08416247367859</v>
       </c>
       <c r="H1687" t="n">
         <v>53067</v>
@@ -49466,7 +49466,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1693" t="n">
         <v>78414</v>
@@ -49495,7 +49495,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.87938737869263</v>
+        <v>2.87938714027405</v>
       </c>
       <c r="H1694" t="n">
         <v>130481</v>
@@ -49553,7 +49553,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.82923817634583</v>
+        <v>2.8292384147644</v>
       </c>
       <c r="H1696" t="n">
         <v>102218</v>
@@ -49669,7 +49669,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.75819373130798</v>
+        <v>2.75819396972656</v>
       </c>
       <c r="H1700" t="n">
         <v>79771</v>
@@ -49756,7 +49756,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.79162669181824</v>
+        <v>2.79162645339966</v>
       </c>
       <c r="H1703" t="n">
         <v>191324</v>
@@ -49814,7 +49814,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.83341765403748</v>
+        <v>2.8334174156189</v>
       </c>
       <c r="H1705" t="n">
         <v>225042</v>
@@ -49901,7 +49901,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.69968700408936</v>
+        <v>2.69968676567078</v>
       </c>
       <c r="H1708" t="n">
         <v>1264562</v>
@@ -49988,7 +49988,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.57431411743164</v>
+        <v>2.57431435585022</v>
       </c>
       <c r="H1711" t="n">
         <v>206609</v>
@@ -50017,7 +50017,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.51162838935852</v>
+        <v>2.51162815093994</v>
       </c>
       <c r="H1712" t="n">
         <v>178826</v>
@@ -50046,7 +50046,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1713" t="n">
         <v>327552</v>
@@ -50104,7 +50104,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1715" t="n">
         <v>395509</v>
@@ -50133,7 +50133,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1716" t="n">
         <v>386802</v>
@@ -50249,7 +50249,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1720" t="n">
         <v>157033</v>
@@ -50278,7 +50278,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.26924133300781</v>
+        <v>2.26924157142639</v>
       </c>
       <c r="H1721" t="n">
         <v>215090</v>
@@ -50307,7 +50307,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.23998808860779</v>
+        <v>2.23998785018921</v>
       </c>
       <c r="H1722" t="n">
         <v>166709</v>
@@ -50336,7 +50336,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1723" t="n">
         <v>163103</v>
@@ -50365,7 +50365,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177881240845</v>
+        <v>2.28177857398987</v>
       </c>
       <c r="H1724" t="n">
         <v>163789</v>
@@ -50394,7 +50394,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1725" t="n">
         <v>189735</v>
@@ -50481,7 +50481,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.1605851650238</v>
+        <v>2.16058540344238</v>
       </c>
       <c r="H1728" t="n">
         <v>328209</v>
@@ -50539,7 +50539,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1730" t="n">
         <v>525600</v>
@@ -50568,7 +50568,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.22745060920715</v>
+        <v>2.22745037078857</v>
       </c>
       <c r="H1731" t="n">
         <v>234021</v>
@@ -50597,7 +50597,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1732" t="n">
         <v>115131</v>
@@ -50626,7 +50626,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1733" t="n">
         <v>131798</v>
@@ -50655,7 +50655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1734" t="n">
         <v>187787</v>
@@ -50684,7 +50684,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1735" t="n">
         <v>172469</v>
@@ -50800,7 +50800,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1739" t="n">
         <v>123630</v>
@@ -50887,7 +50887,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.5032696723938</v>
+        <v>2.50326991081238</v>
       </c>
       <c r="H1742" t="n">
         <v>250081</v>
@@ -50974,7 +50974,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1745" t="n">
         <v>149411</v>
@@ -51003,7 +51003,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849359512329</v>
+        <v>2.57849335670471</v>
       </c>
       <c r="H1746" t="n">
         <v>135722</v>
@@ -51061,7 +51061,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1748" t="n">
         <v>394081</v>
@@ -51090,7 +51090,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1749" t="n">
         <v>280050</v>
@@ -51119,7 +51119,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685159683228</v>
+        <v>2.5868513584137</v>
       </c>
       <c r="H1750" t="n">
         <v>233347</v>
@@ -51177,7 +51177,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.55759811401367</v>
+        <v>2.55759787559509</v>
       </c>
       <c r="H1752" t="n">
         <v>185533</v>
@@ -51206,7 +51206,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.59520959854126</v>
+        <v>2.59520983695984</v>
       </c>
       <c r="H1753" t="n">
         <v>162826</v>
@@ -51293,7 +51293,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1756" t="n">
         <v>119541</v>
@@ -51409,7 +51409,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.72058248519897</v>
+        <v>2.7205822467804</v>
       </c>
       <c r="H1760" t="n">
         <v>266940</v>
@@ -51438,7 +51438,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282155990601</v>
+        <v>2.63282179832458</v>
       </c>
       <c r="H1761" t="n">
         <v>2139834</v>
@@ -51583,7 +51583,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.72476148605347</v>
+        <v>2.72476124763489</v>
       </c>
       <c r="H1766" t="n">
         <v>142984</v>
@@ -51728,7 +51728,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.69132852554321</v>
+        <v>2.69132876396179</v>
       </c>
       <c r="H1771" t="n">
         <v>97612</v>
@@ -51786,7 +51786,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1773" t="n">
         <v>393315</v>
@@ -51815,7 +51815,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.64953780174255</v>
+        <v>2.64953804016113</v>
       </c>
       <c r="H1774" t="n">
         <v>106028</v>
@@ -51960,7 +51960,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.59520959854126</v>
+        <v>2.59520983695984</v>
       </c>
       <c r="H1779" t="n">
         <v>50328</v>
@@ -51989,7 +51989,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1780" t="n">
         <v>86913</v>
@@ -52134,7 +52134,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.72476148605347</v>
+        <v>2.72476124763489</v>
       </c>
       <c r="H1785" t="n">
         <v>159569</v>
@@ -52163,7 +52163,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.69132852554321</v>
+        <v>2.69132876396179</v>
       </c>
       <c r="H1786" t="n">
         <v>125081</v>
@@ -52337,7 +52337,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073121070862</v>
+        <v>2.7707314491272</v>
       </c>
       <c r="H1792" t="n">
         <v>160766</v>
@@ -52395,7 +52395,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.79162669181824</v>
+        <v>2.79162645339966</v>
       </c>
       <c r="H1794" t="n">
         <v>219447</v>
@@ -52453,7 +52453,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.81252217292786</v>
+        <v>2.81252193450928</v>
       </c>
       <c r="H1796" t="n">
         <v>189050</v>
@@ -52511,7 +52511,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.8835666179657</v>
+        <v>2.88356637954712</v>
       </c>
       <c r="H1798" t="n">
         <v>177420</v>
@@ -52540,7 +52540,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1799" t="n">
         <v>296181</v>
@@ -52656,7 +52656,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.30267429351807</v>
+        <v>2.30267405509949</v>
       </c>
       <c r="H1803" t="n">
         <v>1726456</v>
@@ -52743,7 +52743,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.39461398124695</v>
+        <v>2.39461374282837</v>
       </c>
       <c r="H1806" t="n">
         <v>489458</v>
@@ -52772,7 +52772,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.36118125915527</v>
+        <v>2.36118102073669</v>
       </c>
       <c r="H1807" t="n">
         <v>314978</v>
@@ -52801,7 +52801,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1808" t="n">
         <v>588277</v>
@@ -52888,7 +52888,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1811" t="n">
         <v>336694</v>
@@ -52917,7 +52917,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.36536002159119</v>
+        <v>2.36536026000977</v>
       </c>
       <c r="H1812" t="n">
         <v>419736</v>
@@ -52975,7 +52975,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.34446477890015</v>
+        <v>2.34446501731873</v>
       </c>
       <c r="H1814" t="n">
         <v>250677</v>
@@ -53062,7 +53062,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.34446477890015</v>
+        <v>2.34446501731873</v>
       </c>
       <c r="H1817" t="n">
         <v>323266</v>
@@ -53120,7 +53120,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.32356953620911</v>
+        <v>2.32356929779053</v>
       </c>
       <c r="H1819" t="n">
         <v>237689</v>
@@ -53178,7 +53178,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1821" t="n">
         <v>691856</v>
@@ -53207,7 +53207,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.39461398124695</v>
+        <v>2.39461374282837</v>
       </c>
       <c r="H1822" t="n">
         <v>890767</v>
@@ -53236,7 +53236,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.39879298210144</v>
+        <v>2.39879274368286</v>
       </c>
       <c r="H1823" t="n">
         <v>526870</v>
@@ -53294,7 +53294,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.36536002159119</v>
+        <v>2.36536026000977</v>
       </c>
       <c r="H1825" t="n">
         <v>385647</v>
@@ -53352,7 +53352,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.39461398124695</v>
+        <v>2.39461374282837</v>
       </c>
       <c r="H1827" t="n">
         <v>165539</v>
@@ -53410,7 +53410,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.39879298210144</v>
+        <v>2.39879274368286</v>
       </c>
       <c r="H1829" t="n">
         <v>280086</v>
@@ -53497,7 +53497,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1832" t="n">
         <v>440369</v>
@@ -53526,7 +53526,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.36536002159119</v>
+        <v>2.36536026000977</v>
       </c>
       <c r="H1833" t="n">
         <v>744202</v>
@@ -53613,7 +53613,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1836" t="n">
         <v>505563</v>
@@ -53642,7 +53642,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1837" t="n">
         <v>394668</v>
@@ -53671,7 +53671,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.34446477890015</v>
+        <v>2.34446501731873</v>
       </c>
       <c r="H1838" t="n">
         <v>298411</v>
@@ -53700,7 +53700,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.34446477890015</v>
+        <v>2.34446501731873</v>
       </c>
       <c r="H1839" t="n">
         <v>121336</v>
@@ -53787,7 +53787,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1842" t="n">
         <v>375724</v>
@@ -53845,7 +53845,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1844" t="n">
         <v>131363</v>
@@ -53874,7 +53874,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1845" t="n">
         <v>224918</v>
@@ -53932,7 +53932,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.36536002159119</v>
+        <v>2.36536026000977</v>
       </c>
       <c r="H1847" t="n">
         <v>527058</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1851" t="n">
         <v>294292</v>
@@ -54077,7 +54077,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1852" t="n">
         <v>247994</v>
@@ -54106,7 +54106,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1853" t="n">
         <v>352350</v>
@@ -54222,7 +54222,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.46147894859314</v>
+        <v>2.46147918701172</v>
       </c>
       <c r="H1857" t="n">
         <v>276583</v>
@@ -54367,7 +54367,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.39879298210144</v>
+        <v>2.39879274368286</v>
       </c>
       <c r="H1862" t="n">
         <v>204962</v>
@@ -55092,7 +55092,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H1887" t="n">
         <v>204579</v>
@@ -55208,7 +55208,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.43416166305542</v>
+        <v>2.434161901474</v>
       </c>
       <c r="H1891" t="n">
         <v>182470</v>
@@ -55440,7 +55440,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.39219379425049</v>
+        <v>2.39219355583191</v>
       </c>
       <c r="H1899" t="n">
         <v>173762</v>
@@ -55498,7 +55498,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.35955142974854</v>
+        <v>2.35955166816711</v>
       </c>
       <c r="H1901" t="n">
         <v>195477</v>
@@ -55614,7 +55614,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.25229907035828</v>
+        <v>2.25229930877686</v>
       </c>
       <c r="H1905" t="n">
         <v>226323</v>
@@ -55701,7 +55701,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.25229907035828</v>
+        <v>2.25229930877686</v>
       </c>
       <c r="H1908" t="n">
         <v>128561</v>
@@ -55730,7 +55730,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.25696229934692</v>
+        <v>2.2569625377655</v>
       </c>
       <c r="H1909" t="n">
         <v>125903</v>
@@ -55788,7 +55788,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H1911" t="n">
         <v>99769</v>
@@ -55817,7 +55817,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H1912" t="n">
         <v>213003</v>
@@ -56020,7 +56020,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H1919" t="n">
         <v>339392</v>
@@ -56078,7 +56078,7 @@
         <v>2.5</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H1921" t="n">
         <v>125691</v>
@@ -56165,7 +56165,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.39219379425049</v>
+        <v>2.39219355583191</v>
       </c>
       <c r="H1924" t="n">
         <v>86121</v>
@@ -56252,7 +56252,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.35955142974854</v>
+        <v>2.35955166816711</v>
       </c>
       <c r="H1927" t="n">
         <v>159239</v>
@@ -56426,7 +56426,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.31758332252502</v>
+        <v>2.31758308410645</v>
       </c>
       <c r="H1933" t="n">
         <v>132779</v>
@@ -56455,7 +56455,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.25696229934692</v>
+        <v>2.2569625377655</v>
       </c>
       <c r="H1934" t="n">
         <v>387417</v>
@@ -56774,7 +56774,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.13105773925781</v>
+        <v>2.13105750083923</v>
       </c>
       <c r="H1945" t="n">
         <v>190197</v>
@@ -56832,7 +56832,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.13572072982788</v>
+        <v>2.1357204914093</v>
       </c>
       <c r="H1947" t="n">
         <v>156298</v>
@@ -56861,7 +56861,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.13105773925781</v>
+        <v>2.13105750083923</v>
       </c>
       <c r="H1948" t="n">
         <v>270881</v>
@@ -56948,7 +56948,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.14038372039795</v>
+        <v>2.14038395881653</v>
       </c>
       <c r="H1951" t="n">
         <v>169749</v>
@@ -56977,7 +56977,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.14038372039795</v>
+        <v>2.14038395881653</v>
       </c>
       <c r="H1952" t="n">
         <v>131481</v>
@@ -57093,7 +57093,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.06577324867249</v>
+        <v>2.06577348709106</v>
       </c>
       <c r="H1956" t="n">
         <v>240510</v>
@@ -57383,7 +57383,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H1966" t="n">
         <v>593158</v>
@@ -57412,7 +57412,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.9911630153656</v>
+        <v>1.99116313457489</v>
       </c>
       <c r="H1967" t="n">
         <v>316539</v>
@@ -57441,7 +57441,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.97717344760895</v>
+        <v>1.97717356681824</v>
       </c>
       <c r="H1968" t="n">
         <v>131827</v>
@@ -57470,7 +57470,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.93986845016479</v>
+        <v>1.93986856937408</v>
       </c>
       <c r="H1969" t="n">
         <v>432569</v>
@@ -57499,7 +57499,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.93986845016479</v>
+        <v>1.93986856937408</v>
       </c>
       <c r="H1970" t="n">
         <v>247855</v>
@@ -57528,7 +57528,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.93054223060608</v>
+        <v>1.93054211139679</v>
       </c>
       <c r="H1971" t="n">
         <v>176807</v>
@@ -57557,7 +57557,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.93054223060608</v>
+        <v>1.93054211139679</v>
       </c>
       <c r="H1972" t="n">
         <v>257708</v>
@@ -57586,7 +57586,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.9911630153656</v>
+        <v>1.99116313457489</v>
       </c>
       <c r="H1973" t="n">
         <v>293237</v>
@@ -57615,7 +57615,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.97251045703888</v>
+        <v>1.97251057624817</v>
       </c>
       <c r="H1974" t="n">
         <v>221473</v>
@@ -57644,7 +57644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.93986845016479</v>
+        <v>1.93986856937408</v>
       </c>
       <c r="H1975" t="n">
         <v>195355</v>
@@ -57673,7 +57673,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.90256321430206</v>
+        <v>1.90256333351135</v>
       </c>
       <c r="H1976" t="n">
         <v>210212</v>
@@ -57702,7 +57702,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.93054223060608</v>
+        <v>1.93054211139679</v>
       </c>
       <c r="H1977" t="n">
         <v>227069</v>
@@ -57760,7 +57760,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.93520545959473</v>
+        <v>1.93520534038544</v>
       </c>
       <c r="H1979" t="n">
         <v>252513</v>
@@ -57789,7 +57789,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.95385801792145</v>
+        <v>1.95385789871216</v>
       </c>
       <c r="H1980" t="n">
         <v>123199</v>
@@ -57818,7 +57818,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.9911630153656</v>
+        <v>1.99116313457489</v>
       </c>
       <c r="H1981" t="n">
         <v>141624</v>
@@ -57847,7 +57847,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.94453179836273</v>
+        <v>1.94453167915344</v>
       </c>
       <c r="H1982" t="n">
         <v>227004</v>
@@ -57876,7 +57876,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.93986845016479</v>
+        <v>1.93986856937408</v>
       </c>
       <c r="H1983" t="n">
         <v>148968</v>
@@ -57905,7 +57905,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.90256321430206</v>
+        <v>1.90256333351135</v>
       </c>
       <c r="H1984" t="n">
         <v>168629</v>
@@ -58137,7 +58137,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.72722911834717</v>
+        <v>1.72722899913788</v>
       </c>
       <c r="H1992" t="n">
         <v>285261</v>
@@ -58166,7 +58166,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1993" t="n">
-        <v>1.7384204864502</v>
+        <v>1.73842060565948</v>
       </c>
       <c r="H1993" t="n">
         <v>118261</v>
@@ -58195,7 +58195,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1994" t="n">
-        <v>1.753342628479</v>
+        <v>1.75334274768829</v>
       </c>
       <c r="H1994" t="n">
         <v>187136</v>
@@ -58282,7 +58282,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.94453179836273</v>
+        <v>1.94453167915344</v>
       </c>
       <c r="H1997" t="n">
         <v>264413</v>
@@ -58340,7 +58340,7 @@
         <v>2.125</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.98183679580688</v>
+        <v>1.98183691501617</v>
       </c>
       <c r="H1999" t="n">
         <v>205476</v>
@@ -58369,7 +58369,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2000" t="n">
-        <v>2.00515270233154</v>
+        <v>2.00515246391296</v>
       </c>
       <c r="H2000" t="n">
         <v>201943</v>
@@ -58398,7 +58398,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.94453179836273</v>
+        <v>1.94453167915344</v>
       </c>
       <c r="H2001" t="n">
         <v>516252</v>
@@ -58485,7 +58485,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.9911630153656</v>
+        <v>1.99116313457489</v>
       </c>
       <c r="H2004" t="n">
         <v>153346</v>
@@ -58601,7 +58601,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2008" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2008" t="n">
         <v>153383</v>
@@ -58659,7 +58659,7 @@
         <v>2.125</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.98183679580688</v>
+        <v>1.98183691501617</v>
       </c>
       <c r="H2010" t="n">
         <v>254366</v>
@@ -58688,7 +58688,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2011" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2011" t="n">
         <v>113339</v>
@@ -58717,7 +58717,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2012" t="n">
         <v>163134</v>
@@ -58775,7 +58775,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2014" t="n">
         <v>169760</v>
@@ -58833,7 +58833,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2016" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2016" t="n">
         <v>145956</v>
@@ -58949,7 +58949,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2020" t="n">
         <v>113529</v>
@@ -59065,7 +59065,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.06577324867249</v>
+        <v>2.06577348709106</v>
       </c>
       <c r="H2024" t="n">
         <v>134677</v>
@@ -59094,7 +59094,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2025" t="n">
         <v>197283</v>
@@ -59123,7 +59123,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2026" t="n">
         <v>85989</v>
@@ -59297,7 +59297,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.14038372039795</v>
+        <v>2.14038395881653</v>
       </c>
       <c r="H2032" t="n">
         <v>86607</v>
@@ -59326,7 +59326,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.14038372039795</v>
+        <v>2.14038395881653</v>
       </c>
       <c r="H2033" t="n">
         <v>81633</v>
@@ -59384,7 +59384,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.14970993995667</v>
+        <v>2.14971017837524</v>
       </c>
       <c r="H2035" t="n">
         <v>100250</v>
@@ -59413,7 +59413,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14970993995667</v>
+        <v>2.14971017837524</v>
       </c>
       <c r="H2036" t="n">
         <v>126957</v>
@@ -59471,7 +59471,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.13572072982788</v>
+        <v>2.1357204914093</v>
       </c>
       <c r="H2038" t="n">
         <v>242179</v>
@@ -59558,7 +59558,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2041" t="n">
-        <v>2.14970993995667</v>
+        <v>2.14971017837524</v>
       </c>
       <c r="H2041" t="n">
         <v>159169</v>
@@ -59587,7 +59587,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2042" t="n">
-        <v>2.13105773925781</v>
+        <v>2.13105750083923</v>
       </c>
       <c r="H2042" t="n">
         <v>125795</v>
@@ -59674,7 +59674,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.13105773925781</v>
+        <v>2.13105750083923</v>
       </c>
       <c r="H2045" t="n">
         <v>257241</v>
@@ -59790,7 +59790,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2049" t="n">
         <v>93120</v>
@@ -59819,7 +59819,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2050" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2050" t="n">
         <v>54822</v>
@@ -59935,7 +59935,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.0750994682312</v>
+        <v>2.07509970664978</v>
       </c>
       <c r="H2054" t="n">
         <v>73394</v>
@@ -60080,7 +60080,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2059" t="n">
         <v>276853</v>
@@ -60167,7 +60167,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2062" t="n">
         <v>262567</v>
@@ -60225,7 +60225,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.97251045703888</v>
+        <v>1.97251057624817</v>
       </c>
       <c r="H2064" t="n">
         <v>157139</v>
@@ -60254,7 +60254,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.93054223060608</v>
+        <v>1.93054211139679</v>
       </c>
       <c r="H2065" t="n">
         <v>181273</v>
@@ -60341,7 +60341,7 @@
         <v>2.125</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.98183679580688</v>
+        <v>1.98183691501617</v>
       </c>
       <c r="H2068" t="n">
         <v>96186</v>
@@ -60486,7 +60486,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2073" t="n">
         <v>176499</v>
@@ -60515,7 +60515,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.06577324867249</v>
+        <v>2.06577348709106</v>
       </c>
       <c r="H2074" t="n">
         <v>277329</v>
@@ -60602,7 +60602,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.753342628479</v>
+        <v>1.75334274768829</v>
       </c>
       <c r="H2077" t="n">
         <v>2689551</v>
@@ -60660,7 +60660,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.58360409736633</v>
+        <v>1.58360421657562</v>
       </c>
       <c r="H2079" t="n">
         <v>1567809</v>
@@ -60718,7 +60718,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.55002951622009</v>
+        <v>1.5500293970108</v>
       </c>
       <c r="H2081" t="n">
         <v>1301826</v>
@@ -60834,7 +60834,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.52018547058105</v>
+        <v>1.52018535137177</v>
       </c>
       <c r="H2085" t="n">
         <v>709375</v>
@@ -60863,7 +60863,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2086" t="n">
-        <v>1.50153279304504</v>
+        <v>1.50153291225433</v>
       </c>
       <c r="H2086" t="n">
         <v>515829</v>
@@ -60921,7 +60921,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.40640461444855</v>
+        <v>1.40640473365784</v>
       </c>
       <c r="H2088" t="n">
         <v>740307</v>
@@ -60950,7 +60950,7 @@
         <v>1.5</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.39894354343414</v>
+        <v>1.39894366264343</v>
       </c>
       <c r="H2089" t="n">
         <v>1150044</v>
@@ -60979,7 +60979,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.35790801048279</v>
+        <v>1.3579078912735</v>
       </c>
       <c r="H2090" t="n">
         <v>1004942</v>
@@ -61008,7 +61008,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G2091" t="n">
-        <v>1.32246804237366</v>
+        <v>1.32246792316437</v>
       </c>
       <c r="H2091" t="n">
         <v>571213</v>
@@ -61037,7 +61037,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.33179426193237</v>
+        <v>1.33179438114166</v>
       </c>
       <c r="H2092" t="n">
         <v>488121</v>
@@ -61066,7 +61066,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G2093" t="n">
-        <v>1.32619869709015</v>
+        <v>1.32619857788086</v>
       </c>
       <c r="H2093" t="n">
         <v>449989</v>
@@ -61124,7 +61124,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.33552479743958</v>
+        <v>1.33552491664886</v>
       </c>
       <c r="H2095" t="n">
         <v>355290</v>
@@ -61211,7 +61211,7 @@
         <v>1.5</v>
       </c>
       <c r="G2098" t="n">
-        <v>1.39894354343414</v>
+        <v>1.39894366264343</v>
       </c>
       <c r="H2098" t="n">
         <v>654358</v>
@@ -61443,7 +61443,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.3690994977951</v>
+        <v>1.36909961700439</v>
       </c>
       <c r="H2106" t="n">
         <v>530421</v>
@@ -61878,7 +61878,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.55935597419739</v>
+        <v>1.5593558549881</v>
       </c>
       <c r="H2121" t="n">
         <v>264878</v>
@@ -62110,7 +62110,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.71603751182556</v>
+        <v>1.71603763103485</v>
       </c>
       <c r="H2129" t="n">
         <v>365240</v>
@@ -62197,7 +62197,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.70111536979675</v>
+        <v>1.70111548900604</v>
       </c>
       <c r="H2132" t="n">
         <v>159088</v>
@@ -62371,7 +62371,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.76639950275421</v>
+        <v>1.7663996219635</v>
       </c>
       <c r="H2138" t="n">
         <v>215412</v>
@@ -62458,7 +62458,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.8522013425827</v>
+        <v>1.85220122337341</v>
       </c>
       <c r="H2141" t="n">
         <v>363066</v>
@@ -62690,7 +62690,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.7384204864502</v>
+        <v>1.73842060565948</v>
       </c>
       <c r="H2149" t="n">
         <v>395325</v>
@@ -62748,7 +62748,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.70857644081116</v>
+        <v>1.70857656002045</v>
       </c>
       <c r="H2151" t="n">
         <v>548980</v>
@@ -62777,7 +62777,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G2152" t="n">
-        <v>1.70111536979675</v>
+        <v>1.70111548900604</v>
       </c>
       <c r="H2152" t="n">
         <v>267659</v>
@@ -62864,7 +62864,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.58733475208282</v>
+        <v>1.58733463287354</v>
       </c>
       <c r="H2155" t="n">
         <v>228996</v>
@@ -62922,7 +62922,7 @@
         <v>1.75</v>
       </c>
       <c r="G2157" t="n">
-        <v>1.63210093975067</v>
+        <v>1.63210082054138</v>
       </c>
       <c r="H2157" t="n">
         <v>144562</v>
@@ -63125,7 +63125,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G2164" t="n">
-        <v>1.63769662380219</v>
+        <v>1.63769674301147</v>
       </c>
       <c r="H2164" t="n">
         <v>84019</v>
@@ -63154,7 +63154,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2165" t="n">
-        <v>1.67873227596283</v>
+        <v>1.67873239517212</v>
       </c>
       <c r="H2165" t="n">
         <v>117283</v>
@@ -63183,7 +63183,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2166" t="n">
-        <v>1.76639950275421</v>
+        <v>1.7663996219635</v>
       </c>
       <c r="H2166" t="n">
         <v>491089</v>
@@ -63241,7 +63241,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G2168" t="n">
-        <v>1.80370461940765</v>
+        <v>1.80370473861694</v>
       </c>
       <c r="H2168" t="n">
         <v>121256</v>
@@ -63270,7 +63270,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2169" t="n">
-        <v>1.7458815574646</v>
+        <v>1.74588167667389</v>
       </c>
       <c r="H2169" t="n">
         <v>161489</v>
@@ -63299,7 +63299,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G2170" t="n">
-        <v>1.80370461940765</v>
+        <v>1.80370473861694</v>
       </c>
       <c r="H2170" t="n">
         <v>132896</v>
@@ -63328,7 +63328,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G2171" t="n">
-        <v>1.77386045455933</v>
+        <v>1.77386057376862</v>
       </c>
       <c r="H2171" t="n">
         <v>186551</v>
@@ -63357,7 +63357,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G2172" t="n">
-        <v>1.77386045455933</v>
+        <v>1.77386057376862</v>
       </c>
       <c r="H2172" t="n">
         <v>88474</v>
@@ -63589,7 +63589,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G2180" t="n">
-        <v>1.80743503570557</v>
+        <v>1.80743515491486</v>
       </c>
       <c r="H2180" t="n">
         <v>172924</v>
@@ -63705,7 +63705,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.88857388496399</v>
+        <v>1.88857400417328</v>
       </c>
       <c r="H2184" t="n">
         <v>150815</v>
@@ -63908,7 +63908,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2191" t="n">
-        <v>1.93054223060608</v>
+        <v>1.93054211139679</v>
       </c>
       <c r="H2191" t="n">
         <v>184998</v>
@@ -63937,7 +63937,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2192" t="n">
-        <v>1.97251045703888</v>
+        <v>1.97251057624817</v>
       </c>
       <c r="H2192" t="n">
         <v>184859</v>
@@ -63966,7 +63966,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2193" t="n">
-        <v>1.97717344760895</v>
+        <v>1.97717356681824</v>
       </c>
       <c r="H2193" t="n">
         <v>113071</v>
@@ -64024,7 +64024,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G2195" t="n">
-        <v>1.95385801792145</v>
+        <v>1.95385789871216</v>
       </c>
       <c r="H2195" t="n">
         <v>75968</v>
@@ -64053,7 +64053,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2196" t="n">
-        <v>1.95852088928223</v>
+        <v>1.95852100849152</v>
       </c>
       <c r="H2196" t="n">
         <v>82593</v>
@@ -64082,7 +64082,7 @@
         <v>2.125</v>
       </c>
       <c r="G2197" t="n">
-        <v>1.98183679580688</v>
+        <v>1.98183691501617</v>
       </c>
       <c r="H2197" t="n">
         <v>217319</v>
@@ -64111,7 +64111,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2198" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2198" t="n">
         <v>245791</v>
@@ -64227,7 +64227,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2202" t="n">
-        <v>2.1124050617218</v>
+        <v>2.11240482330322</v>
       </c>
       <c r="H2202" t="n">
         <v>98841</v>
@@ -64256,7 +64256,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2203" t="n">
-        <v>2.13105773925781</v>
+        <v>2.13105750083923</v>
       </c>
       <c r="H2203" t="n">
         <v>263217</v>
@@ -64314,7 +64314,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2205" t="n">
-        <v>2.21033096313477</v>
+        <v>2.21033072471619</v>
       </c>
       <c r="H2205" t="n">
         <v>379501</v>
@@ -64343,7 +64343,7 @@
         <v>2.5</v>
       </c>
       <c r="G2206" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2206" t="n">
         <v>774758</v>
@@ -64430,7 +64430,7 @@
         <v>2.5</v>
       </c>
       <c r="G2209" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2209" t="n">
         <v>247764</v>
@@ -64488,7 +64488,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2211" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2211" t="n">
         <v>202277</v>
@@ -64517,7 +64517,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2212" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H2212" t="n">
         <v>126442</v>
@@ -64720,7 +64720,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2219" t="n">
-        <v>2.35955142974854</v>
+        <v>2.35955166816711</v>
       </c>
       <c r="H2219" t="n">
         <v>177581</v>
@@ -64923,7 +64923,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2226" t="n">
-        <v>2.39219379425049</v>
+        <v>2.39219355583191</v>
       </c>
       <c r="H2226" t="n">
         <v>134883</v>
@@ -65010,7 +65010,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2229" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H2229" t="n">
         <v>146285</v>
@@ -65039,7 +65039,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2230" t="n">
-        <v>2.28494143486023</v>
+        <v>2.28494119644165</v>
       </c>
       <c r="H2230" t="n">
         <v>128357</v>
@@ -65068,7 +65068,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2231" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H2231" t="n">
         <v>118080</v>
@@ -65097,7 +65097,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2232" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H2232" t="n">
         <v>151684</v>
@@ -65155,7 +65155,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2234" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2234" t="n">
         <v>123503</v>
@@ -65242,7 +65242,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G2237" t="n">
-        <v>2.31758332252502</v>
+        <v>2.31758308410645</v>
       </c>
       <c r="H2237" t="n">
         <v>59536</v>
@@ -65300,7 +65300,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2239" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2239" t="n">
         <v>172426</v>
@@ -65329,7 +65329,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G2240" t="n">
-        <v>2.31758332252502</v>
+        <v>2.31758308410645</v>
       </c>
       <c r="H2240" t="n">
         <v>211451</v>
@@ -65387,7 +65387,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2242" t="n">
-        <v>2.28494143486023</v>
+        <v>2.28494119644165</v>
       </c>
       <c r="H2242" t="n">
         <v>190715</v>
@@ -65416,7 +65416,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2243" t="n">
-        <v>2.25229907035828</v>
+        <v>2.25229930877686</v>
       </c>
       <c r="H2243" t="n">
         <v>95548</v>
@@ -65474,7 +65474,7 @@
         <v>2.5</v>
       </c>
       <c r="G2245" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2245" t="n">
         <v>141750</v>
@@ -65503,7 +65503,7 @@
         <v>2.5</v>
       </c>
       <c r="G2246" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2246" t="n">
         <v>149143</v>
@@ -65532,7 +65532,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G2247" t="n">
-        <v>2.41084599494934</v>
+        <v>2.41084623336792</v>
       </c>
       <c r="H2247" t="n">
         <v>207309</v>
@@ -65648,7 +65648,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2251" t="n">
-        <v>2.35955142974854</v>
+        <v>2.35955166816711</v>
       </c>
       <c r="H2251" t="n">
         <v>190160</v>
@@ -65938,7 +65938,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.03779458999634</v>
+        <v>2.03779435157776</v>
       </c>
       <c r="H2261" t="n">
         <v>81577</v>
@@ -65996,7 +65996,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2263" t="n">
-        <v>2.02846837043762</v>
+        <v>2.02846813201904</v>
       </c>
       <c r="H2263" t="n">
         <v>46834</v>
@@ -66141,7 +66141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2268" t="n">
-        <v>2.06577324867249</v>
+        <v>2.06577348709106</v>
       </c>
       <c r="H2268" t="n">
         <v>122756</v>
@@ -66170,7 +66170,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.14970993995667</v>
+        <v>2.14971017837524</v>
       </c>
       <c r="H2269" t="n">
         <v>186624</v>
@@ -66199,7 +66199,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2270" t="n">
-        <v>2.21033096313477</v>
+        <v>2.21033072471619</v>
       </c>
       <c r="H2270" t="n">
         <v>172121</v>
@@ -66228,7 +66228,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2271" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2271" t="n">
         <v>379764</v>
@@ -66286,7 +66286,7 @@
         <v>2.5</v>
       </c>
       <c r="G2273" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2273" t="n">
         <v>166107</v>
@@ -66344,7 +66344,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2275" t="n">
-        <v>2.28494143486023</v>
+        <v>2.28494119644165</v>
       </c>
       <c r="H2275" t="n">
         <v>141548</v>
@@ -66721,7 +66721,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.31292033195496</v>
+        <v>2.31292009353638</v>
       </c>
       <c r="H2288" t="n">
         <v>82817</v>
@@ -66750,7 +66750,7 @@
         <v>2.5</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.33157253265381</v>
+        <v>2.33157277107239</v>
       </c>
       <c r="H2289" t="n">
         <v>85778</v>
@@ -66808,7 +66808,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2291" t="n">
-        <v>2.28494143486023</v>
+        <v>2.28494119644165</v>
       </c>
       <c r="H2291" t="n">
         <v>69169</v>
@@ -67156,7 +67156,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2303" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2303" t="n">
         <v>54474</v>
@@ -67214,7 +67214,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2305" t="n">
-        <v>2.28494143486023</v>
+        <v>2.28494119644165</v>
       </c>
       <c r="H2305" t="n">
         <v>47568</v>
@@ -67243,7 +67243,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2306" t="n">
-        <v>2.32690930366516</v>
+        <v>2.32690954208374</v>
       </c>
       <c r="H2306" t="n">
         <v>155107</v>
@@ -67359,7 +67359,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2310" t="n">
-        <v>2.56939339637756</v>
+        <v>2.56939315795898</v>
       </c>
       <c r="H2310" t="n">
         <v>695565</v>
@@ -67475,7 +67475,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2314" t="n">
-        <v>2.65332984924316</v>
+        <v>2.65332961082458</v>
       </c>
       <c r="H2314" t="n">
         <v>291334</v>
@@ -67504,7 +67504,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2315" t="n">
-        <v>2.67198252677917</v>
+        <v>2.6719822883606</v>
       </c>
       <c r="H2315" t="n">
         <v>270920</v>
@@ -67562,7 +67562,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2317" t="n">
-        <v>2.57871961593628</v>
+        <v>2.5787193775177</v>
       </c>
       <c r="H2317" t="n">
         <v>175999</v>
@@ -67649,7 +67649,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2320" t="n">
-        <v>2.74659252166748</v>
+        <v>2.74659276008606</v>
       </c>
       <c r="H2320" t="n">
         <v>379229</v>
@@ -67707,7 +67707,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.65332984924316</v>
+        <v>2.65332961082458</v>
       </c>
       <c r="H2322" t="n">
         <v>188264</v>
@@ -67765,7 +67765,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2324" t="n">
-        <v>2.57871961593628</v>
+        <v>2.5787193775177</v>
       </c>
       <c r="H2324" t="n">
         <v>159924</v>
@@ -67794,7 +67794,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.56939339637756</v>
+        <v>2.56939315795898</v>
       </c>
       <c r="H2325" t="n">
         <v>94219</v>
@@ -67939,7 +67939,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2330" t="n">
-        <v>2.69529795646667</v>
+        <v>2.69529819488525</v>
       </c>
       <c r="H2330" t="n">
         <v>132901</v>
@@ -68026,7 +68026,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G2333" t="n">
-        <v>2.60669827461243</v>
+        <v>2.60669851303101</v>
       </c>
       <c r="H2333" t="n">
         <v>166172</v>
@@ -68055,7 +68055,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2334" t="n">
-        <v>2.63934016227722</v>
+        <v>2.6393404006958</v>
       </c>
       <c r="H2334" t="n">
         <v>199949</v>
@@ -68345,7 +68345,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2344" t="n">
-        <v>2.56939339637756</v>
+        <v>2.56939315795898</v>
       </c>
       <c r="H2344" t="n">
         <v>107353</v>
@@ -68461,7 +68461,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2348" t="n">
-        <v>2.63934016227722</v>
+        <v>2.6393404006958</v>
       </c>
       <c r="H2348" t="n">
         <v>137742</v>
@@ -68490,7 +68490,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G2349" t="n">
-        <v>2.60669827461243</v>
+        <v>2.60669851303101</v>
       </c>
       <c r="H2349" t="n">
         <v>89816</v>
@@ -68519,7 +68519,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2350" t="n">
-        <v>2.67664551734924</v>
+        <v>2.67664527893066</v>
       </c>
       <c r="H2350" t="n">
         <v>364838</v>
@@ -68664,7 +68664,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2355" t="n">
-        <v>2.69063472747803</v>
+        <v>2.69063496589661</v>
       </c>
       <c r="H2355" t="n">
         <v>405461</v>
@@ -68722,7 +68722,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G2357" t="n">
-        <v>2.50877213478088</v>
+        <v>2.50877237319946</v>
       </c>
       <c r="H2357" t="n">
         <v>672680</v>
@@ -68751,7 +68751,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2358" t="n">
-        <v>2.56939339637756</v>
+        <v>2.56939315795898</v>
       </c>
       <c r="H2358" t="n">
         <v>173881</v>
@@ -68896,7 +68896,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2363" t="n">
-        <v>2.75125598907471</v>
+        <v>2.75125575065613</v>
       </c>
       <c r="H2363" t="n">
         <v>218593</v>
@@ -68954,7 +68954,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2365" t="n">
-        <v>2.74659252166748</v>
+        <v>2.74659276008606</v>
       </c>
       <c r="H2365" t="n">
         <v>88851</v>
@@ -68983,7 +68983,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2366" t="n">
-        <v>2.75125598907471</v>
+        <v>2.75125575065613</v>
       </c>
       <c r="H2366" t="n">
         <v>204252</v>
@@ -69041,7 +69041,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2368" t="n">
-        <v>2.77457165718079</v>
+        <v>2.77457141876221</v>
       </c>
       <c r="H2368" t="n">
         <v>151813</v>
@@ -69128,7 +69128,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2371" t="n">
-        <v>2.83519244194031</v>
+        <v>2.83519220352173</v>
       </c>
       <c r="H2371" t="n">
         <v>224125</v>
@@ -69186,7 +69186,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2373" t="n">
-        <v>2.83519244194031</v>
+        <v>2.83519220352173</v>
       </c>
       <c r="H2373" t="n">
         <v>312115</v>
@@ -69215,7 +69215,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G2374" t="n">
-        <v>2.82586622238159</v>
+        <v>2.82586598396301</v>
       </c>
       <c r="H2374" t="n">
         <v>121122</v>
@@ -69331,7 +69331,7 @@
         <v>3</v>
       </c>
       <c r="G2378" t="n">
-        <v>2.79788708686829</v>
+        <v>2.79788732528687</v>
       </c>
       <c r="H2378" t="n">
         <v>285728</v>
@@ -80009,6 +80009,35 @@
         <v>147714</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>3.67499995231628</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>3.67499995231628</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>43144</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G2" t="n">
-        <v>4.56322860717773</v>
+        <v>4.56322813034058</v>
       </c>
       <c r="H2" t="n">
         <v>105854</v>
@@ -456,7 +456,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235925674438</v>
+        <v>4.64235973358154</v>
       </c>
       <c r="H3" t="n">
         <v>62931</v>
@@ -514,7 +514,7 @@
         <v>8.10179138183594</v>
       </c>
       <c r="G5" t="n">
-        <v>4.59751892089844</v>
+        <v>4.59751844406128</v>
       </c>
       <c r="H5" t="n">
         <v>165490</v>
@@ -601,7 +601,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496635437012</v>
       </c>
       <c r="H8" t="n">
         <v>127969</v>
@@ -717,7 +717,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.0172233581543</v>
+        <v>4.01722383499146</v>
       </c>
       <c r="H12" t="n">
         <v>222009</v>
@@ -746,7 +746,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H13" t="n">
         <v>164720</v>
@@ -775,7 +775,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176956176758</v>
+        <v>3.48176980018616</v>
       </c>
       <c r="H14" t="n">
         <v>416053</v>
@@ -804,7 +804,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74553990364075</v>
+        <v>3.74553966522217</v>
       </c>
       <c r="H15" t="n">
         <v>313484</v>
@@ -833,7 +833,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8167576789856</v>
+        <v>3.81675744056702</v>
       </c>
       <c r="H16" t="n">
         <v>176408</v>
@@ -862,7 +862,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8958888053894</v>
+        <v>3.89588928222656</v>
       </c>
       <c r="H17" t="n">
         <v>120439</v>
@@ -891,7 +891,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522152900696</v>
+        <v>3.83522176742554</v>
       </c>
       <c r="H18" t="n">
         <v>75537</v>
@@ -920,7 +920,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884528160095</v>
+        <v>3.80884432792664</v>
       </c>
       <c r="H19" t="n">
         <v>163830</v>
@@ -978,7 +978,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467079162598</v>
+        <v>3.82467174530029</v>
       </c>
       <c r="H21" t="n">
         <v>190130</v>
@@ -1036,7 +1036,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74553990364075</v>
+        <v>3.74553966522217</v>
       </c>
       <c r="H23" t="n">
         <v>350145</v>
@@ -1065,7 +1065,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246808052063</v>
+        <v>3.78246784210205</v>
       </c>
       <c r="H24" t="n">
         <v>251231</v>
@@ -1094,7 +1094,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617617607117</v>
+        <v>3.56617665290833</v>
       </c>
       <c r="H25" t="n">
         <v>406980</v>
@@ -1152,7 +1152,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405804634094</v>
+        <v>3.33405780792236</v>
       </c>
       <c r="H27" t="n">
         <v>238163</v>
@@ -1181,7 +1181,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626099586487</v>
+        <v>3.37626171112061</v>
       </c>
       <c r="H28" t="n">
         <v>216081</v>
@@ -1210,7 +1210,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090044975281</v>
+        <v>3.56090021133423</v>
       </c>
       <c r="H29" t="n">
         <v>200231</v>
@@ -1239,7 +1239,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220399856567</v>
+        <v>3.44220376014709</v>
       </c>
       <c r="H30" t="n">
         <v>158033</v>
@@ -1268,7 +1268,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078391075134</v>
+        <v>3.51078510284424</v>
       </c>
       <c r="H31" t="n">
         <v>208699</v>
@@ -1326,7 +1326,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69278645515442</v>
+        <v>3.69278597831726</v>
       </c>
       <c r="H33" t="n">
         <v>218931</v>
@@ -1355,7 +1355,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467079162598</v>
+        <v>3.82467174530029</v>
       </c>
       <c r="H34" t="n">
         <v>72733</v>
@@ -1384,7 +1384,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829335212708</v>
+        <v>3.79829382896423</v>
       </c>
       <c r="H35" t="n">
         <v>53341</v>
@@ -1413,7 +1413,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498892784119</v>
+        <v>3.73498916625977</v>
       </c>
       <c r="H36" t="n">
         <v>83765</v>
@@ -1442,7 +1442,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699123382568</v>
+        <v>3.91699051856995</v>
       </c>
       <c r="H37" t="n">
         <v>87617</v>
@@ -1500,7 +1500,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.814120054245</v>
+        <v>3.81412029266357</v>
       </c>
       <c r="H39" t="n">
         <v>93458</v>
@@ -1558,7 +1558,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104751586914</v>
+        <v>3.85104775428772</v>
       </c>
       <c r="H41" t="n">
         <v>113404</v>
@@ -1587,7 +1587,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061450958252</v>
+        <v>3.89061307907104</v>
       </c>
       <c r="H42" t="n">
         <v>132642</v>
@@ -1616,7 +1616,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171503067017</v>
+        <v>3.91171550750732</v>
       </c>
       <c r="H43" t="n">
         <v>374802</v>
@@ -1645,7 +1645,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.0910792350769</v>
+        <v>4.09107875823975</v>
       </c>
       <c r="H44" t="n">
         <v>354322</v>
@@ -1761,7 +1761,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G48" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H48" t="n">
         <v>85660</v>
@@ -1790,7 +1790,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603706359863</v>
+        <v>4.18603658676147</v>
       </c>
       <c r="H49" t="n">
         <v>97201</v>
@@ -1848,7 +1848,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803770065308</v>
+        <v>4.36803865432739</v>
       </c>
       <c r="H51" t="n">
         <v>187212</v>
@@ -1877,7 +1877,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.4049654006958</v>
+        <v>4.40496635437012</v>
       </c>
       <c r="H52" t="n">
         <v>135917</v>
@@ -1906,7 +1906,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221242904663</v>
+        <v>4.35221195220947</v>
       </c>
       <c r="H53" t="n">
         <v>202614</v>
@@ -1935,7 +1935,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473327636719</v>
+        <v>4.30473279953003</v>
       </c>
       <c r="H54" t="n">
         <v>145802</v>
@@ -2022,7 +2022,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44716930389404</v>
+        <v>4.44716882705688</v>
       </c>
       <c r="H57" t="n">
         <v>149650</v>
@@ -2051,7 +2051,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G58" t="n">
-        <v>4.38913917541504</v>
+        <v>4.3891396522522</v>
       </c>
       <c r="H58" t="n">
         <v>117447</v>
@@ -2080,7 +2080,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583570480347</v>
+        <v>4.32583475112915</v>
       </c>
       <c r="H59" t="n">
         <v>99265</v>
@@ -2225,7 +2225,7 @@
         <v>7.52076816558838</v>
       </c>
       <c r="G64" t="n">
-        <v>4.2678050994873</v>
+        <v>4.26780605316162</v>
       </c>
       <c r="H64" t="n">
         <v>132175</v>
@@ -2486,7 +2486,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G73" t="n">
-        <v>4.24670362472534</v>
+        <v>4.2467041015625</v>
       </c>
       <c r="H73" t="n">
         <v>30816</v>
@@ -2544,7 +2544,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G75" t="n">
-        <v>4.16757202148438</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H75" t="n">
         <v>72788</v>
@@ -2602,7 +2602,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241283416748</v>
+        <v>4.21241331100464</v>
       </c>
       <c r="H77" t="n">
         <v>65491</v>
@@ -2631,7 +2631,7 @@
         <v>7.25582122802734</v>
       </c>
       <c r="G78" t="n">
-        <v>4.11745595932007</v>
+        <v>4.11745643615723</v>
       </c>
       <c r="H78" t="n">
         <v>140314</v>
@@ -2660,7 +2660,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G79" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H79" t="n">
         <v>28153</v>
@@ -2689,7 +2689,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16757202148438</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H80" t="n">
         <v>71017</v>
@@ -2863,7 +2863,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119577407837</v>
+        <v>4.14119625091553</v>
       </c>
       <c r="H86" t="n">
         <v>95409</v>
@@ -2892,7 +2892,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009334564209</v>
+        <v>4.12009477615356</v>
       </c>
       <c r="H87" t="n">
         <v>20188</v>
@@ -2950,7 +2950,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G89" t="n">
-        <v>4.1939492225647</v>
+        <v>4.19394969940186</v>
       </c>
       <c r="H89" t="n">
         <v>83038</v>
@@ -2979,7 +2979,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383316040039</v>
+        <v>4.14383363723755</v>
       </c>
       <c r="H90" t="n">
         <v>26575</v>
@@ -3008,7 +3008,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.24406623840332</v>
+        <v>4.244065284729</v>
       </c>
       <c r="H91" t="n">
         <v>211317</v>
@@ -3066,7 +3066,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702152252197</v>
+        <v>4.15702199935913</v>
       </c>
       <c r="H93" t="n">
         <v>72826</v>
@@ -3124,7 +3124,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044343948364</v>
+        <v>4.27044296264648</v>
       </c>
       <c r="H95" t="n">
         <v>62480</v>
@@ -3153,7 +3153,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131183624268</v>
+        <v>4.19131135940552</v>
       </c>
       <c r="H96" t="n">
         <v>58862</v>
@@ -3182,7 +3182,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G97" t="n">
-        <v>4.23615312576294</v>
+        <v>4.23615264892578</v>
       </c>
       <c r="H97" t="n">
         <v>39151</v>
@@ -3211,7 +3211,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G98" t="n">
-        <v>4.15174627304077</v>
+        <v>4.15174579620361</v>
       </c>
       <c r="H98" t="n">
         <v>86040</v>
@@ -3269,7 +3269,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.3369402885437</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H100" t="n">
         <v>61620</v>
@@ -3298,7 +3298,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G101" t="n">
-        <v>4.41190767288208</v>
+        <v>4.41190719604492</v>
       </c>
       <c r="H101" t="n">
         <v>66996</v>
@@ -3356,7 +3356,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H103" t="n">
         <v>122131</v>
@@ -3414,7 +3414,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.52852153778076</v>
+        <v>4.52852201461792</v>
       </c>
       <c r="H105" t="n">
         <v>60638</v>
@@ -3472,7 +3472,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G107" t="n">
-        <v>4.45355463027954</v>
+        <v>4.45355558395386</v>
       </c>
       <c r="H107" t="n">
         <v>112417</v>
@@ -3559,7 +3559,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743774414062</v>
+        <v>4.46743726730347</v>
       </c>
       <c r="H110" t="n">
         <v>35336</v>
@@ -3588,7 +3588,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G111" t="n">
-        <v>4.47021436691284</v>
+        <v>4.47021484375</v>
       </c>
       <c r="H111" t="n">
         <v>58171</v>
@@ -3617,7 +3617,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45355463027954</v>
+        <v>4.45355558395386</v>
       </c>
       <c r="H112" t="n">
         <v>53716</v>
@@ -3704,7 +3704,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H115" t="n">
         <v>98580</v>
@@ -3733,7 +3733,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768527030945</v>
+        <v>3.91768455505371</v>
       </c>
       <c r="H116" t="n">
         <v>109038</v>
@@ -3762,7 +3762,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989729881287</v>
+        <v>3.93989658355713</v>
       </c>
       <c r="H117" t="n">
         <v>151204</v>
@@ -3820,7 +3820,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H119" t="n">
         <v>396991</v>
@@ -3878,7 +3878,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G121" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H121" t="n">
         <v>147984</v>
@@ -3965,7 +3965,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.8926956653595</v>
+        <v>3.89269638061523</v>
       </c>
       <c r="H124" t="n">
         <v>186001</v>
@@ -3994,7 +3994,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="n">
-        <v>3.6927855014801</v>
+        <v>3.69278526306152</v>
       </c>
       <c r="H125" t="n">
         <v>299139</v>
@@ -4023,7 +4023,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="n">
-        <v>3.70944547653198</v>
+        <v>3.70944452285767</v>
       </c>
       <c r="H126" t="n">
         <v>201840</v>
@@ -4052,7 +4052,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H127" t="n">
         <v>204444</v>
@@ -4081,7 +4081,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594680786133</v>
+        <v>4.07594728469849</v>
       </c>
       <c r="H128" t="n">
         <v>365836</v>
@@ -4139,7 +4139,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603664398193</v>
+        <v>3.87603735923767</v>
       </c>
       <c r="H130" t="n">
         <v>40805</v>
@@ -4168,7 +4168,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165726661682</v>
+        <v>3.73165678977966</v>
       </c>
       <c r="H131" t="n">
         <v>182299</v>
@@ -4226,7 +4226,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328248023987</v>
+        <v>3.82328271865845</v>
       </c>
       <c r="H133" t="n">
         <v>123098</v>
@@ -4255,7 +4255,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H134" t="n">
         <v>96476</v>
@@ -4284,7 +4284,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.94822692871094</v>
+        <v>3.94822669029236</v>
       </c>
       <c r="H135" t="n">
         <v>150820</v>
@@ -4313,7 +4313,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G136" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H136" t="n">
         <v>104402</v>
@@ -4429,7 +4429,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35915374755859</v>
+        <v>4.35915422439575</v>
       </c>
       <c r="H140" t="n">
         <v>180510</v>
@@ -4487,7 +4487,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.29806900024414</v>
+        <v>4.2980694770813</v>
       </c>
       <c r="H142" t="n">
         <v>180595</v>
@@ -4574,7 +4574,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="n">
-        <v>4.32583522796631</v>
+        <v>4.32583475112915</v>
       </c>
       <c r="H145" t="n">
         <v>68143</v>
@@ -4603,7 +4603,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="n">
-        <v>4.30084657669067</v>
+        <v>4.30084705352783</v>
       </c>
       <c r="H146" t="n">
         <v>72804</v>
@@ -4661,7 +4661,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025833129883</v>
       </c>
       <c r="H148" t="n">
         <v>86165</v>
@@ -4719,7 +4719,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637664794922</v>
+        <v>4.35637712478638</v>
       </c>
       <c r="H150" t="n">
         <v>81896</v>
@@ -4748,7 +4748,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H151" t="n">
         <v>100034</v>
@@ -4806,7 +4806,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="n">
-        <v>4.23420906066895</v>
+        <v>4.2342095375061</v>
       </c>
       <c r="H153" t="n">
         <v>141811</v>
@@ -4835,7 +4835,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917596817017</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H154" t="n">
         <v>185636</v>
@@ -4893,7 +4893,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="n">
-        <v>4.21199750900269</v>
+        <v>4.21199703216553</v>
       </c>
       <c r="H156" t="n">
         <v>137973</v>
@@ -5009,7 +5009,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423223495483</v>
+        <v>4.18423175811768</v>
       </c>
       <c r="H160" t="n">
         <v>85871</v>
@@ -5096,7 +5096,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="n">
-        <v>4.04262924194336</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H163" t="n">
         <v>129575</v>
@@ -5125,7 +5125,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="n">
-        <v>4.05095863342285</v>
+        <v>4.05095767974854</v>
       </c>
       <c r="H164" t="n">
         <v>61371</v>
@@ -5154,7 +5154,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317113876343</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H165" t="n">
         <v>82306</v>
@@ -5212,7 +5212,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371208190918</v>
+        <v>4.10371255874634</v>
       </c>
       <c r="H167" t="n">
         <v>23476</v>
@@ -5270,7 +5270,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H169" t="n">
         <v>96105</v>
@@ -5328,7 +5328,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H171" t="n">
         <v>41159</v>
@@ -5386,7 +5386,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97043871879578</v>
+        <v>3.9704384803772</v>
       </c>
       <c r="H173" t="n">
         <v>185702</v>
@@ -5502,7 +5502,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152227401733</v>
+        <v>4.03152275085449</v>
       </c>
       <c r="H177" t="n">
         <v>101079</v>
@@ -5531,7 +5531,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156743049622</v>
+        <v>3.93156790733337</v>
       </c>
       <c r="H178" t="n">
         <v>219724</v>
@@ -5589,7 +5589,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="n">
-        <v>3.72888088226318</v>
+        <v>3.72888040542603</v>
       </c>
       <c r="H180" t="n">
         <v>212138</v>
@@ -5618,7 +5618,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H181" t="n">
         <v>119833</v>
@@ -5647,7 +5647,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502022743225</v>
+        <v>3.66502070426941</v>
       </c>
       <c r="H182" t="n">
         <v>239810</v>
@@ -5676,7 +5676,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280819892883</v>
+        <v>3.64280796051025</v>
       </c>
       <c r="H183" t="n">
         <v>201842</v>
@@ -5705,7 +5705,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389175415039</v>
+        <v>3.70389223098755</v>
       </c>
       <c r="H184" t="n">
         <v>128389</v>
@@ -5734,7 +5734,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H185" t="n">
         <v>173655</v>
@@ -5792,7 +5792,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332835197449</v>
       </c>
       <c r="H187" t="n">
         <v>126621</v>
@@ -5821,7 +5821,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000959396362</v>
+        <v>3.69000911712646</v>
       </c>
       <c r="H188" t="n">
         <v>175447</v>
@@ -5850,7 +5850,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224431991577</v>
+        <v>3.66224384307861</v>
       </c>
       <c r="H189" t="n">
         <v>128416</v>
@@ -5879,7 +5879,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H190" t="n">
         <v>329741</v>
@@ -5908,7 +5908,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276328086853</v>
+        <v>3.74276375770569</v>
       </c>
       <c r="H191" t="n">
         <v>217887</v>
@@ -5937,7 +5937,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055077552795</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H192" t="n">
         <v>103333</v>
@@ -5966,7 +5966,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332835197449</v>
       </c>
       <c r="H193" t="n">
         <v>167998</v>
@@ -6053,7 +6053,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113806724548</v>
+        <v>3.65113854408264</v>
       </c>
       <c r="H196" t="n">
         <v>131242</v>
@@ -6082,7 +6082,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502022743225</v>
+        <v>3.66502070426941</v>
       </c>
       <c r="H197" t="n">
         <v>103315</v>
@@ -6140,7 +6140,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H199" t="n">
         <v>78308</v>
@@ -6198,7 +6198,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.5817244052887</v>
+        <v>3.58172416687012</v>
       </c>
       <c r="H201" t="n">
         <v>105671</v>
@@ -6314,7 +6314,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="n">
-        <v>3.70666837692261</v>
+        <v>3.70666861534119</v>
       </c>
       <c r="H205" t="n">
         <v>112375</v>
@@ -6343,7 +6343,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660171508789</v>
+        <v>3.85660147666931</v>
       </c>
       <c r="H206" t="n">
         <v>205793</v>
@@ -6372,7 +6372,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046141624451</v>
+        <v>3.92046165466309</v>
       </c>
       <c r="H207" t="n">
         <v>198572</v>
@@ -6401,7 +6401,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156743049622</v>
+        <v>3.93156790733337</v>
       </c>
       <c r="H208" t="n">
         <v>48406</v>
@@ -6430,7 +6430,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.9648859500885</v>
+        <v>3.96488571166992</v>
       </c>
       <c r="H209" t="n">
         <v>111598</v>
@@ -6459,7 +6459,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.94822692871094</v>
+        <v>3.94822669029236</v>
       </c>
       <c r="H210" t="n">
         <v>182662</v>
@@ -6517,7 +6517,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.9426736831665</v>
+        <v>3.94267392158508</v>
       </c>
       <c r="H212" t="n">
         <v>122111</v>
@@ -6546,7 +6546,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547252655029</v>
+        <v>3.89547276496887</v>
       </c>
       <c r="H213" t="n">
         <v>134927</v>
@@ -6575,7 +6575,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8926956653595</v>
+        <v>3.89269638061523</v>
       </c>
       <c r="H214" t="n">
         <v>75318</v>
@@ -6604,7 +6604,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215472221375</v>
+        <v>3.86215400695801</v>
       </c>
       <c r="H215" t="n">
         <v>72762</v>
@@ -6691,7 +6691,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608227729797</v>
+        <v>3.77608156204224</v>
       </c>
       <c r="H218" t="n">
         <v>66379</v>
@@ -6720,7 +6720,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107045173645</v>
+        <v>3.80107116699219</v>
       </c>
       <c r="H219" t="n">
         <v>60701</v>
@@ -6807,7 +6807,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="n">
-        <v>3.75942230224609</v>
+        <v>3.75942254066467</v>
       </c>
       <c r="H222" t="n">
         <v>147024</v>
@@ -6865,7 +6865,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.7122220993042</v>
+        <v>3.71222138404846</v>
       </c>
       <c r="H224" t="n">
         <v>81364</v>
@@ -6894,7 +6894,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H225" t="n">
         <v>166084</v>
@@ -6923,7 +6923,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059664726257</v>
+        <v>3.62059617042542</v>
       </c>
       <c r="H226" t="n">
         <v>137226</v>
@@ -6952,7 +6952,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="n">
-        <v>3.62614846229553</v>
+        <v>3.62614870071411</v>
       </c>
       <c r="H227" t="n">
         <v>55700</v>
@@ -7010,7 +7010,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179225921631</v>
+        <v>3.43179178237915</v>
       </c>
       <c r="H229" t="n">
         <v>391920</v>
@@ -7039,7 +7039,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51508736610413</v>
+        <v>3.51508760452271</v>
       </c>
       <c r="H230" t="n">
         <v>158535</v>
@@ -7068,7 +7068,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007601737976</v>
+        <v>3.54007649421692</v>
       </c>
       <c r="H231" t="n">
         <v>177686</v>
@@ -7097,7 +7097,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897047996521</v>
+        <v>3.52897024154663</v>
       </c>
       <c r="H232" t="n">
         <v>53802</v>
@@ -7126,7 +7126,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400381088257</v>
+        <v>3.45400357246399</v>
       </c>
       <c r="H233" t="n">
         <v>47034</v>
@@ -7155,7 +7155,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="n">
-        <v>3.47066307067871</v>
+        <v>3.47066354751587</v>
       </c>
       <c r="H234" t="n">
         <v>111259</v>
@@ -7184,7 +7184,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.47621631622314</v>
+        <v>3.4762167930603</v>
       </c>
       <c r="H235" t="n">
         <v>66245</v>
@@ -7213,7 +7213,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398254394531</v>
+        <v>3.50398206710815</v>
       </c>
       <c r="H236" t="n">
         <v>83410</v>
@@ -7242,7 +7242,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842858314514</v>
+        <v>3.49842882156372</v>
       </c>
       <c r="H237" t="n">
         <v>59122</v>
@@ -7271,7 +7271,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174662590027</v>
+        <v>3.53174710273743</v>
       </c>
       <c r="H238" t="n">
         <v>110615</v>
@@ -7300,7 +7300,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732280731201</v>
+        <v>3.48732328414917</v>
       </c>
       <c r="H239" t="n">
         <v>109337</v>
@@ -7329,7 +7329,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057371139526</v>
+        <v>3.67057394981384</v>
       </c>
       <c r="H240" t="n">
         <v>90169</v>
@@ -7358,7 +7358,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389175415039</v>
+        <v>3.70389223098755</v>
       </c>
       <c r="H241" t="n">
         <v>121643</v>
@@ -7387,7 +7387,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050561904907</v>
+        <v>3.82050609588623</v>
       </c>
       <c r="H242" t="n">
         <v>97760</v>
@@ -7474,7 +7474,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H245" t="n">
         <v>194032</v>
@@ -7503,7 +7503,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608227729797</v>
+        <v>3.77608156204224</v>
       </c>
       <c r="H246" t="n">
         <v>85390</v>
@@ -7532,7 +7532,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H247" t="n">
         <v>110497</v>
@@ -7561,7 +7561,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161211013794</v>
       </c>
       <c r="H248" t="n">
         <v>128189</v>
@@ -7648,7 +7648,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154592514038</v>
+        <v>3.98154497146606</v>
       </c>
       <c r="H251" t="n">
         <v>198595</v>
@@ -7677,7 +7677,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H252" t="n">
         <v>83758</v>
@@ -7706,7 +7706,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98709774017334</v>
+        <v>3.9870982170105</v>
       </c>
       <c r="H253" t="n">
         <v>124841</v>
@@ -7735,7 +7735,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H254" t="n">
         <v>67846</v>
@@ -7793,7 +7793,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820399284363</v>
+        <v>3.99820351600647</v>
       </c>
       <c r="H256" t="n">
         <v>75406</v>
@@ -7822,7 +7822,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041721343994</v>
+        <v>4.02041673660278</v>
       </c>
       <c r="H257" t="n">
         <v>46248</v>
@@ -7851,7 +7851,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="n">
-        <v>4.04262924194336</v>
+        <v>4.04262828826904</v>
       </c>
       <c r="H258" t="n">
         <v>68035</v>
@@ -7996,7 +7996,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="n">
-        <v>4.13147735595703</v>
+        <v>4.13147783279419</v>
       </c>
       <c r="H263" t="n">
         <v>266804</v>
@@ -8112,7 +8112,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H267" t="n">
         <v>54101</v>
@@ -8141,7 +8141,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="n">
-        <v>4.15091323852539</v>
+        <v>4.15091276168823</v>
       </c>
       <c r="H268" t="n">
         <v>41601</v>
@@ -8170,7 +8170,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H269" t="n">
         <v>45733</v>
@@ -8228,7 +8228,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="n">
-        <v>4.12037229537964</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H271" t="n">
         <v>96672</v>
@@ -8315,7 +8315,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484079360962</v>
+        <v>4.06484127044678</v>
       </c>
       <c r="H274" t="n">
         <v>94442</v>
@@ -8344,7 +8344,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="n">
-        <v>4.03429985046387</v>
+        <v>4.03429937362671</v>
       </c>
       <c r="H275" t="n">
         <v>100684</v>
@@ -8373,7 +8373,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490888595581</v>
+        <v>3.91490840911865</v>
       </c>
       <c r="H276" t="n">
         <v>229142</v>
@@ -8402,7 +8402,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377945899963</v>
+        <v>3.95377969741821</v>
       </c>
       <c r="H277" t="n">
         <v>45852</v>
@@ -8460,7 +8460,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86493110656738</v>
+        <v>3.86492991447449</v>
       </c>
       <c r="H279" t="n">
         <v>46654</v>
@@ -8489,7 +8489,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933318138123</v>
+        <v>3.95933294296265</v>
       </c>
       <c r="H280" t="n">
         <v>55134</v>
@@ -8576,7 +8576,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H283" t="n">
         <v>61425</v>
@@ -8605,7 +8605,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H284" t="n">
         <v>71158</v>
@@ -8663,7 +8663,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594680786133</v>
+        <v>4.07594728469849</v>
       </c>
       <c r="H286" t="n">
         <v>167527</v>
@@ -8692,7 +8692,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G287" t="n">
-        <v>4.05373477935791</v>
+        <v>4.05373525619507</v>
       </c>
       <c r="H287" t="n">
         <v>78301</v>
@@ -8721,7 +8721,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="n">
-        <v>4.07039356231689</v>
+        <v>4.07039403915405</v>
       </c>
       <c r="H288" t="n">
         <v>67876</v>
@@ -8779,7 +8779,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H290" t="n">
         <v>349165</v>
@@ -8837,7 +8837,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="n">
-        <v>4.17867803573608</v>
+        <v>4.17867851257324</v>
       </c>
       <c r="H292" t="n">
         <v>61984</v>
@@ -8895,7 +8895,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317113876343</v>
+        <v>4.07317018508911</v>
       </c>
       <c r="H294" t="n">
         <v>80824</v>
@@ -8924,7 +8924,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="n">
-        <v>4.12037229537964</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H295" t="n">
         <v>85676</v>
@@ -8953,7 +8953,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.12037229537964</v>
+        <v>4.12037181854248</v>
       </c>
       <c r="H296" t="n">
         <v>91728</v>
@@ -8982,7 +8982,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594680786133</v>
+        <v>4.07594728469849</v>
       </c>
       <c r="H297" t="n">
         <v>154156</v>
@@ -9127,7 +9127,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.3369402885437</v>
+        <v>4.33694124221802</v>
       </c>
       <c r="H302" t="n">
         <v>287161</v>
@@ -9156,7 +9156,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.35360050201416</v>
+        <v>4.353600025177</v>
       </c>
       <c r="H303" t="n">
         <v>161681</v>
@@ -9243,7 +9243,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025928497314</v>
+        <v>4.37025833129883</v>
       </c>
       <c r="H306" t="n">
         <v>134817</v>
@@ -9272,7 +9272,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637664794922</v>
+        <v>4.35637712478638</v>
       </c>
       <c r="H307" t="n">
         <v>145037</v>
@@ -9301,7 +9301,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30084657669067</v>
+        <v>4.30084705352783</v>
       </c>
       <c r="H308" t="n">
         <v>223330</v>
@@ -9330,7 +9330,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="n">
-        <v>4.22310352325439</v>
+        <v>4.22310304641724</v>
       </c>
       <c r="H309" t="n">
         <v>193013</v>
@@ -9359,7 +9359,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="n">
-        <v>4.28696393966675</v>
+        <v>4.28696346282959</v>
       </c>
       <c r="H310" t="n">
         <v>169658</v>
@@ -9388,7 +9388,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917596817017</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H311" t="n">
         <v>289755</v>
@@ -9417,7 +9417,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134355545044</v>
+        <v>4.43134260177612</v>
       </c>
       <c r="H312" t="n">
         <v>618378</v>
@@ -9446,7 +9446,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188497543335</v>
+        <v>4.46188545227051</v>
       </c>
       <c r="H313" t="n">
         <v>304602</v>
@@ -9475,7 +9475,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G314" t="n">
-        <v>4.45355463027954</v>
+        <v>4.45355558395386</v>
       </c>
       <c r="H314" t="n">
         <v>193672</v>
@@ -9504,7 +9504,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="n">
-        <v>4.40913057327271</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H315" t="n">
         <v>158255</v>
@@ -9533,7 +9533,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H316" t="n">
         <v>367674</v>
@@ -9562,7 +9562,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="n">
-        <v>4.55351066589355</v>
+        <v>4.5535101890564</v>
       </c>
       <c r="H317" t="n">
         <v>460310</v>
@@ -9678,7 +9678,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H321" t="n">
         <v>141204</v>
@@ -9707,7 +9707,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="n">
-        <v>4.55351066589355</v>
+        <v>4.5535101890564</v>
       </c>
       <c r="H322" t="n">
         <v>95409</v>
@@ -9765,7 +9765,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685140609741</v>
+        <v>4.53685235977173</v>
       </c>
       <c r="H324" t="n">
         <v>98610</v>
@@ -9794,7 +9794,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.52574491500854</v>
+        <v>4.5257453918457</v>
       </c>
       <c r="H325" t="n">
         <v>265003</v>
@@ -9881,7 +9881,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132133483887</v>
+        <v>4.48132085800171</v>
       </c>
       <c r="H328" t="n">
         <v>165632</v>
@@ -9910,7 +9910,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="n">
-        <v>4.45910835266113</v>
+        <v>4.45910787582397</v>
       </c>
       <c r="H329" t="n">
         <v>312941</v>
@@ -9939,7 +9939,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G330" t="n">
-        <v>4.47021436691284</v>
+        <v>4.47021484375</v>
       </c>
       <c r="H330" t="n">
         <v>148997</v>
@@ -9968,7 +9968,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="n">
-        <v>4.40913057327271</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H331" t="n">
         <v>186216</v>
@@ -10171,7 +10171,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075626373291</v>
+        <v>4.50075674057007</v>
       </c>
       <c r="H338" t="n">
         <v>185305</v>
@@ -10287,7 +10287,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127593994141</v>
+        <v>4.58127641677856</v>
       </c>
       <c r="H342" t="n">
         <v>62152</v>
@@ -10316,7 +10316,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="n">
-        <v>4.61459398269653</v>
+        <v>4.61459445953369</v>
       </c>
       <c r="H343" t="n">
         <v>203327</v>
@@ -10374,7 +10374,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346622467041</v>
+        <v>4.65346574783325</v>
       </c>
       <c r="H345" t="n">
         <v>177286</v>
@@ -10461,7 +10461,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895233154297</v>
+        <v>4.80895137786865</v>
       </c>
       <c r="H348" t="n">
         <v>235964</v>
@@ -10490,7 +10490,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H349" t="n">
         <v>172083</v>
@@ -10519,7 +10519,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.87836503982544</v>
+        <v>4.8783655166626</v>
       </c>
       <c r="H350" t="n">
         <v>140823</v>
@@ -10548,7 +10548,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782266616821</v>
+        <v>4.84782314300537</v>
       </c>
       <c r="H351" t="n">
         <v>122329</v>
@@ -10577,7 +10577,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010183334351</v>
+        <v>4.72010231018066</v>
       </c>
       <c r="H352" t="n">
         <v>291161</v>
@@ -10606,7 +10606,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="n">
-        <v>4.69233703613281</v>
+        <v>4.69233655929565</v>
       </c>
       <c r="H353" t="n">
         <v>196081</v>
@@ -10635,7 +10635,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="n">
-        <v>4.65901899337769</v>
+        <v>4.65901851654053</v>
       </c>
       <c r="H354" t="n">
         <v>271037</v>
@@ -10693,7 +10693,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865795135498</v>
+        <v>4.73865747451782</v>
       </c>
       <c r="H356" t="n">
         <v>265806</v>
@@ -10722,7 +10722,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H357" t="n">
         <v>212034</v>
@@ -10751,7 +10751,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H358" t="n">
         <v>157901</v>
@@ -10780,7 +10780,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H359" t="n">
         <v>148993</v>
@@ -10809,7 +10809,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865795135498</v>
+        <v>4.73865747451782</v>
       </c>
       <c r="H360" t="n">
         <v>158526</v>
@@ -10896,7 +10896,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H363" t="n">
         <v>258831</v>
@@ -10925,7 +10925,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83618354797363</v>
+        <v>4.83618450164795</v>
       </c>
       <c r="H364" t="n">
         <v>244646</v>
@@ -10954,7 +10954,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="n">
-        <v>4.79315853118896</v>
+        <v>4.79315805435181</v>
       </c>
       <c r="H365" t="n">
         <v>146539</v>
@@ -10983,7 +10983,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602670669556</v>
       </c>
       <c r="H366" t="n">
         <v>77359</v>
@@ -11041,7 +11041,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H368" t="n">
         <v>114636</v>
@@ -11070,7 +11070,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H369" t="n">
         <v>54213</v>
@@ -11128,7 +11128,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="n">
-        <v>4.76734209060669</v>
+        <v>4.76734256744385</v>
       </c>
       <c r="H371" t="n">
         <v>59047</v>
@@ -11157,7 +11157,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H372" t="n">
         <v>148350</v>
@@ -11186,7 +11186,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571063995361</v>
       </c>
       <c r="H373" t="n">
         <v>190474</v>
@@ -11302,7 +11302,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="n">
-        <v>4.60384178161621</v>
+        <v>4.60384082794189</v>
       </c>
       <c r="H377" t="n">
         <v>76641</v>
@@ -11331,7 +11331,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="n">
-        <v>4.58376216888428</v>
+        <v>4.58376264572144</v>
       </c>
       <c r="H378" t="n">
         <v>95959</v>
@@ -11418,7 +11418,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655168533325</v>
+        <v>4.56655120849609</v>
       </c>
       <c r="H381" t="n">
         <v>80390</v>
@@ -11447,7 +11447,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="n">
-        <v>4.49770832061768</v>
+        <v>4.49770879745483</v>
       </c>
       <c r="H382" t="n">
         <v>132223</v>
@@ -11476,7 +11476,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37436676025391</v>
+        <v>4.37436628341675</v>
       </c>
       <c r="H383" t="n">
         <v>168248</v>
@@ -11563,7 +11563,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786706924438</v>
+        <v>4.53786754608154</v>
       </c>
       <c r="H386" t="n">
         <v>105901</v>
@@ -11621,7 +11621,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476196289062</v>
+        <v>4.47476148605347</v>
       </c>
       <c r="H388" t="n">
         <v>139029</v>
@@ -11737,7 +11737,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66120958328247</v>
+        <v>4.66121006011963</v>
       </c>
       <c r="H392" t="n">
         <v>102329</v>
@@ -11766,7 +11766,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H393" t="n">
         <v>165524</v>
@@ -11795,7 +11795,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="n">
-        <v>4.7644739151001</v>
+        <v>4.76447296142578</v>
       </c>
       <c r="H394" t="n">
         <v>83113</v>
@@ -11824,7 +11824,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H395" t="n">
         <v>98585</v>
@@ -11853,7 +11853,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H396" t="n">
         <v>93726</v>
@@ -11882,7 +11882,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="n">
-        <v>4.76160526275635</v>
+        <v>4.76160478591919</v>
       </c>
       <c r="H397" t="n">
         <v>136912</v>
@@ -11911,7 +11911,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="n">
-        <v>4.79315853118896</v>
+        <v>4.79315805435181</v>
       </c>
       <c r="H398" t="n">
         <v>177747</v>
@@ -11998,7 +11998,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602670669556</v>
       </c>
       <c r="H401" t="n">
         <v>142867</v>
@@ -12056,7 +12056,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602670669556</v>
       </c>
       <c r="H403" t="n">
         <v>128308</v>
@@ -12114,7 +12114,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="n">
-        <v>4.73292112350464</v>
+        <v>4.7329216003418</v>
       </c>
       <c r="H405" t="n">
         <v>130388</v>
@@ -12143,7 +12143,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H406" t="n">
         <v>170600</v>
@@ -12230,7 +12230,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.7960262298584</v>
+        <v>4.79602670669556</v>
       </c>
       <c r="H409" t="n">
         <v>386315</v>
@@ -12259,7 +12259,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757949829102</v>
+        <v>4.82757997512817</v>
       </c>
       <c r="H410" t="n">
         <v>233195</v>
@@ -12317,7 +12317,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="n">
-        <v>4.87060594558716</v>
+        <v>4.87060546875</v>
       </c>
       <c r="H412" t="n">
         <v>185451</v>
@@ -12375,7 +12375,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H414" t="n">
         <v>223989</v>
@@ -12404,7 +12404,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="n">
-        <v>4.81036853790283</v>
+        <v>4.81036901473999</v>
       </c>
       <c r="H415" t="n">
         <v>168442</v>
@@ -12433,7 +12433,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H416" t="n">
         <v>400107</v>
@@ -12491,7 +12491,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="n">
-        <v>4.93084239959717</v>
+        <v>4.93084287643433</v>
       </c>
       <c r="H418" t="n">
         <v>170401</v>
@@ -12549,7 +12549,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="n">
-        <v>4.90215826034546</v>
+        <v>4.90215873718262</v>
       </c>
       <c r="H420" t="n">
         <v>122570</v>
@@ -12607,7 +12607,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="n">
-        <v>4.93371105194092</v>
+        <v>4.93371200561523</v>
       </c>
       <c r="H422" t="n">
         <v>38701</v>
@@ -12723,7 +12723,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H426" t="n">
         <v>53465</v>
@@ -12752,7 +12752,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="n">
-        <v>4.8017635345459</v>
+        <v>4.80176305770874</v>
       </c>
       <c r="H427" t="n">
         <v>143513</v>
@@ -12868,7 +12868,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="n">
-        <v>4.81897354125977</v>
+        <v>4.81897401809692</v>
       </c>
       <c r="H431" t="n">
         <v>59100</v>
@@ -12897,7 +12897,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="n">
-        <v>4.81897354125977</v>
+        <v>4.81897401809692</v>
       </c>
       <c r="H432" t="n">
         <v>85576</v>
@@ -12926,7 +12926,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="n">
-        <v>4.8390531539917</v>
+        <v>4.83905363082886</v>
       </c>
       <c r="H433" t="n">
         <v>35013</v>
@@ -12955,7 +12955,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.88781642913818</v>
+        <v>4.88781690597534</v>
       </c>
       <c r="H434" t="n">
         <v>180331</v>
@@ -13129,7 +13129,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="n">
-        <v>5.05418634414673</v>
+        <v>5.05418586730957</v>
       </c>
       <c r="H440" t="n">
         <v>88520</v>
@@ -13187,7 +13187,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99108028411865</v>
+        <v>4.99107980728149</v>
       </c>
       <c r="H442" t="n">
         <v>93886</v>
@@ -13216,7 +13216,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H443" t="n">
         <v>69536</v>
@@ -13245,7 +13245,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255393981934</v>
+        <v>5.00255346298218</v>
       </c>
       <c r="H444" t="n">
         <v>82992</v>
@@ -13274,7 +13274,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673797607422</v>
       </c>
       <c r="H445" t="n">
         <v>104775</v>
@@ -13332,7 +13332,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="n">
-        <v>5.01115894317627</v>
+        <v>5.01115989685059</v>
       </c>
       <c r="H447" t="n">
         <v>39929</v>
@@ -13390,7 +13390,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="n">
-        <v>5.0656590461731</v>
+        <v>5.06565952301025</v>
       </c>
       <c r="H449" t="n">
         <v>114555</v>
@@ -13448,7 +13448,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.0771336555481</v>
+        <v>5.07713317871094</v>
       </c>
       <c r="H451" t="n">
         <v>127366</v>
@@ -13506,7 +13506,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="n">
-        <v>4.96813249588013</v>
+        <v>4.96813297271729</v>
       </c>
       <c r="H453" t="n">
         <v>121584</v>
@@ -13564,7 +13564,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="n">
-        <v>5.03123760223389</v>
+        <v>5.0312385559082</v>
       </c>
       <c r="H455" t="n">
         <v>77579</v>
@@ -13651,7 +13651,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923896789551</v>
+        <v>5.24923849105835</v>
       </c>
       <c r="H458" t="n">
         <v>199889</v>
@@ -13738,7 +13738,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871398925781</v>
+        <v>5.47871446609497</v>
       </c>
       <c r="H461" t="n">
         <v>90087</v>
@@ -13825,7 +13825,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397743225098</v>
+        <v>5.36397695541382</v>
       </c>
       <c r="H464" t="n">
         <v>416344</v>
@@ -13883,7 +13883,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="n">
-        <v>5.39266157150269</v>
+        <v>5.39266109466553</v>
       </c>
       <c r="H466" t="n">
         <v>156702</v>
@@ -13912,7 +13912,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="n">
-        <v>5.30947589874268</v>
+        <v>5.30947637557983</v>
       </c>
       <c r="H467" t="n">
         <v>337168</v>
@@ -13941,7 +13941,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118696212769</v>
+        <v>5.38118743896484</v>
       </c>
       <c r="H468" t="n">
         <v>235300</v>
@@ -13999,7 +13999,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384717941284</v>
+        <v>5.69384765625</v>
       </c>
       <c r="H470" t="n">
         <v>1020120</v>
@@ -14057,7 +14057,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="n">
-        <v>5.98356008529663</v>
+        <v>5.98355960845947</v>
       </c>
       <c r="H472" t="n">
         <v>839604</v>
@@ -14086,7 +14086,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208547592163</v>
+        <v>5.97208642959595</v>
       </c>
       <c r="H473" t="n">
         <v>582524</v>
@@ -14173,7 +14173,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766450881958</v>
+        <v>5.93766498565674</v>
       </c>
       <c r="H476" t="n">
         <v>309094</v>
@@ -14202,7 +14202,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292652130127</v>
+        <v>5.82292604446411</v>
       </c>
       <c r="H477" t="n">
         <v>320356</v>
@@ -14260,7 +14260,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="n">
-        <v>5.76555776596069</v>
+        <v>5.76555824279785</v>
       </c>
       <c r="H479" t="n">
         <v>231042</v>
@@ -14318,7 +14318,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="n">
-        <v>5.79424238204956</v>
+        <v>5.79424285888672</v>
       </c>
       <c r="H481" t="n">
         <v>340167</v>
@@ -14347,7 +14347,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.06961250305176</v>
+        <v>6.06961297988892</v>
       </c>
       <c r="H482" t="n">
         <v>514848</v>
@@ -14405,7 +14405,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.06961250305176</v>
+        <v>6.06961297988892</v>
       </c>
       <c r="H484" t="n">
         <v>197193</v>
@@ -14492,7 +14492,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H487" t="n">
         <v>223944</v>
@@ -14579,7 +14579,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="n">
-        <v>6.24171829223633</v>
+        <v>6.24171924591064</v>
       </c>
       <c r="H490" t="n">
         <v>199304</v>
@@ -14637,7 +14637,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="n">
-        <v>6.17861270904541</v>
+        <v>6.17861318588257</v>
       </c>
       <c r="H492" t="n">
         <v>176102</v>
@@ -14666,7 +14666,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371788024902</v>
+        <v>6.02371692657471</v>
       </c>
       <c r="H493" t="n">
         <v>167344</v>
@@ -14695,7 +14695,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.06961250305176</v>
+        <v>6.06961297988892</v>
       </c>
       <c r="H494" t="n">
         <v>134266</v>
@@ -14724,7 +14724,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="n">
-        <v>6.16140222549438</v>
+        <v>6.16140270233154</v>
       </c>
       <c r="H495" t="n">
         <v>110811</v>
@@ -14753,7 +14753,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="n">
-        <v>6.13271808624268</v>
+        <v>6.13271760940552</v>
       </c>
       <c r="H496" t="n">
         <v>108347</v>
@@ -14811,7 +14811,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36793041229248</v>
+        <v>6.36793088912964</v>
       </c>
       <c r="H498" t="n">
         <v>358977</v>
@@ -14840,7 +14840,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645627975464</v>
+        <v>6.35645580291748</v>
       </c>
       <c r="H499" t="n">
         <v>283557</v>
@@ -14927,7 +14927,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.4252986907959</v>
+        <v>6.42529916763306</v>
       </c>
       <c r="H502" t="n">
         <v>210048</v>
@@ -14985,7 +14985,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734748840332</v>
+        <v>5.85734796524048</v>
       </c>
       <c r="H504" t="n">
         <v>968569</v>
@@ -15043,7 +15043,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.5647668838501</v>
+        <v>5.56476783752441</v>
       </c>
       <c r="H506" t="n">
         <v>358726</v>
@@ -15072,7 +15072,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="n">
-        <v>5.60492515563965</v>
+        <v>5.60492467880249</v>
       </c>
       <c r="H507" t="n">
         <v>138334</v>
@@ -15101,7 +15101,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.48158311843872</v>
+        <v>5.48158264160156</v>
       </c>
       <c r="H508" t="n">
         <v>285423</v>
@@ -15188,7 +15188,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034639358521</v>
+        <v>5.53034687042236</v>
       </c>
       <c r="H511" t="n">
         <v>118130</v>
@@ -15217,7 +15217,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460908889771</v>
+        <v>5.52460861206055</v>
       </c>
       <c r="H512" t="n">
         <v>137903</v>
@@ -15246,7 +15246,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.5647668838501</v>
+        <v>5.56476783752441</v>
       </c>
       <c r="H513" t="n">
         <v>146003</v>
@@ -15304,7 +15304,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655708312988</v>
+        <v>5.65655755996704</v>
       </c>
       <c r="H515" t="n">
         <v>86233</v>
@@ -15362,7 +15362,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="n">
-        <v>5.74834775924683</v>
+        <v>5.74834728240967</v>
       </c>
       <c r="H517" t="n">
         <v>220803</v>
@@ -15391,7 +15391,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="n">
-        <v>5.71966218948364</v>
+        <v>5.7196626663208</v>
       </c>
       <c r="H518" t="n">
         <v>305356</v>
@@ -15420,7 +15420,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903053283691</v>
+        <v>5.55903100967407</v>
       </c>
       <c r="H519" t="n">
         <v>232788</v>
@@ -15478,7 +15478,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345245361328</v>
+        <v>5.59345149993896</v>
       </c>
       <c r="H521" t="n">
         <v>134956</v>
@@ -15507,7 +15507,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H522" t="n">
         <v>131888</v>
@@ -15652,7 +15652,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329370498657</v>
+        <v>5.55329322814941</v>
       </c>
       <c r="H527" t="n">
         <v>178839</v>
@@ -15681,7 +15681,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.495924949646</v>
+        <v>5.49592542648315</v>
       </c>
       <c r="H528" t="n">
         <v>109874</v>
@@ -15710,7 +15710,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871398925781</v>
+        <v>5.47871446609497</v>
       </c>
       <c r="H529" t="n">
         <v>108597</v>
@@ -15826,7 +15826,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="n">
-        <v>5.39266157150269</v>
+        <v>5.39266109466553</v>
       </c>
       <c r="H533" t="n">
         <v>107752</v>
@@ -15884,7 +15884,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171194076538</v>
+        <v>5.15171241760254</v>
       </c>
       <c r="H535" t="n">
         <v>131851</v>
@@ -15913,7 +15913,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="n">
-        <v>5.03123760223389</v>
+        <v>5.0312385559082</v>
       </c>
       <c r="H536" t="n">
         <v>159220</v>
@@ -15942,7 +15942,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="n">
-        <v>4.97386884689331</v>
+        <v>4.97386837005615</v>
       </c>
       <c r="H537" t="n">
         <v>233015</v>
@@ -15971,7 +15971,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="n">
-        <v>5.12302875518799</v>
+        <v>5.12302827835083</v>
       </c>
       <c r="H538" t="n">
         <v>107280</v>
@@ -16000,7 +16000,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913228988647</v>
+        <v>4.85913181304932</v>
       </c>
       <c r="H539" t="n">
         <v>191289</v>
@@ -16087,7 +16087,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="n">
-        <v>4.49770832061768</v>
+        <v>4.49770879745483</v>
       </c>
       <c r="H542" t="n">
         <v>312675</v>
@@ -16116,7 +16116,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439430236816</v>
+        <v>4.74439477920532</v>
       </c>
       <c r="H543" t="n">
         <v>179153</v>
@@ -16145,7 +16145,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H544" t="n">
         <v>158012</v>
@@ -16174,7 +16174,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="n">
-        <v>4.82471179962158</v>
+        <v>4.82471132278442</v>
       </c>
       <c r="H545" t="n">
         <v>123266</v>
@@ -16203,7 +16203,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849967956543</v>
+        <v>4.69849872589111</v>
       </c>
       <c r="H546" t="n">
         <v>190634</v>
@@ -16232,7 +16232,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307796478271</v>
+        <v>4.77307844161987</v>
       </c>
       <c r="H547" t="n">
         <v>100189</v>
@@ -16290,7 +16290,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239566802979</v>
+        <v>4.96239519119263</v>
       </c>
       <c r="H549" t="n">
         <v>263540</v>
@@ -16319,7 +16319,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.7157096862793</v>
+        <v>4.71571063995361</v>
       </c>
       <c r="H550" t="n">
         <v>314139</v>
@@ -16348,7 +16348,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="n">
-        <v>4.58949899673462</v>
+        <v>4.58949851989746</v>
       </c>
       <c r="H551" t="n">
         <v>187834</v>
@@ -16377,7 +16377,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="n">
-        <v>4.62564086914062</v>
+        <v>4.62564134597778</v>
       </c>
       <c r="H552" t="n">
         <v>201959</v>
@@ -16406,7 +16406,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="n">
-        <v>4.54245662689209</v>
+        <v>4.54245615005493</v>
       </c>
       <c r="H553" t="n">
         <v>199605</v>
@@ -16435,7 +16435,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="n">
-        <v>4.42657136917114</v>
+        <v>4.42657089233398</v>
       </c>
       <c r="H554" t="n">
         <v>163330</v>
@@ -16464,7 +16464,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="n">
-        <v>4.31986618041992</v>
+        <v>4.31986665725708</v>
       </c>
       <c r="H555" t="n">
         <v>182195</v>
@@ -16551,7 +16551,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057697296143</v>
+        <v>4.50057744979858</v>
       </c>
       <c r="H558" t="n">
         <v>119113</v>
@@ -16580,7 +16580,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401973724365</v>
+        <v>4.50401926040649</v>
       </c>
       <c r="H559" t="n">
         <v>186947</v>
@@ -16638,7 +16638,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="n">
-        <v>4.33937072753906</v>
+        <v>4.33937120437622</v>
       </c>
       <c r="H561" t="n">
         <v>283553</v>
@@ -16667,7 +16667,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="n">
-        <v>4.3537130355835</v>
+        <v>4.35371351242065</v>
       </c>
       <c r="H562" t="n">
         <v>116896</v>
@@ -16725,7 +16725,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430730819702</v>
+        <v>4.21430683135986</v>
       </c>
       <c r="H564" t="n">
         <v>433130</v>
@@ -16783,7 +16783,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732343673706</v>
+        <v>4.32732439041138</v>
       </c>
       <c r="H566" t="n">
         <v>299973</v>
@@ -16870,7 +16870,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="n">
-        <v>4.14259624481201</v>
+        <v>4.14259672164917</v>
       </c>
       <c r="H569" t="n">
         <v>904299</v>
@@ -16899,7 +16899,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449653625488</v>
+        <v>4.04449605941772</v>
       </c>
       <c r="H570" t="n">
         <v>630273</v>
@@ -16928,7 +16928,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.4123272895813</v>
+        <v>4.41232681274414</v>
       </c>
       <c r="H571" t="n">
         <v>1211216</v>
@@ -16986,7 +16986,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="n">
-        <v>4.92329263687134</v>
+        <v>4.9232931137085</v>
       </c>
       <c r="H573" t="n">
         <v>1058195</v>
@@ -17102,7 +17102,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="n">
-        <v>5.15902805328369</v>
+        <v>5.15902853012085</v>
       </c>
       <c r="H577" t="n">
         <v>736664</v>
@@ -17131,7 +17131,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="n">
-        <v>5.0967001914978</v>
+        <v>5.09670066833496</v>
       </c>
       <c r="H578" t="n">
         <v>512001</v>
@@ -17189,7 +17189,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628034591675</v>
+        <v>4.83628082275391</v>
       </c>
       <c r="H580" t="n">
         <v>645972</v>
@@ -17305,7 +17305,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H584" t="n">
         <v>346291</v>
@@ -17421,7 +17421,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84923982620239</v>
+        <v>4.84924030303955</v>
       </c>
       <c r="H588" t="n">
         <v>752626</v>
@@ -17566,7 +17566,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="n">
-        <v>4.75235414505005</v>
+        <v>4.75235366821289</v>
       </c>
       <c r="H593" t="n">
         <v>307986</v>
@@ -17624,7 +17624,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="n">
-        <v>4.84862232208252</v>
+        <v>4.84862279891968</v>
       </c>
       <c r="H595" t="n">
         <v>284775</v>
@@ -17711,7 +17711,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="n">
-        <v>4.93686962127686</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H598" t="n">
         <v>231247</v>
@@ -17740,7 +17740,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132905960083</v>
+        <v>4.88132953643799</v>
       </c>
       <c r="H599" t="n">
         <v>300176</v>
@@ -17798,7 +17798,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>4.89120292663574</v>
+        <v>4.8912034034729</v>
       </c>
       <c r="H601" t="n">
         <v>368002</v>
@@ -17827,7 +17827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029081344604</v>
+        <v>5.06029033660889</v>
       </c>
       <c r="H602" t="n">
         <v>586567</v>
@@ -17856,7 +17856,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031999588013</v>
+        <v>4.96031904220581</v>
       </c>
       <c r="H603" t="n">
         <v>320650</v>
@@ -17885,7 +17885,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="n">
-        <v>4.93686962127686</v>
+        <v>4.9368691444397</v>
       </c>
       <c r="H604" t="n">
         <v>278602</v>
@@ -17943,7 +17943,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086734771729</v>
+        <v>4.77086639404297</v>
       </c>
       <c r="H606" t="n">
         <v>413652</v>
@@ -18001,7 +18001,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>4.66472387313843</v>
+        <v>4.66472482681274</v>
       </c>
       <c r="H608" t="n">
         <v>204562</v>
@@ -18030,7 +18030,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>4.61288642883301</v>
+        <v>4.61288738250732</v>
       </c>
       <c r="H609" t="n">
         <v>290843</v>
@@ -18059,7 +18059,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.56660413742065</v>
+        <v>4.56660461425781</v>
       </c>
       <c r="H610" t="n">
         <v>544954</v>
@@ -18088,7 +18088,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="n">
-        <v>4.54870748519897</v>
+        <v>4.54870796203613</v>
       </c>
       <c r="H611" t="n">
         <v>252215</v>
@@ -18117,7 +18117,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>4.49872255325317</v>
+        <v>4.49872207641602</v>
       </c>
       <c r="H612" t="n">
         <v>411982</v>
@@ -18175,7 +18175,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>4.17473983764648</v>
+        <v>4.17474031448364</v>
       </c>
       <c r="H614" t="n">
         <v>685007</v>
@@ -18233,7 +18233,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="n">
-        <v>4.48884868621826</v>
+        <v>4.4888482093811</v>
       </c>
       <c r="H616" t="n">
         <v>397528</v>
@@ -18320,7 +18320,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.6499137878418</v>
+        <v>4.64991426467896</v>
       </c>
       <c r="H619" t="n">
         <v>270055</v>
@@ -18378,7 +18378,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.5190863609314</v>
+        <v>4.51908683776855</v>
       </c>
       <c r="H621" t="n">
         <v>353015</v>
@@ -18465,7 +18465,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="n">
-        <v>4.81534290313721</v>
+        <v>4.81534242630005</v>
       </c>
       <c r="H624" t="n">
         <v>341465</v>
@@ -18494,7 +18494,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716499328613</v>
+        <v>4.71716547012329</v>
       </c>
       <c r="H625" t="n">
         <v>188411</v>
@@ -18523,7 +18523,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="n">
-        <v>4.80870962142944</v>
+        <v>4.80870914459229</v>
       </c>
       <c r="H626" t="n">
         <v>203531</v>
@@ -18610,7 +18610,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="n">
-        <v>4.6262845993042</v>
+        <v>4.62628507614136</v>
       </c>
       <c r="H629" t="n">
         <v>314894</v>
@@ -18639,7 +18639,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="n">
-        <v>4.59311676025391</v>
+        <v>4.59311628341675</v>
       </c>
       <c r="H630" t="n">
         <v>231415</v>
@@ -18697,7 +18697,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.6899676322937</v>
+        <v>4.68996810913086</v>
       </c>
       <c r="H632" t="n">
         <v>571701</v>
@@ -18726,7 +18726,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="n">
-        <v>4.62164115905762</v>
+        <v>4.62164068222046</v>
       </c>
       <c r="H633" t="n">
         <v>306266</v>
@@ -18755,7 +18755,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353227615356</v>
       </c>
       <c r="H634" t="n">
         <v>220436</v>
@@ -18842,7 +18842,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.56525564193726</v>
+        <v>4.5652551651001</v>
       </c>
       <c r="H637" t="n">
         <v>293870</v>
@@ -18871,7 +18871,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="n">
-        <v>4.67471027374268</v>
+        <v>4.67470979690552</v>
       </c>
       <c r="H638" t="n">
         <v>310832</v>
@@ -18900,7 +18900,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H639" t="n">
         <v>277774</v>
@@ -18929,7 +18929,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="n">
-        <v>4.64353179931641</v>
+        <v>4.64353227615356</v>
       </c>
       <c r="H640" t="n">
         <v>196010</v>
@@ -18958,7 +18958,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60174036026001</v>
+        <v>4.60173988342285</v>
       </c>
       <c r="H641" t="n">
         <v>160144</v>
@@ -18987,7 +18987,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>4.74303674697876</v>
+        <v>4.7430362701416</v>
       </c>
       <c r="H642" t="n">
         <v>298183</v>
@@ -19074,7 +19074,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="n">
-        <v>4.65679883956909</v>
+        <v>4.65679979324341</v>
       </c>
       <c r="H645" t="n">
         <v>247525</v>
@@ -19161,7 +19161,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711563110352</v>
+        <v>4.72711610794067</v>
       </c>
       <c r="H648" t="n">
         <v>124423</v>
@@ -19248,7 +19248,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637233734131</v>
+        <v>4.87637138366699</v>
       </c>
       <c r="H651" t="n">
         <v>272806</v>
@@ -19306,7 +19306,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="n">
-        <v>4.8040657043457</v>
+        <v>4.80406522750854</v>
       </c>
       <c r="H653" t="n">
         <v>82622</v>
@@ -19393,7 +19393,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="n">
-        <v>4.80937242507935</v>
+        <v>4.80937337875366</v>
       </c>
       <c r="H656" t="n">
         <v>107726</v>
@@ -19422,7 +19422,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="n">
-        <v>4.6813440322876</v>
+        <v>4.68134450912476</v>
       </c>
       <c r="H657" t="n">
         <v>218824</v>
@@ -19509,7 +19509,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="n">
-        <v>4.76492786407471</v>
+        <v>4.76492738723755</v>
       </c>
       <c r="H660" t="n">
         <v>90031</v>
@@ -19567,7 +19567,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="n">
-        <v>4.66343355178833</v>
+        <v>4.66343307495117</v>
       </c>
       <c r="H662" t="n">
         <v>216850</v>
@@ -19625,7 +19625,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H664" t="n">
         <v>65498</v>
@@ -19683,7 +19683,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="n">
-        <v>4.58316659927368</v>
+        <v>4.58316612243652</v>
       </c>
       <c r="H666" t="n">
         <v>106623</v>
@@ -19712,7 +19712,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="n">
-        <v>4.50621700286865</v>
+        <v>4.50621652603149</v>
       </c>
       <c r="H667" t="n">
         <v>158816</v>
@@ -19770,7 +19770,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="n">
-        <v>4.38283061981201</v>
+        <v>4.38283109664917</v>
       </c>
       <c r="H669" t="n">
         <v>155550</v>
@@ -19799,7 +19799,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30588150024414</v>
+        <v>4.30588102340698</v>
       </c>
       <c r="H670" t="n">
         <v>224367</v>
@@ -19828,7 +19828,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="n">
-        <v>4.32445526123047</v>
+        <v>4.32445573806763</v>
       </c>
       <c r="H671" t="n">
         <v>112382</v>
@@ -19857,7 +19857,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.36027669906616</v>
+        <v>4.360276222229</v>
       </c>
       <c r="H672" t="n">
         <v>84392</v>
@@ -19973,7 +19973,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818765640259</v>
+        <v>4.37818717956543</v>
       </c>
       <c r="H676" t="n">
         <v>76513</v>
@@ -20031,7 +20031,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145421981812</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H678" t="n">
         <v>67624</v>
@@ -20060,7 +20060,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41135597229004</v>
+        <v>4.41135549545288</v>
       </c>
       <c r="H679" t="n">
         <v>86398</v>
@@ -20118,7 +20118,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="n">
-        <v>4.34767246246338</v>
+        <v>4.34767293930054</v>
       </c>
       <c r="H681" t="n">
         <v>198218</v>
@@ -20263,7 +20263,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="n">
-        <v>4.37089109420776</v>
+        <v>4.37089014053345</v>
       </c>
       <c r="H686" t="n">
         <v>63252</v>
@@ -20292,7 +20292,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818765640259</v>
+        <v>4.37818717956543</v>
       </c>
       <c r="H687" t="n">
         <v>314279</v>
@@ -20321,7 +20321,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>4.3516526222229</v>
+        <v>4.35165309906006</v>
       </c>
       <c r="H688" t="n">
         <v>96748</v>
@@ -20350,7 +20350,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="n">
-        <v>4.36558294296265</v>
+        <v>4.3655834197998</v>
       </c>
       <c r="H689" t="n">
         <v>46065</v>
@@ -20379,7 +20379,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="n">
-        <v>4.32710838317871</v>
+        <v>4.32710790634155</v>
       </c>
       <c r="H690" t="n">
         <v>84784</v>
@@ -20437,7 +20437,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="n">
-        <v>4.6156702041626</v>
+        <v>4.61567115783691</v>
       </c>
       <c r="H692" t="n">
         <v>604065</v>
@@ -20553,7 +20553,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392812728882</v>
       </c>
       <c r="H696" t="n">
         <v>221443</v>
@@ -20582,7 +20582,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392860412598</v>
+        <v>4.56392812728882</v>
       </c>
       <c r="H697" t="n">
         <v>91471</v>
@@ -20611,7 +20611,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="n">
-        <v>4.54469156265259</v>
+        <v>4.54469108581543</v>
       </c>
       <c r="H698" t="n">
         <v>102918</v>
@@ -20727,7 +20727,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966373443604</v>
+        <v>4.34966325759888</v>
       </c>
       <c r="H702" t="n">
         <v>84918</v>
@@ -20756,7 +20756,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010942459106</v>
+        <v>4.26010894775391</v>
       </c>
       <c r="H703" t="n">
         <v>227597</v>
@@ -20785,7 +20785,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H704" t="n">
         <v>120717</v>
@@ -20814,7 +20814,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.2455153465271</v>
+        <v>4.24551486968994</v>
       </c>
       <c r="H705" t="n">
         <v>110787</v>
@@ -20843,7 +20843,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984247207642</v>
+        <v>4.17984199523926</v>
       </c>
       <c r="H706" t="n">
         <v>112296</v>
@@ -20901,7 +20901,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>4.05645751953125</v>
+        <v>4.05645656585693</v>
       </c>
       <c r="H708" t="n">
         <v>219320</v>
@@ -20930,7 +20930,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599168777466</v>
+        <v>4.01599216461182</v>
       </c>
       <c r="H709" t="n">
         <v>198493</v>
@@ -20959,7 +20959,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312121391296</v>
+        <v>3.92312097549438</v>
       </c>
       <c r="H710" t="n">
         <v>281423</v>
@@ -21046,7 +21046,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648745536804</v>
       </c>
       <c r="H713" t="n">
         <v>179781</v>
@@ -21133,7 +21133,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>3.91051721572876</v>
+        <v>3.91051745414734</v>
       </c>
       <c r="H716" t="n">
         <v>111436</v>
@@ -21162,7 +21162,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026992797852</v>
+        <v>3.96026921272278</v>
       </c>
       <c r="H717" t="n">
         <v>50070</v>
@@ -21191,7 +21191,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>3.94700217247009</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H718" t="n">
         <v>149820</v>
@@ -21249,7 +21249,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>3.94700217247009</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H720" t="n">
         <v>47658</v>
@@ -21307,7 +21307,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="n">
-        <v>4.07105159759521</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H722" t="n">
         <v>119608</v>
@@ -21336,7 +21336,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="n">
-        <v>4.07105159759521</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H723" t="n">
         <v>51535</v>
@@ -21394,7 +21394,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="n">
-        <v>4.1460108757019</v>
+        <v>4.14601039886475</v>
       </c>
       <c r="H725" t="n">
         <v>144073</v>
@@ -21423,7 +21423,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>4.13871335983276</v>
+        <v>4.13871383666992</v>
       </c>
       <c r="H726" t="n">
         <v>205631</v>
@@ -21452,7 +21452,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>4.07237720489502</v>
+        <v>4.07237768173218</v>
       </c>
       <c r="H727" t="n">
         <v>83950</v>
@@ -21539,7 +21539,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="n">
-        <v>4.07237720489502</v>
+        <v>4.07237768173218</v>
       </c>
       <c r="H730" t="n">
         <v>186832</v>
@@ -21597,7 +21597,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="n">
-        <v>4.07635736465454</v>
+        <v>4.0763578414917</v>
       </c>
       <c r="H732" t="n">
         <v>64043</v>
@@ -21655,7 +21655,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="n">
-        <v>3.98216009140015</v>
+        <v>3.98216032981873</v>
       </c>
       <c r="H734" t="n">
         <v>67397</v>
@@ -21684,7 +21684,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.00604200363159</v>
+        <v>4.00604152679443</v>
       </c>
       <c r="H735" t="n">
         <v>123762</v>
@@ -21742,7 +21742,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766592979431</v>
+        <v>3.94766521453857</v>
       </c>
       <c r="H737" t="n">
         <v>105830</v>
@@ -21800,7 +21800,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260649681091</v>
+        <v>3.89260697364807</v>
       </c>
       <c r="H739" t="n">
         <v>160586</v>
@@ -21887,7 +21887,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503128051758</v>
+        <v>4.07503175735474</v>
       </c>
       <c r="H742" t="n">
         <v>132743</v>
@@ -21945,7 +21945,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05115032196045</v>
+        <v>4.05114984512329</v>
       </c>
       <c r="H744" t="n">
         <v>56164</v>
@@ -21974,7 +21974,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="n">
-        <v>4.04119968414307</v>
+        <v>4.04119920730591</v>
       </c>
       <c r="H745" t="n">
         <v>62982</v>
@@ -22032,7 +22032,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189409255981</v>
+        <v>3.90189337730408</v>
       </c>
       <c r="H747" t="n">
         <v>215638</v>
@@ -22090,7 +22090,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88730001449585</v>
+        <v>3.88730025291443</v>
       </c>
       <c r="H749" t="n">
         <v>111448</v>
@@ -22119,7 +22119,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.85214185714722</v>
+        <v>3.85214138031006</v>
       </c>
       <c r="H750" t="n">
         <v>141352</v>
@@ -22148,7 +22148,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811161994934</v>
+        <v>3.8581120967865</v>
       </c>
       <c r="H751" t="n">
         <v>63514</v>
@@ -22235,7 +22235,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219145774841</v>
+        <v>3.84219074249268</v>
       </c>
       <c r="H754" t="n">
         <v>195412</v>
@@ -22264,7 +22264,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.76789498329163</v>
+        <v>3.76789474487305</v>
       </c>
       <c r="H755" t="n">
         <v>266658</v>
@@ -22293,7 +22293,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.73737978935242</v>
+        <v>3.73738050460815</v>
       </c>
       <c r="H756" t="n">
         <v>138294</v>
@@ -22322,7 +22322,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="n">
-        <v>3.6484899520874</v>
+        <v>3.64848947525024</v>
       </c>
       <c r="H757" t="n">
         <v>182909</v>
@@ -22351,7 +22351,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.5794997215271</v>
+        <v>3.57949995994568</v>
       </c>
       <c r="H758" t="n">
         <v>159867</v>
@@ -22409,7 +22409,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205411911011</v>
+        <v>3.60205388069153</v>
       </c>
       <c r="H760" t="n">
         <v>153511</v>
@@ -22467,7 +22467,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="n">
-        <v>3.52046060562134</v>
+        <v>3.52046084403992</v>
       </c>
       <c r="H762" t="n">
         <v>171756</v>
@@ -22554,7 +22554,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="n">
-        <v>3.7625880241394</v>
+        <v>3.76258754730225</v>
       </c>
       <c r="H765" t="n">
         <v>242926</v>
@@ -22612,7 +22612,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="n">
-        <v>3.83821082115173</v>
+        <v>3.83821105957031</v>
       </c>
       <c r="H767" t="n">
         <v>70343</v>
@@ -22641,7 +22641,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.91980481147766</v>
+        <v>3.91980457305908</v>
       </c>
       <c r="H768" t="n">
         <v>165370</v>
@@ -22670,7 +22670,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587377548218</v>
+        <v>3.90587329864502</v>
       </c>
       <c r="H769" t="n">
         <v>117696</v>
@@ -22699,7 +22699,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444801330566</v>
+        <v>3.92444753646851</v>
       </c>
       <c r="H770" t="n">
         <v>82861</v>
@@ -22728,7 +22728,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>3.90056729316711</v>
+        <v>3.90056753158569</v>
       </c>
       <c r="H771" t="n">
         <v>149636</v>
@@ -22757,7 +22757,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479497909546</v>
+        <v>3.85479426383972</v>
       </c>
       <c r="H772" t="n">
         <v>112700</v>
@@ -22873,7 +22873,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91516089439392</v>
+        <v>3.9151611328125</v>
       </c>
       <c r="H776" t="n">
         <v>169016</v>
@@ -22902,7 +22902,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="n">
-        <v>3.87204241752625</v>
+        <v>3.87204217910767</v>
       </c>
       <c r="H777" t="n">
         <v>97481</v>
@@ -22931,7 +22931,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025026321411</v>
+        <v>3.83025097846985</v>
       </c>
       <c r="H778" t="n">
         <v>123544</v>
@@ -23018,7 +23018,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.07901191711426</v>
+        <v>4.0790114402771</v>
       </c>
       <c r="H781" t="n">
         <v>71053</v>
@@ -23047,7 +23047,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657495498657</v>
+        <v>4.16657543182373</v>
       </c>
       <c r="H782" t="n">
         <v>250025</v>
@@ -23076,7 +23076,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="n">
-        <v>4.13805055618286</v>
+        <v>4.1380500793457</v>
       </c>
       <c r="H783" t="n">
         <v>122859</v>
@@ -23134,7 +23134,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090208053589</v>
+        <v>4.10090303421021</v>
       </c>
       <c r="H785" t="n">
         <v>161482</v>
@@ -23192,7 +23192,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947631835938</v>
+        <v>4.11947679519653</v>
       </c>
       <c r="H787" t="n">
         <v>103841</v>
@@ -23279,7 +23279,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078345298767</v>
+        <v>3.99078416824341</v>
       </c>
       <c r="H790" t="n">
         <v>256263</v>
@@ -23308,7 +23308,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>3.91118121147156</v>
+        <v>3.9111807346344</v>
       </c>
       <c r="H791" t="n">
         <v>263702</v>
@@ -23337,7 +23337,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017048835754</v>
+        <v>3.98017024993896</v>
       </c>
       <c r="H792" t="n">
         <v>238621</v>
@@ -23366,7 +23366,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567584991455</v>
+        <v>3.94567561149597</v>
       </c>
       <c r="H793" t="n">
         <v>513739</v>
@@ -23395,7 +23395,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680424690247</v>
+        <v>3.98680400848389</v>
       </c>
       <c r="H794" t="n">
         <v>129600</v>
@@ -23482,7 +23482,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="n">
-        <v>4.07304096221924</v>
+        <v>4.0730414390564</v>
       </c>
       <c r="H797" t="n">
         <v>221439</v>
@@ -23511,7 +23511,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="n">
-        <v>4.07038736343384</v>
+        <v>4.070387840271</v>
       </c>
       <c r="H798" t="n">
         <v>126559</v>
@@ -23540,7 +23540,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>4.06640720367432</v>
+        <v>4.06640768051147</v>
       </c>
       <c r="H799" t="n">
         <v>186549</v>
@@ -23569,7 +23569,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>4.01665544509888</v>
+        <v>4.01665496826172</v>
       </c>
       <c r="H800" t="n">
         <v>103894</v>
@@ -23598,7 +23598,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>4.07105159759521</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H801" t="n">
         <v>96510</v>
@@ -23627,7 +23627,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13406991958618</v>
+        <v>4.13407039642334</v>
       </c>
       <c r="H802" t="n">
         <v>101135</v>
@@ -23685,7 +23685,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="n">
-        <v>4.10421848297119</v>
+        <v>4.10421895980835</v>
       </c>
       <c r="H804" t="n">
         <v>271028</v>
@@ -23743,7 +23743,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="n">
-        <v>4.184485912323</v>
+        <v>4.18448543548584</v>
       </c>
       <c r="H806" t="n">
         <v>224566</v>
@@ -23772,7 +23772,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="n">
-        <v>4.22030735015869</v>
+        <v>4.22030782699585</v>
       </c>
       <c r="H807" t="n">
         <v>192502</v>
@@ -23830,7 +23830,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="n">
-        <v>4.41334533691406</v>
+        <v>4.41334581375122</v>
       </c>
       <c r="H809" t="n">
         <v>326833</v>
@@ -23888,7 +23888,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H811" t="n">
         <v>155654</v>
@@ -23917,7 +23917,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531742095947</v>
+        <v>4.28531694412231</v>
       </c>
       <c r="H812" t="n">
         <v>82775</v>
@@ -23975,7 +23975,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="n">
-        <v>4.39609861373901</v>
+        <v>4.39609813690186</v>
       </c>
       <c r="H814" t="n">
         <v>210612</v>
@@ -24004,7 +24004,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="n">
-        <v>4.41666221618652</v>
+        <v>4.41666269302368</v>
       </c>
       <c r="H815" t="n">
         <v>132269</v>
@@ -24033,7 +24033,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="n">
-        <v>4.44717741012573</v>
+        <v>4.44717693328857</v>
       </c>
       <c r="H816" t="n">
         <v>261217</v>
@@ -24062,7 +24062,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759292602539</v>
+        <v>4.49759244918823</v>
       </c>
       <c r="H817" t="n">
         <v>195962</v>
@@ -24091,7 +24091,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>4.44452285766602</v>
+        <v>4.44452381134033</v>
       </c>
       <c r="H818" t="n">
         <v>210704</v>
@@ -24207,7 +24207,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="n">
-        <v>4.30057430267334</v>
+        <v>4.30057382583618</v>
       </c>
       <c r="H822" t="n">
         <v>93154</v>
@@ -24323,7 +24323,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27204942703247</v>
+        <v>4.27205038070679</v>
       </c>
       <c r="H826" t="n">
         <v>152125</v>
@@ -24410,7 +24410,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145421981812</v>
+        <v>4.39145469665527</v>
       </c>
       <c r="H829" t="n">
         <v>115908</v>
@@ -24439,7 +24439,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3980884552002</v>
+        <v>4.39808797836304</v>
       </c>
       <c r="H830" t="n">
         <v>151188</v>
@@ -24497,7 +24497,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>4.42462301254272</v>
+        <v>4.42462348937988</v>
       </c>
       <c r="H832" t="n">
         <v>126367</v>
@@ -24526,7 +24526,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.298583984375</v>
+        <v>4.29858446121216</v>
       </c>
       <c r="H833" t="n">
         <v>159721</v>
@@ -24555,7 +24555,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511806488037</v>
+        <v>4.32511854171753</v>
       </c>
       <c r="H834" t="n">
         <v>246478</v>
@@ -24700,7 +24700,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>4.45115756988525</v>
+        <v>4.4511570930481</v>
       </c>
       <c r="H839" t="n">
         <v>130935</v>
@@ -24729,7 +24729,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>4.45115756988525</v>
+        <v>4.4511570930481</v>
       </c>
       <c r="H840" t="n">
         <v>103647</v>
@@ -24816,7 +24816,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="n">
-        <v>4.44452285766602</v>
+        <v>4.44452381134033</v>
       </c>
       <c r="H843" t="n">
         <v>139329</v>
@@ -24845,7 +24845,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>4.41135597229004</v>
+        <v>4.41135549545288</v>
       </c>
       <c r="H844" t="n">
         <v>71545</v>
@@ -24990,7 +24990,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.44452285766602</v>
+        <v>4.44452381134033</v>
       </c>
       <c r="H849" t="n">
         <v>132031</v>
@@ -25019,7 +25019,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066204071045</v>
+        <v>4.55066156387329</v>
       </c>
       <c r="H850" t="n">
         <v>559275</v>
@@ -25077,7 +25077,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838605880737</v>
+        <v>4.33838558197021</v>
       </c>
       <c r="H852" t="n">
         <v>375070</v>
@@ -25135,7 +25135,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H854" t="n">
         <v>242614</v>
@@ -25164,7 +25164,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940948486328</v>
       </c>
       <c r="H855" t="n">
         <v>231782</v>
@@ -25309,7 +25309,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140827178955</v>
       </c>
       <c r="H860" t="n">
         <v>106622</v>
@@ -25483,7 +25483,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H866" t="n">
         <v>83940</v>
@@ -25512,7 +25512,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H867" t="n">
         <v>45354</v>
@@ -25570,7 +25570,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H869" t="n">
         <v>55460</v>
@@ -25599,7 +25599,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H870" t="n">
         <v>116258</v>
@@ -25686,7 +25686,7 @@
         <v>6.25</v>
       </c>
       <c r="G873" t="n">
-        <v>4.48529148101807</v>
+        <v>4.48529100418091</v>
       </c>
       <c r="H873" t="n">
         <v>112876</v>
@@ -25773,7 +25773,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H876" t="n">
         <v>88374</v>
@@ -25860,7 +25860,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G879" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H879" t="n">
         <v>122037</v>
@@ -25889,7 +25889,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G880" t="n">
-        <v>4.26999759674072</v>
+        <v>4.26999711990356</v>
       </c>
       <c r="H880" t="n">
         <v>200349</v>
@@ -26005,7 +26005,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>4.20541000366211</v>
+        <v>4.20540952682495</v>
       </c>
       <c r="H884" t="n">
         <v>123323</v>
@@ -26063,7 +26063,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H886" t="n">
         <v>115183</v>
@@ -26121,7 +26121,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G888" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H888" t="n">
         <v>214075</v>
@@ -26237,7 +26237,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H892" t="n">
         <v>101125</v>
@@ -26266,7 +26266,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H893" t="n">
         <v>56380</v>
@@ -26295,7 +26295,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H894" t="n">
         <v>80568</v>
@@ -26324,7 +26324,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H895" t="n">
         <v>65595</v>
@@ -26353,7 +26353,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H896" t="n">
         <v>44767</v>
@@ -26382,7 +26382,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H897" t="n">
         <v>139790</v>
@@ -26469,7 +26469,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H900" t="n">
         <v>82729</v>
@@ -26556,7 +26556,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H903" t="n">
         <v>213241</v>
@@ -26585,7 +26585,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G904" t="n">
-        <v>4.26999759674072</v>
+        <v>4.26999711990356</v>
       </c>
       <c r="H904" t="n">
         <v>79019</v>
@@ -26614,7 +26614,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H905" t="n">
         <v>82085</v>
@@ -26643,7 +26643,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G906" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H906" t="n">
         <v>211543</v>
@@ -26672,7 +26672,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>4.24846839904785</v>
+        <v>4.24846792221069</v>
       </c>
       <c r="H907" t="n">
         <v>62908</v>
@@ -26730,7 +26730,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129152297974</v>
+        <v>4.24129104614258</v>
       </c>
       <c r="H909" t="n">
         <v>98629</v>
@@ -26817,7 +26817,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H912" t="n">
         <v>162300</v>
@@ -26846,7 +26846,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776258468628</v>
+        <v>4.09776210784912</v>
       </c>
       <c r="H913" t="n">
         <v>213477</v>
@@ -26933,7 +26933,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H916" t="n">
         <v>220296</v>
@@ -27020,7 +27020,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246822357178</v>
+        <v>3.88246846199036</v>
       </c>
       <c r="H919" t="n">
         <v>159908</v>
@@ -27078,7 +27078,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764440536499</v>
+        <v>3.76764512062073</v>
       </c>
       <c r="H921" t="n">
         <v>137747</v>
@@ -27107,7 +27107,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764440536499</v>
+        <v>3.76764512062073</v>
       </c>
       <c r="H922" t="n">
         <v>222826</v>
@@ -27136,7 +27136,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81788015365601</v>
+        <v>3.81787991523743</v>
       </c>
       <c r="H923" t="n">
         <v>149116</v>
@@ -27165,7 +27165,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G924" t="n">
-        <v>3.76046848297119</v>
+        <v>3.76046824455261</v>
       </c>
       <c r="H924" t="n">
         <v>252954</v>
@@ -27194,7 +27194,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H925" t="n">
         <v>84785</v>
@@ -27223,7 +27223,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H926" t="n">
         <v>73998</v>
@@ -27281,7 +27281,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.7819972038269</v>
+        <v>3.78199768066406</v>
       </c>
       <c r="H928" t="n">
         <v>42652</v>
@@ -27310,7 +27310,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352759361267</v>
+        <v>3.80352735519409</v>
       </c>
       <c r="H929" t="n">
         <v>184164</v>
@@ -27339,7 +27339,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81788015365601</v>
+        <v>3.81787991523743</v>
       </c>
       <c r="H930" t="n">
         <v>183973</v>
@@ -27455,7 +27455,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658598899841</v>
+        <v>3.84658646583557</v>
       </c>
       <c r="H934" t="n">
         <v>135055</v>
@@ -27484,7 +27484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399789810181</v>
+        <v>3.90399765968323</v>
       </c>
       <c r="H935" t="n">
         <v>187953</v>
@@ -27513,7 +27513,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G936" t="n">
-        <v>3.9255268573761</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H936" t="n">
         <v>164174</v>
@@ -27542,7 +27542,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423316955566</v>
+        <v>3.95423340797424</v>
       </c>
       <c r="H937" t="n">
         <v>203686</v>
@@ -27658,7 +27658,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H941" t="n">
         <v>174524</v>
@@ -27716,7 +27716,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H943" t="n">
         <v>182425</v>
@@ -27745,7 +27745,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G944" t="n">
-        <v>3.96858620643616</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H944" t="n">
         <v>193559</v>
@@ -27774,7 +27774,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H945" t="n">
         <v>164084</v>
@@ -27803,7 +27803,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H946" t="n">
         <v>137576</v>
@@ -27861,7 +27861,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293900489807</v>
+        <v>3.98293852806091</v>
       </c>
       <c r="H948" t="n">
         <v>118564</v>
@@ -27890,7 +27890,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.96140956878662</v>
+        <v>3.9614098072052</v>
       </c>
       <c r="H949" t="n">
         <v>84704</v>
@@ -27919,7 +27919,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>3.96858620643616</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H950" t="n">
         <v>104322</v>
@@ -27948,7 +27948,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423316955566</v>
+        <v>3.95423340797424</v>
       </c>
       <c r="H951" t="n">
         <v>122102</v>
@@ -28064,7 +28064,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682054519653</v>
       </c>
       <c r="H955" t="n">
         <v>198731</v>
@@ -28093,7 +28093,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G956" t="n">
-        <v>3.9255268573761</v>
+        <v>3.92552661895752</v>
       </c>
       <c r="H956" t="n">
         <v>117055</v>
@@ -28122,7 +28122,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G957" t="n">
-        <v>3.96858620643616</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H957" t="n">
         <v>70802</v>
@@ -28180,7 +28180,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H959" t="n">
         <v>102747</v>
@@ -28267,7 +28267,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>4.08340930938721</v>
+        <v>4.08340883255005</v>
       </c>
       <c r="H962" t="n">
         <v>105538</v>
@@ -28354,7 +28354,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G965" t="n">
-        <v>4.11929130554199</v>
+        <v>4.11929178237915</v>
       </c>
       <c r="H965" t="n">
         <v>251112</v>
@@ -28412,7 +28412,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>4.14082145690918</v>
+        <v>4.14082098007202</v>
       </c>
       <c r="H967" t="n">
         <v>119981</v>
@@ -28470,7 +28470,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H969" t="n">
         <v>66738</v>
@@ -28499,7 +28499,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H970" t="n">
         <v>117936</v>
@@ -28557,7 +28557,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H972" t="n">
         <v>134175</v>
@@ -28586,7 +28586,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799737930298</v>
+        <v>4.14799785614014</v>
       </c>
       <c r="H973" t="n">
         <v>63185</v>
@@ -28615,7 +28615,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H974" t="n">
         <v>38961</v>
@@ -28644,7 +28644,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646865844727</v>
+        <v>4.12646770477295</v>
       </c>
       <c r="H975" t="n">
         <v>83904</v>
@@ -28702,7 +28702,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G977" t="n">
-        <v>4.16235017776489</v>
+        <v>4.16235065460205</v>
       </c>
       <c r="H977" t="n">
         <v>27675</v>
@@ -28731,7 +28731,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G978" t="n">
-        <v>4.22693824768066</v>
+        <v>4.22693872451782</v>
       </c>
       <c r="H978" t="n">
         <v>130439</v>
@@ -28760,7 +28760,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G979" t="n">
-        <v>4.25564479827881</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H979" t="n">
         <v>138951</v>
@@ -28789,7 +28789,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G980" t="n">
-        <v>4.25564479827881</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H980" t="n">
         <v>126747</v>
@@ -28818,7 +28818,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H981" t="n">
         <v>169971</v>
@@ -28847,7 +28847,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G982" t="n">
-        <v>4.25564479827881</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H982" t="n">
         <v>98272</v>
@@ -28876,7 +28876,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H983" t="n">
         <v>94635</v>
@@ -28934,7 +28934,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H985" t="n">
         <v>162590</v>
@@ -28992,7 +28992,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717351913452</v>
+        <v>4.27717399597168</v>
       </c>
       <c r="H987" t="n">
         <v>69784</v>
@@ -29021,7 +29021,7 @@
         <v>6</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30588006973267</v>
+        <v>4.30587959289551</v>
       </c>
       <c r="H988" t="n">
         <v>135917</v>
@@ -29050,7 +29050,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611534118652</v>
+        <v>4.35611486434937</v>
       </c>
       <c r="H989" t="n">
         <v>138068</v>
@@ -29108,7 +29108,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305646896362</v>
+        <v>4.31305599212646</v>
       </c>
       <c r="H991" t="n">
         <v>83600</v>
@@ -29195,7 +29195,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H994" t="n">
         <v>199251</v>
@@ -29224,7 +29224,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H995" t="n">
         <v>358111</v>
@@ -29282,7 +29282,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G997" t="n">
-        <v>4.62164402008057</v>
+        <v>4.62164449691772</v>
       </c>
       <c r="H997" t="n">
         <v>342817</v>
@@ -29311,7 +29311,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552675247192</v>
+        <v>4.53552722930908</v>
       </c>
       <c r="H998" t="n">
         <v>278924</v>
@@ -29427,7 +29427,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H1002" t="n">
         <v>62344</v>
@@ -29514,7 +29514,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940948486328</v>
       </c>
       <c r="H1005" t="n">
         <v>77356</v>
@@ -29543,7 +29543,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1006" t="n">
         <v>100264</v>
@@ -29601,7 +29601,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1008" t="n">
         <v>90036</v>
@@ -29659,7 +29659,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40635061264038</v>
+        <v>4.40635013580322</v>
       </c>
       <c r="H1010" t="n">
         <v>69927</v>
@@ -29804,7 +29804,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940948486328</v>
       </c>
       <c r="H1015" t="n">
         <v>125144</v>
@@ -29833,7 +29833,7 @@
         <v>6.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.48529148101807</v>
+        <v>4.48529100418091</v>
       </c>
       <c r="H1016" t="n">
         <v>85906</v>
@@ -29978,7 +29978,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505668640137</v>
+        <v>4.43505620956421</v>
       </c>
       <c r="H1021" t="n">
         <v>186708</v>
@@ -30007,7 +30007,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1022" t="n">
         <v>89368</v>
@@ -30094,7 +30094,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070341110229</v>
+        <v>4.42070293426514</v>
       </c>
       <c r="H1025" t="n">
         <v>56890</v>
@@ -30210,7 +30210,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940948486328</v>
       </c>
       <c r="H1029" t="n">
         <v>103178</v>
@@ -30268,7 +30268,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940900802612</v>
+        <v>4.44940948486328</v>
       </c>
       <c r="H1031" t="n">
         <v>101854</v>
@@ -30413,7 +30413,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H1036" t="n">
         <v>110854</v>
@@ -30442,7 +30442,7 @@
         <v>6</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.30588006973267</v>
+        <v>4.30587959289551</v>
       </c>
       <c r="H1037" t="n">
         <v>183171</v>
@@ -30500,7 +30500,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.39199686050415</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H1039" t="n">
         <v>164564</v>
@@ -30558,7 +30558,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.58576202392578</v>
+        <v>4.58576154708862</v>
       </c>
       <c r="H1041" t="n">
         <v>516270</v>
@@ -30732,7 +30732,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964427947998</v>
+        <v>4.49964380264282</v>
       </c>
       <c r="H1047" t="n">
         <v>186654</v>
@@ -30761,7 +30761,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.54270315170288</v>
+        <v>4.54270267486572</v>
       </c>
       <c r="H1048" t="n">
         <v>201438</v>
@@ -30790,7 +30790,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.55705642700195</v>
+        <v>4.55705595016479</v>
       </c>
       <c r="H1049" t="n">
         <v>136339</v>
@@ -30819,7 +30819,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140827178955</v>
       </c>
       <c r="H1050" t="n">
         <v>112242</v>
@@ -30935,7 +30935,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.11929130554199</v>
+        <v>4.11929178237915</v>
       </c>
       <c r="H1054" t="n">
         <v>386195</v>
@@ -30964,7 +30964,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952657699585</v>
       </c>
       <c r="H1055" t="n">
         <v>321443</v>
@@ -30993,7 +30993,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729156494141</v>
+        <v>3.99729204177856</v>
       </c>
       <c r="H1056" t="n">
         <v>475594</v>
@@ -31022,7 +31022,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399789810181</v>
+        <v>3.90399765968323</v>
       </c>
       <c r="H1057" t="n">
         <v>651281</v>
@@ -31051,7 +31051,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682102203369</v>
+        <v>3.89682054519653</v>
       </c>
       <c r="H1058" t="n">
         <v>494611</v>
@@ -31080,7 +31080,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.93987989425659</v>
+        <v>3.93987965583801</v>
       </c>
       <c r="H1059" t="n">
         <v>441063</v>
@@ -31109,7 +31109,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.91835045814514</v>
+        <v>3.91835069656372</v>
       </c>
       <c r="H1060" t="n">
         <v>289543</v>
@@ -31138,7 +31138,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505655288696</v>
+        <v>3.82505631446838</v>
       </c>
       <c r="H1061" t="n">
         <v>188804</v>
@@ -31167,7 +31167,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.78917479515076</v>
+        <v>3.7891743183136</v>
       </c>
       <c r="H1062" t="n">
         <v>297718</v>
@@ -31196,7 +31196,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.35858631134033</v>
+        <v>3.35858607292175</v>
       </c>
       <c r="H1063" t="n">
         <v>656502</v>
@@ -31225,7 +31225,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.26529240608215</v>
+        <v>3.26529264450073</v>
       </c>
       <c r="H1064" t="n">
         <v>468123</v>
@@ -31283,7 +31283,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299871444702</v>
+        <v>2.62299847602844</v>
       </c>
       <c r="H1066" t="n">
         <v>700650</v>
@@ -31312,7 +31312,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605734825134</v>
+        <v>2.66605710983276</v>
       </c>
       <c r="H1067" t="n">
         <v>497765</v>
@@ -31341,7 +31341,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076322555542</v>
+        <v>2.45076298713684</v>
       </c>
       <c r="H1068" t="n">
         <v>502127</v>
@@ -31370,7 +31370,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305726051331</v>
+        <v>2.48305749893188</v>
       </c>
       <c r="H1069" t="n">
         <v>316624</v>
@@ -31399,7 +31399,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1070" t="n">
         <v>294654</v>
@@ -31457,7 +31457,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682194709778</v>
+        <v>2.67682218551636</v>
       </c>
       <c r="H1072" t="n">
         <v>1041965</v>
@@ -31486,7 +31486,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.61223363876343</v>
+        <v>2.61223387718201</v>
       </c>
       <c r="H1073" t="n">
         <v>255816</v>
@@ -31515,7 +31515,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446912765503</v>
+        <v>2.78446888923645</v>
       </c>
       <c r="H1074" t="n">
         <v>219271</v>
@@ -31544,7 +31544,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.70911622047424</v>
+        <v>2.70911598205566</v>
       </c>
       <c r="H1075" t="n">
         <v>353763</v>
@@ -31573,7 +31573,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423361778259</v>
+        <v>2.73423385620117</v>
       </c>
       <c r="H1076" t="n">
         <v>156770</v>
@@ -31602,7 +31602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705698013306</v>
+        <v>2.72705721855164</v>
       </c>
       <c r="H1077" t="n">
         <v>193039</v>
@@ -31631,7 +31631,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.59070444107056</v>
+        <v>2.59070420265198</v>
       </c>
       <c r="H1078" t="n">
         <v>244939</v>
@@ -31660,7 +31660,7 @@
         <v>3.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.69117474555969</v>
+        <v>2.69117498397827</v>
       </c>
       <c r="H1079" t="n">
         <v>342391</v>
@@ -31689,7 +31689,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70552802085876</v>
+        <v>2.70552778244019</v>
       </c>
       <c r="H1080" t="n">
         <v>292596</v>
@@ -31747,7 +31747,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505723953247</v>
+        <v>2.60505747795105</v>
       </c>
       <c r="H1082" t="n">
         <v>90176</v>
@@ -31776,7 +31776,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1083" t="n">
         <v>180927</v>
@@ -32037,7 +32037,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.53688097000122</v>
+        <v>2.53688073158264</v>
       </c>
       <c r="H1092" t="n">
         <v>202956</v>
@@ -32066,7 +32066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329229354858</v>
       </c>
       <c r="H1093" t="n">
         <v>139451</v>
@@ -32385,7 +32385,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.50099849700928</v>
+        <v>2.5009982585907</v>
       </c>
       <c r="H1104" t="n">
         <v>172964</v>
@@ -32443,7 +32443,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.36823391914368</v>
+        <v>2.3682336807251</v>
       </c>
       <c r="H1106" t="n">
         <v>326150</v>
@@ -32472,7 +32472,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952784538269</v>
+        <v>2.33952808380127</v>
       </c>
       <c r="H1107" t="n">
         <v>248569</v>
@@ -32501,7 +32501,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.31082201004028</v>
+        <v>2.31082224845886</v>
       </c>
       <c r="H1108" t="n">
         <v>196343</v>
@@ -32559,7 +32559,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305726051331</v>
+        <v>2.48305749893188</v>
       </c>
       <c r="H1110" t="n">
         <v>311033</v>
@@ -32646,7 +32646,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652823448181</v>
+        <v>2.15652799606323</v>
       </c>
       <c r="H1113" t="n">
         <v>565839</v>
@@ -32675,7 +32675,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805767059326</v>
+        <v>2.17805743217468</v>
       </c>
       <c r="H1114" t="n">
         <v>231502</v>
@@ -32733,7 +32733,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.3610577583313</v>
+        <v>2.36105728149414</v>
       </c>
       <c r="H1116" t="n">
         <v>277343</v>
@@ -32820,7 +32820,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876348495483</v>
+        <v>2.32876300811768</v>
       </c>
       <c r="H1119" t="n">
         <v>437387</v>
@@ -32878,7 +32878,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.42564558982849</v>
+        <v>2.42564582824707</v>
       </c>
       <c r="H1121" t="n">
         <v>440602</v>
@@ -33023,7 +33023,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.70552802085876</v>
+        <v>2.70552778244019</v>
       </c>
       <c r="H1126" t="n">
         <v>328129</v>
@@ -33052,7 +33052,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864543914795</v>
       </c>
       <c r="H1127" t="n">
         <v>417942</v>
@@ -33081,7 +33081,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1128" t="n">
         <v>348708</v>
@@ -33139,7 +33139,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1130" t="n">
         <v>287875</v>
@@ -33255,7 +33255,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1134" t="n">
         <v>433647</v>
@@ -33313,7 +33313,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.47588109970093</v>
+        <v>2.47588086128235</v>
       </c>
       <c r="H1136" t="n">
         <v>150113</v>
@@ -33371,7 +33371,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.43999886512756</v>
+        <v>2.43999862670898</v>
       </c>
       <c r="H1138" t="n">
         <v>136490</v>
@@ -33400,7 +33400,7 @@
         <v>3.375</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.42205739021301</v>
+        <v>2.42205715179443</v>
       </c>
       <c r="H1139" t="n">
         <v>98220</v>
@@ -33429,7 +33429,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.49382209777832</v>
+        <v>2.49382162094116</v>
       </c>
       <c r="H1140" t="n">
         <v>92813</v>
@@ -33516,7 +33516,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.50817513465881</v>
+        <v>2.50817489624023</v>
       </c>
       <c r="H1143" t="n">
         <v>142239</v>
@@ -33545,7 +33545,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.47588109970093</v>
+        <v>2.47588086128235</v>
       </c>
       <c r="H1144" t="n">
         <v>135364</v>
@@ -33661,7 +33661,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.47588109970093</v>
+        <v>2.47588086128235</v>
       </c>
       <c r="H1148" t="n">
         <v>130888</v>
@@ -33690,7 +33690,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.47588109970093</v>
+        <v>2.47588086128235</v>
       </c>
       <c r="H1149" t="n">
         <v>127063</v>
@@ -33719,7 +33719,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.50099849700928</v>
+        <v>2.5009982585907</v>
       </c>
       <c r="H1150" t="n">
         <v>183218</v>
@@ -33748,7 +33748,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329229354858</v>
       </c>
       <c r="H1151" t="n">
         <v>202010</v>
@@ -33922,7 +33922,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.53709888458252</v>
+        <v>2.53709864616394</v>
       </c>
       <c r="H1157" t="n">
         <v>213940</v>
@@ -33951,7 +33951,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344421386719</v>
+        <v>2.48344397544861</v>
       </c>
       <c r="H1158" t="n">
         <v>166881</v>
@@ -34009,7 +34009,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1160" t="n">
         <v>154215</v>
@@ -34096,7 +34096,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.34164261817932</v>
+        <v>2.34164237976074</v>
       </c>
       <c r="H1163" t="n">
         <v>191513</v>
@@ -34241,7 +34241,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.40296220779419</v>
+        <v>2.40296196937561</v>
       </c>
       <c r="H1168" t="n">
         <v>113023</v>
@@ -34328,7 +34328,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.50643873214722</v>
+        <v>2.5064389705658</v>
       </c>
       <c r="H1171" t="n">
         <v>229796</v>
@@ -34357,7 +34357,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.46044921875</v>
+        <v>2.46044945716858</v>
       </c>
       <c r="H1172" t="n">
         <v>154679</v>
@@ -34444,7 +34444,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1175" t="n">
         <v>77116</v>
@@ -34589,7 +34589,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1180" t="n">
         <v>124034</v>
@@ -34647,7 +34647,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.33780980110168</v>
+        <v>2.33781003952026</v>
       </c>
       <c r="H1182" t="n">
         <v>87462</v>
@@ -34705,7 +34705,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.33780980110168</v>
+        <v>2.33781003952026</v>
       </c>
       <c r="H1184" t="n">
         <v>68132</v>
@@ -34763,7 +34763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.39912962913513</v>
+        <v>2.39912986755371</v>
       </c>
       <c r="H1186" t="n">
         <v>171526</v>
@@ -34850,7 +34850,7 @@
         <v>3.125</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.39529728889465</v>
+        <v>2.39529705047607</v>
       </c>
       <c r="H1189" t="n">
         <v>62755</v>
@@ -34879,7 +34879,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1190" t="n">
         <v>56050</v>
@@ -34966,7 +34966,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1193" t="n">
         <v>38721</v>
@@ -35053,7 +35053,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1196" t="n">
         <v>154795</v>
@@ -35111,7 +35111,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.47961139678955</v>
+        <v>2.47961163520813</v>
       </c>
       <c r="H1198" t="n">
         <v>196742</v>
@@ -35140,7 +35140,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.41062688827515</v>
+        <v>2.41062712669373</v>
       </c>
       <c r="H1199" t="n">
         <v>350032</v>
@@ -35169,7 +35169,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715036392212</v>
+        <v>2.30715012550354</v>
       </c>
       <c r="H1200" t="n">
         <v>254056</v>
@@ -35285,7 +35285,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.24966311454773</v>
+        <v>2.24966287612915</v>
       </c>
       <c r="H1204" t="n">
         <v>122588</v>
@@ -35459,7 +35459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1210" t="n">
         <v>130645</v>
@@ -35488,7 +35488,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1211" t="n">
         <v>151446</v>
@@ -35517,7 +35517,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.41445994377136</v>
+        <v>2.41445970535278</v>
       </c>
       <c r="H1212" t="n">
         <v>181793</v>
@@ -35691,7 +35691,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283577919006</v>
+        <v>2.22283601760864</v>
       </c>
       <c r="H1218" t="n">
         <v>339921</v>
@@ -35720,7 +35720,7 @@
         <v>2.875</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.20367336273193</v>
+        <v>2.20367312431335</v>
       </c>
       <c r="H1219" t="n">
         <v>195479</v>
@@ -35749,7 +35749,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.22666835784912</v>
+        <v>2.22666811943054</v>
       </c>
       <c r="H1220" t="n">
         <v>102898</v>
@@ -35807,7 +35807,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.17301344871521</v>
+        <v>2.17301368713379</v>
       </c>
       <c r="H1222" t="n">
         <v>242902</v>
@@ -35865,7 +35865,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.06953692436218</v>
+        <v>2.0695366859436</v>
       </c>
       <c r="H1224" t="n">
         <v>397333</v>
@@ -35894,7 +35894,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.03887677192688</v>
+        <v>2.03887701034546</v>
       </c>
       <c r="H1225" t="n">
         <v>168729</v>
@@ -35923,7 +35923,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.98522210121155</v>
+        <v>1.98522222042084</v>
       </c>
       <c r="H1226" t="n">
         <v>131888</v>
@@ -35981,7 +35981,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.9085727930069</v>
+        <v>1.90857291221619</v>
       </c>
       <c r="H1228" t="n">
         <v>240537</v>
@@ -36068,7 +36068,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.01971459388733</v>
+        <v>2.01971435546875</v>
       </c>
       <c r="H1231" t="n">
         <v>141307</v>
@@ -36155,7 +36155,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138999938965</v>
+        <v>1.98138964176178</v>
       </c>
       <c r="H1234" t="n">
         <v>203810</v>
@@ -36184,7 +36184,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.18067860603333</v>
+        <v>2.18067836761475</v>
       </c>
       <c r="H1235" t="n">
         <v>480028</v>
@@ -36242,7 +36242,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291072845459</v>
+        <v>2.63291049003601</v>
       </c>
       <c r="H1237" t="n">
         <v>805282</v>
@@ -36271,7 +36271,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1238" t="n">
         <v>664061</v>
@@ -36329,7 +36329,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1240" t="n">
         <v>992861</v>
@@ -36387,7 +36387,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.71339249610901</v>
+        <v>2.71339273452759</v>
       </c>
       <c r="H1242" t="n">
         <v>459132</v>
@@ -36532,7 +36532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405217170715</v>
+        <v>2.74405241012573</v>
       </c>
       <c r="H1247" t="n">
         <v>450366</v>
@@ -36677,7 +36677,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68656539916992</v>
+        <v>2.68656516075134</v>
       </c>
       <c r="H1252" t="n">
         <v>485014</v>
@@ -36735,7 +36735,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087950706482</v>
       </c>
       <c r="H1254" t="n">
         <v>119317</v>
@@ -36764,7 +36764,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1255" t="n">
         <v>268956</v>
@@ -36851,7 +36851,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1258" t="n">
         <v>858635</v>
@@ -36880,7 +36880,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1259" t="n">
         <v>561880</v>
@@ -36967,7 +36967,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.81686949729919</v>
+        <v>2.81686925888062</v>
       </c>
       <c r="H1262" t="n">
         <v>421624</v>
@@ -36996,7 +36996,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1263" t="n">
         <v>164441</v>
@@ -37025,7 +37025,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1264" t="n">
         <v>1034179</v>
@@ -37083,7 +37083,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1266" t="n">
         <v>404158</v>
@@ -37112,7 +37112,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1267" t="n">
         <v>453222</v>
@@ -37170,7 +37170,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.82836699485779</v>
+        <v>2.82836675643921</v>
       </c>
       <c r="H1269" t="n">
         <v>261734</v>
@@ -37199,7 +37199,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.7593822479248</v>
+        <v>2.75938248634338</v>
       </c>
       <c r="H1270" t="n">
         <v>197407</v>
@@ -37228,7 +37228,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1271" t="n">
         <v>227438</v>
@@ -37286,7 +37286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.82836699485779</v>
+        <v>2.82836675643921</v>
       </c>
       <c r="H1273" t="n">
         <v>137710</v>
@@ -37402,7 +37402,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87052416801453</v>
+        <v>2.87052392959595</v>
       </c>
       <c r="H1277" t="n">
         <v>85060</v>
@@ -37431,7 +37431,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.85519433021545</v>
+        <v>2.85519409179688</v>
       </c>
       <c r="H1278" t="n">
         <v>80215</v>
@@ -37460,7 +37460,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1279" t="n">
         <v>604084</v>
@@ -37489,7 +37489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1280" t="n">
         <v>254659</v>
@@ -37518,7 +37518,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1281" t="n">
         <v>42257</v>
@@ -37547,7 +37547,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.89351916313171</v>
+        <v>2.89351892471313</v>
       </c>
       <c r="H1282" t="n">
         <v>460798</v>
@@ -37605,7 +37605,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620982170105</v>
+        <v>2.78620958328247</v>
       </c>
       <c r="H1284" t="n">
         <v>230927</v>
@@ -37663,7 +37663,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1286" t="n">
         <v>364606</v>
@@ -37692,7 +37692,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1287" t="n">
         <v>186106</v>
@@ -37721,7 +37721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.71339249610901</v>
+        <v>2.71339273452759</v>
       </c>
       <c r="H1288" t="n">
         <v>215050</v>
@@ -37779,7 +37779,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1290" t="n">
         <v>637732</v>
@@ -37837,7 +37837,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087950706482</v>
       </c>
       <c r="H1292" t="n">
         <v>127030</v>
@@ -37953,7 +37953,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651391983032</v>
+        <v>2.91651368141174</v>
       </c>
       <c r="H1296" t="n">
         <v>425681</v>
@@ -38040,7 +38040,7 @@
         <v>4</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1299" t="n">
         <v>272536</v>
@@ -38069,7 +38069,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1300" t="n">
         <v>831090</v>
@@ -38098,7 +38098,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849342346191</v>
+        <v>3.00849294662476</v>
       </c>
       <c r="H1301" t="n">
         <v>169875</v>
@@ -38185,7 +38185,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1304" t="n">
         <v>631921</v>
@@ -38214,7 +38214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1305" t="n">
         <v>141746</v>
@@ -38272,7 +38272,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1307" t="n">
         <v>163152</v>
@@ -38301,7 +38301,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.96250367164612</v>
+        <v>2.96250343322754</v>
       </c>
       <c r="H1308" t="n">
         <v>124483</v>
@@ -38330,7 +38330,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1309" t="n">
         <v>851470</v>
@@ -38359,7 +38359,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.66357040405273</v>
+        <v>2.66357016563416</v>
       </c>
       <c r="H1310" t="n">
         <v>561214</v>
@@ -38417,7 +38417,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1312" t="n">
         <v>318481</v>
@@ -38446,7 +38446,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1313" t="n">
         <v>282164</v>
@@ -38475,7 +38475,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171756744385</v>
+        <v>2.75171732902527</v>
       </c>
       <c r="H1314" t="n">
         <v>329760</v>
@@ -38504,7 +38504,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1315" t="n">
         <v>153154</v>
@@ -38533,7 +38533,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1316" t="n">
         <v>315319</v>
@@ -38562,7 +38562,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1317" t="n">
         <v>259106</v>
@@ -38591,7 +38591,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1318" t="n">
         <v>510876</v>
@@ -38620,7 +38620,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1319" t="n">
         <v>410062</v>
@@ -38765,7 +38765,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.67123532295227</v>
+        <v>2.67123508453369</v>
       </c>
       <c r="H1324" t="n">
         <v>215143</v>
@@ -38794,7 +38794,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1325" t="n">
         <v>410108</v>
@@ -38823,7 +38823,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1326" t="n">
         <v>250248</v>
@@ -38939,7 +38939,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.65973782539368</v>
+        <v>2.65973806381226</v>
       </c>
       <c r="H1330" t="n">
         <v>264773</v>
@@ -39055,7 +39055,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1334" t="n">
         <v>268795</v>
@@ -39084,7 +39084,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1335" t="n">
         <v>669291</v>
@@ -39229,7 +39229,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1340" t="n">
         <v>294026</v>
@@ -39258,7 +39258,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.85902667045593</v>
+        <v>2.85902690887451</v>
       </c>
       <c r="H1341" t="n">
         <v>108872</v>
@@ -39287,7 +39287,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.85519433021545</v>
+        <v>2.85519409179688</v>
       </c>
       <c r="H1342" t="n">
         <v>124489</v>
@@ -39374,7 +39374,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1345" t="n">
         <v>248627</v>
@@ -39432,7 +39432,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1347" t="n">
         <v>196520</v>
@@ -39519,7 +39519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933100700378</v>
       </c>
       <c r="H1350" t="n">
         <v>126106</v>
@@ -39548,7 +39548,7 @@
         <v>4</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1351" t="n">
         <v>440591</v>
@@ -39577,7 +39577,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1352" t="n">
         <v>204988</v>
@@ -39635,7 +39635,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1354" t="n">
         <v>192611</v>
@@ -39693,7 +39693,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.15412712097168</v>
+        <v>3.1541268825531</v>
       </c>
       <c r="H1356" t="n">
         <v>386167</v>
@@ -39780,7 +39780,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676677703857</v>
+        <v>3.27676653862</v>
       </c>
       <c r="H1359" t="n">
         <v>363222</v>
@@ -39809,7 +39809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1360" t="n">
         <v>294112</v>
@@ -39896,7 +39896,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1363" t="n">
         <v>192510</v>
@@ -39925,7 +39925,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1364" t="n">
         <v>441387</v>
@@ -40070,7 +40070,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1369" t="n">
         <v>235700</v>
@@ -40128,7 +40128,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1371" t="n">
         <v>266113</v>
@@ -40331,7 +40331,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1378" t="n">
         <v>159804</v>
@@ -40360,7 +40360,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1379" t="n">
         <v>919643</v>
@@ -40534,7 +40534,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737497329712</v>
+        <v>3.53737449645996</v>
       </c>
       <c r="H1385" t="n">
         <v>247331</v>
@@ -40563,7 +40563,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054739952087</v>
+        <v>3.51054763793945</v>
       </c>
       <c r="H1386" t="n">
         <v>316680</v>
@@ -40592,7 +40592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557337760925</v>
+        <v>3.39557313919067</v>
       </c>
       <c r="H1387" t="n">
         <v>935373</v>
@@ -40650,7 +40650,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.39940571784973</v>
+        <v>3.39940547943115</v>
       </c>
       <c r="H1389" t="n">
         <v>173631</v>
@@ -40708,7 +40708,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1391" t="n">
         <v>184876</v>
@@ -40737,7 +40737,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.33042120933533</v>
+        <v>3.33042097091675</v>
       </c>
       <c r="H1392" t="n">
         <v>314803</v>
@@ -40795,7 +40795,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1394" t="n">
         <v>384891</v>
@@ -40882,7 +40882,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1397" t="n">
         <v>183307</v>
@@ -40911,7 +40911,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1398" t="n">
         <v>112518</v>
@@ -40969,7 +40969,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1400" t="n">
         <v>213421</v>
@@ -41027,7 +41027,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1402" t="n">
         <v>186824</v>
@@ -41056,7 +41056,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1403" t="n">
         <v>236837</v>
@@ -41085,7 +41085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1404" t="n">
         <v>114681</v>
@@ -41114,7 +41114,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1405" t="n">
         <v>245941</v>
@@ -41201,7 +41201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1408" t="n">
         <v>69983</v>
@@ -41230,7 +41230,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1409" t="n">
         <v>221820</v>
@@ -41346,7 +41346,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1413" t="n">
         <v>167993</v>
@@ -41375,7 +41375,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.15412712097168</v>
+        <v>3.1541268825531</v>
       </c>
       <c r="H1414" t="n">
         <v>365235</v>
@@ -41404,7 +41404,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1415" t="n">
         <v>92805</v>
@@ -41549,7 +41549,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.08131003379822</v>
+        <v>3.08131051063538</v>
       </c>
       <c r="H1420" t="n">
         <v>108491</v>
@@ -41665,7 +41665,7 @@
         <v>4.125</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179203987122</v>
       </c>
       <c r="H1424" t="n">
         <v>65763</v>
@@ -41694,7 +41694,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610662460327</v>
+        <v>3.24610686302185</v>
       </c>
       <c r="H1425" t="n">
         <v>182882</v>
@@ -41723,7 +41723,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377178192139</v>
+        <v>3.25377130508423</v>
       </c>
       <c r="H1426" t="n">
         <v>193950</v>
@@ -41781,7 +41781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1428" t="n">
         <v>275646</v>
@@ -41810,7 +41810,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1429" t="n">
         <v>95971</v>
@@ -41839,7 +41839,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1430" t="n">
         <v>236415</v>
@@ -41868,7 +41868,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1431" t="n">
         <v>199731</v>
@@ -41897,7 +41897,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1432" t="n">
         <v>161220</v>
@@ -41926,7 +41926,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.01615810394287</v>
+        <v>3.01615786552429</v>
       </c>
       <c r="H1433" t="n">
         <v>370036</v>
@@ -42071,7 +42071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765560150146</v>
       </c>
       <c r="H1438" t="n">
         <v>232582</v>
@@ -42158,7 +42158,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.09664034843445</v>
+        <v>3.09664011001587</v>
       </c>
       <c r="H1441" t="n">
         <v>308009</v>
@@ -42216,7 +42216,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1443" t="n">
         <v>151117</v>
@@ -42245,7 +42245,7 @@
         <v>3.875</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.97016859054565</v>
+        <v>2.97016835212708</v>
       </c>
       <c r="H1444" t="n">
         <v>484542</v>
@@ -42303,7 +42303,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.86669182777405</v>
+        <v>2.86669158935547</v>
       </c>
       <c r="H1446" t="n">
         <v>425712</v>
@@ -42448,7 +42448,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1451" t="n">
-        <v>2.77471232414246</v>
+        <v>2.77471208572388</v>
       </c>
       <c r="H1451" t="n">
         <v>246594</v>
@@ -42535,7 +42535,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.80920457839966</v>
+        <v>2.80920433998108</v>
       </c>
       <c r="H1454" t="n">
         <v>357222</v>
@@ -42593,7 +42593,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268110275269</v>
+        <v>2.91268134117126</v>
       </c>
       <c r="H1456" t="n">
         <v>226254</v>
@@ -42796,7 +42796,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1463" t="n">
         <v>245831</v>
@@ -42825,7 +42825,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.07364559173584</v>
+        <v>3.07364535331726</v>
       </c>
       <c r="H1464" t="n">
         <v>341626</v>
@@ -42970,7 +42970,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1469" t="n">
         <v>229173</v>
@@ -43057,7 +43057,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.06981325149536</v>
+        <v>3.0698127746582</v>
       </c>
       <c r="H1472" t="n">
         <v>332716</v>
@@ -43086,7 +43086,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214785575867</v>
+        <v>3.06214761734009</v>
       </c>
       <c r="H1473" t="n">
         <v>159481</v>
@@ -43115,7 +43115,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1474" t="n">
         <v>198702</v>
@@ -43202,7 +43202,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1477" t="n">
         <v>1174979</v>
@@ -43289,7 +43289,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1480" t="n">
         <v>585959</v>
@@ -43347,7 +43347,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1482" t="n">
         <v>244885</v>
@@ -43463,7 +43463,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681801795959</v>
       </c>
       <c r="H1486" t="n">
         <v>385290</v>
@@ -43579,7 +43579,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1490" t="n">
         <v>301508</v>
@@ -43637,7 +43637,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1492" t="n">
         <v>256197</v>
@@ -43666,7 +43666,7 @@
         <v>4</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1493" t="n">
         <v>170712</v>
@@ -43695,7 +43695,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430550575256</v>
+        <v>3.10430526733398</v>
       </c>
       <c r="H1494" t="n">
         <v>470480</v>
@@ -43724,7 +43724,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1495" t="n">
         <v>302736</v>
@@ -43753,7 +43753,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.95483875274658</v>
+        <v>2.954838514328</v>
       </c>
       <c r="H1496" t="n">
         <v>427392</v>
@@ -43782,7 +43782,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651391983032</v>
+        <v>2.91651368141174</v>
       </c>
       <c r="H1497" t="n">
         <v>234286</v>
@@ -44043,7 +44043,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1506" t="n">
         <v>191990</v>
@@ -44072,7 +44072,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1507" t="n">
         <v>201693</v>
@@ -44101,7 +44101,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1508" t="n">
         <v>218675</v>
@@ -44159,7 +44159,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1510" t="n">
         <v>424497</v>
@@ -44217,7 +44217,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.72489023208618</v>
+        <v>2.7248899936676</v>
       </c>
       <c r="H1512" t="n">
         <v>148986</v>
@@ -44275,7 +44275,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.66357040405273</v>
+        <v>2.66357016563416</v>
       </c>
       <c r="H1514" t="n">
         <v>189008</v>
@@ -44362,7 +44362,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1517" t="n">
         <v>354141</v>
@@ -44391,7 +44391,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1518" t="n">
         <v>361006</v>
@@ -44420,7 +44420,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.81303691864014</v>
+        <v>2.81303715705872</v>
       </c>
       <c r="H1519" t="n">
         <v>509062</v>
@@ -44449,7 +44449,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1520" t="n">
         <v>325474</v>
@@ -44478,7 +44478,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94717335700989</v>
+        <v>2.94717359542847</v>
       </c>
       <c r="H1521" t="n">
         <v>226415</v>
@@ -44507,7 +44507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1522" t="n">
         <v>232989</v>
@@ -44594,7 +44594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1525" t="n">
         <v>179741</v>
@@ -44623,7 +44623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1526" t="n">
         <v>156246</v>
@@ -44652,7 +44652,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.01615810394287</v>
+        <v>3.01615786552429</v>
       </c>
       <c r="H1527" t="n">
         <v>147446</v>
@@ -44739,7 +44739,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1530" t="n">
         <v>467217</v>
@@ -44768,7 +44768,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1531" t="n">
         <v>229732</v>
@@ -44797,7 +44797,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1532" t="n">
         <v>151799</v>
@@ -44855,7 +44855,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1534" t="n">
         <v>374707</v>
@@ -44942,7 +44942,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1537" t="n">
         <v>601285</v>
@@ -44971,7 +44971,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1538" t="n">
         <v>318781</v>
@@ -45116,7 +45116,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681801795959</v>
       </c>
       <c r="H1543" t="n">
         <v>292809</v>
@@ -45174,7 +45174,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1545" t="n">
         <v>194223</v>
@@ -45261,7 +45261,7 @@
         <v>4.125</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.16179227828979</v>
+        <v>3.16179203987122</v>
       </c>
       <c r="H1548" t="n">
         <v>207618</v>
@@ -45319,7 +45319,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.16945743560791</v>
+        <v>3.16945719718933</v>
       </c>
       <c r="H1550" t="n">
         <v>126850</v>
@@ -45348,7 +45348,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.08131003379822</v>
+        <v>3.08131051063538</v>
       </c>
       <c r="H1551" t="n">
         <v>208252</v>
@@ -45464,7 +45464,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1555" t="n">
         <v>415471</v>
@@ -45493,7 +45493,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.24227452278137</v>
+        <v>3.24227428436279</v>
       </c>
       <c r="H1556" t="n">
         <v>281497</v>
@@ -45551,7 +45551,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1558" t="n">
         <v>301113</v>
@@ -45580,7 +45580,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1559" t="n">
         <v>412974</v>
@@ -45609,7 +45609,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1560" t="n">
         <v>279714</v>
@@ -45638,7 +45638,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.24993896484375</v>
+        <v>3.24993920326233</v>
       </c>
       <c r="H1561" t="n">
         <v>186625</v>
@@ -45667,7 +45667,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.16945743560791</v>
+        <v>3.16945719718933</v>
       </c>
       <c r="H1562" t="n">
         <v>535155</v>
@@ -45696,7 +45696,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1563" t="n">
         <v>304504</v>
@@ -45725,7 +45725,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730026245117</v>
       </c>
       <c r="H1564" t="n">
         <v>412281</v>
@@ -45754,7 +45754,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778179168701</v>
       </c>
       <c r="H1565" t="n">
         <v>975722</v>
@@ -45812,7 +45812,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.45306062698364</v>
+        <v>3.45306038856506</v>
       </c>
       <c r="H1567" t="n">
         <v>647492</v>
@@ -45841,7 +45841,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1568" t="n">
         <v>500504</v>
@@ -45928,7 +45928,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1571" t="n">
         <v>390077</v>
@@ -45957,7 +45957,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933100700378</v>
       </c>
       <c r="H1572" t="n">
         <v>634329</v>
@@ -46102,7 +46102,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694420814514</v>
+        <v>3.2269446849823</v>
       </c>
       <c r="H1577" t="n">
         <v>314566</v>
@@ -46160,7 +46160,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844194412231</v>
+        <v>3.23844170570374</v>
       </c>
       <c r="H1579" t="n">
         <v>280568</v>
@@ -46189,7 +46189,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394968986511</v>
+        <v>3.20394945144653</v>
       </c>
       <c r="H1580" t="n">
         <v>262215</v>
@@ -46218,7 +46218,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1581" t="n">
         <v>292250</v>
@@ -46247,7 +46247,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311186790466</v>
       </c>
       <c r="H1582" t="n">
         <v>154452</v>
@@ -46276,7 +46276,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059887886047</v>
+        <v>3.28059935569763</v>
       </c>
       <c r="H1583" t="n">
         <v>178783</v>
@@ -46305,7 +46305,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.27293419837952</v>
+        <v>3.27293395996094</v>
       </c>
       <c r="H1584" t="n">
         <v>174110</v>
@@ -46363,7 +46363,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1586" t="n">
         <v>154125</v>
@@ -46392,7 +46392,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.2652690410614</v>
+        <v>3.26526927947998</v>
       </c>
       <c r="H1587" t="n">
         <v>169227</v>
@@ -46479,7 +46479,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.34958338737488</v>
+        <v>3.34958362579346</v>
       </c>
       <c r="H1590" t="n">
         <v>338944</v>
@@ -46682,7 +46682,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.5028829574585</v>
+        <v>3.50288271903992</v>
       </c>
       <c r="H1597" t="n">
         <v>291846</v>
@@ -46711,7 +46711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.46455788612366</v>
+        <v>3.46455812454224</v>
       </c>
       <c r="H1598" t="n">
         <v>146124</v>
@@ -46740,7 +46740,7 @@
         <v>4.625</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.54503965377808</v>
+        <v>3.54503989219666</v>
       </c>
       <c r="H1599" t="n">
         <v>184940</v>
@@ -46769,7 +46769,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48372030258179</v>
+        <v>3.48371982574463</v>
       </c>
       <c r="H1600" t="n">
         <v>129996</v>
@@ -46914,7 +46914,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.49138498306274</v>
+        <v>3.49138474464417</v>
       </c>
       <c r="H1605" t="n">
         <v>247326</v>
@@ -46943,7 +46943,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.49138498306274</v>
+        <v>3.49138474464417</v>
       </c>
       <c r="H1606" t="n">
         <v>273277</v>
@@ -46972,7 +46972,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.5067150592804</v>
+        <v>3.50671482086182</v>
       </c>
       <c r="H1607" t="n">
         <v>142915</v>
@@ -47059,7 +47059,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.4147355556488</v>
+        <v>3.41473531723022</v>
       </c>
       <c r="H1610" t="n">
         <v>352993</v>
@@ -47117,7 +47117,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39940571784973</v>
+        <v>3.39940547943115</v>
       </c>
       <c r="H1612" t="n">
         <v>160647</v>
@@ -47146,7 +47146,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1613" t="n">
         <v>656275</v>
@@ -47204,7 +47204,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371364593506</v>
+        <v>3.21371388435364</v>
       </c>
       <c r="H1615" t="n">
         <v>700758</v>
@@ -47262,7 +47262,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1617" t="n">
         <v>369551</v>
@@ -47291,7 +47291,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804208755493</v>
+        <v>3.26804184913635</v>
       </c>
       <c r="H1618" t="n">
         <v>297177</v>
@@ -47349,7 +47349,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177273750305</v>
+        <v>3.40177249908447</v>
       </c>
       <c r="H1620" t="n">
         <v>184041</v>
@@ -47407,7 +47407,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251877784729</v>
+        <v>3.37251901626587</v>
       </c>
       <c r="H1622" t="n">
         <v>196489</v>
@@ -47436,7 +47436,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147433280945</v>
+        <v>3.30147457122803</v>
       </c>
       <c r="H1623" t="n">
         <v>155525</v>
@@ -47465,7 +47465,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.26386260986328</v>
+        <v>3.26386284828186</v>
       </c>
       <c r="H1624" t="n">
         <v>184608</v>
@@ -47494,7 +47494,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1625" t="n">
         <v>92419</v>
@@ -47523,7 +47523,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.33072781562805</v>
+        <v>3.33072805404663</v>
       </c>
       <c r="H1626" t="n">
         <v>136171</v>
@@ -47552,7 +47552,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998153686523</v>
+        <v>3.35998177528381</v>
       </c>
       <c r="H1627" t="n">
         <v>103168</v>
@@ -47581,7 +47581,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.36416101455688</v>
+        <v>3.36416077613831</v>
       </c>
       <c r="H1628" t="n">
         <v>90572</v>
@@ -47668,7 +47668,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087701797485</v>
+        <v>3.38087725639343</v>
       </c>
       <c r="H1631" t="n">
         <v>335342</v>
@@ -47697,7 +47697,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1632" t="n">
         <v>295881</v>
@@ -47755,7 +47755,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983281135559</v>
+        <v>3.30983257293701</v>
       </c>
       <c r="H1634" t="n">
         <v>105059</v>
@@ -47813,7 +47813,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968408584595</v>
+        <v>3.25968384742737</v>
       </c>
       <c r="H1636" t="n">
         <v>115170</v>
@@ -47842,7 +47842,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625088691711</v>
+        <v>3.22625112533569</v>
       </c>
       <c r="H1637" t="n">
         <v>144155</v>
@@ -47900,7 +47900,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.07580423355103</v>
+        <v>3.0758044719696</v>
       </c>
       <c r="H1639" t="n">
         <v>209765</v>
@@ -47929,7 +47929,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1640" t="n">
         <v>210448</v>
@@ -47987,7 +47987,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1642" t="n">
         <v>151991</v>
@@ -48045,7 +48045,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1644" t="n">
         <v>388116</v>
@@ -48103,7 +48103,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132730484009</v>
+        <v>2.97132706642151</v>
       </c>
       <c r="H1646" t="n">
         <v>131405</v>
@@ -48132,7 +48132,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94625282287598</v>
+        <v>2.9462525844574</v>
       </c>
       <c r="H1647" t="n">
         <v>134428</v>
@@ -48161,7 +48161,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1648" t="n">
         <v>163785</v>
@@ -48219,7 +48219,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1650" t="n">
         <v>131117</v>
@@ -48335,7 +48335,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1654" t="n">
         <v>96343</v>
@@ -48422,7 +48422,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595465660095</v>
+        <v>2.84595489501953</v>
       </c>
       <c r="H1657" t="n">
         <v>159265</v>
@@ -48451,7 +48451,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1658" t="n">
         <v>166380</v>
@@ -48509,7 +48509,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893878936768</v>
+        <v>3.00893902778625</v>
       </c>
       <c r="H1660" t="n">
         <v>66664</v>
@@ -48567,7 +48567,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.97550630569458</v>
+        <v>2.975506067276</v>
       </c>
       <c r="H1662" t="n">
         <v>113262</v>
@@ -48654,7 +48654,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1665" t="n">
         <v>42245</v>
@@ -48683,7 +48683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729679107666</v>
+        <v>3.01729702949524</v>
       </c>
       <c r="H1666" t="n">
         <v>33283</v>
@@ -48712,7 +48712,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371558189392</v>
+        <v>2.93371534347534</v>
       </c>
       <c r="H1667" t="n">
         <v>141470</v>
@@ -48799,7 +48799,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804330825806</v>
+        <v>2.98804354667664</v>
       </c>
       <c r="H1670" t="n">
         <v>140069</v>
@@ -48857,7 +48857,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968530654907</v>
+        <v>2.97968554496765</v>
       </c>
       <c r="H1672" t="n">
         <v>143081</v>
@@ -48944,7 +48944,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311802864075</v>
+        <v>3.01311779022217</v>
       </c>
       <c r="H1675" t="n">
         <v>64858</v>
@@ -49408,7 +49408,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1691" t="n">
         <v>76345</v>
@@ -49553,7 +49553,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.8292384147644</v>
+        <v>2.82923817634583</v>
       </c>
       <c r="H1696" t="n">
         <v>102218</v>
@@ -49640,7 +49640,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1699" t="n">
         <v>94641</v>
@@ -49698,7 +49698,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1701" t="n">
         <v>96912</v>
@@ -49727,7 +49727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147772789001</v>
+        <v>2.74147748947144</v>
       </c>
       <c r="H1702" t="n">
         <v>135653</v>
@@ -49814,7 +49814,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.8334174156189</v>
+        <v>2.83341765403748</v>
       </c>
       <c r="H1705" t="n">
         <v>225042</v>
@@ -49959,7 +49959,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1710" t="n">
         <v>271736</v>
@@ -50046,7 +50046,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1713" t="n">
         <v>327552</v>
@@ -50365,7 +50365,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177857398987</v>
+        <v>2.28177881240845</v>
       </c>
       <c r="H1724" t="n">
         <v>163789</v>
@@ -50394,7 +50394,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1725" t="n">
         <v>189735</v>
@@ -50539,7 +50539,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.2149133682251</v>
+        <v>2.21491360664368</v>
       </c>
       <c r="H1730" t="n">
         <v>525600</v>
@@ -50655,7 +50655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1734" t="n">
         <v>187787</v>
@@ -50800,7 +50800,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1739" t="n">
         <v>123630</v>
@@ -50858,7 +50858,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.51998615264893</v>
+        <v>2.5199863910675</v>
       </c>
       <c r="H1741" t="n">
         <v>649724</v>
@@ -50887,7 +50887,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.50326991081238</v>
+        <v>2.5032696723938</v>
       </c>
       <c r="H1742" t="n">
         <v>250081</v>
@@ -50916,7 +50916,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744891166687</v>
+        <v>2.50744915008545</v>
       </c>
       <c r="H1743" t="n">
         <v>179184</v>
@@ -50945,7 +50945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013535499573</v>
+        <v>2.57013511657715</v>
       </c>
       <c r="H1744" t="n">
         <v>319932</v>
@@ -51003,7 +51003,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849335670471</v>
+        <v>2.57849359512329</v>
       </c>
       <c r="H1746" t="n">
         <v>135722</v>
@@ -51032,7 +51032,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1747" t="n">
         <v>321826</v>
@@ -51119,7 +51119,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685159683228</v>
+        <v>2.58685183525085</v>
       </c>
       <c r="H1750" t="n">
         <v>233347</v>
@@ -51438,7 +51438,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282179832458</v>
+        <v>2.63282155990601</v>
       </c>
       <c r="H1761" t="n">
         <v>2139834</v>
@@ -51467,7 +51467,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297052383423</v>
+        <v>2.68297076225281</v>
       </c>
       <c r="H1762" t="n">
         <v>317737</v>
@@ -51757,7 +51757,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.6370005607605</v>
+        <v>2.63700032234192</v>
       </c>
       <c r="H1772" t="n">
         <v>171669</v>
@@ -51844,7 +51844,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.58267259597778</v>
+        <v>2.5826723575592</v>
       </c>
       <c r="H1775" t="n">
         <v>230178</v>
@@ -51873,7 +51873,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1776" t="n">
         <v>215923</v>
@@ -51931,7 +51931,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1778" t="n">
         <v>44718</v>
@@ -52076,7 +52076,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371680259705</v>
+        <v>2.65371704101562</v>
       </c>
       <c r="H1783" t="n">
         <v>59395</v>
@@ -52308,7 +52308,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908945083618</v>
+        <v>2.77908968925476</v>
       </c>
       <c r="H1791" t="n">
         <v>288121</v>
@@ -52337,7 +52337,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073121070862</v>
+        <v>2.77073097229004</v>
       </c>
       <c r="H1792" t="n">
         <v>160766</v>
@@ -52511,7 +52511,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.88356637954712</v>
+        <v>2.8835666179657</v>
       </c>
       <c r="H1798" t="n">
         <v>177420</v>
@@ -52627,7 +52627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.47401642799377</v>
+        <v>2.4740161895752</v>
       </c>
       <c r="H1802" t="n">
         <v>1663657</v>
@@ -53178,7 +53178,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297198295593</v>
+        <v>2.40297222137451</v>
       </c>
       <c r="H1821" t="n">
         <v>691856</v>
@@ -53613,7 +53613,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1836" t="n">
         <v>505563</v>
@@ -53874,7 +53874,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.298495054245</v>
+        <v>2.29849481582642</v>
       </c>
       <c r="H1845" t="n">
         <v>224918</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1851" t="n">
         <v>294292</v>
@@ -54077,7 +54077,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.3904345035553</v>
+        <v>2.39043474197388</v>
       </c>
       <c r="H1852" t="n">
         <v>247994</v>
@@ -54106,7 +54106,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640470504761</v>
+        <v>2.43640446662903</v>
       </c>
       <c r="H1853" t="n">
         <v>352350</v>
@@ -54164,7 +54164,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1855" t="n">
         <v>498934</v>
@@ -54193,7 +54193,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565842628479</v>
+        <v>2.46565818786621</v>
       </c>
       <c r="H1856" t="n">
         <v>347116</v>
@@ -54309,7 +54309,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.4405837059021</v>
+        <v>2.44058394432068</v>
       </c>
       <c r="H1860" t="n">
         <v>158968</v>
@@ -54454,7 +54454,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.48237442970276</v>
+        <v>2.48237466812134</v>
       </c>
       <c r="H1865" t="n">
         <v>433044</v>
@@ -54483,7 +54483,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.44476270675659</v>
+        <v>2.44476294517517</v>
       </c>
       <c r="H1866" t="n">
         <v>307676</v>
@@ -54570,7 +54570,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550922393799</v>
+        <v>2.41550946235657</v>
       </c>
       <c r="H1869" t="n">
         <v>644276</v>
@@ -80081,7 +80081,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="D2749" t="n">
-        <v>3.6800000667572</v>
+        <v>3.68499994277954</v>
       </c>
       <c r="E2749" t="n">
         <v>3.57999992370605</v>
@@ -80093,9 +80093,38 @@
         <v>3.68499994277954</v>
       </c>
       <c r="H2749" t="n">
-        <v>59342</v>
+        <v>59428</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>3.72499990463257</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>3.68499994277954</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>44788</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235973358154</v>
+        <v>4.64235925674438</v>
       </c>
       <c r="H3" t="n">
         <v>62931</v>
@@ -485,7 +485,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G4" t="n">
-        <v>4.60015535354614</v>
+        <v>4.60015630722046</v>
       </c>
       <c r="H4" t="n">
         <v>91949</v>
@@ -543,7 +543,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409700393677</v>
+        <v>4.48409748077393</v>
       </c>
       <c r="H6" t="n">
         <v>164680</v>
@@ -601,7 +601,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.40496635437012</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H8" t="n">
         <v>127969</v>
@@ -630,7 +630,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50783586502075</v>
+        <v>4.50783729553223</v>
       </c>
       <c r="H9" t="n">
         <v>83967</v>
@@ -659,7 +659,7 @@
         <v>7.73923206329346</v>
       </c>
       <c r="G10" t="n">
-        <v>4.39177703857422</v>
+        <v>4.39177751541138</v>
       </c>
       <c r="H10" t="n">
         <v>310256</v>
@@ -688,7 +688,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G11" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H11" t="n">
         <v>287176</v>
@@ -717,7 +717,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G12" t="n">
-        <v>4.01722383499146</v>
+        <v>4.01722288131714</v>
       </c>
       <c r="H12" t="n">
         <v>222009</v>
@@ -746,7 +746,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90380239486694</v>
+        <v>3.9038028717041</v>
       </c>
       <c r="H13" t="n">
         <v>164720</v>
@@ -775,7 +775,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176980018616</v>
+        <v>3.48176956176758</v>
       </c>
       <c r="H14" t="n">
         <v>416053</v>
@@ -862,7 +862,7 @@
         <v>6.86537313461304</v>
       </c>
       <c r="G17" t="n">
-        <v>3.89588928222656</v>
+        <v>3.89588904380798</v>
       </c>
       <c r="H17" t="n">
         <v>120439</v>
@@ -920,7 +920,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884432792664</v>
+        <v>3.80884528160095</v>
       </c>
       <c r="H19" t="n">
         <v>163830</v>
@@ -949,7 +949,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959761619568</v>
+        <v>3.67959713935852</v>
       </c>
       <c r="H20" t="n">
         <v>133261</v>
@@ -978,7 +978,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467174530029</v>
+        <v>3.82467126846313</v>
       </c>
       <c r="H21" t="n">
         <v>190130</v>
@@ -1065,7 +1065,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246784210205</v>
+        <v>3.78246808052063</v>
       </c>
       <c r="H24" t="n">
         <v>251231</v>
@@ -1094,7 +1094,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617665290833</v>
+        <v>3.56617593765259</v>
       </c>
       <c r="H25" t="n">
         <v>406980</v>
@@ -1123,7 +1123,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65322017669678</v>
+        <v>3.65322041511536</v>
       </c>
       <c r="H26" t="n">
         <v>190657</v>
@@ -1152,7 +1152,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405780792236</v>
+        <v>3.33405804634094</v>
       </c>
       <c r="H27" t="n">
         <v>238163</v>
@@ -1181,7 +1181,7 @@
         <v>5.94967985153198</v>
       </c>
       <c r="G28" t="n">
-        <v>3.37626171112061</v>
+        <v>3.37626123428345</v>
       </c>
       <c r="H28" t="n">
         <v>216081</v>
@@ -1210,7 +1210,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090021133423</v>
+        <v>3.56090116500854</v>
       </c>
       <c r="H29" t="n">
         <v>200231</v>
@@ -1268,7 +1268,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078510284424</v>
+        <v>3.51078462600708</v>
       </c>
       <c r="H31" t="n">
         <v>208699</v>
@@ -1326,7 +1326,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G33" t="n">
-        <v>3.69278597831726</v>
+        <v>3.69278645515442</v>
       </c>
       <c r="H33" t="n">
         <v>218931</v>
@@ -1355,7 +1355,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467174530029</v>
+        <v>3.82467126846313</v>
       </c>
       <c r="H34" t="n">
         <v>72733</v>
@@ -1384,7 +1384,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829382896423</v>
+        <v>3.79829359054565</v>
       </c>
       <c r="H35" t="n">
         <v>53341</v>
@@ -1413,7 +1413,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G36" t="n">
-        <v>3.73498916625977</v>
+        <v>3.73498940467834</v>
       </c>
       <c r="H36" t="n">
         <v>83765</v>
@@ -1442,7 +1442,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699051856995</v>
+        <v>3.9169909954071</v>
       </c>
       <c r="H37" t="n">
         <v>87617</v>
@@ -1500,7 +1500,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.81412029266357</v>
+        <v>3.81412053108215</v>
       </c>
       <c r="H39" t="n">
         <v>93458</v>
@@ -1529,7 +1529,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.84577322006226</v>
+        <v>3.84577250480652</v>
       </c>
       <c r="H40" t="n">
         <v>43899</v>
@@ -1587,7 +1587,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061307907104</v>
+        <v>3.89061379432678</v>
       </c>
       <c r="H42" t="n">
         <v>132642</v>
@@ -1616,7 +1616,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171550750732</v>
+        <v>3.91171503067017</v>
       </c>
       <c r="H43" t="n">
         <v>374802</v>
@@ -1645,7 +1645,7 @@
         <v>7.2093391418457</v>
       </c>
       <c r="G44" t="n">
-        <v>4.09107875823975</v>
+        <v>4.09107828140259</v>
       </c>
       <c r="H44" t="n">
         <v>354322</v>
@@ -1674,7 +1674,7 @@
         <v>7.1582088470459</v>
       </c>
       <c r="G45" t="n">
-        <v>4.06206464767456</v>
+        <v>4.0620641708374</v>
       </c>
       <c r="H45" t="n">
         <v>183400</v>
@@ -1732,7 +1732,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339967727661</v>
       </c>
       <c r="H47" t="n">
         <v>153285</v>
@@ -1761,7 +1761,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G48" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H48" t="n">
         <v>85660</v>
@@ -1790,7 +1790,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603658676147</v>
+        <v>4.18603706359863</v>
       </c>
       <c r="H49" t="n">
         <v>97201</v>
@@ -1848,7 +1848,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G51" t="n">
-        <v>4.36803865432739</v>
+        <v>4.36803817749023</v>
       </c>
       <c r="H51" t="n">
         <v>187212</v>
@@ -1877,7 +1877,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40496635437012</v>
+        <v>4.40496587753296</v>
       </c>
       <c r="H52" t="n">
         <v>135917</v>
@@ -1906,7 +1906,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G53" t="n">
-        <v>4.35221195220947</v>
+        <v>4.35221147537231</v>
       </c>
       <c r="H53" t="n">
         <v>202614</v>
@@ -1993,7 +1993,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047372817993</v>
+        <v>4.51047468185425</v>
       </c>
       <c r="H56" t="n">
         <v>440847</v>
@@ -2051,7 +2051,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G58" t="n">
-        <v>4.3891396522522</v>
+        <v>4.38914012908936</v>
       </c>
       <c r="H58" t="n">
         <v>117447</v>
@@ -2080,7 +2080,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G59" t="n">
-        <v>4.32583475112915</v>
+        <v>4.32583427429199</v>
       </c>
       <c r="H59" t="n">
         <v>99265</v>
@@ -2167,7 +2167,7 @@
         <v>7.5161190032959</v>
       </c>
       <c r="G62" t="n">
-        <v>4.26516771316528</v>
+        <v>4.26516723632812</v>
       </c>
       <c r="H62" t="n">
         <v>175234</v>
@@ -2312,7 +2312,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G67" t="n">
-        <v>4.10426807403564</v>
+        <v>4.10426712036133</v>
       </c>
       <c r="H67" t="n">
         <v>86909</v>
@@ -2370,7 +2370,7 @@
         <v>7.18609809875488</v>
       </c>
       <c r="G69" t="n">
-        <v>4.07789087295532</v>
+        <v>4.07789039611816</v>
       </c>
       <c r="H69" t="n">
         <v>110418</v>
@@ -2399,7 +2399,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G70" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H70" t="n">
         <v>73551</v>
@@ -2428,7 +2428,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G71" t="n">
-        <v>4.08844184875488</v>
+        <v>4.08844137191772</v>
       </c>
       <c r="H71" t="n">
         <v>110301</v>
@@ -2457,7 +2457,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H72" t="n">
         <v>138383</v>
@@ -2515,7 +2515,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812347412109</v>
+        <v>4.17812299728394</v>
       </c>
       <c r="H74" t="n">
         <v>11963</v>
@@ -2573,7 +2573,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G76" t="n">
-        <v>4.15438461303711</v>
+        <v>4.15438413619995</v>
       </c>
       <c r="H76" t="n">
         <v>69912</v>
@@ -2602,7 +2602,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241331100464</v>
+        <v>4.21241474151611</v>
       </c>
       <c r="H77" t="n">
         <v>65491</v>
@@ -2660,7 +2660,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G79" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H79" t="n">
         <v>28153</v>
@@ -2805,7 +2805,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339920043945</v>
+        <v>4.18339967727661</v>
       </c>
       <c r="H84" t="n">
         <v>135960</v>
@@ -2863,7 +2863,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119625091553</v>
+        <v>4.14119577407837</v>
       </c>
       <c r="H86" t="n">
         <v>95409</v>
@@ -2892,7 +2892,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009477615356</v>
+        <v>4.12009382247925</v>
       </c>
       <c r="H87" t="n">
         <v>20188</v>
@@ -2921,7 +2921,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G88" t="n">
-        <v>4.10426807403564</v>
+        <v>4.10426712036133</v>
       </c>
       <c r="H88" t="n">
         <v>42052</v>
@@ -2950,7 +2950,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G89" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H89" t="n">
         <v>83038</v>
@@ -2979,7 +2979,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383363723755</v>
+        <v>4.14383316040039</v>
       </c>
       <c r="H90" t="n">
         <v>26575</v>
@@ -3008,7 +3008,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G91" t="n">
-        <v>4.244065284729</v>
+        <v>4.24406671524048</v>
       </c>
       <c r="H91" t="n">
         <v>211317</v>
@@ -3037,7 +3037,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G92" t="n">
-        <v>4.15438461303711</v>
+        <v>4.15438413619995</v>
       </c>
       <c r="H92" t="n">
         <v>118401</v>
@@ -3153,7 +3153,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131135940552</v>
+        <v>4.19131183624268</v>
       </c>
       <c r="H96" t="n">
         <v>58862</v>
@@ -3211,7 +3211,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G98" t="n">
-        <v>4.15174579620361</v>
+        <v>4.15174627304077</v>
       </c>
       <c r="H98" t="n">
         <v>86040</v>
@@ -3269,7 +3269,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G100" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H100" t="n">
         <v>61620</v>
@@ -3327,7 +3327,7 @@
         <v>7.51147079467773</v>
       </c>
       <c r="G102" t="n">
-        <v>4.48687314987183</v>
+        <v>4.48687362670898</v>
       </c>
       <c r="H102" t="n">
         <v>87735</v>
@@ -3414,7 +3414,7 @@
         <v>7.5811939239502</v>
       </c>
       <c r="G105" t="n">
-        <v>4.52852201461792</v>
+        <v>4.52852153778076</v>
       </c>
       <c r="H105" t="n">
         <v>60638</v>
@@ -3472,7 +3472,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G107" t="n">
-        <v>4.45355558395386</v>
+        <v>4.4535551071167</v>
       </c>
       <c r="H107" t="n">
         <v>112417</v>
@@ -3530,7 +3530,7 @@
         <v>7.48823022842407</v>
       </c>
       <c r="G109" t="n">
-        <v>4.47299098968506</v>
+        <v>4.47299146652222</v>
       </c>
       <c r="H109" t="n">
         <v>58116</v>
@@ -3559,7 +3559,7 @@
         <v>7.47893381118774</v>
       </c>
       <c r="G110" t="n">
-        <v>4.46743726730347</v>
+        <v>4.46743822097778</v>
       </c>
       <c r="H110" t="n">
         <v>35336</v>
@@ -3617,7 +3617,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G112" t="n">
-        <v>4.45355558395386</v>
+        <v>4.4535551071167</v>
       </c>
       <c r="H112" t="n">
         <v>53716</v>
@@ -3646,7 +3646,7 @@
         <v>7.49287796020508</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47576665878296</v>
+        <v>4.47576761245728</v>
       </c>
       <c r="H113" t="n">
         <v>86039</v>
@@ -3704,7 +3704,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.19811487197876</v>
+        <v>4.1981143951416</v>
       </c>
       <c r="H115" t="n">
         <v>98580</v>
@@ -3762,7 +3762,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989658355713</v>
+        <v>3.93989706039429</v>
       </c>
       <c r="H117" t="n">
         <v>151204</v>
@@ -3791,7 +3791,7 @@
         <v>6.38196182250977</v>
       </c>
       <c r="G118" t="n">
-        <v>3.81217670440674</v>
+        <v>3.81217694282532</v>
       </c>
       <c r="H118" t="n">
         <v>94805</v>
@@ -3820,7 +3820,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.83161211013794</v>
+        <v>3.8316125869751</v>
       </c>
       <c r="H119" t="n">
         <v>396991</v>
@@ -3849,7 +3849,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G120" t="n">
-        <v>4.01486349105835</v>
+        <v>4.01486396789551</v>
       </c>
       <c r="H120" t="n">
         <v>179714</v>
@@ -3878,7 +3878,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G121" t="n">
-        <v>4.05373525619507</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H121" t="n">
         <v>147984</v>
@@ -3907,7 +3907,7 @@
         <v>6.86072492599487</v>
       </c>
       <c r="G122" t="n">
-        <v>4.0981593132019</v>
+        <v>4.09815979003906</v>
       </c>
       <c r="H122" t="n">
         <v>126979</v>
@@ -3965,7 +3965,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.89269638061523</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H124" t="n">
         <v>186001</v>
@@ -4023,7 +4023,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="n">
-        <v>3.70944452285767</v>
+        <v>3.70944547653198</v>
       </c>
       <c r="H126" t="n">
         <v>201840</v>
@@ -4052,7 +4052,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H127" t="n">
         <v>204444</v>
@@ -4081,7 +4081,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H128" t="n">
         <v>365836</v>
@@ -4139,7 +4139,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603735923767</v>
+        <v>3.87603759765625</v>
       </c>
       <c r="H130" t="n">
         <v>40805</v>
@@ -4168,7 +4168,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165678977966</v>
+        <v>3.73165702819824</v>
       </c>
       <c r="H131" t="n">
         <v>182299</v>
@@ -4226,7 +4226,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328271865845</v>
+        <v>3.82328295707703</v>
       </c>
       <c r="H133" t="n">
         <v>123098</v>
@@ -4313,7 +4313,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G136" t="n">
-        <v>4.05373525619507</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H136" t="n">
         <v>104402</v>
@@ -4429,7 +4429,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35915422439575</v>
+        <v>4.35915327072144</v>
       </c>
       <c r="H140" t="n">
         <v>180510</v>
@@ -4487,7 +4487,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="n">
-        <v>4.2980694770813</v>
+        <v>4.29806900024414</v>
       </c>
       <c r="H142" t="n">
         <v>180595</v>
@@ -4545,7 +4545,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H144" t="n">
         <v>200057</v>
@@ -4603,7 +4603,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="n">
-        <v>4.30084705352783</v>
+        <v>4.30084657669067</v>
       </c>
       <c r="H146" t="n">
         <v>72804</v>
@@ -4632,7 +4632,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858963012695</v>
+        <v>4.37858915328979</v>
       </c>
       <c r="H147" t="n">
         <v>120474</v>
@@ -4661,7 +4661,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025833129883</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H148" t="n">
         <v>86165</v>
@@ -4719,7 +4719,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H150" t="n">
         <v>81896</v>
@@ -4748,7 +4748,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.19811487197876</v>
+        <v>4.1981143951416</v>
       </c>
       <c r="H151" t="n">
         <v>100034</v>
@@ -4777,7 +4777,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H152" t="n">
         <v>260528</v>
@@ -4835,7 +4835,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H154" t="n">
         <v>185636</v>
@@ -4864,7 +4864,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="n">
-        <v>4.22865629196167</v>
+        <v>4.22865581512451</v>
       </c>
       <c r="H155" t="n">
         <v>73708</v>
@@ -4893,7 +4893,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="n">
-        <v>4.21199703216553</v>
+        <v>4.21199750900269</v>
       </c>
       <c r="H156" t="n">
         <v>137973</v>
@@ -4922,7 +4922,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H157" t="n">
         <v>67846</v>
@@ -4980,7 +4980,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644378662109</v>
+        <v>4.20644426345825</v>
       </c>
       <c r="H159" t="n">
         <v>60390</v>
@@ -5067,7 +5067,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="n">
-        <v>4.1620192527771</v>
+        <v>4.16201972961426</v>
       </c>
       <c r="H162" t="n">
         <v>24012</v>
@@ -5096,7 +5096,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="n">
-        <v>4.04262828826904</v>
+        <v>4.0426287651062</v>
       </c>
       <c r="H163" t="n">
         <v>129575</v>
@@ -5125,7 +5125,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="n">
-        <v>4.05095767974854</v>
+        <v>4.05095815658569</v>
       </c>
       <c r="H164" t="n">
         <v>61371</v>
@@ -5154,7 +5154,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H165" t="n">
         <v>82306</v>
@@ -5212,7 +5212,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371255874634</v>
+        <v>4.10371208190918</v>
       </c>
       <c r="H167" t="n">
         <v>23476</v>
@@ -5270,7 +5270,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820399284363</v>
       </c>
       <c r="H169" t="n">
         <v>96105</v>
@@ -5299,7 +5299,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="n">
-        <v>4.04818201065063</v>
+        <v>4.04818153381348</v>
       </c>
       <c r="H170" t="n">
         <v>82611</v>
@@ -5415,7 +5415,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="n">
-        <v>4.05928754806519</v>
+        <v>4.05928802490234</v>
       </c>
       <c r="H174" t="n">
         <v>106032</v>
@@ -5444,7 +5444,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="n">
-        <v>4.00098085403442</v>
+        <v>4.00098037719727</v>
       </c>
       <c r="H175" t="n">
         <v>47175</v>
@@ -5473,7 +5473,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G176" t="n">
-        <v>4.01486349105835</v>
+        <v>4.01486396789551</v>
       </c>
       <c r="H176" t="n">
         <v>82433</v>
@@ -5531,7 +5531,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156790733337</v>
+        <v>3.93156766891479</v>
       </c>
       <c r="H178" t="n">
         <v>219724</v>
@@ -5560,7 +5560,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H179" t="n">
         <v>313330</v>
@@ -5589,7 +5589,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="n">
-        <v>3.72888040542603</v>
+        <v>3.72888088226318</v>
       </c>
       <c r="H180" t="n">
         <v>212138</v>
@@ -5618,7 +5618,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H181" t="n">
         <v>119833</v>
@@ -5705,7 +5705,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389199256897</v>
       </c>
       <c r="H184" t="n">
         <v>128389</v>
@@ -5763,7 +5763,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.61781930923462</v>
+        <v>3.6178195476532</v>
       </c>
       <c r="H186" t="n">
         <v>138681</v>
@@ -5792,7 +5792,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332835197449</v>
+        <v>3.72332787513733</v>
       </c>
       <c r="H187" t="n">
         <v>126621</v>
@@ -5821,7 +5821,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000911712646</v>
+        <v>3.69000887870789</v>
       </c>
       <c r="H188" t="n">
         <v>175447</v>
@@ -5850,7 +5850,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="n">
-        <v>3.66224384307861</v>
+        <v>3.66224360466003</v>
       </c>
       <c r="H189" t="n">
         <v>128416</v>
@@ -5879,7 +5879,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H190" t="n">
         <v>329741</v>
@@ -5908,7 +5908,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276375770569</v>
+        <v>3.74276351928711</v>
       </c>
       <c r="H191" t="n">
         <v>217887</v>
@@ -5937,7 +5937,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.7205502986908</v>
+        <v>3.72055053710938</v>
       </c>
       <c r="H192" t="n">
         <v>103333</v>
@@ -5966,7 +5966,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332835197449</v>
+        <v>3.72332787513733</v>
       </c>
       <c r="H193" t="n">
         <v>167998</v>
@@ -6024,7 +6024,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.61781930923462</v>
+        <v>3.6178195476532</v>
       </c>
       <c r="H195" t="n">
         <v>109567</v>
@@ -6053,7 +6053,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113854408264</v>
+        <v>3.65113806724548</v>
       </c>
       <c r="H196" t="n">
         <v>131242</v>
@@ -6111,7 +6111,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170146942139</v>
       </c>
       <c r="H198" t="n">
         <v>86545</v>
@@ -6169,7 +6169,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.59838366508484</v>
+        <v>3.59838390350342</v>
       </c>
       <c r="H200" t="n">
         <v>58597</v>
@@ -6198,7 +6198,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="n">
-        <v>3.58172416687012</v>
+        <v>3.58172464370728</v>
       </c>
       <c r="H201" t="n">
         <v>105671</v>
@@ -6227,7 +6227,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="n">
-        <v>3.59283065795898</v>
+        <v>3.59283089637756</v>
       </c>
       <c r="H202" t="n">
         <v>105504</v>
@@ -6256,7 +6256,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170146942139</v>
       </c>
       <c r="H203" t="n">
         <v>132879</v>
@@ -6285,7 +6285,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.63170218467712</v>
+        <v>3.63170146942139</v>
       </c>
       <c r="H204" t="n">
         <v>133954</v>
@@ -6314,7 +6314,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="n">
-        <v>3.70666861534119</v>
+        <v>3.70666837692261</v>
       </c>
       <c r="H205" t="n">
         <v>112375</v>
@@ -6343,7 +6343,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660147666931</v>
+        <v>3.85660195350647</v>
       </c>
       <c r="H206" t="n">
         <v>205793</v>
@@ -6372,7 +6372,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046165466309</v>
+        <v>3.92046189308167</v>
       </c>
       <c r="H207" t="n">
         <v>198572</v>
@@ -6401,7 +6401,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156790733337</v>
+        <v>3.93156766891479</v>
       </c>
       <c r="H208" t="n">
         <v>48406</v>
@@ -6430,7 +6430,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.96488571166992</v>
+        <v>3.9648859500885</v>
       </c>
       <c r="H209" t="n">
         <v>111598</v>
@@ -6517,7 +6517,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="n">
-        <v>3.94267392158508</v>
+        <v>3.94267320632935</v>
       </c>
       <c r="H212" t="n">
         <v>122111</v>
@@ -6575,7 +6575,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.89269638061523</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H214" t="n">
         <v>75318</v>
@@ -6604,7 +6604,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215400695801</v>
+        <v>3.86215448379517</v>
       </c>
       <c r="H215" t="n">
         <v>72762</v>
@@ -6633,7 +6633,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H216" t="n">
         <v>114679</v>
@@ -6662,7 +6662,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H217" t="n">
         <v>51844</v>
@@ -6691,7 +6691,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="n">
-        <v>3.77608156204224</v>
+        <v>3.77608180046082</v>
       </c>
       <c r="H218" t="n">
         <v>66379</v>
@@ -6720,7 +6720,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107116699219</v>
+        <v>3.80107092857361</v>
       </c>
       <c r="H219" t="n">
         <v>60701</v>
@@ -6749,7 +6749,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.7871880531311</v>
+        <v>3.78718829154968</v>
       </c>
       <c r="H220" t="n">
         <v>128863</v>
@@ -6778,7 +6778,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="n">
-        <v>3.78996443748474</v>
+        <v>3.78996467590332</v>
       </c>
       <c r="H221" t="n">
         <v>103648</v>
@@ -6923,7 +6923,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059617042542</v>
+        <v>3.62059593200684</v>
       </c>
       <c r="H226" t="n">
         <v>137226</v>
@@ -6952,7 +6952,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="n">
-        <v>3.62614870071411</v>
+        <v>3.62614893913269</v>
       </c>
       <c r="H227" t="n">
         <v>55700</v>
@@ -6981,7 +6981,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="n">
-        <v>3.59283065795898</v>
+        <v>3.59283089637756</v>
       </c>
       <c r="H228" t="n">
         <v>91385</v>
@@ -7010,7 +7010,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179178237915</v>
+        <v>3.43179202079773</v>
       </c>
       <c r="H229" t="n">
         <v>391920</v>
@@ -7039,7 +7039,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51508760452271</v>
+        <v>3.51508736610413</v>
       </c>
       <c r="H230" t="n">
         <v>158535</v>
@@ -7068,7 +7068,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007649421692</v>
+        <v>3.54007601737976</v>
       </c>
       <c r="H231" t="n">
         <v>177686</v>
@@ -7097,7 +7097,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52897024154663</v>
+        <v>3.52897000312805</v>
       </c>
       <c r="H232" t="n">
         <v>53802</v>
@@ -7126,7 +7126,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400357246399</v>
+        <v>3.45400381088257</v>
       </c>
       <c r="H233" t="n">
         <v>47034</v>
@@ -7155,7 +7155,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="n">
-        <v>3.47066354751587</v>
+        <v>3.47066307067871</v>
       </c>
       <c r="H234" t="n">
         <v>111259</v>
@@ -7184,7 +7184,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.4762167930603</v>
+        <v>3.47621655464172</v>
       </c>
       <c r="H235" t="n">
         <v>66245</v>
@@ -7213,7 +7213,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="n">
-        <v>3.50398206710815</v>
+        <v>3.50398182868958</v>
       </c>
       <c r="H236" t="n">
         <v>83410</v>
@@ -7242,7 +7242,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842882156372</v>
+        <v>3.49842834472656</v>
       </c>
       <c r="H237" t="n">
         <v>59122</v>
@@ -7271,7 +7271,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174757957458</v>
       </c>
       <c r="H238" t="n">
         <v>110615</v>
@@ -7300,7 +7300,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732328414917</v>
+        <v>3.48732256889343</v>
       </c>
       <c r="H239" t="n">
         <v>109337</v>
@@ -7329,7 +7329,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="n">
-        <v>3.67057394981384</v>
+        <v>3.67057323455811</v>
       </c>
       <c r="H240" t="n">
         <v>90169</v>
@@ -7358,7 +7358,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389199256897</v>
       </c>
       <c r="H241" t="n">
         <v>121643</v>
@@ -7416,7 +7416,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.7871880531311</v>
+        <v>3.78718829154968</v>
       </c>
       <c r="H243" t="n">
         <v>135353</v>
@@ -7445,7 +7445,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H244" t="n">
         <v>97891</v>
@@ -7474,7 +7474,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.83161211013794</v>
+        <v>3.8316125869751</v>
       </c>
       <c r="H245" t="n">
         <v>194032</v>
@@ -7503,7 +7503,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="n">
-        <v>3.77608156204224</v>
+        <v>3.77608180046082</v>
       </c>
       <c r="H246" t="n">
         <v>85390</v>
@@ -7532,7 +7532,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.83161211013794</v>
+        <v>3.8316125869751</v>
       </c>
       <c r="H247" t="n">
         <v>110497</v>
@@ -7561,7 +7561,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.83161211013794</v>
+        <v>3.8316125869751</v>
       </c>
       <c r="H248" t="n">
         <v>128189</v>
@@ -7619,7 +7619,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102601051331</v>
+        <v>3.90102577209473</v>
       </c>
       <c r="H250" t="n">
         <v>108027</v>
@@ -7648,7 +7648,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154497146606</v>
+        <v>3.98154544830322</v>
       </c>
       <c r="H251" t="n">
         <v>198595</v>
@@ -7677,7 +7677,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820399284363</v>
       </c>
       <c r="H252" t="n">
         <v>83758</v>
@@ -7706,7 +7706,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.9870982170105</v>
+        <v>3.98709797859192</v>
       </c>
       <c r="H253" t="n">
         <v>124841</v>
@@ -7764,7 +7764,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599291801453</v>
       </c>
       <c r="H255" t="n">
         <v>60629</v>
@@ -7793,7 +7793,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820351600647</v>
+        <v>3.99820399284363</v>
       </c>
       <c r="H256" t="n">
         <v>75406</v>
@@ -7851,7 +7851,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="n">
-        <v>4.04262828826904</v>
+        <v>4.0426287651062</v>
       </c>
       <c r="H258" t="n">
         <v>68035</v>
@@ -7938,7 +7938,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="n">
-        <v>4.2147741317749</v>
+        <v>4.21477365493774</v>
       </c>
       <c r="H261" t="n">
         <v>186483</v>
@@ -7996,7 +7996,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="n">
-        <v>4.13147783279419</v>
+        <v>4.13147735595703</v>
       </c>
       <c r="H263" t="n">
         <v>266804</v>
@@ -8054,7 +8054,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533729553223</v>
+        <v>4.19533777236938</v>
       </c>
       <c r="H265" t="n">
         <v>229274</v>
@@ -8141,7 +8141,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="n">
-        <v>4.15091276168823</v>
+        <v>4.15091323852539</v>
       </c>
       <c r="H268" t="n">
         <v>41601</v>
@@ -8170,7 +8170,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481809616089</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H269" t="n">
         <v>45733</v>
@@ -8315,7 +8315,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="n">
-        <v>4.06484127044678</v>
+        <v>4.06484079360962</v>
       </c>
       <c r="H274" t="n">
         <v>94442</v>
@@ -8431,7 +8431,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="n">
-        <v>3.83438897132874</v>
+        <v>3.83438873291016</v>
       </c>
       <c r="H278" t="n">
         <v>128544</v>
@@ -8460,7 +8460,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="n">
-        <v>3.86492991447449</v>
+        <v>3.86493039131165</v>
       </c>
       <c r="H279" t="n">
         <v>46654</v>
@@ -8489,7 +8489,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933294296265</v>
+        <v>3.95933318138123</v>
       </c>
       <c r="H280" t="n">
         <v>55134</v>
@@ -8576,7 +8576,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380191802979</v>
       </c>
       <c r="H283" t="n">
         <v>61425</v>
@@ -8605,7 +8605,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="n">
-        <v>3.9038028717041</v>
+        <v>3.90380191802979</v>
       </c>
       <c r="H284" t="n">
         <v>71158</v>
@@ -8634,7 +8634,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599291801453</v>
       </c>
       <c r="H285" t="n">
         <v>110096</v>
@@ -8663,7 +8663,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H286" t="n">
         <v>167527</v>
@@ -8692,7 +8692,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G287" t="n">
-        <v>4.05373525619507</v>
+        <v>4.05373477935791</v>
       </c>
       <c r="H287" t="n">
         <v>78301</v>
@@ -8750,7 +8750,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H289" t="n">
         <v>61110</v>
@@ -8808,7 +8808,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="n">
-        <v>4.15646648406982</v>
+        <v>4.15646600723267</v>
       </c>
       <c r="H291" t="n">
         <v>112554</v>
@@ -8866,7 +8866,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="n">
-        <v>4.1620192527771</v>
+        <v>4.16201972961426</v>
       </c>
       <c r="H293" t="n">
         <v>49804</v>
@@ -8895,7 +8895,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="n">
-        <v>4.07317018508911</v>
+        <v>4.07317066192627</v>
       </c>
       <c r="H294" t="n">
         <v>80824</v>
@@ -8982,7 +8982,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="n">
-        <v>4.07594728469849</v>
+        <v>4.07594633102417</v>
       </c>
       <c r="H297" t="n">
         <v>154156</v>
@@ -9040,7 +9040,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H299" t="n">
         <v>223547</v>
@@ -9069,7 +9069,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H300" t="n">
         <v>617047</v>
@@ -9127,7 +9127,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G302" t="n">
-        <v>4.33694124221802</v>
+        <v>4.33694076538086</v>
       </c>
       <c r="H302" t="n">
         <v>287161</v>
@@ -9185,7 +9185,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H304" t="n">
         <v>116065</v>
@@ -9243,7 +9243,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025833129883</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H306" t="n">
         <v>134817</v>
@@ -9272,7 +9272,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="n">
-        <v>4.35637712478638</v>
+        <v>4.35637664794922</v>
       </c>
       <c r="H307" t="n">
         <v>145037</v>
@@ -9301,7 +9301,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="n">
-        <v>4.30084705352783</v>
+        <v>4.30084657669067</v>
       </c>
       <c r="H308" t="n">
         <v>223330</v>
@@ -9388,7 +9388,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917549133301</v>
+        <v>4.30917501449585</v>
       </c>
       <c r="H311" t="n">
         <v>289755</v>
@@ -9417,7 +9417,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134260177612</v>
+        <v>4.43134307861328</v>
       </c>
       <c r="H312" t="n">
         <v>618378</v>
@@ -9446,7 +9446,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188545227051</v>
+        <v>4.46188497543335</v>
       </c>
       <c r="H313" t="n">
         <v>304602</v>
@@ -9475,7 +9475,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G314" t="n">
-        <v>4.45355558395386</v>
+        <v>4.4535551071167</v>
       </c>
       <c r="H314" t="n">
         <v>193672</v>
@@ -9591,7 +9591,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.54240417480469</v>
+        <v>4.54240369796753</v>
       </c>
       <c r="H318" t="n">
         <v>245027</v>
@@ -9620,7 +9620,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="n">
-        <v>4.63403034210205</v>
+        <v>4.63402891159058</v>
       </c>
       <c r="H319" t="n">
         <v>498945</v>
@@ -9649,7 +9649,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="n">
-        <v>4.56461668014526</v>
+        <v>4.56461572647095</v>
       </c>
       <c r="H320" t="n">
         <v>231935</v>
@@ -9765,7 +9765,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685235977173</v>
+        <v>4.53685140609741</v>
       </c>
       <c r="H324" t="n">
         <v>98610</v>
@@ -9881,7 +9881,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132085800171</v>
+        <v>4.48132038116455</v>
       </c>
       <c r="H328" t="n">
         <v>165632</v>
@@ -9910,7 +9910,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="n">
-        <v>4.45910787582397</v>
+        <v>4.45910835266113</v>
       </c>
       <c r="H329" t="n">
         <v>312941</v>
@@ -10084,7 +10084,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362224578857</v>
+        <v>4.30362272262573</v>
       </c>
       <c r="H335" t="n">
         <v>151724</v>
@@ -10113,7 +10113,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244861602783</v>
+        <v>4.44244909286499</v>
       </c>
       <c r="H336" t="n">
         <v>246106</v>
@@ -10142,7 +10142,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="n">
-        <v>4.54795694351196</v>
+        <v>4.54795742034912</v>
       </c>
       <c r="H337" t="n">
         <v>152659</v>
@@ -10171,7 +10171,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075674057007</v>
+        <v>4.50075578689575</v>
       </c>
       <c r="H338" t="n">
         <v>185305</v>
@@ -10200,7 +10200,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="n">
-        <v>4.57849836349487</v>
+        <v>4.57849884033203</v>
       </c>
       <c r="H339" t="n">
         <v>327114</v>
@@ -10229,7 +10229,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="n">
-        <v>4.56461668014526</v>
+        <v>4.56461572647095</v>
       </c>
       <c r="H340" t="n">
         <v>221386</v>
@@ -10287,7 +10287,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127641677856</v>
+        <v>4.58127546310425</v>
       </c>
       <c r="H342" t="n">
         <v>62152</v>
@@ -10345,7 +10345,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="n">
-        <v>4.60348796844482</v>
+        <v>4.60348749160767</v>
       </c>
       <c r="H344" t="n">
         <v>103263</v>
@@ -10374,7 +10374,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346574783325</v>
+        <v>4.65346622467041</v>
       </c>
       <c r="H345" t="n">
         <v>177286</v>
@@ -10403,7 +10403,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="n">
-        <v>4.75342035293579</v>
+        <v>4.75342082977295</v>
       </c>
       <c r="H346" t="n">
         <v>342741</v>
@@ -10432,7 +10432,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="n">
-        <v>4.77563333511353</v>
+        <v>4.77563285827637</v>
       </c>
       <c r="H347" t="n">
         <v>352359</v>
@@ -10461,7 +10461,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="n">
-        <v>4.80895137786865</v>
+        <v>4.80895090103149</v>
       </c>
       <c r="H348" t="n">
         <v>235964</v>
@@ -10490,7 +10490,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782266616821</v>
       </c>
       <c r="H349" t="n">
         <v>172083</v>
@@ -10519,7 +10519,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="n">
-        <v>4.8783655166626</v>
+        <v>4.87836503982544</v>
       </c>
       <c r="H350" t="n">
         <v>140823</v>
@@ -10548,7 +10548,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782266616821</v>
       </c>
       <c r="H351" t="n">
         <v>122329</v>
@@ -10577,7 +10577,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010231018066</v>
+        <v>4.72010278701782</v>
       </c>
       <c r="H352" t="n">
         <v>291161</v>
@@ -10606,7 +10606,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="n">
-        <v>4.69233655929565</v>
+        <v>4.69233703613281</v>
       </c>
       <c r="H353" t="n">
         <v>196081</v>
@@ -10693,7 +10693,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865795135498</v>
       </c>
       <c r="H356" t="n">
         <v>265806</v>
@@ -10722,7 +10722,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H357" t="n">
         <v>212034</v>
@@ -10751,7 +10751,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H358" t="n">
         <v>157901</v>
@@ -10780,7 +10780,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H359" t="n">
         <v>148993</v>
@@ -10809,7 +10809,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="n">
-        <v>4.73865747451782</v>
+        <v>4.73865795135498</v>
       </c>
       <c r="H360" t="n">
         <v>158526</v>
@@ -10896,7 +10896,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H363" t="n">
         <v>258831</v>
@@ -10925,7 +10925,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83618450164795</v>
+        <v>4.83618402481079</v>
       </c>
       <c r="H364" t="n">
         <v>244646</v>
@@ -10954,7 +10954,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315853118896</v>
       </c>
       <c r="H365" t="n">
         <v>146539</v>
@@ -10983,7 +10983,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H366" t="n">
         <v>77359</v>
@@ -11041,7 +11041,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H368" t="n">
         <v>114636</v>
@@ -11070,7 +11070,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H369" t="n">
         <v>54213</v>
@@ -11157,7 +11157,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586748123169</v>
       </c>
       <c r="H372" t="n">
         <v>148350</v>
@@ -11186,7 +11186,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.71571063995361</v>
+        <v>4.7157096862793</v>
       </c>
       <c r="H373" t="n">
         <v>190474</v>
@@ -11244,7 +11244,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H375" t="n">
         <v>145512</v>
@@ -11273,7 +11273,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965679168701</v>
+        <v>4.62965726852417</v>
       </c>
       <c r="H376" t="n">
         <v>155173</v>
@@ -11302,7 +11302,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="n">
-        <v>4.60384082794189</v>
+        <v>4.60384130477905</v>
       </c>
       <c r="H377" t="n">
         <v>76641</v>
@@ -11331,7 +11331,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="n">
-        <v>4.58376264572144</v>
+        <v>4.58376216888428</v>
       </c>
       <c r="H378" t="n">
         <v>95959</v>
@@ -11418,7 +11418,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="n">
-        <v>4.56655120849609</v>
+        <v>4.56655216217041</v>
       </c>
       <c r="H381" t="n">
         <v>80390</v>
@@ -11447,7 +11447,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="n">
-        <v>4.49770879745483</v>
+        <v>4.49770927429199</v>
       </c>
       <c r="H382" t="n">
         <v>132223</v>
@@ -11505,7 +11505,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42312908172607</v>
+        <v>4.42312955856323</v>
       </c>
       <c r="H384" t="n">
         <v>90869</v>
@@ -11563,7 +11563,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786754608154</v>
+        <v>4.53786706924438</v>
       </c>
       <c r="H386" t="n">
         <v>105901</v>
@@ -11592,7 +11592,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507802963257</v>
+        <v>4.55507755279541</v>
       </c>
       <c r="H387" t="n">
         <v>112131</v>
@@ -11621,7 +11621,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476148605347</v>
+        <v>4.47476196289062</v>
       </c>
       <c r="H388" t="n">
         <v>139029</v>
@@ -11650,7 +11650,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="n">
-        <v>4.56081438064575</v>
+        <v>4.56081485748291</v>
       </c>
       <c r="H389" t="n">
         <v>61346</v>
@@ -11737,7 +11737,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66121006011963</v>
+        <v>4.66120958328247</v>
       </c>
       <c r="H392" t="n">
         <v>102329</v>
@@ -11766,7 +11766,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586748123169</v>
       </c>
       <c r="H393" t="n">
         <v>165524</v>
@@ -11795,7 +11795,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="n">
-        <v>4.76447296142578</v>
+        <v>4.7644739151001</v>
       </c>
       <c r="H394" t="n">
         <v>83113</v>
@@ -11824,7 +11824,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H395" t="n">
         <v>98585</v>
@@ -11853,7 +11853,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H396" t="n">
         <v>93726</v>
@@ -11882,7 +11882,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="n">
-        <v>4.76160478591919</v>
+        <v>4.76160526275635</v>
       </c>
       <c r="H397" t="n">
         <v>136912</v>
@@ -11911,7 +11911,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315853118896</v>
       </c>
       <c r="H398" t="n">
         <v>177747</v>
@@ -11969,7 +11969,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="n">
-        <v>4.80750036239624</v>
+        <v>4.8075008392334</v>
       </c>
       <c r="H400" t="n">
         <v>175291</v>
@@ -11998,7 +11998,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H401" t="n">
         <v>142867</v>
@@ -12027,7 +12027,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="n">
-        <v>4.77881622314453</v>
+        <v>4.77881574630737</v>
       </c>
       <c r="H402" t="n">
         <v>106729</v>
@@ -12056,7 +12056,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H403" t="n">
         <v>128308</v>
@@ -12114,7 +12114,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="n">
-        <v>4.7329216003418</v>
+        <v>4.73292064666748</v>
       </c>
       <c r="H405" t="n">
         <v>130388</v>
@@ -12143,7 +12143,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67555236816406</v>
+        <v>4.6755518913269</v>
       </c>
       <c r="H406" t="n">
         <v>170600</v>
@@ -12172,7 +12172,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857929229736</v>
       </c>
       <c r="H407" t="n">
         <v>123210</v>
@@ -12201,7 +12201,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857929229736</v>
       </c>
       <c r="H408" t="n">
         <v>135862</v>
@@ -12230,7 +12230,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H409" t="n">
         <v>386315</v>
@@ -12259,7 +12259,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757997512817</v>
+        <v>4.82757902145386</v>
       </c>
       <c r="H410" t="n">
         <v>233195</v>
@@ -12288,7 +12288,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634325027466</v>
       </c>
       <c r="H411" t="n">
         <v>129788</v>
@@ -12317,7 +12317,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="n">
-        <v>4.87060546875</v>
+        <v>4.87060594558716</v>
       </c>
       <c r="H412" t="n">
         <v>185451</v>
@@ -12346,7 +12346,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="n">
-        <v>4.82184219360352</v>
+        <v>4.82184171676636</v>
       </c>
       <c r="H413" t="n">
         <v>171784</v>
@@ -12375,7 +12375,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="n">
-        <v>4.75586795806885</v>
+        <v>4.75586748123169</v>
       </c>
       <c r="H414" t="n">
         <v>223989</v>
@@ -12433,7 +12433,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673749923706</v>
       </c>
       <c r="H416" t="n">
         <v>400107</v>
@@ -12462,7 +12462,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="n">
-        <v>4.94518566131592</v>
+        <v>4.94518613815308</v>
       </c>
       <c r="H417" t="n">
         <v>199295</v>
@@ -12520,7 +12520,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="n">
-        <v>4.89642143249512</v>
+        <v>4.89642190933228</v>
       </c>
       <c r="H419" t="n">
         <v>51293</v>
@@ -12578,7 +12578,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="n">
-        <v>4.91650104522705</v>
+        <v>4.91650056838989</v>
       </c>
       <c r="H421" t="n">
         <v>72335</v>
@@ -12607,7 +12607,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="n">
-        <v>4.93371200561523</v>
+        <v>4.93371105194092</v>
       </c>
       <c r="H422" t="n">
         <v>38701</v>
@@ -12636,7 +12636,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="n">
-        <v>4.91650104522705</v>
+        <v>4.91650056838989</v>
       </c>
       <c r="H423" t="n">
         <v>34375</v>
@@ -12694,7 +12694,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052633285522</v>
+        <v>4.85052680969238</v>
       </c>
       <c r="H425" t="n">
         <v>172662</v>
@@ -12723,7 +12723,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H426" t="n">
         <v>53465</v>
@@ -12839,7 +12839,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.8763427734375</v>
+        <v>4.87634325027466</v>
       </c>
       <c r="H430" t="n">
         <v>81300</v>
@@ -12868,7 +12868,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="n">
-        <v>4.81897401809692</v>
+        <v>4.81897354125977</v>
       </c>
       <c r="H431" t="n">
         <v>59100</v>
@@ -12897,7 +12897,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="n">
-        <v>4.81897401809692</v>
+        <v>4.81897354125977</v>
       </c>
       <c r="H432" t="n">
         <v>85576</v>
@@ -12955,7 +12955,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.88781690597534</v>
+        <v>4.88781642913818</v>
       </c>
       <c r="H434" t="n">
         <v>180331</v>
@@ -12984,7 +12984,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="n">
-        <v>4.95665884017944</v>
+        <v>4.95665836334229</v>
       </c>
       <c r="H435" t="n">
         <v>201090</v>
@@ -13042,7 +13042,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H437" t="n">
         <v>135001</v>
@@ -13187,7 +13187,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99107980728149</v>
+        <v>4.99108028411865</v>
       </c>
       <c r="H442" t="n">
         <v>93886</v>
@@ -13216,7 +13216,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673749923706</v>
       </c>
       <c r="H443" t="n">
         <v>69536</v>
@@ -13245,7 +13245,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255346298218</v>
+        <v>5.00255298614502</v>
       </c>
       <c r="H444" t="n">
         <v>82992</v>
@@ -13274,7 +13274,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673797607422</v>
+        <v>4.97673749923706</v>
       </c>
       <c r="H445" t="n">
         <v>104775</v>
@@ -13303,7 +13303,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="n">
-        <v>5.02550172805786</v>
+        <v>5.0255012512207</v>
       </c>
       <c r="H446" t="n">
         <v>100760</v>
@@ -13448,7 +13448,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713317871094</v>
+        <v>5.0771336555481</v>
       </c>
       <c r="H451" t="n">
         <v>127366</v>
@@ -13506,7 +13506,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="n">
-        <v>4.96813297271729</v>
+        <v>4.96813249588013</v>
       </c>
       <c r="H453" t="n">
         <v>121584</v>
@@ -13535,7 +13535,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="n">
-        <v>4.98247528076172</v>
+        <v>4.9824743270874</v>
       </c>
       <c r="H454" t="n">
         <v>322636</v>
@@ -13564,7 +13564,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="n">
-        <v>5.0312385559082</v>
+        <v>5.03123807907104</v>
       </c>
       <c r="H455" t="n">
         <v>77579</v>
@@ -13593,7 +13593,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="n">
-        <v>5.05992269515991</v>
+        <v>5.05992221832275</v>
       </c>
       <c r="H456" t="n">
         <v>168873</v>
@@ -13651,7 +13651,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923849105835</v>
+        <v>5.24923896789551</v>
       </c>
       <c r="H458" t="n">
         <v>199889</v>
@@ -13680,7 +13680,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H459" t="n">
         <v>352083</v>
@@ -13709,7 +13709,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="n">
-        <v>5.45003032684326</v>
+        <v>5.45003080368042</v>
       </c>
       <c r="H460" t="n">
         <v>197490</v>
@@ -13738,7 +13738,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="n">
         <v>90087</v>
@@ -13854,7 +13854,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="n">
-        <v>5.39839792251587</v>
+        <v>5.39839744567871</v>
       </c>
       <c r="H465" t="n">
         <v>318851</v>
@@ -13883,7 +13883,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266204833984</v>
       </c>
       <c r="H466" t="n">
         <v>156702</v>
@@ -13941,7 +13941,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="n">
-        <v>5.38118743896484</v>
+        <v>5.38118696212769</v>
       </c>
       <c r="H468" t="n">
         <v>235300</v>
@@ -13999,7 +13999,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384765625</v>
+        <v>5.69384717941284</v>
       </c>
       <c r="H470" t="n">
         <v>1020120</v>
@@ -14086,7 +14086,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208642959595</v>
+        <v>5.97208595275879</v>
       </c>
       <c r="H473" t="n">
         <v>582524</v>
@@ -14173,7 +14173,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="n">
-        <v>5.93766498565674</v>
+        <v>5.93766450881958</v>
       </c>
       <c r="H476" t="n">
         <v>309094</v>
@@ -14202,7 +14202,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292604446411</v>
+        <v>5.82292652130127</v>
       </c>
       <c r="H477" t="n">
         <v>320356</v>
@@ -14347,7 +14347,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H482" t="n">
         <v>514848</v>
@@ -14405,7 +14405,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H484" t="n">
         <v>197193</v>
@@ -14463,7 +14463,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287588119507</v>
+        <v>6.17287635803223</v>
       </c>
       <c r="H486" t="n">
         <v>406962</v>
@@ -14492,7 +14492,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="n">
-        <v>6.16140270233154</v>
+        <v>6.16140222549438</v>
       </c>
       <c r="H487" t="n">
         <v>223944</v>
@@ -14550,7 +14550,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="n">
-        <v>6.20729637145996</v>
+        <v>6.20729684829712</v>
       </c>
       <c r="H489" t="n">
         <v>210356</v>
@@ -14579,7 +14579,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="n">
-        <v>6.24171924591064</v>
+        <v>6.24171829223633</v>
       </c>
       <c r="H490" t="n">
         <v>199304</v>
@@ -14637,7 +14637,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="n">
-        <v>6.17861318588257</v>
+        <v>6.17861366271973</v>
       </c>
       <c r="H492" t="n">
         <v>176102</v>
@@ -14666,7 +14666,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371692657471</v>
+        <v>6.02371788024902</v>
       </c>
       <c r="H493" t="n">
         <v>167344</v>
@@ -14695,7 +14695,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.06961297988892</v>
+        <v>6.06961250305176</v>
       </c>
       <c r="H494" t="n">
         <v>134266</v>
@@ -14724,7 +14724,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="n">
-        <v>6.16140270233154</v>
+        <v>6.16140222549438</v>
       </c>
       <c r="H495" t="n">
         <v>110811</v>
@@ -14753,7 +14753,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="n">
-        <v>6.13271760940552</v>
+        <v>6.13271808624268</v>
       </c>
       <c r="H496" t="n">
         <v>108347</v>
@@ -14782,7 +14782,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="n">
-        <v>6.21877145767212</v>
+        <v>6.21877193450928</v>
       </c>
       <c r="H497" t="n">
         <v>176629</v>
@@ -14811,7 +14811,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36793088912964</v>
+        <v>6.36792993545532</v>
       </c>
       <c r="H498" t="n">
         <v>358977</v>
@@ -14840,7 +14840,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645580291748</v>
+        <v>6.35645627975464</v>
       </c>
       <c r="H499" t="n">
         <v>283557</v>
@@ -14927,7 +14927,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.42529916763306</v>
+        <v>6.4252986907959</v>
       </c>
       <c r="H502" t="n">
         <v>210048</v>
@@ -14985,7 +14985,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="n">
-        <v>5.85734796524048</v>
+        <v>5.85734748840332</v>
       </c>
       <c r="H504" t="n">
         <v>968569</v>
@@ -15043,7 +15043,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476783752441</v>
+        <v>5.56476736068726</v>
       </c>
       <c r="H506" t="n">
         <v>358726</v>
@@ -15072,7 +15072,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="n">
-        <v>5.60492467880249</v>
+        <v>5.60492515563965</v>
       </c>
       <c r="H507" t="n">
         <v>138334</v>
@@ -15101,7 +15101,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="n">
-        <v>5.48158264160156</v>
+        <v>5.48158359527588</v>
       </c>
       <c r="H508" t="n">
         <v>285423</v>
@@ -15130,7 +15130,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="n">
-        <v>5.53608274459839</v>
+        <v>5.53608322143555</v>
       </c>
       <c r="H509" t="n">
         <v>190384</v>
@@ -15188,7 +15188,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034687042236</v>
+        <v>5.53034639358521</v>
       </c>
       <c r="H511" t="n">
         <v>118130</v>
@@ -15217,7 +15217,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460861206055</v>
+        <v>5.52460908889771</v>
       </c>
       <c r="H512" t="n">
         <v>137903</v>
@@ -15246,7 +15246,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476783752441</v>
+        <v>5.56476736068726</v>
       </c>
       <c r="H513" t="n">
         <v>146003</v>
@@ -15275,7 +15275,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.65082120895386</v>
+        <v>5.65082025527954</v>
       </c>
       <c r="H514" t="n">
         <v>122075</v>
@@ -15304,7 +15304,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="n">
-        <v>5.65655755996704</v>
+        <v>5.65655708312988</v>
       </c>
       <c r="H515" t="n">
         <v>86233</v>
@@ -15420,7 +15420,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903100967407</v>
+        <v>5.55903053283691</v>
       </c>
       <c r="H519" t="n">
         <v>232788</v>
@@ -15478,7 +15478,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="n">
-        <v>5.59345149993896</v>
+        <v>5.59345245361328</v>
       </c>
       <c r="H521" t="n">
         <v>134956</v>
@@ -15536,7 +15536,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="n">
-        <v>5.48445081710815</v>
+        <v>5.48445129394531</v>
       </c>
       <c r="H523" t="n">
         <v>150058</v>
@@ -15623,7 +15623,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="n">
-        <v>5.53608274459839</v>
+        <v>5.53608322143555</v>
       </c>
       <c r="H526" t="n">
         <v>224626</v>
@@ -15681,7 +15681,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.49592542648315</v>
+        <v>5.495924949646</v>
       </c>
       <c r="H528" t="n">
         <v>109874</v>
@@ -15710,7 +15710,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="n">
         <v>108597</v>
@@ -15768,7 +15768,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.46150350570679</v>
+        <v>5.46150398254395</v>
       </c>
       <c r="H531" t="n">
         <v>150985</v>
@@ -15826,7 +15826,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266204833984</v>
       </c>
       <c r="H533" t="n">
         <v>107752</v>
@@ -15855,7 +15855,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="n">
-        <v>5.26645040512085</v>
+        <v>5.26644945144653</v>
       </c>
       <c r="H534" t="n">
         <v>82474</v>
@@ -15913,7 +15913,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="n">
-        <v>5.0312385559082</v>
+        <v>5.03123807907104</v>
       </c>
       <c r="H536" t="n">
         <v>159220</v>
@@ -15971,7 +15971,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="n">
-        <v>5.12302827835083</v>
+        <v>5.12302875518799</v>
       </c>
       <c r="H538" t="n">
         <v>107280</v>
@@ -16000,7 +16000,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85913181304932</v>
+        <v>4.85913228988647</v>
       </c>
       <c r="H539" t="n">
         <v>191289</v>
@@ -16087,7 +16087,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="n">
-        <v>4.49770879745483</v>
+        <v>4.49770927429199</v>
       </c>
       <c r="H542" t="n">
         <v>312675</v>
@@ -16116,7 +16116,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="n">
-        <v>4.74439477920532</v>
+        <v>4.74439430236816</v>
       </c>
       <c r="H543" t="n">
         <v>179153</v>
@@ -16145,7 +16145,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="n">
-        <v>4.67555236816406</v>
+        <v>4.6755518913269</v>
       </c>
       <c r="H544" t="n">
         <v>158012</v>
@@ -16203,7 +16203,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="n">
-        <v>4.69849872589111</v>
+        <v>4.69849967956543</v>
       </c>
       <c r="H546" t="n">
         <v>190634</v>
@@ -16232,7 +16232,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H547" t="n">
         <v>100189</v>
@@ -16290,7 +16290,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="n">
-        <v>4.96239519119263</v>
+        <v>4.96239566802979</v>
       </c>
       <c r="H549" t="n">
         <v>263540</v>
@@ -16319,7 +16319,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71571063995361</v>
+        <v>4.7157096862793</v>
       </c>
       <c r="H550" t="n">
         <v>314139</v>
@@ -16348,7 +16348,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="n">
-        <v>4.58949851989746</v>
+        <v>4.58949899673462</v>
       </c>
       <c r="H551" t="n">
         <v>187834</v>
@@ -16435,7 +16435,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="n">
-        <v>4.42657089233398</v>
+        <v>4.4265718460083</v>
       </c>
       <c r="H554" t="n">
         <v>163330</v>
@@ -16493,7 +16493,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="n">
-        <v>4.31126070022583</v>
+        <v>4.31126022338867</v>
       </c>
       <c r="H556" t="n">
         <v>191054</v>
@@ -16522,7 +16522,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="n">
-        <v>4.371497631073</v>
+        <v>4.37149715423584</v>
       </c>
       <c r="H557" t="n">
         <v>224606</v>
@@ -16580,7 +16580,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401926040649</v>
+        <v>4.50401973724365</v>
       </c>
       <c r="H559" t="n">
         <v>186947</v>
@@ -16667,7 +16667,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="n">
-        <v>4.35371351242065</v>
+        <v>4.3537130355835</v>
       </c>
       <c r="H562" t="n">
         <v>116896</v>
@@ -16696,7 +16696,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="n">
-        <v>4.25676012039185</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H563" t="n">
         <v>136013</v>
@@ -16725,7 +16725,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="n">
-        <v>4.21430683135986</v>
+        <v>4.21430778503418</v>
       </c>
       <c r="H564" t="n">
         <v>433130</v>
@@ -16783,7 +16783,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="n">
-        <v>4.32732439041138</v>
+        <v>4.32732343673706</v>
       </c>
       <c r="H566" t="n">
         <v>299973</v>
@@ -16812,7 +16812,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.30781841278076</v>
+        <v>4.3078179359436</v>
       </c>
       <c r="H567" t="n">
         <v>181767</v>
@@ -16899,7 +16899,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="n">
-        <v>4.04449605941772</v>
+        <v>4.04449653625488</v>
       </c>
       <c r="H570" t="n">
         <v>630273</v>
@@ -16928,7 +16928,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.41232681274414</v>
+        <v>4.4123272895813</v>
       </c>
       <c r="H571" t="n">
         <v>1211216</v>
@@ -16986,7 +16986,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="n">
-        <v>4.9232931137085</v>
+        <v>4.92329263687134</v>
       </c>
       <c r="H573" t="n">
         <v>1058195</v>
@@ -17015,7 +17015,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262052536011</v>
+        <v>4.68262100219727</v>
       </c>
       <c r="H574" t="n">
         <v>630734</v>
@@ -17102,7 +17102,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="n">
-        <v>5.15902853012085</v>
+        <v>5.15902805328369</v>
       </c>
       <c r="H577" t="n">
         <v>736664</v>
@@ -17189,7 +17189,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="n">
-        <v>4.83628082275391</v>
+        <v>4.83628034591675</v>
       </c>
       <c r="H580" t="n">
         <v>645972</v>
@@ -17218,7 +17218,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493427276611</v>
+        <v>4.79493379592896</v>
       </c>
       <c r="H581" t="n">
         <v>391338</v>
@@ -17276,7 +17276,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344699859619</v>
       </c>
       <c r="H583" t="n">
         <v>201360</v>
@@ -17305,7 +17305,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086639404297</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H584" t="n">
         <v>346291</v>
@@ -17334,7 +17334,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.85479402542114</v>
+        <v>4.85479354858398</v>
       </c>
       <c r="H585" t="n">
         <v>306793</v>
@@ -17363,7 +17363,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344699859619</v>
       </c>
       <c r="H586" t="n">
         <v>659396</v>
@@ -17421,7 +17421,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84924030303955</v>
+        <v>4.84923934936523</v>
       </c>
       <c r="H588" t="n">
         <v>752626</v>
@@ -17450,7 +17450,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813142776489</v>
       </c>
       <c r="H589" t="n">
         <v>513903</v>
@@ -17479,7 +17479,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.90601396560669</v>
+        <v>4.90601348876953</v>
       </c>
       <c r="H590" t="n">
         <v>246728</v>
@@ -17508,7 +17508,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>4.81344747543335</v>
+        <v>4.81344699859619</v>
       </c>
       <c r="H591" t="n">
         <v>329652</v>
@@ -17595,7 +17595,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>4.79061412811279</v>
+        <v>4.79061460494995</v>
       </c>
       <c r="H594" t="n">
         <v>309631</v>
@@ -17653,7 +17653,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="n">
-        <v>4.86281681060791</v>
+        <v>4.86281633377075</v>
       </c>
       <c r="H596" t="n">
         <v>196693</v>
@@ -17711,7 +17711,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="n">
-        <v>4.9368691444397</v>
+        <v>4.93686962127686</v>
       </c>
       <c r="H598" t="n">
         <v>231247</v>
@@ -17740,7 +17740,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132953643799</v>
+        <v>4.88132905960083</v>
       </c>
       <c r="H599" t="n">
         <v>300176</v>
@@ -17769,7 +17769,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="n">
-        <v>4.83813190460205</v>
+        <v>4.83813142776489</v>
       </c>
       <c r="H600" t="n">
         <v>417093</v>
@@ -17798,7 +17798,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="n">
-        <v>4.8912034034729</v>
+        <v>4.89120292663574</v>
       </c>
       <c r="H601" t="n">
         <v>368002</v>
@@ -17827,7 +17827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029033660889</v>
+        <v>5.06029081344604</v>
       </c>
       <c r="H602" t="n">
         <v>586567</v>
@@ -17856,7 +17856,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="n">
-        <v>4.96031904220581</v>
+        <v>4.96031951904297</v>
       </c>
       <c r="H603" t="n">
         <v>320650</v>
@@ -17885,7 +17885,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="n">
-        <v>4.9368691444397</v>
+        <v>4.93686962127686</v>
       </c>
       <c r="H604" t="n">
         <v>278602</v>
@@ -17914,7 +17914,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.80357360839844</v>
+        <v>4.80357313156128</v>
       </c>
       <c r="H605" t="n">
         <v>567119</v>
@@ -17943,7 +17943,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086639404297</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H606" t="n">
         <v>413652</v>
@@ -18001,7 +18001,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>4.66472482681274</v>
+        <v>4.66472387313843</v>
       </c>
       <c r="H608" t="n">
         <v>204562</v>
@@ -18030,7 +18030,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>4.61288738250732</v>
+        <v>4.61288690567017</v>
       </c>
       <c r="H609" t="n">
         <v>290843</v>
@@ -18059,7 +18059,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.56660461425781</v>
+        <v>4.56660413742065</v>
       </c>
       <c r="H610" t="n">
         <v>544954</v>
@@ -18146,7 +18146,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="n">
-        <v>4.39072799682617</v>
+        <v>4.39072847366333</v>
       </c>
       <c r="H613" t="n">
         <v>283150</v>
@@ -18204,7 +18204,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="n">
-        <v>4.41294431686401</v>
+        <v>4.41294384002686</v>
       </c>
       <c r="H615" t="n">
         <v>451434</v>
@@ -18233,7 +18233,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="n">
-        <v>4.4888482093811</v>
+        <v>4.48884868621826</v>
       </c>
       <c r="H616" t="n">
         <v>397528</v>
@@ -18262,7 +18262,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="n">
-        <v>4.46786642074585</v>
+        <v>4.46786594390869</v>
       </c>
       <c r="H617" t="n">
         <v>480697</v>
@@ -18291,7 +18291,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="n">
-        <v>4.56290149688721</v>
+        <v>4.56290197372437</v>
       </c>
       <c r="H618" t="n">
         <v>282682</v>
@@ -18320,7 +18320,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.64991426467896</v>
+        <v>4.64991331100464</v>
       </c>
       <c r="H619" t="n">
         <v>270055</v>
@@ -18378,7 +18378,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="n">
-        <v>4.51908683776855</v>
+        <v>4.5190863609314</v>
       </c>
       <c r="H621" t="n">
         <v>353015</v>
@@ -18407,7 +18407,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="n">
-        <v>4.42528629302979</v>
+        <v>4.42528581619263</v>
       </c>
       <c r="H622" t="n">
         <v>399766</v>
@@ -18494,7 +18494,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716547012329</v>
+        <v>4.71716499328613</v>
       </c>
       <c r="H625" t="n">
         <v>188411</v>
@@ -18552,7 +18552,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="n">
-        <v>4.8544807434082</v>
+        <v>4.85448122024536</v>
       </c>
       <c r="H627" t="n">
         <v>274204</v>
@@ -18581,7 +18581,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>4.62495803833008</v>
+        <v>4.62495851516724</v>
       </c>
       <c r="H628" t="n">
         <v>345226</v>
@@ -18610,7 +18610,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="n">
-        <v>4.62628507614136</v>
+        <v>4.6262845993042</v>
       </c>
       <c r="H629" t="n">
         <v>314894</v>
@@ -18639,7 +18639,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="n">
-        <v>4.59311628341675</v>
+        <v>4.59311676025391</v>
       </c>
       <c r="H630" t="n">
         <v>231415</v>
@@ -18668,7 +18668,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>4.579185962677</v>
+        <v>4.57918548583984</v>
       </c>
       <c r="H631" t="n">
         <v>301522</v>
@@ -18697,7 +18697,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="n">
-        <v>4.68996810913086</v>
+        <v>4.6899676322937</v>
       </c>
       <c r="H632" t="n">
         <v>571701</v>
@@ -18726,7 +18726,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="n">
-        <v>4.62164068222046</v>
+        <v>4.62164115905762</v>
       </c>
       <c r="H633" t="n">
         <v>306266</v>
@@ -18813,7 +18813,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H636" t="n">
         <v>261556</v>
@@ -18842,7 +18842,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.5652551651001</v>
+        <v>4.56525611877441</v>
       </c>
       <c r="H637" t="n">
         <v>293870</v>
@@ -18871,7 +18871,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="n">
-        <v>4.67470979690552</v>
+        <v>4.67471027374268</v>
       </c>
       <c r="H638" t="n">
         <v>310832</v>
@@ -18900,7 +18900,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H639" t="n">
         <v>277774</v>
@@ -19016,7 +19016,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273866653442</v>
+        <v>4.80273914337158</v>
       </c>
       <c r="H643" t="n">
         <v>189484</v>
@@ -19161,7 +19161,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711610794067</v>
+        <v>4.72711563110352</v>
       </c>
       <c r="H648" t="n">
         <v>124423</v>
@@ -19190,7 +19190,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094722747803</v>
+        <v>4.76094675064087</v>
       </c>
       <c r="H649" t="n">
         <v>201117</v>
@@ -19248,7 +19248,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637138366699</v>
+        <v>4.87637186050415</v>
       </c>
       <c r="H651" t="n">
         <v>272806</v>
@@ -19306,7 +19306,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="n">
-        <v>4.80406522750854</v>
+        <v>4.8040657043457</v>
       </c>
       <c r="H653" t="n">
         <v>82622</v>
@@ -19335,7 +19335,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="n">
-        <v>4.81666946411133</v>
+        <v>4.81666994094849</v>
       </c>
       <c r="H654" t="n">
         <v>190438</v>
@@ -19393,7 +19393,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="n">
-        <v>4.80937337875366</v>
+        <v>4.80937242507935</v>
       </c>
       <c r="H656" t="n">
         <v>107726</v>
@@ -19422,7 +19422,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="n">
-        <v>4.68134450912476</v>
+        <v>4.6813440322876</v>
       </c>
       <c r="H657" t="n">
         <v>218824</v>
@@ -19538,7 +19538,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="n">
-        <v>4.74370002746582</v>
+        <v>4.74369955062866</v>
       </c>
       <c r="H661" t="n">
         <v>212597</v>
@@ -19596,7 +19596,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="n">
-        <v>4.59776020050049</v>
+        <v>4.59776067733765</v>
       </c>
       <c r="H663" t="n">
         <v>123007</v>
@@ -19625,7 +19625,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.61832427978516</v>
+        <v>4.618323802948</v>
       </c>
       <c r="H664" t="n">
         <v>65498</v>
@@ -19683,7 +19683,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="n">
-        <v>4.58316612243652</v>
+        <v>4.58316659927368</v>
       </c>
       <c r="H666" t="n">
         <v>106623</v>
@@ -19828,7 +19828,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="n">
-        <v>4.32445573806763</v>
+        <v>4.32445478439331</v>
       </c>
       <c r="H671" t="n">
         <v>112382</v>
@@ -19857,7 +19857,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.360276222229</v>
+        <v>4.36027669906616</v>
       </c>
       <c r="H672" t="n">
         <v>84392</v>
@@ -19886,7 +19886,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44386053085327</v>
+        <v>4.44386005401611</v>
       </c>
       <c r="H673" t="n">
         <v>124244</v>
@@ -19915,7 +19915,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589973449707</v>
+        <v>4.43589925765991</v>
       </c>
       <c r="H674" t="n">
         <v>75809</v>
@@ -19973,7 +19973,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H676" t="n">
         <v>76513</v>
@@ -20031,7 +20031,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H678" t="n">
         <v>67624</v>
@@ -20060,7 +20060,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41135549545288</v>
+        <v>4.41135597229004</v>
       </c>
       <c r="H679" t="n">
         <v>86398</v>
@@ -20089,7 +20089,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="n">
-        <v>4.39211797714233</v>
+        <v>4.39211750030518</v>
       </c>
       <c r="H680" t="n">
         <v>166661</v>
@@ -20118,7 +20118,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="n">
-        <v>4.34767293930054</v>
+        <v>4.34767246246338</v>
       </c>
       <c r="H681" t="n">
         <v>198218</v>
@@ -20176,7 +20176,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="n">
-        <v>4.33241558074951</v>
+        <v>4.33241605758667</v>
       </c>
       <c r="H683" t="n">
         <v>70783</v>
@@ -20263,7 +20263,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="n">
-        <v>4.37089014053345</v>
+        <v>4.37089061737061</v>
       </c>
       <c r="H686" t="n">
         <v>63252</v>
@@ -20292,7 +20292,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H687" t="n">
         <v>314279</v>
@@ -20350,7 +20350,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="n">
-        <v>4.3655834197998</v>
+        <v>4.36558389663696</v>
       </c>
       <c r="H689" t="n">
         <v>46065</v>
@@ -20408,7 +20408,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="n">
-        <v>4.31981134414673</v>
+        <v>4.31981182098389</v>
       </c>
       <c r="H691" t="n">
         <v>143038</v>
@@ -20524,7 +20524,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>4.53739452362061</v>
+        <v>4.53739404678345</v>
       </c>
       <c r="H695" t="n">
         <v>120232</v>
@@ -20553,7 +20553,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>4.56392812728882</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H696" t="n">
         <v>221443</v>
@@ -20582,7 +20582,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="n">
-        <v>4.56392812728882</v>
+        <v>4.56392908096313</v>
       </c>
       <c r="H697" t="n">
         <v>91471</v>
@@ -20669,7 +20669,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="n">
-        <v>4.47039413452148</v>
+        <v>4.47039461135864</v>
       </c>
       <c r="H700" t="n">
         <v>88666</v>
@@ -20698,7 +20698,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012813568115</v>
+        <v>4.39012765884399</v>
       </c>
       <c r="H701" t="n">
         <v>153681</v>
@@ -20756,7 +20756,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="n">
-        <v>4.26010894775391</v>
+        <v>4.26010847091675</v>
       </c>
       <c r="H703" t="n">
         <v>227597</v>
@@ -20814,7 +20814,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>4.24551486968994</v>
+        <v>4.2455153465271</v>
       </c>
       <c r="H705" t="n">
         <v>110787</v>
@@ -20843,7 +20843,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984199523926</v>
+        <v>4.17984247207642</v>
       </c>
       <c r="H706" t="n">
         <v>112296</v>
@@ -20901,7 +20901,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>4.05645656585693</v>
+        <v>4.05645704269409</v>
       </c>
       <c r="H708" t="n">
         <v>219320</v>
@@ -20930,7 +20930,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599216461182</v>
+        <v>4.01599168777466</v>
       </c>
       <c r="H709" t="n">
         <v>198493</v>
@@ -21017,7 +21017,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.84749794006348</v>
+        <v>3.84749841690063</v>
       </c>
       <c r="H712" t="n">
         <v>189134</v>
@@ -21104,7 +21104,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720009803772</v>
       </c>
       <c r="H715" t="n">
         <v>154260</v>
@@ -21162,7 +21162,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026921272278</v>
+        <v>3.96026968955994</v>
       </c>
       <c r="H717" t="n">
         <v>50070</v>
@@ -21220,7 +21220,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="n">
-        <v>3.94434857368469</v>
+        <v>3.94434928894043</v>
       </c>
       <c r="H719" t="n">
         <v>130093</v>
@@ -21278,7 +21278,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="n">
-        <v>3.98614072799683</v>
+        <v>3.98614048957825</v>
       </c>
       <c r="H721" t="n">
         <v>73891</v>
@@ -21307,7 +21307,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="n">
-        <v>4.07105112075806</v>
+        <v>4.0710506439209</v>
       </c>
       <c r="H722" t="n">
         <v>119608</v>
@@ -21336,7 +21336,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="n">
-        <v>4.07105112075806</v>
+        <v>4.0710506439209</v>
       </c>
       <c r="H723" t="n">
         <v>51535</v>
@@ -21365,7 +21365,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H724" t="n">
         <v>227117</v>
@@ -21394,7 +21394,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="n">
-        <v>4.14601039886475</v>
+        <v>4.14601135253906</v>
       </c>
       <c r="H725" t="n">
         <v>144073</v>
@@ -21452,7 +21452,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>4.07237768173218</v>
+        <v>4.07237720489502</v>
       </c>
       <c r="H727" t="n">
         <v>83950</v>
@@ -21481,7 +21481,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00670480728149</v>
+        <v>4.00670528411865</v>
       </c>
       <c r="H728" t="n">
         <v>138495</v>
@@ -21510,7 +21510,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.21234703063965</v>
+        <v>4.21234655380249</v>
       </c>
       <c r="H729" t="n">
         <v>153600</v>
@@ -21539,7 +21539,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="n">
-        <v>4.07237768173218</v>
+        <v>4.07237720489502</v>
       </c>
       <c r="H730" t="n">
         <v>186832</v>
@@ -21568,7 +21568,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="n">
-        <v>4.12544679641724</v>
+        <v>4.12544727325439</v>
       </c>
       <c r="H731" t="n">
         <v>143878</v>
@@ -21713,7 +21713,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>3.98945760726929</v>
+        <v>3.98945808410645</v>
       </c>
       <c r="H736" t="n">
         <v>29837</v>
@@ -21742,7 +21742,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766521453857</v>
+        <v>3.94766616821289</v>
       </c>
       <c r="H737" t="n">
         <v>105830</v>
@@ -21771,7 +21771,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="n">
-        <v>3.89061641693115</v>
+        <v>3.89061617851257</v>
       </c>
       <c r="H738" t="n">
         <v>78191</v>
@@ -21800,7 +21800,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260697364807</v>
+        <v>3.89260649681091</v>
       </c>
       <c r="H739" t="n">
         <v>160586</v>
@@ -21887,7 +21887,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503175735474</v>
+        <v>4.07503128051758</v>
       </c>
       <c r="H742" t="n">
         <v>132743</v>
@@ -21945,7 +21945,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05114984512329</v>
+        <v>4.05115032196045</v>
       </c>
       <c r="H744" t="n">
         <v>56164</v>
@@ -21974,7 +21974,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="n">
-        <v>4.04119920730591</v>
+        <v>4.04119968414307</v>
       </c>
       <c r="H745" t="n">
         <v>62982</v>
@@ -22003,7 +22003,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.96889328956604</v>
+        <v>3.96889305114746</v>
       </c>
       <c r="H746" t="n">
         <v>145833</v>
@@ -22032,7 +22032,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189337730408</v>
+        <v>3.90189361572266</v>
       </c>
       <c r="H747" t="n">
         <v>215638</v>
@@ -22061,7 +22061,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.90720057487488</v>
+        <v>3.90720009803772</v>
       </c>
       <c r="H748" t="n">
         <v>102007</v>
@@ -22090,7 +22090,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88730025291443</v>
+        <v>3.88729977607727</v>
       </c>
       <c r="H749" t="n">
         <v>111448</v>
@@ -22119,7 +22119,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.85214138031006</v>
+        <v>3.85214185714722</v>
       </c>
       <c r="H750" t="n">
         <v>141352</v>
@@ -22148,7 +22148,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.8581120967865</v>
+        <v>3.85811185836792</v>
       </c>
       <c r="H751" t="n">
         <v>63514</v>
@@ -22177,7 +22177,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361698150635</v>
+        <v>3.82361674308777</v>
       </c>
       <c r="H752" t="n">
         <v>90932</v>
@@ -22206,7 +22206,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="n">
-        <v>3.7499840259552</v>
+        <v>3.74998426437378</v>
       </c>
       <c r="H753" t="n">
         <v>184870</v>
@@ -22235,7 +22235,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219074249268</v>
+        <v>3.84219098091125</v>
       </c>
       <c r="H754" t="n">
         <v>195412</v>
@@ -22293,7 +22293,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.73738050460815</v>
+        <v>3.73737978935242</v>
       </c>
       <c r="H756" t="n">
         <v>138294</v>
@@ -22351,7 +22351,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>3.57949995994568</v>
+        <v>3.5794997215271</v>
       </c>
       <c r="H758" t="n">
         <v>159867</v>
@@ -22380,7 +22380,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490612030029</v>
+        <v>3.56490588188171</v>
       </c>
       <c r="H759" t="n">
         <v>317061</v>
@@ -22409,7 +22409,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205388069153</v>
+        <v>3.60205411911011</v>
       </c>
       <c r="H760" t="n">
         <v>153511</v>
@@ -22438,7 +22438,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59741044044495</v>
+        <v>3.59741067886353</v>
       </c>
       <c r="H761" t="n">
         <v>232177</v>
@@ -22612,7 +22612,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="n">
-        <v>3.83821105957031</v>
+        <v>3.83821082115173</v>
       </c>
       <c r="H767" t="n">
         <v>70343</v>
@@ -22670,7 +22670,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="n">
-        <v>3.90587329864502</v>
+        <v>3.90587377548218</v>
       </c>
       <c r="H769" t="n">
         <v>117696</v>
@@ -22699,7 +22699,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444753646851</v>
+        <v>3.92444801330566</v>
       </c>
       <c r="H770" t="n">
         <v>82861</v>
@@ -22728,7 +22728,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>3.90056753158569</v>
+        <v>3.90056705474854</v>
       </c>
       <c r="H771" t="n">
         <v>149636</v>
@@ -22757,7 +22757,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="n">
-        <v>3.85479426383972</v>
+        <v>3.8547945022583</v>
       </c>
       <c r="H772" t="n">
         <v>112700</v>
@@ -22815,7 +22815,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.89857721328735</v>
+        <v>3.89857769012451</v>
       </c>
       <c r="H774" t="n">
         <v>192350</v>
@@ -22844,7 +22844,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="n">
-        <v>3.88000249862671</v>
+        <v>3.88000297546387</v>
       </c>
       <c r="H775" t="n">
         <v>157597</v>
@@ -22873,7 +22873,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="n">
-        <v>3.9151611328125</v>
+        <v>3.91516137123108</v>
       </c>
       <c r="H776" t="n">
         <v>169016</v>
@@ -22989,7 +22989,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="n">
-        <v>3.97287344932556</v>
+        <v>3.97287368774414</v>
       </c>
       <c r="H780" t="n">
         <v>142710</v>
@@ -23018,7 +23018,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="n">
-        <v>4.0790114402771</v>
+        <v>4.07901191711426</v>
       </c>
       <c r="H781" t="n">
         <v>71053</v>
@@ -23047,7 +23047,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657543182373</v>
+        <v>4.16657495498657</v>
       </c>
       <c r="H782" t="n">
         <v>250025</v>
@@ -23076,7 +23076,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="n">
-        <v>4.1380500793457</v>
+        <v>4.13805055618286</v>
       </c>
       <c r="H783" t="n">
         <v>122859</v>
@@ -23105,7 +23105,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937711715698</v>
+        <v>4.13937664031982</v>
       </c>
       <c r="H784" t="n">
         <v>119629</v>
@@ -23134,7 +23134,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090303421021</v>
+        <v>4.10090255737305</v>
       </c>
       <c r="H785" t="n">
         <v>161482</v>
@@ -23192,7 +23192,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947679519653</v>
+        <v>4.11947584152222</v>
       </c>
       <c r="H787" t="n">
         <v>103841</v>
@@ -23221,7 +23221,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.11284255981445</v>
+        <v>4.11284303665161</v>
       </c>
       <c r="H788" t="n">
         <v>160837</v>
@@ -23250,7 +23250,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>4.092942237854</v>
+        <v>4.09294176101685</v>
       </c>
       <c r="H789" t="n">
         <v>263354</v>
@@ -23279,7 +23279,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078416824341</v>
+        <v>3.99078369140625</v>
       </c>
       <c r="H790" t="n">
         <v>256263</v>
@@ -23337,7 +23337,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="n">
-        <v>3.98017024993896</v>
+        <v>3.98017048835754</v>
       </c>
       <c r="H792" t="n">
         <v>238621</v>
@@ -23366,7 +23366,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567561149597</v>
+        <v>3.94567632675171</v>
       </c>
       <c r="H793" t="n">
         <v>513739</v>
@@ -23395,7 +23395,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680400848389</v>
+        <v>3.98680424690247</v>
       </c>
       <c r="H794" t="n">
         <v>129600</v>
@@ -23424,7 +23424,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="n">
-        <v>4.02461576461792</v>
+        <v>4.02461528778076</v>
       </c>
       <c r="H795" t="n">
         <v>148746</v>
@@ -23453,7 +23453,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="n">
-        <v>4.08896207809448</v>
+        <v>4.08896160125732</v>
       </c>
       <c r="H796" t="n">
         <v>427477</v>
@@ -23482,7 +23482,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="n">
-        <v>4.0730414390564</v>
+        <v>4.07304048538208</v>
       </c>
       <c r="H797" t="n">
         <v>221439</v>
@@ -23511,7 +23511,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="n">
-        <v>4.070387840271</v>
+        <v>4.07038736343384</v>
       </c>
       <c r="H798" t="n">
         <v>126559</v>
@@ -23569,7 +23569,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>4.01665496826172</v>
+        <v>4.01665544509888</v>
       </c>
       <c r="H800" t="n">
         <v>103894</v>
@@ -23598,7 +23598,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>4.07105112075806</v>
+        <v>4.0710506439209</v>
       </c>
       <c r="H801" t="n">
         <v>96510</v>
@@ -23627,7 +23627,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13407039642334</v>
+        <v>4.13406991958618</v>
       </c>
       <c r="H802" t="n">
         <v>101135</v>
@@ -23714,7 +23714,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473320007324</v>
       </c>
       <c r="H805" t="n">
         <v>290799</v>
@@ -23801,7 +23801,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="n">
-        <v>4.34501934051514</v>
+        <v>4.34501886367798</v>
       </c>
       <c r="H808" t="n">
         <v>286285</v>
@@ -23859,7 +23859,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848573684692</v>
       </c>
       <c r="H810" t="n">
         <v>124688</v>
@@ -23917,7 +23917,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531694412231</v>
+        <v>4.28531742095947</v>
       </c>
       <c r="H812" t="n">
         <v>82775</v>
@@ -24062,7 +24062,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759244918823</v>
+        <v>4.49759292602539</v>
       </c>
       <c r="H817" t="n">
         <v>195962</v>
@@ -24091,7 +24091,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H818" t="n">
         <v>210704</v>
@@ -24207,7 +24207,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="n">
-        <v>4.30057382583618</v>
+        <v>4.30057430267334</v>
       </c>
       <c r="H822" t="n">
         <v>93154</v>
@@ -24265,7 +24265,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="n">
-        <v>4.31848526000977</v>
+        <v>4.31848573684692</v>
       </c>
       <c r="H824" t="n">
         <v>64218</v>
@@ -24294,7 +24294,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>4.30521774291992</v>
+        <v>4.30521726608276</v>
       </c>
       <c r="H825" t="n">
         <v>258387</v>
@@ -24323,7 +24323,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27205038070679</v>
+        <v>4.27204990386963</v>
       </c>
       <c r="H826" t="n">
         <v>152125</v>
@@ -24381,7 +24381,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>4.36492013931274</v>
+        <v>4.3649206161499</v>
       </c>
       <c r="H828" t="n">
         <v>60554</v>
@@ -24410,7 +24410,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>4.39145469665527</v>
+        <v>4.39145421981812</v>
       </c>
       <c r="H829" t="n">
         <v>115908</v>
@@ -24439,7 +24439,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="n">
-        <v>4.39808797836304</v>
+        <v>4.3980884552002</v>
       </c>
       <c r="H830" t="n">
         <v>151188</v>
@@ -24497,7 +24497,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>4.42462348937988</v>
+        <v>4.42462301254272</v>
       </c>
       <c r="H832" t="n">
         <v>126367</v>
@@ -24526,7 +24526,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.29858446121216</v>
+        <v>4.29858350753784</v>
       </c>
       <c r="H833" t="n">
         <v>159721</v>
@@ -24555,7 +24555,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511854171753</v>
+        <v>4.32511806488037</v>
       </c>
       <c r="H834" t="n">
         <v>246478</v>
@@ -24700,7 +24700,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>4.4511570930481</v>
+        <v>4.45115756988525</v>
       </c>
       <c r="H839" t="n">
         <v>130935</v>
@@ -24729,7 +24729,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>4.4511570930481</v>
+        <v>4.45115756988525</v>
       </c>
       <c r="H840" t="n">
         <v>103647</v>
@@ -24787,7 +24787,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>4.46442461013794</v>
+        <v>4.46442413330078</v>
       </c>
       <c r="H842" t="n">
         <v>113823</v>
@@ -24816,7 +24816,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H843" t="n">
         <v>139329</v>
@@ -24845,7 +24845,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>4.41135549545288</v>
+        <v>4.41135597229004</v>
       </c>
       <c r="H844" t="n">
         <v>71545</v>
@@ -24990,7 +24990,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.44452381134033</v>
+        <v>4.44452333450317</v>
       </c>
       <c r="H849" t="n">
         <v>132031</v>
@@ -25019,7 +25019,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="n">
-        <v>4.55066156387329</v>
+        <v>4.55066204071045</v>
       </c>
       <c r="H850" t="n">
         <v>559275</v>
@@ -25048,7 +25048,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49095916748047</v>
+        <v>4.49095869064331</v>
       </c>
       <c r="H851" t="n">
         <v>276372</v>
@@ -25164,7 +25164,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H855" t="n">
         <v>231782</v>
@@ -25222,7 +25222,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>4.44223260879517</v>
+        <v>4.44223308563232</v>
       </c>
       <c r="H857" t="n">
         <v>126120</v>
@@ -25280,7 +25280,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52835035324097</v>
+        <v>4.52834987640381</v>
       </c>
       <c r="H859" t="n">
         <v>185427</v>
@@ -25309,7 +25309,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140827178955</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H860" t="n">
         <v>106622</v>
@@ -25338,7 +25338,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>4.549880027771</v>
+        <v>4.54987955093384</v>
       </c>
       <c r="H861" t="n">
         <v>64262</v>
@@ -25367,7 +25367,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H862" t="n">
         <v>89495</v>
@@ -25483,7 +25483,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H866" t="n">
         <v>83940</v>
@@ -25512,7 +25512,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H867" t="n">
         <v>45354</v>
@@ -25570,7 +25570,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H869" t="n">
         <v>55460</v>
@@ -25686,7 +25686,7 @@
         <v>6.25</v>
       </c>
       <c r="G873" t="n">
-        <v>4.48529100418091</v>
+        <v>4.48529148101807</v>
       </c>
       <c r="H873" t="n">
         <v>112876</v>
@@ -25715,7 +25715,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G874" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H874" t="n">
         <v>63208</v>
@@ -25773,7 +25773,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G876" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H876" t="n">
         <v>88374</v>
@@ -25831,7 +25831,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>4.29152679443359</v>
+        <v>4.29152727127075</v>
       </c>
       <c r="H878" t="n">
         <v>131085</v>
@@ -26121,7 +26121,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G888" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H888" t="n">
         <v>214075</v>
@@ -26237,7 +26237,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505668640137</v>
       </c>
       <c r="H892" t="n">
         <v>101125</v>
@@ -26295,7 +26295,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G894" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H894" t="n">
         <v>80568</v>
@@ -26382,7 +26382,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G897" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H897" t="n">
         <v>139790</v>
@@ -26440,7 +26440,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>4.34893846511841</v>
+        <v>4.34893894195557</v>
       </c>
       <c r="H899" t="n">
         <v>149764</v>
@@ -26469,7 +26469,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H900" t="n">
         <v>82729</v>
@@ -26556,7 +26556,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H903" t="n">
         <v>213241</v>
@@ -26614,7 +26614,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H905" t="n">
         <v>82085</v>
@@ -26730,7 +26730,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G909" t="n">
-        <v>4.24129104614258</v>
+        <v>4.24129152297974</v>
       </c>
       <c r="H909" t="n">
         <v>98629</v>
@@ -26817,7 +26817,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H912" t="n">
         <v>162300</v>
@@ -26904,7 +26904,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G915" t="n">
-        <v>4.04752683639526</v>
+        <v>4.04752635955811</v>
       </c>
       <c r="H915" t="n">
         <v>117109</v>
@@ -26933,7 +26933,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H916" t="n">
         <v>220296</v>
@@ -26962,7 +26962,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H917" t="n">
         <v>142499</v>
@@ -26991,7 +26991,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H918" t="n">
         <v>243157</v>
@@ -27020,7 +27020,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.88246846199036</v>
+        <v>3.88246774673462</v>
       </c>
       <c r="H919" t="n">
         <v>159908</v>
@@ -27049,7 +27049,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>3.79635071754456</v>
+        <v>3.79635095596313</v>
       </c>
       <c r="H920" t="n">
         <v>329655</v>
@@ -27078,7 +27078,7 @@
         <v>5.25</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76764512062073</v>
+        <v>3.76764488220215</v>
       </c>
       <c r="H921" t="n">
         <v>137747</v>
@@ -27107,7 +27107,7 @@
         <v>5.25</v>
       </c>
       <c r="G922" t="n">
-        <v>3.76764512062073</v>
+        <v>3.76764488220215</v>
       </c>
       <c r="H922" t="n">
         <v>222826</v>
@@ -27252,7 +27252,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G927" t="n">
-        <v>3.79635071754456</v>
+        <v>3.79635095596313</v>
       </c>
       <c r="H927" t="n">
         <v>109743</v>
@@ -27281,7 +27281,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199768066406</v>
+        <v>3.78199791908264</v>
       </c>
       <c r="H928" t="n">
         <v>42652</v>
@@ -27310,7 +27310,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G929" t="n">
-        <v>3.80352735519409</v>
+        <v>3.80352687835693</v>
       </c>
       <c r="H929" t="n">
         <v>184164</v>
@@ -27368,7 +27368,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940935134888</v>
+        <v>3.83940958976746</v>
       </c>
       <c r="H931" t="n">
         <v>200773</v>
@@ -27426,7 +27426,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H933" t="n">
         <v>162454</v>
@@ -27484,7 +27484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H935" t="n">
         <v>187953</v>
@@ -27513,7 +27513,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G936" t="n">
-        <v>3.92552661895752</v>
+        <v>3.92552709579468</v>
       </c>
       <c r="H936" t="n">
         <v>164174</v>
@@ -27542,7 +27542,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G937" t="n">
-        <v>3.95423340797424</v>
+        <v>3.95423316955566</v>
       </c>
       <c r="H937" t="n">
         <v>203686</v>
@@ -27571,7 +27571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G938" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H938" t="n">
         <v>122493</v>
@@ -27629,7 +27629,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H940" t="n">
         <v>133834</v>
@@ -27687,7 +27687,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G942" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H942" t="n">
         <v>254675</v>
@@ -27716,7 +27716,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H943" t="n">
         <v>182425</v>
@@ -27774,7 +27774,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G945" t="n">
-        <v>3.99729204177856</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H945" t="n">
         <v>164084</v>
@@ -27832,7 +27832,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H947" t="n">
         <v>147938</v>
@@ -27861,7 +27861,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293852806091</v>
+        <v>3.98293876647949</v>
       </c>
       <c r="H948" t="n">
         <v>118564</v>
@@ -27890,7 +27890,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H949" t="n">
         <v>84704</v>
@@ -27948,7 +27948,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G951" t="n">
-        <v>3.95423340797424</v>
+        <v>3.95423316955566</v>
       </c>
       <c r="H951" t="n">
         <v>122102</v>
@@ -27977,7 +27977,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H952" t="n">
         <v>71762</v>
@@ -28006,7 +28006,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H953" t="n">
         <v>89858</v>
@@ -28064,7 +28064,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682054519653</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H955" t="n">
         <v>198731</v>
@@ -28093,7 +28093,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G956" t="n">
-        <v>3.92552661895752</v>
+        <v>3.92552709579468</v>
       </c>
       <c r="H956" t="n">
         <v>117055</v>
@@ -28151,7 +28151,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G958" t="n">
-        <v>4.01882123947144</v>
+        <v>4.01882076263428</v>
       </c>
       <c r="H958" t="n">
         <v>65548</v>
@@ -28180,7 +28180,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G959" t="n">
-        <v>3.99729204177856</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H959" t="n">
         <v>102747</v>
@@ -28209,7 +28209,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011540412903</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H960" t="n">
         <v>112689</v>
@@ -28238,7 +28238,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317451477051</v>
+        <v>4.03317403793335</v>
       </c>
       <c r="H961" t="n">
         <v>76598</v>
@@ -28267,7 +28267,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>4.08340883255005</v>
+        <v>4.08340978622437</v>
       </c>
       <c r="H962" t="n">
         <v>105538</v>
@@ -28296,7 +28296,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G963" t="n">
-        <v>4.09058570861816</v>
+        <v>4.09058618545532</v>
       </c>
       <c r="H963" t="n">
         <v>142594</v>
@@ -28383,7 +28383,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G966" t="n">
-        <v>4.15517377853394</v>
+        <v>4.15517425537109</v>
       </c>
       <c r="H966" t="n">
         <v>139348</v>
@@ -28412,7 +28412,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>4.14082098007202</v>
+        <v>4.14082145690918</v>
       </c>
       <c r="H967" t="n">
         <v>119981</v>
@@ -28441,7 +28441,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211538314819</v>
+        <v>4.11211490631104</v>
       </c>
       <c r="H968" t="n">
         <v>76571</v>
@@ -28470,7 +28470,7 @@
         <v>5.75</v>
       </c>
       <c r="G969" t="n">
-        <v>4.12646770477295</v>
+        <v>4.12646865844727</v>
       </c>
       <c r="H969" t="n">
         <v>66738</v>
@@ -28615,7 +28615,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G974" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H974" t="n">
         <v>38961</v>
@@ -28644,7 +28644,7 @@
         <v>5.75</v>
       </c>
       <c r="G975" t="n">
-        <v>4.12646770477295</v>
+        <v>4.12646865844727</v>
       </c>
       <c r="H975" t="n">
         <v>83904</v>
@@ -28673,7 +28673,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G976" t="n">
-        <v>4.13364458084106</v>
+        <v>4.13364505767822</v>
       </c>
       <c r="H976" t="n">
         <v>91697</v>
@@ -28702,7 +28702,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G977" t="n">
-        <v>4.16235065460205</v>
+        <v>4.16235017776489</v>
       </c>
       <c r="H977" t="n">
         <v>27675</v>
@@ -28818,7 +28818,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H981" t="n">
         <v>169971</v>
@@ -28876,7 +28876,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H983" t="n">
         <v>94635</v>
@@ -28934,7 +28934,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28435039520264</v>
+        <v>4.28434991836548</v>
       </c>
       <c r="H985" t="n">
         <v>162590</v>
@@ -28992,7 +28992,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H987" t="n">
         <v>69784</v>
@@ -29021,7 +29021,7 @@
         <v>6</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H988" t="n">
         <v>135917</v>
@@ -29050,7 +29050,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611581802368</v>
       </c>
       <c r="H989" t="n">
         <v>138068</v>
@@ -29108,7 +29108,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G991" t="n">
-        <v>4.31305599212646</v>
+        <v>4.31305646896362</v>
       </c>
       <c r="H991" t="n">
         <v>83600</v>
@@ -29224,7 +29224,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H995" t="n">
         <v>358111</v>
@@ -29253,7 +29253,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G996" t="n">
-        <v>4.57858562469482</v>
+        <v>4.57858610153198</v>
       </c>
       <c r="H996" t="n">
         <v>495439</v>
@@ -29311,7 +29311,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552722930908</v>
+        <v>4.53552675247192</v>
       </c>
       <c r="H998" t="n">
         <v>278924</v>
@@ -29427,7 +29427,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1002" t="n">
         <v>62344</v>
@@ -29456,7 +29456,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1003" t="n">
         <v>114564</v>
@@ -29514,7 +29514,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1005" t="n">
         <v>77356</v>
@@ -29543,7 +29543,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505668640137</v>
       </c>
       <c r="H1006" t="n">
         <v>100264</v>
@@ -29601,7 +29601,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1008" t="n">
         <v>90036</v>
@@ -29659,7 +29659,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.40635013580322</v>
+        <v>4.40635061264038</v>
       </c>
       <c r="H1010" t="n">
         <v>69927</v>
@@ -29804,7 +29804,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1015" t="n">
         <v>125144</v>
@@ -29833,7 +29833,7 @@
         <v>6.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.48529100418091</v>
+        <v>4.48529148101807</v>
       </c>
       <c r="H1016" t="n">
         <v>85906</v>
@@ -29978,7 +29978,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505668640137</v>
       </c>
       <c r="H1021" t="n">
         <v>186708</v>
@@ -30007,7 +30007,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1022" t="n">
         <v>89368</v>
@@ -30094,7 +30094,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.42070293426514</v>
+        <v>4.42070341110229</v>
       </c>
       <c r="H1025" t="n">
         <v>56890</v>
@@ -30152,7 +30152,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1027" t="n">
         <v>46343</v>
@@ -30210,7 +30210,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1029" t="n">
         <v>103178</v>
@@ -30268,7 +30268,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44940948486328</v>
+        <v>4.44940900802612</v>
       </c>
       <c r="H1031" t="n">
         <v>101854</v>
@@ -30355,7 +30355,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.47093820571899</v>
+        <v>4.47093868255615</v>
       </c>
       <c r="H1034" t="n">
         <v>100848</v>
@@ -30442,7 +30442,7 @@
         <v>6</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H1037" t="n">
         <v>183171</v>
@@ -30558,7 +30558,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.58576154708862</v>
+        <v>4.58576250076294</v>
       </c>
       <c r="H1041" t="n">
         <v>516270</v>
@@ -30587,7 +30587,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1042" t="n">
         <v>180031</v>
@@ -30616,7 +30616,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1043" t="n">
         <v>133272</v>
@@ -30703,7 +30703,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1046" t="n">
         <v>128636</v>
@@ -30732,7 +30732,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964380264282</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1047" t="n">
         <v>186654</v>
@@ -30790,7 +30790,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.55705595016479</v>
+        <v>4.55705642700195</v>
       </c>
       <c r="H1049" t="n">
         <v>136339</v>
@@ -30819,7 +30819,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140827178955</v>
+        <v>4.57140922546387</v>
       </c>
       <c r="H1050" t="n">
         <v>112242</v>
@@ -30877,7 +30877,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.47811508178711</v>
+        <v>4.47811460494995</v>
       </c>
       <c r="H1052" t="n">
         <v>122474</v>
@@ -30993,7 +30993,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.99729204177856</v>
+        <v>3.99729180335999</v>
       </c>
       <c r="H1056" t="n">
         <v>475594</v>
@@ -31022,7 +31022,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399765968323</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H1057" t="n">
         <v>651281</v>
@@ -31051,7 +31051,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682054519653</v>
+        <v>3.89682102203369</v>
       </c>
       <c r="H1058" t="n">
         <v>494611</v>
@@ -31080,7 +31080,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.93987965583801</v>
+        <v>3.93987989425659</v>
       </c>
       <c r="H1059" t="n">
         <v>441063</v>
@@ -31138,7 +31138,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505631446838</v>
+        <v>3.82505655288696</v>
       </c>
       <c r="H1061" t="n">
         <v>188804</v>
@@ -31167,7 +31167,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.7891743183136</v>
+        <v>3.78917479515076</v>
       </c>
       <c r="H1062" t="n">
         <v>297718</v>
@@ -31196,7 +31196,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.35858607292175</v>
+        <v>3.35858631134033</v>
       </c>
       <c r="H1063" t="n">
         <v>656502</v>
@@ -31312,7 +31312,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605710983276</v>
+        <v>2.66605734825134</v>
       </c>
       <c r="H1067" t="n">
         <v>497765</v>
@@ -31341,7 +31341,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.45076298713684</v>
+        <v>2.45076322555542</v>
       </c>
       <c r="H1068" t="n">
         <v>502127</v>
@@ -31370,7 +31370,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1069" t="n">
         <v>316624</v>
@@ -31399,7 +31399,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1070" t="n">
         <v>294654</v>
@@ -31457,7 +31457,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682218551636</v>
+        <v>2.67682194709778</v>
       </c>
       <c r="H1072" t="n">
         <v>1041965</v>
@@ -31515,7 +31515,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446888923645</v>
+        <v>2.78446912765503</v>
       </c>
       <c r="H1074" t="n">
         <v>219271</v>
@@ -31544,7 +31544,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.70911598205566</v>
+        <v>2.70911622047424</v>
       </c>
       <c r="H1075" t="n">
         <v>353763</v>
@@ -31573,7 +31573,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423385620117</v>
+        <v>2.73423337936401</v>
       </c>
       <c r="H1076" t="n">
         <v>156770</v>
@@ -31718,7 +31718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.65529251098633</v>
+        <v>2.65529274940491</v>
       </c>
       <c r="H1081" t="n">
         <v>184630</v>
@@ -31747,7 +31747,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505747795105</v>
+        <v>2.60505723953247</v>
       </c>
       <c r="H1082" t="n">
         <v>90176</v>
@@ -31776,7 +31776,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1083" t="n">
         <v>180927</v>
@@ -31950,7 +31950,7 @@
         <v>3.5</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1089" t="n">
         <v>196323</v>
@@ -31979,7 +31979,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1090" t="n">
         <v>129379</v>
@@ -32008,7 +32008,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.59788084030151</v>
+        <v>2.59788060188293</v>
       </c>
       <c r="H1091" t="n">
         <v>79056</v>
@@ -32037,7 +32037,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.53688073158264</v>
+        <v>2.53688097000122</v>
       </c>
       <c r="H1092" t="n">
         <v>202956</v>
@@ -32066,7 +32066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329229354858</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1093" t="n">
         <v>139451</v>
@@ -32124,7 +32124,7 @@
         <v>3.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1095" t="n">
         <v>71153</v>
@@ -32153,7 +32153,7 @@
         <v>3.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1096" t="n">
         <v>133075</v>
@@ -32182,7 +32182,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1097" t="n">
         <v>180573</v>
@@ -32240,7 +32240,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.59788084030151</v>
+        <v>2.59788060188293</v>
       </c>
       <c r="H1099" t="n">
         <v>170890</v>
@@ -32298,7 +32298,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1101" t="n">
         <v>130098</v>
@@ -32356,7 +32356,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1103" t="n">
         <v>141432</v>
@@ -32385,7 +32385,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.5009982585907</v>
+        <v>2.50099849700928</v>
       </c>
       <c r="H1104" t="n">
         <v>172964</v>
@@ -32414,7 +32414,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1105" t="n">
         <v>149130</v>
@@ -32472,7 +32472,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952808380127</v>
+        <v>2.33952784538269</v>
       </c>
       <c r="H1107" t="n">
         <v>248569</v>
@@ -32559,7 +32559,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1110" t="n">
         <v>311033</v>
@@ -32646,7 +32646,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.15652799606323</v>
+        <v>2.15652823448181</v>
       </c>
       <c r="H1113" t="n">
         <v>565839</v>
@@ -32675,7 +32675,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805743217468</v>
+        <v>2.17805790901184</v>
       </c>
       <c r="H1114" t="n">
         <v>231502</v>
@@ -32733,7 +32733,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105728149414</v>
+        <v>2.36105751991272</v>
       </c>
       <c r="H1116" t="n">
         <v>277343</v>
@@ -32820,7 +32820,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876300811768</v>
+        <v>2.32876348495483</v>
       </c>
       <c r="H1119" t="n">
         <v>437387</v>
@@ -32849,7 +32849,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.35388112068176</v>
+        <v>2.35388088226318</v>
       </c>
       <c r="H1120" t="n">
         <v>213833</v>
@@ -32907,7 +32907,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1122" t="n">
         <v>477229</v>
@@ -32936,7 +32936,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.52611613273621</v>
+        <v>2.52611637115479</v>
       </c>
       <c r="H1123" t="n">
         <v>403468</v>
@@ -32965,7 +32965,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.68041014671326</v>
+        <v>2.68041038513184</v>
       </c>
       <c r="H1124" t="n">
         <v>901153</v>
@@ -33052,7 +33052,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864543914795</v>
+        <v>2.60864567756653</v>
       </c>
       <c r="H1127" t="n">
         <v>417942</v>
@@ -33081,7 +33081,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1128" t="n">
         <v>348708</v>
@@ -33139,7 +33139,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1130" t="n">
         <v>287875</v>
@@ -33168,7 +33168,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1131" t="n">
         <v>310297</v>
@@ -33197,7 +33197,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1132" t="n">
         <v>158723</v>
@@ -33255,7 +33255,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.45435166358948</v>
+        <v>2.4543514251709</v>
       </c>
       <c r="H1134" t="n">
         <v>433647</v>
@@ -33284,7 +33284,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511602401733</v>
+        <v>2.46511626243591</v>
       </c>
       <c r="H1135" t="n">
         <v>163840</v>
@@ -33342,7 +33342,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.411292552948</v>
+        <v>2.41129279136658</v>
       </c>
       <c r="H1137" t="n">
         <v>197688</v>
@@ -33400,7 +33400,7 @@
         <v>3.375</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.42205715179443</v>
+        <v>2.42205739021301</v>
       </c>
       <c r="H1139" t="n">
         <v>98220</v>
@@ -33429,7 +33429,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.49382162094116</v>
+        <v>2.49382209777832</v>
       </c>
       <c r="H1140" t="n">
         <v>92813</v>
@@ -33458,7 +33458,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1141" t="n">
         <v>205219</v>
@@ -33487,7 +33487,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.49023389816284</v>
+        <v>2.49023365974426</v>
       </c>
       <c r="H1142" t="n">
         <v>106314</v>
@@ -33574,7 +33574,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1145" t="n">
         <v>166481</v>
@@ -33603,7 +33603,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.52611613273621</v>
+        <v>2.52611637115479</v>
       </c>
       <c r="H1146" t="n">
         <v>122805</v>
@@ -33632,7 +33632,7 @@
         <v>3.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.51176333427429</v>
+        <v>2.51176309585571</v>
       </c>
       <c r="H1147" t="n">
         <v>88292</v>
@@ -33719,7 +33719,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.5009982585907</v>
+        <v>2.50099849700928</v>
       </c>
       <c r="H1150" t="n">
         <v>183218</v>
@@ -33748,7 +33748,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329229354858</v>
+        <v>2.53329277038574</v>
       </c>
       <c r="H1151" t="n">
         <v>202010</v>
@@ -33806,7 +33806,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.51893973350525</v>
+        <v>2.51893949508667</v>
       </c>
       <c r="H1153" t="n">
         <v>399041</v>
@@ -33835,7 +33835,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.56917500495911</v>
+        <v>2.56917476654053</v>
       </c>
       <c r="H1154" t="n">
         <v>549822</v>
@@ -33951,7 +33951,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344397544861</v>
+        <v>2.48344421386719</v>
       </c>
       <c r="H1158" t="n">
         <v>166881</v>
@@ -34328,7 +34328,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.5064389705658</v>
+        <v>2.50643873214722</v>
       </c>
       <c r="H1171" t="n">
         <v>229796</v>
@@ -34415,7 +34415,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.40679454803467</v>
+        <v>2.40679478645325</v>
       </c>
       <c r="H1174" t="n">
         <v>149038</v>
@@ -34444,7 +34444,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1175" t="n">
         <v>77116</v>
@@ -34473,7 +34473,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230253219604</v>
       </c>
       <c r="H1176" t="n">
         <v>101920</v>
@@ -34502,7 +34502,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481528282166</v>
+        <v>2.31481504440308</v>
       </c>
       <c r="H1177" t="n">
         <v>289006</v>
@@ -34531,7 +34531,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1178" t="n">
         <v>133721</v>
@@ -34676,7 +34676,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.32631254196167</v>
+        <v>2.32631278038025</v>
       </c>
       <c r="H1183" t="n">
         <v>40688</v>
@@ -34821,7 +34821,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.42595672607422</v>
+        <v>2.4259569644928</v>
       </c>
       <c r="H1188" t="n">
         <v>131356</v>
@@ -34850,7 +34850,7 @@
         <v>3.125</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.39529705047607</v>
+        <v>2.39529728889465</v>
       </c>
       <c r="H1189" t="n">
         <v>62755</v>
@@ -35053,7 +35053,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.3914647102356</v>
+        <v>2.39146447181702</v>
       </c>
       <c r="H1196" t="n">
         <v>154795</v>
@@ -35169,7 +35169,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.30715012550354</v>
+        <v>2.30715036392212</v>
       </c>
       <c r="H1200" t="n">
         <v>254056</v>
@@ -35372,7 +35372,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27265787124634</v>
+        <v>2.27265810966492</v>
       </c>
       <c r="H1207" t="n">
         <v>253908</v>
@@ -35401,7 +35401,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.36080479621887</v>
+        <v>2.36080503463745</v>
       </c>
       <c r="H1208" t="n">
         <v>142931</v>
@@ -35633,7 +35633,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.37230229377747</v>
+        <v>2.37230253219604</v>
       </c>
       <c r="H1216" t="n">
         <v>160104</v>
@@ -35691,7 +35691,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283601760864</v>
+        <v>2.22283554077148</v>
       </c>
       <c r="H1218" t="n">
         <v>339921</v>
@@ -35720,7 +35720,7 @@
         <v>2.875</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.20367312431335</v>
+        <v>2.20367360115051</v>
       </c>
       <c r="H1219" t="n">
         <v>195479</v>
@@ -35778,7 +35778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750594139099</v>
+        <v>2.20750617980957</v>
       </c>
       <c r="H1221" t="n">
         <v>142174</v>
@@ -35836,7 +35836,7 @@
         <v>2.75</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.10786151885986</v>
+        <v>2.10786128044128</v>
       </c>
       <c r="H1223" t="n">
         <v>329808</v>
@@ -35952,7 +35952,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.89707517623901</v>
+        <v>1.8970752954483</v>
       </c>
       <c r="H1227" t="n">
         <v>334235</v>
@@ -36068,7 +36068,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.01971435546875</v>
+        <v>2.01971459388733</v>
       </c>
       <c r="H1231" t="n">
         <v>141307</v>
@@ -36155,7 +36155,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138964176178</v>
+        <v>1.98138999938965</v>
       </c>
       <c r="H1234" t="n">
         <v>203810</v>
@@ -36184,7 +36184,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.18067836761475</v>
+        <v>2.1806788444519</v>
       </c>
       <c r="H1235" t="n">
         <v>480028</v>
@@ -36213,7 +36213,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.49877405166626</v>
+        <v>2.49877381324768</v>
       </c>
       <c r="H1236" t="n">
         <v>1002989</v>
@@ -36242,7 +36242,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.63291049003601</v>
+        <v>2.63291072845459</v>
       </c>
       <c r="H1237" t="n">
         <v>805282</v>
@@ -36445,7 +36445,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.6444079875946</v>
+        <v>2.64440822601318</v>
       </c>
       <c r="H1244" t="n">
         <v>355424</v>
@@ -36532,7 +36532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405241012573</v>
+        <v>2.74405217170715</v>
       </c>
       <c r="H1247" t="n">
         <v>450366</v>
@@ -36677,7 +36677,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68656516075134</v>
+        <v>2.68656539916992</v>
       </c>
       <c r="H1252" t="n">
         <v>485014</v>
@@ -36735,7 +36735,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.77087950706482</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1254" t="n">
         <v>119317</v>
@@ -36764,7 +36764,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1255" t="n">
         <v>268956</v>
@@ -36851,7 +36851,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1258" t="n">
         <v>858635</v>
@@ -36967,7 +36967,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.81686925888062</v>
+        <v>2.81686949729919</v>
       </c>
       <c r="H1262" t="n">
         <v>421624</v>
@@ -37083,7 +37083,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1266" t="n">
         <v>404158</v>
@@ -37112,7 +37112,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369659423828</v>
       </c>
       <c r="H1267" t="n">
         <v>453222</v>
@@ -37141,7 +37141,7 @@
         <v>3.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.874356508255</v>
+        <v>2.87435674667358</v>
       </c>
       <c r="H1268" t="n">
         <v>163276</v>
@@ -37170,7 +37170,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.82836675643921</v>
+        <v>2.82836723327637</v>
       </c>
       <c r="H1269" t="n">
         <v>261734</v>
@@ -37286,7 +37286,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.82836675643921</v>
+        <v>2.82836723327637</v>
       </c>
       <c r="H1273" t="n">
         <v>137710</v>
@@ -37431,7 +37431,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1278" t="n">
         <v>80215</v>
@@ -37460,7 +37460,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369659423828</v>
       </c>
       <c r="H1279" t="n">
         <v>604084</v>
@@ -37489,7 +37489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369659423828</v>
       </c>
       <c r="H1280" t="n">
         <v>254659</v>
@@ -37547,7 +37547,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.89351892471313</v>
+        <v>2.89351916313171</v>
       </c>
       <c r="H1282" t="n">
         <v>460798</v>
@@ -37576,7 +37576,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285901069641</v>
+        <v>2.86285924911499</v>
       </c>
       <c r="H1283" t="n">
         <v>574210</v>
@@ -37605,7 +37605,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620958328247</v>
+        <v>2.78620982170105</v>
       </c>
       <c r="H1284" t="n">
         <v>230927</v>
@@ -37634,7 +37634,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1285" t="n">
         <v>165121</v>
@@ -37692,7 +37692,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1287" t="n">
         <v>186106</v>
@@ -37808,7 +37808,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1291" t="n">
         <v>279807</v>
@@ -37837,7 +37837,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.77087950706482</v>
+        <v>2.7708797454834</v>
       </c>
       <c r="H1292" t="n">
         <v>127030</v>
@@ -37866,7 +37866,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.8053719997406</v>
+        <v>2.80537176132202</v>
       </c>
       <c r="H1293" t="n">
         <v>280713</v>
@@ -37953,7 +37953,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651368141174</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1296" t="n">
         <v>425681</v>
@@ -38098,7 +38098,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.00849294662476</v>
+        <v>3.00849342346191</v>
       </c>
       <c r="H1301" t="n">
         <v>169875</v>
@@ -38127,7 +38127,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567633628845</v>
+        <v>2.93567609786987</v>
       </c>
       <c r="H1302" t="n">
         <v>184353</v>
@@ -38185,7 +38185,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1304" t="n">
         <v>631921</v>
@@ -38214,7 +38214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369707107544</v>
+        <v>2.84369659423828</v>
       </c>
       <c r="H1305" t="n">
         <v>141746</v>
@@ -38330,7 +38330,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1309" t="n">
         <v>851470</v>
@@ -38359,7 +38359,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.66357016563416</v>
+        <v>2.66357040405273</v>
       </c>
       <c r="H1310" t="n">
         <v>561214</v>
@@ -38388,7 +38388,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1311" t="n">
         <v>333105</v>
@@ -38446,7 +38446,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1313" t="n">
         <v>282164</v>
@@ -38475,7 +38475,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1314" t="n">
-        <v>2.75171732902527</v>
+        <v>2.75171756744385</v>
       </c>
       <c r="H1314" t="n">
         <v>329760</v>
@@ -38562,7 +38562,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1317" t="n">
         <v>259106</v>
@@ -38591,7 +38591,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1318" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1318" t="n">
         <v>510876</v>
@@ -38620,7 +38620,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1319" t="n">
         <v>410062</v>
@@ -38678,7 +38678,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1321" t="n">
         <v>275194</v>
@@ -38736,7 +38736,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1323" t="n">
         <v>221706</v>
@@ -38765,7 +38765,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.67123508453369</v>
+        <v>2.67123556137085</v>
       </c>
       <c r="H1324" t="n">
         <v>215143</v>
@@ -38881,7 +38881,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1328" t="n">
         <v>523941</v>
@@ -38997,7 +38997,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.6559054851532</v>
+        <v>2.65590524673462</v>
       </c>
       <c r="H1332" t="n">
         <v>124651</v>
@@ -39055,7 +39055,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1334" t="n">
         <v>268795</v>
@@ -39113,7 +39113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1336" t="n">
         <v>266103</v>
@@ -39229,7 +39229,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1340" t="n">
         <v>294026</v>
@@ -39258,7 +39258,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.85902690887451</v>
+        <v>2.85902667045593</v>
       </c>
       <c r="H1341" t="n">
         <v>108872</v>
@@ -39287,7 +39287,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.85519409179688</v>
+        <v>2.85519433021545</v>
       </c>
       <c r="H1342" t="n">
         <v>124489</v>
@@ -39403,7 +39403,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.9663360118866</v>
+        <v>2.96633577346802</v>
       </c>
       <c r="H1346" t="n">
         <v>181306</v>
@@ -39490,7 +39490,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1349" t="n">
         <v>150256</v>
@@ -39577,7 +39577,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1352" t="n">
         <v>204988</v>
@@ -39635,7 +39635,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1354" t="n">
         <v>192611</v>
@@ -39664,7 +39664,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1355" t="n">
         <v>350615</v>
@@ -39693,7 +39693,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.1541268825531</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1356" t="n">
         <v>386167</v>
@@ -39780,7 +39780,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676653862</v>
+        <v>3.27676677703857</v>
       </c>
       <c r="H1359" t="n">
         <v>363222</v>
@@ -39925,7 +39925,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.09664011001587</v>
+        <v>3.09664034843445</v>
       </c>
       <c r="H1364" t="n">
         <v>441387</v>
@@ -40012,7 +40012,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1367" t="n">
         <v>167546</v>
@@ -40070,7 +40070,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.09664011001587</v>
+        <v>3.09664034843445</v>
       </c>
       <c r="H1369" t="n">
         <v>235700</v>
@@ -40099,7 +40099,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1370" t="n">
         <v>380013</v>
@@ -40157,7 +40157,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1372" t="n">
         <v>215125</v>
@@ -40186,7 +40186,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1373" t="n">
         <v>109666</v>
@@ -40273,7 +40273,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1376" t="n">
         <v>125022</v>
@@ -40331,7 +40331,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.2269446849823</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1378" t="n">
         <v>159804</v>
@@ -40360,7 +40360,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209685325623</v>
       </c>
       <c r="H1379" t="n">
         <v>919643</v>
@@ -40418,7 +40418,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.43389797210693</v>
+        <v>3.43389821052551</v>
       </c>
       <c r="H1381" t="n">
         <v>491076</v>
@@ -40447,7 +40447,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.5412073135376</v>
+        <v>3.54120755195618</v>
       </c>
       <c r="H1382" t="n">
         <v>720088</v>
@@ -40534,7 +40534,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737449645996</v>
+        <v>3.53737473487854</v>
       </c>
       <c r="H1385" t="n">
         <v>247331</v>
@@ -40650,7 +40650,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.39940547943115</v>
+        <v>3.39940595626831</v>
       </c>
       <c r="H1389" t="n">
         <v>173631</v>
@@ -40737,7 +40737,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.33042097091675</v>
+        <v>3.33042120933533</v>
       </c>
       <c r="H1392" t="n">
         <v>314803</v>
@@ -40853,7 +40853,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1396" t="n">
         <v>543980</v>
@@ -40882,7 +40882,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1397" t="n">
         <v>183307</v>
@@ -40911,7 +40911,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1398" t="n">
         <v>112518</v>
@@ -41027,7 +41027,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1402" t="n">
         <v>186824</v>
@@ -41085,7 +41085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.2269446849823</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1404" t="n">
         <v>114681</v>
@@ -41143,7 +41143,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1406" t="n">
         <v>210201</v>
@@ -41201,7 +41201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1408" t="n">
         <v>69983</v>
@@ -41230,7 +41230,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1409" t="n">
         <v>221820</v>
@@ -41288,7 +41288,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1411" t="n">
         <v>170666</v>
@@ -41346,7 +41346,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.09664011001587</v>
+        <v>3.09664034843445</v>
       </c>
       <c r="H1413" t="n">
         <v>167993</v>
@@ -41375,7 +41375,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.1541268825531</v>
+        <v>3.15412712097168</v>
       </c>
       <c r="H1414" t="n">
         <v>365235</v>
@@ -41404,7 +41404,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646244049072</v>
+        <v>3.14646220207214</v>
       </c>
       <c r="H1415" t="n">
         <v>92805</v>
@@ -41491,7 +41491,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1418" t="n">
         <v>78047</v>
@@ -41549,7 +41549,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.08131051063538</v>
+        <v>3.0813102722168</v>
       </c>
       <c r="H1420" t="n">
         <v>108491</v>
@@ -41665,7 +41665,7 @@
         <v>4.125</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.16179203987122</v>
+        <v>3.16179227828979</v>
       </c>
       <c r="H1424" t="n">
         <v>65763</v>
@@ -41694,7 +41694,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610686302185</v>
+        <v>3.24610662460327</v>
       </c>
       <c r="H1425" t="n">
         <v>182882</v>
@@ -41723,7 +41723,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377130508423</v>
+        <v>3.25377178192139</v>
       </c>
       <c r="H1426" t="n">
         <v>193950</v>
@@ -41839,7 +41839,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.09664011001587</v>
+        <v>3.09664034843445</v>
       </c>
       <c r="H1430" t="n">
         <v>236415</v>
@@ -41868,7 +41868,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.12730026245117</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1431" t="n">
         <v>199731</v>
@@ -41926,7 +41926,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.01615786552429</v>
+        <v>3.01615834236145</v>
       </c>
       <c r="H1433" t="n">
         <v>370036</v>
@@ -42100,7 +42100,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166608810425</v>
+        <v>2.98166632652283</v>
       </c>
       <c r="H1439" t="n">
         <v>590692</v>
@@ -42129,7 +42129,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1440" t="n">
         <v>279680</v>
@@ -42158,7 +42158,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.09664011001587</v>
+        <v>3.09664034843445</v>
       </c>
       <c r="H1441" t="n">
         <v>308009</v>
@@ -42245,7 +42245,7 @@
         <v>3.875</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.97016835212708</v>
+        <v>2.97016859054565</v>
       </c>
       <c r="H1444" t="n">
         <v>484542</v>
@@ -42303,7 +42303,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.86669158935547</v>
+        <v>2.86669182777405</v>
       </c>
       <c r="H1446" t="n">
         <v>425712</v>
@@ -42419,7 +42419,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.79387450218201</v>
+        <v>2.79387474060059</v>
       </c>
       <c r="H1450" t="n">
         <v>304455</v>
@@ -42825,7 +42825,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.07364535331726</v>
+        <v>3.07364559173584</v>
       </c>
       <c r="H1464" t="n">
         <v>341626</v>
@@ -42854,7 +42854,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1465" t="n">
         <v>296217</v>
@@ -42912,7 +42912,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.03148794174194</v>
+        <v>3.03148818016052</v>
       </c>
       <c r="H1467" t="n">
         <v>119381</v>
@@ -42941,7 +42941,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1468" t="n">
         <v>102163</v>
@@ -42999,7 +42999,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1470" t="n">
         <v>167749</v>
@@ -43028,7 +43028,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1471" t="n">
         <v>311050</v>
@@ -43057,7 +43057,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.0698127746582</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H1472" t="n">
         <v>332716</v>
@@ -43086,7 +43086,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214761734009</v>
+        <v>3.06214785575867</v>
       </c>
       <c r="H1473" t="n">
         <v>159481</v>
@@ -43202,7 +43202,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1477" t="n">
         <v>1174979</v>
@@ -43231,7 +43231,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.115802526474</v>
+        <v>3.11580228805542</v>
       </c>
       <c r="H1478" t="n">
         <v>845247</v>
@@ -43289,7 +43289,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1480" t="n">
         <v>585959</v>
@@ -43492,7 +43492,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.03532075881958</v>
+        <v>3.035320520401</v>
       </c>
       <c r="H1487" t="n">
         <v>1594525</v>
@@ -43579,7 +43579,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813736915588</v>
+        <v>3.10813760757446</v>
       </c>
       <c r="H1490" t="n">
         <v>301508</v>
@@ -43608,7 +43608,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1491" t="n">
         <v>141241</v>
@@ -43695,7 +43695,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430526733398</v>
+        <v>3.10430550575256</v>
       </c>
       <c r="H1494" t="n">
         <v>470480</v>
@@ -43753,7 +43753,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.954838514328</v>
+        <v>2.95483875274658</v>
       </c>
       <c r="H1496" t="n">
         <v>427392</v>
@@ -43782,7 +43782,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651368141174</v>
+        <v>2.91651391983032</v>
       </c>
       <c r="H1497" t="n">
         <v>234286</v>
@@ -43840,7 +43840,7 @@
         <v>3.75</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.874356508255</v>
+        <v>2.87435674667358</v>
       </c>
       <c r="H1499" t="n">
         <v>488141</v>
@@ -43985,7 +43985,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.70189547538757</v>
+        <v>2.70189523696899</v>
       </c>
       <c r="H1504" t="n">
         <v>285523</v>
@@ -44014,7 +44014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1505" t="n">
         <v>615078</v>
@@ -44043,7 +44043,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74022006988525</v>
+        <v>2.74021983146667</v>
       </c>
       <c r="H1506" t="n">
         <v>191990</v>
@@ -44072,7 +44072,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1507" t="n">
         <v>201693</v>
@@ -44101,7 +44101,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255491256714</v>
+        <v>2.73255515098572</v>
       </c>
       <c r="H1508" t="n">
         <v>218675</v>
@@ -44130,7 +44130,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1509" t="n">
         <v>131010</v>
@@ -44217,7 +44217,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.7248899936676</v>
+        <v>2.72489023208618</v>
       </c>
       <c r="H1512" t="n">
         <v>148986</v>
@@ -44275,7 +44275,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.66357016563416</v>
+        <v>2.66357040405273</v>
       </c>
       <c r="H1514" t="n">
         <v>189008</v>
@@ -44333,7 +44333,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.88202166557312</v>
+        <v>2.88202142715454</v>
       </c>
       <c r="H1516" t="n">
         <v>659336</v>
@@ -44362,7 +44362,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735150337219</v>
+        <v>2.89735126495361</v>
       </c>
       <c r="H1517" t="n">
         <v>354141</v>
@@ -44652,7 +44652,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.01615786552429</v>
+        <v>3.01615834236145</v>
       </c>
       <c r="H1527" t="n">
         <v>147446</v>
@@ -44710,7 +44710,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.115802526474</v>
+        <v>3.11580228805542</v>
       </c>
       <c r="H1529" t="n">
         <v>212110</v>
@@ -44739,7 +44739,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1530" t="n">
         <v>467217</v>
@@ -44855,7 +44855,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.12730026245117</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1534" t="n">
         <v>374707</v>
@@ -44913,7 +44913,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1536" t="n">
         <v>504076</v>
@@ -45000,7 +45000,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1539" t="n">
         <v>647371</v>
@@ -45174,7 +45174,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113236427307</v>
+        <v>3.13113260269165</v>
       </c>
       <c r="H1545" t="n">
         <v>194223</v>
@@ -45203,7 +45203,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1546" t="n">
         <v>411864</v>
@@ -45261,7 +45261,7 @@
         <v>4.125</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.16179203987122</v>
+        <v>3.16179227828979</v>
       </c>
       <c r="H1548" t="n">
         <v>207618</v>
@@ -45319,7 +45319,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1550" t="n">
         <v>126850</v>
@@ -45348,7 +45348,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.08131051063538</v>
+        <v>3.0813102722168</v>
       </c>
       <c r="H1551" t="n">
         <v>208252</v>
@@ -45435,7 +45435,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.11196994781494</v>
+        <v>3.11197018623352</v>
       </c>
       <c r="H1554" t="n">
         <v>122607</v>
@@ -45464,7 +45464,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.2269446849823</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1555" t="n">
         <v>415471</v>
@@ -45493,7 +45493,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.24227428436279</v>
+        <v>3.24227452278137</v>
       </c>
       <c r="H1556" t="n">
         <v>281497</v>
@@ -45551,7 +45551,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1558" t="n">
         <v>301113</v>
@@ -45609,7 +45609,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1560" t="n">
         <v>279714</v>
@@ -45638,7 +45638,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.24993920326233</v>
+        <v>3.24993896484375</v>
       </c>
       <c r="H1561" t="n">
         <v>186625</v>
@@ -45667,7 +45667,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.16945719718933</v>
+        <v>3.16945743560791</v>
       </c>
       <c r="H1562" t="n">
         <v>535155</v>
@@ -45725,7 +45725,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.12730026245117</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1564" t="n">
         <v>412281</v>
@@ -45841,7 +45841,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1568" t="n">
         <v>500504</v>
@@ -45870,7 +45870,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.30359387397766</v>
+        <v>3.30359363555908</v>
       </c>
       <c r="H1569" t="n">
         <v>301184</v>
@@ -46015,7 +46015,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1574" t="n">
         <v>711393</v>
@@ -46044,7 +46044,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1575" t="n">
         <v>411695</v>
@@ -46073,7 +46073,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.2307767868042</v>
+        <v>3.23077702522278</v>
       </c>
       <c r="H1576" t="n">
         <v>421250</v>
@@ -46102,7 +46102,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.2269446849823</v>
+        <v>3.22694420814514</v>
       </c>
       <c r="H1577" t="n">
         <v>314566</v>
@@ -46189,7 +46189,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394945144653</v>
+        <v>3.20394968986511</v>
       </c>
       <c r="H1580" t="n">
         <v>262215</v>
@@ -46276,7 +46276,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059935569763</v>
+        <v>3.28059911727905</v>
       </c>
       <c r="H1583" t="n">
         <v>178783</v>
@@ -46363,7 +46363,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760412216187</v>
+        <v>3.25760436058044</v>
       </c>
       <c r="H1586" t="n">
         <v>154125</v>
@@ -46479,7 +46479,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.34958362579346</v>
+        <v>3.3495831489563</v>
       </c>
       <c r="H1590" t="n">
         <v>338944</v>
@@ -46682,7 +46682,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.50288271903992</v>
+        <v>3.5028829574585</v>
       </c>
       <c r="H1597" t="n">
         <v>291846</v>
@@ -46711,7 +46711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.46455812454224</v>
+        <v>3.46455788612366</v>
       </c>
       <c r="H1598" t="n">
         <v>146124</v>
@@ -46740,7 +46740,7 @@
         <v>4.625</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.54503989219666</v>
+        <v>3.54503965377808</v>
       </c>
       <c r="H1599" t="n">
         <v>184940</v>
@@ -46769,7 +46769,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.48371982574463</v>
+        <v>3.48372030258179</v>
       </c>
       <c r="H1600" t="n">
         <v>129996</v>
@@ -46885,7 +46885,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.52204513549805</v>
+        <v>3.52204465866089</v>
       </c>
       <c r="H1604" t="n">
         <v>186150</v>
@@ -46972,7 +46972,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.50671482086182</v>
+        <v>3.50671529769897</v>
       </c>
       <c r="H1607" t="n">
         <v>142915</v>
@@ -47059,7 +47059,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.41473531723022</v>
+        <v>3.41473579406738</v>
       </c>
       <c r="H1610" t="n">
         <v>352993</v>
@@ -47088,7 +47088,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.43006563186646</v>
+        <v>3.43006539344788</v>
       </c>
       <c r="H1611" t="n">
         <v>150531</v>
@@ -47117,7 +47117,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39940547943115</v>
+        <v>3.39940595626831</v>
       </c>
       <c r="H1612" t="n">
         <v>160647</v>
@@ -47146,7 +47146,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209637641907</v>
+        <v>3.29209685325623</v>
       </c>
       <c r="H1613" t="n">
         <v>656275</v>
@@ -47204,7 +47204,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.21371388435364</v>
+        <v>3.21371364593506</v>
       </c>
       <c r="H1615" t="n">
         <v>700758</v>
@@ -47262,7 +47262,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1617" t="n">
         <v>369551</v>
@@ -47291,7 +47291,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.26804184913635</v>
+        <v>3.26804208755493</v>
       </c>
       <c r="H1618" t="n">
         <v>297177</v>
@@ -47349,7 +47349,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177249908447</v>
+        <v>3.40177273750305</v>
       </c>
       <c r="H1620" t="n">
         <v>184041</v>
@@ -47407,7 +47407,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.37251901626587</v>
+        <v>3.37251877784729</v>
       </c>
       <c r="H1622" t="n">
         <v>196489</v>
@@ -47436,7 +47436,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147457122803</v>
+        <v>3.30147433280945</v>
       </c>
       <c r="H1623" t="n">
         <v>155525</v>
@@ -47465,7 +47465,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.26386284828186</v>
+        <v>3.26386260986328</v>
       </c>
       <c r="H1624" t="n">
         <v>184608</v>
@@ -47494,7 +47494,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1625" t="n">
         <v>92419</v>
@@ -47523,7 +47523,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.33072805404663</v>
+        <v>3.33072781562805</v>
       </c>
       <c r="H1626" t="n">
         <v>136171</v>
@@ -47552,7 +47552,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.35998177528381</v>
+        <v>3.35998153686523</v>
       </c>
       <c r="H1627" t="n">
         <v>103168</v>
@@ -47581,7 +47581,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.36416077613831</v>
+        <v>3.36416101455688</v>
       </c>
       <c r="H1628" t="n">
         <v>90572</v>
@@ -47668,7 +47668,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38087725639343</v>
+        <v>3.38087701797485</v>
       </c>
       <c r="H1631" t="n">
         <v>335342</v>
@@ -47697,7 +47697,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1632" t="n">
         <v>295881</v>
@@ -47755,7 +47755,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.30983257293701</v>
+        <v>3.30983281135559</v>
       </c>
       <c r="H1634" t="n">
         <v>105059</v>
@@ -47813,7 +47813,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968384742737</v>
+        <v>3.25968408584595</v>
       </c>
       <c r="H1636" t="n">
         <v>115170</v>
@@ -47842,7 +47842,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.22625112533569</v>
+        <v>3.22625088691711</v>
       </c>
       <c r="H1637" t="n">
         <v>144155</v>
@@ -47900,7 +47900,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.0758044719696</v>
+        <v>3.07580423355103</v>
       </c>
       <c r="H1639" t="n">
         <v>209765</v>
@@ -47929,7 +47929,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043182373047</v>
+        <v>2.95043158531189</v>
       </c>
       <c r="H1640" t="n">
         <v>210448</v>
@@ -47987,7 +47987,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1642" t="n">
         <v>151991</v>
@@ -48045,7 +48045,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.90446162223816</v>
+        <v>2.90446186065674</v>
       </c>
       <c r="H1644" t="n">
         <v>388116</v>
@@ -48103,7 +48103,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.97132706642151</v>
+        <v>2.97132730484009</v>
       </c>
       <c r="H1646" t="n">
         <v>131405</v>
@@ -48132,7 +48132,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.9462525844574</v>
+        <v>2.94625282287598</v>
       </c>
       <c r="H1647" t="n">
         <v>134428</v>
@@ -48161,7 +48161,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1648" t="n">
         <v>163785</v>
@@ -48219,7 +48219,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1650" t="n">
         <v>131117</v>
@@ -48335,7 +48335,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.90446162223816</v>
+        <v>2.90446186065674</v>
       </c>
       <c r="H1654" t="n">
         <v>96343</v>
@@ -48422,7 +48422,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.84595489501953</v>
+        <v>2.84595465660095</v>
       </c>
       <c r="H1657" t="n">
         <v>159265</v>
@@ -48451,7 +48451,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1658" t="n">
         <v>166380</v>
@@ -48509,7 +48509,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.00893902778625</v>
+        <v>3.00893878936768</v>
       </c>
       <c r="H1660" t="n">
         <v>66664</v>
@@ -48567,7 +48567,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.975506067276</v>
+        <v>2.97550630569458</v>
       </c>
       <c r="H1662" t="n">
         <v>113262</v>
@@ -48654,7 +48654,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1665" t="n">
         <v>42245</v>
@@ -48683,7 +48683,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.01729702949524</v>
+        <v>3.01729679107666</v>
       </c>
       <c r="H1666" t="n">
         <v>33283</v>
@@ -48712,7 +48712,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93371534347534</v>
+        <v>2.93371558189392</v>
       </c>
       <c r="H1667" t="n">
         <v>141470</v>
@@ -48799,7 +48799,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.98804354667664</v>
+        <v>2.98804330825806</v>
       </c>
       <c r="H1670" t="n">
         <v>140069</v>
@@ -48857,7 +48857,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.97968554496765</v>
+        <v>2.97968530654907</v>
       </c>
       <c r="H1672" t="n">
         <v>143081</v>
@@ -48944,7 +48944,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.01311779022217</v>
+        <v>3.01311802864075</v>
       </c>
       <c r="H1675" t="n">
         <v>64858</v>
@@ -49408,7 +49408,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043182373047</v>
+        <v>2.95043158531189</v>
       </c>
       <c r="H1691" t="n">
         <v>76345</v>
@@ -49553,7 +49553,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.82923817634583</v>
+        <v>2.8292384147644</v>
       </c>
       <c r="H1696" t="n">
         <v>102218</v>
@@ -49640,7 +49640,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1699" t="n">
         <v>94641</v>
@@ -49698,7 +49698,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1701" t="n">
         <v>96912</v>
@@ -49727,7 +49727,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.74147748947144</v>
+        <v>2.74147772789001</v>
       </c>
       <c r="H1702" t="n">
         <v>135653</v>
@@ -49814,7 +49814,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.83341765403748</v>
+        <v>2.8334174156189</v>
       </c>
       <c r="H1705" t="n">
         <v>225042</v>
@@ -49959,7 +49959,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1710" t="n">
         <v>271736</v>
@@ -50046,7 +50046,7 @@
         <v>2.875</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1713" t="n">
         <v>327552</v>
@@ -50365,7 +50365,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.28177881240845</v>
+        <v>2.28177857398987</v>
       </c>
       <c r="H1724" t="n">
         <v>163789</v>
@@ -50394,7 +50394,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1725" t="n">
         <v>189735</v>
@@ -50539,7 +50539,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.21491360664368</v>
+        <v>2.2149133682251</v>
       </c>
       <c r="H1730" t="n">
         <v>525600</v>
@@ -50655,7 +50655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1734" t="n">
         <v>187787</v>
@@ -50800,7 +50800,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1739" t="n">
         <v>123630</v>
@@ -50858,7 +50858,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.5199863910675</v>
+        <v>2.51998615264893</v>
       </c>
       <c r="H1741" t="n">
         <v>649724</v>
@@ -50887,7 +50887,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.5032696723938</v>
+        <v>2.50326991081238</v>
       </c>
       <c r="H1742" t="n">
         <v>250081</v>
@@ -50916,7 +50916,7 @@
         <v>3</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.50744915008545</v>
+        <v>2.50744891166687</v>
       </c>
       <c r="H1743" t="n">
         <v>179184</v>
@@ -50945,7 +50945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013511657715</v>
+        <v>2.57013535499573</v>
       </c>
       <c r="H1744" t="n">
         <v>319932</v>
@@ -51003,7 +51003,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.57849359512329</v>
+        <v>2.57849335670471</v>
       </c>
       <c r="H1746" t="n">
         <v>135722</v>
@@ -51032,7 +51032,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1747" t="n">
         <v>321826</v>
@@ -51119,7 +51119,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685183525085</v>
+        <v>2.58685159683228</v>
       </c>
       <c r="H1750" t="n">
         <v>233347</v>
@@ -51438,7 +51438,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.63282155990601</v>
+        <v>2.63282179832458</v>
       </c>
       <c r="H1761" t="n">
         <v>2139834</v>
@@ -51467,7 +51467,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.68297076225281</v>
+        <v>2.68297052383423</v>
       </c>
       <c r="H1762" t="n">
         <v>317737</v>
@@ -51757,7 +51757,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.63700032234192</v>
+        <v>2.6370005607605</v>
       </c>
       <c r="H1772" t="n">
         <v>171669</v>
@@ -51844,7 +51844,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.5826723575592</v>
+        <v>2.58267259597778</v>
       </c>
       <c r="H1775" t="n">
         <v>230178</v>
@@ -51873,7 +51873,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1776" t="n">
         <v>215923</v>
@@ -51931,7 +51931,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61610531806946</v>
+        <v>2.61610507965088</v>
       </c>
       <c r="H1778" t="n">
         <v>44718</v>
@@ -52076,7 +52076,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.65371704101562</v>
+        <v>2.65371680259705</v>
       </c>
       <c r="H1783" t="n">
         <v>59395</v>
@@ -52308,7 +52308,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.77908968925476</v>
+        <v>2.77908945083618</v>
       </c>
       <c r="H1791" t="n">
         <v>288121</v>
@@ -52337,7 +52337,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073097229004</v>
+        <v>2.77073121070862</v>
       </c>
       <c r="H1792" t="n">
         <v>160766</v>
@@ -52511,7 +52511,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.8835666179657</v>
+        <v>2.88356637954712</v>
       </c>
       <c r="H1798" t="n">
         <v>177420</v>
@@ -52627,7 +52627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.4740161895752</v>
+        <v>2.47401642799377</v>
       </c>
       <c r="H1802" t="n">
         <v>1663657</v>
@@ -53178,7 +53178,7 @@
         <v>2.875</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.40297222137451</v>
+        <v>2.40297198295593</v>
       </c>
       <c r="H1821" t="n">
         <v>691856</v>
@@ -53613,7 +53613,7 @@
         <v>2.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1836" t="n">
         <v>505563</v>
@@ -53874,7 +53874,7 @@
         <v>2.75</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.29849481582642</v>
+        <v>2.298495054245</v>
       </c>
       <c r="H1845" t="n">
         <v>224918</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1851" t="n">
         <v>294292</v>
@@ -54077,7 +54077,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.39043474197388</v>
+        <v>2.3904345035553</v>
       </c>
       <c r="H1852" t="n">
         <v>247994</v>
@@ -54106,7 +54106,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.43640446662903</v>
+        <v>2.43640470504761</v>
       </c>
       <c r="H1853" t="n">
         <v>352350</v>
@@ -54164,7 +54164,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1855" t="n">
         <v>498934</v>
@@ -54193,7 +54193,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.46565818786621</v>
+        <v>2.46565842628479</v>
       </c>
       <c r="H1856" t="n">
         <v>347116</v>
@@ -54309,7 +54309,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.44058394432068</v>
+        <v>2.4405837059021</v>
       </c>
       <c r="H1860" t="n">
         <v>158968</v>
@@ -54454,7 +54454,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.48237466812134</v>
+        <v>2.48237442970276</v>
       </c>
       <c r="H1865" t="n">
         <v>433044</v>
@@ -54483,7 +54483,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.44476294517517</v>
+        <v>2.44476270675659</v>
       </c>
       <c r="H1866" t="n">
         <v>307676</v>
@@ -54570,7 +54570,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.41550946235657</v>
+        <v>2.41550922393799</v>
       </c>
       <c r="H1869" t="n">
         <v>644276</v>
@@ -80125,6 +80125,35 @@
         <v>44788</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>3.6949999332428</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>3.73499989509583</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>3.66499996185303</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>111935</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -456,7 +456,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64235925674438</v>
+        <v>4.64235973358154</v>
       </c>
       <c r="H3" t="n">
         <v>62931</v>
@@ -514,7 +514,7 @@
         <v>8.10179138183594</v>
       </c>
       <c r="G5" t="n">
-        <v>4.59751892089844</v>
+        <v>4.59751844406128</v>
       </c>
       <c r="H5" t="n">
         <v>165490</v>
@@ -543,7 +543,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G6" t="n">
-        <v>4.48409700393677</v>
+        <v>4.48409748077393</v>
       </c>
       <c r="H6" t="n">
         <v>164680</v>
@@ -572,7 +572,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G7" t="n">
-        <v>4.37858867645264</v>
+        <v>4.37858915328979</v>
       </c>
       <c r="H7" t="n">
         <v>111248</v>
@@ -601,7 +601,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G8" t="n">
-        <v>4.40496587753296</v>
+        <v>4.4049654006958</v>
       </c>
       <c r="H8" t="n">
         <v>127969</v>
@@ -630,7 +630,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50783634185791</v>
+        <v>4.50783681869507</v>
       </c>
       <c r="H9" t="n">
         <v>83967</v>
@@ -688,7 +688,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G11" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H11" t="n">
         <v>287176</v>
@@ -775,7 +775,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48176956176758</v>
+        <v>3.48176980018616</v>
       </c>
       <c r="H14" t="n">
         <v>416053</v>
@@ -804,7 +804,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G15" t="n">
-        <v>3.74554038047791</v>
+        <v>3.74554014205933</v>
       </c>
       <c r="H15" t="n">
         <v>313484</v>
@@ -833,7 +833,7 @@
         <v>6.72592687606812</v>
       </c>
       <c r="G16" t="n">
-        <v>3.81675791740417</v>
+        <v>3.81675744056702</v>
       </c>
       <c r="H16" t="n">
         <v>176408</v>
@@ -891,7 +891,7 @@
         <v>6.75846481323242</v>
       </c>
       <c r="G18" t="n">
-        <v>3.83522152900696</v>
+        <v>3.83522200584412</v>
       </c>
       <c r="H18" t="n">
         <v>75537</v>
@@ -920,7 +920,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G19" t="n">
-        <v>3.80884504318237</v>
+        <v>3.80884480476379</v>
       </c>
       <c r="H19" t="n">
         <v>163830</v>
@@ -949,7 +949,7 @@
         <v>6.48422193527222</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67959713935852</v>
+        <v>3.6795973777771</v>
       </c>
       <c r="H20" t="n">
         <v>133261</v>
@@ -978,7 +978,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G21" t="n">
-        <v>3.82467103004456</v>
+        <v>3.82467079162598</v>
       </c>
       <c r="H21" t="n">
         <v>190130</v>
@@ -1007,7 +1007,7 @@
         <v>6.92115116119385</v>
       </c>
       <c r="G22" t="n">
-        <v>3.92754125595093</v>
+        <v>3.92754149436951</v>
       </c>
       <c r="H22" t="n">
         <v>169554</v>
@@ -1036,7 +1036,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G23" t="n">
-        <v>3.74554038047791</v>
+        <v>3.74554014205933</v>
       </c>
       <c r="H23" t="n">
         <v>350145</v>
@@ -1065,7 +1065,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G24" t="n">
-        <v>3.78246736526489</v>
+        <v>3.78246808052063</v>
       </c>
       <c r="H24" t="n">
         <v>251231</v>
@@ -1094,7 +1094,7 @@
         <v>6.28434991836548</v>
       </c>
       <c r="G25" t="n">
-        <v>3.56617617607117</v>
+        <v>3.56617641448975</v>
       </c>
       <c r="H25" t="n">
         <v>406980</v>
@@ -1123,7 +1123,7 @@
         <v>6.43773984909058</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65322065353394</v>
+        <v>3.65322041511536</v>
       </c>
       <c r="H26" t="n">
         <v>190657</v>
@@ -1152,7 +1152,7 @@
         <v>5.87530899047852</v>
       </c>
       <c r="G27" t="n">
-        <v>3.33405828475952</v>
+        <v>3.33405780792236</v>
       </c>
       <c r="H27" t="n">
         <v>238163</v>
@@ -1210,7 +1210,7 @@
         <v>6.27505302429199</v>
       </c>
       <c r="G29" t="n">
-        <v>3.56090044975281</v>
+        <v>3.56090092658997</v>
       </c>
       <c r="H29" t="n">
         <v>200231</v>
@@ -1239,7 +1239,7 @@
         <v>6.06588506698608</v>
       </c>
       <c r="G30" t="n">
-        <v>3.44220399856567</v>
+        <v>3.44220447540283</v>
       </c>
       <c r="H30" t="n">
         <v>158033</v>
@@ -1268,7 +1268,7 @@
         <v>6.18673801422119</v>
       </c>
       <c r="G31" t="n">
-        <v>3.51078414916992</v>
+        <v>3.5107843875885</v>
       </c>
       <c r="H31" t="n">
         <v>208699</v>
@@ -1297,7 +1297,7 @@
         <v>6.60507488250732</v>
       </c>
       <c r="G32" t="n">
-        <v>3.74817800521851</v>
+        <v>3.74817752838135</v>
       </c>
       <c r="H32" t="n">
         <v>131098</v>
@@ -1355,7 +1355,7 @@
         <v>6.73987197875977</v>
       </c>
       <c r="G34" t="n">
-        <v>3.82467103004456</v>
+        <v>3.82467079162598</v>
       </c>
       <c r="H34" t="n">
         <v>72733</v>
@@ -1384,7 +1384,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G35" t="n">
-        <v>3.79829406738281</v>
+        <v>3.79829454421997</v>
       </c>
       <c r="H35" t="n">
         <v>53341</v>
@@ -1442,7 +1442,7 @@
         <v>6.90255880355835</v>
       </c>
       <c r="G37" t="n">
-        <v>3.91699051856995</v>
+        <v>3.91699123382568</v>
       </c>
       <c r="H37" t="n">
         <v>87617</v>
@@ -1500,7 +1500,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G39" t="n">
-        <v>3.81411981582642</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H39" t="n">
         <v>93458</v>
@@ -1529,7 +1529,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G40" t="n">
-        <v>3.84577298164368</v>
+        <v>3.84577322006226</v>
       </c>
       <c r="H40" t="n">
         <v>43899</v>
@@ -1558,7 +1558,7 @@
         <v>6.78635406494141</v>
       </c>
       <c r="G41" t="n">
-        <v>3.85104870796204</v>
+        <v>3.8510479927063</v>
       </c>
       <c r="H41" t="n">
         <v>113404</v>
@@ -1587,7 +1587,7 @@
         <v>6.85607719421387</v>
       </c>
       <c r="G42" t="n">
-        <v>3.89061331748962</v>
+        <v>3.89061379432678</v>
       </c>
       <c r="H42" t="n">
         <v>132642</v>
@@ -1616,7 +1616,7 @@
         <v>6.89326190948486</v>
       </c>
       <c r="G43" t="n">
-        <v>3.91171479225159</v>
+        <v>3.91171503067017</v>
       </c>
       <c r="H43" t="n">
         <v>374802</v>
@@ -1732,7 +1732,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G47" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339967727661</v>
       </c>
       <c r="H47" t="n">
         <v>153285</v>
@@ -1761,7 +1761,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G48" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H48" t="n">
         <v>85660</v>
@@ -1790,7 +1790,7 @@
         <v>7.37667417526245</v>
       </c>
       <c r="G49" t="n">
-        <v>4.18603658676147</v>
+        <v>4.18603610992432</v>
       </c>
       <c r="H49" t="n">
         <v>97201</v>
@@ -1877,7 +1877,7 @@
         <v>7.76247310638428</v>
       </c>
       <c r="G52" t="n">
-        <v>4.40496587753296</v>
+        <v>4.4049654006958</v>
       </c>
       <c r="H52" t="n">
         <v>135917</v>
@@ -1935,7 +1935,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G54" t="n">
-        <v>4.30473375320435</v>
+        <v>4.30473327636719</v>
       </c>
       <c r="H54" t="n">
         <v>145802</v>
@@ -1993,7 +1993,7 @@
         <v>7.94840097427368</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51047420501709</v>
+        <v>4.51047372817993</v>
       </c>
       <c r="H56" t="n">
         <v>440847</v>
@@ -2022,7 +2022,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44716882705688</v>
+        <v>4.44716930389404</v>
       </c>
       <c r="H57" t="n">
         <v>149650</v>
@@ -2109,7 +2109,7 @@
         <v>7.39526700973511</v>
       </c>
       <c r="G60" t="n">
-        <v>4.19658756256104</v>
+        <v>4.19658803939819</v>
       </c>
       <c r="H60" t="n">
         <v>142725</v>
@@ -2283,7 +2283,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G66" t="n">
-        <v>4.11481904983521</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H66" t="n">
         <v>76088</v>
@@ -2312,7 +2312,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G67" t="n">
-        <v>4.10426807403564</v>
+        <v>4.10426759719849</v>
       </c>
       <c r="H67" t="n">
         <v>86909</v>
@@ -2341,7 +2341,7 @@
         <v>7.18144989013672</v>
       </c>
       <c r="G68" t="n">
-        <v>4.07525396347046</v>
+        <v>4.07525300979614</v>
       </c>
       <c r="H68" t="n">
         <v>38160</v>
@@ -2370,7 +2370,7 @@
         <v>7.18609809875488</v>
       </c>
       <c r="G69" t="n">
-        <v>4.07789039611816</v>
+        <v>4.07789087295532</v>
       </c>
       <c r="H69" t="n">
         <v>110418</v>
@@ -2399,7 +2399,7 @@
         <v>7.36737680435181</v>
       </c>
       <c r="G70" t="n">
-        <v>4.18076038360596</v>
+        <v>4.18076086044312</v>
       </c>
       <c r="H70" t="n">
         <v>73551</v>
@@ -2428,7 +2428,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G71" t="n">
-        <v>4.08844137191772</v>
+        <v>4.08844184875488</v>
       </c>
       <c r="H71" t="n">
         <v>110301</v>
@@ -2457,7 +2457,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812252044678</v>
       </c>
       <c r="H72" t="n">
         <v>138383</v>
@@ -2486,7 +2486,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G73" t="n">
-        <v>4.24670314788818</v>
+        <v>4.2467041015625</v>
       </c>
       <c r="H73" t="n">
         <v>30816</v>
@@ -2515,7 +2515,7 @@
         <v>7.3627290725708</v>
       </c>
       <c r="G74" t="n">
-        <v>4.17812299728394</v>
+        <v>4.17812252044678</v>
       </c>
       <c r="H74" t="n">
         <v>11963</v>
@@ -2544,7 +2544,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G75" t="n">
-        <v>4.16757202148438</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H75" t="n">
         <v>72788</v>
@@ -2573,7 +2573,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G76" t="n">
-        <v>4.15438508987427</v>
+        <v>4.15438461303711</v>
       </c>
       <c r="H76" t="n">
         <v>69912</v>
@@ -2602,7 +2602,7 @@
         <v>7.42315578460693</v>
       </c>
       <c r="G77" t="n">
-        <v>4.21241331100464</v>
+        <v>4.21241426467896</v>
       </c>
       <c r="H77" t="n">
         <v>65491</v>
@@ -2631,7 +2631,7 @@
         <v>7.25582122802734</v>
       </c>
       <c r="G78" t="n">
-        <v>4.11745691299438</v>
+        <v>4.11745595932007</v>
       </c>
       <c r="H78" t="n">
         <v>140314</v>
@@ -2660,7 +2660,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G79" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H79" t="n">
         <v>28153</v>
@@ -2689,7 +2689,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16757202148438</v>
+        <v>4.16757249832153</v>
       </c>
       <c r="H80" t="n">
         <v>71017</v>
@@ -2718,7 +2718,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G81" t="n">
-        <v>4.11481904983521</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H81" t="n">
         <v>109357</v>
@@ -2747,7 +2747,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11481904983521</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H82" t="n">
         <v>88007</v>
@@ -2776,7 +2776,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G83" t="n">
-        <v>4.11481904983521</v>
+        <v>4.11481857299805</v>
       </c>
       <c r="H83" t="n">
         <v>220387</v>
@@ -2805,7 +2805,7 @@
         <v>7.37202596664429</v>
       </c>
       <c r="G84" t="n">
-        <v>4.18339872360229</v>
+        <v>4.18339967727661</v>
       </c>
       <c r="H84" t="n">
         <v>135960</v>
@@ -2863,7 +2863,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G86" t="n">
-        <v>4.14119625091553</v>
+        <v>4.14119577407837</v>
       </c>
       <c r="H86" t="n">
         <v>95409</v>
@@ -2892,7 +2892,7 @@
         <v>7.26046895980835</v>
       </c>
       <c r="G87" t="n">
-        <v>4.12009382247925</v>
+        <v>4.12009429931641</v>
       </c>
       <c r="H87" t="n">
         <v>20188</v>
@@ -2921,7 +2921,7 @@
         <v>7.23258018493652</v>
       </c>
       <c r="G88" t="n">
-        <v>4.10426807403564</v>
+        <v>4.10426759719849</v>
       </c>
       <c r="H88" t="n">
         <v>42052</v>
@@ -2950,7 +2950,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G89" t="n">
-        <v>4.19394969940186</v>
+        <v>4.1939492225647</v>
       </c>
       <c r="H89" t="n">
         <v>83038</v>
@@ -2979,7 +2979,7 @@
         <v>7.30230283737183</v>
       </c>
       <c r="G90" t="n">
-        <v>4.14383316040039</v>
+        <v>4.14383363723755</v>
       </c>
       <c r="H90" t="n">
         <v>26575</v>
@@ -3037,7 +3037,7 @@
         <v>7.32089614868164</v>
       </c>
       <c r="G92" t="n">
-        <v>4.15438508987427</v>
+        <v>4.15438461303711</v>
       </c>
       <c r="H92" t="n">
         <v>118401</v>
@@ -3066,7 +3066,7 @@
         <v>7.32554388046265</v>
       </c>
       <c r="G93" t="n">
-        <v>4.15702199935913</v>
+        <v>4.15702104568481</v>
       </c>
       <c r="H93" t="n">
         <v>72826</v>
@@ -3095,7 +3095,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G94" t="n">
-        <v>4.23351526260376</v>
+        <v>4.2335147857666</v>
       </c>
       <c r="H94" t="n">
         <v>64992</v>
@@ -3124,7 +3124,7 @@
         <v>7.52541589736938</v>
       </c>
       <c r="G95" t="n">
-        <v>4.27044343948364</v>
+        <v>4.27044296264648</v>
       </c>
       <c r="H95" t="n">
         <v>62480</v>
@@ -3153,7 +3153,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G96" t="n">
-        <v>4.19131183624268</v>
+        <v>4.19131231307983</v>
       </c>
       <c r="H96" t="n">
         <v>58862</v>
@@ -3182,7 +3182,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G97" t="n">
-        <v>4.23615312576294</v>
+        <v>4.23615264892578</v>
       </c>
       <c r="H97" t="n">
         <v>39151</v>
@@ -3211,7 +3211,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G98" t="n">
-        <v>4.15174579620361</v>
+        <v>4.15174627304077</v>
       </c>
       <c r="H98" t="n">
         <v>86040</v>
@@ -3298,7 +3298,7 @@
         <v>7.38597011566162</v>
       </c>
       <c r="G101" t="n">
-        <v>4.41190671920776</v>
+        <v>4.41190767288208</v>
       </c>
       <c r="H101" t="n">
         <v>66996</v>
@@ -3356,7 +3356,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G103" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H103" t="n">
         <v>122131</v>
@@ -3385,7 +3385,7 @@
         <v>7.55795288085938</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51463890075684</v>
+        <v>4.51463937759399</v>
       </c>
       <c r="H104" t="n">
         <v>64852</v>
@@ -3443,7 +3443,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G106" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H106" t="n">
         <v>102357</v>
@@ -3472,7 +3472,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G107" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H107" t="n">
         <v>112417</v>
@@ -3501,7 +3501,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G108" t="n">
-        <v>4.4146842956543</v>
+        <v>4.41468334197998</v>
       </c>
       <c r="H108" t="n">
         <v>75432</v>
@@ -3530,7 +3530,7 @@
         <v>7.48823022842407</v>
       </c>
       <c r="G109" t="n">
-        <v>4.47299098968506</v>
+        <v>4.47299146652222</v>
       </c>
       <c r="H109" t="n">
         <v>58116</v>
@@ -3617,7 +3617,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G112" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H112" t="n">
         <v>53716</v>
@@ -3704,7 +3704,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G115" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H115" t="n">
         <v>98580</v>
@@ -3733,7 +3733,7 @@
         <v>6.55859279632568</v>
       </c>
       <c r="G116" t="n">
-        <v>3.91768455505371</v>
+        <v>3.91768503189087</v>
       </c>
       <c r="H116" t="n">
         <v>109038</v>
@@ -3762,7 +3762,7 @@
         <v>6.59577798843384</v>
       </c>
       <c r="G117" t="n">
-        <v>3.93989729881287</v>
+        <v>3.93989658355713</v>
       </c>
       <c r="H117" t="n">
         <v>151204</v>
@@ -3791,7 +3791,7 @@
         <v>6.38196182250977</v>
       </c>
       <c r="G118" t="n">
-        <v>3.81217694282532</v>
+        <v>3.81217670440674</v>
       </c>
       <c r="H118" t="n">
         <v>94805</v>
@@ -3820,7 +3820,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G119" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H119" t="n">
         <v>396991</v>
@@ -3849,7 +3849,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G120" t="n">
-        <v>4.01486301422119</v>
+        <v>4.01486349105835</v>
       </c>
       <c r="H120" t="n">
         <v>179714</v>
@@ -3965,7 +3965,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G124" t="n">
-        <v>3.89269614219666</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H124" t="n">
         <v>186001</v>
@@ -3994,7 +3994,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="n">
-        <v>3.6927855014801</v>
+        <v>3.69278597831726</v>
       </c>
       <c r="H125" t="n">
         <v>299139</v>
@@ -4052,7 +4052,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="n">
-        <v>3.72055101394653</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H127" t="n">
         <v>204444</v>
@@ -4110,7 +4110,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="n">
-        <v>4.01208686828613</v>
+        <v>4.01208639144897</v>
       </c>
       <c r="H129" t="n">
         <v>121922</v>
@@ -4139,7 +4139,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="n">
-        <v>3.87603688240051</v>
+        <v>3.87603712081909</v>
       </c>
       <c r="H130" t="n">
         <v>40805</v>
@@ -4168,7 +4168,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="n">
-        <v>3.73165678977966</v>
+        <v>3.73165702819824</v>
       </c>
       <c r="H131" t="n">
         <v>182299</v>
@@ -4197,7 +4197,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="n">
-        <v>3.70111560821533</v>
+        <v>3.70111584663391</v>
       </c>
       <c r="H132" t="n">
         <v>120419</v>
@@ -4226,7 +4226,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="n">
-        <v>3.82328224182129</v>
+        <v>3.82328295707703</v>
       </c>
       <c r="H133" t="n">
         <v>123098</v>
@@ -4255,7 +4255,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="n">
-        <v>3.91490864753723</v>
+        <v>3.91490888595581</v>
       </c>
       <c r="H134" t="n">
         <v>96476</v>
@@ -4284,7 +4284,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="n">
-        <v>3.9482262134552</v>
+        <v>3.94822716712952</v>
       </c>
       <c r="H135" t="n">
         <v>150820</v>
@@ -4342,7 +4342,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H137" t="n">
         <v>161569</v>
@@ -4545,7 +4545,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H144" t="n">
         <v>200057</v>
@@ -4632,7 +4632,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="n">
-        <v>4.37858963012695</v>
+        <v>4.37858915328979</v>
       </c>
       <c r="H147" t="n">
         <v>120474</v>
@@ -4661,7 +4661,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="n">
-        <v>4.37025880813599</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H148" t="n">
         <v>86165</v>
@@ -4748,7 +4748,7 @@
         <v>7.02805995941162</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1981143951416</v>
+        <v>4.19811487197876</v>
       </c>
       <c r="H151" t="n">
         <v>100034</v>
@@ -4777,7 +4777,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H152" t="n">
         <v>260528</v>
@@ -4835,7 +4835,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="n">
-        <v>4.30917596817017</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H154" t="n">
         <v>185636</v>
@@ -4922,7 +4922,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="n">
-        <v>4.22032690048218</v>
+        <v>4.22032642364502</v>
       </c>
       <c r="H157" t="n">
         <v>67846</v>
@@ -4951,7 +4951,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="n">
-        <v>4.25919818878174</v>
+        <v>4.2591986656189</v>
       </c>
       <c r="H158" t="n">
         <v>110609</v>
@@ -4980,7 +4980,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="n">
-        <v>4.20644426345825</v>
+        <v>4.20644378662109</v>
       </c>
       <c r="H159" t="n">
         <v>60390</v>
@@ -5009,7 +5009,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="n">
-        <v>4.18423223495483</v>
+        <v>4.18423175811768</v>
       </c>
       <c r="H160" t="n">
         <v>85871</v>
@@ -5038,7 +5038,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="n">
-        <v>4.1425838470459</v>
+        <v>4.14258337020874</v>
       </c>
       <c r="H161" t="n">
         <v>44304</v>
@@ -5212,7 +5212,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="n">
-        <v>4.10371208190918</v>
+        <v>4.10371160507202</v>
       </c>
       <c r="H167" t="n">
         <v>23476</v>
@@ -5241,7 +5241,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="n">
-        <v>4.08150053024292</v>
+        <v>4.08150005340576</v>
       </c>
       <c r="H168" t="n">
         <v>81619</v>
@@ -5270,7 +5270,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820470809937</v>
       </c>
       <c r="H169" t="n">
         <v>96105</v>
@@ -5299,7 +5299,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="n">
-        <v>4.04818248748779</v>
+        <v>4.04818201065063</v>
       </c>
       <c r="H170" t="n">
         <v>82611</v>
@@ -5328,7 +5328,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H171" t="n">
         <v>41159</v>
@@ -5386,7 +5386,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="n">
-        <v>3.97043871879578</v>
+        <v>3.97043800354004</v>
       </c>
       <c r="H173" t="n">
         <v>185702</v>
@@ -5415,7 +5415,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="n">
-        <v>4.05928754806519</v>
+        <v>4.05928802490234</v>
       </c>
       <c r="H174" t="n">
         <v>106032</v>
@@ -5444,7 +5444,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="n">
-        <v>4.00098085403442</v>
+        <v>4.00097990036011</v>
       </c>
       <c r="H175" t="n">
         <v>47175</v>
@@ -5473,7 +5473,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G176" t="n">
-        <v>4.01486301422119</v>
+        <v>4.01486349105835</v>
       </c>
       <c r="H176" t="n">
         <v>82433</v>
@@ -5502,7 +5502,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="n">
-        <v>4.03152275085449</v>
+        <v>4.03152227401733</v>
       </c>
       <c r="H177" t="n">
         <v>101079</v>
@@ -5531,7 +5531,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="n">
-        <v>3.93156743049622</v>
+        <v>3.93156766891479</v>
       </c>
       <c r="H178" t="n">
         <v>219724</v>
@@ -5560,7 +5560,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H179" t="n">
         <v>313330</v>
@@ -5589,7 +5589,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="n">
-        <v>3.72888088226318</v>
+        <v>3.72888016700745</v>
       </c>
       <c r="H180" t="n">
         <v>212138</v>
@@ -5618,7 +5618,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="n">
-        <v>3.72055101394653</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H181" t="n">
         <v>119833</v>
@@ -5647,7 +5647,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="n">
-        <v>3.66502070426941</v>
+        <v>3.66502094268799</v>
       </c>
       <c r="H182" t="n">
         <v>239810</v>
@@ -5676,7 +5676,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="n">
-        <v>3.64280843734741</v>
+        <v>3.64280819892883</v>
       </c>
       <c r="H183" t="n">
         <v>201842</v>
@@ -5705,7 +5705,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389175415039</v>
       </c>
       <c r="H184" t="n">
         <v>128389</v>
@@ -5734,7 +5734,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H185" t="n">
         <v>173655</v>
@@ -5763,7 +5763,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="n">
-        <v>3.61781930923462</v>
+        <v>3.61781907081604</v>
       </c>
       <c r="H186" t="n">
         <v>138681</v>
@@ -5792,7 +5792,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332859039307</v>
       </c>
       <c r="H187" t="n">
         <v>126621</v>
@@ -5821,7 +5821,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="n">
-        <v>3.69000935554504</v>
+        <v>3.69000911712646</v>
       </c>
       <c r="H188" t="n">
         <v>175447</v>
@@ -5879,7 +5879,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="n">
-        <v>3.72055101394653</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H190" t="n">
         <v>329741</v>
@@ -5908,7 +5908,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="n">
-        <v>3.74276399612427</v>
+        <v>3.74276328086853</v>
       </c>
       <c r="H191" t="n">
         <v>217887</v>
@@ -5937,7 +5937,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="n">
-        <v>3.72055101394653</v>
+        <v>3.7205502986908</v>
       </c>
       <c r="H192" t="n">
         <v>103333</v>
@@ -5966,7 +5966,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="n">
-        <v>3.72332787513733</v>
+        <v>3.72332859039307</v>
       </c>
       <c r="H193" t="n">
         <v>167998</v>
@@ -5995,7 +5995,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="n">
-        <v>3.67612600326538</v>
+        <v>3.67612648010254</v>
       </c>
       <c r="H194" t="n">
         <v>104706</v>
@@ -6024,7 +6024,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="n">
-        <v>3.61781930923462</v>
+        <v>3.61781907081604</v>
       </c>
       <c r="H195" t="n">
         <v>109567</v>
@@ -6053,7 +6053,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="n">
-        <v>3.65113830566406</v>
+        <v>3.65113806724548</v>
       </c>
       <c r="H196" t="n">
         <v>131242</v>
@@ -6082,7 +6082,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="n">
-        <v>3.66502070426941</v>
+        <v>3.66502094268799</v>
       </c>
       <c r="H197" t="n">
         <v>103315</v>
@@ -6111,7 +6111,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170218467712</v>
       </c>
       <c r="H198" t="n">
         <v>86545</v>
@@ -6140,7 +6140,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H199" t="n">
         <v>78308</v>
@@ -6169,7 +6169,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="n">
-        <v>3.598384141922</v>
+        <v>3.59838390350342</v>
       </c>
       <c r="H200" t="n">
         <v>58597</v>
@@ -6256,7 +6256,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170218467712</v>
       </c>
       <c r="H203" t="n">
         <v>132879</v>
@@ -6285,7 +6285,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="n">
-        <v>3.63170194625854</v>
+        <v>3.63170218467712</v>
       </c>
       <c r="H204" t="n">
         <v>133954</v>
@@ -6314,7 +6314,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="n">
-        <v>3.70666766166687</v>
+        <v>3.70666813850403</v>
       </c>
       <c r="H205" t="n">
         <v>112375</v>
@@ -6343,7 +6343,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="n">
-        <v>3.85660147666931</v>
+        <v>3.85660171508789</v>
       </c>
       <c r="H206" t="n">
         <v>205793</v>
@@ -6372,7 +6372,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92046165466309</v>
+        <v>3.92046189308167</v>
       </c>
       <c r="H207" t="n">
         <v>198572</v>
@@ -6401,7 +6401,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="n">
-        <v>3.93156743049622</v>
+        <v>3.93156766891479</v>
       </c>
       <c r="H208" t="n">
         <v>48406</v>
@@ -6430,7 +6430,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="n">
-        <v>3.9648859500885</v>
+        <v>3.96488642692566</v>
       </c>
       <c r="H209" t="n">
         <v>111598</v>
@@ -6459,7 +6459,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="n">
-        <v>3.9482262134552</v>
+        <v>3.94822716712952</v>
       </c>
       <c r="H210" t="n">
         <v>182662</v>
@@ -6546,7 +6546,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="n">
-        <v>3.89547204971313</v>
+        <v>3.89547276496887</v>
       </c>
       <c r="H213" t="n">
         <v>134927</v>
@@ -6575,7 +6575,7 @@
         <v>6.51675891876221</v>
       </c>
       <c r="G214" t="n">
-        <v>3.89269614219666</v>
+        <v>3.89269590377808</v>
       </c>
       <c r="H214" t="n">
         <v>75318</v>
@@ -6604,7 +6604,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="n">
-        <v>3.86215400695801</v>
+        <v>3.86215472221375</v>
       </c>
       <c r="H215" t="n">
         <v>72762</v>
@@ -6633,7 +6633,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H216" t="n">
         <v>114679</v>
@@ -6720,7 +6720,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="n">
-        <v>3.80107045173645</v>
+        <v>3.80107069015503</v>
       </c>
       <c r="H219" t="n">
         <v>60701</v>
@@ -6749,7 +6749,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="n">
-        <v>3.78718829154968</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H220" t="n">
         <v>128863</v>
@@ -6836,7 +6836,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="n">
-        <v>3.67612600326538</v>
+        <v>3.67612648010254</v>
       </c>
       <c r="H223" t="n">
         <v>123488</v>
@@ -6865,7 +6865,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="n">
-        <v>3.71222186088562</v>
+        <v>3.71222138404846</v>
       </c>
       <c r="H224" t="n">
         <v>81364</v>
@@ -6894,7 +6894,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="n">
-        <v>3.6150426864624</v>
+        <v>3.61504340171814</v>
       </c>
       <c r="H225" t="n">
         <v>166084</v>
@@ -6923,7 +6923,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="n">
-        <v>3.62059640884399</v>
+        <v>3.62059593200684</v>
       </c>
       <c r="H226" t="n">
         <v>137226</v>
@@ -6952,7 +6952,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="n">
-        <v>3.62614941596985</v>
+        <v>3.62614893913269</v>
       </c>
       <c r="H227" t="n">
         <v>55700</v>
@@ -7010,7 +7010,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="n">
-        <v>3.43179202079773</v>
+        <v>3.43179249763489</v>
       </c>
       <c r="H229" t="n">
         <v>391920</v>
@@ -7039,7 +7039,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="n">
-        <v>3.51508784294128</v>
+        <v>3.51508712768555</v>
       </c>
       <c r="H230" t="n">
         <v>158535</v>
@@ -7068,7 +7068,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="n">
-        <v>3.54007649421692</v>
+        <v>3.54007601737976</v>
       </c>
       <c r="H231" t="n">
         <v>177686</v>
@@ -7097,7 +7097,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="n">
-        <v>3.52896976470947</v>
+        <v>3.52897000312805</v>
       </c>
       <c r="H232" t="n">
         <v>53802</v>
@@ -7126,7 +7126,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="n">
-        <v>3.45400357246399</v>
+        <v>3.45400381088257</v>
       </c>
       <c r="H233" t="n">
         <v>47034</v>
@@ -7155,7 +7155,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="n">
-        <v>3.47066283226013</v>
+        <v>3.47066307067871</v>
       </c>
       <c r="H234" t="n">
         <v>111259</v>
@@ -7184,7 +7184,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="n">
-        <v>3.47621631622314</v>
+        <v>3.4762167930603</v>
       </c>
       <c r="H235" t="n">
         <v>66245</v>
@@ -7242,7 +7242,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="n">
-        <v>3.49842834472656</v>
+        <v>3.49842858314514</v>
       </c>
       <c r="H237" t="n">
         <v>59122</v>
@@ -7271,7 +7271,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="n">
-        <v>3.53174710273743</v>
+        <v>3.53174757957458</v>
       </c>
       <c r="H238" t="n">
         <v>110615</v>
@@ -7300,7 +7300,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="n">
-        <v>3.48732209205627</v>
+        <v>3.48732280731201</v>
       </c>
       <c r="H239" t="n">
         <v>109337</v>
@@ -7358,7 +7358,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="n">
-        <v>3.70389223098755</v>
+        <v>3.70389175415039</v>
       </c>
       <c r="H241" t="n">
         <v>121643</v>
@@ -7387,7 +7387,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="n">
-        <v>3.82050633430481</v>
+        <v>3.82050609588623</v>
       </c>
       <c r="H242" t="n">
         <v>97760</v>
@@ -7416,7 +7416,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="n">
-        <v>3.78718829154968</v>
+        <v>3.78718781471252</v>
       </c>
       <c r="H243" t="n">
         <v>135353</v>
@@ -7445,7 +7445,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="n">
-        <v>3.80384707450867</v>
+        <v>3.80384731292725</v>
       </c>
       <c r="H244" t="n">
         <v>97891</v>
@@ -7474,7 +7474,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G245" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H245" t="n">
         <v>194032</v>
@@ -7532,7 +7532,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G247" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H247" t="n">
         <v>110497</v>
@@ -7561,7 +7561,7 @@
         <v>6.41449880599976</v>
       </c>
       <c r="G248" t="n">
-        <v>3.8316125869751</v>
+        <v>3.83161234855652</v>
       </c>
       <c r="H248" t="n">
         <v>128189</v>
@@ -7590,7 +7590,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="n">
-        <v>3.92879056930542</v>
+        <v>3.92879104614258</v>
       </c>
       <c r="H249" t="n">
         <v>130892</v>
@@ -7619,7 +7619,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="n">
-        <v>3.90102624893188</v>
+        <v>3.90102577209473</v>
       </c>
       <c r="H250" t="n">
         <v>108027</v>
@@ -7648,7 +7648,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="n">
-        <v>3.98154473304749</v>
+        <v>3.98154544830322</v>
       </c>
       <c r="H251" t="n">
         <v>198595</v>
@@ -7677,7 +7677,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820470809937</v>
       </c>
       <c r="H252" t="n">
         <v>83758</v>
@@ -7706,7 +7706,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="n">
-        <v>3.98709750175476</v>
+        <v>3.98709845542908</v>
       </c>
       <c r="H253" t="n">
         <v>124841</v>
@@ -7735,7 +7735,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H254" t="n">
         <v>67846</v>
@@ -7764,7 +7764,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599244117737</v>
       </c>
       <c r="H255" t="n">
         <v>60629</v>
@@ -7793,7 +7793,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="n">
-        <v>3.99820423126221</v>
+        <v>3.99820470809937</v>
       </c>
       <c r="H256" t="n">
         <v>75406</v>
@@ -7822,7 +7822,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="n">
-        <v>4.02041673660278</v>
+        <v>4.02041721343994</v>
       </c>
       <c r="H257" t="n">
         <v>46248</v>
@@ -7880,7 +7880,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H259" t="n">
         <v>250610</v>
@@ -8025,7 +8025,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="n">
-        <v>4.18700838088989</v>
+        <v>4.18700885772705</v>
       </c>
       <c r="H264" t="n">
         <v>111880</v>
@@ -8054,7 +8054,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="n">
-        <v>4.19533824920654</v>
+        <v>4.19533681869507</v>
       </c>
       <c r="H265" t="n">
         <v>229274</v>
@@ -8170,7 +8170,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="n">
-        <v>4.11481857299805</v>
+        <v>4.11481809616089</v>
       </c>
       <c r="H269" t="n">
         <v>45733</v>
@@ -8257,7 +8257,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="n">
-        <v>4.1064887046814</v>
+        <v>4.10648918151855</v>
       </c>
       <c r="H272" t="n">
         <v>88527</v>
@@ -8286,7 +8286,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="n">
-        <v>4.07872438430786</v>
+        <v>4.0787239074707</v>
       </c>
       <c r="H273" t="n">
         <v>127436</v>
@@ -8373,7 +8373,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="n">
-        <v>3.91490864753723</v>
+        <v>3.91490888595581</v>
       </c>
       <c r="H276" t="n">
         <v>229142</v>
@@ -8402,7 +8402,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="n">
-        <v>3.95377945899963</v>
+        <v>3.95377969741821</v>
       </c>
       <c r="H277" t="n">
         <v>45852</v>
@@ -8489,7 +8489,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="n">
-        <v>3.95933294296265</v>
+        <v>3.95933318138123</v>
       </c>
       <c r="H280" t="n">
         <v>55134</v>
@@ -8518,7 +8518,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="n">
-        <v>3.8871431350708</v>
+        <v>3.88714289665222</v>
       </c>
       <c r="H281" t="n">
         <v>68408</v>
@@ -8547,7 +8547,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="n">
-        <v>3.9260139465332</v>
+        <v>3.92601418495178</v>
       </c>
       <c r="H282" t="n">
         <v>106269</v>
@@ -8576,7 +8576,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="n">
-        <v>3.90380334854126</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H283" t="n">
         <v>61425</v>
@@ -8605,7 +8605,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="n">
-        <v>3.90380334854126</v>
+        <v>3.90380239486694</v>
       </c>
       <c r="H284" t="n">
         <v>71158</v>
@@ -8634,7 +8634,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="n">
-        <v>3.97599220275879</v>
+        <v>3.97599244117737</v>
       </c>
       <c r="H285" t="n">
         <v>110096</v>
@@ -8721,7 +8721,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="n">
-        <v>4.07039356231689</v>
+        <v>4.07039403915405</v>
       </c>
       <c r="H288" t="n">
         <v>67876</v>
@@ -8750,7 +8750,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H289" t="n">
         <v>61110</v>
@@ -9011,7 +9011,7 @@
         <v>6.70268678665161</v>
       </c>
       <c r="G298" t="n">
-        <v>4.00375747680664</v>
+        <v>4.0037579536438</v>
       </c>
       <c r="H298" t="n">
         <v>298097</v>
@@ -9040,7 +9040,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="n">
-        <v>4.10926580429077</v>
+        <v>4.10926628112793</v>
       </c>
       <c r="H299" t="n">
         <v>223547</v>
@@ -9069,7 +9069,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H300" t="n">
         <v>617047</v>
@@ -9156,7 +9156,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="n">
-        <v>4.353600025177</v>
+        <v>4.35360050201416</v>
       </c>
       <c r="H303" t="n">
         <v>161681</v>
@@ -9185,7 +9185,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="n">
-        <v>4.31472873687744</v>
+        <v>4.3147292137146</v>
       </c>
       <c r="H304" t="n">
         <v>116065</v>
@@ -9243,7 +9243,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="n">
-        <v>4.37025880813599</v>
+        <v>4.37025928497314</v>
       </c>
       <c r="H306" t="n">
         <v>134817</v>
@@ -9330,7 +9330,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="n">
-        <v>4.22310256958008</v>
+        <v>4.22310304641724</v>
       </c>
       <c r="H309" t="n">
         <v>193013</v>
@@ -9359,7 +9359,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="n">
-        <v>4.28696393966675</v>
+        <v>4.28696298599243</v>
       </c>
       <c r="H310" t="n">
         <v>169658</v>
@@ -9388,7 +9388,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="n">
-        <v>4.30917596817017</v>
+        <v>4.30917549133301</v>
       </c>
       <c r="H311" t="n">
         <v>289755</v>
@@ -9417,7 +9417,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="n">
-        <v>4.43134260177612</v>
+        <v>4.43134307861328</v>
       </c>
       <c r="H312" t="n">
         <v>618378</v>
@@ -9446,7 +9446,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="n">
-        <v>4.46188545227051</v>
+        <v>4.46188497543335</v>
       </c>
       <c r="H313" t="n">
         <v>304602</v>
@@ -9475,7 +9475,7 @@
         <v>7.45569276809692</v>
       </c>
       <c r="G314" t="n">
-        <v>4.4535551071167</v>
+        <v>4.45355463027954</v>
       </c>
       <c r="H314" t="n">
         <v>193672</v>
@@ -9504,7 +9504,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="n">
-        <v>4.40913057327271</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H315" t="n">
         <v>158255</v>
@@ -9533,7 +9533,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G316" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H316" t="n">
         <v>367674</v>
@@ -9562,7 +9562,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351114273071</v>
       </c>
       <c r="H317" t="n">
         <v>460310</v>
@@ -9591,7 +9591,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="n">
-        <v>4.54240465164185</v>
+        <v>4.54240417480469</v>
       </c>
       <c r="H318" t="n">
         <v>245027</v>
@@ -9678,7 +9678,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G321" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H321" t="n">
         <v>141204</v>
@@ -9707,7 +9707,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="n">
-        <v>4.5535101890564</v>
+        <v>4.55351114273071</v>
       </c>
       <c r="H322" t="n">
         <v>95409</v>
@@ -9736,7 +9736,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="n">
-        <v>4.53962755203247</v>
+        <v>4.53962850570679</v>
       </c>
       <c r="H323" t="n">
         <v>188080</v>
@@ -9765,7 +9765,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="n">
-        <v>4.53685092926025</v>
+        <v>4.53685188293457</v>
       </c>
       <c r="H324" t="n">
         <v>98610</v>
@@ -9794,7 +9794,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G325" t="n">
-        <v>4.5257453918457</v>
+        <v>4.52574491500854</v>
       </c>
       <c r="H325" t="n">
         <v>265003</v>
@@ -9823,7 +9823,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G326" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H326" t="n">
         <v>200779</v>
@@ -9852,7 +9852,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G327" t="n">
-        <v>4.49797964096069</v>
+        <v>4.49798059463501</v>
       </c>
       <c r="H327" t="n">
         <v>109257</v>
@@ -9881,7 +9881,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="n">
-        <v>4.48132038116455</v>
+        <v>4.48132085800171</v>
       </c>
       <c r="H328" t="n">
         <v>165632</v>
@@ -9968,7 +9968,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="n">
-        <v>4.40913057327271</v>
+        <v>4.40913105010986</v>
       </c>
       <c r="H331" t="n">
         <v>186216</v>
@@ -9997,7 +9997,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="n">
-        <v>4.38691806793213</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H332" t="n">
         <v>206018</v>
@@ -10026,7 +10026,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="n">
-        <v>4.38691806793213</v>
+        <v>4.38691854476929</v>
       </c>
       <c r="H333" t="n">
         <v>196119</v>
@@ -10055,7 +10055,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="n">
-        <v>4.36748266220093</v>
+        <v>4.36748218536377</v>
       </c>
       <c r="H334" t="n">
         <v>175407</v>
@@ -10084,7 +10084,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="n">
-        <v>4.30362224578857</v>
+        <v>4.30362272262573</v>
       </c>
       <c r="H335" t="n">
         <v>151724</v>
@@ -10113,7 +10113,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="n">
-        <v>4.44244813919067</v>
+        <v>4.44244909286499</v>
       </c>
       <c r="H336" t="n">
         <v>246106</v>
@@ -10171,7 +10171,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="n">
-        <v>4.50075578689575</v>
+        <v>4.50075626373291</v>
       </c>
       <c r="H338" t="n">
         <v>185305</v>
@@ -10258,7 +10258,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="n">
-        <v>4.59793567657471</v>
+        <v>4.59793472290039</v>
       </c>
       <c r="H341" t="n">
         <v>312555</v>
@@ -10287,7 +10287,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="n">
-        <v>4.58127593994141</v>
+        <v>4.58127546310425</v>
       </c>
       <c r="H342" t="n">
         <v>62152</v>
@@ -10374,7 +10374,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="n">
-        <v>4.65346574783325</v>
+        <v>4.65346622467041</v>
       </c>
       <c r="H345" t="n">
         <v>177286</v>
@@ -10403,7 +10403,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="n">
-        <v>4.75342082977295</v>
+        <v>4.75342035293579</v>
       </c>
       <c r="H346" t="n">
         <v>342741</v>
@@ -10432,7 +10432,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="n">
-        <v>4.77563381195068</v>
+        <v>4.77563333511353</v>
       </c>
       <c r="H347" t="n">
         <v>352359</v>
@@ -10490,7 +10490,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H349" t="n">
         <v>172083</v>
@@ -10548,7 +10548,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="n">
-        <v>4.84782314300537</v>
+        <v>4.84782361984253</v>
       </c>
       <c r="H351" t="n">
         <v>122329</v>
@@ -10577,7 +10577,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="n">
-        <v>4.72010278701782</v>
+        <v>4.72010231018066</v>
       </c>
       <c r="H352" t="n">
         <v>291161</v>
@@ -10954,7 +10954,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315853118896</v>
       </c>
       <c r="H365" t="n">
         <v>146539</v>
@@ -10983,7 +10983,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H366" t="n">
         <v>77359</v>
@@ -11070,7 +11070,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H369" t="n">
         <v>54213</v>
@@ -11128,7 +11128,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="n">
-        <v>4.76734161376953</v>
+        <v>4.76734256744385</v>
       </c>
       <c r="H371" t="n">
         <v>59047</v>
@@ -11157,7 +11157,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H372" t="n">
         <v>148350</v>
@@ -11186,7 +11186,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="n">
-        <v>4.71571016311646</v>
+        <v>4.71570920944214</v>
       </c>
       <c r="H373" t="n">
         <v>190474</v>
@@ -11215,7 +11215,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="n">
-        <v>4.684157371521</v>
+        <v>4.68415689468384</v>
       </c>
       <c r="H374" t="n">
         <v>257849</v>
@@ -11244,7 +11244,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="n">
-        <v>4.62965726852417</v>
+        <v>4.62965679168701</v>
       </c>
       <c r="H375" t="n">
         <v>145512</v>
@@ -11273,7 +11273,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="n">
-        <v>4.62965726852417</v>
+        <v>4.62965679168701</v>
       </c>
       <c r="H376" t="n">
         <v>155173</v>
@@ -11302,7 +11302,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="n">
-        <v>4.60384082794189</v>
+        <v>4.60384130477905</v>
       </c>
       <c r="H377" t="n">
         <v>76641</v>
@@ -11360,7 +11360,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="n">
-        <v>4.61818265914917</v>
+        <v>4.61818313598633</v>
       </c>
       <c r="H379" t="n">
         <v>135778</v>
@@ -11389,7 +11389,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="n">
-        <v>4.61818265914917</v>
+        <v>4.61818313598633</v>
       </c>
       <c r="H380" t="n">
         <v>65236</v>
@@ -11505,7 +11505,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="n">
-        <v>4.42312908172607</v>
+        <v>4.42312955856323</v>
       </c>
       <c r="H384" t="n">
         <v>90869</v>
@@ -11534,7 +11534,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="n">
-        <v>4.45468282699585</v>
+        <v>4.45468235015869</v>
       </c>
       <c r="H385" t="n">
         <v>104028</v>
@@ -11563,7 +11563,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="n">
-        <v>4.53786754608154</v>
+        <v>4.53786706924438</v>
       </c>
       <c r="H386" t="n">
         <v>105901</v>
@@ -11592,7 +11592,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="n">
-        <v>4.55507802963257</v>
+        <v>4.55507850646973</v>
       </c>
       <c r="H387" t="n">
         <v>112131</v>
@@ -11621,7 +11621,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="n">
-        <v>4.47476196289062</v>
+        <v>4.47476148605347</v>
       </c>
       <c r="H388" t="n">
         <v>139029</v>
@@ -11650,7 +11650,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="n">
-        <v>4.56081438064575</v>
+        <v>4.56081390380859</v>
       </c>
       <c r="H389" t="n">
         <v>61346</v>
@@ -11708,7 +11708,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="n">
-        <v>4.684157371521</v>
+        <v>4.68415689468384</v>
       </c>
       <c r="H391" t="n">
         <v>162812</v>
@@ -11737,7 +11737,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="n">
-        <v>4.66120958328247</v>
+        <v>4.66121006011963</v>
       </c>
       <c r="H392" t="n">
         <v>102329</v>
@@ -11766,7 +11766,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H393" t="n">
         <v>165524</v>
@@ -11853,7 +11853,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H396" t="n">
         <v>93726</v>
@@ -11911,7 +11911,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="n">
-        <v>4.79315805435181</v>
+        <v>4.79315853118896</v>
       </c>
       <c r="H398" t="n">
         <v>177747</v>
@@ -11998,7 +11998,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H401" t="n">
         <v>142867</v>
@@ -12056,7 +12056,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H403" t="n">
         <v>128308</v>
@@ -12114,7 +12114,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="n">
-        <v>4.73292112350464</v>
+        <v>4.73292064666748</v>
       </c>
       <c r="H405" t="n">
         <v>130388</v>
@@ -12143,7 +12143,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H406" t="n">
         <v>170600</v>
@@ -12172,7 +12172,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857833862305</v>
       </c>
       <c r="H407" t="n">
         <v>123210</v>
@@ -12201,7 +12201,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="n">
-        <v>4.71857881546021</v>
+        <v>4.71857833862305</v>
       </c>
       <c r="H408" t="n">
         <v>135862</v>
@@ -12230,7 +12230,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="n">
-        <v>4.79602670669556</v>
+        <v>4.7960262298584</v>
       </c>
       <c r="H409" t="n">
         <v>386315</v>
@@ -12259,7 +12259,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="n">
-        <v>4.82757949829102</v>
+        <v>4.82757902145386</v>
       </c>
       <c r="H410" t="n">
         <v>233195</v>
@@ -12288,7 +12288,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="n">
-        <v>4.87634229660034</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H411" t="n">
         <v>129788</v>
@@ -12375,7 +12375,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="n">
-        <v>4.75586843490601</v>
+        <v>4.75586795806885</v>
       </c>
       <c r="H414" t="n">
         <v>223989</v>
@@ -12404,7 +12404,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="n">
-        <v>4.81036901473999</v>
+        <v>4.81036853790283</v>
       </c>
       <c r="H415" t="n">
         <v>168442</v>
@@ -12433,7 +12433,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H416" t="n">
         <v>400107</v>
@@ -12491,7 +12491,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="n">
-        <v>4.93084335327148</v>
+        <v>4.93084287643433</v>
       </c>
       <c r="H418" t="n">
         <v>170401</v>
@@ -12578,7 +12578,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H421" t="n">
         <v>72335</v>
@@ -12607,7 +12607,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="n">
-        <v>4.93371105194092</v>
+        <v>4.93371152877808</v>
       </c>
       <c r="H422" t="n">
         <v>38701</v>
@@ -12636,7 +12636,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="n">
-        <v>4.91650056838989</v>
+        <v>4.91650104522705</v>
       </c>
       <c r="H423" t="n">
         <v>34375</v>
@@ -12665,7 +12665,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H424" t="n">
         <v>42823</v>
@@ -12694,7 +12694,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.85052633285522</v>
+        <v>4.85052680969238</v>
       </c>
       <c r="H425" t="n">
         <v>172662</v>
@@ -12723,7 +12723,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H426" t="n">
         <v>53465</v>
@@ -12810,7 +12810,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="n">
-        <v>4.86200046539307</v>
+        <v>4.86199998855591</v>
       </c>
       <c r="H429" t="n">
         <v>34336</v>
@@ -12839,7 +12839,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="n">
-        <v>4.87634229660034</v>
+        <v>4.8763427734375</v>
       </c>
       <c r="H430" t="n">
         <v>81300</v>
@@ -12868,7 +12868,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="n">
-        <v>4.81897354125977</v>
+        <v>4.81897401809692</v>
       </c>
       <c r="H431" t="n">
         <v>59100</v>
@@ -12897,7 +12897,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="n">
-        <v>4.81897354125977</v>
+        <v>4.81897401809692</v>
       </c>
       <c r="H432" t="n">
         <v>85576</v>
@@ -12955,7 +12955,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="n">
-        <v>4.88781690597534</v>
+        <v>4.88781642913818</v>
       </c>
       <c r="H434" t="n">
         <v>180331</v>
@@ -12984,7 +12984,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="n">
-        <v>4.9566593170166</v>
+        <v>4.95665884017944</v>
       </c>
       <c r="H435" t="n">
         <v>201090</v>
@@ -13129,7 +13129,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="n">
-        <v>5.05418634414673</v>
+        <v>5.05418539047241</v>
       </c>
       <c r="H440" t="n">
         <v>88520</v>
@@ -13158,7 +13158,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="n">
-        <v>5.01402807235718</v>
+        <v>5.01402759552002</v>
       </c>
       <c r="H441" t="n">
         <v>64746</v>
@@ -13187,7 +13187,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="n">
-        <v>4.99107980728149</v>
+        <v>4.99108028411865</v>
       </c>
       <c r="H442" t="n">
         <v>93886</v>
@@ -13216,7 +13216,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H443" t="n">
         <v>69536</v>
@@ -13245,7 +13245,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="n">
-        <v>5.00255298614502</v>
+        <v>5.00255393981934</v>
       </c>
       <c r="H444" t="n">
         <v>82992</v>
@@ -13274,7 +13274,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="n">
-        <v>4.97673749923706</v>
+        <v>4.97673845291138</v>
       </c>
       <c r="H445" t="n">
         <v>104775</v>
@@ -13303,7 +13303,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="n">
-        <v>5.02550172805786</v>
+        <v>5.02550220489502</v>
       </c>
       <c r="H446" t="n">
         <v>100760</v>
@@ -13361,7 +13361,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="n">
-        <v>5.06279134750366</v>
+        <v>5.06279039382935</v>
       </c>
       <c r="H448" t="n">
         <v>73261</v>
@@ -13419,7 +13419,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="n">
-        <v>5.06279134750366</v>
+        <v>5.06279039382935</v>
       </c>
       <c r="H450" t="n">
         <v>80452</v>
@@ -13448,7 +13448,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="n">
-        <v>5.07713317871094</v>
+        <v>5.0771336555481</v>
       </c>
       <c r="H451" t="n">
         <v>127366</v>
@@ -13506,7 +13506,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="n">
-        <v>4.96813249588013</v>
+        <v>4.96813297271729</v>
       </c>
       <c r="H453" t="n">
         <v>121584</v>
@@ -13564,7 +13564,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="n">
-        <v>5.03123807907104</v>
+        <v>5.03123760223389</v>
       </c>
       <c r="H455" t="n">
         <v>77579</v>
@@ -13622,7 +13622,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="n">
-        <v>5.16318607330322</v>
+        <v>5.16318655014038</v>
       </c>
       <c r="H457" t="n">
         <v>184063</v>
@@ -13651,7 +13651,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="n">
-        <v>5.24923896789551</v>
+        <v>5.24923944473267</v>
       </c>
       <c r="H458" t="n">
         <v>199889</v>
@@ -13738,7 +13738,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H461" t="n">
         <v>90087</v>
@@ -13767,7 +13767,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="n">
-        <v>5.27792358398438</v>
+        <v>5.27792310714722</v>
       </c>
       <c r="H462" t="n">
         <v>293930</v>
@@ -13796,7 +13796,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="n">
-        <v>5.27505493164062</v>
+        <v>5.27505540847778</v>
       </c>
       <c r="H463" t="n">
         <v>137784</v>
@@ -13825,7 +13825,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="n">
-        <v>5.36397743225098</v>
+        <v>5.36397695541382</v>
       </c>
       <c r="H464" t="n">
         <v>416344</v>
@@ -13883,7 +13883,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266157150269</v>
       </c>
       <c r="H466" t="n">
         <v>156702</v>
@@ -13970,7 +13970,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="n">
-        <v>5.54755687713623</v>
+        <v>5.54755735397339</v>
       </c>
       <c r="H469" t="n">
         <v>346414</v>
@@ -13999,7 +13999,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="n">
-        <v>5.69384717941284</v>
+        <v>5.69384813308716</v>
       </c>
       <c r="H470" t="n">
         <v>1020120</v>
@@ -14028,7 +14028,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H471" t="n">
         <v>456989</v>
@@ -14086,7 +14086,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="n">
-        <v>5.97208595275879</v>
+        <v>5.97208642959595</v>
       </c>
       <c r="H473" t="n">
         <v>582524</v>
@@ -14144,7 +14144,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H475" t="n">
         <v>361115</v>
@@ -14202,7 +14202,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="n">
-        <v>5.82292699813843</v>
+        <v>5.82292604446411</v>
       </c>
       <c r="H477" t="n">
         <v>320356</v>
@@ -14231,7 +14231,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="n">
-        <v>5.90898036956787</v>
+        <v>5.90897989273071</v>
       </c>
       <c r="H478" t="n">
         <v>447808</v>
@@ -14347,7 +14347,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H482" t="n">
         <v>514848</v>
@@ -14376,7 +14376,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="n">
-        <v>6.12124395370483</v>
+        <v>6.12124347686768</v>
       </c>
       <c r="H483" t="n">
         <v>340121</v>
@@ -14405,7 +14405,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H484" t="n">
         <v>197193</v>
@@ -14434,7 +14434,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="n">
-        <v>5.96061134338379</v>
+        <v>5.96061182022095</v>
       </c>
       <c r="H485" t="n">
         <v>214159</v>
@@ -14463,7 +14463,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="n">
-        <v>6.17287635803223</v>
+        <v>6.17287540435791</v>
       </c>
       <c r="H486" t="n">
         <v>406962</v>
@@ -14521,7 +14521,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="n">
-        <v>6.10977077484131</v>
+        <v>6.10977029800415</v>
       </c>
       <c r="H488" t="n">
         <v>152139</v>
@@ -14579,7 +14579,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="n">
-        <v>6.24171876907349</v>
+        <v>6.24171829223633</v>
       </c>
       <c r="H490" t="n">
         <v>199304</v>
@@ -14608,7 +14608,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="n">
-        <v>6.19008588790894</v>
+        <v>6.19008684158325</v>
       </c>
       <c r="H491" t="n">
         <v>234121</v>
@@ -14666,7 +14666,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="n">
-        <v>6.02371692657471</v>
+        <v>6.02371740341187</v>
       </c>
       <c r="H493" t="n">
         <v>167344</v>
@@ -14695,7 +14695,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="n">
-        <v>6.06961154937744</v>
+        <v>6.0696120262146</v>
       </c>
       <c r="H494" t="n">
         <v>134266</v>
@@ -14811,7 +14811,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="n">
-        <v>6.36793041229248</v>
+        <v>6.36793088912964</v>
       </c>
       <c r="H498" t="n">
         <v>358977</v>
@@ -14840,7 +14840,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="n">
-        <v>6.35645580291748</v>
+        <v>6.3564567565918</v>
       </c>
       <c r="H499" t="n">
         <v>283557</v>
@@ -14869,7 +14869,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="n">
-        <v>6.48266649246216</v>
+        <v>6.48266792297363</v>
       </c>
       <c r="H500" t="n">
         <v>169190</v>
@@ -14898,7 +14898,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="n">
-        <v>6.48266649246216</v>
+        <v>6.48266792297363</v>
       </c>
       <c r="H501" t="n">
         <v>258499</v>
@@ -14927,7 +14927,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="n">
-        <v>6.42529916763306</v>
+        <v>6.42529773712158</v>
       </c>
       <c r="H502" t="n">
         <v>210048</v>
@@ -15043,7 +15043,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="n">
-        <v>5.56476736068726</v>
+        <v>5.56476783752441</v>
       </c>
       <c r="H506" t="n">
         <v>358726</v>
@@ -15072,7 +15072,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="n">
-        <v>5.60492610931396</v>
+        <v>5.60492515563965</v>
       </c>
       <c r="H507" t="n">
         <v>138334</v>
@@ -15130,7 +15130,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="n">
-        <v>5.53608322143555</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H509" t="n">
         <v>190384</v>
@@ -15188,7 +15188,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="n">
-        <v>5.53034687042236</v>
+        <v>5.53034639358521</v>
       </c>
       <c r="H511" t="n">
         <v>118130</v>
@@ -15217,7 +15217,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="n">
-        <v>5.52460908889771</v>
+        <v>5.52460861206055</v>
       </c>
       <c r="H512" t="n">
         <v>137903</v>
@@ -15246,7 +15246,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="n">
-        <v>5.56476736068726</v>
+        <v>5.56476783752441</v>
       </c>
       <c r="H513" t="n">
         <v>146003</v>
@@ -15275,7 +15275,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="n">
-        <v>5.6508207321167</v>
+        <v>5.65082025527954</v>
       </c>
       <c r="H514" t="n">
         <v>122075</v>
@@ -15333,7 +15333,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70818948745728</v>
+        <v>5.70818996429443</v>
       </c>
       <c r="H516" t="n">
         <v>147363</v>
@@ -15391,7 +15391,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="n">
-        <v>5.71966314315796</v>
+        <v>5.71966361999512</v>
       </c>
       <c r="H518" t="n">
         <v>305356</v>
@@ -15420,7 +15420,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="n">
-        <v>5.55903100967407</v>
+        <v>5.55903053283691</v>
       </c>
       <c r="H519" t="n">
         <v>232788</v>
@@ -15449,7 +15449,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="n">
-        <v>5.50739812850952</v>
+        <v>5.50739860534668</v>
       </c>
       <c r="H520" t="n">
         <v>204669</v>
@@ -15507,7 +15507,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H522" t="n">
         <v>131888</v>
@@ -15565,7 +15565,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="n">
-        <v>5.50739812850952</v>
+        <v>5.50739860534668</v>
       </c>
       <c r="H524" t="n">
         <v>112539</v>
@@ -15594,7 +15594,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="n">
-        <v>5.50739812850952</v>
+        <v>5.50739860534668</v>
       </c>
       <c r="H525" t="n">
         <v>136487</v>
@@ -15623,7 +15623,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="n">
-        <v>5.53608322143555</v>
+        <v>5.53608274459839</v>
       </c>
       <c r="H526" t="n">
         <v>224626</v>
@@ -15652,7 +15652,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="n">
-        <v>5.55329322814941</v>
+        <v>5.55329370498657</v>
       </c>
       <c r="H527" t="n">
         <v>178839</v>
@@ -15681,7 +15681,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="n">
-        <v>5.495924949646</v>
+        <v>5.49592542648315</v>
       </c>
       <c r="H528" t="n">
         <v>109874</v>
@@ -15710,7 +15710,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="n">
-        <v>5.47871446609497</v>
+        <v>5.47871398925781</v>
       </c>
       <c r="H529" t="n">
         <v>108597</v>
@@ -15739,7 +15739,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="n">
-        <v>5.50739812850952</v>
+        <v>5.50739860534668</v>
       </c>
       <c r="H530" t="n">
         <v>94275</v>
@@ -15768,7 +15768,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="n">
-        <v>5.46150398254395</v>
+        <v>5.46150350570679</v>
       </c>
       <c r="H531" t="n">
         <v>150985</v>
@@ -15797,7 +15797,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="n">
-        <v>5.31234502792358</v>
+        <v>5.31234550476074</v>
       </c>
       <c r="H532" t="n">
         <v>243466</v>
@@ -15826,7 +15826,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="n">
-        <v>5.39266109466553</v>
+        <v>5.39266157150269</v>
       </c>
       <c r="H533" t="n">
         <v>107752</v>
@@ -15884,7 +15884,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="n">
-        <v>5.15171194076538</v>
+        <v>5.15171241760254</v>
       </c>
       <c r="H535" t="n">
         <v>131851</v>
@@ -15913,7 +15913,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="n">
-        <v>5.03123807907104</v>
+        <v>5.03123760223389</v>
       </c>
       <c r="H536" t="n">
         <v>159220</v>
@@ -15942,7 +15942,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="n">
-        <v>4.97386932373047</v>
+        <v>4.97386884689331</v>
       </c>
       <c r="H537" t="n">
         <v>233015</v>
@@ -15971,7 +15971,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="n">
-        <v>5.12302875518799</v>
+        <v>5.12302827835083</v>
       </c>
       <c r="H538" t="n">
         <v>107280</v>
@@ -16145,7 +16145,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="n">
-        <v>4.6755518913269</v>
+        <v>4.67555236816406</v>
       </c>
       <c r="H544" t="n">
         <v>158012</v>
@@ -16232,7 +16232,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="n">
-        <v>4.77307844161987</v>
+        <v>4.77307891845703</v>
       </c>
       <c r="H547" t="n">
         <v>100189</v>
@@ -16261,7 +16261,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="n">
-        <v>4.68128871917725</v>
+        <v>4.6812891960144</v>
       </c>
       <c r="H548" t="n">
         <v>251480</v>
@@ -16319,7 +16319,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="n">
-        <v>4.71571016311646</v>
+        <v>4.71570920944214</v>
       </c>
       <c r="H550" t="n">
         <v>314139</v>
@@ -16348,7 +16348,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="n">
-        <v>4.58949851989746</v>
+        <v>4.58949899673462</v>
       </c>
       <c r="H551" t="n">
         <v>187834</v>
@@ -16377,7 +16377,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="n">
-        <v>4.62564086914062</v>
+        <v>4.62564134597778</v>
       </c>
       <c r="H552" t="n">
         <v>201959</v>
@@ -16435,7 +16435,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="n">
-        <v>4.42657136917114</v>
+        <v>4.4265718460083</v>
       </c>
       <c r="H554" t="n">
         <v>163330</v>
@@ -16464,7 +16464,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="n">
-        <v>4.31986665725708</v>
+        <v>4.31986618041992</v>
       </c>
       <c r="H555" t="n">
         <v>182195</v>
@@ -16493,7 +16493,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="n">
-        <v>4.31126022338867</v>
+        <v>4.31126070022583</v>
       </c>
       <c r="H556" t="n">
         <v>191054</v>
@@ -16522,7 +16522,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="n">
-        <v>4.37149715423584</v>
+        <v>4.371497631073</v>
       </c>
       <c r="H557" t="n">
         <v>224606</v>
@@ -16551,7 +16551,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="n">
-        <v>4.50057697296143</v>
+        <v>4.50057744979858</v>
       </c>
       <c r="H558" t="n">
         <v>119113</v>
@@ -16580,7 +16580,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="n">
-        <v>4.50401973724365</v>
+        <v>4.50401878356934</v>
       </c>
       <c r="H559" t="n">
         <v>186947</v>
@@ -16609,7 +16609,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="n">
-        <v>4.39444541931152</v>
+        <v>4.39444494247437</v>
       </c>
       <c r="H560" t="n">
         <v>218932</v>
@@ -16696,7 +16696,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="n">
-        <v>4.25675964355469</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H563" t="n">
         <v>136013</v>
@@ -16754,7 +16754,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="n">
-        <v>4.14775991439819</v>
+        <v>4.14775943756104</v>
       </c>
       <c r="H565" t="n">
         <v>280816</v>
@@ -16812,7 +16812,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="n">
-        <v>4.3078179359436</v>
+        <v>4.30781841278076</v>
       </c>
       <c r="H567" t="n">
         <v>181767</v>
@@ -16841,7 +16841,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="n">
-        <v>4.28544473648071</v>
+        <v>4.28544425964355</v>
       </c>
       <c r="H568" t="n">
         <v>215982</v>
@@ -16928,7 +16928,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="n">
-        <v>4.41232681274414</v>
+        <v>4.4123272895813</v>
       </c>
       <c r="H571" t="n">
         <v>1211216</v>
@@ -16986,7 +16986,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="n">
-        <v>4.92329359054565</v>
+        <v>4.9232931137085</v>
       </c>
       <c r="H573" t="n">
         <v>1058195</v>
@@ -17015,7 +17015,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="n">
-        <v>4.68262004852295</v>
+        <v>4.68262052536011</v>
       </c>
       <c r="H574" t="n">
         <v>630734</v>
@@ -17044,7 +17044,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="n">
-        <v>4.78259181976318</v>
+        <v>4.7825927734375</v>
       </c>
       <c r="H575" t="n">
         <v>785969</v>
@@ -17102,7 +17102,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="n">
-        <v>5.15902805328369</v>
+        <v>5.15902853012085</v>
       </c>
       <c r="H577" t="n">
         <v>736664</v>
@@ -17160,7 +17160,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="n">
-        <v>4.99549531936646</v>
+        <v>4.9954948425293</v>
       </c>
       <c r="H579" t="n">
         <v>881747</v>
@@ -17218,7 +17218,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="n">
-        <v>4.79493474960327</v>
+        <v>4.79493379592896</v>
       </c>
       <c r="H581" t="n">
         <v>391338</v>
@@ -17247,7 +17247,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="n">
-        <v>4.87454175949097</v>
+        <v>4.87454080581665</v>
       </c>
       <c r="H582" t="n">
         <v>274280</v>
@@ -17305,7 +17305,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="n">
-        <v>4.77086687088013</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H584" t="n">
         <v>346291</v>
@@ -17334,7 +17334,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="n">
-        <v>4.85479402542114</v>
+        <v>4.85479354858398</v>
       </c>
       <c r="H585" t="n">
         <v>306793</v>
@@ -17421,7 +17421,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84924030303955</v>
+        <v>4.84923934936523</v>
       </c>
       <c r="H588" t="n">
         <v>752626</v>
@@ -17566,7 +17566,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="n">
-        <v>4.75235366821289</v>
+        <v>4.75235414505005</v>
       </c>
       <c r="H593" t="n">
         <v>307986</v>
@@ -17624,7 +17624,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="n">
-        <v>4.84862327575684</v>
+        <v>4.84862279891968</v>
       </c>
       <c r="H595" t="n">
         <v>284775</v>
@@ -17682,7 +17682,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.84430313110352</v>
+        <v>4.84430265426636</v>
       </c>
       <c r="H597" t="n">
         <v>183693</v>
@@ -17740,7 +17740,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>4.88132905960083</v>
+        <v>4.88132953643799</v>
       </c>
       <c r="H599" t="n">
         <v>300176</v>
@@ -17827,7 +17827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.06029033660889</v>
+        <v>5.06029081344604</v>
       </c>
       <c r="H602" t="n">
         <v>586567</v>
@@ -17914,7 +17914,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>4.80357360839844</v>
+        <v>4.80357313156128</v>
       </c>
       <c r="H605" t="n">
         <v>567119</v>
@@ -17943,7 +17943,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="n">
-        <v>4.77086687088013</v>
+        <v>4.77086734771729</v>
       </c>
       <c r="H606" t="n">
         <v>413652</v>
@@ -17972,7 +17972,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="n">
-        <v>4.59684276580811</v>
+        <v>4.59684181213379</v>
       </c>
       <c r="H607" t="n">
         <v>613084</v>
@@ -18059,7 +18059,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="n">
-        <v>4.5666036605835</v>
+        <v>4.56660413742065</v>
       </c>
       <c r="H610" t="n">
         <v>544954</v>
@@ -18088,7 +18088,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="n">
-        <v>4.54870796203613</v>
+        <v>4.54870700836182</v>
       </c>
       <c r="H611" t="n">
         <v>252215</v>
@@ -18175,7 +18175,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="n">
-        <v>4.17473983764648</v>
+        <v>4.1747407913208</v>
       </c>
       <c r="H614" t="n">
         <v>685007</v>
@@ -18291,7 +18291,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="n">
-        <v>4.56290149688721</v>
+        <v>4.56290197372437</v>
       </c>
       <c r="H618" t="n">
         <v>282682</v>
@@ -18494,7 +18494,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="n">
-        <v>4.71716594696045</v>
+        <v>4.71716547012329</v>
       </c>
       <c r="H625" t="n">
         <v>188411</v>
@@ -18523,7 +18523,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="n">
-        <v>4.80870866775513</v>
+        <v>4.80870962142944</v>
       </c>
       <c r="H626" t="n">
         <v>203531</v>
@@ -18552,7 +18552,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="n">
-        <v>4.8544807434082</v>
+        <v>4.85448122024536</v>
       </c>
       <c r="H627" t="n">
         <v>274204</v>
@@ -18639,7 +18639,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="n">
-        <v>4.59311628341675</v>
+        <v>4.59311676025391</v>
       </c>
       <c r="H630" t="n">
         <v>231415</v>
@@ -18784,7 +18784,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="n">
-        <v>4.56061220169067</v>
+        <v>4.56061172485352</v>
       </c>
       <c r="H635" t="n">
         <v>364336</v>
@@ -18813,7 +18813,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="n">
-        <v>4.60373067855835</v>
+        <v>4.60373020172119</v>
       </c>
       <c r="H636" t="n">
         <v>261556</v>
@@ -18842,7 +18842,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="n">
-        <v>4.56525564193726</v>
+        <v>4.56525611877441</v>
       </c>
       <c r="H637" t="n">
         <v>293870</v>
@@ -18871,7 +18871,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="n">
-        <v>4.67470979690552</v>
+        <v>4.67471027374268</v>
       </c>
       <c r="H638" t="n">
         <v>310832</v>
@@ -18900,7 +18900,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H639" t="n">
         <v>277774</v>
@@ -18958,7 +18958,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="n">
-        <v>4.60174036026001</v>
+        <v>4.60173988342285</v>
       </c>
       <c r="H641" t="n">
         <v>160144</v>
@@ -19016,7 +19016,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="n">
-        <v>4.80273866653442</v>
+        <v>4.80273818969727</v>
       </c>
       <c r="H643" t="n">
         <v>189484</v>
@@ -19132,7 +19132,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="n">
-        <v>4.68930387496948</v>
+        <v>4.68930435180664</v>
       </c>
       <c r="H647" t="n">
         <v>52795</v>
@@ -19161,7 +19161,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="n">
-        <v>4.72711610794067</v>
+        <v>4.72711563110352</v>
       </c>
       <c r="H648" t="n">
         <v>124423</v>
@@ -19190,7 +19190,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="n">
-        <v>4.76094722747803</v>
+        <v>4.76094675064087</v>
       </c>
       <c r="H649" t="n">
         <v>201117</v>
@@ -19248,7 +19248,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="n">
-        <v>4.87637186050415</v>
+        <v>4.87637233734131</v>
       </c>
       <c r="H651" t="n">
         <v>272806</v>
@@ -19277,7 +19277,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="n">
-        <v>4.78681802749634</v>
+        <v>4.7868185043335</v>
       </c>
       <c r="H652" t="n">
         <v>248174</v>
@@ -19335,7 +19335,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="n">
-        <v>4.81666994094849</v>
+        <v>4.81666898727417</v>
       </c>
       <c r="H654" t="n">
         <v>190438</v>
@@ -19393,7 +19393,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="n">
-        <v>4.8093729019165</v>
+        <v>4.80937242507935</v>
       </c>
       <c r="H656" t="n">
         <v>107726</v>
@@ -19422,7 +19422,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="n">
-        <v>4.68134355545044</v>
+        <v>4.6813440322876</v>
       </c>
       <c r="H657" t="n">
         <v>218824</v>
@@ -19480,7 +19480,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="n">
-        <v>4.79676914215088</v>
+        <v>4.79676866531372</v>
       </c>
       <c r="H659" t="n">
         <v>207399</v>
@@ -19509,7 +19509,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="n">
-        <v>4.76492691040039</v>
+        <v>4.76492738723755</v>
       </c>
       <c r="H660" t="n">
         <v>90031</v>
@@ -19538,7 +19538,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="n">
-        <v>4.74369955062866</v>
+        <v>4.74370002746582</v>
       </c>
       <c r="H661" t="n">
         <v>212597</v>
@@ -19596,7 +19596,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="n">
-        <v>4.59776020050049</v>
+        <v>4.59776067733765</v>
       </c>
       <c r="H663" t="n">
         <v>123007</v>
@@ -19625,7 +19625,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="n">
-        <v>4.618323802948</v>
+        <v>4.61832427978516</v>
       </c>
       <c r="H664" t="n">
         <v>65498</v>
@@ -19712,7 +19712,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="n">
-        <v>4.50621604919434</v>
+        <v>4.50621652603149</v>
       </c>
       <c r="H667" t="n">
         <v>158816</v>
@@ -19741,7 +19741,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="n">
-        <v>4.41997957229614</v>
+        <v>4.41997909545898</v>
       </c>
       <c r="H668" t="n">
         <v>131656</v>
@@ -19799,7 +19799,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="n">
-        <v>4.30588150024414</v>
+        <v>4.30588102340698</v>
       </c>
       <c r="H670" t="n">
         <v>224367</v>
@@ -19857,7 +19857,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="n">
-        <v>4.360276222229</v>
+        <v>4.36027717590332</v>
       </c>
       <c r="H672" t="n">
         <v>84392</v>
@@ -19886,7 +19886,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="n">
-        <v>4.44386005401611</v>
+        <v>4.44386053085327</v>
       </c>
       <c r="H673" t="n">
         <v>124244</v>
@@ -19915,7 +19915,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="n">
-        <v>4.43589973449707</v>
+        <v>4.43590021133423</v>
       </c>
       <c r="H674" t="n">
         <v>75809</v>
@@ -19944,7 +19944,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="n">
-        <v>4.3702278137207</v>
+        <v>4.37022686004639</v>
       </c>
       <c r="H675" t="n">
         <v>98634</v>
@@ -19973,7 +19973,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H676" t="n">
         <v>76513</v>
@@ -20002,7 +20002,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H677" t="n">
         <v>51262</v>
@@ -20060,7 +20060,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41135597229004</v>
+        <v>4.41135549545288</v>
       </c>
       <c r="H679" t="n">
         <v>86398</v>
@@ -20089,7 +20089,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="n">
-        <v>4.39211797714233</v>
+        <v>4.39211750030518</v>
       </c>
       <c r="H680" t="n">
         <v>166661</v>
@@ -20176,7 +20176,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="n">
-        <v>4.33241510391235</v>
+        <v>4.33241558074951</v>
       </c>
       <c r="H683" t="n">
         <v>70783</v>
@@ -20263,7 +20263,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="n">
-        <v>4.37089014053345</v>
+        <v>4.37089061737061</v>
       </c>
       <c r="H686" t="n">
         <v>63252</v>
@@ -20292,7 +20292,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="n">
-        <v>4.37818717956543</v>
+        <v>4.37818765640259</v>
       </c>
       <c r="H687" t="n">
         <v>314279</v>
@@ -20321,7 +20321,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>4.3516526222229</v>
+        <v>4.35165309906006</v>
       </c>
       <c r="H688" t="n">
         <v>96748</v>
@@ -20408,7 +20408,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="n">
-        <v>4.31981182098389</v>
+        <v>4.31981134414673</v>
       </c>
       <c r="H691" t="n">
         <v>143038</v>
@@ -20437,7 +20437,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="n">
-        <v>4.61567163467407</v>
+        <v>4.61567068099976</v>
       </c>
       <c r="H692" t="n">
         <v>604065</v>
@@ -20698,7 +20698,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="n">
-        <v>4.39012861251831</v>
+        <v>4.39012765884399</v>
       </c>
       <c r="H701" t="n">
         <v>153681</v>
@@ -20727,7 +20727,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="n">
-        <v>4.34966325759888</v>
+        <v>4.34966278076172</v>
       </c>
       <c r="H702" t="n">
         <v>84918</v>
@@ -20785,7 +20785,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H704" t="n">
         <v>120717</v>
@@ -20843,7 +20843,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="n">
-        <v>4.17984294891357</v>
+        <v>4.17984199523926</v>
       </c>
       <c r="H706" t="n">
         <v>112296</v>
@@ -20872,7 +20872,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="n">
-        <v>4.07370471954346</v>
+        <v>4.0737042427063</v>
       </c>
       <c r="H707" t="n">
         <v>234307</v>
@@ -20901,7 +20901,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>4.05645751953125</v>
+        <v>4.05645656585693</v>
       </c>
       <c r="H708" t="n">
         <v>219320</v>
@@ -20930,7 +20930,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="n">
-        <v>4.01599216461182</v>
+        <v>4.01599168777466</v>
       </c>
       <c r="H709" t="n">
         <v>198493</v>
@@ -20959,7 +20959,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="n">
-        <v>3.92312097549438</v>
+        <v>3.92312145233154</v>
       </c>
       <c r="H710" t="n">
         <v>281423</v>
@@ -20988,7 +20988,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="n">
-        <v>3.94899225234985</v>
+        <v>3.94899272918701</v>
       </c>
       <c r="H711" t="n">
         <v>223508</v>
@@ -21017,7 +21017,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>3.84749794006348</v>
+        <v>3.8474977016449</v>
       </c>
       <c r="H712" t="n">
         <v>189134</v>
@@ -21046,7 +21046,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="n">
-        <v>3.91648769378662</v>
+        <v>3.91648745536804</v>
       </c>
       <c r="H713" t="n">
         <v>179781</v>
@@ -21104,7 +21104,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="n">
-        <v>3.9072003364563</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H715" t="n">
         <v>154260</v>
@@ -21133,7 +21133,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="n">
-        <v>3.91051745414734</v>
+        <v>3.91051697731018</v>
       </c>
       <c r="H716" t="n">
         <v>111436</v>
@@ -21162,7 +21162,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="n">
-        <v>3.96026921272278</v>
+        <v>3.96026968955994</v>
       </c>
       <c r="H717" t="n">
         <v>50070</v>
@@ -21191,7 +21191,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>3.94700193405151</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H718" t="n">
         <v>149820</v>
@@ -21220,7 +21220,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="n">
-        <v>3.94434881210327</v>
+        <v>3.94434928894043</v>
       </c>
       <c r="H719" t="n">
         <v>130093</v>
@@ -21249,7 +21249,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>3.94700193405151</v>
+        <v>3.94700241088867</v>
       </c>
       <c r="H720" t="n">
         <v>47658</v>
@@ -21307,7 +21307,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H722" t="n">
         <v>119608</v>
@@ -21336,7 +21336,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H723" t="n">
         <v>51535</v>
@@ -21365,7 +21365,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473415374756</v>
       </c>
       <c r="H724" t="n">
         <v>227117</v>
@@ -21394,7 +21394,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="n">
-        <v>4.14601039886475</v>
+        <v>4.14601135253906</v>
       </c>
       <c r="H725" t="n">
         <v>144073</v>
@@ -21510,7 +21510,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.21234703063965</v>
+        <v>4.21234655380249</v>
       </c>
       <c r="H729" t="n">
         <v>153600</v>
@@ -21568,7 +21568,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="n">
-        <v>4.12544631958008</v>
+        <v>4.12544679641724</v>
       </c>
       <c r="H731" t="n">
         <v>143878</v>
@@ -21626,7 +21626,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="n">
-        <v>4.04716968536377</v>
+        <v>4.04717016220093</v>
       </c>
       <c r="H733" t="n">
         <v>135061</v>
@@ -21655,7 +21655,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="n">
-        <v>3.98215985298157</v>
+        <v>3.98216080665588</v>
       </c>
       <c r="H734" t="n">
         <v>67397</v>
@@ -21742,7 +21742,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="n">
-        <v>3.94766545295715</v>
+        <v>3.94766616821289</v>
       </c>
       <c r="H737" t="n">
         <v>105830</v>
@@ -21771,7 +21771,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="n">
-        <v>3.89061641693115</v>
+        <v>3.89061665534973</v>
       </c>
       <c r="H738" t="n">
         <v>78191</v>
@@ -21800,7 +21800,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="n">
-        <v>3.89260721206665</v>
+        <v>3.89260697364807</v>
       </c>
       <c r="H739" t="n">
         <v>160586</v>
@@ -21829,7 +21829,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="n">
-        <v>3.91184425354004</v>
+        <v>3.91184401512146</v>
       </c>
       <c r="H740" t="n">
         <v>58482</v>
@@ -21887,7 +21887,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07503080368042</v>
+        <v>4.07503128051758</v>
       </c>
       <c r="H742" t="n">
         <v>132743</v>
@@ -21945,7 +21945,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="n">
-        <v>4.05115032196045</v>
+        <v>4.05114984512329</v>
       </c>
       <c r="H744" t="n">
         <v>56164</v>
@@ -22003,7 +22003,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="n">
-        <v>3.96889328956604</v>
+        <v>3.96889305114746</v>
       </c>
       <c r="H746" t="n">
         <v>145833</v>
@@ -22032,7 +22032,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>3.90189337730408</v>
+        <v>3.9018931388855</v>
       </c>
       <c r="H747" t="n">
         <v>215638</v>
@@ -22061,7 +22061,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="n">
-        <v>3.9072003364563</v>
+        <v>3.90720057487488</v>
       </c>
       <c r="H748" t="n">
         <v>102007</v>
@@ -22090,7 +22090,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="n">
-        <v>3.88730025291443</v>
+        <v>3.88729977607727</v>
       </c>
       <c r="H749" t="n">
         <v>111448</v>
@@ -22119,7 +22119,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="n">
-        <v>3.85214233398438</v>
+        <v>3.85214161872864</v>
       </c>
       <c r="H750" t="n">
         <v>141352</v>
@@ -22148,7 +22148,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="n">
-        <v>3.85811138153076</v>
+        <v>3.85811185836792</v>
       </c>
       <c r="H751" t="n">
         <v>63514</v>
@@ -22177,7 +22177,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="n">
-        <v>3.82361698150635</v>
+        <v>3.82361674308777</v>
       </c>
       <c r="H752" t="n">
         <v>90932</v>
@@ -22206,7 +22206,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="n">
-        <v>3.74998378753662</v>
+        <v>3.7499840259552</v>
       </c>
       <c r="H753" t="n">
         <v>184870</v>
@@ -22235,7 +22235,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="n">
-        <v>3.84219121932983</v>
+        <v>3.84219169616699</v>
       </c>
       <c r="H754" t="n">
         <v>195412</v>
@@ -22293,7 +22293,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="n">
-        <v>3.73737955093384</v>
+        <v>3.737380027771</v>
       </c>
       <c r="H756" t="n">
         <v>138294</v>
@@ -22380,7 +22380,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="n">
-        <v>3.56490612030029</v>
+        <v>3.56490635871887</v>
       </c>
       <c r="H759" t="n">
         <v>317061</v>
@@ -22409,7 +22409,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="n">
-        <v>3.60205411911011</v>
+        <v>3.60205388069153</v>
       </c>
       <c r="H760" t="n">
         <v>153511</v>
@@ -22438,7 +22438,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59741044044495</v>
+        <v>3.59741067886353</v>
       </c>
       <c r="H761" t="n">
         <v>232177</v>
@@ -22496,7 +22496,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="n">
-        <v>3.57021260261536</v>
+        <v>3.57021284103394</v>
       </c>
       <c r="H763" t="n">
         <v>158919</v>
@@ -22583,7 +22583,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="n">
-        <v>3.85280537605286</v>
+        <v>3.85280513763428</v>
       </c>
       <c r="H766" t="n">
         <v>126158</v>
@@ -22641,7 +22641,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="n">
-        <v>3.9198043346405</v>
+        <v>3.91980457305908</v>
       </c>
       <c r="H768" t="n">
         <v>165370</v>
@@ -22699,7 +22699,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="n">
-        <v>3.92444801330566</v>
+        <v>3.92444753646851</v>
       </c>
       <c r="H770" t="n">
         <v>82861</v>
@@ -22728,7 +22728,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="n">
-        <v>3.90056681632996</v>
+        <v>3.90056705474854</v>
       </c>
       <c r="H771" t="n">
         <v>149636</v>
@@ -22786,7 +22786,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="n">
-        <v>3.81565690040588</v>
+        <v>3.81565713882446</v>
       </c>
       <c r="H773" t="n">
         <v>122612</v>
@@ -22815,7 +22815,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="n">
-        <v>3.8985767364502</v>
+        <v>3.89857721328735</v>
       </c>
       <c r="H774" t="n">
         <v>192350</v>
@@ -22844,7 +22844,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="n">
-        <v>3.88000273704529</v>
+        <v>3.88000249862671</v>
       </c>
       <c r="H775" t="n">
         <v>157597</v>
@@ -22931,7 +22931,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="n">
-        <v>3.83025050163269</v>
+        <v>3.83025097846985</v>
       </c>
       <c r="H778" t="n">
         <v>123544</v>
@@ -22960,7 +22960,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="n">
-        <v>3.92842841148376</v>
+        <v>3.92842817306519</v>
       </c>
       <c r="H779" t="n">
         <v>186851</v>
@@ -23047,7 +23047,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="n">
-        <v>4.16657495498657</v>
+        <v>4.16657447814941</v>
       </c>
       <c r="H782" t="n">
         <v>250025</v>
@@ -23076,7 +23076,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="n">
-        <v>4.13805055618286</v>
+        <v>4.1380500793457</v>
       </c>
       <c r="H783" t="n">
         <v>122859</v>
@@ -23105,7 +23105,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="n">
-        <v>4.13937711715698</v>
+        <v>4.13937664031982</v>
       </c>
       <c r="H784" t="n">
         <v>119629</v>
@@ -23134,7 +23134,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="n">
-        <v>4.10090208053589</v>
+        <v>4.10090255737305</v>
       </c>
       <c r="H785" t="n">
         <v>161482</v>
@@ -23192,7 +23192,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>4.11947679519653</v>
+        <v>4.11947584152222</v>
       </c>
       <c r="H787" t="n">
         <v>103841</v>
@@ -23221,7 +23221,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.11284255981445</v>
+        <v>4.11284303665161</v>
       </c>
       <c r="H788" t="n">
         <v>160837</v>
@@ -23250,7 +23250,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="n">
-        <v>4.092942237854</v>
+        <v>4.09294176101685</v>
       </c>
       <c r="H789" t="n">
         <v>263354</v>
@@ -23279,7 +23279,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="n">
-        <v>3.99078392982483</v>
+        <v>3.99078369140625</v>
       </c>
       <c r="H790" t="n">
         <v>256263</v>
@@ -23308,7 +23308,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="n">
-        <v>3.91118025779724</v>
+        <v>3.91118121147156</v>
       </c>
       <c r="H791" t="n">
         <v>263702</v>
@@ -23366,7 +23366,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="n">
-        <v>3.94567561149597</v>
+        <v>3.94567584991455</v>
       </c>
       <c r="H793" t="n">
         <v>513739</v>
@@ -23395,7 +23395,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="n">
-        <v>3.98680424690247</v>
+        <v>3.98680377006531</v>
       </c>
       <c r="H794" t="n">
         <v>129600</v>
@@ -23511,7 +23511,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="n">
-        <v>4.070387840271</v>
+        <v>4.07038688659668</v>
       </c>
       <c r="H798" t="n">
         <v>126559</v>
@@ -23569,7 +23569,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="n">
-        <v>4.01665496826172</v>
+        <v>4.01665544509888</v>
       </c>
       <c r="H800" t="n">
         <v>103894</v>
@@ -23598,7 +23598,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="n">
-        <v>4.0710506439209</v>
+        <v>4.07105112075806</v>
       </c>
       <c r="H801" t="n">
         <v>96510</v>
@@ -23627,7 +23627,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="n">
-        <v>4.13407039642334</v>
+        <v>4.13406991958618</v>
       </c>
       <c r="H802" t="n">
         <v>101135</v>
@@ -23656,7 +23656,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="n">
-        <v>4.19178247451782</v>
+        <v>4.19178295135498</v>
       </c>
       <c r="H803" t="n">
         <v>306156</v>
@@ -23685,7 +23685,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="n">
-        <v>4.10421848297119</v>
+        <v>4.10421943664551</v>
       </c>
       <c r="H804" t="n">
         <v>271028</v>
@@ -23714,7 +23714,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="n">
-        <v>4.1347336769104</v>
+        <v>4.13473415374756</v>
       </c>
       <c r="H805" t="n">
         <v>290799</v>
@@ -23743,7 +23743,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="n">
-        <v>4.18448638916016</v>
+        <v>4.184485912323</v>
       </c>
       <c r="H806" t="n">
         <v>224566</v>
@@ -23888,7 +23888,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="n">
-        <v>4.27138614654541</v>
+        <v>4.27138662338257</v>
       </c>
       <c r="H811" t="n">
         <v>155654</v>
@@ -23917,7 +23917,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.28531646728516</v>
+        <v>4.28531742095947</v>
       </c>
       <c r="H812" t="n">
         <v>82775</v>
@@ -23946,7 +23946,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="n">
-        <v>4.29195070266724</v>
+        <v>4.29195022583008</v>
       </c>
       <c r="H813" t="n">
         <v>178878</v>
@@ -24033,7 +24033,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="n">
-        <v>4.44717741012573</v>
+        <v>4.44717693328857</v>
       </c>
       <c r="H816" t="n">
         <v>261217</v>
@@ -24062,7 +24062,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="n">
-        <v>4.49759292602539</v>
+        <v>4.49759244918823</v>
       </c>
       <c r="H817" t="n">
         <v>195962</v>
@@ -24120,7 +24120,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="n">
-        <v>4.41002893447876</v>
+        <v>4.4100284576416</v>
       </c>
       <c r="H819" t="n">
         <v>92629</v>
@@ -24149,7 +24149,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="n">
-        <v>4.41069221496582</v>
+        <v>4.41069269180298</v>
       </c>
       <c r="H820" t="n">
         <v>59197</v>
@@ -24178,7 +24178,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="n">
-        <v>4.34900045394897</v>
+        <v>4.34899950027466</v>
       </c>
       <c r="H821" t="n">
         <v>196343</v>
@@ -24236,7 +24236,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="n">
-        <v>4.26408958435059</v>
+        <v>4.26408910751343</v>
       </c>
       <c r="H823" t="n">
         <v>139907</v>
@@ -24381,7 +24381,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>4.3649206161499</v>
+        <v>4.36492013931274</v>
       </c>
       <c r="H828" t="n">
         <v>60554</v>
@@ -24468,7 +24468,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.41798877716064</v>
+        <v>4.4179892539978</v>
       </c>
       <c r="H831" t="n">
         <v>94151</v>
@@ -24526,7 +24526,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>4.29858446121216</v>
+        <v>4.298583984375</v>
       </c>
       <c r="H833" t="n">
         <v>159721</v>
@@ -24555,7 +24555,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32511901855469</v>
+        <v>4.32511806488037</v>
       </c>
       <c r="H834" t="n">
         <v>246478</v>
@@ -24584,7 +24584,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="n">
-        <v>4.37155342102051</v>
+        <v>4.37155389785767</v>
       </c>
       <c r="H835" t="n">
         <v>103376</v>
@@ -24613,7 +24613,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>4.40472221374512</v>
+        <v>4.40472173690796</v>
       </c>
       <c r="H836" t="n">
         <v>75933</v>
@@ -24671,7 +24671,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H838" t="n">
         <v>224598</v>
@@ -24758,7 +24758,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="n">
-        <v>4.45779085159302</v>
+        <v>4.45779132843018</v>
       </c>
       <c r="H841" t="n">
         <v>100477</v>
@@ -24845,7 +24845,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="n">
-        <v>4.41135597229004</v>
+        <v>4.41135549545288</v>
       </c>
       <c r="H844" t="n">
         <v>71545</v>
@@ -24874,7 +24874,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H845" t="n">
         <v>105374</v>
@@ -24903,7 +24903,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H846" t="n">
         <v>104980</v>
@@ -24932,7 +24932,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H847" t="n">
         <v>116029</v>
@@ -24961,7 +24961,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="n">
-        <v>4.47769117355347</v>
+        <v>4.47769165039062</v>
       </c>
       <c r="H848" t="n">
         <v>96863</v>
@@ -25077,7 +25077,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.33838558197021</v>
+        <v>4.33838605880737</v>
       </c>
       <c r="H852" t="n">
         <v>375070</v>
@@ -25135,7 +25135,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="n">
-        <v>4.39199781417847</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H854" t="n">
         <v>242614</v>
@@ -25280,7 +25280,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G859" t="n">
-        <v>4.52835035324097</v>
+        <v>4.52834987640381</v>
       </c>
       <c r="H859" t="n">
         <v>185427</v>
@@ -25309,7 +25309,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G860" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140970230103</v>
       </c>
       <c r="H860" t="n">
         <v>106622</v>
@@ -25338,7 +25338,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G861" t="n">
-        <v>4.549880027771</v>
+        <v>4.54987955093384</v>
       </c>
       <c r="H861" t="n">
         <v>64262</v>
@@ -25396,7 +25396,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G863" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H863" t="n">
         <v>56929</v>
@@ -25425,7 +25425,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G864" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H864" t="n">
         <v>67638</v>
@@ -25483,7 +25483,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G866" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H866" t="n">
         <v>83940</v>
@@ -25512,7 +25512,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G867" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H867" t="n">
         <v>45354</v>
@@ -25599,7 +25599,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G870" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H870" t="n">
         <v>116258</v>
@@ -25744,7 +25744,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G875" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H875" t="n">
         <v>68064</v>
@@ -26034,7 +26034,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H885" t="n">
         <v>158011</v>
@@ -26063,7 +26063,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H886" t="n">
         <v>115183</v>
@@ -26092,7 +26092,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H887" t="n">
         <v>184524</v>
@@ -26237,7 +26237,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G892" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H892" t="n">
         <v>101125</v>
@@ -26266,7 +26266,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="n">
-        <v>4.39199781417847</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H893" t="n">
         <v>56380</v>
@@ -26324,7 +26324,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G895" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H895" t="n">
         <v>65595</v>
@@ -26353,7 +26353,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H896" t="n">
         <v>44767</v>
@@ -26469,7 +26469,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G900" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H900" t="n">
         <v>82729</v>
@@ -26527,7 +26527,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>4.32740926742554</v>
+        <v>4.3274097442627</v>
       </c>
       <c r="H902" t="n">
         <v>66350</v>
@@ -26556,7 +26556,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H903" t="n">
         <v>213241</v>
@@ -26614,7 +26614,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H905" t="n">
         <v>82085</v>
@@ -26672,7 +26672,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G907" t="n">
-        <v>4.24846839904785</v>
+        <v>4.24846792221069</v>
       </c>
       <c r="H907" t="n">
         <v>62908</v>
@@ -26701,7 +26701,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G908" t="n">
-        <v>4.23411512374878</v>
+        <v>4.23411560058594</v>
       </c>
       <c r="H908" t="n">
         <v>58990</v>
@@ -26759,7 +26759,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H910" t="n">
         <v>110250</v>
@@ -26788,7 +26788,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G911" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H911" t="n">
         <v>121403</v>
@@ -26846,7 +26846,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G913" t="n">
-        <v>4.09776210784912</v>
+        <v>4.09776258468628</v>
       </c>
       <c r="H913" t="n">
         <v>213477</v>
@@ -26875,7 +26875,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G914" t="n">
-        <v>4.05470371246338</v>
+        <v>4.05470323562622</v>
       </c>
       <c r="H914" t="n">
         <v>180985</v>
@@ -26904,7 +26904,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G915" t="n">
-        <v>4.04752683639526</v>
+        <v>4.04752635955811</v>
       </c>
       <c r="H915" t="n">
         <v>117109</v>
@@ -26933,7 +26933,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G916" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H916" t="n">
         <v>220296</v>
@@ -26962,7 +26962,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G917" t="n">
-        <v>3.99011564254761</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H917" t="n">
         <v>142499</v>
@@ -26991,7 +26991,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H918" t="n">
         <v>243157</v>
@@ -27020,7 +27020,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G919" t="n">
-        <v>3.8824679851532</v>
+        <v>3.88246870040894</v>
       </c>
       <c r="H919" t="n">
         <v>159908</v>
@@ -27049,7 +27049,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>3.79635119438171</v>
+        <v>3.79635071754456</v>
       </c>
       <c r="H920" t="n">
         <v>329655</v>
@@ -27136,7 +27136,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G923" t="n">
-        <v>3.81787967681885</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H923" t="n">
         <v>149116</v>
@@ -27194,7 +27194,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H925" t="n">
         <v>84785</v>
@@ -27223,7 +27223,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H926" t="n">
         <v>73998</v>
@@ -27252,7 +27252,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G927" t="n">
-        <v>3.79635119438171</v>
+        <v>3.79635071754456</v>
       </c>
       <c r="H927" t="n">
         <v>109743</v>
@@ -27281,7 +27281,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.78199791908264</v>
+        <v>3.78199768066406</v>
       </c>
       <c r="H928" t="n">
         <v>42652</v>
@@ -27339,7 +27339,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G930" t="n">
-        <v>3.81787967681885</v>
+        <v>3.81788039207458</v>
       </c>
       <c r="H930" t="n">
         <v>183973</v>
@@ -27368,7 +27368,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.83940935134888</v>
+        <v>3.83940887451172</v>
       </c>
       <c r="H931" t="n">
         <v>200773</v>
@@ -27426,7 +27426,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G933" t="n">
-        <v>3.8752920627594</v>
+        <v>3.87529182434082</v>
       </c>
       <c r="H933" t="n">
         <v>162454</v>
@@ -27455,7 +27455,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G934" t="n">
-        <v>3.84658646583557</v>
+        <v>3.84658575057983</v>
       </c>
       <c r="H934" t="n">
         <v>135055</v>
@@ -27484,7 +27484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G935" t="n">
-        <v>3.90399742126465</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H935" t="n">
         <v>187953</v>
@@ -27600,7 +27600,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G939" t="n">
-        <v>4.04035043716431</v>
+        <v>4.04035091400146</v>
       </c>
       <c r="H939" t="n">
         <v>113996</v>
@@ -27629,7 +27629,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H940" t="n">
         <v>133834</v>
@@ -27658,7 +27658,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G941" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H941" t="n">
         <v>174524</v>
@@ -27716,7 +27716,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H943" t="n">
         <v>182425</v>
@@ -27745,7 +27745,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G944" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H944" t="n">
         <v>193559</v>
@@ -27803,7 +27803,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G946" t="n">
-        <v>4.02599811553955</v>
+        <v>4.02599763870239</v>
       </c>
       <c r="H946" t="n">
         <v>137576</v>
@@ -27832,7 +27832,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H947" t="n">
         <v>147938</v>
@@ -27861,7 +27861,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>3.98293924331665</v>
+        <v>3.98293876647949</v>
       </c>
       <c r="H948" t="n">
         <v>118564</v>
@@ -27890,7 +27890,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>3.9614098072052</v>
+        <v>3.96140956878662</v>
       </c>
       <c r="H949" t="n">
         <v>84704</v>
@@ -27919,7 +27919,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H950" t="n">
         <v>104322</v>
@@ -27977,7 +27977,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G952" t="n">
-        <v>3.99011564254761</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H952" t="n">
         <v>71762</v>
@@ -28006,7 +28006,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G953" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H953" t="n">
         <v>89858</v>
@@ -28035,7 +28035,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G954" t="n">
-        <v>4.01164531707764</v>
+        <v>4.01164484024048</v>
       </c>
       <c r="H954" t="n">
         <v>113185</v>
@@ -28064,7 +28064,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G955" t="n">
-        <v>3.89682126045227</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H955" t="n">
         <v>198731</v>
@@ -28122,7 +28122,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G957" t="n">
-        <v>3.96858549118042</v>
+        <v>3.96858596801758</v>
       </c>
       <c r="H957" t="n">
         <v>70802</v>
@@ -28209,7 +28209,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>3.99011564254761</v>
+        <v>3.99011516571045</v>
       </c>
       <c r="H960" t="n">
         <v>112689</v>
@@ -28238,7 +28238,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G961" t="n">
-        <v>4.03317403793335</v>
+        <v>4.03317356109619</v>
       </c>
       <c r="H961" t="n">
         <v>76598</v>
@@ -28325,7 +28325,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G964" t="n">
-        <v>4.17670392990112</v>
+        <v>4.17670345306396</v>
       </c>
       <c r="H964" t="n">
         <v>184280</v>
@@ -28441,7 +28441,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>4.11211538314819</v>
+        <v>4.11211490631104</v>
       </c>
       <c r="H968" t="n">
         <v>76571</v>
@@ -28499,7 +28499,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H970" t="n">
         <v>117936</v>
@@ -28528,7 +28528,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H971" t="n">
         <v>154145</v>
@@ -28557,7 +28557,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H972" t="n">
         <v>134175</v>
@@ -28586,7 +28586,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G973" t="n">
-        <v>4.14799785614014</v>
+        <v>4.14799737930298</v>
       </c>
       <c r="H973" t="n">
         <v>63185</v>
@@ -28673,7 +28673,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G976" t="n">
-        <v>4.13364458084106</v>
+        <v>4.13364505767822</v>
       </c>
       <c r="H976" t="n">
         <v>91697</v>
@@ -28818,7 +28818,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H981" t="n">
         <v>169971</v>
@@ -28876,7 +28876,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G983" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H983" t="n">
         <v>94635</v>
@@ -28934,7 +28934,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G985" t="n">
-        <v>4.28434991836548</v>
+        <v>4.28435039520264</v>
       </c>
       <c r="H985" t="n">
         <v>162590</v>
@@ -28992,7 +28992,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>4.27717399597168</v>
+        <v>4.27717351913452</v>
       </c>
       <c r="H987" t="n">
         <v>69784</v>
@@ -29021,7 +29021,7 @@
         <v>6</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H988" t="n">
         <v>135917</v>
@@ -29050,7 +29050,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G989" t="n">
-        <v>4.35611486434937</v>
+        <v>4.35611534118652</v>
       </c>
       <c r="H989" t="n">
         <v>138068</v>
@@ -29166,7 +29166,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G993" t="n">
-        <v>4.29870367050171</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H993" t="n">
         <v>45492</v>
@@ -29195,7 +29195,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>4.39199781417847</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H994" t="n">
         <v>199251</v>
@@ -29224,7 +29224,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H995" t="n">
         <v>358111</v>
@@ -29311,7 +29311,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G998" t="n">
-        <v>4.53552675247192</v>
+        <v>4.53552722930908</v>
       </c>
       <c r="H998" t="n">
         <v>278924</v>
@@ -29398,7 +29398,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1001" t="n">
         <v>134768</v>
@@ -29427,7 +29427,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1002" t="n">
         <v>62344</v>
@@ -29485,7 +29485,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1004" t="n">
         <v>58554</v>
@@ -29543,7 +29543,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H1006" t="n">
         <v>100264</v>
@@ -29978,7 +29978,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.43505620956421</v>
+        <v>4.43505573272705</v>
       </c>
       <c r="H1021" t="n">
         <v>186708</v>
@@ -30181,7 +30181,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1028" t="n">
         <v>79009</v>
@@ -30413,7 +30413,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.39917421340942</v>
+        <v>4.39917373657227</v>
       </c>
       <c r="H1036" t="n">
         <v>110854</v>
@@ -30442,7 +30442,7 @@
         <v>6</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.30587959289551</v>
+        <v>4.30588006973267</v>
       </c>
       <c r="H1037" t="n">
         <v>183171</v>
@@ -30471,7 +30471,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.29870367050171</v>
+        <v>4.29870319366455</v>
       </c>
       <c r="H1038" t="n">
         <v>161115</v>
@@ -30500,7 +30500,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.39199781417847</v>
+        <v>4.39199733734131</v>
       </c>
       <c r="H1039" t="n">
         <v>164564</v>
@@ -30645,7 +30645,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.49246788024902</v>
+        <v>4.49246835708618</v>
       </c>
       <c r="H1044" t="n">
         <v>130372</v>
@@ -30674,7 +30674,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.50682067871094</v>
+        <v>4.5068211555481</v>
       </c>
       <c r="H1045" t="n">
         <v>167360</v>
@@ -30732,7 +30732,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.49964475631714</v>
+        <v>4.49964427947998</v>
       </c>
       <c r="H1047" t="n">
         <v>186654</v>
@@ -30790,7 +30790,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.55705595016479</v>
+        <v>4.55705642700195</v>
       </c>
       <c r="H1049" t="n">
         <v>136339</v>
@@ -30819,7 +30819,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.57140922546387</v>
+        <v>4.57140970230103</v>
       </c>
       <c r="H1050" t="n">
         <v>112242</v>
@@ -30848,7 +30848,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.52117443084717</v>
+        <v>4.52117395401001</v>
       </c>
       <c r="H1051" t="n">
         <v>126242</v>
@@ -30906,7 +30906,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.19823265075684</v>
+        <v>4.19823312759399</v>
       </c>
       <c r="H1053" t="n">
         <v>645418</v>
@@ -30964,7 +30964,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.16952705383301</v>
+        <v>4.16952753067017</v>
       </c>
       <c r="H1055" t="n">
         <v>321443</v>
@@ -31022,7 +31022,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.90399742126465</v>
+        <v>3.90399789810181</v>
       </c>
       <c r="H1057" t="n">
         <v>651281</v>
@@ -31051,7 +31051,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.89682126045227</v>
+        <v>3.89682149887085</v>
       </c>
       <c r="H1058" t="n">
         <v>494611</v>
@@ -31138,7 +31138,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.82505679130554</v>
+        <v>3.82505631446838</v>
       </c>
       <c r="H1061" t="n">
         <v>188804</v>
@@ -31167,7 +31167,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.78917407989502</v>
+        <v>3.7891743183136</v>
       </c>
       <c r="H1062" t="n">
         <v>297718</v>
@@ -31254,7 +31254,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.25811576843262</v>
+        <v>3.25811553001404</v>
       </c>
       <c r="H1065" t="n">
         <v>364873</v>
@@ -31283,7 +31283,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.62299847602844</v>
+        <v>2.62299823760986</v>
       </c>
       <c r="H1066" t="n">
         <v>700650</v>
@@ -31312,7 +31312,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.66605710983276</v>
+        <v>2.66605734825134</v>
       </c>
       <c r="H1067" t="n">
         <v>497765</v>
@@ -31341,7 +31341,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.450763463974</v>
+        <v>2.45076322555542</v>
       </c>
       <c r="H1068" t="n">
         <v>502127</v>
@@ -31370,7 +31370,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1069" t="n">
         <v>316624</v>
@@ -31399,7 +31399,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1070" t="n">
         <v>294654</v>
@@ -31457,7 +31457,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.67682194709778</v>
+        <v>2.67682218551636</v>
       </c>
       <c r="H1072" t="n">
         <v>1041965</v>
@@ -31515,7 +31515,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.78446888923645</v>
+        <v>2.78446912765503</v>
       </c>
       <c r="H1074" t="n">
         <v>219271</v>
@@ -31573,7 +31573,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.73423361778259</v>
+        <v>2.73423385620117</v>
       </c>
       <c r="H1076" t="n">
         <v>156770</v>
@@ -31602,7 +31602,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.72705698013306</v>
+        <v>2.72705721855164</v>
       </c>
       <c r="H1077" t="n">
         <v>193039</v>
@@ -31660,7 +31660,7 @@
         <v>3.75</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.69117474555969</v>
+        <v>2.69117498397827</v>
       </c>
       <c r="H1079" t="n">
         <v>342391</v>
@@ -31747,7 +31747,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.60505747795105</v>
+        <v>2.60505723953247</v>
       </c>
       <c r="H1082" t="n">
         <v>90176</v>
@@ -31776,7 +31776,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1083" t="n">
         <v>180927</v>
@@ -31863,7 +31863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.64093971252441</v>
+        <v>2.64093947410583</v>
       </c>
       <c r="H1086" t="n">
         <v>261581</v>
@@ -31979,7 +31979,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.56917476654053</v>
+        <v>2.56917500495911</v>
       </c>
       <c r="H1090" t="n">
         <v>129379</v>
@@ -32066,7 +32066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329300880432</v>
       </c>
       <c r="H1093" t="n">
         <v>139451</v>
@@ -32095,7 +32095,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1094" t="n">
         <v>108032</v>
@@ -32182,7 +32182,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1097" t="n">
         <v>180573</v>
@@ -32298,7 +32298,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1101" t="n">
         <v>130098</v>
@@ -32327,7 +32327,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.54046893119812</v>
+        <v>2.5404691696167</v>
       </c>
       <c r="H1102" t="n">
         <v>82440</v>
@@ -32356,7 +32356,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1103" t="n">
         <v>141432</v>
@@ -32414,7 +32414,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1105" t="n">
         <v>149130</v>
@@ -32443,7 +32443,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.36823415756226</v>
+        <v>2.36823391914368</v>
       </c>
       <c r="H1106" t="n">
         <v>326150</v>
@@ -32472,7 +32472,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.33952808380127</v>
+        <v>2.33952784538269</v>
       </c>
       <c r="H1107" t="n">
         <v>248569</v>
@@ -32530,7 +32530,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.31799864768982</v>
+        <v>2.3179988861084</v>
       </c>
       <c r="H1109" t="n">
         <v>123243</v>
@@ -32559,7 +32559,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.48305749893188</v>
+        <v>2.48305726051331</v>
       </c>
       <c r="H1110" t="n">
         <v>311033</v>
@@ -32588,7 +32588,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.38258671760559</v>
+        <v>2.38258695602417</v>
       </c>
       <c r="H1111" t="n">
         <v>243942</v>
@@ -32675,7 +32675,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.17805743217468</v>
+        <v>2.17805767059326</v>
       </c>
       <c r="H1114" t="n">
         <v>231502</v>
@@ -32733,7 +32733,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.36105751991272</v>
+        <v>2.36105728149414</v>
       </c>
       <c r="H1116" t="n">
         <v>277343</v>
@@ -32762,7 +32762,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.30005741119385</v>
+        <v>2.30005764961243</v>
       </c>
       <c r="H1117" t="n">
         <v>282326</v>
@@ -32791,7 +32791,7 @@
         <v>3.25</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.33235144615173</v>
+        <v>2.33235168457031</v>
       </c>
       <c r="H1118" t="n">
         <v>359504</v>
@@ -32820,7 +32820,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.32876348495483</v>
+        <v>2.32876324653625</v>
       </c>
       <c r="H1119" t="n">
         <v>437387</v>
@@ -32849,7 +32849,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.35388112068176</v>
+        <v>2.35388088226318</v>
       </c>
       <c r="H1120" t="n">
         <v>213833</v>
@@ -32965,7 +32965,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.68040990829468</v>
+        <v>2.68041014671326</v>
       </c>
       <c r="H1124" t="n">
         <v>901153</v>
@@ -32994,7 +32994,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81317496299744</v>
+        <v>2.81317520141602</v>
       </c>
       <c r="H1125" t="n">
         <v>470004</v>
@@ -33052,7 +33052,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.60864567756653</v>
+        <v>2.60864520072937</v>
       </c>
       <c r="H1127" t="n">
         <v>417942</v>
@@ -33081,7 +33081,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1128" t="n">
         <v>348708</v>
@@ -33139,7 +33139,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1130" t="n">
         <v>287875</v>
@@ -33168,7 +33168,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1131" t="n">
         <v>310297</v>
@@ -33197,7 +33197,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56199860572815</v>
+        <v>2.56199836730957</v>
       </c>
       <c r="H1132" t="n">
         <v>158723</v>
@@ -33226,7 +33226,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.54764556884766</v>
+        <v>2.54764580726624</v>
       </c>
       <c r="H1133" t="n">
         <v>139107</v>
@@ -33255,7 +33255,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.4543514251709</v>
+        <v>2.45435166358948</v>
       </c>
       <c r="H1134" t="n">
         <v>433647</v>
@@ -33284,7 +33284,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.46511626243591</v>
+        <v>2.46511602401733</v>
       </c>
       <c r="H1135" t="n">
         <v>163840</v>
@@ -33342,7 +33342,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.411292552948</v>
+        <v>2.41129279136658</v>
       </c>
       <c r="H1137" t="n">
         <v>197688</v>
@@ -33400,7 +33400,7 @@
         <v>3.375</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.42205715179443</v>
+        <v>2.42205739021301</v>
       </c>
       <c r="H1139" t="n">
         <v>98220</v>
@@ -33429,7 +33429,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.49382209777832</v>
+        <v>2.49382185935974</v>
       </c>
       <c r="H1140" t="n">
         <v>92813</v>
@@ -33458,7 +33458,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1141" t="n">
         <v>205219</v>
@@ -33574,7 +33574,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.51535153388977</v>
+        <v>2.51535129547119</v>
       </c>
       <c r="H1145" t="n">
         <v>166481</v>
@@ -33748,7 +33748,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.53329253196716</v>
+        <v>2.53329300880432</v>
       </c>
       <c r="H1151" t="n">
         <v>202010</v>
@@ -33835,7 +33835,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.56917476654053</v>
+        <v>2.56917500495911</v>
       </c>
       <c r="H1154" t="n">
         <v>549822</v>
@@ -33951,7 +33951,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.48344421386719</v>
+        <v>2.48344397544861</v>
       </c>
       <c r="H1158" t="n">
         <v>166881</v>
@@ -34009,7 +34009,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1160" t="n">
         <v>154215</v>
@@ -34038,7 +34038,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1161" t="n">
         <v>154775</v>
@@ -34067,7 +34067,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1162" t="n">
         <v>148965</v>
@@ -34154,7 +34154,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1165" t="n">
         <v>148256</v>
@@ -34241,7 +34241,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.40296220779419</v>
+        <v>2.40296196937561</v>
       </c>
       <c r="H1168" t="n">
         <v>113023</v>
@@ -34270,7 +34270,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1169" t="n">
         <v>159196</v>
@@ -34444,7 +34444,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1175" t="n">
         <v>77116</v>
@@ -34502,7 +34502,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.31481528282166</v>
+        <v>2.31481504440308</v>
       </c>
       <c r="H1177" t="n">
         <v>289006</v>
@@ -34589,7 +34589,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1180" t="n">
         <v>124034</v>
@@ -34647,7 +34647,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.33780980110168</v>
+        <v>2.33781003952026</v>
       </c>
       <c r="H1182" t="n">
         <v>87462</v>
@@ -34705,7 +34705,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.33780980110168</v>
+        <v>2.33781003952026</v>
       </c>
       <c r="H1184" t="n">
         <v>68132</v>
@@ -34763,7 +34763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.39912962913513</v>
+        <v>2.39912986755371</v>
       </c>
       <c r="H1186" t="n">
         <v>171526</v>
@@ -34792,7 +34792,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.36846995353699</v>
+        <v>2.36846947669983</v>
       </c>
       <c r="H1187" t="n">
         <v>74015</v>
@@ -34821,7 +34821,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.42595672607422</v>
+        <v>2.42595720291138</v>
       </c>
       <c r="H1188" t="n">
         <v>131356</v>
@@ -34879,7 +34879,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1190" t="n">
         <v>56050</v>
@@ -34937,7 +34937,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1192" t="n">
         <v>36038</v>
@@ -34966,7 +34966,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1193" t="n">
         <v>38721</v>
@@ -34995,7 +34995,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1194" t="n">
         <v>286707</v>
@@ -35024,7 +35024,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1195" t="n">
         <v>112081</v>
@@ -35053,7 +35053,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.39146447181702</v>
+        <v>2.3914647102356</v>
       </c>
       <c r="H1196" t="n">
         <v>154795</v>
@@ -35082,7 +35082,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.38379955291748</v>
+        <v>2.38379979133606</v>
       </c>
       <c r="H1197" t="n">
         <v>56722</v>
@@ -35111,7 +35111,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.47961139678955</v>
+        <v>2.47961163520813</v>
       </c>
       <c r="H1198" t="n">
         <v>196742</v>
@@ -35140,7 +35140,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.41062688827515</v>
+        <v>2.41062712669373</v>
       </c>
       <c r="H1199" t="n">
         <v>350032</v>
@@ -35256,7 +35256,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1203" t="n">
         <v>110332</v>
@@ -35372,7 +35372,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27265787124634</v>
+        <v>2.27265810966492</v>
       </c>
       <c r="H1207" t="n">
         <v>253908</v>
@@ -35459,7 +35459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.37613463401794</v>
+        <v>2.37613487243652</v>
       </c>
       <c r="H1210" t="n">
         <v>130645</v>
@@ -35546,7 +35546,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1213" t="n">
         <v>269685</v>
@@ -35575,7 +35575,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.47577929496765</v>
+        <v>2.47577905654907</v>
       </c>
       <c r="H1214" t="n">
         <v>246638</v>
@@ -35662,7 +35662,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.3109827041626</v>
+        <v>2.31098294258118</v>
       </c>
       <c r="H1217" t="n">
         <v>451980</v>
@@ -35691,7 +35691,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.22283577919006</v>
+        <v>2.22283554077148</v>
       </c>
       <c r="H1218" t="n">
         <v>339921</v>
@@ -35778,7 +35778,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.20750594139099</v>
+        <v>2.20750617980957</v>
       </c>
       <c r="H1221" t="n">
         <v>142174</v>
@@ -35807,7 +35807,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.17301344871521</v>
+        <v>2.17301368713379</v>
       </c>
       <c r="H1222" t="n">
         <v>242902</v>
@@ -35865,7 +35865,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.06953692436218</v>
+        <v>2.0695366859436</v>
       </c>
       <c r="H1224" t="n">
         <v>397333</v>
@@ -35894,7 +35894,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.03887677192688</v>
+        <v>2.03887701034546</v>
       </c>
       <c r="H1225" t="n">
         <v>168729</v>
@@ -35923,7 +35923,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.98522210121155</v>
+        <v>1.98522222042084</v>
       </c>
       <c r="H1226" t="n">
         <v>131888</v>
@@ -35952,7 +35952,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.89707517623901</v>
+        <v>1.8970752954483</v>
       </c>
       <c r="H1227" t="n">
         <v>334235</v>
@@ -35981,7 +35981,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.9085727930069</v>
+        <v>1.90857267379761</v>
       </c>
       <c r="H1228" t="n">
         <v>240537</v>
@@ -36155,7 +36155,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.98138999938965</v>
+        <v>1.98138976097107</v>
       </c>
       <c r="H1234" t="n">
         <v>203810</v>
@@ -36271,7 +36271,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1238" t="n">
         <v>664061</v>
@@ -36329,7 +36329,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1240" t="n">
         <v>992861</v>
@@ -36358,7 +36358,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1241" t="n">
         <v>318659</v>
@@ -36387,7 +36387,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.71339249610901</v>
+        <v>2.71339273452759</v>
       </c>
       <c r="H1242" t="n">
         <v>459132</v>
@@ -36416,7 +36416,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.67506790161133</v>
+        <v>2.67506766319275</v>
       </c>
       <c r="H1243" t="n">
         <v>494900</v>
@@ -36445,7 +36445,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.6444079875946</v>
+        <v>2.64440822601318</v>
       </c>
       <c r="H1244" t="n">
         <v>355424</v>
@@ -36532,7 +36532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.74405217170715</v>
+        <v>2.74405241012573</v>
       </c>
       <c r="H1247" t="n">
         <v>450366</v>
@@ -36706,7 +36706,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1253" t="n">
         <v>729352</v>
@@ -36735,7 +36735,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087998390198</v>
       </c>
       <c r="H1254" t="n">
         <v>119317</v>
@@ -36938,7 +36938,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1261" t="n">
         <v>448800</v>
@@ -37054,7 +37054,7 @@
         <v>3.5</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.68273282051086</v>
+        <v>2.68273305892944</v>
       </c>
       <c r="H1265" t="n">
         <v>582306</v>
@@ -37083,7 +37083,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1266" t="n">
         <v>404158</v>
@@ -37112,7 +37112,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1267" t="n">
         <v>453222</v>
@@ -37228,7 +37228,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1271" t="n">
         <v>227438</v>
@@ -37257,7 +37257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1272" t="n">
         <v>280324</v>
@@ -37315,7 +37315,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.83603191375732</v>
+        <v>2.83603167533875</v>
       </c>
       <c r="H1274" t="n">
         <v>136480</v>
@@ -37373,7 +37373,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1276" t="n">
         <v>358795</v>
@@ -37402,7 +37402,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87052416801453</v>
+        <v>2.87052392959595</v>
       </c>
       <c r="H1277" t="n">
         <v>85060</v>
@@ -37460,7 +37460,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1279" t="n">
         <v>604084</v>
@@ -37489,7 +37489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1280" t="n">
         <v>254659</v>
@@ -37576,7 +37576,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.86285901069641</v>
+        <v>2.86285924911499</v>
       </c>
       <c r="H1283" t="n">
         <v>574210</v>
@@ -37605,7 +37605,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.78620982170105</v>
+        <v>2.78620958328247</v>
       </c>
       <c r="H1284" t="n">
         <v>230927</v>
@@ -37634,7 +37634,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1285" t="n">
         <v>165121</v>
@@ -37663,7 +37663,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1286" t="n">
         <v>364606</v>
@@ -37721,7 +37721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.71339249610901</v>
+        <v>2.71339273452759</v>
       </c>
       <c r="H1288" t="n">
         <v>215050</v>
@@ -37750,7 +37750,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1289" t="n">
         <v>357241</v>
@@ -37808,7 +37808,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1291" t="n">
         <v>279807</v>
@@ -37837,7 +37837,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.7708797454834</v>
+        <v>2.77087998390198</v>
       </c>
       <c r="H1292" t="n">
         <v>127030</v>
@@ -37895,7 +37895,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.82070207595825</v>
+        <v>2.82070183753967</v>
       </c>
       <c r="H1294" t="n">
         <v>128387</v>
@@ -37924,7 +37924,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87818908691406</v>
+        <v>2.87818932533264</v>
       </c>
       <c r="H1295" t="n">
         <v>278892</v>
@@ -37953,7 +37953,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.91651391983032</v>
+        <v>2.9165141582489</v>
       </c>
       <c r="H1296" t="n">
         <v>425681</v>
@@ -38011,7 +38011,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1298" t="n">
         <v>938387</v>
@@ -38040,7 +38040,7 @@
         <v>4</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1299" t="n">
         <v>272536</v>
@@ -38127,7 +38127,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.93567633628845</v>
+        <v>2.93567609786987</v>
       </c>
       <c r="H1302" t="n">
         <v>184353</v>
@@ -38156,7 +38156,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.99699592590332</v>
+        <v>2.9969961643219</v>
       </c>
       <c r="H1303" t="n">
         <v>311894</v>
@@ -38214,7 +38214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.84369683265686</v>
+        <v>2.84369707107544</v>
       </c>
       <c r="H1305" t="n">
         <v>141746</v>
@@ -38243,7 +38243,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.9203462600708</v>
+        <v>2.92034649848938</v>
       </c>
       <c r="H1306" t="n">
         <v>122098</v>
@@ -38272,7 +38272,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1307" t="n">
         <v>163152</v>
@@ -38301,7 +38301,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.96250367164612</v>
+        <v>2.96250343322754</v>
       </c>
       <c r="H1308" t="n">
         <v>124483</v>
@@ -38330,7 +38330,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1309" t="n">
         <v>851470</v>
@@ -38388,7 +38388,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1311" t="n">
         <v>333105</v>
@@ -38417,7 +38417,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1312" t="n">
         <v>318481</v>
@@ -38504,7 +38504,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.72872257232666</v>
+        <v>2.72872233390808</v>
       </c>
       <c r="H1315" t="n">
         <v>153154</v>
@@ -38562,7 +38562,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1317" t="n">
         <v>259106</v>
@@ -38620,7 +38620,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1319" t="n">
         <v>410062</v>
@@ -38678,7 +38678,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.70572757720947</v>
+        <v>2.70572781562805</v>
       </c>
       <c r="H1321" t="n">
         <v>275194</v>
@@ -38707,7 +38707,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.70956015586853</v>
+        <v>2.70956039428711</v>
       </c>
       <c r="H1322" t="n">
         <v>275948</v>
@@ -38794,7 +38794,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.69039797782898</v>
+        <v>2.6903977394104</v>
       </c>
       <c r="H1325" t="n">
         <v>410108</v>
@@ -38823,7 +38823,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.61758089065552</v>
+        <v>2.61758065223694</v>
       </c>
       <c r="H1326" t="n">
         <v>250248</v>
@@ -38881,7 +38881,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1328" t="n">
         <v>523941</v>
@@ -38968,7 +38968,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1331" t="n">
-        <v>2.62907814979553</v>
+        <v>2.62907838821411</v>
       </c>
       <c r="H1331" t="n">
         <v>129956</v>
@@ -38997,7 +38997,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1332" t="n">
-        <v>2.6559054851532</v>
+        <v>2.65590524673462</v>
       </c>
       <c r="H1332" t="n">
         <v>124651</v>
@@ -39026,7 +39026,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>2.71722507476807</v>
+        <v>2.71722531318665</v>
       </c>
       <c r="H1333" t="n">
         <v>642244</v>
@@ -39055,7 +39055,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1334" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1334" t="n">
         <v>268795</v>
@@ -39084,7 +39084,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1335" t="n">
         <v>669291</v>
@@ -39113,7 +39113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1336" t="n">
         <v>266103</v>
@@ -39142,7 +39142,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.7363874912262</v>
+        <v>2.73638772964478</v>
       </c>
       <c r="H1337" t="n">
         <v>148748</v>
@@ -39374,7 +39374,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1345" t="n">
         <v>248627</v>
@@ -39403,7 +39403,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.9663360118866</v>
+        <v>2.96633577346802</v>
       </c>
       <c r="H1346" t="n">
         <v>181306</v>
@@ -39432,7 +39432,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765583992004</v>
       </c>
       <c r="H1347" t="n">
         <v>196520</v>
@@ -39519,7 +39519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933100700378</v>
       </c>
       <c r="H1350" t="n">
         <v>126106</v>
@@ -39548,7 +39548,7 @@
         <v>4</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1351" t="n">
         <v>440591</v>
@@ -39664,7 +39664,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1355" t="n">
         <v>350615</v>
@@ -39751,7 +39751,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1358" t="n">
         <v>187366</v>
@@ -39780,7 +39780,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.27676677703857</v>
+        <v>3.27676653862</v>
       </c>
       <c r="H1359" t="n">
         <v>363222</v>
@@ -39809,7 +39809,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1360" t="n">
         <v>294112</v>
@@ -39838,7 +39838,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1361" t="n">
         <v>174283</v>
@@ -39867,7 +39867,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1362" t="n">
         <v>296147</v>
@@ -39896,7 +39896,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1363" t="n">
         <v>192510</v>
@@ -40012,7 +40012,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1367" t="n">
         <v>167546</v>
@@ -40128,7 +40128,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1371" t="n">
         <v>266113</v>
@@ -40157,7 +40157,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1372" t="n">
         <v>215125</v>
@@ -40244,7 +40244,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1375" t="n">
         <v>216825</v>
@@ -40273,7 +40273,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1376" t="n">
         <v>125022</v>
@@ -40331,7 +40331,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1378" t="n">
         <v>159804</v>
@@ -40360,7 +40360,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1379" t="n">
         <v>919643</v>
@@ -40389,7 +40389,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.28826403617859</v>
+        <v>3.28826379776001</v>
       </c>
       <c r="H1380" t="n">
         <v>310169</v>
@@ -40447,7 +40447,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.5412073135376</v>
+        <v>3.54120755195618</v>
       </c>
       <c r="H1382" t="n">
         <v>720088</v>
@@ -40476,7 +40476,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.56036996841431</v>
+        <v>3.56036972999573</v>
       </c>
       <c r="H1383" t="n">
         <v>247312</v>
@@ -40505,7 +40505,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.56420230865479</v>
+        <v>3.56420254707336</v>
       </c>
       <c r="H1384" t="n">
         <v>205143</v>
@@ -40534,7 +40534,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.53737497329712</v>
+        <v>3.53737473487854</v>
       </c>
       <c r="H1385" t="n">
         <v>247331</v>
@@ -40563,7 +40563,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.51054739952087</v>
+        <v>3.51054716110229</v>
       </c>
       <c r="H1386" t="n">
         <v>316680</v>
@@ -40592,7 +40592,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.39557337760925</v>
+        <v>3.39557313919067</v>
       </c>
       <c r="H1387" t="n">
         <v>935373</v>
@@ -40621,7 +40621,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.33425354957581</v>
+        <v>3.33425378799438</v>
       </c>
       <c r="H1388" t="n">
         <v>400605</v>
@@ -40708,7 +40708,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1391" t="n">
         <v>184876</v>
@@ -40737,7 +40737,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.33042120933533</v>
+        <v>3.33042097091675</v>
       </c>
       <c r="H1392" t="n">
         <v>314803</v>
@@ -40766,7 +40766,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.31892371177673</v>
+        <v>3.31892395019531</v>
       </c>
       <c r="H1393" t="n">
         <v>211919</v>
@@ -40795,7 +40795,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1394" t="n">
         <v>384891</v>
@@ -40882,7 +40882,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1397" t="n">
         <v>183307</v>
@@ -40911,7 +40911,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1398" t="n">
         <v>112518</v>
@@ -40940,7 +40940,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.21927928924561</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1399" t="n">
         <v>295169</v>
@@ -40969,7 +40969,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1400" t="n">
         <v>213421</v>
@@ -41027,7 +41027,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1402" t="n">
         <v>186824</v>
@@ -41056,7 +41056,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1403" t="n">
         <v>236837</v>
@@ -41085,7 +41085,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1404" t="n">
         <v>114681</v>
@@ -41114,7 +41114,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1405" t="n">
         <v>245941</v>
@@ -41143,7 +41143,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1406" t="n">
         <v>210201</v>
@@ -41201,7 +41201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1408" t="n">
         <v>69983</v>
@@ -41259,7 +41259,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1410" t="n">
         <v>178327</v>
@@ -41288,7 +41288,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1411" t="n">
         <v>170666</v>
@@ -41317,7 +41317,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.07747769355774</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1412" t="n">
         <v>221901</v>
@@ -41404,7 +41404,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.14646220207214</v>
+        <v>3.14646244049072</v>
       </c>
       <c r="H1415" t="n">
         <v>92805</v>
@@ -41549,7 +41549,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.08131003379822</v>
+        <v>3.0813102722168</v>
       </c>
       <c r="H1420" t="n">
         <v>108491</v>
@@ -41578,7 +41578,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.07747769355774</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1421" t="n">
         <v>39418</v>
@@ -41636,7 +41636,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1423" t="n">
         <v>123011</v>
@@ -41694,7 +41694,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.24610662460327</v>
+        <v>3.24610686302185</v>
       </c>
       <c r="H1425" t="n">
         <v>182882</v>
@@ -41723,7 +41723,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.25377178192139</v>
+        <v>3.25377154350281</v>
       </c>
       <c r="H1426" t="n">
         <v>193950</v>
@@ -41752,7 +41752,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1427" t="n">
         <v>123787</v>
@@ -41781,7 +41781,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1428" t="n">
         <v>275646</v>
@@ -41810,7 +41810,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.15795993804932</v>
+        <v>3.15795969963074</v>
       </c>
       <c r="H1429" t="n">
         <v>95971</v>
@@ -41868,7 +41868,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1431" t="n">
         <v>199731</v>
@@ -41897,7 +41897,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1432" t="n">
         <v>161220</v>
@@ -42013,7 +42013,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1436" t="n">
         <v>177399</v>
@@ -42071,7 +42071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.02765536308289</v>
+        <v>3.02765583992004</v>
       </c>
       <c r="H1438" t="n">
         <v>232582</v>
@@ -42100,7 +42100,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.98166608810425</v>
+        <v>2.98166584968567</v>
       </c>
       <c r="H1439" t="n">
         <v>590692</v>
@@ -42216,7 +42216,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1443" t="n">
         <v>151117</v>
@@ -42332,7 +42332,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.8858540058136</v>
+        <v>2.88585424423218</v>
       </c>
       <c r="H1447" t="n">
         <v>350177</v>
@@ -42361,7 +42361,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1448" t="n">
         <v>367975</v>
@@ -42390,7 +42390,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.80153965950012</v>
+        <v>2.80153942108154</v>
       </c>
       <c r="H1449" t="n">
         <v>397419</v>
@@ -42506,7 +42506,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1453" t="n">
         <v>1621448</v>
@@ -42564,7 +42564,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1455" t="n">
         <v>118227</v>
@@ -42593,7 +42593,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91268110275269</v>
+        <v>2.91268134117126</v>
       </c>
       <c r="H1456" t="n">
         <v>226254</v>
@@ -42622,7 +42622,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.99699592590332</v>
+        <v>2.9969961643219</v>
       </c>
       <c r="H1457" t="n">
         <v>610266</v>
@@ -42738,7 +42738,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.07747769355774</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1461" t="n">
         <v>309712</v>
@@ -42796,7 +42796,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.11963534355164</v>
+        <v>3.11963510513306</v>
       </c>
       <c r="H1463" t="n">
         <v>245831</v>
@@ -42854,7 +42854,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1465" t="n">
         <v>296217</v>
@@ -42912,7 +42912,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.03148794174194</v>
+        <v>3.03148818016052</v>
       </c>
       <c r="H1467" t="n">
         <v>119381</v>
@@ -42970,7 +42970,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1469" t="n">
         <v>229173</v>
@@ -42999,7 +42999,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1470" t="n">
         <v>167749</v>
@@ -43028,7 +43028,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.08897542953491</v>
+        <v>3.08897519111633</v>
       </c>
       <c r="H1471" t="n">
         <v>311050</v>
@@ -43057,7 +43057,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.06981325149536</v>
+        <v>3.06981301307678</v>
       </c>
       <c r="H1472" t="n">
         <v>332716</v>
@@ -43086,7 +43086,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.06214785575867</v>
+        <v>3.06214809417725</v>
       </c>
       <c r="H1473" t="n">
         <v>159481</v>
@@ -43115,7 +43115,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1474" t="n">
         <v>198702</v>
@@ -43202,7 +43202,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1477" t="n">
         <v>1174979</v>
@@ -43289,7 +43289,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1480" t="n">
         <v>585959</v>
@@ -43434,7 +43434,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.94334125518799</v>
+        <v>2.94334101676941</v>
       </c>
       <c r="H1485" t="n">
         <v>218046</v>
@@ -43463,7 +43463,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681801795959</v>
       </c>
       <c r="H1486" t="n">
         <v>385290</v>
@@ -43550,7 +43550,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.21161437034607</v>
+        <v>3.21161460876465</v>
       </c>
       <c r="H1489" t="n">
         <v>399032</v>
@@ -43579,7 +43579,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.10813760757446</v>
+        <v>3.10813736915588</v>
       </c>
       <c r="H1490" t="n">
         <v>301508</v>
@@ -43608,7 +43608,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.10047268867493</v>
+        <v>3.10047292709351</v>
       </c>
       <c r="H1491" t="n">
         <v>141241</v>
@@ -43637,7 +43637,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1492" t="n">
         <v>256197</v>
@@ -43666,7 +43666,7 @@
         <v>4</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.06598019599915</v>
+        <v>3.06598043441772</v>
       </c>
       <c r="H1493" t="n">
         <v>170712</v>
@@ -43695,7 +43695,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.10430550575256</v>
+        <v>3.10430526733398</v>
       </c>
       <c r="H1494" t="n">
         <v>470480</v>
@@ -43724,7 +43724,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.03915309906006</v>
+        <v>3.03915286064148</v>
       </c>
       <c r="H1495" t="n">
         <v>302736</v>
@@ -43782,7 +43782,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.91651391983032</v>
+        <v>2.9165141582489</v>
       </c>
       <c r="H1497" t="n">
         <v>234286</v>
@@ -43811,7 +43811,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.84752917289734</v>
+        <v>2.84752941131592</v>
       </c>
       <c r="H1498" t="n">
         <v>505896</v>
@@ -43898,7 +43898,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.8513617515564</v>
+        <v>2.85136198997498</v>
       </c>
       <c r="H1501" t="n">
         <v>263324</v>
@@ -44014,7 +44014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.65207314491272</v>
+        <v>2.65207290649414</v>
       </c>
       <c r="H1505" t="n">
         <v>615078</v>
@@ -44043,7 +44043,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.74021983146667</v>
+        <v>2.74022006988525</v>
       </c>
       <c r="H1506" t="n">
         <v>191990</v>
@@ -44101,7 +44101,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.73255515098572</v>
+        <v>2.73255491256714</v>
       </c>
       <c r="H1508" t="n">
         <v>218675</v>
@@ -44130,7 +44130,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.79004216194153</v>
+        <v>2.79004240036011</v>
       </c>
       <c r="H1509" t="n">
         <v>131010</v>
@@ -44159,7 +44159,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.78237748146057</v>
+        <v>2.78237724304199</v>
       </c>
       <c r="H1510" t="n">
         <v>424497</v>
@@ -44362,7 +44362,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.89735126495361</v>
+        <v>2.89735150337219</v>
       </c>
       <c r="H1517" t="n">
         <v>354141</v>
@@ -44391,7 +44391,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1518" t="n">
         <v>361006</v>
@@ -44420,7 +44420,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.81303691864014</v>
+        <v>2.81303715705872</v>
       </c>
       <c r="H1519" t="n">
         <v>509062</v>
@@ -44449,7 +44449,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1520" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1520" t="n">
         <v>325474</v>
@@ -44507,7 +44507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.92801141738892</v>
+        <v>2.92801117897034</v>
       </c>
       <c r="H1522" t="n">
         <v>232989</v>
@@ -44565,7 +44565,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.97783350944519</v>
+        <v>2.97783327102661</v>
       </c>
       <c r="H1524" t="n">
         <v>362207</v>
@@ -44594,7 +44594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1525" t="n">
         <v>179741</v>
@@ -44623,7 +44623,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.95867085456848</v>
+        <v>2.95867109298706</v>
       </c>
       <c r="H1526" t="n">
         <v>156246</v>
@@ -44739,7 +44739,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1530" t="n">
         <v>467217</v>
@@ -44768,7 +44768,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1531" t="n">
         <v>229732</v>
@@ -44797,7 +44797,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.08514308929443</v>
+        <v>3.08514285087585</v>
       </c>
       <c r="H1532" t="n">
         <v>151799</v>
@@ -44855,7 +44855,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1534" t="n">
         <v>374707</v>
@@ -44884,7 +44884,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.21927928924561</v>
+        <v>3.21927905082703</v>
       </c>
       <c r="H1535" t="n">
         <v>639377</v>
@@ -44913,7 +44913,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.20011711120605</v>
+        <v>3.20011734962463</v>
       </c>
       <c r="H1536" t="n">
         <v>504076</v>
@@ -44942,7 +44942,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1537" t="n">
         <v>601285</v>
@@ -44971,7 +44971,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1538" t="n">
         <v>318781</v>
@@ -45000,7 +45000,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.16562485694885</v>
+        <v>3.16562509536743</v>
       </c>
       <c r="H1539" t="n">
         <v>647371</v>
@@ -45029,7 +45029,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1540" t="n">
         <v>383529</v>
@@ -45058,7 +45058,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1541" t="n">
         <v>164325</v>
@@ -45116,7 +45116,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.04681777954102</v>
+        <v>3.04681801795959</v>
       </c>
       <c r="H1543" t="n">
         <v>292809</v>
@@ -45145,7 +45145,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.12346744537354</v>
+        <v>3.12346720695496</v>
       </c>
       <c r="H1544" t="n">
         <v>157684</v>
@@ -45174,7 +45174,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.13113260269165</v>
+        <v>3.13113236427307</v>
       </c>
       <c r="H1545" t="n">
         <v>194223</v>
@@ -45290,7 +45290,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.17712211608887</v>
+        <v>3.17712235450745</v>
       </c>
       <c r="H1549" t="n">
         <v>251214</v>
@@ -45348,7 +45348,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.08131003379822</v>
+        <v>3.0813102722168</v>
       </c>
       <c r="H1551" t="n">
         <v>208252</v>
@@ -45464,7 +45464,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1555" t="n">
         <v>415471</v>
@@ -45551,7 +45551,7 @@
         <v>4.25</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1558" t="n">
         <v>301113</v>
@@ -45580,7 +45580,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1559" t="n">
         <v>412974</v>
@@ -45609,7 +45609,7 @@
         <v>4.25</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1560" t="n">
         <v>279714</v>
@@ -45696,7 +45696,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.18861985206604</v>
+        <v>3.18861961364746</v>
       </c>
       <c r="H1563" t="n">
         <v>304504</v>
@@ -45725,7 +45725,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.12729978561401</v>
+        <v>3.12730002403259</v>
       </c>
       <c r="H1564" t="n">
         <v>412281</v>
@@ -45754,7 +45754,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.20778155326843</v>
+        <v>3.20778203010559</v>
       </c>
       <c r="H1565" t="n">
         <v>975722</v>
@@ -45841,7 +45841,7 @@
         <v>4.25</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1568" t="n">
         <v>500504</v>
@@ -45928,7 +45928,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.05065059661865</v>
+        <v>3.05065035820007</v>
       </c>
       <c r="H1571" t="n">
         <v>390077</v>
@@ -45957,7 +45957,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.98933124542236</v>
+        <v>2.98933100700378</v>
       </c>
       <c r="H1572" t="n">
         <v>634329</v>
@@ -45986,7 +45986,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.07747769355774</v>
+        <v>3.07747745513916</v>
       </c>
       <c r="H1573" t="n">
         <v>427181</v>
@@ -46015,7 +46015,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1574" t="n">
         <v>711393</v>
@@ -46044,7 +46044,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.13879728317261</v>
+        <v>3.13879752159119</v>
       </c>
       <c r="H1575" t="n">
         <v>411695</v>
@@ -46073,7 +46073,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.2307767868042</v>
+        <v>3.23077702522278</v>
       </c>
       <c r="H1576" t="n">
         <v>421250</v>
@@ -46102,7 +46102,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.22694420814514</v>
+        <v>3.22694444656372</v>
       </c>
       <c r="H1577" t="n">
         <v>314566</v>
@@ -46160,7 +46160,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.23844194412231</v>
+        <v>3.23844170570374</v>
       </c>
       <c r="H1579" t="n">
         <v>280568</v>
@@ -46189,7 +46189,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.20394968986511</v>
+        <v>3.20394945144653</v>
       </c>
       <c r="H1580" t="n">
         <v>262215</v>
@@ -46218,7 +46218,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.28443145751953</v>
+        <v>3.28443121910095</v>
       </c>
       <c r="H1581" t="n">
         <v>292250</v>
@@ -46247,7 +46247,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1582" t="n">
-        <v>3.22311210632324</v>
+        <v>3.22311162948608</v>
       </c>
       <c r="H1582" t="n">
         <v>154452</v>
@@ -46276,7 +46276,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.28059887886047</v>
+        <v>3.28059935569763</v>
       </c>
       <c r="H1583" t="n">
         <v>178783</v>
@@ -46305,7 +46305,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.27293419837952</v>
+        <v>3.27293395996094</v>
       </c>
       <c r="H1584" t="n">
         <v>174110</v>
@@ -46334,7 +46334,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.19245195388794</v>
+        <v>3.19245219230652</v>
       </c>
       <c r="H1585" t="n">
         <v>234986</v>
@@ -46363,7 +46363,7 @@
         <v>4.25</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.25760436058044</v>
+        <v>3.25760412216187</v>
       </c>
       <c r="H1586" t="n">
         <v>154125</v>
@@ -46392,7 +46392,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.2652690410614</v>
+        <v>3.26526927947998</v>
       </c>
       <c r="H1587" t="n">
         <v>169227</v>
@@ -46450,7 +46450,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.36491346359253</v>
+        <v>3.36491322517395</v>
       </c>
       <c r="H1589" t="n">
         <v>186298</v>
@@ -46508,7 +46508,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.41856837272644</v>
+        <v>3.41856813430786</v>
       </c>
       <c r="H1591" t="n">
         <v>408839</v>
@@ -46537,7 +46537,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.42240071296692</v>
+        <v>3.4224009513855</v>
       </c>
       <c r="H1592" t="n">
         <v>323923</v>
@@ -46595,7 +46595,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.33425354957581</v>
+        <v>3.33425378799438</v>
       </c>
       <c r="H1594" t="n">
         <v>214421</v>
@@ -46653,7 +46653,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.42240071296692</v>
+        <v>3.4224009513855</v>
       </c>
       <c r="H1596" t="n">
         <v>153963</v>
@@ -46682,7 +46682,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.5028829574585</v>
+        <v>3.50288271903992</v>
       </c>
       <c r="H1597" t="n">
         <v>291846</v>
@@ -46827,7 +46827,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.56420230865479</v>
+        <v>3.56420254707336</v>
       </c>
       <c r="H1602" t="n">
         <v>309642</v>
@@ -46856,7 +46856,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.54887223243713</v>
+        <v>3.54887247085571</v>
       </c>
       <c r="H1603" t="n">
         <v>187426</v>
@@ -46885,7 +46885,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.52204513549805</v>
+        <v>3.52204489707947</v>
       </c>
       <c r="H1604" t="n">
         <v>186150</v>
@@ -46972,7 +46972,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.5067150592804</v>
+        <v>3.50671482086182</v>
       </c>
       <c r="H1607" t="n">
         <v>142915</v>
@@ -47001,7 +47001,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.54887223243713</v>
+        <v>3.54887247085571</v>
       </c>
       <c r="H1608" t="n">
         <v>166419</v>
@@ -47030,7 +47030,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.46072506904602</v>
+        <v>3.46072554588318</v>
       </c>
       <c r="H1609" t="n">
         <v>338152</v>
@@ -47146,7 +47146,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.29209661483765</v>
+        <v>3.29209637641907</v>
       </c>
       <c r="H1613" t="n">
         <v>656275</v>
@@ -47233,7 +47233,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1616" t="n">
         <v>826619</v>
@@ -47349,7 +47349,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.40177273750305</v>
+        <v>3.40177249908447</v>
       </c>
       <c r="H1620" t="n">
         <v>184041</v>
@@ -47378,7 +47378,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1621" t="n">
         <v>194836</v>
@@ -47436,7 +47436,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.30147433280945</v>
+        <v>3.30147457122803</v>
       </c>
       <c r="H1623" t="n">
         <v>155525</v>
@@ -47465,7 +47465,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.26386260986328</v>
+        <v>3.26386284828186</v>
       </c>
       <c r="H1624" t="n">
         <v>184608</v>
@@ -47523,7 +47523,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.33072781562805</v>
+        <v>3.33072805404663</v>
       </c>
       <c r="H1626" t="n">
         <v>136171</v>
@@ -47581,7 +47581,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.36416101455688</v>
+        <v>3.36416077613831</v>
       </c>
       <c r="H1628" t="n">
         <v>90572</v>
@@ -47639,7 +47639,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.36834001541138</v>
+        <v>3.36834025382996</v>
       </c>
       <c r="H1630" t="n">
         <v>441762</v>
@@ -47813,7 +47813,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.25968408584595</v>
+        <v>3.25968384742737</v>
       </c>
       <c r="H1636" t="n">
         <v>115170</v>
@@ -47900,7 +47900,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.07580423355103</v>
+        <v>3.07580399513245</v>
       </c>
       <c r="H1639" t="n">
         <v>209765</v>
@@ -47929,7 +47929,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1640" t="n">
         <v>210448</v>
@@ -48045,7 +48045,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1644" t="n">
         <v>388116</v>
@@ -48335,7 +48335,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.90446186065674</v>
+        <v>2.90446162223816</v>
       </c>
       <c r="H1654" t="n">
         <v>96343</v>
@@ -48393,7 +48393,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78326821327209</v>
+        <v>2.78326845169067</v>
       </c>
       <c r="H1656" t="n">
         <v>290500</v>
@@ -48480,7 +48480,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.0883412361145</v>
+        <v>3.08834147453308</v>
       </c>
       <c r="H1659" t="n">
         <v>188155</v>
@@ -48625,7 +48625,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.96296882629395</v>
+        <v>2.96296906471252</v>
       </c>
       <c r="H1664" t="n">
         <v>85037</v>
@@ -49002,7 +49002,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1677" t="n">
         <v>141377</v>
@@ -49118,7 +49118,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.14684844017029</v>
+        <v>3.14684867858887</v>
       </c>
       <c r="H1681" t="n">
         <v>121914</v>
@@ -49205,7 +49205,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.20953488349915</v>
+        <v>3.20953464508057</v>
       </c>
       <c r="H1684" t="n">
         <v>173010</v>
@@ -49408,7 +49408,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.95043158531189</v>
+        <v>2.95043182373047</v>
       </c>
       <c r="H1691" t="n">
         <v>76345</v>
@@ -49437,7 +49437,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.95461082458496</v>
+        <v>2.95461106300354</v>
       </c>
       <c r="H1692" t="n">
         <v>112148</v>
@@ -49466,7 +49466,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1693" t="n">
         <v>78414</v>
@@ -49872,7 +49872,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.74983596801758</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H1707" t="n">
         <v>130433</v>
@@ -49901,7 +49901,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.69968700408936</v>
+        <v>2.69968676567078</v>
       </c>
       <c r="H1708" t="n">
         <v>1264562</v>
@@ -49959,7 +49959,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1710" t="n">
         <v>271736</v>
@@ -50104,7 +50104,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1715" t="n">
         <v>395509</v>
@@ -50133,7 +50133,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.29013681411743</v>
+        <v>2.29013705253601</v>
       </c>
       <c r="H1716" t="n">
         <v>386802</v>
@@ -50249,7 +50249,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1720" t="n">
         <v>157033</v>
@@ -50278,7 +50278,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.26924133300781</v>
+        <v>2.26924157142639</v>
       </c>
       <c r="H1721" t="n">
         <v>215090</v>
@@ -50307,7 +50307,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.23998808860779</v>
+        <v>2.23998785018921</v>
       </c>
       <c r="H1722" t="n">
         <v>166709</v>
@@ -50336,7 +50336,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1723" t="n">
         <v>163103</v>
@@ -50568,7 +50568,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>2.22745060920715</v>
+        <v>2.22745037078857</v>
       </c>
       <c r="H1731" t="n">
         <v>234021</v>
@@ -50597,7 +50597,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1732" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1732" t="n">
         <v>115131</v>
@@ -50626,7 +50626,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1733" t="n">
         <v>131798</v>
@@ -50684,7 +50684,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1735" t="n">
         <v>172469</v>
@@ -50858,7 +50858,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.51998615264893</v>
+        <v>2.5199863910675</v>
       </c>
       <c r="H1741" t="n">
         <v>649724</v>
@@ -50945,7 +50945,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.57013535499573</v>
+        <v>2.57013511657715</v>
       </c>
       <c r="H1744" t="n">
         <v>319932</v>
@@ -50974,7 +50974,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1745" t="n">
         <v>149411</v>
@@ -51061,7 +51061,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1748" t="n">
         <v>394081</v>
@@ -51090,7 +51090,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1749" t="n">
         <v>280050</v>
@@ -51119,7 +51119,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.58685159683228</v>
+        <v>2.5868513584137</v>
       </c>
       <c r="H1750" t="n">
         <v>233347</v>
@@ -51177,7 +51177,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.55759811401367</v>
+        <v>2.55759787559509</v>
       </c>
       <c r="H1752" t="n">
         <v>185533</v>
@@ -51235,7 +51235,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.62864232063293</v>
+        <v>2.62864255905151</v>
       </c>
       <c r="H1754" t="n">
         <v>261004</v>
@@ -51293,7 +51293,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1756" t="n">
         <v>119541</v>
@@ -51351,7 +51351,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.70386552810669</v>
+        <v>2.70386576652527</v>
       </c>
       <c r="H1758" t="n">
         <v>241900</v>
@@ -51409,7 +51409,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.72058248519897</v>
+        <v>2.7205822467804</v>
       </c>
       <c r="H1760" t="n">
         <v>266940</v>
@@ -51641,7 +51641,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.71222424507141</v>
+        <v>2.71222400665283</v>
       </c>
       <c r="H1768" t="n">
         <v>103137</v>
@@ -51699,7 +51699,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.70386552810669</v>
+        <v>2.70386576652527</v>
       </c>
       <c r="H1770" t="n">
         <v>182873</v>
@@ -51786,7 +51786,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.59938859939575</v>
+        <v>2.59938883781433</v>
       </c>
       <c r="H1773" t="n">
         <v>393315</v>
@@ -51815,7 +51815,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.64953780174255</v>
+        <v>2.64953804016113</v>
       </c>
       <c r="H1774" t="n">
         <v>106028</v>
@@ -51844,7 +51844,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.58267259597778</v>
+        <v>2.5826723575592</v>
       </c>
       <c r="H1775" t="n">
         <v>230178</v>
@@ -51873,7 +51873,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1776" t="n">
         <v>215923</v>
@@ -51931,7 +51931,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.61610507965088</v>
+        <v>2.61610531806946</v>
       </c>
       <c r="H1778" t="n">
         <v>44718</v>
@@ -51989,7 +51989,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.59103059768677</v>
+        <v>2.59103083610535</v>
       </c>
       <c r="H1780" t="n">
         <v>86913</v>
@@ -52279,7 +52279,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.73729872703552</v>
+        <v>2.73729848861694</v>
       </c>
       <c r="H1790" t="n">
         <v>107038</v>
@@ -52337,7 +52337,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.77073121070862</v>
+        <v>2.7707314491272</v>
       </c>
       <c r="H1792" t="n">
         <v>160766</v>
@@ -52424,7 +52424,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.81670117378235</v>
+        <v>2.81670093536377</v>
       </c>
       <c r="H1795" t="n">
         <v>143387</v>
@@ -52482,7 +52482,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.81670117378235</v>
+        <v>2.81670093536377</v>
       </c>
       <c r="H1797" t="n">
         <v>146684</v>
@@ -52540,7 +52540,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.89192461967468</v>
+        <v>2.8919243812561</v>
       </c>
       <c r="H1799" t="n">
         <v>296181</v>
@@ -52598,7 +52598,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.62864232063293</v>
+        <v>2.62864255905151</v>
       </c>
       <c r="H1801" t="n">
         <v>850615</v>
@@ -52772,7 +52772,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.36118125915527</v>
+        <v>2.36118102073669</v>
       </c>
       <c r="H1807" t="n">
         <v>314978</v>
@@ -52801,7 +52801,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1808" t="n">
         <v>588277</v>
@@ -52888,7 +52888,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1811" t="n">
         <v>336694</v>
@@ -53120,7 +53120,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.32356953620911</v>
+        <v>2.32356929779053</v>
       </c>
       <c r="H1819" t="n">
         <v>237689</v>
@@ -53497,7 +53497,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.37371850013733</v>
+        <v>2.37371826171875</v>
       </c>
       <c r="H1832" t="n">
         <v>440369</v>
@@ -53642,7 +53642,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.2734203338623</v>
+        <v>2.27342057228088</v>
       </c>
       <c r="H1837" t="n">
         <v>394668</v>
@@ -53787,7 +53787,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1842" t="n">
         <v>375724</v>
@@ -53845,7 +53845,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.28595757484436</v>
+        <v>2.28595781326294</v>
       </c>
       <c r="H1844" t="n">
         <v>131363</v>
@@ -54309,7 +54309,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.4405837059021</v>
+        <v>2.44058394432068</v>
       </c>
       <c r="H1860" t="n">
         <v>158968</v>
@@ -54454,7 +54454,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.48237442970276</v>
+        <v>2.48237466812134</v>
       </c>
       <c r="H1865" t="n">
         <v>433044</v>
@@ -54483,7 +54483,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.44476270675659</v>
+        <v>2.44476294517517</v>
       </c>
       <c r="H1866" t="n">
         <v>307676</v>
@@ -54512,7 +54512,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.4113302230835</v>
+        <v>2.41132998466492</v>
       </c>
       <c r="H1867" t="n">
         <v>276802</v>
@@ -80209,9 +80209,38 @@
         <v>3.8050000667572</v>
       </c>
       <c r="H2753" t="n">
-        <v>97054</v>
+        <v>97484</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>3.67499995231628</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>3.67000007629395</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>116299</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
